--- a/strategy/ig-content-strategy.xlsx
+++ b/strategy/ig-content-strategy.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="890" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="958" uniqueCount="462">
   <si>
     <t xml:space="preserve">Luxury Beauty by Cleo R</t>
   </si>
@@ -45,7 +45,7 @@
     <t xml:space="preserve">Tuesday</t>
   </si>
   <si>
-    <t xml:space="preserve">Reel or video. Cross-post to TikTok and Facebook Reels.</t>
+    <t xml:space="preserve">Single image with a strong hook. Cross-post to Facebook and TikTok.</t>
   </si>
   <si>
     <t xml:space="preserve">Thursday</t>
@@ -60,7 +60,7 @@
     <t xml:space="preserve">Saturday</t>
   </si>
   <si>
-    <t xml:space="preserve">Quote, testimonial, or engagement post. Cross-post to FB and TikTok.</t>
+    <t xml:space="preserve">Quote, testimonial, or engagement image. Cross-post to FB and TikTok.</t>
   </si>
   <si>
     <t xml:space="preserve">HOW TO WORK THIS SHEET</t>
@@ -75,7 +75,13 @@
     <t xml:space="preserve">2. Design</t>
   </si>
   <si>
-    <t xml:space="preserve">Ask Claude to build any carousel from its row. Week 1 Monday is already done.</t>
+    <t xml:space="preserve">Ask Claude to build any post from its row. Week 1 Monday is already done.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2b. Files</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every post has its own folder in the repo. Click its Folder Link for the brief and final images.</t>
   </si>
   <si>
     <t xml:space="preserve">3. Track</t>
@@ -159,6 +165,9 @@
     <t xml:space="preserve">Visual / Asset</t>
   </si>
   <si>
+    <t xml:space="preserve">Folder Link</t>
+  </si>
+  <si>
     <t xml:space="preserve">Status</t>
   </si>
   <si>
@@ -207,7 +216,10 @@
     <t xml:space="preserve">Set A</t>
   </si>
   <si>
-    <t xml:space="preserve">READY: 8 slides in repo (design/renders/botox-myths)</t>
+    <t xml:space="preserve">READY: 8 final slides in this post's folder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-08-17-5-botox-lies-you-still</t>
   </si>
   <si>
     <t xml:space="preserve">Ready</t>
@@ -216,874 +228,1069 @@
     <t xml:space="preserve">Tue</t>
   </si>
   <si>
-    <t xml:space="preserve">Reel / Video</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IG Reels + TikTok + FB Reels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POV: Your First Botox Consult | Walk through what actually happens, no surprises.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No pressure, no judgment, just a plan. This is what a real consultation looks like. 🎥 Sound on.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Book yours. Link in bio</t>
+    <t xml:space="preserve">Single Image</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IG + FB + TikTok photo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Spotlight: Botox | Smooth, not frozen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Softened lines, full expression, and nobody can tell why you look so rested. That is Botox done right. ✨</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DM BOTOX to book</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single image: treatment photo + hook overlay in brand style</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-08-18-service-spotlight-botox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Idea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trust &amp; Proof</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 Red Flags at a Med Spa. Run. | Your face deserves better than a bargain.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A menu with no consultation, prices too good to be true, and nobody asking about your medical history. If you see these, walk away. Save this checklist before you book anywhere. 💛</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Save this checklist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Design in editorial template (sequel to Choosing the Right NP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-08-20-5-red-flags-at-a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personality &amp; BTS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Behind the Scenes: The Prep | Zero shortcuts. Ever.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sealed products, precise dosing, clean everything. This is the part you never see, and the part that matters most. 💛</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Book with confidence. Link in bio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single image: prep tray photo + hook overlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-08-21-behind-the-scenes-the-prep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quote: Great Work Is Invisible | Brand quote card.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Great work is invisible. Bad work is what gave Botox its reputation. Agree or disagree? 👇</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comment below</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quote card in editorial brand style</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-08-22-quote-great-work-is-invisible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your First Visit, Step by Step | Nervous about your first appointment? Here is exactly what happens.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80 percent of first-timers tell me they waited years because they did not know what to expect. Consider this your preview. Send it to the friend who keeps saying one day.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Book your consult. Link in bio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Design in editorial template + treatment room photos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-08-24-your-first-visit-step-by</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 Signs Your Injector Is Rushing You | Protect yourself before you book.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If your consult is shorter than your coffee order, that is a problem. Save this checklist and trust your gut.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Save + share this</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single image: 3-point checklist card in brand style</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-08-25-3-signs-your-injector-is</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meet NP Cleo: The Face Behind the Glow | Real education. Real results. Real care.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Before you trust someone with your face, you should know who they are. Here is my story, my training, and why I will always tell you the truth about what you need. 💛</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Say hi in the comments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portrait photos of Cleo (reuse cleo.png + new shots)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-08-27-meet-np-cleo-the-face</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Welcome to the Treatment Room | Where calm meets careful.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clean, quiet, and designed for you to feel safe asking anything. Come see it in person. 💛</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Book a visit. Link in bio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single image: treatment room photo + hook</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-08-28-welcome-to-the-treatment-room</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This or That: Rested vs Frozen | Engagement post.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When you picture your results, which one are you actually asking for? Vote below. 👇</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vote in the comments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two-panel comparison card in brand style</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-08-29-this-or-that-rested-vs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preventative Botox: When to Actually Start | Your friend who never seems to age? This is why.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lines are easier to prevent than to erase. Here is how to know if your late 20s or 30s is the right time to start, and when it is genuinely too early.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DM PREVENT for a consult</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Design in editorial template</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-08-31-preventative-botox-when-to-actually</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Botox Education Month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Spotlight: Preventative Botox | Start before the lines do.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The friend who never seems to age did not find a miracle cream. She started early and kept it subtle.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DM PREVENT to talk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single image: young client or product photo + hook</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-01-service-spotlight-preventative-botox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What 20 Units Actually Looks Like | Unit math, finally explained.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You have seen the price per unit. But what does 20 units actually do? Here is the honest breakdown of dosing, areas, and why cheaper per unit is not cheaper overall.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Save this for your consult</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Design in editorial template + dosing diagram</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-03-what-20-units-actually-looks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meet Your Injector | Board certified. Botox obsessed. Brutally honest.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your face deserves a nurse practitioner who tells the truth about what you need and what you do not. Hi, I am Cleo. 💛</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single image: Cleo portrait + credentials hook</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-04-meet-your-injector</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quote: Prevention Beats Erasing | Brand quote card.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lines are easier to prevent than to erase. Save this reminder. ✨</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Save this</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quote card in brand style</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-05-quote-prevention-beats-erasing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Botox vs Dysport: The Real Difference | Same family. Different personalities.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The most Googled question in aesthetics, answered honestly. Slide 5 explains why you should never compare prices unit to unit. Save this for later. ✨</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Book a consult. Link in bio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-07-botox-vs-dysport-the-real</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Botox vs Dysport at a Glance | Same family. Different personalities.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dysport kicks in faster and spreads wider. Botox is precise. The right one depends on your face, not the price list.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full breakdown on our feed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single image: side-by-side comparison card</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-08-botox-vs-dysport-at-a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Botox Aftercare: The First 48 Hours | You got Botox. Now what?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The first 48 hours matter more than most people think. Here is exactly what to do, what to skip, and when to call me. Bookmark this one.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Save this guide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-10-botox-aftercare-the-first-48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Face Map | Every face gets a plan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nothing touches your skin before I map your anatomy, your movement, and your goals. Planning is the treatment.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Book your mapping. Link in bio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single image: assessment photo + hook</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-11-the-face-map</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ: Does Botox Hurt? | Honest answer, no fluff.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The honest answer: less than plucking a brow. Tiny needle, seconds per area, numbing if you want it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">More questions? DM me</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ card in brand style</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-12-faq-does-botox-hurt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 Things Botox Can't Do | Honest expectations, always.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Botox is amazing at what it does. But it cannot do everything, and anyone who says otherwise is selling you something. Here is what it fixes and what needs a different plan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comment your questions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-14-5-things-botox-can-t</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What Botox Can't Fix | Honest expectations, always.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sagging skin, volume loss, texture. Botox is not the tool for everything, and I will always tell you what is.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single image: myth-vs-reality card</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-15-what-botox-can-t-fix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Still You, Just Refreshed | You won't look done. You'll look rested.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The 2026 standard is not transformation. It is restoration. My goal is that people ask if you have been on vacation, not what you had done. 💛</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DM GLOW to start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Template exists (design/slides.html), needs photos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-17-still-you-just-refreshed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Myth vs Truth: The Frozen Face | The classic fear, debunked.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYTH: Botox freezes your face. TRUTH: correct dosing softens movement while you keep every expression that makes you, you.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share with a friend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single image: myth vs truth split card</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-18-myth-vs-truth-the-frozen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Client Words: Natural Results | Testimonial card.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nobody could tell. They just kept saying I looked happy and rested. That is the whole goal. 💛 (Shared with permission.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your turn. Link in bio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Testimonial quote card (with consent)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-19-client-words-natural-results</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Botox or Filler? You Might Be Asking for the Wrong One | Lines or volume? They are not the same problem.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Half the DMs I get ask for the wrong treatment. Here is the simple way to know whether your concern is about movement or volume, and what that means for your plan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DM CONSULT and I will help</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-21-botox-or-filler-you-might</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lines vs Volume | Which one is your concern?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smile in the mirror. Movement lines need Botox. Lost volume needs filler. The answer decides your plan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DM CONSULT for help</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single image: two-column explainer card</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-22-lines-vs-volume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ask NP Cleo: Your Questions, Answered Honestly | You asked. I answered. No filter.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This month you sent amazing questions. Here are the honest answers, including the one nobody else will give you about cheap Botox. Keep them coming. 👇</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drop your question below</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Design Q&amp;A layout from real DM questions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-24-ask-np-cleo-your-questions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your DMs, Answered | The question everyone asks quietly.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You asked: will people know I had work done? Honest answer: only if you want them to. Subtle is the standard here.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Send your question</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single image: Q&amp;A card in brand style</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-25-your-dms-answered</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Poll: What Should NP Cleo Cover Next? | Audience chooses next month's content.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">October is filler month. What do you want the truth about first: lips, cheeks, or under eyes? Vote. 👇</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vote in comments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Poll card + matching story poll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-26-poll-what-should-np-cleo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How Long Does Botox Really Last? | The honest timeline, month by month.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anyone promising six months is overpromising. Here is the real timeline, what makes it fade faster, and how to make results last longer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Save this timeline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Design timeline layout in editorial template</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-28-how-long-does-botox-really</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The 3-Month Botox Timeline | Week by week, what to expect.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Day 3 it starts. Week 2 it settles. Month 3 it softens. Save this so you know exactly what is normal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single image: timeline infographic card</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-29-the-3-month-botox-timeline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fillers, Naturally</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Why We Sometimes Say No | A provider who says yes to everyone is a red flag.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I have turned people away, and they thanked me later. Here is why honest candidacy matters and what it says about any provider who never says no.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Book an honest consult</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-01-why-we-sometimes-say-no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What I Tell Every First-Timer | The pep talk before every first appointment.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You do not need to know the treatment names. You just need to show up honest about your goals. I handle the rest. 💛</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Book your first visit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single image: Cleo photo + quote overlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-02-what-i-tell-every-first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quote: No Is Protection | Brand quote card.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An honest provider will sometimes tell you no. That is protection, not rejection. ✨</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share this</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-03-quote-no-is-protection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filler Won't Make You Look Fake. Bad Technique Does. | The fear is real. The cause is not what you think.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every overdone face you have seen came from heavy hands, not from filler itself. Great work is invisible. You have seen it a hundred times without knowing. ✨</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DM FILLER for a consult</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Design in editorial template. October filler month opener</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-05-filler-won-t-make-you</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Spotlight: Dermal Filler | Volume where you lost it. Nowhere else.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filler is not about changing your face. It is about restoring what time quietly took. October is filler month. 👀</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DM FILLER to start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single image: filler product or treatment photo + hook</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-06-service-spotlight-dermal-filler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lip Filler: Natural vs Overdone | The difference is the injector.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soft, balanced, still you. Here is what separates natural lip results from the duck lips everyone fears, and the questions to ask before anyone touches your lips.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Save before you book anywhere</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Design in editorial template + consented lip photos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-08-lip-filler-natural-vs-overdone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inside the Filler Appointment | Planned to the last drop.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cannulas, numbing, and a plan drawn before we start. This is what careful looks like.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Follow for filler month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single image: filler prep photo + hook</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-09-inside-the-filler-appointment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quote: Subtle Is the New Dramatic | Brand quote card.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subtle is the new dramatic. The best work whispers. 💛</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-10-quote-subtle-is-the-new</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cheek Filler: The Secret Nobody Talks About | The treatment behind the best natural glow-ups.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Everyone asks about lips. But cheek filler is quietly behind some of the most natural transformations you have seen. Here is how facial balancing works.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DM CHEEKS to learn more</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-12-cheek-filler-the-secret-nobody</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Spotlight: Cheek Filler | The lift nobody talks about.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lifted, refreshed, never puffy. Cheek filler is quietly behind the most natural glow-ups you have seen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single image: cheek treatment photo + hook</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-13-service-spotlight-cheek-filler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is Filler Right for You? An Honest Checklist | Not everyone is a candidate. Here is how to know.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An honest provider will sometimes tell you not yet. Run through this checklist before your consult and you will walk in knowing exactly what to ask.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-15-is-filler-right-for-you</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Facial Balancing 101 | One plan beats three syringes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One syringe in the right place beats three in the wrong ones. Balance first, volume second. Always.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Book a balancing consult</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single image: face-map diagram card</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-16-facial-balancing-101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ: How Much Filler Do I Need? | The honest answer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Less than Instagram makes you think. Most natural results start with one syringe or less. Here is why.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">More FAQs? DM me</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-17-faq-how-much-filler-do</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filler Dissolves. Here Is the Real Timeline. | What they do not tell you about longevity.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filler is not forever, and that is a feature, not a flaw. Here is how long each area really lasts and what maintenance actually looks like.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Book your plan. Link in bio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Design timeline layout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-19-filler-dissolves-here-is-the</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Filler Timeline | What happens as it fades.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filler does not vanish overnight and you will not deflate. It softens slowly, on a schedule you can plan around.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-20-the-filler-timeline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lip Filler Aftercare: Your First Week | Swelling is normal. Panic is optional.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Day 1 looks different from day 7. Here is the honest day-by-day so you know exactly what is normal and when to reach out. Save this before your appointment.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-22-lip-filler-aftercare-your-first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aftercare Essentials | Save this for after your appointment.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ice, no gym for 24 hours, sleep on your back, and message me with anything. That is it. Save this. ✨</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Save + share</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single image: 4-point checklist card</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-23-aftercare-essentials</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Client Words: The Lip Glow-Up | Testimonial card.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I finally got my lips done and nobody said filler. They said I looked prettier and could not say why. (Shared with permission.) 💛</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your turn. DM FILLER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Testimonial card (with consent)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-24-client-words-the-lip-glow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 Filler Lies You Still Believe | The sequel you asked for.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You loved the Botox edition, so here is the filler truth round. Slide 4 is the one that surprises everyone. Share it with your group chat. ✨</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Design in editorial template. Sequel to Botox lies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-26-5-filler-lies-you-still</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Myth vs Truth: Filler Edition | The one everyone believes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYTH: filler stretches your lips forever. TRUTH: treated well, your lips return to baseline as filler softens.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full carousel on our feed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-27-myth-vs-truth-filler-edition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Facial Balancing: Why We Treat Faces, Not Lines | Chasing lines is old school.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Great aesthetics looks at the whole face: proportions, balance, harmony. Here is why the best results come from a plan, not a single syringe.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DM BALANCE for a consult</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-29-facial-balancing-why-we-treat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faces, Not Lines | The philosophy behind natural results.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chasing individual lines is old school. Balance and harmony are why my patients look rested instead of done.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single image: philosophy card + portrait</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-30-faces-not-lines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ask Anything: Filler Edition | Engagement post.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filler month is almost over. Drop every remaining question below and I will answer all of them. No judgment. 👇</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comment your question</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engagement card in brand style</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-31-ask-anything-filler-edition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rested by the Holidays</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Promo &amp; CTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rested by the Holidays: Your Treatment Timeline | Party season is closer than you think.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Botox needs 2 weeks to settle. Filler needs up to 4. If you want to glow in the December photos, here is exactly when to book each treatment. 🗓️</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Book now. Link in bio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Design holiday timeline layout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-11-02-rested-by-the-holidays-your</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holiday Countdown: Book by These Dates | Work backwards from party season.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Botox needs 2 weeks. Filler needs 4. If you want to glow in the December photos, these are your deadlines. 🗓️</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single image: countdown-dates card</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-11-03-holiday-countdown-book-by-these</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Party Season Prep: What to Book and When | Your holiday glow, planned backwards.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Work back from your event date and nothing is rushed, nothing is swollen, and everything looks like you. Here is the smart booking order.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DM HOLIDAY to book</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-11-05-party-season-prep-what-to</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Clinic Is Holiday Ready | Glow-up season is officially open.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The calendar is filling and the season is here. Your December self will thank your November self. ✨</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Book your spot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single image: decorated clinic photo + hook</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-11-06-the-clinic-is-holiday-ready</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quote: Book the Appointment | Seasonal self-care push.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You cannot pour from an empty cup. Book the appointment. Take the hour. You have earned it. 💛</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Link in bio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-11-07-quote-book-the-appointment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Gift of Glow: Gift Certificates Are Here | The present nobody returns.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Give the people you love something they actually want. Luxury Beauty gift certificates are available in any amount, wrapped and ready. 🎁</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DM GIFT to order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Design gift certificate reveal layout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-11-09-the-gift-of-glow-gift</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gift Certificates Are Here | The present nobody returns.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In any amount, wrapped and beautiful. Give the people you love something they actually want. 🎁</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single image: gift certificate photo + hook</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-11-10-gift-certificates-are-here</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 Months of Honest Answers: The Recap | Real education. Real results. Thank you.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Since August we have busted myths, answered your questions, and kept every promise about natural results. Here are the posts you loved most, in case you missed one. 💛</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Follow for what is next</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compile top slides from past carousels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-11-12-3-months-of-honest-answers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thank You: 3 Months of Honest Aesthetics | Gratitude post.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Since August you have asked incredible questions and trusted us with the answers. Here is to honest aesthetics. Thank you. 💛</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single image: team or Cleo photo + thank you overlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-11-13-thank-you-3-months-of</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tag Someone Who Deserves a Glow-Up Gift | Engagement + promo close.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Know someone who never treats themselves? Tag them below. We will take care of the rest. 🎁</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tag a friend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-11-14-tag-someone-who-deserves-a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Theme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Goal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carousel Topics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reel / Syndication Focus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">August 17-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Launch the educational brand voice and post the finished Botox myths carousel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 Botox Lies (ready) / 5 Red Flags / First Visit / Meet NP Cleo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service spotlight cards, BTS prep photo, brand quote cards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">September</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Own every Botox question a first-timer Googles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preventative / 20 Units / Botox vs Dysport / Aftercare / What Botox Can't Do / Natural Promise / Botox or Filler / Ask Cleo / How Long It Lasts / Why We Say No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hook image cards: explainers, myth vs truth, FAQ, BTS photos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">October</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Convert filler fear into filler bookings with honesty-first education</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not Fake / Lips Natural vs Overdone / Cheek Filler / Candidacy Checklist / Dissolve Timeline / Lip Aftercare / 5 Filler Lies / Facial Balancing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service spotlight cards, testimonials, FAQ and checklist cards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">November 1-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create urgency: book now to glow for party season + launch gift certificates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holiday Timeline / Party Season Prep / Gift of Glow / 3-Month Recap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Countdown cards, holiday BTS photo, gift reveal, tag-a-friend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share of Posts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What It Is</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Success Metric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teach one thing per post: myths, comparisons, timelines, aftercare, candidacy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carousels, explainer image cards, FAQ cards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saves and shares</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Show honesty and results: testimonials, natural-results promise, why we say no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quote cards, testimonial posts, philosophy carousels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DMs and consults</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Humanize NP Cleo: day in the life, room tours, Q&amp;A, prep clips</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BTS photo posts, Q&amp;A cards, polls</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comments and follows</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direct booking pushes: seasonal timelines, gift certificates, offers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Countdown cards, promo carousels, engagement + tag posts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hashtags (copy-paste)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Botox Education</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#botox #botoxeducation #botoxmyths #preventativebotox #antiwrinkleinjections #nurseinjector #medspa #naturalbotox #botoxbeforeandafter #aestheticnurse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#dermalfiller #lipfiller #cheekfiller #naturalfiller #facialbalancing #lipfillernatural #aestheticnurse #medspa #fillerjourney #lipgoals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brand &amp; Trust</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#npinjector #nursepractitioner #medspalife #luxurybeauty #aestheticnurse #skincareexpert #beautyclinic #selfcare #naturalresults #honestbeauty</t>
   </si>
   <si>
     <t xml:space="preserve">Set D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Film 20-30s vertical walkthrough</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Idea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trust &amp; Proof</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 Red Flags at a Med Spa. Run. | Your face deserves better than a bargain.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A menu with no consultation, prices too good to be true, and nobody asking about your medical history. If you see these, walk away. Save this checklist before you book anywhere. 💛</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Save this checklist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Set C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Design in editorial template (sequel to Choosing the Right NP)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fri</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personality &amp; BTS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drawing Up Botox: Prep With Me | Satisfying behind-the-scenes prep.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clean hands, precise dosing, zero shortcuts. This is the part you never see. ✨</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Follow for more BTS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Film 15s ASMR-style prep clip</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quote / Engagement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IG + FB + TikTok photo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quote: Great Work Is Invisible | Brand quote card.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Great work is invisible. Bad work is what gave Botox its reputation. Agree or disagree? 👇</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comment below</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quote card in editorial brand style</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Your First Visit, Step by Step | Nervous about your first appointment? Here is exactly what happens.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80 percent of first-timers tell me they waited years because they did not know what to expect. Consider this your preview. Send it to the friend who keeps saying one day.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Book your consult. Link in bio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Design in editorial template + treatment room photos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 Signs Your Injector Is Rushing You | Protect yourself in 20 seconds.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">If your consult is shorter than your coffee order, that is a problem. Watch for these three signs.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Share to help a friend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Film 20s talking-head reel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meet NP Cleo: The Face Behind the Glow | Real education. Real results. Real care.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Before you trust someone with your face, you should know who they are. Here is my story, my training, and why I will always tell you the truth about what you need. 💛</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Say hi in the comments</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portrait photos of Cleo (reuse cleo.png + new shots)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Treatment Room Tour | Where the magic happens.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clean, calm, and designed for you to feel safe. Welcome to Luxury Beauty. Come see it in person. 💛</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Book a visit. Link in bio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Film 15-20s room tour with music</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This or That: Rested vs Frozen | Engagement post.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">When you picture your results, which one are you actually asking for? Vote below. 👇</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vote in the comments</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Two-panel graphic in brand style</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preventative Botox: When to Actually Start | Your friend who never seems to age? This is why.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lines are easier to prevent than to erase. Here is how to know if your late 20s or 30s is the right time to start, and when it is genuinely too early.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DM PREVENT for a consult</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Design in editorial template</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Botox Education Month</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Botox in Your 20s: The Truth | Preventative explained in 20 seconds.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Too early? Too late? Here is the honest answer about when preventative Botox makes sense.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DM PREVENT to talk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What 20 Units Actually Looks Like | Unit math, finally explained.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">You have seen the price per unit. But what does 20 units actually do? Here is the honest breakdown of dosing, areas, and why cheaper per unit is not cheaper overall.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Save this for your consult</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Design in editorial template + dosing diagram</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Day in the Life of a Nurse Injector | From first coffee to last consult.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The 6am start, the consults, the artistry, the aftercare texts. This is what your injector's day really looks like.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Follow along</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Film day-in-the-life montage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quote: Prevention Beats Erasing | Brand quote card.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lines are easier to prevent than to erase. Save this reminder. ✨</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Save this</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quote card in brand style</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Botox vs Dysport: The Real Difference | Same family. Different personalities.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The most Googled question in aesthetics, answered honestly. Slide 5 explains why you should never compare prices unit to unit. Save this for later. ✨</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Book a consult. Link in bio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Botox vs Dysport in 15 Seconds | The fastest honest comparison online.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Same family, different personalities. Here is the 15-second version of the most asked question in aesthetics.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Full breakdown on our feed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Film 15s quick-cut reel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Botox Aftercare: The First 48 Hours | You got Botox. Now what?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The first 48 hours matter more than most people think. Here is exactly what to do, what to skip, and when to call me. Bookmark this one.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Save this guide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How I Map Your Face | BTS: the assessment before a single unit.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Every face is different. Here is how I plan your treatment before anything touches your skin.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Book your mapping. Link in bio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Film 20-30s assessment BTS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FAQ: Does Botox Hurt? | Honest answer, no fluff.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The honest answer: less than plucking a brow. Here is what it actually feels like and how we keep you comfortable.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">More questions? DM me</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FAQ card or 10s clip</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 Things Botox Can't Do | Honest expectations, always.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Botox is amazing at what it does. But it cannot do everything, and anyone who says otherwise is selling you something. Here is what it fixes and what needs a different plan.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comment your questions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What Botox Can't Fix | Save this before your consult.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sagging skin, volume loss, texture. Botox is not the tool for everything. Here is what works instead.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Still You, Just Refreshed | You won't look done. You'll look rested.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The 2026 standard is not transformation. It is restoration. My goal is that people ask if you have been on vacation, not what you had done. 💛</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DM GLOW to start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">READY: template exists (design/slides.html), needs photos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Myth or Fact: Rapid Fire | 6 aesthetics claims in 30 seconds.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frozen faces, addiction, men and Botox. Let's rapid-fire the truth. How many did you get right?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Score in the comments</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Film 30s rapid-fire reel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Client Words: Natural Results | Testimonial graphic.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nobody could tell. They just kept saying I looked happy and rested. That is the whole goal. 💛 (Shared with permission.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Your turn. Link in bio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Testimonial quote card (with consent)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Botox or Filler? You Might Be Asking for the Wrong One | Lines or volume? They are not the same problem.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Half the DMs I get ask for the wrong treatment. Here is the simple way to know whether your concern is about movement or volume, and what that means for your plan.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DM CONSULT and I will help</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Set B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lines vs Volume in 20 Seconds | Which one is your concern?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Look in the mirror and smile. Movement lines or lost volume? The answer decides your treatment. Here is how to tell.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DM CONSULT for help</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Film 20s explainer reel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ask NP Cleo: Your Questions, Answered Honestly | You asked. I answered. No filter.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This month you sent amazing questions. Here are the honest answers, including the one nobody else will give you about cheap Botox. Keep them coming. 👇</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drop your question below</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Design Q&amp;A layout from real DM questions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Answering Your DMs on Camera | Your real questions, my honest answers.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">You asked about pricing, pain, and how to spot filters. I answered everything on camera. No scripts.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Send your question</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Film 30-45s Q&amp;A reel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Poll: What Should NP Cleo Cover Next? | Audience chooses next month's content.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">October is filler month. What do you want the truth about first: lips, cheeks, or under eyes? Vote. 👇</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vote in comments</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Poll graphic + story poll</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How Long Does Botox Really Last? | The honest timeline, month by month.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anyone promising six months is overpromising. Here is the real timeline, what makes it fade faster, and how to make results last longer.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Save this timeline</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Design timeline layout in editorial template</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The 3-Month Botox Timeline | Week by week, what to expect.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Day 3, week 2, month 3. Here is exactly how your results evolve, in 20 seconds.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Film 20s timeline reel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fillers, Naturally</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Why We Sometimes Say No | A provider who says yes to everyone is a red flag.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I have turned people away, and they thanked me later. Here is why honest candidacy matters and what it says about any provider who never says no.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Book an honest consult</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What I Tell Every First-Timer | The pep talk before every first appointment.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">If you are nervous, this is for you. Here is what I tell every single first-time patient before we start.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Book your first visit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Film 20-30s talking-head reel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quote: No Is Protection | Brand quote card.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">An honest provider will sometimes tell you no. That is protection, not rejection. ✨</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Share this</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filler Won't Make You Look Fake. Bad Technique Does. | The fear is real. The cause is not what you think.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Every overdone face you have seen came from heavy hands, not from filler itself. Great work is invisible. You have seen it a hundred times without knowing. ✨</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DM FILLER for a consult</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Design in editorial template. October filler month opener</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Why Filler Looks Fake (Sometimes) | It is not the filler. It is the hands.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Overfilled faces come from bad technique, wrong product, wrong placement. Here is the 20-second truth.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Full carousel on our feed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lip Filler: Natural vs Overdone | The difference is the injector.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Soft, balanced, still you. Here is what separates natural lip results from the duck lips everyone fears, and the questions to ask before anyone touches your lips.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Save before you book anywhere</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Design in editorial template + consented lip photos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filler Prep: Behind the Scenes | The setup you never see.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cannulas vs needles, numbing, planning. Here is everything that happens before a single drop of filler.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Follow for filler month</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Film 20s BTS prep clip</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quote: Subtle Is the New Dramatic | Brand quote card.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subtle is the new dramatic. The best work whispers. 💛</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cheek Filler: The Secret Nobody Talks About | The treatment behind the best natural glow-ups.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Everyone asks about lips. But cheek filler is quietly behind some of the most natural transformations you have seen. Here is how facial balancing works.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DM CHEEKS to learn more</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cheek Filler in 20 Seconds | The most underrated treatment, explained.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lifted, refreshed, never puffy. Here is what cheek filler actually does when it is done right.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Is Filler Right for You? An Honest Checklist | Not everyone is a candidate. Here is how to know.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">An honest provider will sometimes tell you not yet. Run through this checklist before your consult and you will walk in knowing exactly what to ask.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Facial Balancing Breakdown | Why the plan matters more than the syringe.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">One syringe in the right place beats three in the wrong ones. Here is how facial balancing thinking works.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Book a balancing consult</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Film 30s explainer with face map graphic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FAQ: How Much Filler Do I Need? | The honest answer.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Less than Instagram makes you think. Most natural results start with one syringe or less. Here is why.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">More FAQs? DM me</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FAQ card in brand style</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filler Dissolves. Here Is the Real Timeline. | What they do not tell you about longevity.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filler is not forever, and that is a feature, not a flaw. Here is how long each area really lasts and what maintenance actually looks like.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Book your plan. Link in bio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Design timeline layout</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What Happens When Filler Dissolves | The timeline nobody explains.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">It does not vanish overnight and you will not deflate. Here is what actually happens as filler fades.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lip Filler Aftercare: Your First Week | Swelling is normal. Panic is optional.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Day 1 looks different from day 7. Here is the honest day-by-day so you know exactly what is normal and when to reach out. Save this before your appointment.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aftercare in 15 Seconds | Save this for after your appointment.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ice, no gym for 24 hours, sleep on your back, and message me with anything. That is it. Save this. ✨</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Save + share</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Film 15s quick-tips reel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Client Words: The Lip Glow-Up | Testimonial graphic.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I finally got my lips done and nobody said filler. They said I looked prettier and could not say why. (Shared with permission.) 💛</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Your turn. DM FILLER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Testimonial card (with consent)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 Filler Lies You Still Believe | The sequel you asked for.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">You loved the Botox edition, so here is the filler truth round. Slide 4 is the one that surprises everyone. Share it with your group chat. ✨</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Share with a friend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Design in editorial template. Sequel to Botox lies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filler Myths: Rapid Fire | 5 filler lies in 30 seconds.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">It stretches your lips, it is permanent, everyone can tell. Rapid-fire truth round. How many did you believe?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Facial Balancing: Why We Treat Faces, Not Lines | Chasing lines is old school.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Great aesthetics looks at the whole face: proportions, balance, harmony. Here is why the best results come from a plan, not a single syringe.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DM BALANCE for a consult</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Why I Treat Faces, Not Lines | The philosophy behind natural results.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chasing individual lines is old school. Balance and harmony are why my patients look rested instead of done.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ask Anything: Filler Edition | Engagement post.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filler month is almost over. Drop every remaining question below and I will answer all of them. No judgment. 👇</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comment your question</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Engagement graphic in brand style</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rested by the Holidays</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Promo &amp; CTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rested by the Holidays: Your Treatment Timeline | Party season is closer than you think.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Botox needs 2 weeks to settle. Filler needs up to 4. If you want to glow in the December photos, here is exactly when to book each treatment. 🗓️</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Book now. Link in bio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Set E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Design holiday timeline layout</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holiday Timeline: Book Now, Glow by December | Work backwards from party season.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Botox needs 2 weeks. Filler needs 4. December is closer than you think. Here is the math in 15 seconds. 🗓️</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Film 15s countdown-style reel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Party Season Prep: What to Book and When | Your holiday glow, planned backwards.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Work back from your event date and nothing is rushed, nothing is swollen, and everything looks like you. Here is the smart booking order.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DM HOLIDAY to book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Getting the Clinic Holiday Ready | BTS: decorating and booking season.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The tree is up, the calendar is filling, and the glow-up season is officially here. Come see us. ✨</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Book your spot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Film 15-20s BTS holiday clip</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quote: Book the Appointment | Seasonal self-care push.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">You cannot pour from an empty cup. Book the appointment. Take the hour. You have earned it. 💛</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Link in bio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Gift of Glow: Gift Certificates Are Here | The present nobody returns.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Give the people you love something they actually want. Luxury Beauty gift certificates are available in any amount, wrapped and ready. 🎁</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DM GIFT to order</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Design gift certificate reveal layout</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gift Certificate Reveal | The present nobody returns.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gift certificates are officially here, in any amount, wrapped and beautiful. Watch the reveal. 🎁</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Film 15s unboxing-style reveal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 Months of Honest Answers: The Recap | Real education. Real results. Thank you.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Since August we have busted myths, answered your questions, and kept every promise about natural results. Here are the posts you loved most, in case you missed one. 💛</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Follow for what is next</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compile top slides from past carousels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thank You: 3 Months of Honest Aesthetics | Gratitude reel + highlights.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Since August you have asked incredible questions and trusted us with the answers. Here is to honest aesthetics. Thank you. 💛</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compile highlight montage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tag Someone Who Deserves a Glow-Up Gift | Engagement + promo close.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Know someone who never treats themselves? Tag them below. We will take care of the rest. 🎁</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tag a friend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Period</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Theme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Goal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carousel Topics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reel / Syndication Focus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">August 17-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Launch the educational brand voice and post the finished Botox myths carousel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 Botox Lies (ready) / 5 Red Flags / First Visit / Meet NP Cleo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consult POV, BTS prep, injector-choice safety</t>
-  </si>
-  <si>
-    <t xml:space="preserve">September</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Own every Botox question a first-timer Googles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preventative / 20 Units / Botox vs Dysport / Aftercare / What Botox Can't Do / Natural Promise / Botox or Filler / Ask Cleo / How Long It Lasts / Why We Say No</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quick explainers, myth rapid-fire, day in the life, FAQ cards</t>
-  </si>
-  <si>
-    <t xml:space="preserve">October</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Convert filler fear into filler bookings with honesty-first education</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not Fake / Lips Natural vs Overdone / Cheek Filler / Candidacy Checklist / Dissolve Timeline / Lip Aftercare / 5 Filler Lies / Facial Balancing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filler explainers, BTS prep, testimonials, FAQ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">November 1-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Create urgency: book now to glow for party season + launch gift certificates</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holiday Timeline / Party Season Prep / Gift of Glow / 3-Month Recap</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Countdown reels, holiday BTS, gift reveal, tag-a-friend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Share of Posts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What It Is</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Formats</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Success Metric</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teach one thing per post: myths, comparisons, timelines, aftercare, candidacy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carousels, explainer reels, FAQ cards</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saves and shares</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Show honesty and results: testimonials, natural-results promise, why we say no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quote cards, testimonial posts, philosophy carousels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMs and consults</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Humanize NP Cleo: day in the life, room tours, Q&amp;A, prep clips</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BTS reels, Q&amp;A posts, polls</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comments and follows</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Direct booking pushes: seasonal timelines, gift certificates, offers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Timeline reels, promo carousels, engagement + tag posts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Set</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hashtags (copy-paste)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Botox Education</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#botox #botoxeducation #botoxmyths #preventativebotox #antiwrinkleinjections #nurseinjector #medspa #naturalbotox #botoxbeforeandafter #aestheticnurse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#dermalfiller #lipfiller #cheekfiller #naturalfiller #facialbalancing #lipfillernatural #aestheticnurse #medspa #fillerjourney #lipgoals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brand &amp; Trust</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#npinjector #nursepractitioner #medspalife #luxurybeauty #aestheticnurse #skincareexpert #beautyclinic #selfcare #naturalresults #honestbeauty</t>
   </si>
   <si>
     <t xml:space="preserve">Reels &amp; TikTok</t>
@@ -1664,7 +1871,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:C29"/>
+  <dimension ref="B2:C30"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -1752,7 +1959,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="3" t="s">
         <v>15</v>
       </c>
@@ -1768,7 +1975,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="3" t="s">
         <v>19</v>
       </c>
@@ -1785,75 +1992,83 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="3"/>
-      <c r="C19" s="4"/>
-    </row>
-    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="3" t="s">
+      <c r="B19" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C19" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="3"/>
-      <c r="C21" s="4"/>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="3"/>
+      <c r="C20" s="4"/>
+    </row>
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="5" t="s">
-        <v>25</v>
-      </c>
+      <c r="B22" s="3"/>
       <c r="C22" s="4"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C23" s="3" t="n">
+      <c r="B23" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="4"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <f aca="false">COUNTA('Posting Schedule'!A2:A66)</f>
         <v>65</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C24" s="3" t="n">
-        <f aca="false">COUNTIF('Posting Schedule'!M2:M66,"Idea")</f>
-        <v>64</v>
-      </c>
-    </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C25" s="3" t="n">
-        <f aca="false">COUNTIF('Posting Schedule'!M2:M66,"Design")</f>
-        <v>0</v>
+        <f aca="false">COUNTIF('Posting Schedule'!N2:N66,"Idea")</f>
+        <v>64</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C26" s="3" t="n">
-        <f aca="false">COUNTIF('Posting Schedule'!M2:M66,"Ready")</f>
-        <v>1</v>
+        <f aca="false">COUNTIF('Posting Schedule'!N2:N66,"Design")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C27" s="3" t="n">
-        <f aca="false">COUNTIF('Posting Schedule'!M2:M66,"Posted")</f>
+        <f aca="false">COUNTIF('Posting Schedule'!N2:N66,"Ready")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <f aca="false">COUNTIF('Posting Schedule'!N2:N66,"Posted")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="7" t="s">
-        <v>31</v>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="7" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1872,7 +2087,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:S66"/>
+  <dimension ref="A1:T66"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -1886,71 +2101,75 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="15" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="16" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="10"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="R1" s="8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="S1" s="8" t="s">
-        <v>50</v>
+        <v>52</v>
+      </c>
+      <c r="T1" s="8" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1958,3059 +2177,3254 @@
         <v>46251</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C2" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J2" s="10" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K2" s="10" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="L2" s="10" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M2" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="N2" s="10"/>
+        <v>64</v>
+      </c>
+      <c r="N2" s="10" t="s">
+        <v>65</v>
+      </c>
       <c r="O2" s="10"/>
       <c r="P2" s="10"/>
       <c r="Q2" s="10"/>
       <c r="R2" s="10"/>
       <c r="S2" s="10"/>
-    </row>
-    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T2" s="10"/>
+    </row>
+    <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="n">
         <v>46252</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C3" s="12" t="n">
         <v>1</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="I3" s="12" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="J3" s="12" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K3" s="12" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="L3" s="12" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="M3" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="N3" s="12"/>
+        <v>73</v>
+      </c>
+      <c r="N3" s="12" t="s">
+        <v>74</v>
+      </c>
       <c r="O3" s="12"/>
       <c r="P3" s="12"/>
       <c r="Q3" s="12"/>
       <c r="R3" s="12"/>
       <c r="S3" s="12"/>
+      <c r="T3" s="12"/>
     </row>
     <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="n">
         <v>46254</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C4" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="L4" s="10" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="M4" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="N4" s="10"/>
+        <v>82</v>
+      </c>
+      <c r="N4" s="10" t="s">
+        <v>74</v>
+      </c>
       <c r="O4" s="10"/>
       <c r="P4" s="10"/>
       <c r="Q4" s="10"/>
       <c r="R4" s="10"/>
       <c r="S4" s="10"/>
-    </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T4" s="10"/>
+    </row>
+    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="n">
         <v>46255</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C5" s="12" t="n">
         <v>1</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="H5" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="I5" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="K5" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="I5" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="J5" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="K5" s="12" t="s">
-        <v>68</v>
-      </c>
       <c r="L5" s="12" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="M5" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="N5" s="12"/>
+        <v>89</v>
+      </c>
+      <c r="N5" s="12" t="s">
+        <v>74</v>
+      </c>
       <c r="O5" s="12"/>
       <c r="P5" s="12"/>
       <c r="Q5" s="12"/>
       <c r="R5" s="12"/>
       <c r="S5" s="12"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T5" s="12"/>
+    </row>
+    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="n">
         <v>46256</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>1</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="K6" s="12" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="L6" s="12" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="M6" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="N6" s="12"/>
+        <v>95</v>
+      </c>
+      <c r="N6" s="12" t="s">
+        <v>74</v>
+      </c>
       <c r="O6" s="12"/>
       <c r="P6" s="12"/>
       <c r="Q6" s="12"/>
       <c r="R6" s="12"/>
       <c r="S6" s="12"/>
-    </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T6" s="12"/>
+    </row>
+    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="n">
         <v>46258</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C7" s="10" t="n">
         <v>2</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="L7" s="10" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="M7" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="N7" s="10"/>
+        <v>100</v>
+      </c>
+      <c r="N7" s="10" t="s">
+        <v>74</v>
+      </c>
       <c r="O7" s="10"/>
       <c r="P7" s="10"/>
       <c r="Q7" s="10"/>
       <c r="R7" s="10"/>
       <c r="S7" s="10"/>
-    </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T7" s="10"/>
+    </row>
+    <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="n">
         <v>46259</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C8" s="12" t="n">
         <v>2</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="K8" s="12" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="L8" s="12" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="M8" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="N8" s="12"/>
+        <v>105</v>
+      </c>
+      <c r="N8" s="12" t="s">
+        <v>74</v>
+      </c>
       <c r="O8" s="12"/>
       <c r="P8" s="12"/>
       <c r="Q8" s="12"/>
       <c r="R8" s="12"/>
       <c r="S8" s="12"/>
-    </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T8" s="12"/>
+    </row>
+    <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="n">
         <v>46261</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C9" s="10" t="n">
         <v>2</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="L9" s="10" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="M9" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="N9" s="10"/>
+        <v>110</v>
+      </c>
+      <c r="N9" s="10" t="s">
+        <v>74</v>
+      </c>
       <c r="O9" s="10"/>
       <c r="P9" s="10"/>
       <c r="Q9" s="10"/>
       <c r="R9" s="10"/>
       <c r="S9" s="10"/>
-    </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T9" s="10"/>
+    </row>
+    <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="n">
         <v>46262</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C10" s="12" t="n">
         <v>2</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="K10" s="12" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="L10" s="12" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="M10" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="N10" s="12"/>
+        <v>115</v>
+      </c>
+      <c r="N10" s="12" t="s">
+        <v>74</v>
+      </c>
       <c r="O10" s="12"/>
       <c r="P10" s="12"/>
       <c r="Q10" s="12"/>
       <c r="R10" s="12"/>
       <c r="S10" s="12"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T10" s="12"/>
+    </row>
+    <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="n">
         <v>46263</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C11" s="12" t="n">
         <v>2</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="K11" s="12" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="L11" s="12" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="M11" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="N11" s="12"/>
+        <v>120</v>
+      </c>
+      <c r="N11" s="12" t="s">
+        <v>74</v>
+      </c>
       <c r="O11" s="12"/>
       <c r="P11" s="12"/>
       <c r="Q11" s="12"/>
       <c r="R11" s="12"/>
       <c r="S11" s="12"/>
-    </row>
-    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T11" s="12"/>
+    </row>
+    <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="n">
         <v>46265</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C12" s="10" t="n">
         <v>3</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="L12" s="10" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="M12" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="N12" s="10"/>
+        <v>125</v>
+      </c>
+      <c r="N12" s="10" t="s">
+        <v>74</v>
+      </c>
       <c r="O12" s="10"/>
       <c r="P12" s="10"/>
       <c r="Q12" s="10"/>
       <c r="R12" s="10"/>
       <c r="S12" s="10"/>
-    </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T12" s="10"/>
+    </row>
+    <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="n">
         <v>46266</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C13" s="12" t="n">
         <v>3</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="I13" s="12" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="K13" s="12" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="L13" s="12" t="s">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="M13" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="N13" s="12"/>
+        <v>131</v>
+      </c>
+      <c r="N13" s="12" t="s">
+        <v>74</v>
+      </c>
       <c r="O13" s="12"/>
       <c r="P13" s="12"/>
       <c r="Q13" s="12"/>
       <c r="R13" s="12"/>
       <c r="S13" s="12"/>
-    </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T13" s="12"/>
+    </row>
+    <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="n">
         <v>46268</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C14" s="10" t="n">
         <v>3</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="L14" s="10" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="M14" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="N14" s="10"/>
+        <v>136</v>
+      </c>
+      <c r="N14" s="10" t="s">
+        <v>74</v>
+      </c>
       <c r="O14" s="10"/>
       <c r="P14" s="10"/>
       <c r="Q14" s="10"/>
       <c r="R14" s="10"/>
       <c r="S14" s="10"/>
-    </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T14" s="10"/>
+    </row>
+    <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="n">
         <v>46269</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C15" s="12" t="n">
         <v>3</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="K15" s="12" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="L15" s="12" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="M15" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="N15" s="12"/>
+        <v>140</v>
+      </c>
+      <c r="N15" s="12" t="s">
+        <v>74</v>
+      </c>
       <c r="O15" s="12"/>
       <c r="P15" s="12"/>
       <c r="Q15" s="12"/>
       <c r="R15" s="12"/>
       <c r="S15" s="12"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T15" s="12"/>
+    </row>
+    <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="n">
         <v>46270</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C16" s="12" t="n">
         <v>3</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="I16" s="12" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="K16" s="12" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="L16" s="12" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="M16" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="N16" s="12"/>
+        <v>145</v>
+      </c>
+      <c r="N16" s="12" t="s">
+        <v>74</v>
+      </c>
       <c r="O16" s="12"/>
       <c r="P16" s="12"/>
       <c r="Q16" s="12"/>
       <c r="R16" s="12"/>
       <c r="S16" s="12"/>
-    </row>
-    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T16" s="12"/>
+    </row>
+    <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="n">
         <v>46272</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C17" s="10" t="n">
         <v>4</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="L17" s="10" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="M17" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="N17" s="10"/>
+        <v>149</v>
+      </c>
+      <c r="N17" s="10" t="s">
+        <v>74</v>
+      </c>
       <c r="O17" s="10"/>
       <c r="P17" s="10"/>
       <c r="Q17" s="10"/>
       <c r="R17" s="10"/>
       <c r="S17" s="10"/>
-    </row>
-    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T17" s="10"/>
+    </row>
+    <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="n">
         <v>46273</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C18" s="12" t="n">
         <v>4</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="I18" s="12" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="L18" s="12" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="M18" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="N18" s="12"/>
+        <v>154</v>
+      </c>
+      <c r="N18" s="12" t="s">
+        <v>74</v>
+      </c>
       <c r="O18" s="12"/>
       <c r="P18" s="12"/>
       <c r="Q18" s="12"/>
       <c r="R18" s="12"/>
       <c r="S18" s="12"/>
-    </row>
-    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T18" s="12"/>
+    </row>
+    <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="n">
         <v>46275</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C19" s="10" t="n">
         <v>4</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="J19" s="10" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="K19" s="10" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="L19" s="10" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="M19" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="N19" s="10"/>
+        <v>158</v>
+      </c>
+      <c r="N19" s="10" t="s">
+        <v>74</v>
+      </c>
       <c r="O19" s="10"/>
       <c r="P19" s="10"/>
       <c r="Q19" s="10"/>
       <c r="R19" s="10"/>
       <c r="S19" s="10"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T19" s="10"/>
+    </row>
+    <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="n">
         <v>46276</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C20" s="12" t="n">
         <v>4</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="I20" s="12" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="L20" s="12" t="s">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="M20" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="N20" s="12"/>
+        <v>163</v>
+      </c>
+      <c r="N20" s="12" t="s">
+        <v>74</v>
+      </c>
       <c r="O20" s="12"/>
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
       <c r="R20" s="12"/>
       <c r="S20" s="12"/>
-    </row>
-    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T20" s="12"/>
+    </row>
+    <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="n">
         <v>46277</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C21" s="12" t="n">
         <v>4</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="I21" s="12" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="K21" s="12" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="L21" s="12" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="M21" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="N21" s="12"/>
+        <v>168</v>
+      </c>
+      <c r="N21" s="12" t="s">
+        <v>74</v>
+      </c>
       <c r="O21" s="12"/>
       <c r="P21" s="12"/>
       <c r="Q21" s="12"/>
       <c r="R21" s="12"/>
       <c r="S21" s="12"/>
-    </row>
-    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T21" s="12"/>
+    </row>
+    <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="n">
         <v>46279</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C22" s="10" t="n">
         <v>5</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>151</v>
+        <v>171</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="L22" s="10" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="M22" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="N22" s="10"/>
+        <v>172</v>
+      </c>
+      <c r="N22" s="10" t="s">
+        <v>74</v>
+      </c>
       <c r="O22" s="10"/>
       <c r="P22" s="10"/>
       <c r="Q22" s="10"/>
       <c r="R22" s="10"/>
       <c r="S22" s="10"/>
-    </row>
-    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T22" s="10"/>
+    </row>
+    <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="n">
         <v>46280</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C23" s="12" t="n">
         <v>5</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="I23" s="12" t="s">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="K23" s="12" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="L23" s="12" t="s">
-        <v>98</v>
+        <v>175</v>
       </c>
       <c r="M23" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="N23" s="12"/>
+        <v>176</v>
+      </c>
+      <c r="N23" s="12" t="s">
+        <v>74</v>
+      </c>
       <c r="O23" s="12"/>
       <c r="P23" s="12"/>
       <c r="Q23" s="12"/>
       <c r="R23" s="12"/>
       <c r="S23" s="12"/>
-    </row>
-    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T23" s="12"/>
+    </row>
+    <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="9" t="n">
         <v>46282</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C24" s="10" t="n">
         <v>5</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="L24" s="10" t="s">
-        <v>157</v>
+        <v>180</v>
       </c>
       <c r="M24" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="N24" s="10"/>
+        <v>181</v>
+      </c>
+      <c r="N24" s="10" t="s">
+        <v>74</v>
+      </c>
       <c r="O24" s="10"/>
       <c r="P24" s="10"/>
       <c r="Q24" s="10"/>
       <c r="R24" s="10"/>
       <c r="S24" s="10"/>
-    </row>
-    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T24" s="10"/>
+    </row>
+    <row r="25" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="n">
         <v>46283</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C25" s="12" t="n">
         <v>5</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H25" s="12" t="s">
-        <v>158</v>
+        <v>182</v>
       </c>
       <c r="I25" s="12" t="s">
-        <v>159</v>
+        <v>183</v>
       </c>
       <c r="J25" s="12" t="s">
-        <v>160</v>
+        <v>184</v>
       </c>
       <c r="K25" s="12" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="L25" s="12" t="s">
-        <v>161</v>
+        <v>185</v>
       </c>
       <c r="M25" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="N25" s="12"/>
+        <v>186</v>
+      </c>
+      <c r="N25" s="12" t="s">
+        <v>74</v>
+      </c>
       <c r="O25" s="12"/>
       <c r="P25" s="12"/>
       <c r="Q25" s="12"/>
       <c r="R25" s="12"/>
       <c r="S25" s="12"/>
-    </row>
-    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T25" s="12"/>
+    </row>
+    <row r="26" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="n">
         <v>46284</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C26" s="12" t="n">
         <v>5</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H26" s="12" t="s">
-        <v>162</v>
+        <v>187</v>
       </c>
       <c r="I26" s="12" t="s">
-        <v>163</v>
+        <v>188</v>
       </c>
       <c r="J26" s="12" t="s">
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="K26" s="12" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="L26" s="12" t="s">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="M26" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="N26" s="12"/>
+        <v>191</v>
+      </c>
+      <c r="N26" s="12" t="s">
+        <v>74</v>
+      </c>
       <c r="O26" s="12"/>
       <c r="P26" s="12"/>
       <c r="Q26" s="12"/>
       <c r="R26" s="12"/>
       <c r="S26" s="12"/>
-    </row>
-    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T26" s="12"/>
+    </row>
+    <row r="27" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="n">
         <v>46286</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C27" s="10" t="n">
         <v>6</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>166</v>
+        <v>192</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>167</v>
+        <v>193</v>
       </c>
       <c r="J27" s="10" t="s">
-        <v>168</v>
+        <v>194</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>169</v>
+        <v>195</v>
       </c>
       <c r="L27" s="10" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="M27" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="N27" s="10"/>
+        <v>196</v>
+      </c>
+      <c r="N27" s="10" t="s">
+        <v>74</v>
+      </c>
       <c r="O27" s="10"/>
       <c r="P27" s="10"/>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
       <c r="S27" s="10"/>
-    </row>
-    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T27" s="10"/>
+    </row>
+    <row r="28" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="n">
         <v>46287</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C28" s="12" t="n">
         <v>6</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H28" s="12" t="s">
-        <v>170</v>
+        <v>197</v>
       </c>
       <c r="I28" s="12" t="s">
-        <v>171</v>
+        <v>198</v>
       </c>
       <c r="J28" s="12" t="s">
-        <v>172</v>
+        <v>199</v>
       </c>
       <c r="K28" s="12" t="s">
-        <v>68</v>
+        <v>195</v>
       </c>
       <c r="L28" s="12" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="M28" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="N28" s="12"/>
+        <v>201</v>
+      </c>
+      <c r="N28" s="12" t="s">
+        <v>74</v>
+      </c>
       <c r="O28" s="12"/>
       <c r="P28" s="12"/>
       <c r="Q28" s="12"/>
       <c r="R28" s="12"/>
       <c r="S28" s="12"/>
-    </row>
-    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T28" s="12"/>
+    </row>
+    <row r="29" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="9" t="n">
         <v>46289</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C29" s="10" t="n">
         <v>6</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>174</v>
+        <v>202</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>175</v>
+        <v>203</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>176</v>
+        <v>204</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="L29" s="10" t="s">
-        <v>177</v>
+        <v>205</v>
       </c>
       <c r="M29" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="N29" s="10"/>
+        <v>206</v>
+      </c>
+      <c r="N29" s="10" t="s">
+        <v>74</v>
+      </c>
       <c r="O29" s="10"/>
       <c r="P29" s="10"/>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
       <c r="S29" s="10"/>
-    </row>
-    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T29" s="10"/>
+    </row>
+    <row r="30" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="n">
         <v>46290</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C30" s="12" t="n">
         <v>6</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="H30" s="12" t="s">
-        <v>178</v>
+        <v>207</v>
       </c>
       <c r="I30" s="12" t="s">
-        <v>179</v>
+        <v>208</v>
       </c>
       <c r="J30" s="12" t="s">
-        <v>180</v>
+        <v>209</v>
       </c>
       <c r="K30" s="12" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="L30" s="12" t="s">
-        <v>181</v>
+        <v>210</v>
       </c>
       <c r="M30" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="N30" s="12"/>
+        <v>211</v>
+      </c>
+      <c r="N30" s="12" t="s">
+        <v>74</v>
+      </c>
       <c r="O30" s="12"/>
       <c r="P30" s="12"/>
       <c r="Q30" s="12"/>
       <c r="R30" s="12"/>
       <c r="S30" s="12"/>
-    </row>
-    <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T30" s="12"/>
+    </row>
+    <row r="31" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="11" t="n">
         <v>46291</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C31" s="12" t="n">
         <v>6</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="G31" s="12" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="H31" s="12" t="s">
-        <v>182</v>
+        <v>212</v>
       </c>
       <c r="I31" s="12" t="s">
-        <v>183</v>
+        <v>213</v>
       </c>
       <c r="J31" s="12" t="s">
-        <v>184</v>
+        <v>214</v>
       </c>
       <c r="K31" s="12" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="L31" s="12" t="s">
-        <v>185</v>
+        <v>215</v>
       </c>
       <c r="M31" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="N31" s="12"/>
+        <v>216</v>
+      </c>
+      <c r="N31" s="12" t="s">
+        <v>74</v>
+      </c>
       <c r="O31" s="12"/>
       <c r="P31" s="12"/>
       <c r="Q31" s="12"/>
       <c r="R31" s="12"/>
       <c r="S31" s="12"/>
-    </row>
-    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T31" s="12"/>
+    </row>
+    <row r="32" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="9" t="n">
         <v>46293</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C32" s="10" t="n">
         <v>7</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F32" s="10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>186</v>
+        <v>217</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>187</v>
+        <v>218</v>
       </c>
       <c r="J32" s="10" t="s">
-        <v>188</v>
+        <v>219</v>
       </c>
       <c r="K32" s="10" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="L32" s="10" t="s">
-        <v>189</v>
+        <v>220</v>
       </c>
       <c r="M32" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="N32" s="10"/>
+        <v>221</v>
+      </c>
+      <c r="N32" s="10" t="s">
+        <v>74</v>
+      </c>
       <c r="O32" s="10"/>
       <c r="P32" s="10"/>
       <c r="Q32" s="10"/>
       <c r="R32" s="10"/>
       <c r="S32" s="10"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T32" s="10"/>
+    </row>
+    <row r="33" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="11" t="n">
         <v>46294</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C33" s="12" t="n">
         <v>7</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G33" s="12" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H33" s="12" t="s">
-        <v>190</v>
+        <v>222</v>
       </c>
       <c r="I33" s="12" t="s">
-        <v>191</v>
+        <v>223</v>
       </c>
       <c r="J33" s="12" t="s">
-        <v>188</v>
+        <v>219</v>
       </c>
       <c r="K33" s="12" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="L33" s="12" t="s">
-        <v>192</v>
+        <v>224</v>
       </c>
       <c r="M33" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="N33" s="12"/>
+        <v>225</v>
+      </c>
+      <c r="N33" s="12" t="s">
+        <v>74</v>
+      </c>
       <c r="O33" s="12"/>
       <c r="P33" s="12"/>
       <c r="Q33" s="12"/>
       <c r="R33" s="12"/>
       <c r="S33" s="12"/>
-    </row>
-    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T33" s="12"/>
+    </row>
+    <row r="34" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="9" t="n">
         <v>46296</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C34" s="10" t="n">
         <v>7</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>193</v>
+        <v>226</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G34" s="10" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>194</v>
+        <v>227</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>195</v>
+        <v>228</v>
       </c>
       <c r="J34" s="10" t="s">
-        <v>196</v>
+        <v>229</v>
       </c>
       <c r="K34" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="L34" s="10" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="M34" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="N34" s="10"/>
+        <v>230</v>
+      </c>
+      <c r="N34" s="10" t="s">
+        <v>74</v>
+      </c>
       <c r="O34" s="10"/>
       <c r="P34" s="10"/>
       <c r="Q34" s="10"/>
       <c r="R34" s="10"/>
       <c r="S34" s="10"/>
-    </row>
-    <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T34" s="10"/>
+    </row>
+    <row r="35" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="11" t="n">
         <v>46297</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C35" s="12" t="n">
         <v>7</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>193</v>
+        <v>226</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G35" s="12" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H35" s="12" t="s">
-        <v>197</v>
+        <v>231</v>
       </c>
       <c r="I35" s="12" t="s">
-        <v>198</v>
+        <v>232</v>
       </c>
       <c r="J35" s="12" t="s">
-        <v>199</v>
+        <v>233</v>
       </c>
       <c r="K35" s="12" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="L35" s="12" t="s">
-        <v>200</v>
+        <v>234</v>
       </c>
       <c r="M35" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="N35" s="12"/>
+        <v>235</v>
+      </c>
+      <c r="N35" s="12" t="s">
+        <v>74</v>
+      </c>
       <c r="O35" s="12"/>
       <c r="P35" s="12"/>
       <c r="Q35" s="12"/>
       <c r="R35" s="12"/>
       <c r="S35" s="12"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T35" s="12"/>
+    </row>
+    <row r="36" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="11" t="n">
         <v>46298</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C36" s="12" t="n">
         <v>7</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>193</v>
+        <v>226</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="G36" s="12" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H36" s="12" t="s">
-        <v>201</v>
+        <v>236</v>
       </c>
       <c r="I36" s="12" t="s">
-        <v>202</v>
+        <v>237</v>
       </c>
       <c r="J36" s="12" t="s">
-        <v>203</v>
+        <v>238</v>
       </c>
       <c r="K36" s="12" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="L36" s="12" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="M36" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="N36" s="12"/>
+        <v>239</v>
+      </c>
+      <c r="N36" s="12" t="s">
+        <v>74</v>
+      </c>
       <c r="O36" s="12"/>
       <c r="P36" s="12"/>
       <c r="Q36" s="12"/>
       <c r="R36" s="12"/>
       <c r="S36" s="12"/>
-    </row>
-    <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T36" s="12"/>
+    </row>
+    <row r="37" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="9" t="n">
         <v>46300</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C37" s="10" t="n">
         <v>8</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>193</v>
+        <v>226</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F37" s="10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>204</v>
+        <v>240</v>
       </c>
       <c r="I37" s="10" t="s">
-        <v>205</v>
+        <v>241</v>
       </c>
       <c r="J37" s="10" t="s">
-        <v>206</v>
+        <v>242</v>
       </c>
       <c r="K37" s="10" t="s">
-        <v>169</v>
+        <v>195</v>
       </c>
       <c r="L37" s="10" t="s">
-        <v>207</v>
+        <v>243</v>
       </c>
       <c r="M37" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="N37" s="10"/>
+        <v>244</v>
+      </c>
+      <c r="N37" s="10" t="s">
+        <v>74</v>
+      </c>
       <c r="O37" s="10"/>
       <c r="P37" s="10"/>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
       <c r="S37" s="10"/>
-    </row>
-    <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T37" s="10"/>
+    </row>
+    <row r="38" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="11" t="n">
         <v>46301</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C38" s="12" t="n">
         <v>8</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>193</v>
+        <v>226</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G38" s="12" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H38" s="12" t="s">
-        <v>208</v>
+        <v>245</v>
       </c>
       <c r="I38" s="12" t="s">
-        <v>209</v>
+        <v>246</v>
       </c>
       <c r="J38" s="12" t="s">
-        <v>210</v>
+        <v>247</v>
       </c>
       <c r="K38" s="12" t="s">
-        <v>68</v>
+        <v>195</v>
       </c>
       <c r="L38" s="12" t="s">
-        <v>98</v>
+        <v>248</v>
       </c>
       <c r="M38" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="N38" s="12"/>
+        <v>249</v>
+      </c>
+      <c r="N38" s="12" t="s">
+        <v>74</v>
+      </c>
       <c r="O38" s="12"/>
       <c r="P38" s="12"/>
       <c r="Q38" s="12"/>
       <c r="R38" s="12"/>
       <c r="S38" s="12"/>
-    </row>
-    <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T38" s="12"/>
+    </row>
+    <row r="39" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="9" t="n">
         <v>46303</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C39" s="10" t="n">
         <v>8</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>193</v>
+        <v>226</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>211</v>
+        <v>250</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>212</v>
+        <v>251</v>
       </c>
       <c r="J39" s="10" t="s">
-        <v>213</v>
+        <v>252</v>
       </c>
       <c r="K39" s="10" t="s">
-        <v>169</v>
+        <v>195</v>
       </c>
       <c r="L39" s="10" t="s">
-        <v>214</v>
+        <v>253</v>
       </c>
       <c r="M39" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="N39" s="10"/>
+        <v>254</v>
+      </c>
+      <c r="N39" s="10" t="s">
+        <v>74</v>
+      </c>
       <c r="O39" s="10"/>
       <c r="P39" s="10"/>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
       <c r="S39" s="10"/>
-    </row>
-    <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T39" s="10"/>
+    </row>
+    <row r="40" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="11" t="n">
         <v>46304</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C40" s="12" t="n">
         <v>8</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>193</v>
+        <v>226</v>
       </c>
       <c r="E40" s="12" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F40" s="12" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G40" s="12" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="H40" s="12" t="s">
-        <v>215</v>
+        <v>255</v>
       </c>
       <c r="I40" s="12" t="s">
-        <v>216</v>
+        <v>256</v>
       </c>
       <c r="J40" s="12" t="s">
-        <v>217</v>
+        <v>257</v>
       </c>
       <c r="K40" s="12" t="s">
-        <v>68</v>
+        <v>195</v>
       </c>
       <c r="L40" s="12" t="s">
-        <v>218</v>
+        <v>258</v>
       </c>
       <c r="M40" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="N40" s="12"/>
+        <v>259</v>
+      </c>
+      <c r="N40" s="12" t="s">
+        <v>74</v>
+      </c>
       <c r="O40" s="12"/>
       <c r="P40" s="12"/>
       <c r="Q40" s="12"/>
       <c r="R40" s="12"/>
       <c r="S40" s="12"/>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T40" s="12"/>
+    </row>
+    <row r="41" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="11" t="n">
         <v>46305</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C41" s="12" t="n">
         <v>8</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>193</v>
+        <v>226</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="F41" s="12" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="G41" s="12" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H41" s="12" t="s">
-        <v>219</v>
+        <v>260</v>
       </c>
       <c r="I41" s="12" t="s">
-        <v>220</v>
+        <v>261</v>
       </c>
       <c r="J41" s="12" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="K41" s="12" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="L41" s="12" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="M41" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="N41" s="12"/>
+        <v>262</v>
+      </c>
+      <c r="N41" s="12" t="s">
+        <v>74</v>
+      </c>
       <c r="O41" s="12"/>
       <c r="P41" s="12"/>
       <c r="Q41" s="12"/>
       <c r="R41" s="12"/>
       <c r="S41" s="12"/>
-    </row>
-    <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T41" s="12"/>
+    </row>
+    <row r="42" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="9" t="n">
         <v>46307</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C42" s="10" t="n">
         <v>9</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>193</v>
+        <v>226</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G42" s="10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>221</v>
+        <v>263</v>
       </c>
       <c r="I42" s="10" t="s">
-        <v>222</v>
+        <v>264</v>
       </c>
       <c r="J42" s="10" t="s">
-        <v>223</v>
+        <v>265</v>
       </c>
       <c r="K42" s="10" t="s">
-        <v>169</v>
+        <v>195</v>
       </c>
       <c r="L42" s="10" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="M42" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="N42" s="10"/>
+        <v>266</v>
+      </c>
+      <c r="N42" s="10" t="s">
+        <v>74</v>
+      </c>
       <c r="O42" s="10"/>
       <c r="P42" s="10"/>
       <c r="Q42" s="10"/>
       <c r="R42" s="10"/>
       <c r="S42" s="10"/>
-    </row>
-    <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T42" s="10"/>
+    </row>
+    <row r="43" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="11" t="n">
         <v>46308</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C43" s="12" t="n">
         <v>9</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>193</v>
+        <v>226</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G43" s="12" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H43" s="12" t="s">
-        <v>224</v>
+        <v>267</v>
       </c>
       <c r="I43" s="12" t="s">
-        <v>225</v>
+        <v>268</v>
       </c>
       <c r="J43" s="12" t="s">
-        <v>223</v>
+        <v>265</v>
       </c>
       <c r="K43" s="12" t="s">
-        <v>68</v>
+        <v>195</v>
       </c>
       <c r="L43" s="12" t="s">
-        <v>173</v>
+        <v>269</v>
       </c>
       <c r="M43" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="N43" s="12"/>
+        <v>270</v>
+      </c>
+      <c r="N43" s="12" t="s">
+        <v>74</v>
+      </c>
       <c r="O43" s="12"/>
       <c r="P43" s="12"/>
       <c r="Q43" s="12"/>
       <c r="R43" s="12"/>
       <c r="S43" s="12"/>
-    </row>
-    <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T43" s="12"/>
+    </row>
+    <row r="44" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="9" t="n">
         <v>46310</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C44" s="10" t="n">
         <v>9</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>193</v>
+        <v>226</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G44" s="10" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H44" s="10" t="s">
-        <v>226</v>
+        <v>271</v>
       </c>
       <c r="I44" s="10" t="s">
-        <v>227</v>
+        <v>272</v>
       </c>
       <c r="J44" s="10" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="K44" s="10" t="s">
-        <v>169</v>
+        <v>195</v>
       </c>
       <c r="L44" s="10" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="M44" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="N44" s="10"/>
+        <v>273</v>
+      </c>
+      <c r="N44" s="10" t="s">
+        <v>74</v>
+      </c>
       <c r="O44" s="10"/>
       <c r="P44" s="10"/>
       <c r="Q44" s="10"/>
       <c r="R44" s="10"/>
       <c r="S44" s="10"/>
-    </row>
-    <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T44" s="10"/>
+    </row>
+    <row r="45" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="11" t="n">
         <v>46311</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C45" s="12" t="n">
         <v>9</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>193</v>
+        <v>226</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F45" s="12" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G45" s="12" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H45" s="12" t="s">
-        <v>228</v>
+        <v>274</v>
       </c>
       <c r="I45" s="12" t="s">
-        <v>229</v>
+        <v>275</v>
       </c>
       <c r="J45" s="12" t="s">
-        <v>230</v>
+        <v>276</v>
       </c>
       <c r="K45" s="12" t="s">
-        <v>68</v>
+        <v>195</v>
       </c>
       <c r="L45" s="12" t="s">
-        <v>231</v>
+        <v>277</v>
       </c>
       <c r="M45" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="N45" s="12"/>
+        <v>278</v>
+      </c>
+      <c r="N45" s="12" t="s">
+        <v>74</v>
+      </c>
       <c r="O45" s="12"/>
       <c r="P45" s="12"/>
       <c r="Q45" s="12"/>
       <c r="R45" s="12"/>
       <c r="S45" s="12"/>
-    </row>
-    <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T45" s="12"/>
+    </row>
+    <row r="46" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="11" t="n">
         <v>46312</v>
       </c>
       <c r="B46" s="12" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C46" s="12" t="n">
         <v>9</v>
       </c>
       <c r="D46" s="12" t="s">
-        <v>193</v>
+        <v>226</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="F46" s="12" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="G46" s="12" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H46" s="12" t="s">
-        <v>232</v>
+        <v>279</v>
       </c>
       <c r="I46" s="12" t="s">
-        <v>233</v>
+        <v>280</v>
       </c>
       <c r="J46" s="12" t="s">
-        <v>234</v>
+        <v>281</v>
       </c>
       <c r="K46" s="12" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="L46" s="12" t="s">
-        <v>235</v>
+        <v>167</v>
       </c>
       <c r="M46" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="N46" s="12"/>
+        <v>282</v>
+      </c>
+      <c r="N46" s="12" t="s">
+        <v>74</v>
+      </c>
       <c r="O46" s="12"/>
       <c r="P46" s="12"/>
       <c r="Q46" s="12"/>
       <c r="R46" s="12"/>
       <c r="S46" s="12"/>
-    </row>
-    <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T46" s="12"/>
+    </row>
+    <row r="47" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="9" t="n">
         <v>46314</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C47" s="10" t="n">
         <v>10</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>193</v>
+        <v>226</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F47" s="10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>236</v>
+        <v>283</v>
       </c>
       <c r="I47" s="10" t="s">
-        <v>237</v>
+        <v>284</v>
       </c>
       <c r="J47" s="10" t="s">
-        <v>238</v>
+        <v>285</v>
       </c>
       <c r="K47" s="10" t="s">
-        <v>169</v>
+        <v>195</v>
       </c>
       <c r="L47" s="10" t="s">
-        <v>239</v>
+        <v>286</v>
       </c>
       <c r="M47" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="N47" s="10"/>
+        <v>287</v>
+      </c>
+      <c r="N47" s="10" t="s">
+        <v>74</v>
+      </c>
       <c r="O47" s="10"/>
       <c r="P47" s="10"/>
       <c r="Q47" s="10"/>
       <c r="R47" s="10"/>
       <c r="S47" s="10"/>
-    </row>
-    <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T47" s="10"/>
+    </row>
+    <row r="48" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="11" t="n">
         <v>46315</v>
       </c>
       <c r="B48" s="12" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C48" s="12" t="n">
         <v>10</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>193</v>
+        <v>226</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F48" s="12" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G48" s="12" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H48" s="12" t="s">
-        <v>240</v>
+        <v>288</v>
       </c>
       <c r="I48" s="12" t="s">
-        <v>241</v>
+        <v>289</v>
       </c>
       <c r="J48" s="12" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="K48" s="12" t="s">
-        <v>68</v>
+        <v>195</v>
       </c>
       <c r="L48" s="12" t="s">
-        <v>173</v>
+        <v>224</v>
       </c>
       <c r="M48" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="N48" s="12"/>
+        <v>290</v>
+      </c>
+      <c r="N48" s="12" t="s">
+        <v>74</v>
+      </c>
       <c r="O48" s="12"/>
       <c r="P48" s="12"/>
       <c r="Q48" s="12"/>
       <c r="R48" s="12"/>
       <c r="S48" s="12"/>
-    </row>
-    <row r="49" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T48" s="12"/>
+    </row>
+    <row r="49" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="9" t="n">
         <v>46317</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C49" s="10" t="n">
         <v>10</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>193</v>
+        <v>226</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F49" s="10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>242</v>
+        <v>291</v>
       </c>
       <c r="I49" s="10" t="s">
-        <v>243</v>
+        <v>292</v>
       </c>
       <c r="J49" s="10" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="K49" s="10" t="s">
-        <v>169</v>
+        <v>195</v>
       </c>
       <c r="L49" s="10" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="M49" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="N49" s="10"/>
+        <v>293</v>
+      </c>
+      <c r="N49" s="10" t="s">
+        <v>74</v>
+      </c>
       <c r="O49" s="10"/>
       <c r="P49" s="10"/>
       <c r="Q49" s="10"/>
       <c r="R49" s="10"/>
       <c r="S49" s="10"/>
-    </row>
-    <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T49" s="10"/>
+    </row>
+    <row r="50" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="11" t="n">
         <v>46318</v>
       </c>
       <c r="B50" s="12" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C50" s="12" t="n">
         <v>10</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>193</v>
+        <v>226</v>
       </c>
       <c r="E50" s="12" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F50" s="12" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G50" s="12" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H50" s="12" t="s">
-        <v>244</v>
+        <v>294</v>
       </c>
       <c r="I50" s="12" t="s">
-        <v>245</v>
+        <v>295</v>
       </c>
       <c r="J50" s="12" t="s">
-        <v>246</v>
+        <v>296</v>
       </c>
       <c r="K50" s="12" t="s">
-        <v>68</v>
+        <v>195</v>
       </c>
       <c r="L50" s="12" t="s">
-        <v>247</v>
+        <v>297</v>
       </c>
       <c r="M50" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="N50" s="12"/>
+        <v>298</v>
+      </c>
+      <c r="N50" s="12" t="s">
+        <v>74</v>
+      </c>
       <c r="O50" s="12"/>
       <c r="P50" s="12"/>
       <c r="Q50" s="12"/>
       <c r="R50" s="12"/>
       <c r="S50" s="12"/>
-    </row>
-    <row r="51" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T50" s="12"/>
+    </row>
+    <row r="51" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="11" t="n">
         <v>46319</v>
       </c>
       <c r="B51" s="12" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C51" s="12" t="n">
         <v>10</v>
       </c>
       <c r="D51" s="12" t="s">
-        <v>193</v>
+        <v>226</v>
       </c>
       <c r="E51" s="12" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="F51" s="12" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="G51" s="12" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H51" s="12" t="s">
-        <v>248</v>
+        <v>299</v>
       </c>
       <c r="I51" s="12" t="s">
-        <v>249</v>
+        <v>300</v>
       </c>
       <c r="J51" s="12" t="s">
-        <v>250</v>
+        <v>301</v>
       </c>
       <c r="K51" s="12" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="L51" s="12" t="s">
-        <v>251</v>
+        <v>302</v>
       </c>
       <c r="M51" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="N51" s="12"/>
+        <v>303</v>
+      </c>
+      <c r="N51" s="12" t="s">
+        <v>74</v>
+      </c>
       <c r="O51" s="12"/>
       <c r="P51" s="12"/>
       <c r="Q51" s="12"/>
       <c r="R51" s="12"/>
       <c r="S51" s="12"/>
-    </row>
-    <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T51" s="12"/>
+    </row>
+    <row r="52" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="9" t="n">
         <v>46321</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C52" s="10" t="n">
         <v>11</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>193</v>
+        <v>226</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F52" s="10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G52" s="10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H52" s="10" t="s">
-        <v>252</v>
+        <v>304</v>
       </c>
       <c r="I52" s="10" t="s">
-        <v>253</v>
+        <v>305</v>
       </c>
       <c r="J52" s="10" t="s">
-        <v>254</v>
+        <v>184</v>
       </c>
       <c r="K52" s="10" t="s">
-        <v>169</v>
+        <v>195</v>
       </c>
       <c r="L52" s="10" t="s">
-        <v>255</v>
+        <v>306</v>
       </c>
       <c r="M52" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="N52" s="10"/>
+        <v>307</v>
+      </c>
+      <c r="N52" s="10" t="s">
+        <v>74</v>
+      </c>
       <c r="O52" s="10"/>
       <c r="P52" s="10"/>
       <c r="Q52" s="10"/>
       <c r="R52" s="10"/>
       <c r="S52" s="10"/>
-    </row>
-    <row r="53" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T52" s="10"/>
+    </row>
+    <row r="53" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="11" t="n">
         <v>46322</v>
       </c>
       <c r="B53" s="12" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C53" s="12" t="n">
         <v>11</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>193</v>
+        <v>226</v>
       </c>
       <c r="E53" s="12" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F53" s="12" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G53" s="12" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H53" s="12" t="s">
-        <v>256</v>
+        <v>308</v>
       </c>
       <c r="I53" s="12" t="s">
-        <v>257</v>
+        <v>309</v>
       </c>
       <c r="J53" s="12" t="s">
-        <v>210</v>
+        <v>310</v>
       </c>
       <c r="K53" s="12" t="s">
-        <v>68</v>
+        <v>195</v>
       </c>
       <c r="L53" s="12" t="s">
-        <v>161</v>
+        <v>185</v>
       </c>
       <c r="M53" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="N53" s="12"/>
+        <v>311</v>
+      </c>
+      <c r="N53" s="12" t="s">
+        <v>74</v>
+      </c>
       <c r="O53" s="12"/>
       <c r="P53" s="12"/>
       <c r="Q53" s="12"/>
       <c r="R53" s="12"/>
       <c r="S53" s="12"/>
-    </row>
-    <row r="54" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T53" s="12"/>
+    </row>
+    <row r="54" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="9" t="n">
         <v>46324</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C54" s="10" t="n">
         <v>11</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>193</v>
+        <v>226</v>
       </c>
       <c r="E54" s="10" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F54" s="10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G54" s="10" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H54" s="10" t="s">
-        <v>258</v>
+        <v>312</v>
       </c>
       <c r="I54" s="10" t="s">
-        <v>259</v>
+        <v>313</v>
       </c>
       <c r="J54" s="10" t="s">
-        <v>260</v>
+        <v>314</v>
       </c>
       <c r="K54" s="10" t="s">
-        <v>169</v>
+        <v>195</v>
       </c>
       <c r="L54" s="10" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="M54" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="N54" s="10"/>
+        <v>315</v>
+      </c>
+      <c r="N54" s="10" t="s">
+        <v>74</v>
+      </c>
       <c r="O54" s="10"/>
       <c r="P54" s="10"/>
       <c r="Q54" s="10"/>
       <c r="R54" s="10"/>
       <c r="S54" s="10"/>
-    </row>
-    <row r="55" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T54" s="10"/>
+    </row>
+    <row r="55" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="11" t="n">
         <v>46325</v>
       </c>
       <c r="B55" s="12" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C55" s="12" t="n">
         <v>11</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>193</v>
+        <v>226</v>
       </c>
       <c r="E55" s="12" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F55" s="12" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G55" s="12" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H55" s="12" t="s">
-        <v>261</v>
+        <v>316</v>
       </c>
       <c r="I55" s="12" t="s">
-        <v>262</v>
+        <v>317</v>
       </c>
       <c r="J55" s="12" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="K55" s="12" t="s">
-        <v>68</v>
+        <v>195</v>
       </c>
       <c r="L55" s="12" t="s">
-        <v>200</v>
+        <v>318</v>
       </c>
       <c r="M55" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="N55" s="12"/>
+        <v>319</v>
+      </c>
+      <c r="N55" s="12" t="s">
+        <v>74</v>
+      </c>
       <c r="O55" s="12"/>
       <c r="P55" s="12"/>
       <c r="Q55" s="12"/>
       <c r="R55" s="12"/>
       <c r="S55" s="12"/>
-    </row>
-    <row r="56" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T55" s="12"/>
+    </row>
+    <row r="56" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="11" t="n">
         <v>46326</v>
       </c>
       <c r="B56" s="12" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C56" s="12" t="n">
         <v>11</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>193</v>
+        <v>226</v>
       </c>
       <c r="E56" s="12" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="F56" s="12" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="G56" s="12" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="H56" s="12" t="s">
-        <v>263</v>
+        <v>320</v>
       </c>
       <c r="I56" s="12" t="s">
-        <v>264</v>
+        <v>321</v>
       </c>
       <c r="J56" s="12" t="s">
-        <v>265</v>
+        <v>322</v>
       </c>
       <c r="K56" s="12" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="L56" s="12" t="s">
-        <v>266</v>
+        <v>323</v>
       </c>
       <c r="M56" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="N56" s="12"/>
+        <v>324</v>
+      </c>
+      <c r="N56" s="12" t="s">
+        <v>74</v>
+      </c>
       <c r="O56" s="12"/>
       <c r="P56" s="12"/>
       <c r="Q56" s="12"/>
       <c r="R56" s="12"/>
       <c r="S56" s="12"/>
-    </row>
-    <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T56" s="12"/>
+    </row>
+    <row r="57" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="9" t="n">
         <v>46328</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C57" s="10" t="n">
         <v>12</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>267</v>
+        <v>325</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F57" s="10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>268</v>
+        <v>326</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>269</v>
+        <v>327</v>
       </c>
       <c r="I57" s="10" t="s">
-        <v>270</v>
+        <v>328</v>
       </c>
       <c r="J57" s="10" t="s">
-        <v>271</v>
+        <v>329</v>
       </c>
       <c r="K57" s="10" t="s">
-        <v>272</v>
+        <v>330</v>
       </c>
       <c r="L57" s="10" t="s">
-        <v>273</v>
+        <v>331</v>
       </c>
       <c r="M57" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="N57" s="10"/>
+        <v>332</v>
+      </c>
+      <c r="N57" s="10" t="s">
+        <v>74</v>
+      </c>
       <c r="O57" s="10"/>
       <c r="P57" s="10"/>
       <c r="Q57" s="10"/>
       <c r="R57" s="10"/>
       <c r="S57" s="10"/>
-    </row>
-    <row r="58" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T57" s="10"/>
+    </row>
+    <row r="58" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="11" t="n">
         <v>46329</v>
       </c>
       <c r="B58" s="12" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C58" s="12" t="n">
         <v>12</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>267</v>
+        <v>325</v>
       </c>
       <c r="E58" s="12" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F58" s="12" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G58" s="12" t="s">
-        <v>268</v>
+        <v>326</v>
       </c>
       <c r="H58" s="12" t="s">
-        <v>274</v>
+        <v>333</v>
       </c>
       <c r="I58" s="12" t="s">
-        <v>275</v>
+        <v>334</v>
       </c>
       <c r="J58" s="12" t="s">
-        <v>271</v>
+        <v>329</v>
       </c>
       <c r="K58" s="12" t="s">
-        <v>272</v>
+        <v>330</v>
       </c>
       <c r="L58" s="12" t="s">
-        <v>276</v>
+        <v>335</v>
       </c>
       <c r="M58" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="N58" s="12"/>
+        <v>336</v>
+      </c>
+      <c r="N58" s="12" t="s">
+        <v>74</v>
+      </c>
       <c r="O58" s="12"/>
       <c r="P58" s="12"/>
       <c r="Q58" s="12"/>
       <c r="R58" s="12"/>
       <c r="S58" s="12"/>
-    </row>
-    <row r="59" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T58" s="12"/>
+    </row>
+    <row r="59" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="9" t="n">
         <v>46331</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C59" s="10" t="n">
         <v>12</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>267</v>
+        <v>325</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F59" s="10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>268</v>
+        <v>326</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>277</v>
+        <v>337</v>
       </c>
       <c r="I59" s="10" t="s">
-        <v>278</v>
+        <v>338</v>
       </c>
       <c r="J59" s="10" t="s">
-        <v>279</v>
+        <v>339</v>
       </c>
       <c r="K59" s="10" t="s">
-        <v>272</v>
+        <v>330</v>
       </c>
       <c r="L59" s="10" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="M59" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="N59" s="10"/>
+        <v>340</v>
+      </c>
+      <c r="N59" s="10" t="s">
+        <v>74</v>
+      </c>
       <c r="O59" s="10"/>
       <c r="P59" s="10"/>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
       <c r="S59" s="10"/>
-    </row>
-    <row r="60" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T59" s="10"/>
+    </row>
+    <row r="60" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="11" t="n">
         <v>46332</v>
       </c>
       <c r="B60" s="12" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C60" s="12" t="n">
         <v>12</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>267</v>
+        <v>325</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F60" s="12" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G60" s="12" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="H60" s="12" t="s">
-        <v>280</v>
+        <v>341</v>
       </c>
       <c r="I60" s="12" t="s">
-        <v>281</v>
+        <v>342</v>
       </c>
       <c r="J60" s="12" t="s">
-        <v>282</v>
+        <v>343</v>
       </c>
       <c r="K60" s="12" t="s">
-        <v>272</v>
+        <v>330</v>
       </c>
       <c r="L60" s="12" t="s">
-        <v>283</v>
+        <v>344</v>
       </c>
       <c r="M60" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="N60" s="12"/>
+        <v>345</v>
+      </c>
+      <c r="N60" s="12" t="s">
+        <v>74</v>
+      </c>
       <c r="O60" s="12"/>
       <c r="P60" s="12"/>
       <c r="Q60" s="12"/>
       <c r="R60" s="12"/>
       <c r="S60" s="12"/>
-    </row>
-    <row r="61" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T60" s="12"/>
+    </row>
+    <row r="61" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="11" t="n">
         <v>46333</v>
       </c>
       <c r="B61" s="12" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C61" s="12" t="n">
         <v>12</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>267</v>
+        <v>325</v>
       </c>
       <c r="E61" s="12" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="F61" s="12" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="G61" s="12" t="s">
-        <v>268</v>
+        <v>326</v>
       </c>
       <c r="H61" s="12" t="s">
-        <v>284</v>
+        <v>346</v>
       </c>
       <c r="I61" s="12" t="s">
-        <v>285</v>
+        <v>347</v>
       </c>
       <c r="J61" s="12" t="s">
-        <v>286</v>
+        <v>348</v>
       </c>
       <c r="K61" s="12" t="s">
-        <v>272</v>
+        <v>330</v>
       </c>
       <c r="L61" s="12" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="M61" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="N61" s="12"/>
+        <v>349</v>
+      </c>
+      <c r="N61" s="12" t="s">
+        <v>74</v>
+      </c>
       <c r="O61" s="12"/>
       <c r="P61" s="12"/>
       <c r="Q61" s="12"/>
       <c r="R61" s="12"/>
       <c r="S61" s="12"/>
-    </row>
-    <row r="62" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T61" s="12"/>
+    </row>
+    <row r="62" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="9" t="n">
         <v>46335</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C62" s="10" t="n">
         <v>13</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>267</v>
+        <v>325</v>
       </c>
       <c r="E62" s="10" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F62" s="10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G62" s="10" t="s">
-        <v>268</v>
+        <v>326</v>
       </c>
       <c r="H62" s="10" t="s">
-        <v>287</v>
+        <v>350</v>
       </c>
       <c r="I62" s="10" t="s">
-        <v>288</v>
+        <v>351</v>
       </c>
       <c r="J62" s="10" t="s">
-        <v>289</v>
+        <v>352</v>
       </c>
       <c r="K62" s="10" t="s">
-        <v>272</v>
+        <v>330</v>
       </c>
       <c r="L62" s="10" t="s">
-        <v>290</v>
+        <v>353</v>
       </c>
       <c r="M62" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="N62" s="10"/>
+        <v>354</v>
+      </c>
+      <c r="N62" s="10" t="s">
+        <v>74</v>
+      </c>
       <c r="O62" s="10"/>
       <c r="P62" s="10"/>
       <c r="Q62" s="10"/>
       <c r="R62" s="10"/>
       <c r="S62" s="10"/>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T62" s="10"/>
+    </row>
+    <row r="63" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="11" t="n">
         <v>46336</v>
       </c>
       <c r="B63" s="12" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C63" s="12" t="n">
         <v>13</v>
       </c>
       <c r="D63" s="12" t="s">
-        <v>267</v>
+        <v>325</v>
       </c>
       <c r="E63" s="12" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F63" s="12" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G63" s="12" t="s">
-        <v>268</v>
+        <v>326</v>
       </c>
       <c r="H63" s="12" t="s">
-        <v>291</v>
+        <v>355</v>
       </c>
       <c r="I63" s="12" t="s">
-        <v>292</v>
+        <v>356</v>
       </c>
       <c r="J63" s="12" t="s">
-        <v>289</v>
+        <v>352</v>
       </c>
       <c r="K63" s="12" t="s">
-        <v>272</v>
+        <v>330</v>
       </c>
       <c r="L63" s="12" t="s">
-        <v>293</v>
+        <v>357</v>
       </c>
       <c r="M63" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="N63" s="12"/>
+        <v>358</v>
+      </c>
+      <c r="N63" s="12" t="s">
+        <v>74</v>
+      </c>
       <c r="O63" s="12"/>
       <c r="P63" s="12"/>
       <c r="Q63" s="12"/>
       <c r="R63" s="12"/>
       <c r="S63" s="12"/>
-    </row>
-    <row r="64" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T63" s="12"/>
+    </row>
+    <row r="64" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="9" t="n">
         <v>46338</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C64" s="10" t="n">
         <v>13</v>
       </c>
       <c r="D64" s="10" t="s">
-        <v>267</v>
+        <v>325</v>
       </c>
       <c r="E64" s="10" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F64" s="10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G64" s="10" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H64" s="10" t="s">
-        <v>294</v>
+        <v>359</v>
       </c>
       <c r="I64" s="10" t="s">
-        <v>295</v>
+        <v>360</v>
       </c>
       <c r="J64" s="10" t="s">
-        <v>296</v>
+        <v>361</v>
       </c>
       <c r="K64" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="L64" s="10" t="s">
-        <v>297</v>
+        <v>362</v>
       </c>
       <c r="M64" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="N64" s="10"/>
+        <v>363</v>
+      </c>
+      <c r="N64" s="10" t="s">
+        <v>74</v>
+      </c>
       <c r="O64" s="10"/>
       <c r="P64" s="10"/>
       <c r="Q64" s="10"/>
       <c r="R64" s="10"/>
       <c r="S64" s="10"/>
-    </row>
-    <row r="65" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T64" s="10"/>
+    </row>
+    <row r="65" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="11" t="n">
         <v>46339</v>
       </c>
       <c r="B65" s="12" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C65" s="12" t="n">
         <v>13</v>
       </c>
       <c r="D65" s="12" t="s">
-        <v>267</v>
+        <v>325</v>
       </c>
       <c r="E65" s="12" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F65" s="12" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G65" s="12" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="H65" s="12" t="s">
-        <v>298</v>
+        <v>364</v>
       </c>
       <c r="I65" s="12" t="s">
-        <v>299</v>
+        <v>365</v>
       </c>
       <c r="J65" s="12" t="s">
-        <v>296</v>
+        <v>361</v>
       </c>
       <c r="K65" s="12" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="L65" s="12" t="s">
-        <v>300</v>
+        <v>366</v>
       </c>
       <c r="M65" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="N65" s="12"/>
+        <v>367</v>
+      </c>
+      <c r="N65" s="12" t="s">
+        <v>74</v>
+      </c>
       <c r="O65" s="12"/>
       <c r="P65" s="12"/>
       <c r="Q65" s="12"/>
       <c r="R65" s="12"/>
       <c r="S65" s="12"/>
-    </row>
-    <row r="66" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T65" s="12"/>
+    </row>
+    <row r="66" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="11" t="n">
         <v>46340</v>
       </c>
       <c r="B66" s="12" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C66" s="12" t="n">
         <v>13</v>
       </c>
       <c r="D66" s="12" t="s">
-        <v>267</v>
+        <v>325</v>
       </c>
       <c r="E66" s="12" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="F66" s="12" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="G66" s="12" t="s">
-        <v>268</v>
+        <v>326</v>
       </c>
       <c r="H66" s="12" t="s">
-        <v>301</v>
+        <v>368</v>
       </c>
       <c r="I66" s="12" t="s">
-        <v>302</v>
+        <v>369</v>
       </c>
       <c r="J66" s="12" t="s">
-        <v>303</v>
+        <v>370</v>
       </c>
       <c r="K66" s="12" t="s">
-        <v>272</v>
+        <v>330</v>
       </c>
       <c r="L66" s="12" t="s">
-        <v>266</v>
+        <v>323</v>
       </c>
       <c r="M66" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="N66" s="12"/>
+        <v>371</v>
+      </c>
+      <c r="N66" s="12" t="s">
+        <v>74</v>
+      </c>
       <c r="O66" s="12"/>
       <c r="P66" s="12"/>
       <c r="Q66" s="12"/>
       <c r="R66" s="12"/>
       <c r="S66" s="12"/>
+      <c r="T66" s="12"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M2:M66" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="N2:N66" type="list">
       <formula1>"Idea,Design,Ready,Posted"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -5042,87 +5456,87 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>304</v>
+        <v>372</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>305</v>
+        <v>373</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>306</v>
+        <v>374</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>307</v>
+        <v>375</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>308</v>
+        <v>376</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>309</v>
+        <v>377</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>310</v>
+        <v>378</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>311</v>
+        <v>379</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>312</v>
+        <v>380</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>313</v>
+        <v>381</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>314</v>
+        <v>382</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>315</v>
+        <v>383</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>316</v>
+        <v>384</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>317</v>
+        <v>385</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>193</v>
+        <v>226</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>318</v>
+        <v>386</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>319</v>
+        <v>387</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>320</v>
+        <v>388</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>321</v>
+        <v>389</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>267</v>
+        <v>325</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>322</v>
+        <v>390</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>323</v>
+        <v>391</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>324</v>
+        <v>392</v>
       </c>
     </row>
   </sheetData>
@@ -5153,87 +5567,87 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>325</v>
+        <v>393</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>326</v>
+        <v>394</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>327</v>
+        <v>395</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>328</v>
+        <v>396</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>329</v>
+        <v>397</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>330</v>
+        <v>398</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>331</v>
+        <v>399</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>332</v>
+        <v>400</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>333</v>
+        <v>401</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>334</v>
+        <v>402</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>335</v>
+        <v>403</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>336</v>
+        <v>404</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>337</v>
+        <v>405</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>338</v>
+        <v>406</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>339</v>
+        <v>407</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>340</v>
+        <v>408</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>268</v>
+        <v>326</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>341</v>
+        <v>409</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>342</v>
+        <v>410</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>343</v>
+        <v>411</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -5262,68 +5676,68 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>344</v>
+        <v>412</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>345</v>
+        <v>413</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>346</v>
+        <v>414</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>347</v>
+        <v>415</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>348</v>
+        <v>416</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>169</v>
+        <v>195</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>349</v>
+        <v>417</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>350</v>
+        <v>418</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>351</v>
+        <v>419</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>352</v>
+        <v>420</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>68</v>
+        <v>421</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>353</v>
+        <v>422</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>354</v>
+        <v>423</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>272</v>
+        <v>330</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>355</v>
+        <v>424</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>356</v>
+        <v>425</v>
       </c>
     </row>
   </sheetData>
@@ -5354,189 +5768,189 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>357</v>
+        <v>426</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>358</v>
+        <v>427</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>359</v>
+        <v>428</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>360</v>
+        <v>429</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>361</v>
+        <v>430</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>362</v>
+        <v>431</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>363</v>
+        <v>432</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>364</v>
+        <v>433</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>365</v>
+        <v>434</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>366</v>
+        <v>435</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>367</v>
+        <v>436</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>368</v>
+        <v>437</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>369</v>
+        <v>438</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>370</v>
+        <v>439</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>371</v>
+        <v>440</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>372</v>
+        <v>441</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>373</v>
+        <v>442</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>374</v>
+        <v>443</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>375</v>
+        <v>444</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>376</v>
+        <v>445</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>377</v>
+        <v>446</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>378</v>
+        <v>447</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>379</v>
+        <v>448</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>380</v>
+        <v>449</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>381</v>
+        <v>450</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>382</v>
+        <v>451</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>383</v>
+        <v>452</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>384</v>
+        <v>453</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>385</v>
+        <v>454</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>386</v>
+        <v>455</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>387</v>
+        <v>456</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>388</v>
+        <v>457</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>389</v>
+        <v>458</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>390</v>
+        <v>459</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>268</v>
+        <v>326</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>391</v>
+        <v>460</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>392</v>
+        <v>461</v>
       </c>
     </row>
   </sheetData>

--- a/strategy/ig-content-strategy.xlsx
+++ b/strategy/ig-content-strategy.xlsx
@@ -207,7 +207,8 @@
     <t xml:space="preserve">5 Botox Lies You Still Believe | The truth, from a nurse injector.</t>
   </si>
   <si>
-    <t xml:space="preserve">Half of what you have heard about Botox came from someone who saw bad work. Let's set the record straight. Which myth did you believe? Drop it below and share this with a friend who needs slide 5. ✨</t>
+    <t xml:space="preserve">Half of what you have heard about Botox came from someone who saw bad work. Let's set the record straight. Which myth did you believe? Drop it below and share this with a friend who needs slide 5. ✨
+#botox #botoxeducation #botoxmyths #preventativebotox #antiwrinkleinjections #nurseinjector #medspa #naturalbotox #botoxbeforeandafter #aestheticnurse</t>
   </si>
   <si>
     <t xml:space="preserve">DM BOTOX or link in bio</t>
@@ -237,7 +238,8 @@
     <t xml:space="preserve">Service Spotlight: Botox | Smooth, not frozen.</t>
   </si>
   <si>
-    <t xml:space="preserve">Softened lines, full expression, and nobody can tell why you look so rested. That is Botox done right. ✨</t>
+    <t xml:space="preserve">Softened lines, full expression, and nobody can tell why you look so rested. That is Botox done right. ✨
+#botox #botoxeducation #botoxmyths #preventativebotox #antiwrinkleinjections #nurseinjector #medspa #naturalbotox #botoxbeforeandafter #aestheticnurse</t>
   </si>
   <si>
     <t xml:space="preserve">DM BOTOX to book</t>
@@ -261,7 +263,8 @@
     <t xml:space="preserve">5 Red Flags at a Med Spa. Run. | Your face deserves better than a bargain.</t>
   </si>
   <si>
-    <t xml:space="preserve">A menu with no consultation, prices too good to be true, and nobody asking about your medical history. If you see these, walk away. Save this checklist before you book anywhere. 💛</t>
+    <t xml:space="preserve">A menu with no consultation, prices too good to be true, and nobody asking about your medical history. If you see these, walk away. I want you safe, even if you never book with me. Save this checklist. 💛
+#npinjector #nursepractitioner #medspalife #luxurybeauty #aestheticnurse #skincareexpert #beautyclinic #selfcare #naturalresults #honestbeauty</t>
   </si>
   <si>
     <t xml:space="preserve">Save this checklist</t>
@@ -285,7 +288,8 @@
     <t xml:space="preserve">Behind the Scenes: The Prep | Zero shortcuts. Ever.</t>
   </si>
   <si>
-    <t xml:space="preserve">Sealed products, precise dosing, clean everything. This is the part you never see, and the part that matters most. 💛</t>
+    <t xml:space="preserve">Sealed products, precise dosing, clean everything. This is the part you never see, and the part that matters most. 💛
+#npinjector #nursepractitioner #medspalife #luxurybeauty #aestheticnurse #skincareexpert #beautyclinic #selfcare #naturalresults #honestbeauty</t>
   </si>
   <si>
     <t xml:space="preserve">Book with confidence. Link in bio</t>
@@ -303,7 +307,8 @@
     <t xml:space="preserve">Quote: Great Work Is Invisible | Brand quote card.</t>
   </si>
   <si>
-    <t xml:space="preserve">Great work is invisible. Bad work is what gave Botox its reputation. Agree or disagree? 👇</t>
+    <t xml:space="preserve">Great work is invisible. Bad work is what gave Botox its reputation. Agree or disagree? 👇
+#npinjector #nursepractitioner #medspalife #luxurybeauty #aestheticnurse #skincareexpert #beautyclinic #selfcare #naturalresults #honestbeauty</t>
   </si>
   <si>
     <t xml:space="preserve">Comment below</t>
@@ -318,7 +323,8 @@
     <t xml:space="preserve">Your First Visit, Step by Step | Nervous about your first appointment? Here is exactly what happens.</t>
   </si>
   <si>
-    <t xml:space="preserve">80 percent of first-timers tell me they waited years because they did not know what to expect. Consider this your preview. Send it to the friend who keeps saying one day.</t>
+    <t xml:space="preserve">80 percent of first-timers tell me they waited years because they did not know what to expect. Consider this your preview. Send it to the friend who keeps saying one day.
+#npinjector #nursepractitioner #medspalife #luxurybeauty #aestheticnurse #skincareexpert #beautyclinic #selfcare #naturalresults #honestbeauty</t>
   </si>
   <si>
     <t xml:space="preserve">Book your consult. Link in bio</t>
@@ -333,7 +339,8 @@
     <t xml:space="preserve">3 Signs Your Injector Is Rushing You | Protect yourself before you book.</t>
   </si>
   <si>
-    <t xml:space="preserve">If your consult is shorter than your coffee order, that is a problem. Save this checklist and trust your gut.</t>
+    <t xml:space="preserve">If your consult is shorter than your coffee order, that is a problem. Save this checklist and trust your gut.
+#botox #botoxeducation #botoxmyths #preventativebotox #antiwrinkleinjections #nurseinjector #medspa #naturalbotox #botoxbeforeandafter #aestheticnurse</t>
   </si>
   <si>
     <t xml:space="preserve">Save + share this</t>
@@ -348,7 +355,8 @@
     <t xml:space="preserve">Meet NP Cleo: The Face Behind the Glow | Real education. Real results. Real care.</t>
   </si>
   <si>
-    <t xml:space="preserve">Before you trust someone with your face, you should know who they are. Here is my story, my training, and why I will always tell you the truth about what you need. 💛</t>
+    <t xml:space="preserve">Before you trust someone with your face, you should know who they are. Here is my story, my training, and why I will always tell you the truth about what you need. 💛
+#npinjector #nursepractitioner #medspalife #luxurybeauty #aestheticnurse #skincareexpert #beautyclinic #selfcare #naturalresults #honestbeauty</t>
   </si>
   <si>
     <t xml:space="preserve">Say hi in the comments</t>
@@ -363,7 +371,8 @@
     <t xml:space="preserve">Welcome to the Treatment Room | Where calm meets careful.</t>
   </si>
   <si>
-    <t xml:space="preserve">Clean, quiet, and designed for you to feel safe asking anything. Come see it in person. 💛</t>
+    <t xml:space="preserve">Clean, quiet, and designed for you to feel safe asking anything. Come see it in person. 💛
+#npinjector #nursepractitioner #medspalife #luxurybeauty #aestheticnurse #skincareexpert #beautyclinic #selfcare #naturalresults #honestbeauty</t>
   </si>
   <si>
     <t xml:space="preserve">Book a visit. Link in bio</t>
@@ -378,7 +387,8 @@
     <t xml:space="preserve">This or That: Rested vs Frozen | Engagement post.</t>
   </si>
   <si>
-    <t xml:space="preserve">When you picture your results, which one are you actually asking for? Vote below. 👇</t>
+    <t xml:space="preserve">When you picture your results, which one are you actually asking for? Vote below. 👇
+#npinjector #nursepractitioner #medspalife #luxurybeauty #aestheticnurse #skincareexpert #beautyclinic #selfcare #naturalresults #honestbeauty</t>
   </si>
   <si>
     <t xml:space="preserve">Vote in the comments</t>
@@ -393,7 +403,8 @@
     <t xml:space="preserve">Preventative Botox: When to Actually Start | Your friend who never seems to age? This is why.</t>
   </si>
   <si>
-    <t xml:space="preserve">Lines are easier to prevent than to erase. Here is how to know if your late 20s or 30s is the right time to start, and when it is genuinely too early.</t>
+    <t xml:space="preserve">Lines are easier to prevent than to erase. Here is how to know if your late 20s or 30s is the right time to start, and when it is honestly still too early. No pressure, just real timing.
+#botox #botoxeducation #botoxmyths #preventativebotox #antiwrinkleinjections #nurseinjector #medspa #naturalbotox #botoxbeforeandafter #aestheticnurse</t>
   </si>
   <si>
     <t xml:space="preserve">DM PREVENT for a consult</t>
@@ -411,7 +422,8 @@
     <t xml:space="preserve">Service Spotlight: Preventative Botox | Start before the lines do.</t>
   </si>
   <si>
-    <t xml:space="preserve">The friend who never seems to age did not find a miracle cream. She started early and kept it subtle.</t>
+    <t xml:space="preserve">The friend who never seems to age did not find a miracle cream. She started early and kept it subtle.
+#botox #botoxeducation #botoxmyths #preventativebotox #antiwrinkleinjections #nurseinjector #medspa #naturalbotox #botoxbeforeandafter #aestheticnurse</t>
   </si>
   <si>
     <t xml:space="preserve">DM PREVENT to talk</t>
@@ -426,7 +438,8 @@
     <t xml:space="preserve">What 20 Units Actually Looks Like | Unit math, finally explained.</t>
   </si>
   <si>
-    <t xml:space="preserve">You have seen the price per unit. But what does 20 units actually do? Here is the honest breakdown of dosing, areas, and why cheaper per unit is not cheaper overall.</t>
+    <t xml:space="preserve">You have seen the price per unit. But what does 20 units actually do? Here is the honest breakdown of dosing, areas, and why cheaper per unit is not cheaper overall.
+#botox #botoxeducation #botoxmyths #preventativebotox #antiwrinkleinjections #nurseinjector #medspa #naturalbotox #botoxbeforeandafter #aestheticnurse</t>
   </si>
   <si>
     <t xml:space="preserve">Save this for your consult</t>
@@ -441,7 +454,8 @@
     <t xml:space="preserve">Meet Your Injector | Board certified. Botox obsessed. Brutally honest.</t>
   </si>
   <si>
-    <t xml:space="preserve">Your face deserves a nurse practitioner who tells the truth about what you need and what you do not. Hi, I am Cleo. 💛</t>
+    <t xml:space="preserve">Your face deserves a nurse practitioner who tells the truth about what you need and what you do not. Hi, I am Cleo. 💛
+#npinjector #nursepractitioner #medspalife #luxurybeauty #aestheticnurse #skincareexpert #beautyclinic #selfcare #naturalresults #honestbeauty</t>
   </si>
   <si>
     <t xml:space="preserve">Single image: Cleo portrait + credentials hook</t>
@@ -453,7 +467,8 @@
     <t xml:space="preserve">Quote: Prevention Beats Erasing | Brand quote card.</t>
   </si>
   <si>
-    <t xml:space="preserve">Lines are easier to prevent than to erase. Save this reminder. ✨</t>
+    <t xml:space="preserve">Lines are easier to prevent than to erase. Save this reminder. ✨
+#npinjector #nursepractitioner #medspalife #luxurybeauty #aestheticnurse #skincareexpert #beautyclinic #selfcare #naturalresults #honestbeauty</t>
   </si>
   <si>
     <t xml:space="preserve">Save this</t>
@@ -468,7 +483,8 @@
     <t xml:space="preserve">Botox vs Dysport: The Real Difference | Same family. Different personalities.</t>
   </si>
   <si>
-    <t xml:space="preserve">The most Googled question in aesthetics, answered honestly. Slide 5 explains why you should never compare prices unit to unit. Save this for later. ✨</t>
+    <t xml:space="preserve">The most Googled question in aesthetics, answered honestly. Slide 5 explains why you should never compare prices unit to unit. Save this for later. ✨
+#botox #botoxeducation #botoxmyths #preventativebotox #antiwrinkleinjections #nurseinjector #medspa #naturalbotox #botoxbeforeandafter #aestheticnurse</t>
   </si>
   <si>
     <t xml:space="preserve">Book a consult. Link in bio</t>
@@ -480,7 +496,8 @@
     <t xml:space="preserve">Botox vs Dysport at a Glance | Same family. Different personalities.</t>
   </si>
   <si>
-    <t xml:space="preserve">Dysport kicks in faster and spreads wider. Botox is precise. The right one depends on your face, not the price list.</t>
+    <t xml:space="preserve">Dysport kicks in faster and spreads wider. Botox is precise. The right one depends on your face, not the price list.
+#botox #botoxeducation #botoxmyths #preventativebotox #antiwrinkleinjections #nurseinjector #medspa #naturalbotox #botoxbeforeandafter #aestheticnurse</t>
   </si>
   <si>
     <t xml:space="preserve">Full breakdown on our feed</t>
@@ -495,7 +512,8 @@
     <t xml:space="preserve">Botox Aftercare: The First 48 Hours | You got Botox. Now what?</t>
   </si>
   <si>
-    <t xml:space="preserve">The first 48 hours matter more than most people think. Here is exactly what to do, what to skip, and when to call me. Bookmark this one.</t>
+    <t xml:space="preserve">The first 48 hours matter more than most people think. Here is exactly what to do, what to skip, and when to call me. Bookmark this one.
+#botox #botoxeducation #botoxmyths #preventativebotox #antiwrinkleinjections #nurseinjector #medspa #naturalbotox #botoxbeforeandafter #aestheticnurse</t>
   </si>
   <si>
     <t xml:space="preserve">Save this guide</t>
@@ -507,7 +525,8 @@
     <t xml:space="preserve">The Face Map | Every face gets a plan.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nothing touches your skin before I map your anatomy, your movement, and your goals. Planning is the treatment.</t>
+    <t xml:space="preserve">Nothing touches your skin before I map your anatomy, your movement, and your goals. Planning is the treatment.
+#npinjector #nursepractitioner #medspalife #luxurybeauty #aestheticnurse #skincareexpert #beautyclinic #selfcare #naturalresults #honestbeauty</t>
   </si>
   <si>
     <t xml:space="preserve">Book your mapping. Link in bio</t>
@@ -522,7 +541,8 @@
     <t xml:space="preserve">FAQ: Does Botox Hurt? | Honest answer, no fluff.</t>
   </si>
   <si>
-    <t xml:space="preserve">The honest answer: less than plucking a brow. Tiny needle, seconds per area, numbing if you want it.</t>
+    <t xml:space="preserve">Honestly? Less than plucking a brow. Tiny needle, a few seconds per area, and numbing if you want it. Most people say wait, that was it?
+#npinjector #nursepractitioner #medspalife #luxurybeauty #aestheticnurse #skincareexpert #beautyclinic #selfcare #naturalresults #honestbeauty</t>
   </si>
   <si>
     <t xml:space="preserve">More questions? DM me</t>
@@ -537,7 +557,8 @@
     <t xml:space="preserve">5 Things Botox Can't Do | Honest expectations, always.</t>
   </si>
   <si>
-    <t xml:space="preserve">Botox is amazing at what it does. But it cannot do everything, and anyone who says otherwise is selling you something. Here is what it fixes and what needs a different plan.</t>
+    <t xml:space="preserve">Botox is amazing at what it does. But it cannot do everything, and anyone who says otherwise is selling you something. Here is what it fixes and what needs a different plan.
+#botox #botoxeducation #botoxmyths #preventativebotox #antiwrinkleinjections #nurseinjector #medspa #naturalbotox #botoxbeforeandafter #aestheticnurse</t>
   </si>
   <si>
     <t xml:space="preserve">Comment your questions</t>
@@ -549,7 +570,8 @@
     <t xml:space="preserve">What Botox Can't Fix | Honest expectations, always.</t>
   </si>
   <si>
-    <t xml:space="preserve">Sagging skin, volume loss, texture. Botox is not the tool for everything, and I will always tell you what is.</t>
+    <t xml:space="preserve">Sagging skin, volume loss, texture. Botox is not the tool for everything, and I would rather tell you that now than take your money and disappoint you.
+#botox #botoxeducation #botoxmyths #preventativebotox #antiwrinkleinjections #nurseinjector #medspa #naturalbotox #botoxbeforeandafter #aestheticnurse</t>
   </si>
   <si>
     <t xml:space="preserve">Single image: myth-vs-reality card</t>
@@ -561,7 +583,8 @@
     <t xml:space="preserve">Still You, Just Refreshed | You won't look done. You'll look rested.</t>
   </si>
   <si>
-    <t xml:space="preserve">The 2026 standard is not transformation. It is restoration. My goal is that people ask if you have been on vacation, not what you had done. 💛</t>
+    <t xml:space="preserve">The 2026 standard is not transformation. It is restoration. My goal is that people ask if you have been on vacation, not what you had done. 💛
+#npinjector #nursepractitioner #medspalife #luxurybeauty #aestheticnurse #skincareexpert #beautyclinic #selfcare #naturalresults #honestbeauty</t>
   </si>
   <si>
     <t xml:space="preserve">DM GLOW to start</t>
@@ -576,7 +599,8 @@
     <t xml:space="preserve">Myth vs Truth: The Frozen Face | The classic fear, debunked.</t>
   </si>
   <si>
-    <t xml:space="preserve">MYTH: Botox freezes your face. TRUTH: correct dosing softens movement while you keep every expression that makes you, you.</t>
+    <t xml:space="preserve">MYTH: Botox freezes your face. TRUTH: correct dosing softens movement while you keep every expression that makes you, you.
+#botox #botoxeducation #botoxmyths #preventativebotox #antiwrinkleinjections #nurseinjector #medspa #naturalbotox #botoxbeforeandafter #aestheticnurse</t>
   </si>
   <si>
     <t xml:space="preserve">Share with a friend</t>
@@ -591,7 +615,8 @@
     <t xml:space="preserve">Client Words: Natural Results | Testimonial card.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nobody could tell. They just kept saying I looked happy and rested. That is the whole goal. 💛 (Shared with permission.)</t>
+    <t xml:space="preserve">Nobody could tell. They just kept saying I looked happy and rested. That is the whole goal. 💛 (Shared with permission.)
+#npinjector #nursepractitioner #medspalife #luxurybeauty #aestheticnurse #skincareexpert #beautyclinic #selfcare #naturalresults #honestbeauty</t>
   </si>
   <si>
     <t xml:space="preserve">Your turn. Link in bio</t>
@@ -606,7 +631,8 @@
     <t xml:space="preserve">Botox or Filler? You Might Be Asking for the Wrong One | Lines or volume? They are not the same problem.</t>
   </si>
   <si>
-    <t xml:space="preserve">Half the DMs I get ask for the wrong treatment. Here is the simple way to know whether your concern is about movement or volume, and what that means for your plan.</t>
+    <t xml:space="preserve">Half the DMs I get ask for the wrong treatment. Here is the simple way to know whether your concern is about movement or volume, and what that means for your plan.
+#dermalfiller #lipfiller #cheekfiller #naturalfiller #facialbalancing #lipfillernatural #aestheticnurse #medspa #fillerjourney #lipgoals</t>
   </si>
   <si>
     <t xml:space="preserve">DM CONSULT and I will help</t>
@@ -621,7 +647,8 @@
     <t xml:space="preserve">Lines vs Volume | Which one is your concern?</t>
   </si>
   <si>
-    <t xml:space="preserve">Smile in the mirror. Movement lines need Botox. Lost volume needs filler. The answer decides your plan.</t>
+    <t xml:space="preserve">Smile in the mirror. Movement lines need Botox. Lost volume needs filler. The answer decides your plan.
+#dermalfiller #lipfiller #cheekfiller #naturalfiller #facialbalancing #lipfillernatural #aestheticnurse #medspa #fillerjourney #lipgoals</t>
   </si>
   <si>
     <t xml:space="preserve">DM CONSULT for help</t>
@@ -636,7 +663,8 @@
     <t xml:space="preserve">Ask NP Cleo: Your Questions, Answered Honestly | You asked. I answered. No filter.</t>
   </si>
   <si>
-    <t xml:space="preserve">This month you sent amazing questions. Here are the honest answers, including the one nobody else will give you about cheap Botox. Keep them coming. 👇</t>
+    <t xml:space="preserve">This month you sent amazing questions. Here are the honest answers, including the one nobody else will give you about cheap Botox. Keep them coming. 👇
+#npinjector #nursepractitioner #medspalife #luxurybeauty #aestheticnurse #skincareexpert #beautyclinic #selfcare #naturalresults #honestbeauty</t>
   </si>
   <si>
     <t xml:space="preserve">Drop your question below</t>
@@ -651,7 +679,8 @@
     <t xml:space="preserve">Your DMs, Answered | The question everyone asks quietly.</t>
   </si>
   <si>
-    <t xml:space="preserve">You asked: will people know I had work done? Honest answer: only if you want them to. Subtle is the standard here.</t>
+    <t xml:space="preserve">You asked: will people know I had work done? Honest answer: only if you want them to. Subtle is the standard here.
+#npinjector #nursepractitioner #medspalife #luxurybeauty #aestheticnurse #skincareexpert #beautyclinic #selfcare #naturalresults #honestbeauty</t>
   </si>
   <si>
     <t xml:space="preserve">Send your question</t>
@@ -666,7 +695,8 @@
     <t xml:space="preserve">Poll: What Should NP Cleo Cover Next? | Audience chooses next month's content.</t>
   </si>
   <si>
-    <t xml:space="preserve">October is filler month. What do you want the truth about first: lips, cheeks, or under eyes? Vote. 👇</t>
+    <t xml:space="preserve">October is filler month. What do you want the truth about first: lips, cheeks, or under eyes? Vote. 👇
+#npinjector #nursepractitioner #medspalife #luxurybeauty #aestheticnurse #skincareexpert #beautyclinic #selfcare #naturalresults #honestbeauty</t>
   </si>
   <si>
     <t xml:space="preserve">Vote in comments</t>
@@ -681,7 +711,8 @@
     <t xml:space="preserve">How Long Does Botox Really Last? | The honest timeline, month by month.</t>
   </si>
   <si>
-    <t xml:space="preserve">Anyone promising six months is overpromising. Here is the real timeline, what makes it fade faster, and how to make results last longer.</t>
+    <t xml:space="preserve">Anyone promising six months is overpromising. Here is the real timeline, what makes it fade faster, and how to make results last longer.
+#botox #botoxeducation #botoxmyths #preventativebotox #antiwrinkleinjections #nurseinjector #medspa #naturalbotox #botoxbeforeandafter #aestheticnurse</t>
   </si>
   <si>
     <t xml:space="preserve">Save this timeline</t>
@@ -696,7 +727,8 @@
     <t xml:space="preserve">The 3-Month Botox Timeline | Week by week, what to expect.</t>
   </si>
   <si>
-    <t xml:space="preserve">Day 3 it starts. Week 2 it settles. Month 3 it softens. Save this so you know exactly what is normal.</t>
+    <t xml:space="preserve">Day 3 it starts. Week 2 it settles. Month 3 it softens. Save this so you know exactly what is normal.
+#botox #botoxeducation #botoxmyths #preventativebotox #antiwrinkleinjections #nurseinjector #medspa #naturalbotox #botoxbeforeandafter #aestheticnurse</t>
   </si>
   <si>
     <t xml:space="preserve">Single image: timeline infographic card</t>
@@ -711,7 +743,8 @@
     <t xml:space="preserve">Why We Sometimes Say No | A provider who says yes to everyone is a red flag.</t>
   </si>
   <si>
-    <t xml:space="preserve">I have turned people away, and they thanked me later. Here is why honest candidacy matters and what it says about any provider who never says no.</t>
+    <t xml:space="preserve">I have turned people away, and they thanked me later. Here is why honest candidacy matters and what it says about any provider who never says no.
+#npinjector #nursepractitioner #medspalife #luxurybeauty #aestheticnurse #skincareexpert #beautyclinic #selfcare #naturalresults #honestbeauty</t>
   </si>
   <si>
     <t xml:space="preserve">Book an honest consult</t>
@@ -723,7 +756,8 @@
     <t xml:space="preserve">What I Tell Every First-Timer | The pep talk before every first appointment.</t>
   </si>
   <si>
-    <t xml:space="preserve">You do not need to know the treatment names. You just need to show up honest about your goals. I handle the rest. 💛</t>
+    <t xml:space="preserve">You do not need to know the treatment names. You just need to show up honest about your goals. I handle the rest. 💛
+#npinjector #nursepractitioner #medspalife #luxurybeauty #aestheticnurse #skincareexpert #beautyclinic #selfcare #naturalresults #honestbeauty</t>
   </si>
   <si>
     <t xml:space="preserve">Book your first visit</t>
@@ -738,7 +772,8 @@
     <t xml:space="preserve">Quote: No Is Protection | Brand quote card.</t>
   </si>
   <si>
-    <t xml:space="preserve">An honest provider will sometimes tell you no. That is protection, not rejection. ✨</t>
+    <t xml:space="preserve">An honest provider will sometimes tell you no. That is protection, not rejection. ✨
+#npinjector #nursepractitioner #medspalife #luxurybeauty #aestheticnurse #skincareexpert #beautyclinic #selfcare #naturalresults #honestbeauty</t>
   </si>
   <si>
     <t xml:space="preserve">Share this</t>
@@ -750,7 +785,8 @@
     <t xml:space="preserve">Filler Won't Make You Look Fake. Bad Technique Does. | The fear is real. The cause is not what you think.</t>
   </si>
   <si>
-    <t xml:space="preserve">Every overdone face you have seen came from heavy hands, not from filler itself. Great work is invisible. You have seen it a hundred times without knowing. ✨</t>
+    <t xml:space="preserve">Every overdone face you have seen came from heavy hands, not from filler itself. Great work is invisible. You have seen it a hundred times without knowing. ✨
+#dermalfiller #lipfiller #cheekfiller #naturalfiller #facialbalancing #lipfillernatural #aestheticnurse #medspa #fillerjourney #lipgoals</t>
   </si>
   <si>
     <t xml:space="preserve">DM FILLER for a consult</t>
@@ -765,7 +801,8 @@
     <t xml:space="preserve">Service Spotlight: Dermal Filler | Volume where you lost it. Nowhere else.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filler is not about changing your face. It is about restoring what time quietly took. October is filler month. 👀</t>
+    <t xml:space="preserve">Filler is not about changing your face. It is about restoring what time quietly took. October is filler month. 👀
+#dermalfiller #lipfiller #cheekfiller #naturalfiller #facialbalancing #lipfillernatural #aestheticnurse #medspa #fillerjourney #lipgoals</t>
   </si>
   <si>
     <t xml:space="preserve">DM FILLER to start</t>
@@ -780,7 +817,8 @@
     <t xml:space="preserve">Lip Filler: Natural vs Overdone | The difference is the injector.</t>
   </si>
   <si>
-    <t xml:space="preserve">Soft, balanced, still you. Here is what separates natural lip results from the duck lips everyone fears, and the questions to ask before anyone touches your lips.</t>
+    <t xml:space="preserve">Soft, balanced, still you. Here is what separates natural lip results from the duck lips everyone fears, and the questions to ask before anyone touches your lips.
+#dermalfiller #lipfiller #cheekfiller #naturalfiller #facialbalancing #lipfillernatural #aestheticnurse #medspa #fillerjourney #lipgoals</t>
   </si>
   <si>
     <t xml:space="preserve">Save before you book anywhere</t>
@@ -795,7 +833,8 @@
     <t xml:space="preserve">Inside the Filler Appointment | Planned to the last drop.</t>
   </si>
   <si>
-    <t xml:space="preserve">Cannulas, numbing, and a plan drawn before we start. This is what careful looks like.</t>
+    <t xml:space="preserve">Cannulas, numbing, and a plan drawn before we start. This is what careful looks like.
+#dermalfiller #lipfiller #cheekfiller #naturalfiller #facialbalancing #lipfillernatural #aestheticnurse #medspa #fillerjourney #lipgoals</t>
   </si>
   <si>
     <t xml:space="preserve">Follow for filler month</t>
@@ -810,7 +849,8 @@
     <t xml:space="preserve">Quote: Subtle Is the New Dramatic | Brand quote card.</t>
   </si>
   <si>
-    <t xml:space="preserve">Subtle is the new dramatic. The best work whispers. 💛</t>
+    <t xml:space="preserve">Subtle is the new dramatic. The best work whispers. 💛
+#npinjector #nursepractitioner #medspalife #luxurybeauty #aestheticnurse #skincareexpert #beautyclinic #selfcare #naturalresults #honestbeauty</t>
   </si>
   <si>
     <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-10-quote-subtle-is-the-new</t>
@@ -819,7 +859,8 @@
     <t xml:space="preserve">Cheek Filler: The Secret Nobody Talks About | The treatment behind the best natural glow-ups.</t>
   </si>
   <si>
-    <t xml:space="preserve">Everyone asks about lips. But cheek filler is quietly behind some of the most natural transformations you have seen. Here is how facial balancing works.</t>
+    <t xml:space="preserve">Everyone asks about lips. But cheek filler is quietly behind some of the most natural transformations you have seen. Here is how facial balancing works.
+#dermalfiller #lipfiller #cheekfiller #naturalfiller #facialbalancing #lipfillernatural #aestheticnurse #medspa #fillerjourney #lipgoals</t>
   </si>
   <si>
     <t xml:space="preserve">DM CHEEKS to learn more</t>
@@ -831,7 +872,8 @@
     <t xml:space="preserve">Service Spotlight: Cheek Filler | The lift nobody talks about.</t>
   </si>
   <si>
-    <t xml:space="preserve">Lifted, refreshed, never puffy. Cheek filler is quietly behind the most natural glow-ups you have seen.</t>
+    <t xml:space="preserve">Lifted, refreshed, never puffy. Cheek filler is quietly behind the most natural glow-ups you have seen.
+#dermalfiller #lipfiller #cheekfiller #naturalfiller #facialbalancing #lipfillernatural #aestheticnurse #medspa #fillerjourney #lipgoals</t>
   </si>
   <si>
     <t xml:space="preserve">Single image: cheek treatment photo + hook</t>
@@ -843,7 +885,8 @@
     <t xml:space="preserve">Is Filler Right for You? An Honest Checklist | Not everyone is a candidate. Here is how to know.</t>
   </si>
   <si>
-    <t xml:space="preserve">An honest provider will sometimes tell you not yet. Run through this checklist before your consult and you will walk in knowing exactly what to ask.</t>
+    <t xml:space="preserve">An honest provider will sometimes tell you not yet. Run through this checklist before your consult and you will walk in knowing exactly what to ask.
+#dermalfiller #lipfiller #cheekfiller #naturalfiller #facialbalancing #lipfillernatural #aestheticnurse #medspa #fillerjourney #lipgoals</t>
   </si>
   <si>
     <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-15-is-filler-right-for-you</t>
@@ -852,7 +895,8 @@
     <t xml:space="preserve">Facial Balancing 101 | One plan beats three syringes.</t>
   </si>
   <si>
-    <t xml:space="preserve">One syringe in the right place beats three in the wrong ones. Balance first, volume second. Always.</t>
+    <t xml:space="preserve">One syringe in the right place beats three in the wrong ones. Balance first, volume second. Always.
+#dermalfiller #lipfiller #cheekfiller #naturalfiller #facialbalancing #lipfillernatural #aestheticnurse #medspa #fillerjourney #lipgoals</t>
   </si>
   <si>
     <t xml:space="preserve">Book a balancing consult</t>
@@ -867,7 +911,8 @@
     <t xml:space="preserve">FAQ: How Much Filler Do I Need? | The honest answer.</t>
   </si>
   <si>
-    <t xml:space="preserve">Less than Instagram makes you think. Most natural results start with one syringe or less. Here is why.</t>
+    <t xml:space="preserve">Less than Instagram makes you think. Most natural results start with one syringe or less. Here is why.
+#npinjector #nursepractitioner #medspalife #luxurybeauty #aestheticnurse #skincareexpert #beautyclinic #selfcare #naturalresults #honestbeauty</t>
   </si>
   <si>
     <t xml:space="preserve">More FAQs? DM me</t>
@@ -879,7 +924,8 @@
     <t xml:space="preserve">Filler Dissolves. Here Is the Real Timeline. | What they do not tell you about longevity.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filler is not forever, and that is a feature, not a flaw. Here is how long each area really lasts and what maintenance actually looks like.</t>
+    <t xml:space="preserve">Filler is not forever, and honestly, that is a good thing. Here is how long each area really lasts and what keeping it up actually looks like.
+#dermalfiller #lipfiller #cheekfiller #naturalfiller #facialbalancing #lipfillernatural #aestheticnurse #medspa #fillerjourney #lipgoals</t>
   </si>
   <si>
     <t xml:space="preserve">Book your plan. Link in bio</t>
@@ -894,7 +940,8 @@
     <t xml:space="preserve">The Filler Timeline | What happens as it fades.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filler does not vanish overnight and you will not deflate. It softens slowly, on a schedule you can plan around.</t>
+    <t xml:space="preserve">Filler does not vanish overnight and you will not deflate. It softens slowly, on a schedule you can plan around.
+#dermalfiller #lipfiller #cheekfiller #naturalfiller #facialbalancing #lipfillernatural #aestheticnurse #medspa #fillerjourney #lipgoals</t>
   </si>
   <si>
     <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-20-the-filler-timeline</t>
@@ -903,7 +950,8 @@
     <t xml:space="preserve">Lip Filler Aftercare: Your First Week | Swelling is normal. Panic is optional.</t>
   </si>
   <si>
-    <t xml:space="preserve">Day 1 looks different from day 7. Here is the honest day-by-day so you know exactly what is normal and when to reach out. Save this before your appointment.</t>
+    <t xml:space="preserve">Day 1 looks different from day 7. Here is the honest day-by-day so you know exactly what is normal and when to reach out. Save this before your appointment.
+#dermalfiller #lipfiller #cheekfiller #naturalfiller #facialbalancing #lipfillernatural #aestheticnurse #medspa #fillerjourney #lipgoals</t>
   </si>
   <si>
     <t xml:space="preserve">https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-22-lip-filler-aftercare-your-first</t>
@@ -912,7 +960,8 @@
     <t xml:space="preserve">Aftercare Essentials | Save this for after your appointment.</t>
   </si>
   <si>
-    <t xml:space="preserve">Ice, no gym for 24 hours, sleep on your back, and message me with anything. That is it. Save this. ✨</t>
+    <t xml:space="preserve">Ice, no gym for 24 hours, sleep on your back, and message me with anything. That is it. Save this. ✨
+#dermalfiller #lipfiller #cheekfiller #naturalfiller #facialbalancing #lipfillernatural #aestheticnurse #medspa #fillerjourney #lipgoals</t>
   </si>
   <si>
     <t xml:space="preserve">Save + share</t>
@@ -927,7 +976,8 @@
     <t xml:space="preserve">Client Words: The Lip Glow-Up | Testimonial card.</t>
   </si>
   <si>
-    <t xml:space="preserve">I finally got my lips done and nobody said filler. They said I looked prettier and could not say why. (Shared with permission.) 💛</t>
+    <t xml:space="preserve">I finally got my lips done and nobody said filler. They said I looked prettier and could not say why. (Shared with permission.) 💛
+#npinjector #nursepractitioner #medspalife #luxurybeauty #aestheticnurse #skincareexpert #beautyclinic #selfcare #naturalresults #honestbeauty</t>
   </si>
   <si>
     <t xml:space="preserve">Your turn. DM FILLER</t>
@@ -942,7 +992,8 @@
     <t xml:space="preserve">5 Filler Lies You Still Believe | The sequel you asked for.</t>
   </si>
   <si>
-    <t xml:space="preserve">You loved the Botox edition, so here is the filler truth round. Slide 4 is the one that surprises everyone. Share it with your group chat. ✨</t>
+    <t xml:space="preserve">You loved the Botox edition, so here is the filler truth round. Slide 4 is the one that surprises everyone. Share it with your group chat. ✨
+#dermalfiller #lipfiller #cheekfiller #naturalfiller #facialbalancing #lipfillernatural #aestheticnurse #medspa #fillerjourney #lipgoals</t>
   </si>
   <si>
     <t xml:space="preserve">Design in editorial template. Sequel to Botox lies</t>
@@ -954,7 +1005,8 @@
     <t xml:space="preserve">Myth vs Truth: Filler Edition | The one everyone believes.</t>
   </si>
   <si>
-    <t xml:space="preserve">MYTH: filler stretches your lips forever. TRUTH: treated well, your lips return to baseline as filler softens.</t>
+    <t xml:space="preserve">MYTH: filler stretches your lips forever. TRUTH: treated well, your lips return to baseline as filler softens.
+#dermalfiller #lipfiller #cheekfiller #naturalfiller #facialbalancing #lipfillernatural #aestheticnurse #medspa #fillerjourney #lipgoals</t>
   </si>
   <si>
     <t xml:space="preserve">Full carousel on our feed</t>
@@ -966,7 +1018,8 @@
     <t xml:space="preserve">Facial Balancing: Why We Treat Faces, Not Lines | Chasing lines is old school.</t>
   </si>
   <si>
-    <t xml:space="preserve">Great aesthetics looks at the whole face: proportions, balance, harmony. Here is why the best results come from a plan, not a single syringe.</t>
+    <t xml:space="preserve">Great aesthetics looks at the whole face: proportions, balance, harmony. Here is why the best results come from a plan, not a single syringe.
+#dermalfiller #lipfiller #cheekfiller #naturalfiller #facialbalancing #lipfillernatural #aestheticnurse #medspa #fillerjourney #lipgoals</t>
   </si>
   <si>
     <t xml:space="preserve">DM BALANCE for a consult</t>
@@ -978,7 +1031,8 @@
     <t xml:space="preserve">Faces, Not Lines | The philosophy behind natural results.</t>
   </si>
   <si>
-    <t xml:space="preserve">Chasing individual lines is old school. Balance and harmony are why my patients look rested instead of done.</t>
+    <t xml:space="preserve">Chasing individual lines is old school. Balance and harmony are why my patients look rested instead of done.
+#dermalfiller #lipfiller #cheekfiller #naturalfiller #facialbalancing #lipfillernatural #aestheticnurse #medspa #fillerjourney #lipgoals</t>
   </si>
   <si>
     <t xml:space="preserve">Single image: philosophy card + portrait</t>
@@ -990,7 +1044,8 @@
     <t xml:space="preserve">Ask Anything: Filler Edition | Engagement post.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filler month is almost over. Drop every remaining question below and I will answer all of them. No judgment. 👇</t>
+    <t xml:space="preserve">Filler month is almost over. Drop every remaining question below and I will answer all of them. No judgment. 👇
+#npinjector #nursepractitioner #medspalife #luxurybeauty #aestheticnurse #skincareexpert #beautyclinic #selfcare #naturalresults #honestbeauty</t>
   </si>
   <si>
     <t xml:space="preserve">Comment your question</t>
@@ -1011,7 +1066,8 @@
     <t xml:space="preserve">Rested by the Holidays: Your Treatment Timeline | Party season is closer than you think.</t>
   </si>
   <si>
-    <t xml:space="preserve">Botox needs 2 weeks to settle. Filler needs up to 4. If you want to glow in the December photos, here is exactly when to book each treatment. 🗓️</t>
+    <t xml:space="preserve">Botox needs 2 weeks to settle. Filler needs up to 4. If you want to glow in the December photos, here is exactly when to book each treatment. 🗓️
+#holidayglow #treatyourself #giftcertificate #bookyourappointment #medspaspecial #glowupseason #selfcaregift #luxuryselfcare #holidayready #giftideas</t>
   </si>
   <si>
     <t xml:space="preserve">Book now. Link in bio</t>
@@ -1029,7 +1085,8 @@
     <t xml:space="preserve">Holiday Countdown: Book by These Dates | Work backwards from party season.</t>
   </si>
   <si>
-    <t xml:space="preserve">Botox needs 2 weeks. Filler needs 4. If you want to glow in the December photos, these are your deadlines. 🗓️</t>
+    <t xml:space="preserve">Botox needs 2 weeks. Filler needs 4. If you want to glow in the December photos, these are your deadlines. 🗓️
+#holidayglow #treatyourself #giftcertificate #bookyourappointment #medspaspecial #glowupseason #selfcaregift #luxuryselfcare #holidayready #giftideas</t>
   </si>
   <si>
     <t xml:space="preserve">Single image: countdown-dates card</t>
@@ -1041,7 +1098,8 @@
     <t xml:space="preserve">Party Season Prep: What to Book and When | Your holiday glow, planned backwards.</t>
   </si>
   <si>
-    <t xml:space="preserve">Work back from your event date and nothing is rushed, nothing is swollen, and everything looks like you. Here is the smart booking order.</t>
+    <t xml:space="preserve">Work back from your event date and nothing is rushed, nothing is swollen, and everything looks like you. Here is the smart booking order.
+#holidayglow #treatyourself #giftcertificate #bookyourappointment #medspaspecial #glowupseason #selfcaregift #luxuryselfcare #holidayready #giftideas</t>
   </si>
   <si>
     <t xml:space="preserve">DM HOLIDAY to book</t>
@@ -1053,7 +1111,8 @@
     <t xml:space="preserve">The Clinic Is Holiday Ready | Glow-up season is officially open.</t>
   </si>
   <si>
-    <t xml:space="preserve">The calendar is filling and the season is here. Your December self will thank your November self. ✨</t>
+    <t xml:space="preserve">The calendar is filling and the season is here. Your December self will thank your November self. ✨
+#holidayglow #treatyourself #giftcertificate #bookyourappointment #medspaspecial #glowupseason #selfcaregift #luxuryselfcare #holidayready #giftideas</t>
   </si>
   <si>
     <t xml:space="preserve">Book your spot</t>
@@ -1068,7 +1127,8 @@
     <t xml:space="preserve">Quote: Book the Appointment | Seasonal self-care push.</t>
   </si>
   <si>
-    <t xml:space="preserve">You cannot pour from an empty cup. Book the appointment. Take the hour. You have earned it. 💛</t>
+    <t xml:space="preserve">You cannot pour from an empty cup. Book the appointment. Take the hour. You have earned it. 💛
+#holidayglow #treatyourself #giftcertificate #bookyourappointment #medspaspecial #glowupseason #selfcaregift #luxuryselfcare #holidayready #giftideas</t>
   </si>
   <si>
     <t xml:space="preserve">Link in bio</t>
@@ -1080,7 +1140,8 @@
     <t xml:space="preserve">The Gift of Glow: Gift Certificates Are Here | The present nobody returns.</t>
   </si>
   <si>
-    <t xml:space="preserve">Give the people you love something they actually want. Luxury Beauty gift certificates are available in any amount, wrapped and ready. 🎁</t>
+    <t xml:space="preserve">Give the people you love something they actually want. Luxury Beauty gift certificates are available in any amount, wrapped and ready. 🎁
+#holidayglow #treatyourself #giftcertificate #bookyourappointment #medspaspecial #glowupseason #selfcaregift #luxuryselfcare #holidayready #giftideas</t>
   </si>
   <si>
     <t xml:space="preserve">DM GIFT to order</t>
@@ -1095,7 +1156,8 @@
     <t xml:space="preserve">Gift Certificates Are Here | The present nobody returns.</t>
   </si>
   <si>
-    <t xml:space="preserve">In any amount, wrapped and beautiful. Give the people you love something they actually want. 🎁</t>
+    <t xml:space="preserve">In any amount, wrapped and beautiful. Give the people you love something they actually want. 🎁
+#holidayglow #treatyourself #giftcertificate #bookyourappointment #medspaspecial #glowupseason #selfcaregift #luxuryselfcare #holidayready #giftideas</t>
   </si>
   <si>
     <t xml:space="preserve">Single image: gift certificate photo + hook</t>
@@ -1107,7 +1169,8 @@
     <t xml:space="preserve">3 Months of Honest Answers: The Recap | Real education. Real results. Thank you.</t>
   </si>
   <si>
-    <t xml:space="preserve">Since August we have busted myths, answered your questions, and kept every promise about natural results. Here are the posts you loved most, in case you missed one. 💛</t>
+    <t xml:space="preserve">Since August we have busted myths, answered your questions, and kept every promise about natural results. Here are the posts you loved most, in case you missed one. 💛
+#npinjector #nursepractitioner #medspalife #luxurybeauty #aestheticnurse #skincareexpert #beautyclinic #selfcare #naturalresults #honestbeauty</t>
   </si>
   <si>
     <t xml:space="preserve">Follow for what is next</t>
@@ -1122,7 +1185,8 @@
     <t xml:space="preserve">Thank You: 3 Months of Honest Aesthetics | Gratitude post.</t>
   </si>
   <si>
-    <t xml:space="preserve">Since August you have asked incredible questions and trusted us with the answers. Here is to honest aesthetics. Thank you. 💛</t>
+    <t xml:space="preserve">Since August you have asked incredible questions and trusted us with the answers. Here is to honest aesthetics. Thank you. 💛
+#npinjector #nursepractitioner #medspalife #luxurybeauty #aestheticnurse #skincareexpert #beautyclinic #selfcare #naturalresults #honestbeauty</t>
   </si>
   <si>
     <t xml:space="preserve">Single image: team or Cleo photo + thank you overlay</t>
@@ -1134,7 +1198,8 @@
     <t xml:space="preserve">Tag Someone Who Deserves a Glow-Up Gift | Engagement + promo close.</t>
   </si>
   <si>
-    <t xml:space="preserve">Know someone who never treats themselves? Tag them below. We will take care of the rest. 🎁</t>
+    <t xml:space="preserve">Know someone who never treats themselves? Tag them below. We will take care of the rest. 🎁
+#holidayglow #treatyourself #giftcertificate #bookyourappointment #medspaspecial #glowupseason #selfcaregift #luxuryselfcare #holidayready #giftideas</t>
   </si>
   <si>
     <t xml:space="preserve">Tag a friend</t>
@@ -2172,7 +2237,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="n">
         <v>46251</v>
       </c>
@@ -2222,7 +2287,7 @@
       <c r="S2" s="10"/>
       <c r="T2" s="10"/>
     </row>
-    <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="n">
         <v>46252</v>
       </c>
@@ -2272,7 +2337,7 @@
       <c r="S3" s="12"/>
       <c r="T3" s="12"/>
     </row>
-    <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="n">
         <v>46254</v>
       </c>
@@ -2322,7 +2387,7 @@
       <c r="S4" s="10"/>
       <c r="T4" s="10"/>
     </row>
-    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="n">
         <v>46255</v>
       </c>
@@ -2372,7 +2437,7 @@
       <c r="S5" s="12"/>
       <c r="T5" s="12"/>
     </row>
-    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="n">
         <v>46256</v>
       </c>
@@ -2422,7 +2487,7 @@
       <c r="S6" s="12"/>
       <c r="T6" s="12"/>
     </row>
-    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="n">
         <v>46258</v>
       </c>
@@ -2472,7 +2537,7 @@
       <c r="S7" s="10"/>
       <c r="T7" s="10"/>
     </row>
-    <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="n">
         <v>46259</v>
       </c>
@@ -2522,7 +2587,7 @@
       <c r="S8" s="12"/>
       <c r="T8" s="12"/>
     </row>
-    <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="n">
         <v>46261</v>
       </c>
@@ -2572,7 +2637,7 @@
       <c r="S9" s="10"/>
       <c r="T9" s="10"/>
     </row>
-    <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="n">
         <v>46262</v>
       </c>
@@ -2622,7 +2687,7 @@
       <c r="S10" s="12"/>
       <c r="T10" s="12"/>
     </row>
-    <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="n">
         <v>46263</v>
       </c>
@@ -2672,7 +2737,7 @@
       <c r="S11" s="12"/>
       <c r="T11" s="12"/>
     </row>
-    <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="n">
         <v>46265</v>
       </c>
@@ -2722,7 +2787,7 @@
       <c r="S12" s="10"/>
       <c r="T12" s="10"/>
     </row>
-    <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="n">
         <v>46266</v>
       </c>
@@ -2772,7 +2837,7 @@
       <c r="S13" s="12"/>
       <c r="T13" s="12"/>
     </row>
-    <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="n">
         <v>46268</v>
       </c>
@@ -2822,7 +2887,7 @@
       <c r="S14" s="10"/>
       <c r="T14" s="10"/>
     </row>
-    <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="n">
         <v>46269</v>
       </c>
@@ -2872,7 +2937,7 @@
       <c r="S15" s="12"/>
       <c r="T15" s="12"/>
     </row>
-    <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="n">
         <v>46270</v>
       </c>
@@ -2922,7 +2987,7 @@
       <c r="S16" s="12"/>
       <c r="T16" s="12"/>
     </row>
-    <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="n">
         <v>46272</v>
       </c>
@@ -2972,7 +3037,7 @@
       <c r="S17" s="10"/>
       <c r="T17" s="10"/>
     </row>
-    <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="n">
         <v>46273</v>
       </c>
@@ -3022,7 +3087,7 @@
       <c r="S18" s="12"/>
       <c r="T18" s="12"/>
     </row>
-    <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="n">
         <v>46275</v>
       </c>
@@ -3072,7 +3137,7 @@
       <c r="S19" s="10"/>
       <c r="T19" s="10"/>
     </row>
-    <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="n">
         <v>46276</v>
       </c>
@@ -3122,7 +3187,7 @@
       <c r="S20" s="12"/>
       <c r="T20" s="12"/>
     </row>
-    <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="n">
         <v>46277</v>
       </c>
@@ -3172,7 +3237,7 @@
       <c r="S21" s="12"/>
       <c r="T21" s="12"/>
     </row>
-    <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="n">
         <v>46279</v>
       </c>
@@ -3222,7 +3287,7 @@
       <c r="S22" s="10"/>
       <c r="T22" s="10"/>
     </row>
-    <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="n">
         <v>46280</v>
       </c>
@@ -3272,7 +3337,7 @@
       <c r="S23" s="12"/>
       <c r="T23" s="12"/>
     </row>
-    <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="9" t="n">
         <v>46282</v>
       </c>
@@ -3322,7 +3387,7 @@
       <c r="S24" s="10"/>
       <c r="T24" s="10"/>
     </row>
-    <row r="25" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="n">
         <v>46283</v>
       </c>
@@ -3372,7 +3437,7 @@
       <c r="S25" s="12"/>
       <c r="T25" s="12"/>
     </row>
-    <row r="26" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="n">
         <v>46284</v>
       </c>
@@ -3422,7 +3487,7 @@
       <c r="S26" s="12"/>
       <c r="T26" s="12"/>
     </row>
-    <row r="27" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="n">
         <v>46286</v>
       </c>
@@ -3472,7 +3537,7 @@
       <c r="S27" s="10"/>
       <c r="T27" s="10"/>
     </row>
-    <row r="28" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="n">
         <v>46287</v>
       </c>
@@ -3522,7 +3587,7 @@
       <c r="S28" s="12"/>
       <c r="T28" s="12"/>
     </row>
-    <row r="29" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="9" t="n">
         <v>46289</v>
       </c>
@@ -3572,7 +3637,7 @@
       <c r="S29" s="10"/>
       <c r="T29" s="10"/>
     </row>
-    <row r="30" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="n">
         <v>46290</v>
       </c>
@@ -3622,7 +3687,7 @@
       <c r="S30" s="12"/>
       <c r="T30" s="12"/>
     </row>
-    <row r="31" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="11" t="n">
         <v>46291</v>
       </c>
@@ -3672,7 +3737,7 @@
       <c r="S31" s="12"/>
       <c r="T31" s="12"/>
     </row>
-    <row r="32" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="9" t="n">
         <v>46293</v>
       </c>
@@ -3722,7 +3787,7 @@
       <c r="S32" s="10"/>
       <c r="T32" s="10"/>
     </row>
-    <row r="33" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="11" t="n">
         <v>46294</v>
       </c>
@@ -3772,7 +3837,7 @@
       <c r="S33" s="12"/>
       <c r="T33" s="12"/>
     </row>
-    <row r="34" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="9" t="n">
         <v>46296</v>
       </c>
@@ -3822,7 +3887,7 @@
       <c r="S34" s="10"/>
       <c r="T34" s="10"/>
     </row>
-    <row r="35" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="11" t="n">
         <v>46297</v>
       </c>
@@ -3872,7 +3937,7 @@
       <c r="S35" s="12"/>
       <c r="T35" s="12"/>
     </row>
-    <row r="36" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="11" t="n">
         <v>46298</v>
       </c>
@@ -3922,7 +3987,7 @@
       <c r="S36" s="12"/>
       <c r="T36" s="12"/>
     </row>
-    <row r="37" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="9" t="n">
         <v>46300</v>
       </c>
@@ -3972,7 +4037,7 @@
       <c r="S37" s="10"/>
       <c r="T37" s="10"/>
     </row>
-    <row r="38" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="11" t="n">
         <v>46301</v>
       </c>
@@ -4022,7 +4087,7 @@
       <c r="S38" s="12"/>
       <c r="T38" s="12"/>
     </row>
-    <row r="39" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="9" t="n">
         <v>46303</v>
       </c>
@@ -4072,7 +4137,7 @@
       <c r="S39" s="10"/>
       <c r="T39" s="10"/>
     </row>
-    <row r="40" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="11" t="n">
         <v>46304</v>
       </c>
@@ -4122,7 +4187,7 @@
       <c r="S40" s="12"/>
       <c r="T40" s="12"/>
     </row>
-    <row r="41" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="11" t="n">
         <v>46305</v>
       </c>
@@ -4172,7 +4237,7 @@
       <c r="S41" s="12"/>
       <c r="T41" s="12"/>
     </row>
-    <row r="42" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="9" t="n">
         <v>46307</v>
       </c>
@@ -4222,7 +4287,7 @@
       <c r="S42" s="10"/>
       <c r="T42" s="10"/>
     </row>
-    <row r="43" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="11" t="n">
         <v>46308</v>
       </c>
@@ -4272,7 +4337,7 @@
       <c r="S43" s="12"/>
       <c r="T43" s="12"/>
     </row>
-    <row r="44" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="9" t="n">
         <v>46310</v>
       </c>
@@ -4322,7 +4387,7 @@
       <c r="S44" s="10"/>
       <c r="T44" s="10"/>
     </row>
-    <row r="45" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="11" t="n">
         <v>46311</v>
       </c>
@@ -4372,7 +4437,7 @@
       <c r="S45" s="12"/>
       <c r="T45" s="12"/>
     </row>
-    <row r="46" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="11" t="n">
         <v>46312</v>
       </c>
@@ -4422,7 +4487,7 @@
       <c r="S46" s="12"/>
       <c r="T46" s="12"/>
     </row>
-    <row r="47" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="9" t="n">
         <v>46314</v>
       </c>
@@ -4472,7 +4537,7 @@
       <c r="S47" s="10"/>
       <c r="T47" s="10"/>
     </row>
-    <row r="48" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="11" t="n">
         <v>46315</v>
       </c>
@@ -4522,7 +4587,7 @@
       <c r="S48" s="12"/>
       <c r="T48" s="12"/>
     </row>
-    <row r="49" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="9" t="n">
         <v>46317</v>
       </c>
@@ -4572,7 +4637,7 @@
       <c r="S49" s="10"/>
       <c r="T49" s="10"/>
     </row>
-    <row r="50" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="11" t="n">
         <v>46318</v>
       </c>
@@ -4622,7 +4687,7 @@
       <c r="S50" s="12"/>
       <c r="T50" s="12"/>
     </row>
-    <row r="51" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="11" t="n">
         <v>46319</v>
       </c>
@@ -4672,7 +4737,7 @@
       <c r="S51" s="12"/>
       <c r="T51" s="12"/>
     </row>
-    <row r="52" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="9" t="n">
         <v>46321</v>
       </c>
@@ -4722,7 +4787,7 @@
       <c r="S52" s="10"/>
       <c r="T52" s="10"/>
     </row>
-    <row r="53" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="11" t="n">
         <v>46322</v>
       </c>
@@ -4772,7 +4837,7 @@
       <c r="S53" s="12"/>
       <c r="T53" s="12"/>
     </row>
-    <row r="54" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="9" t="n">
         <v>46324</v>
       </c>
@@ -4822,7 +4887,7 @@
       <c r="S54" s="10"/>
       <c r="T54" s="10"/>
     </row>
-    <row r="55" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="11" t="n">
         <v>46325</v>
       </c>
@@ -4872,7 +4937,7 @@
       <c r="S55" s="12"/>
       <c r="T55" s="12"/>
     </row>
-    <row r="56" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="11" t="n">
         <v>46326</v>
       </c>
@@ -4922,7 +4987,7 @@
       <c r="S56" s="12"/>
       <c r="T56" s="12"/>
     </row>
-    <row r="57" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="9" t="n">
         <v>46328</v>
       </c>
@@ -4972,7 +5037,7 @@
       <c r="S57" s="10"/>
       <c r="T57" s="10"/>
     </row>
-    <row r="58" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="11" t="n">
         <v>46329</v>
       </c>
@@ -5022,7 +5087,7 @@
       <c r="S58" s="12"/>
       <c r="T58" s="12"/>
     </row>
-    <row r="59" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="9" t="n">
         <v>46331</v>
       </c>
@@ -5072,7 +5137,7 @@
       <c r="S59" s="10"/>
       <c r="T59" s="10"/>
     </row>
-    <row r="60" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="11" t="n">
         <v>46332</v>
       </c>
@@ -5122,7 +5187,7 @@
       <c r="S60" s="12"/>
       <c r="T60" s="12"/>
     </row>
-    <row r="61" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="11" t="n">
         <v>46333</v>
       </c>
@@ -5172,7 +5237,7 @@
       <c r="S61" s="12"/>
       <c r="T61" s="12"/>
     </row>
-    <row r="62" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="9" t="n">
         <v>46335</v>
       </c>
@@ -5222,7 +5287,7 @@
       <c r="S62" s="10"/>
       <c r="T62" s="10"/>
     </row>
-    <row r="63" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="11" t="n">
         <v>46336</v>
       </c>
@@ -5272,7 +5337,7 @@
       <c r="S63" s="12"/>
       <c r="T63" s="12"/>
     </row>
-    <row r="64" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="9" t="n">
         <v>46338</v>
       </c>
@@ -5322,7 +5387,7 @@
       <c r="S64" s="10"/>
       <c r="T64" s="10"/>
     </row>
-    <row r="65" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="11" t="n">
         <v>46339</v>
       </c>
@@ -5372,7 +5437,7 @@
       <c r="S65" s="12"/>
       <c r="T65" s="12"/>
     </row>
-    <row r="66" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="11" t="n">
         <v>46340</v>
       </c>

--- a/strategy/ig-content-strategy.xlsx
+++ b/strategy/ig-content-strategy.xlsx
@@ -25,7 +25,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mmm\ d&quot;, &quot;yyyy"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -115,6 +115,12 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF0563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -175,7 +181,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -264,6 +270,15 @@
       <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -519,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3" customWidth="1" style="13" min="1" max="1"/>
@@ -792,6 +807,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="B32" s="22" t="inlineStr">
         <is>
@@ -856,6 +872,18 @@
       <c r="C37" s="24" t="inlineStr">
         <is>
           <t>The Photo Library tab tracks every client photo, its consent status and where it is used.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="22" t="inlineStr">
+        <is>
+          <t>Image Link</t>
+        </is>
+      </c>
+      <c r="C39" s="24" t="inlineStr">
+        <is>
+          <t>Click to see the finished image for that post. Single-image posts open the picture directly; carousels open the folder of slides. "Not designed yet" means the post has a brief but no artwork.</t>
         </is>
       </c>
     </row>
@@ -872,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:V66"/>
+  <dimension ref="A1:W66"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="13" min="1" max="1"/>
@@ -889,7 +917,7 @@
     <col width="34" customWidth="1" style="13" min="13" max="13"/>
     <col width="14" customWidth="1" style="13" min="14" max="14"/>
     <col width="16" customWidth="1" style="13" min="15" max="15"/>
-    <col width="8" customWidth="1" style="13" min="16" max="17"/>
+    <col width="46" customWidth="1" style="13" min="16" max="17"/>
     <col width="10" customWidth="1" style="13" min="18" max="18"/>
     <col width="8" customWidth="1" style="13" min="19" max="19"/>
     <col width="10" customWidth="1" style="13" min="20" max="20"/>
@@ -971,37 +999,42 @@
           <t>Folder Link</t>
         </is>
       </c>
-      <c r="P1" s="25" t="inlineStr">
+      <c r="P1" s="26" t="inlineStr">
+        <is>
+          <t>Image Link</t>
+        </is>
+      </c>
+      <c r="Q1" s="25" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="Q1" s="25" t="inlineStr">
+      <c r="R1" s="25" t="inlineStr">
         <is>
           <t>Posted Link</t>
         </is>
       </c>
-      <c r="R1" s="25" t="inlineStr">
+      <c r="S1" s="25" t="inlineStr">
         <is>
           <t>Reach</t>
         </is>
       </c>
-      <c r="S1" s="25" t="inlineStr">
+      <c r="T1" s="25" t="inlineStr">
         <is>
           <t>Saves</t>
         </is>
       </c>
-      <c r="T1" s="25" t="inlineStr">
+      <c r="U1" s="25" t="inlineStr">
         <is>
           <t>Comments</t>
         </is>
       </c>
-      <c r="U1" s="25" t="inlineStr">
+      <c r="V1" s="25" t="inlineStr">
         <is>
           <t>DMs</t>
         </is>
       </c>
-      <c r="V1" s="25" t="inlineStr">
+      <c r="W1" s="25" t="inlineStr">
         <is>
           <t>Bookings</t>
         </is>
@@ -1067,22 +1100,27 @@
       </c>
       <c r="M2" s="24" t="n"/>
       <c r="N2" s="24" t="n"/>
-      <c r="O2" s="28" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-08-17-5-botox-lies-you-still</t>
-        </is>
-      </c>
-      <c r="P2" s="28" t="inlineStr">
+      <c r="O2" s="32" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P2" s="33" t="inlineStr">
+        <is>
+          <t>View 8 slides</t>
+        </is>
+      </c>
+      <c r="Q2" s="28" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q2" s="28" t="n"/>
       <c r="R2" s="28" t="n"/>
       <c r="S2" s="28" t="n"/>
       <c r="T2" s="28" t="n"/>
       <c r="U2" s="28" t="n"/>
       <c r="V2" s="28" t="n"/>
+      <c r="W2" s="28" t="n"/>
     </row>
     <row r="3" ht="57.45" customHeight="1" s="14">
       <c r="A3" s="29" t="n">
@@ -1144,22 +1182,27 @@
       </c>
       <c r="M3" s="24" t="n"/>
       <c r="N3" s="24" t="n"/>
-      <c r="O3" s="30" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-08-18-service-spotlight-botox</t>
-        </is>
-      </c>
-      <c r="P3" s="30" t="inlineStr">
+      <c r="O3" s="34" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P3" s="33" t="inlineStr">
+        <is>
+          <t>View image</t>
+        </is>
+      </c>
+      <c r="Q3" s="30" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q3" s="30" t="n"/>
       <c r="R3" s="30" t="n"/>
       <c r="S3" s="30" t="n"/>
       <c r="T3" s="30" t="n"/>
       <c r="U3" s="30" t="n"/>
       <c r="V3" s="30" t="n"/>
+      <c r="W3" s="30" t="n"/>
     </row>
     <row r="4" ht="68.65000000000001" customHeight="1" s="14">
       <c r="A4" s="27" t="n">
@@ -1221,22 +1264,27 @@
       </c>
       <c r="M4" s="24" t="n"/>
       <c r="N4" s="24" t="n"/>
-      <c r="O4" s="28" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-08-20-5-red-flags-at-a</t>
-        </is>
-      </c>
-      <c r="P4" s="28" t="inlineStr">
+      <c r="O4" s="32" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P4" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="Q4" s="28" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="Q4" s="28" t="n"/>
       <c r="R4" s="28" t="n"/>
       <c r="S4" s="28" t="n"/>
       <c r="T4" s="28" t="n"/>
       <c r="U4" s="28" t="n"/>
       <c r="V4" s="28" t="n"/>
+      <c r="W4" s="28" t="n"/>
     </row>
     <row r="5" ht="57.45" customHeight="1" s="14">
       <c r="A5" s="29" t="n">
@@ -1298,22 +1346,27 @@
       </c>
       <c r="M5" s="24" t="n"/>
       <c r="N5" s="24" t="n"/>
-      <c r="O5" s="30" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-08-21-behind-the-scenes-the-prep</t>
-        </is>
-      </c>
-      <c r="P5" s="30" t="inlineStr">
+      <c r="O5" s="34" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P5" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="Q5" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="Q5" s="30" t="n"/>
       <c r="R5" s="30" t="n"/>
       <c r="S5" s="30" t="n"/>
       <c r="T5" s="30" t="n"/>
       <c r="U5" s="30" t="n"/>
       <c r="V5" s="30" t="n"/>
+      <c r="W5" s="30" t="n"/>
     </row>
     <row r="6" ht="46.25" customHeight="1" s="14">
       <c r="A6" s="29" t="n">
@@ -1375,22 +1428,27 @@
       </c>
       <c r="M6" s="24" t="n"/>
       <c r="N6" s="24" t="n"/>
-      <c r="O6" s="30" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-08-22-quote-great-work-is-invisible</t>
-        </is>
-      </c>
-      <c r="P6" s="30" t="inlineStr">
+      <c r="O6" s="34" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P6" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="Q6" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="Q6" s="30" t="n"/>
       <c r="R6" s="30" t="n"/>
       <c r="S6" s="30" t="n"/>
       <c r="T6" s="30" t="n"/>
       <c r="U6" s="30" t="n"/>
       <c r="V6" s="30" t="n"/>
+      <c r="W6" s="30" t="n"/>
     </row>
     <row r="7" ht="57.45" customHeight="1" s="14">
       <c r="A7" s="27" t="n">
@@ -1452,22 +1510,27 @@
       </c>
       <c r="M7" s="24" t="n"/>
       <c r="N7" s="24" t="n"/>
-      <c r="O7" s="28" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-08-24-your-first-visit-step-by</t>
-        </is>
-      </c>
-      <c r="P7" s="28" t="inlineStr">
+      <c r="O7" s="32" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P7" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="Q7" s="28" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="Q7" s="28" t="n"/>
       <c r="R7" s="28" t="n"/>
       <c r="S7" s="28" t="n"/>
       <c r="T7" s="28" t="n"/>
       <c r="U7" s="28" t="n"/>
       <c r="V7" s="28" t="n"/>
+      <c r="W7" s="28" t="n"/>
     </row>
     <row r="8" ht="57.45" customHeight="1" s="14">
       <c r="A8" s="29" t="n">
@@ -1529,22 +1592,27 @@
       </c>
       <c r="M8" s="24" t="n"/>
       <c r="N8" s="24" t="n"/>
-      <c r="O8" s="30" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-08-25-3-signs-your-injector-is</t>
-        </is>
-      </c>
-      <c r="P8" s="30" t="inlineStr">
+      <c r="O8" s="34" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P8" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="Q8" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="Q8" s="30" t="n"/>
       <c r="R8" s="30" t="n"/>
       <c r="S8" s="30" t="n"/>
       <c r="T8" s="30" t="n"/>
       <c r="U8" s="30" t="n"/>
       <c r="V8" s="30" t="n"/>
+      <c r="W8" s="30" t="n"/>
     </row>
     <row r="9" ht="57.45" customHeight="1" s="14">
       <c r="A9" s="27" t="n">
@@ -1606,22 +1674,27 @@
       </c>
       <c r="M9" s="24" t="n"/>
       <c r="N9" s="24" t="n"/>
-      <c r="O9" s="28" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-08-27-meet-np-cleo-the-face</t>
-        </is>
-      </c>
-      <c r="P9" s="28" t="inlineStr">
+      <c r="O9" s="32" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P9" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="Q9" s="28" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="Q9" s="28" t="n"/>
       <c r="R9" s="28" t="n"/>
       <c r="S9" s="28" t="n"/>
       <c r="T9" s="28" t="n"/>
       <c r="U9" s="28" t="n"/>
       <c r="V9" s="28" t="n"/>
+      <c r="W9" s="28" t="n"/>
     </row>
     <row r="10" ht="46.25" customHeight="1" s="14">
       <c r="A10" s="29" t="n">
@@ -1683,22 +1756,27 @@
       </c>
       <c r="M10" s="24" t="n"/>
       <c r="N10" s="24" t="n"/>
-      <c r="O10" s="30" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-08-28-welcome-to-the-treatment-room</t>
-        </is>
-      </c>
-      <c r="P10" s="30" t="inlineStr">
+      <c r="O10" s="34" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P10" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="Q10" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="Q10" s="30" t="n"/>
       <c r="R10" s="30" t="n"/>
       <c r="S10" s="30" t="n"/>
       <c r="T10" s="30" t="n"/>
       <c r="U10" s="30" t="n"/>
       <c r="V10" s="30" t="n"/>
+      <c r="W10" s="30" t="n"/>
     </row>
     <row r="11" ht="46.25" customHeight="1" s="14">
       <c r="A11" s="29" t="n">
@@ -1760,22 +1838,27 @@
       </c>
       <c r="M11" s="24" t="n"/>
       <c r="N11" s="24" t="n"/>
-      <c r="O11" s="30" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-08-29-this-or-that-rested-vs</t>
-        </is>
-      </c>
-      <c r="P11" s="30" t="inlineStr">
+      <c r="O11" s="34" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P11" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="Q11" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="Q11" s="30" t="n"/>
       <c r="R11" s="30" t="n"/>
       <c r="S11" s="30" t="n"/>
       <c r="T11" s="30" t="n"/>
       <c r="U11" s="30" t="n"/>
       <c r="V11" s="30" t="n"/>
+      <c r="W11" s="30" t="n"/>
     </row>
     <row r="12" ht="57.45" customHeight="1" s="14">
       <c r="A12" s="27" t="n">
@@ -1837,22 +1920,27 @@
       </c>
       <c r="M12" s="24" t="n"/>
       <c r="N12" s="24" t="n"/>
-      <c r="O12" s="28" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-08-31-preventative-botox-when-to-actually</t>
-        </is>
-      </c>
-      <c r="P12" s="28" t="inlineStr">
+      <c r="O12" s="32" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P12" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="Q12" s="28" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="Q12" s="28" t="n"/>
       <c r="R12" s="28" t="n"/>
       <c r="S12" s="28" t="n"/>
       <c r="T12" s="28" t="n"/>
       <c r="U12" s="28" t="n"/>
       <c r="V12" s="28" t="n"/>
+      <c r="W12" s="28" t="n"/>
     </row>
     <row r="13" ht="57.45" customHeight="1" s="14">
       <c r="A13" s="29" t="n">
@@ -1914,22 +2002,27 @@
       </c>
       <c r="M13" s="24" t="n"/>
       <c r="N13" s="24" t="n"/>
-      <c r="O13" s="30" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-01-service-spotlight-preventative-botox</t>
-        </is>
-      </c>
-      <c r="P13" s="30" t="inlineStr">
+      <c r="O13" s="34" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P13" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="Q13" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="Q13" s="30" t="n"/>
       <c r="R13" s="30" t="n"/>
       <c r="S13" s="30" t="n"/>
       <c r="T13" s="30" t="n"/>
       <c r="U13" s="30" t="n"/>
       <c r="V13" s="30" t="n"/>
+      <c r="W13" s="30" t="n"/>
     </row>
     <row r="14" ht="57.45" customHeight="1" s="14">
       <c r="A14" s="27" t="n">
@@ -1991,22 +2084,27 @@
       </c>
       <c r="M14" s="24" t="n"/>
       <c r="N14" s="24" t="n"/>
-      <c r="O14" s="28" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-03-what-20-units-actually-looks</t>
-        </is>
-      </c>
-      <c r="P14" s="28" t="inlineStr">
+      <c r="O14" s="32" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P14" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="Q14" s="28" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="Q14" s="28" t="n"/>
       <c r="R14" s="28" t="n"/>
       <c r="S14" s="28" t="n"/>
       <c r="T14" s="28" t="n"/>
       <c r="U14" s="28" t="n"/>
       <c r="V14" s="28" t="n"/>
+      <c r="W14" s="28" t="n"/>
     </row>
     <row r="15" ht="57.45" customHeight="1" s="14">
       <c r="A15" s="29" t="n">
@@ -2068,22 +2166,27 @@
       </c>
       <c r="M15" s="24" t="n"/>
       <c r="N15" s="24" t="n"/>
-      <c r="O15" s="30" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-04-meet-your-injector</t>
-        </is>
-      </c>
-      <c r="P15" s="30" t="inlineStr">
+      <c r="O15" s="34" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P15" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="Q15" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="Q15" s="30" t="n"/>
       <c r="R15" s="30" t="n"/>
       <c r="S15" s="30" t="n"/>
       <c r="T15" s="30" t="n"/>
       <c r="U15" s="30" t="n"/>
       <c r="V15" s="30" t="n"/>
+      <c r="W15" s="30" t="n"/>
     </row>
     <row r="16" ht="46.25" customHeight="1" s="14">
       <c r="A16" s="29" t="n">
@@ -2145,22 +2248,27 @@
       </c>
       <c r="M16" s="24" t="n"/>
       <c r="N16" s="24" t="n"/>
-      <c r="O16" s="30" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-05-quote-prevention-beats-erasing</t>
-        </is>
-      </c>
-      <c r="P16" s="30" t="inlineStr">
+      <c r="O16" s="34" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P16" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="Q16" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="Q16" s="30" t="n"/>
       <c r="R16" s="30" t="n"/>
       <c r="S16" s="30" t="n"/>
       <c r="T16" s="30" t="n"/>
       <c r="U16" s="30" t="n"/>
       <c r="V16" s="30" t="n"/>
+      <c r="W16" s="30" t="n"/>
     </row>
     <row r="17" ht="57.45" customHeight="1" s="14">
       <c r="A17" s="27" t="n">
@@ -2222,22 +2330,27 @@
       </c>
       <c r="M17" s="24" t="n"/>
       <c r="N17" s="24" t="n"/>
-      <c r="O17" s="28" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-07-botox-vs-dysport-the-real</t>
-        </is>
-      </c>
-      <c r="P17" s="28" t="inlineStr">
+      <c r="O17" s="32" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P17" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="Q17" s="28" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="Q17" s="28" t="n"/>
       <c r="R17" s="28" t="n"/>
       <c r="S17" s="28" t="n"/>
       <c r="T17" s="28" t="n"/>
       <c r="U17" s="28" t="n"/>
       <c r="V17" s="28" t="n"/>
+      <c r="W17" s="28" t="n"/>
     </row>
     <row r="18" ht="57.45" customHeight="1" s="14">
       <c r="A18" s="29" t="n">
@@ -2299,22 +2412,27 @@
       </c>
       <c r="M18" s="24" t="n"/>
       <c r="N18" s="24" t="n"/>
-      <c r="O18" s="30" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-08-botox-vs-dysport-at-a</t>
-        </is>
-      </c>
-      <c r="P18" s="30" t="inlineStr">
+      <c r="O18" s="34" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P18" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="Q18" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="Q18" s="30" t="n"/>
       <c r="R18" s="30" t="n"/>
       <c r="S18" s="30" t="n"/>
       <c r="T18" s="30" t="n"/>
       <c r="U18" s="30" t="n"/>
       <c r="V18" s="30" t="n"/>
+      <c r="W18" s="30" t="n"/>
     </row>
     <row r="19" ht="57.45" customHeight="1" s="14">
       <c r="A19" s="27" t="n">
@@ -2376,22 +2494,27 @@
       </c>
       <c r="M19" s="24" t="n"/>
       <c r="N19" s="24" t="n"/>
-      <c r="O19" s="28" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-10-botox-aftercare-the-first-48</t>
-        </is>
-      </c>
-      <c r="P19" s="28" t="inlineStr">
+      <c r="O19" s="32" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P19" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="Q19" s="28" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="Q19" s="28" t="n"/>
       <c r="R19" s="28" t="n"/>
       <c r="S19" s="28" t="n"/>
       <c r="T19" s="28" t="n"/>
       <c r="U19" s="28" t="n"/>
       <c r="V19" s="28" t="n"/>
+      <c r="W19" s="28" t="n"/>
     </row>
     <row r="20" ht="57.45" customHeight="1" s="14">
       <c r="A20" s="29" t="n">
@@ -2453,22 +2576,27 @@
       </c>
       <c r="M20" s="24" t="n"/>
       <c r="N20" s="24" t="n"/>
-      <c r="O20" s="30" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-11-the-face-map</t>
-        </is>
-      </c>
-      <c r="P20" s="30" t="inlineStr">
+      <c r="O20" s="34" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P20" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="Q20" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="Q20" s="30" t="n"/>
       <c r="R20" s="30" t="n"/>
       <c r="S20" s="30" t="n"/>
       <c r="T20" s="30" t="n"/>
       <c r="U20" s="30" t="n"/>
       <c r="V20" s="30" t="n"/>
+      <c r="W20" s="30" t="n"/>
     </row>
     <row r="21" ht="57.45" customHeight="1" s="14">
       <c r="A21" s="29" t="n">
@@ -2530,22 +2658,27 @@
       </c>
       <c r="M21" s="24" t="n"/>
       <c r="N21" s="24" t="n"/>
-      <c r="O21" s="30" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-12-faq-does-botox-hurt</t>
-        </is>
-      </c>
-      <c r="P21" s="30" t="inlineStr">
+      <c r="O21" s="34" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P21" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="Q21" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="Q21" s="30" t="n"/>
       <c r="R21" s="30" t="n"/>
       <c r="S21" s="30" t="n"/>
       <c r="T21" s="30" t="n"/>
       <c r="U21" s="30" t="n"/>
       <c r="V21" s="30" t="n"/>
+      <c r="W21" s="30" t="n"/>
     </row>
     <row r="22" ht="57.45" customHeight="1" s="14">
       <c r="A22" s="27" t="n">
@@ -2607,22 +2740,27 @@
       </c>
       <c r="M22" s="24" t="n"/>
       <c r="N22" s="24" t="n"/>
-      <c r="O22" s="28" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-14-5-things-botox-can-t</t>
-        </is>
-      </c>
-      <c r="P22" s="28" t="inlineStr">
+      <c r="O22" s="32" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P22" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="Q22" s="28" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="Q22" s="28" t="n"/>
       <c r="R22" s="28" t="n"/>
       <c r="S22" s="28" t="n"/>
       <c r="T22" s="28" t="n"/>
       <c r="U22" s="28" t="n"/>
       <c r="V22" s="28" t="n"/>
+      <c r="W22" s="28" t="n"/>
     </row>
     <row r="23" ht="57.45" customHeight="1" s="14">
       <c r="A23" s="29" t="n">
@@ -2684,22 +2822,27 @@
       </c>
       <c r="M23" s="24" t="n"/>
       <c r="N23" s="24" t="n"/>
-      <c r="O23" s="30" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-15-what-botox-can-t-fix</t>
-        </is>
-      </c>
-      <c r="P23" s="30" t="inlineStr">
+      <c r="O23" s="34" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P23" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="Q23" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="Q23" s="30" t="n"/>
       <c r="R23" s="30" t="n"/>
       <c r="S23" s="30" t="n"/>
       <c r="T23" s="30" t="n"/>
       <c r="U23" s="30" t="n"/>
       <c r="V23" s="30" t="n"/>
+      <c r="W23" s="30" t="n"/>
     </row>
     <row r="24" ht="57.45" customHeight="1" s="14">
       <c r="A24" s="27" t="n">
@@ -2761,22 +2904,27 @@
       </c>
       <c r="M24" s="24" t="n"/>
       <c r="N24" s="24" t="n"/>
-      <c r="O24" s="28" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-17-still-you-just-refreshed</t>
-        </is>
-      </c>
-      <c r="P24" s="28" t="inlineStr">
+      <c r="O24" s="32" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P24" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="Q24" s="28" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="Q24" s="28" t="n"/>
       <c r="R24" s="28" t="n"/>
       <c r="S24" s="28" t="n"/>
       <c r="T24" s="28" t="n"/>
       <c r="U24" s="28" t="n"/>
       <c r="V24" s="28" t="n"/>
+      <c r="W24" s="28" t="n"/>
     </row>
     <row r="25" ht="57.45" customHeight="1" s="14">
       <c r="A25" s="29" t="n">
@@ -2838,22 +2986,27 @@
       </c>
       <c r="M25" s="24" t="n"/>
       <c r="N25" s="24" t="n"/>
-      <c r="O25" s="30" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-18-myth-vs-truth-the-frozen</t>
-        </is>
-      </c>
-      <c r="P25" s="30" t="inlineStr">
+      <c r="O25" s="34" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P25" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="Q25" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="Q25" s="30" t="n"/>
       <c r="R25" s="30" t="n"/>
       <c r="S25" s="30" t="n"/>
       <c r="T25" s="30" t="n"/>
       <c r="U25" s="30" t="n"/>
       <c r="V25" s="30" t="n"/>
+      <c r="W25" s="30" t="n"/>
     </row>
     <row r="26" ht="57.45" customHeight="1" s="14">
       <c r="A26" s="29" t="n">
@@ -2915,22 +3068,27 @@
       </c>
       <c r="M26" s="24" t="n"/>
       <c r="N26" s="24" t="n"/>
-      <c r="O26" s="30" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-19-client-words-natural-results</t>
-        </is>
-      </c>
-      <c r="P26" s="30" t="inlineStr">
+      <c r="O26" s="34" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P26" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="Q26" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="Q26" s="30" t="n"/>
       <c r="R26" s="30" t="n"/>
       <c r="S26" s="30" t="n"/>
       <c r="T26" s="30" t="n"/>
       <c r="U26" s="30" t="n"/>
       <c r="V26" s="30" t="n"/>
+      <c r="W26" s="30" t="n"/>
     </row>
     <row r="27" ht="57.45" customHeight="1" s="14">
       <c r="A27" s="27" t="n">
@@ -2992,22 +3150,27 @@
       </c>
       <c r="M27" s="24" t="n"/>
       <c r="N27" s="24" t="n"/>
-      <c r="O27" s="28" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-21-botox-or-filler-you-might</t>
-        </is>
-      </c>
-      <c r="P27" s="28" t="inlineStr">
+      <c r="O27" s="32" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P27" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="Q27" s="28" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="Q27" s="28" t="n"/>
       <c r="R27" s="28" t="n"/>
       <c r="S27" s="28" t="n"/>
       <c r="T27" s="28" t="n"/>
       <c r="U27" s="28" t="n"/>
       <c r="V27" s="28" t="n"/>
+      <c r="W27" s="28" t="n"/>
     </row>
     <row r="28" ht="57.45" customHeight="1" s="14">
       <c r="A28" s="29" t="n">
@@ -3069,22 +3232,27 @@
       </c>
       <c r="M28" s="24" t="n"/>
       <c r="N28" s="24" t="n"/>
-      <c r="O28" s="30" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-22-lines-vs-volume</t>
-        </is>
-      </c>
-      <c r="P28" s="30" t="inlineStr">
+      <c r="O28" s="34" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P28" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="Q28" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="Q28" s="30" t="n"/>
       <c r="R28" s="30" t="n"/>
       <c r="S28" s="30" t="n"/>
       <c r="T28" s="30" t="n"/>
       <c r="U28" s="30" t="n"/>
       <c r="V28" s="30" t="n"/>
+      <c r="W28" s="30" t="n"/>
     </row>
     <row r="29" ht="57.45" customHeight="1" s="14">
       <c r="A29" s="27" t="n">
@@ -3146,22 +3314,27 @@
       </c>
       <c r="M29" s="24" t="n"/>
       <c r="N29" s="24" t="n"/>
-      <c r="O29" s="28" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-24-ask-np-cleo-your-questions</t>
-        </is>
-      </c>
-      <c r="P29" s="28" t="inlineStr">
+      <c r="O29" s="32" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P29" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="Q29" s="28" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="Q29" s="28" t="n"/>
       <c r="R29" s="28" t="n"/>
       <c r="S29" s="28" t="n"/>
       <c r="T29" s="28" t="n"/>
       <c r="U29" s="28" t="n"/>
       <c r="V29" s="28" t="n"/>
+      <c r="W29" s="28" t="n"/>
     </row>
     <row r="30" ht="57.45" customHeight="1" s="14">
       <c r="A30" s="29" t="n">
@@ -3223,22 +3396,27 @@
       </c>
       <c r="M30" s="24" t="n"/>
       <c r="N30" s="24" t="n"/>
-      <c r="O30" s="30" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-25-your-dms-answered</t>
-        </is>
-      </c>
-      <c r="P30" s="30" t="inlineStr">
+      <c r="O30" s="34" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P30" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="Q30" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="Q30" s="30" t="n"/>
       <c r="R30" s="30" t="n"/>
       <c r="S30" s="30" t="n"/>
       <c r="T30" s="30" t="n"/>
       <c r="U30" s="30" t="n"/>
       <c r="V30" s="30" t="n"/>
+      <c r="W30" s="30" t="n"/>
     </row>
     <row r="31" ht="57.45" customHeight="1" s="14">
       <c r="A31" s="29" t="n">
@@ -3300,22 +3478,27 @@
       </c>
       <c r="M31" s="24" t="n"/>
       <c r="N31" s="24" t="n"/>
-      <c r="O31" s="30" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-26-poll-what-should-np-cleo</t>
-        </is>
-      </c>
-      <c r="P31" s="30" t="inlineStr">
+      <c r="O31" s="34" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P31" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="Q31" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="Q31" s="30" t="n"/>
       <c r="R31" s="30" t="n"/>
       <c r="S31" s="30" t="n"/>
       <c r="T31" s="30" t="n"/>
       <c r="U31" s="30" t="n"/>
       <c r="V31" s="30" t="n"/>
+      <c r="W31" s="30" t="n"/>
     </row>
     <row r="32" ht="57.45" customHeight="1" s="14">
       <c r="A32" s="27" t="n">
@@ -3377,22 +3560,27 @@
       </c>
       <c r="M32" s="24" t="n"/>
       <c r="N32" s="24" t="n"/>
-      <c r="O32" s="28" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-28-how-long-does-botox-really</t>
-        </is>
-      </c>
-      <c r="P32" s="28" t="inlineStr">
+      <c r="O32" s="32" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P32" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="Q32" s="28" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="Q32" s="28" t="n"/>
       <c r="R32" s="28" t="n"/>
       <c r="S32" s="28" t="n"/>
       <c r="T32" s="28" t="n"/>
       <c r="U32" s="28" t="n"/>
       <c r="V32" s="28" t="n"/>
+      <c r="W32" s="28" t="n"/>
     </row>
     <row r="33" ht="57.45" customHeight="1" s="14">
       <c r="A33" s="29" t="n">
@@ -3454,22 +3642,27 @@
       </c>
       <c r="M33" s="24" t="n"/>
       <c r="N33" s="24" t="n"/>
-      <c r="O33" s="30" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-29-the-3-month-botox-timeline</t>
-        </is>
-      </c>
-      <c r="P33" s="30" t="inlineStr">
+      <c r="O33" s="34" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P33" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="Q33" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="Q33" s="30" t="n"/>
       <c r="R33" s="30" t="n"/>
       <c r="S33" s="30" t="n"/>
       <c r="T33" s="30" t="n"/>
       <c r="U33" s="30" t="n"/>
       <c r="V33" s="30" t="n"/>
+      <c r="W33" s="30" t="n"/>
     </row>
     <row r="34" ht="57.45" customHeight="1" s="14">
       <c r="A34" s="27" t="n">
@@ -3531,22 +3724,27 @@
       </c>
       <c r="M34" s="24" t="n"/>
       <c r="N34" s="24" t="n"/>
-      <c r="O34" s="28" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-01-why-we-sometimes-say-no</t>
-        </is>
-      </c>
-      <c r="P34" s="28" t="inlineStr">
+      <c r="O34" s="32" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P34" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="Q34" s="28" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="Q34" s="28" t="n"/>
       <c r="R34" s="28" t="n"/>
       <c r="S34" s="28" t="n"/>
       <c r="T34" s="28" t="n"/>
       <c r="U34" s="28" t="n"/>
       <c r="V34" s="28" t="n"/>
+      <c r="W34" s="28" t="n"/>
     </row>
     <row r="35" ht="57.45" customHeight="1" s="14">
       <c r="A35" s="29" t="n">
@@ -3608,22 +3806,27 @@
       </c>
       <c r="M35" s="24" t="n"/>
       <c r="N35" s="24" t="n"/>
-      <c r="O35" s="30" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-02-what-i-tell-every-first</t>
-        </is>
-      </c>
-      <c r="P35" s="30" t="inlineStr">
+      <c r="O35" s="34" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P35" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="Q35" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="Q35" s="30" t="n"/>
       <c r="R35" s="30" t="n"/>
       <c r="S35" s="30" t="n"/>
       <c r="T35" s="30" t="n"/>
       <c r="U35" s="30" t="n"/>
       <c r="V35" s="30" t="n"/>
+      <c r="W35" s="30" t="n"/>
     </row>
     <row r="36" ht="46.25" customHeight="1" s="14">
       <c r="A36" s="29" t="n">
@@ -3685,22 +3888,27 @@
       </c>
       <c r="M36" s="24" t="n"/>
       <c r="N36" s="24" t="n"/>
-      <c r="O36" s="30" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-03-quote-no-is-protection</t>
-        </is>
-      </c>
-      <c r="P36" s="30" t="inlineStr">
+      <c r="O36" s="34" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P36" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="Q36" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="Q36" s="30" t="n"/>
       <c r="R36" s="30" t="n"/>
       <c r="S36" s="30" t="n"/>
       <c r="T36" s="30" t="n"/>
       <c r="U36" s="30" t="n"/>
       <c r="V36" s="30" t="n"/>
+      <c r="W36" s="30" t="n"/>
     </row>
     <row r="37" ht="57.45" customHeight="1" s="14">
       <c r="A37" s="27" t="n">
@@ -3762,22 +3970,27 @@
       </c>
       <c r="M37" s="24" t="n"/>
       <c r="N37" s="24" t="n"/>
-      <c r="O37" s="28" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-05-filler-won-t-make-you</t>
-        </is>
-      </c>
-      <c r="P37" s="28" t="inlineStr">
+      <c r="O37" s="32" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P37" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="Q37" s="28" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="Q37" s="28" t="n"/>
       <c r="R37" s="28" t="n"/>
       <c r="S37" s="28" t="n"/>
       <c r="T37" s="28" t="n"/>
       <c r="U37" s="28" t="n"/>
       <c r="V37" s="28" t="n"/>
+      <c r="W37" s="28" t="n"/>
     </row>
     <row r="38" ht="57.45" customHeight="1" s="14">
       <c r="A38" s="29" t="n">
@@ -3839,22 +4052,27 @@
       </c>
       <c r="M38" s="24" t="n"/>
       <c r="N38" s="24" t="n"/>
-      <c r="O38" s="30" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-06-service-spotlight-dermal-filler</t>
-        </is>
-      </c>
-      <c r="P38" s="30" t="inlineStr">
+      <c r="O38" s="34" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P38" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="Q38" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="Q38" s="30" t="n"/>
       <c r="R38" s="30" t="n"/>
       <c r="S38" s="30" t="n"/>
       <c r="T38" s="30" t="n"/>
       <c r="U38" s="30" t="n"/>
       <c r="V38" s="30" t="n"/>
+      <c r="W38" s="30" t="n"/>
     </row>
     <row r="39" ht="57.45" customHeight="1" s="14">
       <c r="A39" s="27" t="n">
@@ -3924,22 +4142,27 @@
           <t>Not needed</t>
         </is>
       </c>
-      <c r="O39" s="28" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-08-lip-filler-natural-vs-overdone</t>
-        </is>
-      </c>
-      <c r="P39" s="28" t="inlineStr">
+      <c r="O39" s="32" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P39" s="33" t="inlineStr">
+        <is>
+          <t>View image</t>
+        </is>
+      </c>
+      <c r="Q39" s="28" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q39" s="28" t="n"/>
       <c r="R39" s="28" t="n"/>
       <c r="S39" s="28" t="n"/>
       <c r="T39" s="28" t="n"/>
       <c r="U39" s="28" t="n"/>
       <c r="V39" s="28" t="n"/>
+      <c r="W39" s="28" t="n"/>
     </row>
     <row r="40" ht="46.25" customHeight="1" s="14">
       <c r="A40" s="29" t="n">
@@ -4001,22 +4224,27 @@
       </c>
       <c r="M40" s="24" t="n"/>
       <c r="N40" s="24" t="n"/>
-      <c r="O40" s="30" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-09-inside-the-filler-appointment</t>
-        </is>
-      </c>
-      <c r="P40" s="30" t="inlineStr">
+      <c r="O40" s="34" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P40" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="Q40" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="Q40" s="30" t="n"/>
       <c r="R40" s="30" t="n"/>
       <c r="S40" s="30" t="n"/>
       <c r="T40" s="30" t="n"/>
       <c r="U40" s="30" t="n"/>
       <c r="V40" s="30" t="n"/>
+      <c r="W40" s="30" t="n"/>
     </row>
     <row r="41" ht="46.25" customHeight="1" s="14">
       <c r="A41" s="29" t="n">
@@ -4086,22 +4314,27 @@
           <t>On file</t>
         </is>
       </c>
-      <c r="O41" s="30" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-10-10-subtle-is-the-new-dramatic</t>
-        </is>
-      </c>
-      <c r="P41" s="30" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="Q41" s="30" t="n"/>
+      <c r="O41" s="34" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P41" s="33" t="inlineStr">
+        <is>
+          <t>View image</t>
+        </is>
+      </c>
+      <c r="Q41" s="30" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
       <c r="R41" s="30" t="n"/>
       <c r="S41" s="30" t="n"/>
       <c r="T41" s="30" t="n"/>
       <c r="U41" s="30" t="n"/>
       <c r="V41" s="30" t="n"/>
+      <c r="W41" s="30" t="n"/>
     </row>
     <row r="42" ht="57.45" customHeight="1" s="14">
       <c r="A42" s="27" t="n">
@@ -4163,22 +4396,27 @@
       </c>
       <c r="M42" s="24" t="n"/>
       <c r="N42" s="24" t="n"/>
-      <c r="O42" s="28" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-12-cheek-filler-the-secret-nobody</t>
-        </is>
-      </c>
-      <c r="P42" s="28" t="inlineStr">
+      <c r="O42" s="32" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P42" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="Q42" s="28" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="Q42" s="28" t="n"/>
       <c r="R42" s="28" t="n"/>
       <c r="S42" s="28" t="n"/>
       <c r="T42" s="28" t="n"/>
       <c r="U42" s="28" t="n"/>
       <c r="V42" s="28" t="n"/>
+      <c r="W42" s="28" t="n"/>
     </row>
     <row r="43" ht="57.45" customHeight="1" s="14">
       <c r="A43" s="29" t="n">
@@ -4240,22 +4478,27 @@
       </c>
       <c r="M43" s="24" t="n"/>
       <c r="N43" s="24" t="n"/>
-      <c r="O43" s="30" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-13-service-spotlight-cheek-filler</t>
-        </is>
-      </c>
-      <c r="P43" s="30" t="inlineStr">
+      <c r="O43" s="34" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P43" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="Q43" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="Q43" s="30" t="n"/>
       <c r="R43" s="30" t="n"/>
       <c r="S43" s="30" t="n"/>
       <c r="T43" s="30" t="n"/>
       <c r="U43" s="30" t="n"/>
       <c r="V43" s="30" t="n"/>
+      <c r="W43" s="30" t="n"/>
     </row>
     <row r="44" ht="57.45" customHeight="1" s="14">
       <c r="A44" s="27" t="n">
@@ -4312,12 +4555,12 @@
       </c>
       <c r="L44" s="28" t="inlineStr">
         <is>
-          <t>Carousel: cover + 4 before and after slides + CTA. Crop to treatment area, no faces</t>
+          <t>Carousel: cover + 5 before and after slides + CTA. Crop to treatment area, no faces</t>
         </is>
       </c>
       <c r="M44" s="24" t="inlineStr">
         <is>
-          <t>Pairs: 9908/9912, 0221/0233, 0962/0998, 1119/1123</t>
+          <t>Pairs: 9908/9912, 0221/0233, 0962/0998, 1119/1123, 9848/9850</t>
         </is>
       </c>
       <c r="N44" s="24" t="inlineStr">
@@ -4325,22 +4568,27 @@
           <t>On file</t>
         </is>
       </c>
-      <c r="O44" s="28" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-10-15-real-lips-real-results</t>
-        </is>
-      </c>
-      <c r="P44" s="28" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="Q44" s="28" t="n"/>
+      <c r="O44" s="32" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P44" s="33" t="inlineStr">
+        <is>
+          <t>View 7 slides</t>
+        </is>
+      </c>
+      <c r="Q44" s="28" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
       <c r="R44" s="28" t="n"/>
       <c r="S44" s="28" t="n"/>
       <c r="T44" s="28" t="n"/>
       <c r="U44" s="28" t="n"/>
       <c r="V44" s="28" t="n"/>
+      <c r="W44" s="28" t="n"/>
     </row>
     <row r="45" ht="57.45" customHeight="1" s="14">
       <c r="A45" s="29" t="n">
@@ -4402,22 +4650,27 @@
       </c>
       <c r="M45" s="24" t="n"/>
       <c r="N45" s="24" t="n"/>
-      <c r="O45" s="30" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-16-facial-balancing-101</t>
-        </is>
-      </c>
-      <c r="P45" s="30" t="inlineStr">
+      <c r="O45" s="34" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P45" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="Q45" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="Q45" s="30" t="n"/>
       <c r="R45" s="30" t="n"/>
       <c r="S45" s="30" t="n"/>
       <c r="T45" s="30" t="n"/>
       <c r="U45" s="30" t="n"/>
       <c r="V45" s="30" t="n"/>
+      <c r="W45" s="30" t="n"/>
     </row>
     <row r="46" ht="57.45" customHeight="1" s="14">
       <c r="A46" s="29" t="n">
@@ -4479,22 +4732,27 @@
       </c>
       <c r="M46" s="24" t="n"/>
       <c r="N46" s="24" t="n"/>
-      <c r="O46" s="30" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-17-faq-how-much-filler-do</t>
-        </is>
-      </c>
-      <c r="P46" s="30" t="inlineStr">
+      <c r="O46" s="34" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P46" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="Q46" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="Q46" s="30" t="n"/>
       <c r="R46" s="30" t="n"/>
       <c r="S46" s="30" t="n"/>
       <c r="T46" s="30" t="n"/>
       <c r="U46" s="30" t="n"/>
       <c r="V46" s="30" t="n"/>
+      <c r="W46" s="30" t="n"/>
     </row>
     <row r="47" ht="57.45" customHeight="1" s="14">
       <c r="A47" s="27" t="n">
@@ -4556,22 +4814,27 @@
       </c>
       <c r="M47" s="24" t="n"/>
       <c r="N47" s="24" t="n"/>
-      <c r="O47" s="28" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-19-filler-dissolves-here-is-the</t>
-        </is>
-      </c>
-      <c r="P47" s="28" t="inlineStr">
+      <c r="O47" s="32" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P47" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="Q47" s="28" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="Q47" s="28" t="n"/>
       <c r="R47" s="28" t="n"/>
       <c r="S47" s="28" t="n"/>
       <c r="T47" s="28" t="n"/>
       <c r="U47" s="28" t="n"/>
       <c r="V47" s="28" t="n"/>
+      <c r="W47" s="28" t="n"/>
     </row>
     <row r="48" ht="57.45" customHeight="1" s="14">
       <c r="A48" s="29" t="n">
@@ -4633,22 +4896,27 @@
       </c>
       <c r="M48" s="24" t="n"/>
       <c r="N48" s="24" t="n"/>
-      <c r="O48" s="30" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-20-the-filler-timeline</t>
-        </is>
-      </c>
-      <c r="P48" s="30" t="inlineStr">
+      <c r="O48" s="34" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P48" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="Q48" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="Q48" s="30" t="n"/>
       <c r="R48" s="30" t="n"/>
       <c r="S48" s="30" t="n"/>
       <c r="T48" s="30" t="n"/>
       <c r="U48" s="30" t="n"/>
       <c r="V48" s="30" t="n"/>
+      <c r="W48" s="30" t="n"/>
     </row>
     <row r="49" ht="57.45" customHeight="1" s="14">
       <c r="A49" s="27" t="n">
@@ -4705,12 +4973,12 @@
       </c>
       <c r="L49" s="28" t="inlineStr">
         <is>
-          <t>Carousel: day by day, with real day 0 photos. Crop to treatment area, no faces</t>
+          <t>Carousel: day by day. Day zero card built from the img_9848 / img_9850 pair. Crop to treatment area, no faces</t>
         </is>
       </c>
       <c r="M49" s="24" t="inlineStr">
         <is>
-          <t>img_7715, img_9848, img_9850, whatsapp composite</t>
+          <t>img_9848 (before) + img_9850 (right after); img_7715, whatsapp composite</t>
         </is>
       </c>
       <c r="N49" s="24" t="inlineStr">
@@ -4718,22 +4986,27 @@
           <t>On file</t>
         </is>
       </c>
-      <c r="O49" s="28" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-22-lip-filler-aftercare-your-first</t>
-        </is>
-      </c>
-      <c r="P49" s="28" t="inlineStr">
+      <c r="O49" s="32" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P49" s="33" t="inlineStr">
+        <is>
+          <t>View image</t>
+        </is>
+      </c>
+      <c r="Q49" s="28" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="Q49" s="28" t="n"/>
       <c r="R49" s="28" t="n"/>
       <c r="S49" s="28" t="n"/>
       <c r="T49" s="28" t="n"/>
       <c r="U49" s="28" t="n"/>
       <c r="V49" s="28" t="n"/>
+      <c r="W49" s="28" t="n"/>
     </row>
     <row r="50" ht="57.45" customHeight="1" s="14">
       <c r="A50" s="29" t="n">
@@ -4795,22 +5068,27 @@
       </c>
       <c r="M50" s="24" t="n"/>
       <c r="N50" s="24" t="n"/>
-      <c r="O50" s="30" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-23-aftercare-essentials</t>
-        </is>
-      </c>
-      <c r="P50" s="30" t="inlineStr">
+      <c r="O50" s="34" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P50" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="Q50" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="Q50" s="30" t="n"/>
       <c r="R50" s="30" t="n"/>
       <c r="S50" s="30" t="n"/>
       <c r="T50" s="30" t="n"/>
       <c r="U50" s="30" t="n"/>
       <c r="V50" s="30" t="n"/>
+      <c r="W50" s="30" t="n"/>
     </row>
     <row r="51" ht="57.45" customHeight="1" s="14">
       <c r="A51" s="29" t="n">
@@ -4880,22 +5158,27 @@
           <t>On file</t>
         </is>
       </c>
-      <c r="O51" s="30" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-10-24-client-words-the-lip-glow</t>
-        </is>
-      </c>
-      <c r="P51" s="30" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="Q51" s="30" t="n"/>
+      <c r="O51" s="34" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P51" s="33" t="inlineStr">
+        <is>
+          <t>View image</t>
+        </is>
+      </c>
+      <c r="Q51" s="30" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
       <c r="R51" s="30" t="n"/>
       <c r="S51" s="30" t="n"/>
       <c r="T51" s="30" t="n"/>
       <c r="U51" s="30" t="n"/>
       <c r="V51" s="30" t="n"/>
+      <c r="W51" s="30" t="n"/>
     </row>
     <row r="52" ht="57.45" customHeight="1" s="14">
       <c r="A52" s="27" t="n">
@@ -4957,22 +5240,27 @@
       </c>
       <c r="M52" s="24" t="n"/>
       <c r="N52" s="24" t="n"/>
-      <c r="O52" s="28" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-26-5-filler-lies-you-still</t>
-        </is>
-      </c>
-      <c r="P52" s="28" t="inlineStr">
+      <c r="O52" s="32" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P52" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="Q52" s="28" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="Q52" s="28" t="n"/>
       <c r="R52" s="28" t="n"/>
       <c r="S52" s="28" t="n"/>
       <c r="T52" s="28" t="n"/>
       <c r="U52" s="28" t="n"/>
       <c r="V52" s="28" t="n"/>
+      <c r="W52" s="28" t="n"/>
     </row>
     <row r="53" ht="57.45" customHeight="1" s="14">
       <c r="A53" s="29" t="n">
@@ -5034,22 +5322,27 @@
       </c>
       <c r="M53" s="24" t="n"/>
       <c r="N53" s="24" t="n"/>
-      <c r="O53" s="30" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-27-myth-vs-truth-filler-edition</t>
-        </is>
-      </c>
-      <c r="P53" s="30" t="inlineStr">
+      <c r="O53" s="34" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P53" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="Q53" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="Q53" s="30" t="n"/>
       <c r="R53" s="30" t="n"/>
       <c r="S53" s="30" t="n"/>
       <c r="T53" s="30" t="n"/>
       <c r="U53" s="30" t="n"/>
       <c r="V53" s="30" t="n"/>
+      <c r="W53" s="30" t="n"/>
     </row>
     <row r="54" ht="57.45" customHeight="1" s="14">
       <c r="A54" s="27" t="n">
@@ -5111,22 +5404,27 @@
       </c>
       <c r="M54" s="24" t="n"/>
       <c r="N54" s="24" t="n"/>
-      <c r="O54" s="28" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-29-facial-balancing-why-we-treat</t>
-        </is>
-      </c>
-      <c r="P54" s="28" t="inlineStr">
+      <c r="O54" s="32" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P54" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="Q54" s="28" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="Q54" s="28" t="n"/>
       <c r="R54" s="28" t="n"/>
       <c r="S54" s="28" t="n"/>
       <c r="T54" s="28" t="n"/>
       <c r="U54" s="28" t="n"/>
       <c r="V54" s="28" t="n"/>
+      <c r="W54" s="28" t="n"/>
     </row>
     <row r="55" ht="57.45" customHeight="1" s="14">
       <c r="A55" s="29" t="n">
@@ -5196,22 +5494,27 @@
           <t>On file</t>
         </is>
       </c>
-      <c r="O55" s="30" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-10-30-one-syringe-balanced-lips</t>
-        </is>
-      </c>
-      <c r="P55" s="30" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="Q55" s="30" t="n"/>
+      <c r="O55" s="34" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P55" s="33" t="inlineStr">
+        <is>
+          <t>View image</t>
+        </is>
+      </c>
+      <c r="Q55" s="30" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
       <c r="R55" s="30" t="n"/>
       <c r="S55" s="30" t="n"/>
       <c r="T55" s="30" t="n"/>
       <c r="U55" s="30" t="n"/>
       <c r="V55" s="30" t="n"/>
+      <c r="W55" s="30" t="n"/>
     </row>
     <row r="56" ht="57.45" customHeight="1" s="14">
       <c r="A56" s="29" t="n">
@@ -5273,22 +5576,27 @@
       </c>
       <c r="M56" s="24" t="n"/>
       <c r="N56" s="24" t="n"/>
-      <c r="O56" s="30" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-31-ask-anything-filler-edition</t>
-        </is>
-      </c>
-      <c r="P56" s="30" t="inlineStr">
+      <c r="O56" s="34" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P56" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="Q56" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="Q56" s="30" t="n"/>
       <c r="R56" s="30" t="n"/>
       <c r="S56" s="30" t="n"/>
       <c r="T56" s="30" t="n"/>
       <c r="U56" s="30" t="n"/>
       <c r="V56" s="30" t="n"/>
+      <c r="W56" s="30" t="n"/>
     </row>
     <row r="57" ht="57.45" customHeight="1" s="14">
       <c r="A57" s="27" t="n">
@@ -5350,22 +5658,27 @@
       </c>
       <c r="M57" s="24" t="n"/>
       <c r="N57" s="24" t="n"/>
-      <c r="O57" s="28" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-11-02-rested-by-the-holidays-your</t>
-        </is>
-      </c>
-      <c r="P57" s="28" t="inlineStr">
+      <c r="O57" s="32" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P57" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="Q57" s="28" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="Q57" s="28" t="n"/>
       <c r="R57" s="28" t="n"/>
       <c r="S57" s="28" t="n"/>
       <c r="T57" s="28" t="n"/>
       <c r="U57" s="28" t="n"/>
       <c r="V57" s="28" t="n"/>
+      <c r="W57" s="28" t="n"/>
     </row>
     <row r="58" ht="57.45" customHeight="1" s="14">
       <c r="A58" s="29" t="n">
@@ -5427,22 +5740,27 @@
       </c>
       <c r="M58" s="24" t="n"/>
       <c r="N58" s="24" t="n"/>
-      <c r="O58" s="30" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-11-03-holiday-countdown-book-by-these</t>
-        </is>
-      </c>
-      <c r="P58" s="30" t="inlineStr">
+      <c r="O58" s="34" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P58" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="Q58" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="Q58" s="30" t="n"/>
       <c r="R58" s="30" t="n"/>
       <c r="S58" s="30" t="n"/>
       <c r="T58" s="30" t="n"/>
       <c r="U58" s="30" t="n"/>
       <c r="V58" s="30" t="n"/>
+      <c r="W58" s="30" t="n"/>
     </row>
     <row r="59" ht="57.45" customHeight="1" s="14">
       <c r="A59" s="27" t="n">
@@ -5504,22 +5822,27 @@
       </c>
       <c r="M59" s="24" t="n"/>
       <c r="N59" s="24" t="n"/>
-      <c r="O59" s="28" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-11-05-party-season-prep-what-to</t>
-        </is>
-      </c>
-      <c r="P59" s="28" t="inlineStr">
+      <c r="O59" s="32" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P59" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="Q59" s="28" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="Q59" s="28" t="n"/>
       <c r="R59" s="28" t="n"/>
       <c r="S59" s="28" t="n"/>
       <c r="T59" s="28" t="n"/>
       <c r="U59" s="28" t="n"/>
       <c r="V59" s="28" t="n"/>
+      <c r="W59" s="28" t="n"/>
     </row>
     <row r="60" ht="57.45" customHeight="1" s="14">
       <c r="A60" s="29" t="n">
@@ -5589,22 +5912,27 @@
           <t>On file</t>
         </is>
       </c>
-      <c r="O60" s="30" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-11-06-one-result-every-angle</t>
-        </is>
-      </c>
-      <c r="P60" s="30" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="Q60" s="30" t="n"/>
+      <c r="O60" s="34" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P60" s="33" t="inlineStr">
+        <is>
+          <t>View 7 slides</t>
+        </is>
+      </c>
+      <c r="Q60" s="30" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
       <c r="R60" s="30" t="n"/>
       <c r="S60" s="30" t="n"/>
       <c r="T60" s="30" t="n"/>
       <c r="U60" s="30" t="n"/>
       <c r="V60" s="30" t="n"/>
+      <c r="W60" s="30" t="n"/>
     </row>
     <row r="61" ht="57.45" customHeight="1" s="14">
       <c r="A61" s="29" t="n">
@@ -5666,22 +5994,27 @@
       </c>
       <c r="M61" s="24" t="n"/>
       <c r="N61" s="24" t="n"/>
-      <c r="O61" s="30" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-11-07-quote-book-the-appointment</t>
-        </is>
-      </c>
-      <c r="P61" s="30" t="inlineStr">
+      <c r="O61" s="34" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P61" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="Q61" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="Q61" s="30" t="n"/>
       <c r="R61" s="30" t="n"/>
       <c r="S61" s="30" t="n"/>
       <c r="T61" s="30" t="n"/>
       <c r="U61" s="30" t="n"/>
       <c r="V61" s="30" t="n"/>
+      <c r="W61" s="30" t="n"/>
     </row>
     <row r="62" ht="57.45" customHeight="1" s="14">
       <c r="A62" s="27" t="n">
@@ -5743,22 +6076,27 @@
       </c>
       <c r="M62" s="24" t="n"/>
       <c r="N62" s="24" t="n"/>
-      <c r="O62" s="28" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-11-09-the-gift-of-glow-gift</t>
-        </is>
-      </c>
-      <c r="P62" s="28" t="inlineStr">
+      <c r="O62" s="32" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P62" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="Q62" s="28" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="Q62" s="28" t="n"/>
       <c r="R62" s="28" t="n"/>
       <c r="S62" s="28" t="n"/>
       <c r="T62" s="28" t="n"/>
       <c r="U62" s="28" t="n"/>
       <c r="V62" s="28" t="n"/>
+      <c r="W62" s="28" t="n"/>
     </row>
     <row r="63" ht="57.45" customHeight="1" s="14">
       <c r="A63" s="29" t="n">
@@ -5820,22 +6158,27 @@
       </c>
       <c r="M63" s="24" t="n"/>
       <c r="N63" s="24" t="n"/>
-      <c r="O63" s="30" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-11-10-gift-certificates-are-here</t>
-        </is>
-      </c>
-      <c r="P63" s="30" t="inlineStr">
+      <c r="O63" s="34" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P63" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="Q63" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="Q63" s="30" t="n"/>
       <c r="R63" s="30" t="n"/>
       <c r="S63" s="30" t="n"/>
       <c r="T63" s="30" t="n"/>
       <c r="U63" s="30" t="n"/>
       <c r="V63" s="30" t="n"/>
+      <c r="W63" s="30" t="n"/>
     </row>
     <row r="64" ht="57.45" customHeight="1" s="14">
       <c r="A64" s="27" t="n">
@@ -5897,22 +6240,27 @@
       </c>
       <c r="M64" s="24" t="n"/>
       <c r="N64" s="24" t="n"/>
-      <c r="O64" s="28" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-11-12-3-months-of-honest-answers</t>
-        </is>
-      </c>
-      <c r="P64" s="28" t="inlineStr">
+      <c r="O64" s="32" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P64" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="Q64" s="28" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="Q64" s="28" t="n"/>
       <c r="R64" s="28" t="n"/>
       <c r="S64" s="28" t="n"/>
       <c r="T64" s="28" t="n"/>
       <c r="U64" s="28" t="n"/>
       <c r="V64" s="28" t="n"/>
+      <c r="W64" s="28" t="n"/>
     </row>
     <row r="65" ht="57.45" customHeight="1" s="14">
       <c r="A65" s="29" t="n">
@@ -5974,22 +6322,27 @@
       </c>
       <c r="M65" s="24" t="n"/>
       <c r="N65" s="24" t="n"/>
-      <c r="O65" s="30" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-11-13-thank-you-3-months-of</t>
-        </is>
-      </c>
-      <c r="P65" s="30" t="inlineStr">
+      <c r="O65" s="34" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P65" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="Q65" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="Q65" s="30" t="n"/>
       <c r="R65" s="30" t="n"/>
       <c r="S65" s="30" t="n"/>
       <c r="T65" s="30" t="n"/>
       <c r="U65" s="30" t="n"/>
       <c r="V65" s="30" t="n"/>
+      <c r="W65" s="30" t="n"/>
     </row>
     <row r="66" ht="57.45" customHeight="1" s="14">
       <c r="A66" s="29" t="n">
@@ -6051,22 +6404,27 @@
       </c>
       <c r="M66" s="24" t="n"/>
       <c r="N66" s="24" t="n"/>
-      <c r="O66" s="30" t="inlineStr">
-        <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-11-14-tag-someone-who-deserves-a</t>
-        </is>
-      </c>
-      <c r="P66" s="30" t="inlineStr">
+      <c r="O66" s="34" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="P66" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="Q66" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="Q66" s="30" t="n"/>
       <c r="R66" s="30" t="n"/>
       <c r="S66" s="30" t="n"/>
       <c r="T66" s="30" t="n"/>
       <c r="U66" s="30" t="n"/>
       <c r="V66" s="30" t="n"/>
+      <c r="W66" s="30" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -6074,6 +6432,82 @@
       <formula1>"Idea,Design,Ready,Hold,Posted"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O5" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O6" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O8" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O39" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P39" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P41" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P44" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O45" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O46" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P49" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O50" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O51" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P51" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O52" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O53" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O54" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O55" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P55" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O56" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O57" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O58" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O59" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O60" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P60" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O61" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O62" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O63" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O64" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O65" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O66" r:id="rId74"/>
+  </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -7155,10 +7589,14 @@
       </c>
       <c r="C18" s="24" t="inlineStr">
         <is>
-          <t>Day 0</t>
-        </is>
-      </c>
-      <c r="D18" s="24" t="inlineStr"/>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
       <c r="E18" s="24" t="inlineStr">
         <is>
           <t>On file</t>
@@ -7166,12 +7604,12 @@
       </c>
       <c r="F18" s="24" t="inlineStr">
         <is>
-          <t>Oct 22</t>
+          <t>Oct 15, Oct 22</t>
         </is>
       </c>
       <c r="G18" s="24" t="inlineStr">
         <is>
-          <t>Yellow headband, day 0, swelling and injection marks visible</t>
+          <t>Before and after from one appointment, minutes apart. Same camera position, so the best matched pair in the library. The after has visible swelling and pinpoint marks, so label it Right after, never After</t>
         </is>
       </c>
     </row>
@@ -7188,10 +7626,14 @@
       </c>
       <c r="C19" s="24" t="inlineStr">
         <is>
-          <t>Day 0</t>
-        </is>
-      </c>
-      <c r="D19" s="24" t="inlineStr"/>
+          <t>After (day 0)</t>
+        </is>
+      </c>
+      <c r="D19" s="24" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
       <c r="E19" s="24" t="inlineStr">
         <is>
           <t>On file</t>
@@ -7199,12 +7641,12 @@
       </c>
       <c r="F19" s="24" t="inlineStr">
         <is>
-          <t>Oct 22</t>
+          <t>Oct 15, Oct 22</t>
         </is>
       </c>
       <c r="G19" s="24" t="inlineStr">
         <is>
-          <t>Yellow headband, day 0, swelling and injection marks visible</t>
+          <t>Before and after from one appointment, minutes apart. Same camera position, so the best matched pair in the library. The after has visible swelling and pinpoint marks, so label it Right after, never After</t>
         </is>
       </c>
     </row>
@@ -7221,7 +7663,7 @@
       </c>
       <c r="C20" s="24" t="inlineStr">
         <is>
-          <t>Day 0 composite</t>
+          <t>After collage</t>
         </is>
       </c>
       <c r="D20" s="24" t="inlineStr"/>
@@ -7237,7 +7679,7 @@
       </c>
       <c r="G20" s="24" t="inlineStr">
         <is>
-          <t>Yellow headband, day 0, swelling and injection marks visible</t>
+          <t>Before and after from one appointment, minutes apart. Same camera position, so the best matched pair in the library. The after has visible swelling and pinpoint marks, so label it Right after, never After</t>
         </is>
       </c>
     </row>
@@ -7270,7 +7712,7 @@
       </c>
       <c r="G21" s="24" t="inlineStr">
         <is>
-          <t>Reclined, day 0, heavily swollen</t>
+          <t>Reclined, day 0, heavily swollen. No before</t>
         </is>
       </c>
     </row>

--- a/strategy/ig-content-strategy.xlsx
+++ b/strategy/ig-content-strategy.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:C39"/>
+  <dimension ref="B2:C49"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3" customWidth="1" style="13" min="1" max="1"/>
@@ -544,7 +544,6 @@
     <col width="20" customWidth="1" style="13" min="5" max="6"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="19.7" customHeight="1" s="14">
       <c r="B2" s="15" t="inlineStr">
         <is>
@@ -559,7 +558,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="14">
       <c r="B5" s="17" t="n"/>
       <c r="C5" s="18" t="n"/>
@@ -799,7 +797,6 @@
         <v/>
       </c>
     </row>
-    <row r="29"/>
     <row r="30" ht="15" customHeight="1" s="14">
       <c r="B30" s="21" t="inlineStr">
         <is>
@@ -807,7 +804,6 @@
         </is>
       </c>
     </row>
-    <row r="31"/>
     <row r="32">
       <c r="B32" s="22" t="inlineStr">
         <is>
@@ -884,6 +880,104 @@
       <c r="C39" s="24" t="inlineStr">
         <is>
           <t>Click to see the finished image for that post. Single-image posts open the picture directly; carousels open the folder of slides. "Not designed yet" means the post has a brief but no artwork.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="22" t="inlineStr">
+        <is>
+          <t>GOOGLE BUSINESS PROFILE</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="C42" s="24" t="inlineStr">
+        <is>
+          <t>Use the GBP Image Link, not the Instagram one. GBP is 1200x900 and crops to a square in Maps.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>Caption</t>
+        </is>
+      </c>
+      <c r="C43" s="24" t="inlineStr">
+        <is>
+          <t>GBP Caption has no hashtags. They do not work on GBP. Only the first 80 characters show before the fold.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="C44" s="24" t="inlineStr">
+        <is>
+          <t>Set the post button to Learn more and point it at the Instagram profile until a booking page exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="23" t="inlineStr">
+        <is>
+          <t>Carousels</t>
+        </is>
+      </c>
+      <c r="C45" s="24" t="inlineStr">
+        <is>
+          <t>GBP has no carousel. One image per post, so carousels use their cover.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="22" t="inlineStr">
+        <is>
+          <t>LOCATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="23" t="inlineStr">
+        <is>
+          <t>Address</t>
+        </is>
+      </c>
+      <c r="C47" s="24" t="inlineStr">
+        <is>
+          <t>3060 Preserve Dr, Oakville, ON L6M 4L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="23" t="inlineStr">
+        <is>
+          <t>Service area</t>
+        </is>
+      </c>
+      <c r="C48" s="24" t="inlineStr">
+        <is>
+          <t>Oakville, Burlington, Milton, Mississauga</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="23" t="inlineStr">
+        <is>
+          <t>Hashtags</t>
+        </is>
+      </c>
+      <c r="C49" s="24" t="inlineStr">
+        <is>
+          <t>Every set now leads with local tags. Location plus service is the highest intent combination.</t>
         </is>
       </c>
     </row>
@@ -900,7 +994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:W66"/>
+  <dimension ref="A1:AA66"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="13" min="1" max="1"/>
@@ -918,9 +1012,13 @@
     <col width="14" customWidth="1" style="13" min="14" max="14"/>
     <col width="16" customWidth="1" style="13" min="15" max="15"/>
     <col width="46" customWidth="1" style="13" min="16" max="17"/>
+    <col width="22" customWidth="1" style="14" min="17" max="17"/>
     <col width="10" customWidth="1" style="13" min="18" max="18"/>
     <col width="8" customWidth="1" style="13" min="19" max="19"/>
     <col width="10" customWidth="1" style="13" min="20" max="20"/>
+    <col width="60" customWidth="1" style="14" min="24" max="24"/>
+    <col width="26" customWidth="1" style="14" min="25" max="25"/>
+    <col width="20" customWidth="1" style="14" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="14">
@@ -1004,39 +1102,59 @@
           <t>Image Link</t>
         </is>
       </c>
-      <c r="Q1" s="25" t="inlineStr">
+      <c r="Q1" s="26" t="inlineStr">
+        <is>
+          <t>Preview</t>
+        </is>
+      </c>
+      <c r="R1" s="25" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="R1" s="25" t="inlineStr">
+      <c r="S1" s="25" t="inlineStr">
         <is>
           <t>Posted Link</t>
         </is>
       </c>
-      <c r="S1" s="25" t="inlineStr">
+      <c r="T1" s="25" t="inlineStr">
         <is>
           <t>Reach</t>
         </is>
       </c>
-      <c r="T1" s="25" t="inlineStr">
+      <c r="U1" s="25" t="inlineStr">
         <is>
           <t>Saves</t>
         </is>
       </c>
-      <c r="U1" s="25" t="inlineStr">
+      <c r="V1" s="25" t="inlineStr">
         <is>
           <t>Comments</t>
         </is>
       </c>
-      <c r="V1" s="25" t="inlineStr">
+      <c r="W1" s="25" t="inlineStr">
         <is>
           <t>DMs</t>
         </is>
       </c>
-      <c r="W1" s="25" t="inlineStr">
+      <c r="X1" s="25" t="inlineStr">
         <is>
           <t>Bookings</t>
+        </is>
+      </c>
+      <c r="Y1" s="26" t="inlineStr">
+        <is>
+          <t>GBP Caption</t>
+        </is>
+      </c>
+      <c r="Z1" s="26" t="inlineStr">
+        <is>
+          <t>GBP CTA</t>
+        </is>
+      </c>
+      <c r="AA1" s="26" t="inlineStr">
+        <is>
+          <t>GBP Image Link</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1182,7 @@
       </c>
       <c r="F2" s="28" t="inlineStr">
         <is>
-          <t>Instagram feed</t>
+          <t>Instagram feed + GBP</t>
         </is>
       </c>
       <c r="G2" s="28" t="inlineStr">
@@ -1079,7 +1197,7 @@
       </c>
       <c r="I2" s="28" t="inlineStr">
         <is>
-          <t>Half of what you have heard about Botox came from someone who saw bad work. Let's set the record straight. Which myth did you believe? Drop it below and share this with a friend who needs slide 5. ✨
+          <t>Half of what you have heard about Botox came from someone who saw bad work. Let's set the record straight. Which myth did you believe? Drop it below and share this with a friend who needs slide 5.
 #botox #botoxeducation #botoxmyths #preventativebotox #antiwrinkleinjections #nurseinjector #medspa #naturalbotox #botoxbeforeandafter #aestheticnurse</t>
         </is>
       </c>
@@ -1110,17 +1228,28 @@
           <t>View 8 slides</t>
         </is>
       </c>
-      <c r="Q2" s="28" t="inlineStr">
+      <c r="Q2" s="24">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-08-17-5-botox-lies-you-still/images/slide-1.png")</f>
+        <v/>
+      </c>
+      <c r="R2" s="28" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="R2" s="28" t="n"/>
       <c r="S2" s="28" t="n"/>
       <c r="T2" s="28" t="n"/>
       <c r="U2" s="28" t="n"/>
       <c r="V2" s="28" t="n"/>
       <c r="W2" s="28" t="n"/>
+      <c r="X2" s="28" t="n"/>
+      <c r="Y2" s="24" t="n"/>
+      <c r="Z2" s="24" t="n"/>
+      <c r="AA2" s="33" t="inlineStr">
+        <is>
+          <t>View GBP image</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="57.45" customHeight="1" s="14">
       <c r="A3" s="29" t="n">
@@ -1146,7 +1275,7 @@
       </c>
       <c r="F3" s="30" t="inlineStr">
         <is>
-          <t>IG + FB + TikTok photo</t>
+          <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
       <c r="G3" s="30" t="inlineStr">
@@ -1161,7 +1290,7 @@
       </c>
       <c r="I3" s="30" t="inlineStr">
         <is>
-          <t>Softened lines, full expression, and nobody can tell why you look so rested. That is Botox done right. ✨
+          <t>Softened lines, full expression, and nobody can tell why you look so rested. That is Botox done right.
 #botox #botoxeducation #botoxmyths #preventativebotox #antiwrinkleinjections #nurseinjector #medspa #naturalbotox #botoxbeforeandafter #aestheticnurse</t>
         </is>
       </c>
@@ -1192,17 +1321,28 @@
           <t>View image</t>
         </is>
       </c>
-      <c r="Q3" s="30" t="inlineStr">
+      <c r="Q3" s="24">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-08-18-service-spotlight-botox/images/post.png")</f>
+        <v/>
+      </c>
+      <c r="R3" s="30" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="R3" s="30" t="n"/>
       <c r="S3" s="30" t="n"/>
       <c r="T3" s="30" t="n"/>
       <c r="U3" s="30" t="n"/>
       <c r="V3" s="30" t="n"/>
       <c r="W3" s="30" t="n"/>
+      <c r="X3" s="30" t="n"/>
+      <c r="Y3" s="24" t="n"/>
+      <c r="Z3" s="24" t="n"/>
+      <c r="AA3" s="33" t="inlineStr">
+        <is>
+          <t>View GBP image</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="68.65000000000001" customHeight="1" s="14">
       <c r="A4" s="27" t="n">
@@ -1228,7 +1368,7 @@
       </c>
       <c r="F4" s="28" t="inlineStr">
         <is>
-          <t>Instagram feed</t>
+          <t>Instagram feed + GBP</t>
         </is>
       </c>
       <c r="G4" s="28" t="inlineStr">
@@ -1243,13 +1383,19 @@
       </c>
       <c r="I4" s="28" t="inlineStr">
         <is>
-          <t>A menu with no consultation, prices too good to be true, and nobody asking about your medical history. If you see these, walk away. I want you safe, even if you never book with me. Save this checklist. 💛
-#npinjector #nursepractitioner #medspalife #luxurybeauty #aestheticnurse #skincareexpert #beautyclinic #selfcare #naturalresults #honestbeauty</t>
+          <t>If nobody asked you a single question before picking up a needle, leave.
+I have fixed enough work from other clinics to know the pattern. The problem is
+almost never the product. It starts with an appointment that skipped the part
+where somebody actually looked at your face.
+Five things worth walking away from. The last one is the one people forget to
+ask about, and it is the one that matters most if something ever goes wrong.
+Save this and take it to your next consult, wherever you book.
+#oakvillemedspa #burlingtonmedspa #miltonontario #mississaugabeauty #haltonregion #honestinjector #naturalresults #aestheticnurse #nursepractitioner #medspacanada #luxurybeautybycleor #npcleo</t>
         </is>
       </c>
       <c r="J4" s="28" t="inlineStr">
         <is>
-          <t>Save this checklist</t>
+          <t>Save this before you book</t>
         </is>
       </c>
       <c r="K4" s="28" t="inlineStr">
@@ -1269,22 +1415,41 @@
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P4" s="24" t="inlineStr">
-        <is>
-          <t>Not designed yet</t>
-        </is>
-      </c>
-      <c r="Q4" s="28" t="inlineStr">
-        <is>
-          <t>Idea</t>
-        </is>
-      </c>
-      <c r="R4" s="28" t="n"/>
+      <c r="P4" s="33" t="inlineStr">
+        <is>
+          <t>View 7 slides</t>
+        </is>
+      </c>
+      <c r="Q4" s="24">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-08-20-5-red-flags-at-a/images/slide-1.png")</f>
+        <v/>
+      </c>
+      <c r="R4" s="28" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
       <c r="S4" s="28" t="n"/>
       <c r="T4" s="28" t="n"/>
       <c r="U4" s="28" t="n"/>
       <c r="V4" s="28" t="n"/>
       <c r="W4" s="28" t="n"/>
+      <c r="X4" s="28" t="n"/>
+      <c r="Y4" s="24" t="inlineStr">
+        <is>
+          <t>Five things to walk away from at a med spa: no consultation, bargain pricing, a provider who never says no, no named injector, and no plan for complications. Know them before you book anywhere. Serving Oakville, Burlington, Milton and Mississauga.</t>
+        </is>
+      </c>
+      <c r="Z4" s="24" t="inlineStr">
+        <is>
+          <t>Learn more &gt; Instagram</t>
+        </is>
+      </c>
+      <c r="AA4" s="33" t="inlineStr">
+        <is>
+          <t>View GBP image</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="57.45" customHeight="1" s="14">
       <c r="A5" s="29" t="n">
@@ -1310,7 +1475,7 @@
       </c>
       <c r="F5" s="30" t="inlineStr">
         <is>
-          <t>IG + FB + TikTok photo</t>
+          <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
       <c r="G5" s="30" t="inlineStr">
@@ -1325,18 +1490,24 @@
       </c>
       <c r="I5" s="30" t="inlineStr">
         <is>
-          <t>Sealed products, precise dosing, clean everything. This is the part you never see, and the part that matters most. 💛
-#npinjector #nursepractitioner #medspalife #luxurybeauty #aestheticnurse #skincareexpert #beautyclinic #selfcare #naturalresults #honestbeauty</t>
+          <t>The part nobody films is the part that keeps you safe.
+New tray. New gloves. Product opened in front of you so you can see the vial,
+the lot number and the date. Your face marked while you are moving, because
+muscles do not sit still and neither should the plan.
+None of this is impressive. It is just the standard. I am showing it because
+plenty of places skip it and you would never know.
+Ask to watch next time. Anyone doing it properly will say yes.
+#oakville #oakvillebusiness #burlingtonontario #miltonontario #mississauga #haltonregion #womeninbusiness #nursepractitioner #aestheticnurse #medspalife #luxurybeautybycleor #npcleo</t>
         </is>
       </c>
       <c r="J5" s="30" t="inlineStr">
         <is>
-          <t>Book with confidence. Link in bio</t>
+          <t>Zero shortcuts. Ever.</t>
         </is>
       </c>
       <c r="K5" s="30" t="inlineStr">
         <is>
-          <t>Set C</t>
+          <t>Set D</t>
         </is>
       </c>
       <c r="L5" s="30" t="inlineStr">
@@ -1351,22 +1522,41 @@
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P5" s="24" t="inlineStr">
-        <is>
-          <t>Not designed yet</t>
-        </is>
-      </c>
-      <c r="Q5" s="30" t="inlineStr">
-        <is>
-          <t>Idea</t>
-        </is>
-      </c>
-      <c r="R5" s="30" t="n"/>
+      <c r="P5" s="33" t="inlineStr">
+        <is>
+          <t>View image</t>
+        </is>
+      </c>
+      <c r="Q5" s="24">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-08-21-behind-the-scenes-the-prep/images/post.png")</f>
+        <v/>
+      </c>
+      <c r="R5" s="30" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
       <c r="S5" s="30" t="n"/>
       <c r="T5" s="30" t="n"/>
       <c r="U5" s="30" t="n"/>
       <c r="V5" s="30" t="n"/>
       <c r="W5" s="30" t="n"/>
+      <c r="X5" s="30" t="n"/>
+      <c r="Y5" s="24" t="inlineStr">
+        <is>
+          <t>Every appointment starts the same way. New tray, sealed product opened in front of you, and your face mapped while it moves so the plan fits how you actually move. Ask to watch. Serving Oakville, Burlington, Milton and Mississauga.</t>
+        </is>
+      </c>
+      <c r="Z5" s="24" t="inlineStr">
+        <is>
+          <t>Learn more &gt; Instagram</t>
+        </is>
+      </c>
+      <c r="AA5" s="33" t="inlineStr">
+        <is>
+          <t>View GBP image</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="46.25" customHeight="1" s="14">
       <c r="A6" s="29" t="n">
@@ -1387,12 +1577,12 @@
       </c>
       <c r="E6" s="30" t="inlineStr">
         <is>
-          <t>Single Image</t>
+          <t>Before/After</t>
         </is>
       </c>
       <c r="F6" s="30" t="inlineStr">
         <is>
-          <t>IG + FB + TikTok photo</t>
+          <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
       <c r="G6" s="30" t="inlineStr">
@@ -1402,53 +1592,86 @@
       </c>
       <c r="H6" s="30" t="inlineStr">
         <is>
-          <t>Quote: Great Work Is Invisible | Brand quote card.</t>
+          <t>Great Work Is Invisible | You were not supposed to notice.</t>
         </is>
       </c>
       <c r="I6" s="30" t="inlineStr">
         <is>
-          <t>Great work is invisible. Bad work is what gave Botox its reputation. Agree or disagree? 👇
-#npinjector #nursepractitioner #medspalife #luxurybeauty #aestheticnurse #skincareexpert #beautyclinic #selfcare #naturalresults #honestbeauty</t>
+          <t>She booked because her top lip disappeared when she smiled.
+Not because she wanted bigger lips. She was very clear about that. One syringe,
+placed along a lip line that was already there, and the shape she was born with
+stayed exactly where it was.
+If you scrolled past this without stopping, that is the result doing its job.
+Good work does not announce itself.
+Shared with her permission. Individual results vary.
+#lipfilleroakville #fillersoakville #oakvillemedspa #burlingtonfiller #miltonlipfiller #mississaugamedspa #dermalfillers #naturallips #facialbalancing #aestheticnurse #luxurybeautybycleor #npcleo</t>
         </is>
       </c>
       <c r="J6" s="30" t="inlineStr">
         <is>
-          <t>Comment below</t>
+          <t>Message to book</t>
         </is>
       </c>
       <c r="K6" s="30" t="inlineStr">
         <is>
-          <t>Set C</t>
+          <t>Set B</t>
         </is>
       </c>
       <c r="L6" s="30" t="inlineStr">
         <is>
-          <t>Quote card in editorial brand style</t>
-        </is>
-      </c>
-      <c r="M6" s="24" t="n"/>
-      <c r="N6" s="24" t="n"/>
+          <t>Before and after card in editorial template. Crop to treatment area, no faces</t>
+        </is>
+      </c>
+      <c r="M6" s="24" t="inlineStr">
+        <is>
+          <t>img_9908 (before), img_9912 (after)</t>
+        </is>
+      </c>
+      <c r="N6" s="24" t="inlineStr">
+        <is>
+          <t>Not needed</t>
+        </is>
+      </c>
       <c r="O6" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P6" s="24" t="inlineStr">
-        <is>
-          <t>Not designed yet</t>
-        </is>
-      </c>
-      <c r="Q6" s="30" t="inlineStr">
-        <is>
-          <t>Idea</t>
-        </is>
-      </c>
-      <c r="R6" s="30" t="n"/>
+      <c r="P6" s="33" t="inlineStr">
+        <is>
+          <t>View image</t>
+        </is>
+      </c>
+      <c r="Q6" s="24">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-08-22-great-work-is-invisible/images/before-after-result.png")</f>
+        <v/>
+      </c>
+      <c r="R6" s="30" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
       <c r="S6" s="30" t="n"/>
       <c r="T6" s="30" t="n"/>
       <c r="U6" s="30" t="n"/>
       <c r="V6" s="30" t="n"/>
       <c r="W6" s="30" t="n"/>
+      <c r="X6" s="30" t="n"/>
+      <c r="Y6" s="24" t="inlineStr">
+        <is>
+          <t>One syringe of lip filler, with her own lip shape kept exactly where it was. Natural results are the whole point of how we practise. Shared with client consent, individual results vary. Serving Oakville, Burlington, Milton and Mississauga.</t>
+        </is>
+      </c>
+      <c r="Z6" s="24" t="inlineStr">
+        <is>
+          <t>Learn more &gt; Instagram</t>
+        </is>
+      </c>
+      <c r="AA6" s="33" t="inlineStr">
+        <is>
+          <t>View GBP image</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="57.45" customHeight="1" s="14">
       <c r="A7" s="27" t="n">
@@ -1474,7 +1697,7 @@
       </c>
       <c r="F7" s="28" t="inlineStr">
         <is>
-          <t>Instagram feed</t>
+          <t>Instagram feed + GBP</t>
         </is>
       </c>
       <c r="G7" s="28" t="inlineStr">
@@ -1489,18 +1712,25 @@
       </c>
       <c r="I7" s="28" t="inlineStr">
         <is>
-          <t>80 percent of first-timers tell me they waited years because they did not know what to expect. Consider this your preview. Send it to the friend who keeps saying one day.
-#npinjector #nursepractitioner #medspalife #luxurybeauty #aestheticnurse #skincareexpert #beautyclinic #selfcare #naturalresults #honestbeauty</t>
+          <t>Most people arrive nervous and leave asking why they waited so long.
+Usually that is because nobody told them what actually happens. So here it is,
+start to finish, including the part where we agree on the areas, the units and
+the price before anything gets opened.
+The treatment itself is the short part. Ten to fifteen minutes for most people.
+Everything before it is what makes the difference.
+Swipe through. If you are still nervous at the end, send me the question you
+are embarrassed to ask. I have heard it before.
+#botoxoakville #oakvillemedspa #burlingtonbotox #miltonmedspa #mississaugainjector #haltonregion #preventativebotox #botoxcanada #nursepractitionerinjector #naturalresults #luxurybeautybycleor #npcleo</t>
         </is>
       </c>
       <c r="J7" s="28" t="inlineStr">
         <is>
-          <t>Book your consult. Link in bio</t>
+          <t>DM to book a consult</t>
         </is>
       </c>
       <c r="K7" s="28" t="inlineStr">
         <is>
-          <t>Set C</t>
+          <t>Set A</t>
         </is>
       </c>
       <c r="L7" s="28" t="inlineStr">
@@ -1515,22 +1745,41 @@
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P7" s="24" t="inlineStr">
-        <is>
-          <t>Not designed yet</t>
-        </is>
-      </c>
-      <c r="Q7" s="28" t="inlineStr">
-        <is>
-          <t>Idea</t>
-        </is>
-      </c>
-      <c r="R7" s="28" t="n"/>
+      <c r="P7" s="33" t="inlineStr">
+        <is>
+          <t>View 8 slides</t>
+        </is>
+      </c>
+      <c r="Q7" s="24">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-08-24-your-first-visit-step-by/images/slide-1.png")</f>
+        <v/>
+      </c>
+      <c r="R7" s="28" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
       <c r="S7" s="28" t="n"/>
       <c r="T7" s="28" t="n"/>
       <c r="U7" s="28" t="n"/>
       <c r="V7" s="28" t="n"/>
       <c r="W7" s="28" t="n"/>
+      <c r="X7" s="28" t="n"/>
+      <c r="Y7" s="24" t="inlineStr">
+        <is>
+          <t>Nervous about your first appointment? A real consultation, your face mapped in motion, then the areas and the price agreed before anything is opened. The treatment itself takes about ten minutes. Serving Oakville, Burlington, Milton and Mississauga.</t>
+        </is>
+      </c>
+      <c r="Z7" s="24" t="inlineStr">
+        <is>
+          <t>Learn more &gt; Instagram</t>
+        </is>
+      </c>
+      <c r="AA7" s="33" t="inlineStr">
+        <is>
+          <t>View GBP image</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="57.45" customHeight="1" s="14">
       <c r="A8" s="29" t="n">
@@ -1556,7 +1805,7 @@
       </c>
       <c r="F8" s="30" t="inlineStr">
         <is>
-          <t>IG + FB + TikTok photo</t>
+          <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
       <c r="G8" s="30" t="inlineStr">
@@ -1571,18 +1820,23 @@
       </c>
       <c r="I8" s="30" t="inlineStr">
         <is>
-          <t>If your consult is shorter than your coffee order, that is a problem. Save this checklist and trust your gut.
-#botox #botoxeducation #botoxmyths #preventativebotox #antiwrinkleinjections #nurseinjector #medspa #naturalbotox #botoxbeforeandafter #aestheticnurse</t>
+          <t>Ten minutes in and out is not efficient. It is skipped steps.
+The injecting really is quick. The looking, the mapping and the conversation
+are not, and those are the parts that decide whether you like your face in two
+weeks.
+Three signs you are being processed instead of treated. Screenshot them and
+take them to your next appointment, wherever that is.
+#oakvillemedspa #burlingtonmedspa #miltonontario #mississaugabeauty #haltonregion #honestinjector #naturalresults #aestheticnurse #nursepractitioner #medspacanada #luxurybeautybycleor #npcleo</t>
         </is>
       </c>
       <c r="J8" s="30" t="inlineStr">
         <is>
-          <t>Save + share this</t>
+          <t>Save this. Use it.</t>
         </is>
       </c>
       <c r="K8" s="30" t="inlineStr">
         <is>
-          <t>Set A</t>
+          <t>Set C</t>
         </is>
       </c>
       <c r="L8" s="30" t="inlineStr">
@@ -1597,22 +1851,41 @@
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P8" s="24" t="inlineStr">
-        <is>
-          <t>Not designed yet</t>
-        </is>
-      </c>
-      <c r="Q8" s="30" t="inlineStr">
-        <is>
-          <t>Idea</t>
-        </is>
-      </c>
-      <c r="R8" s="30" t="n"/>
+      <c r="P8" s="33" t="inlineStr">
+        <is>
+          <t>View image</t>
+        </is>
+      </c>
+      <c r="Q8" s="24">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-08-25-3-signs-your-injector-is/images/post.png")</f>
+        <v/>
+      </c>
+      <c r="R8" s="30" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
       <c r="S8" s="30" t="n"/>
       <c r="T8" s="30" t="n"/>
       <c r="U8" s="30" t="n"/>
       <c r="V8" s="30" t="n"/>
       <c r="W8" s="30" t="n"/>
+      <c r="X8" s="30" t="n"/>
+      <c r="Y8" s="24" t="inlineStr">
+        <is>
+          <t>Three signs your injector is rushing you: no mirror and no map, units decided before you spoke, and the whole visit over in under ten minutes. Worth knowing before you book anywhere. Serving Oakville, Burlington, Milton and Mississauga.</t>
+        </is>
+      </c>
+      <c r="Z8" s="24" t="inlineStr">
+        <is>
+          <t>Learn more &gt; Instagram</t>
+        </is>
+      </c>
+      <c r="AA8" s="33" t="inlineStr">
+        <is>
+          <t>View GBP image</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="57.45" customHeight="1" s="14">
       <c r="A9" s="27" t="n">
@@ -1638,7 +1911,7 @@
       </c>
       <c r="F9" s="28" t="inlineStr">
         <is>
-          <t>Instagram feed</t>
+          <t>Instagram feed + GBP</t>
         </is>
       </c>
       <c r="G9" s="28" t="inlineStr">
@@ -1653,18 +1926,25 @@
       </c>
       <c r="I9" s="28" t="inlineStr">
         <is>
-          <t>Before you trust someone with your face, you should know who they are. Here is my story, my training, and why I will always tell you the truth about what you need. 💛
-#npinjector #nursepractitioner #medspalife #luxurybeauty #aestheticnurse #skincareexpert #beautyclinic #selfcare #naturalresults #honestbeauty</t>
+          <t>I got tired of fixing work that never should have happened.
+That is the honest reason this clinic exists. Most people who sit in my chair
+are not asking for a different face. They want to stop looking tired, and
+somewhere along the way the industry decided more was always the answer.
+So I go slow. I dose conservatively, I build over sessions, and I say not yet
+more often than people expect. I have never once regretted that.
+Nurse practitioner. Every appointment injected by me, never handed off to
+somebody you have not met.
+#oakville #oakvillebusiness #burlingtonontario #miltonontario #mississauga #haltonregion #womeninbusiness #nursepractitioner #aestheticnurse #medspalife #luxurybeautybycleor #npcleo</t>
         </is>
       </c>
       <c r="J9" s="28" t="inlineStr">
         <is>
-          <t>Say hi in the comments</t>
+          <t>DM the word CONSULT</t>
         </is>
       </c>
       <c r="K9" s="28" t="inlineStr">
         <is>
-          <t>Set C</t>
+          <t>Set D</t>
         </is>
       </c>
       <c r="L9" s="28" t="inlineStr">
@@ -1679,22 +1959,41 @@
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P9" s="24" t="inlineStr">
-        <is>
-          <t>Not designed yet</t>
-        </is>
-      </c>
-      <c r="Q9" s="28" t="inlineStr">
-        <is>
-          <t>Idea</t>
-        </is>
-      </c>
-      <c r="R9" s="28" t="n"/>
+      <c r="P9" s="33" t="inlineStr">
+        <is>
+          <t>View 5 slides</t>
+        </is>
+      </c>
+      <c r="Q9" s="24">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-08-27-meet-np-cleo-the-face/images/slide-1.png")</f>
+        <v/>
+      </c>
+      <c r="R9" s="28" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
       <c r="S9" s="28" t="n"/>
       <c r="T9" s="28" t="n"/>
       <c r="U9" s="28" t="n"/>
       <c r="V9" s="28" t="n"/>
       <c r="W9" s="28" t="n"/>
+      <c r="X9" s="28" t="n"/>
+      <c r="Y9" s="24" t="inlineStr">
+        <is>
+          <t>Meet NP Cleo. Nurse practitioner and injector, and the person who will tell you no when the honest answer is not yet. Every appointment is injected by Cleo, never delegated. Serving Oakville, Burlington, Milton and Mississauga.</t>
+        </is>
+      </c>
+      <c r="Z9" s="24" t="inlineStr">
+        <is>
+          <t>Learn more &gt; Instagram</t>
+        </is>
+      </c>
+      <c r="AA9" s="33" t="inlineStr">
+        <is>
+          <t>View GBP image</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="46.25" customHeight="1" s="14">
       <c r="A10" s="29" t="n">
@@ -1720,7 +2019,7 @@
       </c>
       <c r="F10" s="30" t="inlineStr">
         <is>
-          <t>IG + FB + TikTok photo</t>
+          <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
       <c r="G10" s="30" t="inlineStr">
@@ -1735,18 +2034,23 @@
       </c>
       <c r="I10" s="30" t="inlineStr">
         <is>
-          <t>Clean, quiet, and designed for you to feel safe asking anything. Come see it in person. 💛
-#npinjector #nursepractitioner #medspalife #luxurybeauty #aestheticnurse #skincareexpert #beautyclinic #selfcare #naturalresults #honestbeauty</t>
+          <t>One person in the room at a time, and the door stays shut.
+Nobody rushes the client before you, which means nobody rushes you either. You
+get the whole appointment, the questions you were too shy to ask somewhere
+else, and a plan we agree on before anything happens.
+It is a quiet room on purpose. Decisions about your face deserve one.
+In Oakville, and worth the short drive from Burlington, Milton or Mississauga.
+#oakville #oakvillebusiness #burlingtonontario #miltonontario #mississauga #haltonregion #womeninbusiness #nursepractitioner #aestheticnurse #medspalife #luxurybeautybycleor #npcleo</t>
         </is>
       </c>
       <c r="J10" s="30" t="inlineStr">
         <is>
-          <t>Book a visit. Link in bio</t>
+          <t>Come see it</t>
         </is>
       </c>
       <c r="K10" s="30" t="inlineStr">
         <is>
-          <t>Set C</t>
+          <t>Set D</t>
         </is>
       </c>
       <c r="L10" s="30" t="inlineStr">
@@ -1761,22 +2065,41 @@
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P10" s="24" t="inlineStr">
-        <is>
-          <t>Not designed yet</t>
-        </is>
-      </c>
-      <c r="Q10" s="30" t="inlineStr">
-        <is>
-          <t>Idea</t>
-        </is>
-      </c>
-      <c r="R10" s="30" t="n"/>
+      <c r="P10" s="33" t="inlineStr">
+        <is>
+          <t>View image</t>
+        </is>
+      </c>
+      <c r="Q10" s="24">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-08-28-welcome-to-the-treatment-room/images/post.png")</f>
+        <v/>
+      </c>
+      <c r="R10" s="30" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
       <c r="S10" s="30" t="n"/>
       <c r="T10" s="30" t="n"/>
       <c r="U10" s="30" t="n"/>
       <c r="V10" s="30" t="n"/>
       <c r="W10" s="30" t="n"/>
+      <c r="X10" s="30" t="n"/>
+      <c r="Y10" s="24" t="inlineStr">
+        <is>
+          <t>One client in the treatment room at a time. Nobody rushes the person before you, so nobody rushes you. Questions welcome, and a plan agreed before anything happens. Serving Oakville, Burlington, Milton and Mississauga.</t>
+        </is>
+      </c>
+      <c r="Z10" s="24" t="inlineStr">
+        <is>
+          <t>Learn more &gt; Instagram</t>
+        </is>
+      </c>
+      <c r="AA10" s="33" t="inlineStr">
+        <is>
+          <t>View GBP image</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="46.25" customHeight="1" s="14">
       <c r="A11" s="29" t="n">
@@ -1802,7 +2125,7 @@
       </c>
       <c r="F11" s="30" t="inlineStr">
         <is>
-          <t>IG + FB + TikTok photo</t>
+          <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
       <c r="G11" s="30" t="inlineStr">
@@ -1812,18 +2135,22 @@
       </c>
       <c r="H11" s="30" t="inlineStr">
         <is>
-          <t>This or That: Rested vs Frozen | Engagement post.</t>
+          <t>This or That: Rested vs Frozen | If people ask what you had done, the dose was wrong.</t>
         </is>
       </c>
       <c r="I11" s="30" t="inlineStr">
         <is>
-          <t>When you picture your results, which one are you actually asking for? Vote below. 👇
-#npinjector #nursepractitioner #medspalife #luxurybeauty #aestheticnurse #skincareexpert #beautyclinic #selfcare #naturalresults #honestbeauty</t>
+          <t>If people ask what you had done, the dose was wrong.
+The goal was never to erase your expressions. You should still frown at your
+inbox and squint in the sun. Softer, not stiller.
+Rested or frozen. Which were you actually hoping for? Tell me in the comments,
+I read all of them.
+#oakvillemedspa #burlingtonmedspa #miltonontario #mississaugabeauty #haltonregion #honestinjector #naturalresults #aestheticnurse #nursepractitioner #medspacanada #luxurybeautybycleor #npcleo</t>
         </is>
       </c>
       <c r="J11" s="30" t="inlineStr">
         <is>
-          <t>Vote in the comments</t>
+          <t>Which one do you want?</t>
         </is>
       </c>
       <c r="K11" s="30" t="inlineStr">
@@ -1843,22 +2170,41 @@
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P11" s="24" t="inlineStr">
-        <is>
-          <t>Not designed yet</t>
-        </is>
-      </c>
-      <c r="Q11" s="30" t="inlineStr">
-        <is>
-          <t>Idea</t>
-        </is>
-      </c>
-      <c r="R11" s="30" t="n"/>
+      <c r="P11" s="33" t="inlineStr">
+        <is>
+          <t>View image</t>
+        </is>
+      </c>
+      <c r="Q11" s="24">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-08-29-this-or-that-rested-vs/images/post.png")</f>
+        <v/>
+      </c>
+      <c r="R11" s="30" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
       <c r="S11" s="30" t="n"/>
       <c r="T11" s="30" t="n"/>
       <c r="U11" s="30" t="n"/>
       <c r="V11" s="30" t="n"/>
       <c r="W11" s="30" t="n"/>
+      <c r="X11" s="30" t="n"/>
+      <c r="Y11" s="24" t="inlineStr">
+        <is>
+          <t>Rested, not frozen. You should still frown, squint and smile. If people ask what you had done instead of whether you slept well, the dose was wrong. Serving Oakville, Burlington, Milton and Mississauga.</t>
+        </is>
+      </c>
+      <c r="Z11" s="24" t="inlineStr">
+        <is>
+          <t>Learn more &gt; Instagram</t>
+        </is>
+      </c>
+      <c r="AA11" s="33" t="inlineStr">
+        <is>
+          <t>View GBP image</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="57.45" customHeight="1" s="14">
       <c r="A12" s="27" t="n">
@@ -1884,7 +2230,7 @@
       </c>
       <c r="F12" s="28" t="inlineStr">
         <is>
-          <t>Instagram feed</t>
+          <t>Instagram feed + GBP</t>
         </is>
       </c>
       <c r="G12" s="28" t="inlineStr">
@@ -1899,13 +2245,20 @@
       </c>
       <c r="I12" s="28" t="inlineStr">
         <is>
-          <t>Lines are easier to prevent than to erase. Here is how to know if your late 20s or 30s is the right time to start, and when it is honestly still too early. No pressure, just real timing.
-#botox #botoxeducation #botoxmyths #preventativebotox #antiwrinkleinjections #nurseinjector #medspa #naturalbotox #botoxbeforeandafter #aestheticnurse</t>
+          <t>Your friend who never seems to age did not get lucky.
+She started before there was anything to fix. That is the whole trick, and it
+has very little to do with turning thirty.
+Here is the test you can do right now. Make your strongest expression, then let
+your face go completely still. If a line is still sitting there, that one is
+setting in, and that is the conversation worth having.
+Swipe for when to actually start. If you do not need it yet, I will tell you
+that too.
+#botoxoakville #oakvillemedspa #burlingtonbotox #miltonmedspa #mississaugainjector #haltonregion #preventativebotox #botoxcanada #nursepractitionerinjector #naturalresults #luxurybeautybycleor #npcleo</t>
         </is>
       </c>
       <c r="J12" s="28" t="inlineStr">
         <is>
-          <t>DM PREVENT for a consult</t>
+          <t>DM the word START</t>
         </is>
       </c>
       <c r="K12" s="28" t="inlineStr">
@@ -1925,22 +2278,41 @@
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P12" s="24" t="inlineStr">
-        <is>
-          <t>Not designed yet</t>
-        </is>
-      </c>
-      <c r="Q12" s="28" t="inlineStr">
-        <is>
-          <t>Idea</t>
-        </is>
-      </c>
-      <c r="R12" s="28" t="n"/>
+      <c r="P12" s="33" t="inlineStr">
+        <is>
+          <t>View 7 slides</t>
+        </is>
+      </c>
+      <c r="Q12" s="24">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-08-31-preventative-botox-when-to-actually/images/slide-1.png")</f>
+        <v/>
+      </c>
+      <c r="R12" s="28" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
       <c r="S12" s="28" t="n"/>
       <c r="T12" s="28" t="n"/>
       <c r="U12" s="28" t="n"/>
       <c r="V12" s="28" t="n"/>
       <c r="W12" s="28" t="n"/>
+      <c r="X12" s="28" t="n"/>
+      <c r="Y12" s="24" t="inlineStr">
+        <is>
+          <t>When should you actually start preventative treatment? It is not about your age. Make your strongest expression, then relax completely. A line that stays is one that is setting in. Serving Oakville, Burlington, Milton and Mississauga.</t>
+        </is>
+      </c>
+      <c r="Z12" s="24" t="inlineStr">
+        <is>
+          <t>Learn more &gt; Instagram</t>
+        </is>
+      </c>
+      <c r="AA12" s="33" t="inlineStr">
+        <is>
+          <t>View GBP image</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="57.45" customHeight="1" s="14">
       <c r="A13" s="29" t="n">
@@ -1966,7 +2338,7 @@
       </c>
       <c r="F13" s="30" t="inlineStr">
         <is>
-          <t>IG + FB + TikTok photo</t>
+          <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
       <c r="G13" s="30" t="inlineStr">
@@ -2012,17 +2384,25 @@
           <t>Not designed yet</t>
         </is>
       </c>
-      <c r="Q13" s="30" t="inlineStr">
+      <c r="Q13" s="24" t="n"/>
+      <c r="R13" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="R13" s="30" t="n"/>
       <c r="S13" s="30" t="n"/>
       <c r="T13" s="30" t="n"/>
       <c r="U13" s="30" t="n"/>
       <c r="V13" s="30" t="n"/>
       <c r="W13" s="30" t="n"/>
+      <c r="X13" s="30" t="n"/>
+      <c r="Y13" s="24" t="n"/>
+      <c r="Z13" s="24" t="n"/>
+      <c r="AA13" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="57.45" customHeight="1" s="14">
       <c r="A14" s="27" t="n">
@@ -2048,7 +2428,7 @@
       </c>
       <c r="F14" s="28" t="inlineStr">
         <is>
-          <t>Instagram feed</t>
+          <t>Instagram feed + GBP</t>
         </is>
       </c>
       <c r="G14" s="28" t="inlineStr">
@@ -2094,17 +2474,25 @@
           <t>Not designed yet</t>
         </is>
       </c>
-      <c r="Q14" s="28" t="inlineStr">
+      <c r="Q14" s="24" t="n"/>
+      <c r="R14" s="28" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="R14" s="28" t="n"/>
       <c r="S14" s="28" t="n"/>
       <c r="T14" s="28" t="n"/>
       <c r="U14" s="28" t="n"/>
       <c r="V14" s="28" t="n"/>
       <c r="W14" s="28" t="n"/>
+      <c r="X14" s="28" t="n"/>
+      <c r="Y14" s="24" t="n"/>
+      <c r="Z14" s="24" t="n"/>
+      <c r="AA14" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="57.45" customHeight="1" s="14">
       <c r="A15" s="29" t="n">
@@ -2130,7 +2518,7 @@
       </c>
       <c r="F15" s="30" t="inlineStr">
         <is>
-          <t>IG + FB + TikTok photo</t>
+          <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
       <c r="G15" s="30" t="inlineStr">
@@ -2176,17 +2564,25 @@
           <t>Not designed yet</t>
         </is>
       </c>
-      <c r="Q15" s="30" t="inlineStr">
+      <c r="Q15" s="24" t="n"/>
+      <c r="R15" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="R15" s="30" t="n"/>
       <c r="S15" s="30" t="n"/>
       <c r="T15" s="30" t="n"/>
       <c r="U15" s="30" t="n"/>
       <c r="V15" s="30" t="n"/>
       <c r="W15" s="30" t="n"/>
+      <c r="X15" s="30" t="n"/>
+      <c r="Y15" s="24" t="n"/>
+      <c r="Z15" s="24" t="n"/>
+      <c r="AA15" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="46.25" customHeight="1" s="14">
       <c r="A16" s="29" t="n">
@@ -2212,7 +2608,7 @@
       </c>
       <c r="F16" s="30" t="inlineStr">
         <is>
-          <t>IG + FB + TikTok photo</t>
+          <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
       <c r="G16" s="30" t="inlineStr">
@@ -2227,7 +2623,7 @@
       </c>
       <c r="I16" s="30" t="inlineStr">
         <is>
-          <t>Lines are easier to prevent than to erase. Save this reminder. ✨
+          <t>Lines are easier to prevent than to erase. Save this reminder.
 #npinjector #nursepractitioner #medspalife #luxurybeauty #aestheticnurse #skincareexpert #beautyclinic #selfcare #naturalresults #honestbeauty</t>
         </is>
       </c>
@@ -2258,17 +2654,25 @@
           <t>Not designed yet</t>
         </is>
       </c>
-      <c r="Q16" s="30" t="inlineStr">
+      <c r="Q16" s="24" t="n"/>
+      <c r="R16" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="R16" s="30" t="n"/>
       <c r="S16" s="30" t="n"/>
       <c r="T16" s="30" t="n"/>
       <c r="U16" s="30" t="n"/>
       <c r="V16" s="30" t="n"/>
       <c r="W16" s="30" t="n"/>
+      <c r="X16" s="30" t="n"/>
+      <c r="Y16" s="24" t="n"/>
+      <c r="Z16" s="24" t="n"/>
+      <c r="AA16" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="57.45" customHeight="1" s="14">
       <c r="A17" s="27" t="n">
@@ -2294,7 +2698,7 @@
       </c>
       <c r="F17" s="28" t="inlineStr">
         <is>
-          <t>Instagram feed</t>
+          <t>Instagram feed + GBP</t>
         </is>
       </c>
       <c r="G17" s="28" t="inlineStr">
@@ -2309,7 +2713,7 @@
       </c>
       <c r="I17" s="28" t="inlineStr">
         <is>
-          <t>The most Googled question in aesthetics, answered honestly. Slide 5 explains why you should never compare prices unit to unit. Save this for later. ✨
+          <t>The most Googled question in aesthetics, answered honestly. Slide 5 explains why you should never compare prices unit to unit. Save this for later.
 #botox #botoxeducation #botoxmyths #preventativebotox #antiwrinkleinjections #nurseinjector #medspa #naturalbotox #botoxbeforeandafter #aestheticnurse</t>
         </is>
       </c>
@@ -2340,17 +2744,25 @@
           <t>Not designed yet</t>
         </is>
       </c>
-      <c r="Q17" s="28" t="inlineStr">
+      <c r="Q17" s="24" t="n"/>
+      <c r="R17" s="28" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="R17" s="28" t="n"/>
       <c r="S17" s="28" t="n"/>
       <c r="T17" s="28" t="n"/>
       <c r="U17" s="28" t="n"/>
       <c r="V17" s="28" t="n"/>
       <c r="W17" s="28" t="n"/>
+      <c r="X17" s="28" t="n"/>
+      <c r="Y17" s="24" t="n"/>
+      <c r="Z17" s="24" t="n"/>
+      <c r="AA17" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="57.45" customHeight="1" s="14">
       <c r="A18" s="29" t="n">
@@ -2376,7 +2788,7 @@
       </c>
       <c r="F18" s="30" t="inlineStr">
         <is>
-          <t>IG + FB + TikTok photo</t>
+          <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
       <c r="G18" s="30" t="inlineStr">
@@ -2422,17 +2834,25 @@
           <t>Not designed yet</t>
         </is>
       </c>
-      <c r="Q18" s="30" t="inlineStr">
+      <c r="Q18" s="24" t="n"/>
+      <c r="R18" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="R18" s="30" t="n"/>
       <c r="S18" s="30" t="n"/>
       <c r="T18" s="30" t="n"/>
       <c r="U18" s="30" t="n"/>
       <c r="V18" s="30" t="n"/>
       <c r="W18" s="30" t="n"/>
+      <c r="X18" s="30" t="n"/>
+      <c r="Y18" s="24" t="n"/>
+      <c r="Z18" s="24" t="n"/>
+      <c r="AA18" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="57.45" customHeight="1" s="14">
       <c r="A19" s="27" t="n">
@@ -2458,7 +2878,7 @@
       </c>
       <c r="F19" s="28" t="inlineStr">
         <is>
-          <t>Instagram feed</t>
+          <t>Instagram feed + GBP</t>
         </is>
       </c>
       <c r="G19" s="28" t="inlineStr">
@@ -2504,17 +2924,25 @@
           <t>Not designed yet</t>
         </is>
       </c>
-      <c r="Q19" s="28" t="inlineStr">
+      <c r="Q19" s="24" t="n"/>
+      <c r="R19" s="28" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="R19" s="28" t="n"/>
       <c r="S19" s="28" t="n"/>
       <c r="T19" s="28" t="n"/>
       <c r="U19" s="28" t="n"/>
       <c r="V19" s="28" t="n"/>
       <c r="W19" s="28" t="n"/>
+      <c r="X19" s="28" t="n"/>
+      <c r="Y19" s="24" t="n"/>
+      <c r="Z19" s="24" t="n"/>
+      <c r="AA19" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="57.45" customHeight="1" s="14">
       <c r="A20" s="29" t="n">
@@ -2540,7 +2968,7 @@
       </c>
       <c r="F20" s="30" t="inlineStr">
         <is>
-          <t>IG + FB + TikTok photo</t>
+          <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
       <c r="G20" s="30" t="inlineStr">
@@ -2586,17 +3014,25 @@
           <t>Not designed yet</t>
         </is>
       </c>
-      <c r="Q20" s="30" t="inlineStr">
+      <c r="Q20" s="24" t="n"/>
+      <c r="R20" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="R20" s="30" t="n"/>
       <c r="S20" s="30" t="n"/>
       <c r="T20" s="30" t="n"/>
       <c r="U20" s="30" t="n"/>
       <c r="V20" s="30" t="n"/>
       <c r="W20" s="30" t="n"/>
+      <c r="X20" s="30" t="n"/>
+      <c r="Y20" s="24" t="n"/>
+      <c r="Z20" s="24" t="n"/>
+      <c r="AA20" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="57.45" customHeight="1" s="14">
       <c r="A21" s="29" t="n">
@@ -2622,7 +3058,7 @@
       </c>
       <c r="F21" s="30" t="inlineStr">
         <is>
-          <t>IG + FB + TikTok photo</t>
+          <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
       <c r="G21" s="30" t="inlineStr">
@@ -2668,17 +3104,25 @@
           <t>Not designed yet</t>
         </is>
       </c>
-      <c r="Q21" s="30" t="inlineStr">
+      <c r="Q21" s="24" t="n"/>
+      <c r="R21" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="R21" s="30" t="n"/>
       <c r="S21" s="30" t="n"/>
       <c r="T21" s="30" t="n"/>
       <c r="U21" s="30" t="n"/>
       <c r="V21" s="30" t="n"/>
       <c r="W21" s="30" t="n"/>
+      <c r="X21" s="30" t="n"/>
+      <c r="Y21" s="24" t="n"/>
+      <c r="Z21" s="24" t="n"/>
+      <c r="AA21" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="57.45" customHeight="1" s="14">
       <c r="A22" s="27" t="n">
@@ -2704,7 +3148,7 @@
       </c>
       <c r="F22" s="28" t="inlineStr">
         <is>
-          <t>Instagram feed</t>
+          <t>Instagram feed + GBP</t>
         </is>
       </c>
       <c r="G22" s="28" t="inlineStr">
@@ -2750,17 +3194,25 @@
           <t>Not designed yet</t>
         </is>
       </c>
-      <c r="Q22" s="28" t="inlineStr">
+      <c r="Q22" s="24" t="n"/>
+      <c r="R22" s="28" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="R22" s="28" t="n"/>
       <c r="S22" s="28" t="n"/>
       <c r="T22" s="28" t="n"/>
       <c r="U22" s="28" t="n"/>
       <c r="V22" s="28" t="n"/>
       <c r="W22" s="28" t="n"/>
+      <c r="X22" s="28" t="n"/>
+      <c r="Y22" s="24" t="n"/>
+      <c r="Z22" s="24" t="n"/>
+      <c r="AA22" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="57.45" customHeight="1" s="14">
       <c r="A23" s="29" t="n">
@@ -2786,7 +3238,7 @@
       </c>
       <c r="F23" s="30" t="inlineStr">
         <is>
-          <t>IG + FB + TikTok photo</t>
+          <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
       <c r="G23" s="30" t="inlineStr">
@@ -2832,17 +3284,25 @@
           <t>Not designed yet</t>
         </is>
       </c>
-      <c r="Q23" s="30" t="inlineStr">
+      <c r="Q23" s="24" t="n"/>
+      <c r="R23" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="R23" s="30" t="n"/>
       <c r="S23" s="30" t="n"/>
       <c r="T23" s="30" t="n"/>
       <c r="U23" s="30" t="n"/>
       <c r="V23" s="30" t="n"/>
       <c r="W23" s="30" t="n"/>
+      <c r="X23" s="30" t="n"/>
+      <c r="Y23" s="24" t="n"/>
+      <c r="Z23" s="24" t="n"/>
+      <c r="AA23" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="57.45" customHeight="1" s="14">
       <c r="A24" s="27" t="n">
@@ -2868,7 +3328,7 @@
       </c>
       <c r="F24" s="28" t="inlineStr">
         <is>
-          <t>Instagram feed</t>
+          <t>Instagram feed + GBP</t>
         </is>
       </c>
       <c r="G24" s="28" t="inlineStr">
@@ -2914,17 +3374,25 @@
           <t>Not designed yet</t>
         </is>
       </c>
-      <c r="Q24" s="28" t="inlineStr">
+      <c r="Q24" s="24" t="n"/>
+      <c r="R24" s="28" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="R24" s="28" t="n"/>
       <c r="S24" s="28" t="n"/>
       <c r="T24" s="28" t="n"/>
       <c r="U24" s="28" t="n"/>
       <c r="V24" s="28" t="n"/>
       <c r="W24" s="28" t="n"/>
+      <c r="X24" s="28" t="n"/>
+      <c r="Y24" s="24" t="n"/>
+      <c r="Z24" s="24" t="n"/>
+      <c r="AA24" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="57.45" customHeight="1" s="14">
       <c r="A25" s="29" t="n">
@@ -2950,7 +3418,7 @@
       </c>
       <c r="F25" s="30" t="inlineStr">
         <is>
-          <t>IG + FB + TikTok photo</t>
+          <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
       <c r="G25" s="30" t="inlineStr">
@@ -2996,17 +3464,25 @@
           <t>Not designed yet</t>
         </is>
       </c>
-      <c r="Q25" s="30" t="inlineStr">
+      <c r="Q25" s="24" t="n"/>
+      <c r="R25" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="R25" s="30" t="n"/>
       <c r="S25" s="30" t="n"/>
       <c r="T25" s="30" t="n"/>
       <c r="U25" s="30" t="n"/>
       <c r="V25" s="30" t="n"/>
       <c r="W25" s="30" t="n"/>
+      <c r="X25" s="30" t="n"/>
+      <c r="Y25" s="24" t="n"/>
+      <c r="Z25" s="24" t="n"/>
+      <c r="AA25" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="57.45" customHeight="1" s="14">
       <c r="A26" s="29" t="n">
@@ -3032,7 +3508,7 @@
       </c>
       <c r="F26" s="30" t="inlineStr">
         <is>
-          <t>IG + FB + TikTok photo</t>
+          <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
       <c r="G26" s="30" t="inlineStr">
@@ -3078,17 +3554,25 @@
           <t>Not designed yet</t>
         </is>
       </c>
-      <c r="Q26" s="30" t="inlineStr">
+      <c r="Q26" s="24" t="n"/>
+      <c r="R26" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="R26" s="30" t="n"/>
       <c r="S26" s="30" t="n"/>
       <c r="T26" s="30" t="n"/>
       <c r="U26" s="30" t="n"/>
       <c r="V26" s="30" t="n"/>
       <c r="W26" s="30" t="n"/>
+      <c r="X26" s="30" t="n"/>
+      <c r="Y26" s="24" t="n"/>
+      <c r="Z26" s="24" t="n"/>
+      <c r="AA26" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="57.45" customHeight="1" s="14">
       <c r="A27" s="27" t="n">
@@ -3114,7 +3598,7 @@
       </c>
       <c r="F27" s="28" t="inlineStr">
         <is>
-          <t>Instagram feed</t>
+          <t>Instagram feed + GBP</t>
         </is>
       </c>
       <c r="G27" s="28" t="inlineStr">
@@ -3160,17 +3644,25 @@
           <t>Not designed yet</t>
         </is>
       </c>
-      <c r="Q27" s="28" t="inlineStr">
+      <c r="Q27" s="24" t="n"/>
+      <c r="R27" s="28" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="R27" s="28" t="n"/>
       <c r="S27" s="28" t="n"/>
       <c r="T27" s="28" t="n"/>
       <c r="U27" s="28" t="n"/>
       <c r="V27" s="28" t="n"/>
       <c r="W27" s="28" t="n"/>
+      <c r="X27" s="28" t="n"/>
+      <c r="Y27" s="24" t="n"/>
+      <c r="Z27" s="24" t="n"/>
+      <c r="AA27" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="57.45" customHeight="1" s="14">
       <c r="A28" s="29" t="n">
@@ -3196,7 +3688,7 @@
       </c>
       <c r="F28" s="30" t="inlineStr">
         <is>
-          <t>IG + FB + TikTok photo</t>
+          <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
       <c r="G28" s="30" t="inlineStr">
@@ -3242,17 +3734,25 @@
           <t>Not designed yet</t>
         </is>
       </c>
-      <c r="Q28" s="30" t="inlineStr">
+      <c r="Q28" s="24" t="n"/>
+      <c r="R28" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="R28" s="30" t="n"/>
       <c r="S28" s="30" t="n"/>
       <c r="T28" s="30" t="n"/>
       <c r="U28" s="30" t="n"/>
       <c r="V28" s="30" t="n"/>
       <c r="W28" s="30" t="n"/>
+      <c r="X28" s="30" t="n"/>
+      <c r="Y28" s="24" t="n"/>
+      <c r="Z28" s="24" t="n"/>
+      <c r="AA28" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="57.45" customHeight="1" s="14">
       <c r="A29" s="27" t="n">
@@ -3278,7 +3778,7 @@
       </c>
       <c r="F29" s="28" t="inlineStr">
         <is>
-          <t>Instagram feed</t>
+          <t>Instagram feed + GBP</t>
         </is>
       </c>
       <c r="G29" s="28" t="inlineStr">
@@ -3324,17 +3824,25 @@
           <t>Not designed yet</t>
         </is>
       </c>
-      <c r="Q29" s="28" t="inlineStr">
+      <c r="Q29" s="24" t="n"/>
+      <c r="R29" s="28" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="R29" s="28" t="n"/>
       <c r="S29" s="28" t="n"/>
       <c r="T29" s="28" t="n"/>
       <c r="U29" s="28" t="n"/>
       <c r="V29" s="28" t="n"/>
       <c r="W29" s="28" t="n"/>
+      <c r="X29" s="28" t="n"/>
+      <c r="Y29" s="24" t="n"/>
+      <c r="Z29" s="24" t="n"/>
+      <c r="AA29" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="57.45" customHeight="1" s="14">
       <c r="A30" s="29" t="n">
@@ -3360,7 +3868,7 @@
       </c>
       <c r="F30" s="30" t="inlineStr">
         <is>
-          <t>IG + FB + TikTok photo</t>
+          <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
       <c r="G30" s="30" t="inlineStr">
@@ -3406,17 +3914,25 @@
           <t>Not designed yet</t>
         </is>
       </c>
-      <c r="Q30" s="30" t="inlineStr">
+      <c r="Q30" s="24" t="n"/>
+      <c r="R30" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="R30" s="30" t="n"/>
       <c r="S30" s="30" t="n"/>
       <c r="T30" s="30" t="n"/>
       <c r="U30" s="30" t="n"/>
       <c r="V30" s="30" t="n"/>
       <c r="W30" s="30" t="n"/>
+      <c r="X30" s="30" t="n"/>
+      <c r="Y30" s="24" t="n"/>
+      <c r="Z30" s="24" t="n"/>
+      <c r="AA30" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="57.45" customHeight="1" s="14">
       <c r="A31" s="29" t="n">
@@ -3442,7 +3958,7 @@
       </c>
       <c r="F31" s="30" t="inlineStr">
         <is>
-          <t>IG + FB + TikTok photo</t>
+          <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
       <c r="G31" s="30" t="inlineStr">
@@ -3488,17 +4004,25 @@
           <t>Not designed yet</t>
         </is>
       </c>
-      <c r="Q31" s="30" t="inlineStr">
+      <c r="Q31" s="24" t="n"/>
+      <c r="R31" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="R31" s="30" t="n"/>
       <c r="S31" s="30" t="n"/>
       <c r="T31" s="30" t="n"/>
       <c r="U31" s="30" t="n"/>
       <c r="V31" s="30" t="n"/>
       <c r="W31" s="30" t="n"/>
+      <c r="X31" s="30" t="n"/>
+      <c r="Y31" s="24" t="n"/>
+      <c r="Z31" s="24" t="n"/>
+      <c r="AA31" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="57.45" customHeight="1" s="14">
       <c r="A32" s="27" t="n">
@@ -3524,7 +4048,7 @@
       </c>
       <c r="F32" s="28" t="inlineStr">
         <is>
-          <t>Instagram feed</t>
+          <t>Instagram feed + GBP</t>
         </is>
       </c>
       <c r="G32" s="28" t="inlineStr">
@@ -3570,17 +4094,25 @@
           <t>Not designed yet</t>
         </is>
       </c>
-      <c r="Q32" s="28" t="inlineStr">
+      <c r="Q32" s="24" t="n"/>
+      <c r="R32" s="28" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="R32" s="28" t="n"/>
       <c r="S32" s="28" t="n"/>
       <c r="T32" s="28" t="n"/>
       <c r="U32" s="28" t="n"/>
       <c r="V32" s="28" t="n"/>
       <c r="W32" s="28" t="n"/>
+      <c r="X32" s="28" t="n"/>
+      <c r="Y32" s="24" t="n"/>
+      <c r="Z32" s="24" t="n"/>
+      <c r="AA32" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="57.45" customHeight="1" s="14">
       <c r="A33" s="29" t="n">
@@ -3606,7 +4138,7 @@
       </c>
       <c r="F33" s="30" t="inlineStr">
         <is>
-          <t>IG + FB + TikTok photo</t>
+          <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
       <c r="G33" s="30" t="inlineStr">
@@ -3652,17 +4184,25 @@
           <t>Not designed yet</t>
         </is>
       </c>
-      <c r="Q33" s="30" t="inlineStr">
+      <c r="Q33" s="24" t="n"/>
+      <c r="R33" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="R33" s="30" t="n"/>
       <c r="S33" s="30" t="n"/>
       <c r="T33" s="30" t="n"/>
       <c r="U33" s="30" t="n"/>
       <c r="V33" s="30" t="n"/>
       <c r="W33" s="30" t="n"/>
+      <c r="X33" s="30" t="n"/>
+      <c r="Y33" s="24" t="n"/>
+      <c r="Z33" s="24" t="n"/>
+      <c r="AA33" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="57.45" customHeight="1" s="14">
       <c r="A34" s="27" t="n">
@@ -3688,7 +4228,7 @@
       </c>
       <c r="F34" s="28" t="inlineStr">
         <is>
-          <t>Instagram feed</t>
+          <t>Instagram feed + GBP</t>
         </is>
       </c>
       <c r="G34" s="28" t="inlineStr">
@@ -3734,17 +4274,25 @@
           <t>Not designed yet</t>
         </is>
       </c>
-      <c r="Q34" s="28" t="inlineStr">
+      <c r="Q34" s="24" t="n"/>
+      <c r="R34" s="28" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="R34" s="28" t="n"/>
       <c r="S34" s="28" t="n"/>
       <c r="T34" s="28" t="n"/>
       <c r="U34" s="28" t="n"/>
       <c r="V34" s="28" t="n"/>
       <c r="W34" s="28" t="n"/>
+      <c r="X34" s="28" t="n"/>
+      <c r="Y34" s="24" t="n"/>
+      <c r="Z34" s="24" t="n"/>
+      <c r="AA34" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="57.45" customHeight="1" s="14">
       <c r="A35" s="29" t="n">
@@ -3770,7 +4318,7 @@
       </c>
       <c r="F35" s="30" t="inlineStr">
         <is>
-          <t>IG + FB + TikTok photo</t>
+          <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
       <c r="G35" s="30" t="inlineStr">
@@ -3816,17 +4364,25 @@
           <t>Not designed yet</t>
         </is>
       </c>
-      <c r="Q35" s="30" t="inlineStr">
+      <c r="Q35" s="24" t="n"/>
+      <c r="R35" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="R35" s="30" t="n"/>
       <c r="S35" s="30" t="n"/>
       <c r="T35" s="30" t="n"/>
       <c r="U35" s="30" t="n"/>
       <c r="V35" s="30" t="n"/>
       <c r="W35" s="30" t="n"/>
+      <c r="X35" s="30" t="n"/>
+      <c r="Y35" s="24" t="n"/>
+      <c r="Z35" s="24" t="n"/>
+      <c r="AA35" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="46.25" customHeight="1" s="14">
       <c r="A36" s="29" t="n">
@@ -3852,7 +4408,7 @@
       </c>
       <c r="F36" s="30" t="inlineStr">
         <is>
-          <t>IG + FB + TikTok photo</t>
+          <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
       <c r="G36" s="30" t="inlineStr">
@@ -3867,7 +4423,7 @@
       </c>
       <c r="I36" s="30" t="inlineStr">
         <is>
-          <t>An honest provider will sometimes tell you no. That is protection, not rejection. ✨
+          <t>An honest provider will sometimes tell you no. That is protection, not rejection.
 #npinjector #nursepractitioner #medspalife #luxurybeauty #aestheticnurse #skincareexpert #beautyclinic #selfcare #naturalresults #honestbeauty</t>
         </is>
       </c>
@@ -3898,17 +4454,25 @@
           <t>Not designed yet</t>
         </is>
       </c>
-      <c r="Q36" s="30" t="inlineStr">
+      <c r="Q36" s="24" t="n"/>
+      <c r="R36" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="R36" s="30" t="n"/>
       <c r="S36" s="30" t="n"/>
       <c r="T36" s="30" t="n"/>
       <c r="U36" s="30" t="n"/>
       <c r="V36" s="30" t="n"/>
       <c r="W36" s="30" t="n"/>
+      <c r="X36" s="30" t="n"/>
+      <c r="Y36" s="24" t="n"/>
+      <c r="Z36" s="24" t="n"/>
+      <c r="AA36" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="57.45" customHeight="1" s="14">
       <c r="A37" s="27" t="n">
@@ -3934,7 +4498,7 @@
       </c>
       <c r="F37" s="28" t="inlineStr">
         <is>
-          <t>Instagram feed</t>
+          <t>Instagram feed + GBP</t>
         </is>
       </c>
       <c r="G37" s="28" t="inlineStr">
@@ -3949,7 +4513,7 @@
       </c>
       <c r="I37" s="28" t="inlineStr">
         <is>
-          <t>Every overdone face you have seen came from heavy hands, not from filler itself. Great work is invisible. You have seen it a hundred times without knowing. ✨
+          <t>Every overdone face you have seen came from heavy hands, not from filler itself. Great work is invisible. You have seen it a hundred times without knowing.
 #dermalfiller #lipfiller #cheekfiller #naturalfiller #facialbalancing #lipfillernatural #aestheticnurse #medspa #fillerjourney #lipgoals</t>
         </is>
       </c>
@@ -3980,17 +4544,25 @@
           <t>Not designed yet</t>
         </is>
       </c>
-      <c r="Q37" s="28" t="inlineStr">
+      <c r="Q37" s="24" t="n"/>
+      <c r="R37" s="28" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="R37" s="28" t="n"/>
       <c r="S37" s="28" t="n"/>
       <c r="T37" s="28" t="n"/>
       <c r="U37" s="28" t="n"/>
       <c r="V37" s="28" t="n"/>
       <c r="W37" s="28" t="n"/>
+      <c r="X37" s="28" t="n"/>
+      <c r="Y37" s="24" t="n"/>
+      <c r="Z37" s="24" t="n"/>
+      <c r="AA37" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="57.45" customHeight="1" s="14">
       <c r="A38" s="29" t="n">
@@ -4016,7 +4588,7 @@
       </c>
       <c r="F38" s="30" t="inlineStr">
         <is>
-          <t>IG + FB + TikTok photo</t>
+          <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
       <c r="G38" s="30" t="inlineStr">
@@ -4062,17 +4634,25 @@
           <t>Not designed yet</t>
         </is>
       </c>
-      <c r="Q38" s="30" t="inlineStr">
+      <c r="Q38" s="24" t="n"/>
+      <c r="R38" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="R38" s="30" t="n"/>
       <c r="S38" s="30" t="n"/>
       <c r="T38" s="30" t="n"/>
       <c r="U38" s="30" t="n"/>
       <c r="V38" s="30" t="n"/>
       <c r="W38" s="30" t="n"/>
+      <c r="X38" s="30" t="n"/>
+      <c r="Y38" s="24" t="n"/>
+      <c r="Z38" s="24" t="n"/>
+      <c r="AA38" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="57.45" customHeight="1" s="14">
       <c r="A39" s="27" t="n">
@@ -4098,7 +4678,7 @@
       </c>
       <c r="F39" s="28" t="inlineStr">
         <is>
-          <t>Instagram feed</t>
+          <t>Instagram feed + GBP</t>
         </is>
       </c>
       <c r="G39" s="28" t="inlineStr">
@@ -4152,17 +4732,28 @@
           <t>View image</t>
         </is>
       </c>
-      <c r="Q39" s="28" t="inlineStr">
+      <c r="Q39" s="24">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-10-08-lip-filler-natural-vs-overdone/images/before-after-result.png")</f>
+        <v/>
+      </c>
+      <c r="R39" s="28" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="R39" s="28" t="n"/>
       <c r="S39" s="28" t="n"/>
       <c r="T39" s="28" t="n"/>
       <c r="U39" s="28" t="n"/>
       <c r="V39" s="28" t="n"/>
       <c r="W39" s="28" t="n"/>
+      <c r="X39" s="28" t="n"/>
+      <c r="Y39" s="24" t="n"/>
+      <c r="Z39" s="24" t="n"/>
+      <c r="AA39" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="46.25" customHeight="1" s="14">
       <c r="A40" s="29" t="n">
@@ -4188,7 +4779,7 @@
       </c>
       <c r="F40" s="30" t="inlineStr">
         <is>
-          <t>IG + FB + TikTok photo</t>
+          <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
       <c r="G40" s="30" t="inlineStr">
@@ -4234,17 +4825,25 @@
           <t>Not designed yet</t>
         </is>
       </c>
-      <c r="Q40" s="30" t="inlineStr">
+      <c r="Q40" s="24" t="n"/>
+      <c r="R40" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="R40" s="30" t="n"/>
       <c r="S40" s="30" t="n"/>
       <c r="T40" s="30" t="n"/>
       <c r="U40" s="30" t="n"/>
       <c r="V40" s="30" t="n"/>
       <c r="W40" s="30" t="n"/>
+      <c r="X40" s="30" t="n"/>
+      <c r="Y40" s="24" t="n"/>
+      <c r="Z40" s="24" t="n"/>
+      <c r="AA40" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="46.25" customHeight="1" s="14">
       <c r="A41" s="29" t="n">
@@ -4270,7 +4869,7 @@
       </c>
       <c r="F41" s="30" t="inlineStr">
         <is>
-          <t>IG + FB + TikTok photo</t>
+          <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
       <c r="G41" s="30" t="inlineStr">
@@ -4324,17 +4923,28 @@
           <t>View image</t>
         </is>
       </c>
-      <c r="Q41" s="30" t="inlineStr">
+      <c r="Q41" s="24">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-10-10-subtle-is-the-new-dramatic/images/before-after-result.png")</f>
+        <v/>
+      </c>
+      <c r="R41" s="30" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="R41" s="30" t="n"/>
       <c r="S41" s="30" t="n"/>
       <c r="T41" s="30" t="n"/>
       <c r="U41" s="30" t="n"/>
       <c r="V41" s="30" t="n"/>
       <c r="W41" s="30" t="n"/>
+      <c r="X41" s="30" t="n"/>
+      <c r="Y41" s="24" t="n"/>
+      <c r="Z41" s="24" t="n"/>
+      <c r="AA41" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="57.45" customHeight="1" s="14">
       <c r="A42" s="27" t="n">
@@ -4360,7 +4970,7 @@
       </c>
       <c r="F42" s="28" t="inlineStr">
         <is>
-          <t>Instagram feed</t>
+          <t>Instagram feed + GBP</t>
         </is>
       </c>
       <c r="G42" s="28" t="inlineStr">
@@ -4406,17 +5016,25 @@
           <t>Not designed yet</t>
         </is>
       </c>
-      <c r="Q42" s="28" t="inlineStr">
+      <c r="Q42" s="24" t="n"/>
+      <c r="R42" s="28" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="R42" s="28" t="n"/>
       <c r="S42" s="28" t="n"/>
       <c r="T42" s="28" t="n"/>
       <c r="U42" s="28" t="n"/>
       <c r="V42" s="28" t="n"/>
       <c r="W42" s="28" t="n"/>
+      <c r="X42" s="28" t="n"/>
+      <c r="Y42" s="24" t="n"/>
+      <c r="Z42" s="24" t="n"/>
+      <c r="AA42" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="57.45" customHeight="1" s="14">
       <c r="A43" s="29" t="n">
@@ -4442,7 +5060,7 @@
       </c>
       <c r="F43" s="30" t="inlineStr">
         <is>
-          <t>IG + FB + TikTok photo</t>
+          <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
       <c r="G43" s="30" t="inlineStr">
@@ -4488,17 +5106,25 @@
           <t>Not designed yet</t>
         </is>
       </c>
-      <c r="Q43" s="30" t="inlineStr">
+      <c r="Q43" s="24" t="n"/>
+      <c r="R43" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="R43" s="30" t="n"/>
       <c r="S43" s="30" t="n"/>
       <c r="T43" s="30" t="n"/>
       <c r="U43" s="30" t="n"/>
       <c r="V43" s="30" t="n"/>
       <c r="W43" s="30" t="n"/>
+      <c r="X43" s="30" t="n"/>
+      <c r="Y43" s="24" t="n"/>
+      <c r="Z43" s="24" t="n"/>
+      <c r="AA43" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="57.45" customHeight="1" s="14">
       <c r="A44" s="27" t="n">
@@ -4524,7 +5150,7 @@
       </c>
       <c r="F44" s="28" t="inlineStr">
         <is>
-          <t>Instagram feed</t>
+          <t>Instagram feed + GBP</t>
         </is>
       </c>
       <c r="G44" s="28" t="inlineStr">
@@ -4578,17 +5204,28 @@
           <t>View 7 slides</t>
         </is>
       </c>
-      <c r="Q44" s="28" t="inlineStr">
+      <c r="Q44" s="24">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-10-15-real-lips-real-results/images/slide-1.png")</f>
+        <v/>
+      </c>
+      <c r="R44" s="28" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="R44" s="28" t="n"/>
       <c r="S44" s="28" t="n"/>
       <c r="T44" s="28" t="n"/>
       <c r="U44" s="28" t="n"/>
       <c r="V44" s="28" t="n"/>
       <c r="W44" s="28" t="n"/>
+      <c r="X44" s="28" t="n"/>
+      <c r="Y44" s="24" t="n"/>
+      <c r="Z44" s="24" t="n"/>
+      <c r="AA44" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="57.45" customHeight="1" s="14">
       <c r="A45" s="29" t="n">
@@ -4614,7 +5251,7 @@
       </c>
       <c r="F45" s="30" t="inlineStr">
         <is>
-          <t>IG + FB + TikTok photo</t>
+          <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
       <c r="G45" s="30" t="inlineStr">
@@ -4660,17 +5297,25 @@
           <t>Not designed yet</t>
         </is>
       </c>
-      <c r="Q45" s="30" t="inlineStr">
+      <c r="Q45" s="24" t="n"/>
+      <c r="R45" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="R45" s="30" t="n"/>
       <c r="S45" s="30" t="n"/>
       <c r="T45" s="30" t="n"/>
       <c r="U45" s="30" t="n"/>
       <c r="V45" s="30" t="n"/>
       <c r="W45" s="30" t="n"/>
+      <c r="X45" s="30" t="n"/>
+      <c r="Y45" s="24" t="n"/>
+      <c r="Z45" s="24" t="n"/>
+      <c r="AA45" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="57.45" customHeight="1" s="14">
       <c r="A46" s="29" t="n">
@@ -4696,7 +5341,7 @@
       </c>
       <c r="F46" s="30" t="inlineStr">
         <is>
-          <t>IG + FB + TikTok photo</t>
+          <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
       <c r="G46" s="30" t="inlineStr">
@@ -4742,17 +5387,25 @@
           <t>Not designed yet</t>
         </is>
       </c>
-      <c r="Q46" s="30" t="inlineStr">
+      <c r="Q46" s="24" t="n"/>
+      <c r="R46" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="R46" s="30" t="n"/>
       <c r="S46" s="30" t="n"/>
       <c r="T46" s="30" t="n"/>
       <c r="U46" s="30" t="n"/>
       <c r="V46" s="30" t="n"/>
       <c r="W46" s="30" t="n"/>
+      <c r="X46" s="30" t="n"/>
+      <c r="Y46" s="24" t="n"/>
+      <c r="Z46" s="24" t="n"/>
+      <c r="AA46" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="57.45" customHeight="1" s="14">
       <c r="A47" s="27" t="n">
@@ -4778,7 +5431,7 @@
       </c>
       <c r="F47" s="28" t="inlineStr">
         <is>
-          <t>Instagram feed</t>
+          <t>Instagram feed + GBP</t>
         </is>
       </c>
       <c r="G47" s="28" t="inlineStr">
@@ -4824,17 +5477,25 @@
           <t>Not designed yet</t>
         </is>
       </c>
-      <c r="Q47" s="28" t="inlineStr">
+      <c r="Q47" s="24" t="n"/>
+      <c r="R47" s="28" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="R47" s="28" t="n"/>
       <c r="S47" s="28" t="n"/>
       <c r="T47" s="28" t="n"/>
       <c r="U47" s="28" t="n"/>
       <c r="V47" s="28" t="n"/>
       <c r="W47" s="28" t="n"/>
+      <c r="X47" s="28" t="n"/>
+      <c r="Y47" s="24" t="n"/>
+      <c r="Z47" s="24" t="n"/>
+      <c r="AA47" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="57.45" customHeight="1" s="14">
       <c r="A48" s="29" t="n">
@@ -4860,7 +5521,7 @@
       </c>
       <c r="F48" s="30" t="inlineStr">
         <is>
-          <t>IG + FB + TikTok photo</t>
+          <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
       <c r="G48" s="30" t="inlineStr">
@@ -4906,17 +5567,25 @@
           <t>Not designed yet</t>
         </is>
       </c>
-      <c r="Q48" s="30" t="inlineStr">
+      <c r="Q48" s="24" t="n"/>
+      <c r="R48" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="R48" s="30" t="n"/>
       <c r="S48" s="30" t="n"/>
       <c r="T48" s="30" t="n"/>
       <c r="U48" s="30" t="n"/>
       <c r="V48" s="30" t="n"/>
       <c r="W48" s="30" t="n"/>
+      <c r="X48" s="30" t="n"/>
+      <c r="Y48" s="24" t="n"/>
+      <c r="Z48" s="24" t="n"/>
+      <c r="AA48" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="57.45" customHeight="1" s="14">
       <c r="A49" s="27" t="n">
@@ -4942,7 +5611,7 @@
       </c>
       <c r="F49" s="28" t="inlineStr">
         <is>
-          <t>Instagram feed</t>
+          <t>Instagram feed + GBP</t>
         </is>
       </c>
       <c r="G49" s="28" t="inlineStr">
@@ -4996,17 +5665,28 @@
           <t>View image</t>
         </is>
       </c>
-      <c r="Q49" s="28" t="inlineStr">
+      <c r="Q49" s="24">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-10-22-lip-filler-aftercare-your-first/images/day-zero-before-after.png")</f>
+        <v/>
+      </c>
+      <c r="R49" s="28" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="R49" s="28" t="n"/>
       <c r="S49" s="28" t="n"/>
       <c r="T49" s="28" t="n"/>
       <c r="U49" s="28" t="n"/>
       <c r="V49" s="28" t="n"/>
       <c r="W49" s="28" t="n"/>
+      <c r="X49" s="28" t="n"/>
+      <c r="Y49" s="24" t="n"/>
+      <c r="Z49" s="24" t="n"/>
+      <c r="AA49" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="57.45" customHeight="1" s="14">
       <c r="A50" s="29" t="n">
@@ -5032,7 +5712,7 @@
       </c>
       <c r="F50" s="30" t="inlineStr">
         <is>
-          <t>IG + FB + TikTok photo</t>
+          <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
       <c r="G50" s="30" t="inlineStr">
@@ -5047,7 +5727,7 @@
       </c>
       <c r="I50" s="30" t="inlineStr">
         <is>
-          <t>Ice, no gym for 24 hours, sleep on your back, and message me with anything. That is it. Save this. ✨
+          <t>Ice, no gym for 24 hours, sleep on your back, and message me with anything. That is it. Save this.
 #dermalfiller #lipfiller #cheekfiller #naturalfiller #facialbalancing #lipfillernatural #aestheticnurse #medspa #fillerjourney #lipgoals</t>
         </is>
       </c>
@@ -5078,17 +5758,25 @@
           <t>Not designed yet</t>
         </is>
       </c>
-      <c r="Q50" s="30" t="inlineStr">
+      <c r="Q50" s="24" t="n"/>
+      <c r="R50" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="R50" s="30" t="n"/>
       <c r="S50" s="30" t="n"/>
       <c r="T50" s="30" t="n"/>
       <c r="U50" s="30" t="n"/>
       <c r="V50" s="30" t="n"/>
       <c r="W50" s="30" t="n"/>
+      <c r="X50" s="30" t="n"/>
+      <c r="Y50" s="24" t="n"/>
+      <c r="Z50" s="24" t="n"/>
+      <c r="AA50" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="57.45" customHeight="1" s="14">
       <c r="A51" s="29" t="n">
@@ -5114,7 +5802,7 @@
       </c>
       <c r="F51" s="30" t="inlineStr">
         <is>
-          <t>IG + FB + TikTok photo</t>
+          <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
       <c r="G51" s="30" t="inlineStr">
@@ -5168,17 +5856,28 @@
           <t>View image</t>
         </is>
       </c>
-      <c r="Q51" s="30" t="inlineStr">
+      <c r="Q51" s="24">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-10-24-client-words-the-lip-glow/images/before-after-result.png")</f>
+        <v/>
+      </c>
+      <c r="R51" s="30" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="R51" s="30" t="n"/>
       <c r="S51" s="30" t="n"/>
       <c r="T51" s="30" t="n"/>
       <c r="U51" s="30" t="n"/>
       <c r="V51" s="30" t="n"/>
       <c r="W51" s="30" t="n"/>
+      <c r="X51" s="30" t="n"/>
+      <c r="Y51" s="24" t="n"/>
+      <c r="Z51" s="24" t="n"/>
+      <c r="AA51" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="57.45" customHeight="1" s="14">
       <c r="A52" s="27" t="n">
@@ -5204,7 +5903,7 @@
       </c>
       <c r="F52" s="28" t="inlineStr">
         <is>
-          <t>Instagram feed</t>
+          <t>Instagram feed + GBP</t>
         </is>
       </c>
       <c r="G52" s="28" t="inlineStr">
@@ -5219,7 +5918,7 @@
       </c>
       <c r="I52" s="28" t="inlineStr">
         <is>
-          <t>You loved the Botox edition, so here is the filler truth round. Slide 4 is the one that surprises everyone. Share it with your group chat. ✨
+          <t>You loved the Botox edition, so here is the filler truth round. Slide 4 is the one that surprises everyone. Share it with your group chat.
 #dermalfiller #lipfiller #cheekfiller #naturalfiller #facialbalancing #lipfillernatural #aestheticnurse #medspa #fillerjourney #lipgoals</t>
         </is>
       </c>
@@ -5250,17 +5949,25 @@
           <t>Not designed yet</t>
         </is>
       </c>
-      <c r="Q52" s="28" t="inlineStr">
+      <c r="Q52" s="24" t="n"/>
+      <c r="R52" s="28" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="R52" s="28" t="n"/>
       <c r="S52" s="28" t="n"/>
       <c r="T52" s="28" t="n"/>
       <c r="U52" s="28" t="n"/>
       <c r="V52" s="28" t="n"/>
       <c r="W52" s="28" t="n"/>
+      <c r="X52" s="28" t="n"/>
+      <c r="Y52" s="24" t="n"/>
+      <c r="Z52" s="24" t="n"/>
+      <c r="AA52" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="57.45" customHeight="1" s="14">
       <c r="A53" s="29" t="n">
@@ -5286,7 +5993,7 @@
       </c>
       <c r="F53" s="30" t="inlineStr">
         <is>
-          <t>IG + FB + TikTok photo</t>
+          <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
       <c r="G53" s="30" t="inlineStr">
@@ -5332,17 +6039,25 @@
           <t>Not designed yet</t>
         </is>
       </c>
-      <c r="Q53" s="30" t="inlineStr">
+      <c r="Q53" s="24" t="n"/>
+      <c r="R53" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="R53" s="30" t="n"/>
       <c r="S53" s="30" t="n"/>
       <c r="T53" s="30" t="n"/>
       <c r="U53" s="30" t="n"/>
       <c r="V53" s="30" t="n"/>
       <c r="W53" s="30" t="n"/>
+      <c r="X53" s="30" t="n"/>
+      <c r="Y53" s="24" t="n"/>
+      <c r="Z53" s="24" t="n"/>
+      <c r="AA53" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="57.45" customHeight="1" s="14">
       <c r="A54" s="27" t="n">
@@ -5368,7 +6083,7 @@
       </c>
       <c r="F54" s="28" t="inlineStr">
         <is>
-          <t>Instagram feed</t>
+          <t>Instagram feed + GBP</t>
         </is>
       </c>
       <c r="G54" s="28" t="inlineStr">
@@ -5414,17 +6129,25 @@
           <t>Not designed yet</t>
         </is>
       </c>
-      <c r="Q54" s="28" t="inlineStr">
+      <c r="Q54" s="24" t="n"/>
+      <c r="R54" s="28" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="R54" s="28" t="n"/>
       <c r="S54" s="28" t="n"/>
       <c r="T54" s="28" t="n"/>
       <c r="U54" s="28" t="n"/>
       <c r="V54" s="28" t="n"/>
       <c r="W54" s="28" t="n"/>
+      <c r="X54" s="28" t="n"/>
+      <c r="Y54" s="24" t="n"/>
+      <c r="Z54" s="24" t="n"/>
+      <c r="AA54" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="57.45" customHeight="1" s="14">
       <c r="A55" s="29" t="n">
@@ -5450,7 +6173,7 @@
       </c>
       <c r="F55" s="30" t="inlineStr">
         <is>
-          <t>IG + FB + TikTok photo</t>
+          <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
       <c r="G55" s="30" t="inlineStr">
@@ -5504,17 +6227,28 @@
           <t>View image</t>
         </is>
       </c>
-      <c r="Q55" s="30" t="inlineStr">
+      <c r="Q55" s="24">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-10-30-one-syringe-balanced-lips/images/before-after-result.png")</f>
+        <v/>
+      </c>
+      <c r="R55" s="30" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="R55" s="30" t="n"/>
       <c r="S55" s="30" t="n"/>
       <c r="T55" s="30" t="n"/>
       <c r="U55" s="30" t="n"/>
       <c r="V55" s="30" t="n"/>
       <c r="W55" s="30" t="n"/>
+      <c r="X55" s="30" t="n"/>
+      <c r="Y55" s="24" t="n"/>
+      <c r="Z55" s="24" t="n"/>
+      <c r="AA55" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="57.45" customHeight="1" s="14">
       <c r="A56" s="29" t="n">
@@ -5540,7 +6274,7 @@
       </c>
       <c r="F56" s="30" t="inlineStr">
         <is>
-          <t>IG + FB + TikTok photo</t>
+          <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
       <c r="G56" s="30" t="inlineStr">
@@ -5586,17 +6320,25 @@
           <t>Not designed yet</t>
         </is>
       </c>
-      <c r="Q56" s="30" t="inlineStr">
+      <c r="Q56" s="24" t="n"/>
+      <c r="R56" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="R56" s="30" t="n"/>
       <c r="S56" s="30" t="n"/>
       <c r="T56" s="30" t="n"/>
       <c r="U56" s="30" t="n"/>
       <c r="V56" s="30" t="n"/>
       <c r="W56" s="30" t="n"/>
+      <c r="X56" s="30" t="n"/>
+      <c r="Y56" s="24" t="n"/>
+      <c r="Z56" s="24" t="n"/>
+      <c r="AA56" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="57.45" customHeight="1" s="14">
       <c r="A57" s="27" t="n">
@@ -5622,7 +6364,7 @@
       </c>
       <c r="F57" s="28" t="inlineStr">
         <is>
-          <t>Instagram feed</t>
+          <t>Instagram feed + GBP</t>
         </is>
       </c>
       <c r="G57" s="28" t="inlineStr">
@@ -5668,17 +6410,25 @@
           <t>Not designed yet</t>
         </is>
       </c>
-      <c r="Q57" s="28" t="inlineStr">
+      <c r="Q57" s="24" t="n"/>
+      <c r="R57" s="28" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="R57" s="28" t="n"/>
       <c r="S57" s="28" t="n"/>
       <c r="T57" s="28" t="n"/>
       <c r="U57" s="28" t="n"/>
       <c r="V57" s="28" t="n"/>
       <c r="W57" s="28" t="n"/>
+      <c r="X57" s="28" t="n"/>
+      <c r="Y57" s="24" t="n"/>
+      <c r="Z57" s="24" t="n"/>
+      <c r="AA57" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="57.45" customHeight="1" s="14">
       <c r="A58" s="29" t="n">
@@ -5704,7 +6454,7 @@
       </c>
       <c r="F58" s="30" t="inlineStr">
         <is>
-          <t>IG + FB + TikTok photo</t>
+          <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
       <c r="G58" s="30" t="inlineStr">
@@ -5750,17 +6500,25 @@
           <t>Not designed yet</t>
         </is>
       </c>
-      <c r="Q58" s="30" t="inlineStr">
+      <c r="Q58" s="24" t="n"/>
+      <c r="R58" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="R58" s="30" t="n"/>
       <c r="S58" s="30" t="n"/>
       <c r="T58" s="30" t="n"/>
       <c r="U58" s="30" t="n"/>
       <c r="V58" s="30" t="n"/>
       <c r="W58" s="30" t="n"/>
+      <c r="X58" s="30" t="n"/>
+      <c r="Y58" s="24" t="n"/>
+      <c r="Z58" s="24" t="n"/>
+      <c r="AA58" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="57.45" customHeight="1" s="14">
       <c r="A59" s="27" t="n">
@@ -5786,7 +6544,7 @@
       </c>
       <c r="F59" s="28" t="inlineStr">
         <is>
-          <t>Instagram feed</t>
+          <t>Instagram feed + GBP</t>
         </is>
       </c>
       <c r="G59" s="28" t="inlineStr">
@@ -5832,17 +6590,25 @@
           <t>Not designed yet</t>
         </is>
       </c>
-      <c r="Q59" s="28" t="inlineStr">
+      <c r="Q59" s="24" t="n"/>
+      <c r="R59" s="28" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="R59" s="28" t="n"/>
       <c r="S59" s="28" t="n"/>
       <c r="T59" s="28" t="n"/>
       <c r="U59" s="28" t="n"/>
       <c r="V59" s="28" t="n"/>
       <c r="W59" s="28" t="n"/>
+      <c r="X59" s="28" t="n"/>
+      <c r="Y59" s="24" t="n"/>
+      <c r="Z59" s="24" t="n"/>
+      <c r="AA59" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="57.45" customHeight="1" s="14">
       <c r="A60" s="29" t="n">
@@ -5868,7 +6634,7 @@
       </c>
       <c r="F60" s="30" t="inlineStr">
         <is>
-          <t>Instagram feed</t>
+          <t>Instagram feed + GBP</t>
         </is>
       </c>
       <c r="G60" s="30" t="inlineStr">
@@ -5922,17 +6688,28 @@
           <t>View 7 slides</t>
         </is>
       </c>
-      <c r="Q60" s="30" t="inlineStr">
+      <c r="Q60" s="24">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-11-06-one-result-every-angle/images/slide-1.png")</f>
+        <v/>
+      </c>
+      <c r="R60" s="30" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="R60" s="30" t="n"/>
       <c r="S60" s="30" t="n"/>
       <c r="T60" s="30" t="n"/>
       <c r="U60" s="30" t="n"/>
       <c r="V60" s="30" t="n"/>
       <c r="W60" s="30" t="n"/>
+      <c r="X60" s="30" t="n"/>
+      <c r="Y60" s="24" t="n"/>
+      <c r="Z60" s="24" t="n"/>
+      <c r="AA60" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="57.45" customHeight="1" s="14">
       <c r="A61" s="29" t="n">
@@ -5958,7 +6735,7 @@
       </c>
       <c r="F61" s="30" t="inlineStr">
         <is>
-          <t>IG + FB + TikTok photo</t>
+          <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
       <c r="G61" s="30" t="inlineStr">
@@ -6004,17 +6781,25 @@
           <t>Not designed yet</t>
         </is>
       </c>
-      <c r="Q61" s="30" t="inlineStr">
+      <c r="Q61" s="24" t="n"/>
+      <c r="R61" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="R61" s="30" t="n"/>
       <c r="S61" s="30" t="n"/>
       <c r="T61" s="30" t="n"/>
       <c r="U61" s="30" t="n"/>
       <c r="V61" s="30" t="n"/>
       <c r="W61" s="30" t="n"/>
+      <c r="X61" s="30" t="n"/>
+      <c r="Y61" s="24" t="n"/>
+      <c r="Z61" s="24" t="n"/>
+      <c r="AA61" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="57.45" customHeight="1" s="14">
       <c r="A62" s="27" t="n">
@@ -6040,7 +6825,7 @@
       </c>
       <c r="F62" s="28" t="inlineStr">
         <is>
-          <t>Instagram feed</t>
+          <t>Instagram feed + GBP</t>
         </is>
       </c>
       <c r="G62" s="28" t="inlineStr">
@@ -6086,17 +6871,25 @@
           <t>Not designed yet</t>
         </is>
       </c>
-      <c r="Q62" s="28" t="inlineStr">
+      <c r="Q62" s="24" t="n"/>
+      <c r="R62" s="28" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="R62" s="28" t="n"/>
       <c r="S62" s="28" t="n"/>
       <c r="T62" s="28" t="n"/>
       <c r="U62" s="28" t="n"/>
       <c r="V62" s="28" t="n"/>
       <c r="W62" s="28" t="n"/>
+      <c r="X62" s="28" t="n"/>
+      <c r="Y62" s="24" t="n"/>
+      <c r="Z62" s="24" t="n"/>
+      <c r="AA62" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="57.45" customHeight="1" s="14">
       <c r="A63" s="29" t="n">
@@ -6122,7 +6915,7 @@
       </c>
       <c r="F63" s="30" t="inlineStr">
         <is>
-          <t>IG + FB + TikTok photo</t>
+          <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
       <c r="G63" s="30" t="inlineStr">
@@ -6168,17 +6961,25 @@
           <t>Not designed yet</t>
         </is>
       </c>
-      <c r="Q63" s="30" t="inlineStr">
+      <c r="Q63" s="24" t="n"/>
+      <c r="R63" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="R63" s="30" t="n"/>
       <c r="S63" s="30" t="n"/>
       <c r="T63" s="30" t="n"/>
       <c r="U63" s="30" t="n"/>
       <c r="V63" s="30" t="n"/>
       <c r="W63" s="30" t="n"/>
+      <c r="X63" s="30" t="n"/>
+      <c r="Y63" s="24" t="n"/>
+      <c r="Z63" s="24" t="n"/>
+      <c r="AA63" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="57.45" customHeight="1" s="14">
       <c r="A64" s="27" t="n">
@@ -6204,7 +7005,7 @@
       </c>
       <c r="F64" s="28" t="inlineStr">
         <is>
-          <t>Instagram feed</t>
+          <t>Instagram feed + GBP</t>
         </is>
       </c>
       <c r="G64" s="28" t="inlineStr">
@@ -6250,17 +7051,25 @@
           <t>Not designed yet</t>
         </is>
       </c>
-      <c r="Q64" s="28" t="inlineStr">
+      <c r="Q64" s="24" t="n"/>
+      <c r="R64" s="28" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="R64" s="28" t="n"/>
       <c r="S64" s="28" t="n"/>
       <c r="T64" s="28" t="n"/>
       <c r="U64" s="28" t="n"/>
       <c r="V64" s="28" t="n"/>
       <c r="W64" s="28" t="n"/>
+      <c r="X64" s="28" t="n"/>
+      <c r="Y64" s="24" t="n"/>
+      <c r="Z64" s="24" t="n"/>
+      <c r="AA64" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="57.45" customHeight="1" s="14">
       <c r="A65" s="29" t="n">
@@ -6286,7 +7095,7 @@
       </c>
       <c r="F65" s="30" t="inlineStr">
         <is>
-          <t>IG + FB + TikTok photo</t>
+          <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
       <c r="G65" s="30" t="inlineStr">
@@ -6332,17 +7141,25 @@
           <t>Not designed yet</t>
         </is>
       </c>
-      <c r="Q65" s="30" t="inlineStr">
+      <c r="Q65" s="24" t="n"/>
+      <c r="R65" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="R65" s="30" t="n"/>
       <c r="S65" s="30" t="n"/>
       <c r="T65" s="30" t="n"/>
       <c r="U65" s="30" t="n"/>
       <c r="V65" s="30" t="n"/>
       <c r="W65" s="30" t="n"/>
+      <c r="X65" s="30" t="n"/>
+      <c r="Y65" s="24" t="n"/>
+      <c r="Z65" s="24" t="n"/>
+      <c r="AA65" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="57.45" customHeight="1" s="14">
       <c r="A66" s="29" t="n">
@@ -6368,7 +7185,7 @@
       </c>
       <c r="F66" s="30" t="inlineStr">
         <is>
-          <t>IG + FB + TikTok photo</t>
+          <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
       <c r="G66" s="30" t="inlineStr">
@@ -6414,17 +7231,25 @@
           <t>Not designed yet</t>
         </is>
       </c>
-      <c r="Q66" s="30" t="inlineStr">
+      <c r="Q66" s="24" t="n"/>
+      <c r="R66" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="R66" s="30" t="n"/>
       <c r="S66" s="30" t="n"/>
       <c r="T66" s="30" t="n"/>
       <c r="U66" s="30" t="n"/>
       <c r="V66" s="30" t="n"/>
       <c r="W66" s="30" t="n"/>
+      <c r="X66" s="30" t="n"/>
+      <c r="Y66" s="24" t="n"/>
+      <c r="Z66" s="24" t="n"/>
+      <c r="AA66" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -6435,78 +7260,98 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P3" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O5" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O6" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O8" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O39" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P39" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P41" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P44" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O45" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O46" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P49" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O50" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O51" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P51" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O52" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O53" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O54" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O55" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P55" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O56" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O57" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O58" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O59" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O60" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P60" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O61" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O62" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O63" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O64" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O65" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O66" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P3" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA3" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O4" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P4" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA4" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O5" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P5" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA5" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O6" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P6" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA6" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P7" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA7" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O8" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P8" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA8" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P9" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA9" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P10" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA10" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P11" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA11" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P12" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA12" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O39" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P39" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P41" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P44" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O45" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O46" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P49" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O50" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O51" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P51" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O52" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O53" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O54" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O55" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P55" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O56" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O57" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O58" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O59" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O60" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P60" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O61" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O62" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O63" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O64" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O65" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O66" r:id="rId94"/>
   </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -6862,87 +7707,87 @@
       </c>
     </row>
     <row r="2" ht="15" customHeight="1" s="14">
-      <c r="A2" s="30" t="inlineStr">
+      <c r="A2" s="31" t="inlineStr">
         <is>
           <t>Set A</t>
         </is>
       </c>
-      <c r="B2" s="30" t="inlineStr">
-        <is>
-          <t>Botox Education</t>
-        </is>
-      </c>
-      <c r="C2" s="30" t="inlineStr">
-        <is>
-          <t>#botox #botoxeducation #botoxmyths #preventativebotox #antiwrinkleinjections #nurseinjector #medspa #naturalbotox #botoxbeforeandafter #aestheticnurse</t>
+      <c r="B2" s="31" t="inlineStr">
+        <is>
+          <t>Botox / Neuromodulator</t>
+        </is>
+      </c>
+      <c r="C2" s="31" t="inlineStr">
+        <is>
+          <t>#botoxoakville #oakvillemedspa #burlingtonbotox #miltonmedspa #mississaugainjector #haltonregion #preventativebotox #botoxcanada #nursepractitionerinjector #naturalresults #luxurybeautybycleor #npcleo</t>
         </is>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" s="14">
-      <c r="A3" s="30" t="inlineStr">
+      <c r="A3" s="31" t="inlineStr">
         <is>
           <t>Set B</t>
         </is>
       </c>
-      <c r="B3" s="30" t="inlineStr">
+      <c r="B3" s="31" t="inlineStr">
         <is>
           <t>Filler</t>
         </is>
       </c>
-      <c r="C3" s="30" t="inlineStr">
-        <is>
-          <t>#dermalfiller #lipfiller #cheekfiller #naturalfiller #facialbalancing #lipfillernatural #aestheticnurse #medspa #fillerjourney #lipgoals</t>
+      <c r="C3" s="31" t="inlineStr">
+        <is>
+          <t>#lipfilleroakville #fillersoakville #oakvillemedspa #burlingtonfiller #miltonlipfiller #mississaugamedspa #dermalfillers #naturallips #facialbalancing #aestheticnurse #luxurybeautybycleor #npcleo</t>
         </is>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="14">
-      <c r="A4" s="30" t="inlineStr">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>Set C</t>
         </is>
       </c>
-      <c r="B4" s="30" t="inlineStr">
-        <is>
-          <t>Brand &amp; Trust</t>
-        </is>
-      </c>
-      <c r="C4" s="30" t="inlineStr">
-        <is>
-          <t>#npinjector #nursepractitioner #medspalife #luxurybeauty #aestheticnurse #skincareexpert #beautyclinic #selfcare #naturalresults #honestbeauty</t>
+      <c r="B4" s="31" t="inlineStr">
+        <is>
+          <t>Trust &amp; Proof</t>
+        </is>
+      </c>
+      <c r="C4" s="31" t="inlineStr">
+        <is>
+          <t>#oakvillemedspa #burlingtonmedspa #miltonontario #mississaugabeauty #haltonregion #honestinjector #naturalresults #aestheticnurse #nursepractitioner #medspacanada #luxurybeautybycleor #npcleo</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="14">
-      <c r="A5" s="30" t="inlineStr">
+      <c r="A5" s="31" t="inlineStr">
         <is>
           <t>Set D</t>
         </is>
       </c>
-      <c r="B5" s="30" t="inlineStr">
-        <is>
-          <t>Reels &amp; TikTok</t>
-        </is>
-      </c>
-      <c r="C5" s="30" t="inlineStr">
-        <is>
-          <t>#medspatiktok #botoxtok #aesthetictok #injectorlife #beautyreels #skincareroutine #glowup #aesthetics #medspareels #beautytok</t>
+      <c r="B5" s="31" t="inlineStr">
+        <is>
+          <t>Personality &amp; BTS</t>
+        </is>
+      </c>
+      <c r="C5" s="31" t="inlineStr">
+        <is>
+          <t>#oakville #oakvillebusiness #burlingtonontario #miltonontario #mississauga #haltonregion #womeninbusiness #nursepractitioner #aestheticnurse #medspalife #luxurybeautybycleor #npcleo</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="14">
-      <c r="A6" s="30" t="inlineStr">
+      <c r="A6" s="31" t="inlineStr">
         <is>
           <t>Set E</t>
         </is>
       </c>
-      <c r="B6" s="30" t="inlineStr">
-        <is>
-          <t>Promo &amp; Seasonal</t>
-        </is>
-      </c>
-      <c r="C6" s="30" t="inlineStr">
-        <is>
-          <t>#holidayglow #treatyourself #giftcertificate #bookyourappointment #medspaspecial #glowupseason #selfcaregift #luxuryselfcare #holidayready #giftideas</t>
+      <c r="B6" s="31" t="inlineStr">
+        <is>
+          <t>Promo &amp; CTA</t>
+        </is>
+      </c>
+      <c r="C6" s="31" t="inlineStr">
+        <is>
+          <t>#oakvillemedspa #burlingtonontario #miltonontario #mississaugabeauty #haltonregion #treatyourself #selfcare #giftcertificate #medspaspecial #bookyourappointment #luxurybeautybycleor #npcleo</t>
         </is>
       </c>
     </row>

--- a/strategy/ig-content-strategy.xlsx
+++ b/strategy/ig-content-strategy.xlsx
@@ -1512,7 +1512,7 @@
       </c>
       <c r="L5" s="30" t="inlineStr">
         <is>
-          <t>Single image: prep tray photo + hook overlay</t>
+          <t>prep tray photo + hook overlay</t>
         </is>
       </c>
       <c r="M5" s="24" t="n"/>
@@ -1810,28 +1810,32 @@
       </c>
       <c r="G8" s="30" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Trust &amp; Proof</t>
         </is>
       </c>
       <c r="H8" s="30" t="inlineStr">
         <is>
-          <t>3 Signs Your Injector Is Rushing You | Protect yourself before you book.</t>
+          <t>Why I Do Not Post Prices | Every clinic gets this DM. Almost nobody answers it honestly.</t>
         </is>
       </c>
       <c r="I8" s="30" t="inlineStr">
         <is>
-          <t>Ten minutes in and out is not efficient. It is skipped steps.
-The injecting really is quick. The looking, the mapping and the conversation
-are not, and those are the parts that decide whether you like your face in two
-weeks.
-Three signs you are being processed instead of treated. Screenshot them and
-take them to your next appointment, wherever that is.
+          <t>Every clinic gets this DM. Almost nobody answers it honestly.
+Units are not a menu item. Two people who want the same result can need very
+different doses, so one flat price either overcharges you or under treats you.
+And cheap injectables end up being the most expensive thing in this industry,
+because correcting bad work takes more time and more product than doing it
+properly the first time.
+What you do get is a number before anything starts. At your consult, in writing,
+after I have actually looked at your face. Nothing is opened until you have
+agreed to it.
+Ask me anything about cost. I will not dodge it.
 #oakvillemedspa #burlingtonmedspa #miltonontario #mississaugabeauty #haltonregion #honestinjector #naturalresults #aestheticnurse #nursepractitioner #medspacanada #luxurybeautybycleor #npcleo</t>
         </is>
       </c>
       <c r="J8" s="30" t="inlineStr">
         <is>
-          <t>Save this. Use it.</t>
+          <t>DM the word PRICE</t>
         </is>
       </c>
       <c r="K8" s="30" t="inlineStr">
@@ -1841,7 +1845,7 @@
       </c>
       <c r="L8" s="30" t="inlineStr">
         <is>
-          <t>Single image: 3-point checklist card in brand style</t>
+          <t>Single image, dark variant. Type led, no photo</t>
         </is>
       </c>
       <c r="M8" s="24" t="n"/>
@@ -1857,7 +1861,7 @@
         </is>
       </c>
       <c r="Q8" s="24">
-        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-08-25-3-signs-your-injector-is/images/post.png")</f>
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-08-25-why-i-do-not-post/images/post.png")</f>
         <v/>
       </c>
       <c r="R8" s="30" t="inlineStr">
@@ -1873,7 +1877,7 @@
       <c r="X8" s="30" t="n"/>
       <c r="Y8" s="24" t="inlineStr">
         <is>
-          <t>Three signs your injector is rushing you: no mirror and no map, units decided before you spoke, and the whole visit over in under ten minutes. Worth knowing before you book anywhere. Serving Oakville, Burlington, Milton and Mississauga.</t>
+          <t>Why we do not post a price list. Doses differ from face to face, so one flat price either overcharges you or under treats you. You get a written number at your consult, before anything is opened. Serving Oakville, Burlington, Milton and Mississauga.</t>
         </is>
       </c>
       <c r="Z8" s="24" t="inlineStr">
@@ -2055,7 +2059,7 @@
       </c>
       <c r="L10" s="30" t="inlineStr">
         <is>
-          <t>Single image: treatment room photo + hook</t>
+          <t>Single image, dark photo led. Uses botox-prep.png framed on the room</t>
         </is>
       </c>
       <c r="M10" s="24" t="n"/>
@@ -2268,7 +2272,7 @@
       </c>
       <c r="L12" s="28" t="inlineStr">
         <is>
-          <t>Design in editorial template</t>
+          <t>Carousel, 7 slides. Photo cover using smile-portrait.png</t>
         </is>
       </c>
       <c r="M12" s="24" t="n"/>

--- a/strategy/ig-content-strategy.xlsx
+++ b/strategy/ig-content-strategy.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="B2:C49"/>
+  <dimension ref="A1:C55"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3" customWidth="1" style="13" min="1" max="1"/>
@@ -544,6 +544,7 @@
     <col width="20" customWidth="1" style="13" min="5" max="6"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="19.7" customHeight="1" s="14">
       <c r="B2" s="15" t="inlineStr">
         <is>
@@ -558,6 +559,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="14">
       <c r="B5" s="17" t="n"/>
       <c r="C5" s="18" t="n"/>
@@ -797,6 +799,7 @@
         <v/>
       </c>
     </row>
+    <row r="29"/>
     <row r="30" ht="15" customHeight="1" s="14">
       <c r="B30" s="21" t="inlineStr">
         <is>
@@ -804,6 +807,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="B32" s="22" t="inlineStr">
         <is>
@@ -871,6 +875,7 @@
         </is>
       </c>
     </row>
+    <row r="38"/>
     <row r="39">
       <c r="B39" s="22" t="inlineStr">
         <is>
@@ -883,6 +888,7 @@
         </is>
       </c>
     </row>
+    <row r="40"/>
     <row r="41">
       <c r="B41" s="22" t="inlineStr">
         <is>
@@ -978,6 +984,61 @@
       <c r="C49" s="24" t="inlineStr">
         <is>
           <t>Every set now leads with local tags. Location plus service is the highest intent combination.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="22" t="inlineStr">
+        <is>
+          <t>GRID RHYTHM</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="23" t="inlineStr">
+        <is>
+          <t>Rule</t>
+        </is>
+      </c>
+      <c r="C52" s="24" t="inlineStr">
+        <is>
+          <t>The profile grid runs three tiles per row, newest first. Keep exactly one Dark or dark-photo tile in each row of three, and never let two Dark tiles sit side by side.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="23" t="inlineStr">
+        <is>
+          <t>Tone column</t>
+        </is>
+      </c>
+      <c r="C53" s="24" t="inlineStr">
+        <is>
+          <t>Light = cream, Dark = ink variant, Photo = photo led cover. Check it when moving dates: swapping two posts can put two Dark tiles together.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="23" t="inlineStr">
+        <is>
+          <t>How</t>
+        </is>
+      </c>
+      <c r="C54" s="24" t="inlineStr">
+        <is>
+          <t>The single-image and carousel templates take a dark theme flag, so flipping a post is a one-line change and a re-render, not a redesign.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="23" t="inlineStr">
+        <is>
+          <t>Sept onward</t>
+        </is>
+      </c>
+      <c r="C55" s="24" t="inlineStr">
+        <is>
+          <t>September to November posts are all Light today. Assign Dark to roughly one post per week when designing them, matching the August rhythm.</t>
         </is>
       </c>
     </row>
@@ -994,14 +1055,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AA66"/>
+  <dimension ref="A1:AB66"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="13" min="1" max="1"/>
     <col width="6" customWidth="1" style="13" min="2" max="3"/>
     <col width="20" customWidth="1" style="13" min="4" max="4"/>
     <col width="14" customWidth="1" style="13" min="5" max="5"/>
-    <col width="24" customWidth="1" style="13" min="6" max="6"/>
+    <col width="10" customWidth="1" style="13" min="6" max="6"/>
     <col width="15" customWidth="1" style="13" min="7" max="7"/>
     <col width="42" customWidth="1" style="13" min="8" max="8"/>
     <col width="60" customWidth="1" style="13" min="9" max="9"/>
@@ -1047,112 +1108,117 @@
           <t>Format</t>
         </is>
       </c>
-      <c r="F1" s="25" t="inlineStr">
+      <c r="F1" s="26" t="inlineStr">
+        <is>
+          <t>Tone</t>
+        </is>
+      </c>
+      <c r="G1" s="25" t="inlineStr">
         <is>
           <t>Platforms</t>
         </is>
       </c>
-      <c r="G1" s="25" t="inlineStr">
+      <c r="H1" s="25" t="inlineStr">
         <is>
           <t>Pillar</t>
         </is>
       </c>
-      <c r="H1" s="25" t="inlineStr">
+      <c r="I1" s="25" t="inlineStr">
         <is>
           <t>Topic &amp; Hook</t>
         </is>
       </c>
-      <c r="I1" s="25" t="inlineStr">
+      <c r="J1" s="25" t="inlineStr">
         <is>
           <t>Caption Draft</t>
         </is>
       </c>
-      <c r="J1" s="25" t="inlineStr">
+      <c r="K1" s="25" t="inlineStr">
         <is>
           <t>CTA</t>
         </is>
       </c>
-      <c r="K1" s="25" t="inlineStr">
+      <c r="L1" s="25" t="inlineStr">
         <is>
           <t>Hashtag Set</t>
         </is>
       </c>
-      <c r="L1" s="25" t="inlineStr">
+      <c r="M1" s="25" t="inlineStr">
         <is>
           <t>Visual / Asset</t>
         </is>
       </c>
-      <c r="M1" s="26" t="inlineStr">
+      <c r="N1" s="26" t="inlineStr">
         <is>
           <t>Photo Assets</t>
         </is>
       </c>
-      <c r="N1" s="26" t="inlineStr">
+      <c r="O1" s="26" t="inlineStr">
         <is>
           <t>Consent</t>
         </is>
       </c>
-      <c r="O1" s="25" t="inlineStr">
+      <c r="P1" s="25" t="inlineStr">
         <is>
           <t>Folder Link</t>
         </is>
       </c>
-      <c r="P1" s="26" t="inlineStr">
+      <c r="Q1" s="26" t="inlineStr">
         <is>
           <t>Image Link</t>
         </is>
       </c>
-      <c r="Q1" s="26" t="inlineStr">
+      <c r="R1" s="26" t="inlineStr">
         <is>
           <t>Preview</t>
         </is>
       </c>
-      <c r="R1" s="25" t="inlineStr">
+      <c r="S1" s="25" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="S1" s="25" t="inlineStr">
+      <c r="T1" s="25" t="inlineStr">
         <is>
           <t>Posted Link</t>
         </is>
       </c>
-      <c r="T1" s="25" t="inlineStr">
+      <c r="U1" s="25" t="inlineStr">
         <is>
           <t>Reach</t>
         </is>
       </c>
-      <c r="U1" s="25" t="inlineStr">
+      <c r="V1" s="25" t="inlineStr">
         <is>
           <t>Saves</t>
         </is>
       </c>
-      <c r="V1" s="25" t="inlineStr">
+      <c r="W1" s="25" t="inlineStr">
         <is>
           <t>Comments</t>
         </is>
       </c>
-      <c r="W1" s="25" t="inlineStr">
+      <c r="X1" s="25" t="inlineStr">
         <is>
           <t>DMs</t>
         </is>
       </c>
-      <c r="X1" s="25" t="inlineStr">
+      <c r="Y1" s="25" t="inlineStr">
         <is>
           <t>Bookings</t>
         </is>
       </c>
-      <c r="Y1" s="26" t="inlineStr">
+      <c r="Z1" s="26" t="inlineStr">
         <is>
           <t>GBP Caption</t>
         </is>
       </c>
-      <c r="Z1" s="26" t="inlineStr">
+      <c r="AA1" s="26" t="inlineStr">
         <is>
           <t>GBP CTA</t>
         </is>
       </c>
-      <c r="AA1" s="26" t="inlineStr">
+      <c r="AB1" s="26" t="inlineStr">
         <is>
           <t>GBP Image Link</t>
         </is>
@@ -1180,72 +1246,77 @@
           <t>Carousel</t>
         </is>
       </c>
-      <c r="F2" s="28" t="inlineStr">
+      <c r="F2" s="24" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G2" s="28" t="inlineStr">
         <is>
           <t>Instagram feed + GBP</t>
         </is>
       </c>
-      <c r="G2" s="28" t="inlineStr">
+      <c r="H2" s="28" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
       </c>
-      <c r="H2" s="28" t="inlineStr">
+      <c r="I2" s="28" t="inlineStr">
         <is>
           <t>5 Botox Lies You Still Believe | The truth, from a nurse injector.</t>
         </is>
       </c>
-      <c r="I2" s="28" t="inlineStr">
+      <c r="J2" s="28" t="inlineStr">
         <is>
           <t>Half of what you have heard about Botox came from someone who saw bad work. Let's set the record straight. Which myth did you believe? Drop it below and share this with a friend who needs slide 5.
 #botox #botoxeducation #botoxmyths #preventativebotox #antiwrinkleinjections #nurseinjector #medspa #naturalbotox #botoxbeforeandafter #aestheticnurse</t>
         </is>
       </c>
-      <c r="J2" s="28" t="inlineStr">
+      <c r="K2" s="28" t="inlineStr">
         <is>
           <t>DM BOTOX or link in bio</t>
         </is>
       </c>
-      <c r="K2" s="28" t="inlineStr">
+      <c r="L2" s="28" t="inlineStr">
         <is>
           <t>Set A</t>
         </is>
       </c>
-      <c r="L2" s="28" t="inlineStr">
+      <c r="M2" s="28" t="inlineStr">
         <is>
           <t>READY: 8 final slides in this post's folder</t>
         </is>
       </c>
-      <c r="M2" s="24" t="n"/>
       <c r="N2" s="24" t="n"/>
-      <c r="O2" s="32" t="inlineStr">
+      <c r="O2" s="24" t="n"/>
+      <c r="P2" s="32" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P2" s="33" t="inlineStr">
+      <c r="Q2" s="33" t="inlineStr">
         <is>
           <t>View 8 slides</t>
         </is>
       </c>
-      <c r="Q2" s="24">
+      <c r="R2" s="24">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-08-17-5-botox-lies-you-still/images/slide-1.png")</f>
         <v/>
       </c>
-      <c r="R2" s="28" t="inlineStr">
+      <c r="S2" s="28" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="S2" s="28" t="n"/>
       <c r="T2" s="28" t="n"/>
       <c r="U2" s="28" t="n"/>
       <c r="V2" s="28" t="n"/>
       <c r="W2" s="28" t="n"/>
       <c r="X2" s="28" t="n"/>
-      <c r="Y2" s="24" t="n"/>
+      <c r="Y2" s="28" t="n"/>
       <c r="Z2" s="24" t="n"/>
-      <c r="AA2" s="33" t="inlineStr">
+      <c r="AA2" s="24" t="n"/>
+      <c r="AB2" s="33" t="inlineStr">
         <is>
           <t>View GBP image</t>
         </is>
@@ -1273,72 +1344,77 @@
           <t>Single Image</t>
         </is>
       </c>
-      <c r="F3" s="30" t="inlineStr">
+      <c r="F3" s="24" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+      <c r="G3" s="30" t="inlineStr">
         <is>
           <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
-      <c r="G3" s="30" t="inlineStr">
+      <c r="H3" s="30" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
       </c>
-      <c r="H3" s="30" t="inlineStr">
+      <c r="I3" s="30" t="inlineStr">
         <is>
           <t>Service Spotlight: Botox | Smooth, not frozen.</t>
         </is>
       </c>
-      <c r="I3" s="30" t="inlineStr">
+      <c r="J3" s="30" t="inlineStr">
         <is>
           <t>Softened lines, full expression, and nobody can tell why you look so rested. That is Botox done right.
 #botox #botoxeducation #botoxmyths #preventativebotox #antiwrinkleinjections #nurseinjector #medspa #naturalbotox #botoxbeforeandafter #aestheticnurse</t>
         </is>
       </c>
-      <c r="J3" s="30" t="inlineStr">
+      <c r="K3" s="30" t="inlineStr">
         <is>
           <t>DM BOTOX to book</t>
         </is>
       </c>
-      <c r="K3" s="30" t="inlineStr">
+      <c r="L3" s="30" t="inlineStr">
         <is>
           <t>Set A</t>
         </is>
       </c>
-      <c r="L3" s="30" t="inlineStr">
+      <c r="M3" s="30" t="inlineStr">
         <is>
           <t>READY: final image in this post's folder</t>
         </is>
       </c>
-      <c r="M3" s="24" t="n"/>
       <c r="N3" s="24" t="n"/>
-      <c r="O3" s="34" t="inlineStr">
+      <c r="O3" s="24" t="n"/>
+      <c r="P3" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P3" s="33" t="inlineStr">
+      <c r="Q3" s="33" t="inlineStr">
         <is>
           <t>View image</t>
         </is>
       </c>
-      <c r="Q3" s="24">
+      <c r="R3" s="24">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-08-18-service-spotlight-botox/images/post.png")</f>
         <v/>
       </c>
-      <c r="R3" s="30" t="inlineStr">
+      <c r="S3" s="30" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="S3" s="30" t="n"/>
       <c r="T3" s="30" t="n"/>
       <c r="U3" s="30" t="n"/>
       <c r="V3" s="30" t="n"/>
       <c r="W3" s="30" t="n"/>
       <c r="X3" s="30" t="n"/>
-      <c r="Y3" s="24" t="n"/>
+      <c r="Y3" s="30" t="n"/>
       <c r="Z3" s="24" t="n"/>
-      <c r="AA3" s="33" t="inlineStr">
+      <c r="AA3" s="24" t="n"/>
+      <c r="AB3" s="33" t="inlineStr">
         <is>
           <t>View GBP image</t>
         </is>
@@ -1366,22 +1442,27 @@
           <t>Carousel</t>
         </is>
       </c>
-      <c r="F4" s="28" t="inlineStr">
+      <c r="F4" s="24" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G4" s="28" t="inlineStr">
         <is>
           <t>Instagram feed + GBP</t>
         </is>
       </c>
-      <c r="G4" s="28" t="inlineStr">
+      <c r="H4" s="28" t="inlineStr">
         <is>
           <t>Trust &amp; Proof</t>
         </is>
       </c>
-      <c r="H4" s="28" t="inlineStr">
+      <c r="I4" s="28" t="inlineStr">
         <is>
           <t>5 Red Flags at a Med Spa. Run. | Your face deserves better than a bargain.</t>
         </is>
       </c>
-      <c r="I4" s="28" t="inlineStr">
+      <c r="J4" s="28" t="inlineStr">
         <is>
           <t>If nobody asked you a single question before picking up a needle, leave.
 I have fixed enough work from other clinics to know the pattern. The problem is
@@ -1393,59 +1474,59 @@
 #oakvillemedspa #burlingtonmedspa #miltonontario #mississaugabeauty #haltonregion #honestinjector #naturalresults #aestheticnurse #nursepractitioner #medspacanada #luxurybeautybycleor #npcleo</t>
         </is>
       </c>
-      <c r="J4" s="28" t="inlineStr">
+      <c r="K4" s="28" t="inlineStr">
         <is>
           <t>Save this before you book</t>
         </is>
       </c>
-      <c r="K4" s="28" t="inlineStr">
+      <c r="L4" s="28" t="inlineStr">
         <is>
           <t>Set C</t>
         </is>
       </c>
-      <c r="L4" s="28" t="inlineStr">
+      <c r="M4" s="28" t="inlineStr">
         <is>
           <t>Design in editorial template (sequel to Choosing the Right NP)</t>
         </is>
       </c>
-      <c r="M4" s="24" t="n"/>
       <c r="N4" s="24" t="n"/>
-      <c r="O4" s="32" t="inlineStr">
+      <c r="O4" s="24" t="n"/>
+      <c r="P4" s="32" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P4" s="33" t="inlineStr">
+      <c r="Q4" s="33" t="inlineStr">
         <is>
           <t>View 7 slides</t>
         </is>
       </c>
-      <c r="Q4" s="24">
+      <c r="R4" s="24">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-08-20-5-red-flags-at-a/images/slide-1.png")</f>
         <v/>
       </c>
-      <c r="R4" s="28" t="inlineStr">
+      <c r="S4" s="28" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="S4" s="28" t="n"/>
       <c r="T4" s="28" t="n"/>
       <c r="U4" s="28" t="n"/>
       <c r="V4" s="28" t="n"/>
       <c r="W4" s="28" t="n"/>
       <c r="X4" s="28" t="n"/>
-      <c r="Y4" s="24" t="inlineStr">
+      <c r="Y4" s="28" t="n"/>
+      <c r="Z4" s="24" t="inlineStr">
         <is>
           <t>Five things to walk away from at a med spa: no consultation, bargain pricing, a provider who never says no, no named injector, and no plan for complications. Know them before you book anywhere. Serving Oakville, Burlington, Milton and Mississauga.</t>
         </is>
       </c>
-      <c r="Z4" s="24" t="inlineStr">
+      <c r="AA4" s="24" t="inlineStr">
         <is>
           <t>Learn more &gt; Instagram</t>
         </is>
       </c>
-      <c r="AA4" s="33" t="inlineStr">
+      <c r="AB4" s="33" t="inlineStr">
         <is>
           <t>View GBP image</t>
         </is>
@@ -1473,22 +1554,27 @@
           <t>Single Image</t>
         </is>
       </c>
-      <c r="F5" s="30" t="inlineStr">
+      <c r="F5" s="24" t="inlineStr">
+        <is>
+          <t>Dark</t>
+        </is>
+      </c>
+      <c r="G5" s="30" t="inlineStr">
         <is>
           <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
-      <c r="G5" s="30" t="inlineStr">
+      <c r="H5" s="30" t="inlineStr">
         <is>
           <t>Personality &amp; BTS</t>
         </is>
       </c>
-      <c r="H5" s="30" t="inlineStr">
+      <c r="I5" s="30" t="inlineStr">
         <is>
           <t>Behind the Scenes: The Prep | Zero shortcuts. Ever.</t>
         </is>
       </c>
-      <c r="I5" s="30" t="inlineStr">
+      <c r="J5" s="30" t="inlineStr">
         <is>
           <t>The part nobody films is the part that keeps you safe.
 New tray. New gloves. Product opened in front of you so you can see the vial,
@@ -1500,59 +1586,59 @@
 #oakville #oakvillebusiness #burlingtonontario #miltonontario #mississauga #haltonregion #womeninbusiness #nursepractitioner #aestheticnurse #medspalife #luxurybeautybycleor #npcleo</t>
         </is>
       </c>
-      <c r="J5" s="30" t="inlineStr">
+      <c r="K5" s="30" t="inlineStr">
         <is>
           <t>Zero shortcuts. Ever.</t>
         </is>
       </c>
-      <c r="K5" s="30" t="inlineStr">
+      <c r="L5" s="30" t="inlineStr">
         <is>
           <t>Set D</t>
         </is>
       </c>
-      <c r="L5" s="30" t="inlineStr">
+      <c r="M5" s="30" t="inlineStr">
         <is>
           <t>prep tray photo + hook overlay</t>
         </is>
       </c>
-      <c r="M5" s="24" t="n"/>
       <c r="N5" s="24" t="n"/>
-      <c r="O5" s="34" t="inlineStr">
+      <c r="O5" s="24" t="n"/>
+      <c r="P5" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P5" s="33" t="inlineStr">
+      <c r="Q5" s="33" t="inlineStr">
         <is>
           <t>View image</t>
         </is>
       </c>
-      <c r="Q5" s="24">
+      <c r="R5" s="24">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-08-21-behind-the-scenes-the-prep/images/post.png")</f>
         <v/>
       </c>
-      <c r="R5" s="30" t="inlineStr">
+      <c r="S5" s="30" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="S5" s="30" t="n"/>
       <c r="T5" s="30" t="n"/>
       <c r="U5" s="30" t="n"/>
       <c r="V5" s="30" t="n"/>
       <c r="W5" s="30" t="n"/>
       <c r="X5" s="30" t="n"/>
-      <c r="Y5" s="24" t="inlineStr">
+      <c r="Y5" s="30" t="n"/>
+      <c r="Z5" s="24" t="inlineStr">
         <is>
           <t>Every appointment starts the same way. New tray, sealed product opened in front of you, and your face mapped while it moves so the plan fits how you actually move. Ask to watch. Serving Oakville, Burlington, Milton and Mississauga.</t>
         </is>
       </c>
-      <c r="Z5" s="24" t="inlineStr">
+      <c r="AA5" s="24" t="inlineStr">
         <is>
           <t>Learn more &gt; Instagram</t>
         </is>
       </c>
-      <c r="AA5" s="33" t="inlineStr">
+      <c r="AB5" s="33" t="inlineStr">
         <is>
           <t>View GBP image</t>
         </is>
@@ -1580,22 +1666,27 @@
           <t>Before/After</t>
         </is>
       </c>
-      <c r="F6" s="30" t="inlineStr">
+      <c r="F6" s="24" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G6" s="30" t="inlineStr">
         <is>
           <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
-      <c r="G6" s="30" t="inlineStr">
+      <c r="H6" s="30" t="inlineStr">
         <is>
           <t>Trust &amp; Proof</t>
         </is>
       </c>
-      <c r="H6" s="30" t="inlineStr">
+      <c r="I6" s="30" t="inlineStr">
         <is>
           <t>Great Work Is Invisible | You were not supposed to notice.</t>
         </is>
       </c>
-      <c r="I6" s="30" t="inlineStr">
+      <c r="J6" s="30" t="inlineStr">
         <is>
           <t>She booked because her top lip disappeared when she smiled.
 Not because she wanted bigger lips. She was very clear about that. One syringe,
@@ -1607,67 +1698,67 @@
 #lipfilleroakville #fillersoakville #oakvillemedspa #burlingtonfiller #miltonlipfiller #mississaugamedspa #dermalfillers #naturallips #facialbalancing #aestheticnurse #luxurybeautybycleor #npcleo</t>
         </is>
       </c>
-      <c r="J6" s="30" t="inlineStr">
+      <c r="K6" s="30" t="inlineStr">
         <is>
           <t>Message to book</t>
         </is>
       </c>
-      <c r="K6" s="30" t="inlineStr">
+      <c r="L6" s="30" t="inlineStr">
         <is>
           <t>Set B</t>
         </is>
       </c>
-      <c r="L6" s="30" t="inlineStr">
+      <c r="M6" s="30" t="inlineStr">
         <is>
           <t>Before and after card in editorial template. Crop to treatment area, no faces</t>
         </is>
       </c>
-      <c r="M6" s="24" t="inlineStr">
+      <c r="N6" s="24" t="inlineStr">
         <is>
           <t>img_9908 (before), img_9912 (after)</t>
         </is>
       </c>
-      <c r="N6" s="24" t="inlineStr">
+      <c r="O6" s="24" t="inlineStr">
         <is>
           <t>Not needed</t>
         </is>
       </c>
-      <c r="O6" s="34" t="inlineStr">
+      <c r="P6" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P6" s="33" t="inlineStr">
+      <c r="Q6" s="33" t="inlineStr">
         <is>
           <t>View image</t>
         </is>
       </c>
-      <c r="Q6" s="24">
+      <c r="R6" s="24">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-08-22-great-work-is-invisible/images/before-after-result.png")</f>
         <v/>
       </c>
-      <c r="R6" s="30" t="inlineStr">
+      <c r="S6" s="30" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="S6" s="30" t="n"/>
       <c r="T6" s="30" t="n"/>
       <c r="U6" s="30" t="n"/>
       <c r="V6" s="30" t="n"/>
       <c r="W6" s="30" t="n"/>
       <c r="X6" s="30" t="n"/>
-      <c r="Y6" s="24" t="inlineStr">
+      <c r="Y6" s="30" t="n"/>
+      <c r="Z6" s="24" t="inlineStr">
         <is>
           <t>One syringe of lip filler, with her own lip shape kept exactly where it was. Natural results are the whole point of how we practise. Shared with client consent, individual results vary. Serving Oakville, Burlington, Milton and Mississauga.</t>
         </is>
       </c>
-      <c r="Z6" s="24" t="inlineStr">
+      <c r="AA6" s="24" t="inlineStr">
         <is>
           <t>Learn more &gt; Instagram</t>
         </is>
       </c>
-      <c r="AA6" s="33" t="inlineStr">
+      <c r="AB6" s="33" t="inlineStr">
         <is>
           <t>View GBP image</t>
         </is>
@@ -1695,22 +1786,27 @@
           <t>Carousel</t>
         </is>
       </c>
-      <c r="F7" s="28" t="inlineStr">
+      <c r="F7" s="24" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G7" s="28" t="inlineStr">
         <is>
           <t>Instagram feed + GBP</t>
         </is>
       </c>
-      <c r="G7" s="28" t="inlineStr">
+      <c r="H7" s="28" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
       </c>
-      <c r="H7" s="28" t="inlineStr">
+      <c r="I7" s="28" t="inlineStr">
         <is>
           <t>Your First Visit, Step by Step | Nervous about your first appointment? Here is exactly what happens.</t>
         </is>
       </c>
-      <c r="I7" s="28" t="inlineStr">
+      <c r="J7" s="28" t="inlineStr">
         <is>
           <t>Most people arrive nervous and leave asking why they waited so long.
 Usually that is because nobody told them what actually happens. So here it is,
@@ -1723,59 +1819,59 @@
 #botoxoakville #oakvillemedspa #burlingtonbotox #miltonmedspa #mississaugainjector #haltonregion #preventativebotox #botoxcanada #nursepractitionerinjector #naturalresults #luxurybeautybycleor #npcleo</t>
         </is>
       </c>
-      <c r="J7" s="28" t="inlineStr">
+      <c r="K7" s="28" t="inlineStr">
         <is>
           <t>DM to book a consult</t>
         </is>
       </c>
-      <c r="K7" s="28" t="inlineStr">
+      <c r="L7" s="28" t="inlineStr">
         <is>
           <t>Set A</t>
         </is>
       </c>
-      <c r="L7" s="28" t="inlineStr">
+      <c r="M7" s="28" t="inlineStr">
         <is>
           <t>Design in editorial template + treatment room photos</t>
         </is>
       </c>
-      <c r="M7" s="24" t="n"/>
       <c r="N7" s="24" t="n"/>
-      <c r="O7" s="32" t="inlineStr">
+      <c r="O7" s="24" t="n"/>
+      <c r="P7" s="32" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P7" s="33" t="inlineStr">
+      <c r="Q7" s="33" t="inlineStr">
         <is>
           <t>View 8 slides</t>
         </is>
       </c>
-      <c r="Q7" s="24">
+      <c r="R7" s="24">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-08-24-your-first-visit-step-by/images/slide-1.png")</f>
         <v/>
       </c>
-      <c r="R7" s="28" t="inlineStr">
+      <c r="S7" s="28" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="S7" s="28" t="n"/>
       <c r="T7" s="28" t="n"/>
       <c r="U7" s="28" t="n"/>
       <c r="V7" s="28" t="n"/>
       <c r="W7" s="28" t="n"/>
       <c r="X7" s="28" t="n"/>
-      <c r="Y7" s="24" t="inlineStr">
+      <c r="Y7" s="28" t="n"/>
+      <c r="Z7" s="24" t="inlineStr">
         <is>
           <t>Nervous about your first appointment? A real consultation, your face mapped in motion, then the areas and the price agreed before anything is opened. The treatment itself takes about ten minutes. Serving Oakville, Burlington, Milton and Mississauga.</t>
         </is>
       </c>
-      <c r="Z7" s="24" t="inlineStr">
+      <c r="AA7" s="24" t="inlineStr">
         <is>
           <t>Learn more &gt; Instagram</t>
         </is>
       </c>
-      <c r="AA7" s="33" t="inlineStr">
+      <c r="AB7" s="33" t="inlineStr">
         <is>
           <t>View GBP image</t>
         </is>
@@ -1803,22 +1899,27 @@
           <t>Single Image</t>
         </is>
       </c>
-      <c r="F8" s="30" t="inlineStr">
+      <c r="F8" s="24" t="inlineStr">
+        <is>
+          <t>Dark</t>
+        </is>
+      </c>
+      <c r="G8" s="30" t="inlineStr">
         <is>
           <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
-      <c r="G8" s="30" t="inlineStr">
+      <c r="H8" s="30" t="inlineStr">
         <is>
           <t>Trust &amp; Proof</t>
         </is>
       </c>
-      <c r="H8" s="30" t="inlineStr">
+      <c r="I8" s="30" t="inlineStr">
         <is>
           <t>Why I Do Not Post Prices | Every clinic gets this DM. Almost nobody answers it honestly.</t>
         </is>
       </c>
-      <c r="I8" s="30" t="inlineStr">
+      <c r="J8" s="30" t="inlineStr">
         <is>
           <t>Every clinic gets this DM. Almost nobody answers it honestly.
 Units are not a menu item. Two people who want the same result can need very
@@ -1833,59 +1934,59 @@
 #oakvillemedspa #burlingtonmedspa #miltonontario #mississaugabeauty #haltonregion #honestinjector #naturalresults #aestheticnurse #nursepractitioner #medspacanada #luxurybeautybycleor #npcleo</t>
         </is>
       </c>
-      <c r="J8" s="30" t="inlineStr">
+      <c r="K8" s="30" t="inlineStr">
         <is>
           <t>DM the word PRICE</t>
         </is>
       </c>
-      <c r="K8" s="30" t="inlineStr">
+      <c r="L8" s="30" t="inlineStr">
         <is>
           <t>Set C</t>
         </is>
       </c>
-      <c r="L8" s="30" t="inlineStr">
+      <c r="M8" s="30" t="inlineStr">
         <is>
           <t>Single image, dark variant. Type led, no photo</t>
         </is>
       </c>
-      <c r="M8" s="24" t="n"/>
       <c r="N8" s="24" t="n"/>
-      <c r="O8" s="34" t="inlineStr">
+      <c r="O8" s="24" t="n"/>
+      <c r="P8" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P8" s="33" t="inlineStr">
+      <c r="Q8" s="33" t="inlineStr">
         <is>
           <t>View image</t>
         </is>
       </c>
-      <c r="Q8" s="24">
+      <c r="R8" s="24">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-08-25-why-i-do-not-post/images/post.png")</f>
         <v/>
       </c>
-      <c r="R8" s="30" t="inlineStr">
+      <c r="S8" s="30" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="S8" s="30" t="n"/>
       <c r="T8" s="30" t="n"/>
       <c r="U8" s="30" t="n"/>
       <c r="V8" s="30" t="n"/>
       <c r="W8" s="30" t="n"/>
       <c r="X8" s="30" t="n"/>
-      <c r="Y8" s="24" t="inlineStr">
+      <c r="Y8" s="30" t="n"/>
+      <c r="Z8" s="24" t="inlineStr">
         <is>
           <t>Why we do not post a price list. Doses differ from face to face, so one flat price either overcharges you or under treats you. You get a written number at your consult, before anything is opened. Serving Oakville, Burlington, Milton and Mississauga.</t>
         </is>
       </c>
-      <c r="Z8" s="24" t="inlineStr">
+      <c r="AA8" s="24" t="inlineStr">
         <is>
           <t>Learn more &gt; Instagram</t>
         </is>
       </c>
-      <c r="AA8" s="33" t="inlineStr">
+      <c r="AB8" s="33" t="inlineStr">
         <is>
           <t>View GBP image</t>
         </is>
@@ -1913,22 +2014,27 @@
           <t>Carousel</t>
         </is>
       </c>
-      <c r="F9" s="28" t="inlineStr">
+      <c r="F9" s="24" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+      <c r="G9" s="28" t="inlineStr">
         <is>
           <t>Instagram feed + GBP</t>
         </is>
       </c>
-      <c r="G9" s="28" t="inlineStr">
+      <c r="H9" s="28" t="inlineStr">
         <is>
           <t>Personality &amp; BTS</t>
         </is>
       </c>
-      <c r="H9" s="28" t="inlineStr">
+      <c r="I9" s="28" t="inlineStr">
         <is>
           <t>Meet NP Cleo: The Face Behind the Glow | Real education. Real results. Real care.</t>
         </is>
       </c>
-      <c r="I9" s="28" t="inlineStr">
+      <c r="J9" s="28" t="inlineStr">
         <is>
           <t>I got tired of fixing work that never should have happened.
 That is the honest reason this clinic exists. Most people who sit in my chair
@@ -1941,59 +2047,59 @@
 #oakville #oakvillebusiness #burlingtonontario #miltonontario #mississauga #haltonregion #womeninbusiness #nursepractitioner #aestheticnurse #medspalife #luxurybeautybycleor #npcleo</t>
         </is>
       </c>
-      <c r="J9" s="28" t="inlineStr">
+      <c r="K9" s="28" t="inlineStr">
         <is>
           <t>DM the word CONSULT</t>
         </is>
       </c>
-      <c r="K9" s="28" t="inlineStr">
+      <c r="L9" s="28" t="inlineStr">
         <is>
           <t>Set D</t>
         </is>
       </c>
-      <c r="L9" s="28" t="inlineStr">
+      <c r="M9" s="28" t="inlineStr">
         <is>
           <t>Portrait photos of Cleo (reuse cleo.png + new shots)</t>
         </is>
       </c>
-      <c r="M9" s="24" t="n"/>
       <c r="N9" s="24" t="n"/>
-      <c r="O9" s="32" t="inlineStr">
+      <c r="O9" s="24" t="n"/>
+      <c r="P9" s="32" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P9" s="33" t="inlineStr">
+      <c r="Q9" s="33" t="inlineStr">
         <is>
           <t>View 5 slides</t>
         </is>
       </c>
-      <c r="Q9" s="24">
+      <c r="R9" s="24">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-08-27-meet-np-cleo-the-face/images/slide-1.png")</f>
         <v/>
       </c>
-      <c r="R9" s="28" t="inlineStr">
+      <c r="S9" s="28" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="S9" s="28" t="n"/>
       <c r="T9" s="28" t="n"/>
       <c r="U9" s="28" t="n"/>
       <c r="V9" s="28" t="n"/>
       <c r="W9" s="28" t="n"/>
       <c r="X9" s="28" t="n"/>
-      <c r="Y9" s="24" t="inlineStr">
+      <c r="Y9" s="28" t="n"/>
+      <c r="Z9" s="24" t="inlineStr">
         <is>
           <t>Meet NP Cleo. Nurse practitioner and injector, and the person who will tell you no when the honest answer is not yet. Every appointment is injected by Cleo, never delegated. Serving Oakville, Burlington, Milton and Mississauga.</t>
         </is>
       </c>
-      <c r="Z9" s="24" t="inlineStr">
+      <c r="AA9" s="24" t="inlineStr">
         <is>
           <t>Learn more &gt; Instagram</t>
         </is>
       </c>
-      <c r="AA9" s="33" t="inlineStr">
+      <c r="AB9" s="33" t="inlineStr">
         <is>
           <t>View GBP image</t>
         </is>
@@ -2021,22 +2127,27 @@
           <t>Single Image</t>
         </is>
       </c>
-      <c r="F10" s="30" t="inlineStr">
+      <c r="F10" s="24" t="inlineStr">
+        <is>
+          <t>Dark</t>
+        </is>
+      </c>
+      <c r="G10" s="30" t="inlineStr">
         <is>
           <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
-      <c r="G10" s="30" t="inlineStr">
+      <c r="H10" s="30" t="inlineStr">
         <is>
           <t>Personality &amp; BTS</t>
         </is>
       </c>
-      <c r="H10" s="30" t="inlineStr">
+      <c r="I10" s="30" t="inlineStr">
         <is>
           <t>Welcome to the Treatment Room | Where calm meets careful.</t>
         </is>
       </c>
-      <c r="I10" s="30" t="inlineStr">
+      <c r="J10" s="30" t="inlineStr">
         <is>
           <t>One person in the room at a time, and the door stays shut.
 Nobody rushes the client before you, which means nobody rushes you either. You
@@ -2047,59 +2158,59 @@
 #oakville #oakvillebusiness #burlingtonontario #miltonontario #mississauga #haltonregion #womeninbusiness #nursepractitioner #aestheticnurse #medspalife #luxurybeautybycleor #npcleo</t>
         </is>
       </c>
-      <c r="J10" s="30" t="inlineStr">
+      <c r="K10" s="30" t="inlineStr">
         <is>
           <t>Come see it</t>
         </is>
       </c>
-      <c r="K10" s="30" t="inlineStr">
+      <c r="L10" s="30" t="inlineStr">
         <is>
           <t>Set D</t>
         </is>
       </c>
-      <c r="L10" s="30" t="inlineStr">
+      <c r="M10" s="30" t="inlineStr">
         <is>
           <t>Single image, dark photo led. Uses botox-prep.png framed on the room</t>
         </is>
       </c>
-      <c r="M10" s="24" t="n"/>
       <c r="N10" s="24" t="n"/>
-      <c r="O10" s="34" t="inlineStr">
+      <c r="O10" s="24" t="n"/>
+      <c r="P10" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P10" s="33" t="inlineStr">
+      <c r="Q10" s="33" t="inlineStr">
         <is>
           <t>View image</t>
         </is>
       </c>
-      <c r="Q10" s="24">
+      <c r="R10" s="24">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-08-28-welcome-to-the-treatment-room/images/post.png")</f>
         <v/>
       </c>
-      <c r="R10" s="30" t="inlineStr">
+      <c r="S10" s="30" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="S10" s="30" t="n"/>
       <c r="T10" s="30" t="n"/>
       <c r="U10" s="30" t="n"/>
       <c r="V10" s="30" t="n"/>
       <c r="W10" s="30" t="n"/>
       <c r="X10" s="30" t="n"/>
-      <c r="Y10" s="24" t="inlineStr">
+      <c r="Y10" s="30" t="n"/>
+      <c r="Z10" s="24" t="inlineStr">
         <is>
           <t>One client in the treatment room at a time. Nobody rushes the person before you, so nobody rushes you. Questions welcome, and a plan agreed before anything happens. Serving Oakville, Burlington, Milton and Mississauga.</t>
         </is>
       </c>
-      <c r="Z10" s="24" t="inlineStr">
+      <c r="AA10" s="24" t="inlineStr">
         <is>
           <t>Learn more &gt; Instagram</t>
         </is>
       </c>
-      <c r="AA10" s="33" t="inlineStr">
+      <c r="AB10" s="33" t="inlineStr">
         <is>
           <t>View GBP image</t>
         </is>
@@ -2127,22 +2238,27 @@
           <t>Single Image</t>
         </is>
       </c>
-      <c r="F11" s="30" t="inlineStr">
+      <c r="F11" s="24" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G11" s="30" t="inlineStr">
         <is>
           <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
-      <c r="G11" s="30" t="inlineStr">
+      <c r="H11" s="30" t="inlineStr">
         <is>
           <t>Trust &amp; Proof</t>
         </is>
       </c>
-      <c r="H11" s="30" t="inlineStr">
+      <c r="I11" s="30" t="inlineStr">
         <is>
           <t>This or That: Rested vs Frozen | If people ask what you had done, the dose was wrong.</t>
         </is>
       </c>
-      <c r="I11" s="30" t="inlineStr">
+      <c r="J11" s="30" t="inlineStr">
         <is>
           <t>If people ask what you had done, the dose was wrong.
 The goal was never to erase your expressions. You should still frown at your
@@ -2152,59 +2268,59 @@
 #oakvillemedspa #burlingtonmedspa #miltonontario #mississaugabeauty #haltonregion #honestinjector #naturalresults #aestheticnurse #nursepractitioner #medspacanada #luxurybeautybycleor #npcleo</t>
         </is>
       </c>
-      <c r="J11" s="30" t="inlineStr">
+      <c r="K11" s="30" t="inlineStr">
         <is>
           <t>Which one do you want?</t>
         </is>
       </c>
-      <c r="K11" s="30" t="inlineStr">
+      <c r="L11" s="30" t="inlineStr">
         <is>
           <t>Set C</t>
         </is>
       </c>
-      <c r="L11" s="30" t="inlineStr">
+      <c r="M11" s="30" t="inlineStr">
         <is>
           <t>Two-panel comparison card in brand style</t>
         </is>
       </c>
-      <c r="M11" s="24" t="n"/>
       <c r="N11" s="24" t="n"/>
-      <c r="O11" s="34" t="inlineStr">
+      <c r="O11" s="24" t="n"/>
+      <c r="P11" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P11" s="33" t="inlineStr">
+      <c r="Q11" s="33" t="inlineStr">
         <is>
           <t>View image</t>
         </is>
       </c>
-      <c r="Q11" s="24">
+      <c r="R11" s="24">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-08-29-this-or-that-rested-vs/images/post.png")</f>
         <v/>
       </c>
-      <c r="R11" s="30" t="inlineStr">
+      <c r="S11" s="30" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="S11" s="30" t="n"/>
       <c r="T11" s="30" t="n"/>
       <c r="U11" s="30" t="n"/>
       <c r="V11" s="30" t="n"/>
       <c r="W11" s="30" t="n"/>
       <c r="X11" s="30" t="n"/>
-      <c r="Y11" s="24" t="inlineStr">
+      <c r="Y11" s="30" t="n"/>
+      <c r="Z11" s="24" t="inlineStr">
         <is>
           <t>Rested, not frozen. You should still frown, squint and smile. If people ask what you had done instead of whether you slept well, the dose was wrong. Serving Oakville, Burlington, Milton and Mississauga.</t>
         </is>
       </c>
-      <c r="Z11" s="24" t="inlineStr">
+      <c r="AA11" s="24" t="inlineStr">
         <is>
           <t>Learn more &gt; Instagram</t>
         </is>
       </c>
-      <c r="AA11" s="33" t="inlineStr">
+      <c r="AB11" s="33" t="inlineStr">
         <is>
           <t>View GBP image</t>
         </is>
@@ -2232,22 +2348,27 @@
           <t>Carousel</t>
         </is>
       </c>
-      <c r="F12" s="28" t="inlineStr">
+      <c r="F12" s="24" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+      <c r="G12" s="28" t="inlineStr">
         <is>
           <t>Instagram feed + GBP</t>
         </is>
       </c>
-      <c r="G12" s="28" t="inlineStr">
+      <c r="H12" s="28" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
       </c>
-      <c r="H12" s="28" t="inlineStr">
+      <c r="I12" s="28" t="inlineStr">
         <is>
           <t>Preventative Botox: When to Actually Start | Your friend who never seems to age? This is why.</t>
         </is>
       </c>
-      <c r="I12" s="28" t="inlineStr">
+      <c r="J12" s="28" t="inlineStr">
         <is>
           <t>Your friend who never seems to age did not get lucky.
 She started before there was anything to fix. That is the whole trick, and it
@@ -2260,59 +2381,59 @@
 #botoxoakville #oakvillemedspa #burlingtonbotox #miltonmedspa #mississaugainjector #haltonregion #preventativebotox #botoxcanada #nursepractitionerinjector #naturalresults #luxurybeautybycleor #npcleo</t>
         </is>
       </c>
-      <c r="J12" s="28" t="inlineStr">
+      <c r="K12" s="28" t="inlineStr">
         <is>
           <t>DM the word START</t>
         </is>
       </c>
-      <c r="K12" s="28" t="inlineStr">
+      <c r="L12" s="28" t="inlineStr">
         <is>
           <t>Set A</t>
         </is>
       </c>
-      <c r="L12" s="28" t="inlineStr">
+      <c r="M12" s="28" t="inlineStr">
         <is>
           <t>Carousel, 7 slides. Photo cover using smile-portrait.png</t>
         </is>
       </c>
-      <c r="M12" s="24" t="n"/>
       <c r="N12" s="24" t="n"/>
-      <c r="O12" s="32" t="inlineStr">
+      <c r="O12" s="24" t="n"/>
+      <c r="P12" s="32" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P12" s="33" t="inlineStr">
+      <c r="Q12" s="33" t="inlineStr">
         <is>
           <t>View 7 slides</t>
         </is>
       </c>
-      <c r="Q12" s="24">
+      <c r="R12" s="24">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-08-31-preventative-botox-when-to-actually/images/slide-1.png")</f>
         <v/>
       </c>
-      <c r="R12" s="28" t="inlineStr">
+      <c r="S12" s="28" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="S12" s="28" t="n"/>
       <c r="T12" s="28" t="n"/>
       <c r="U12" s="28" t="n"/>
       <c r="V12" s="28" t="n"/>
       <c r="W12" s="28" t="n"/>
       <c r="X12" s="28" t="n"/>
-      <c r="Y12" s="24" t="inlineStr">
+      <c r="Y12" s="28" t="n"/>
+      <c r="Z12" s="24" t="inlineStr">
         <is>
           <t>When should you actually start preventative treatment? It is not about your age. Make your strongest expression, then relax completely. A line that stays is one that is setting in. Serving Oakville, Burlington, Milton and Mississauga.</t>
         </is>
       </c>
-      <c r="Z12" s="24" t="inlineStr">
+      <c r="AA12" s="24" t="inlineStr">
         <is>
           <t>Learn more &gt; Instagram</t>
         </is>
       </c>
-      <c r="AA12" s="33" t="inlineStr">
+      <c r="AB12" s="33" t="inlineStr">
         <is>
           <t>View GBP image</t>
         </is>
@@ -2340,69 +2461,74 @@
           <t>Single Image</t>
         </is>
       </c>
-      <c r="F13" s="30" t="inlineStr">
+      <c r="F13" s="24" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G13" s="30" t="inlineStr">
         <is>
           <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
-      <c r="G13" s="30" t="inlineStr">
+      <c r="H13" s="30" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
       </c>
-      <c r="H13" s="30" t="inlineStr">
+      <c r="I13" s="30" t="inlineStr">
         <is>
           <t>Service Spotlight: Preventative Botox | Start before the lines do.</t>
         </is>
       </c>
-      <c r="I13" s="30" t="inlineStr">
+      <c r="J13" s="30" t="inlineStr">
         <is>
           <t>The friend who never seems to age did not find a miracle cream. She started early and kept it subtle.
 #botox #botoxeducation #botoxmyths #preventativebotox #antiwrinkleinjections #nurseinjector #medspa #naturalbotox #botoxbeforeandafter #aestheticnurse</t>
         </is>
       </c>
-      <c r="J13" s="30" t="inlineStr">
+      <c r="K13" s="30" t="inlineStr">
         <is>
           <t>DM PREVENT to talk</t>
         </is>
       </c>
-      <c r="K13" s="30" t="inlineStr">
+      <c r="L13" s="30" t="inlineStr">
         <is>
           <t>Set A</t>
         </is>
       </c>
-      <c r="L13" s="30" t="inlineStr">
+      <c r="M13" s="30" t="inlineStr">
         <is>
           <t>Single image: young client or product photo + hook</t>
         </is>
       </c>
-      <c r="M13" s="24" t="n"/>
       <c r="N13" s="24" t="n"/>
-      <c r="O13" s="34" t="inlineStr">
+      <c r="O13" s="24" t="n"/>
+      <c r="P13" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P13" s="24" t="inlineStr">
-        <is>
-          <t>Not designed yet</t>
-        </is>
-      </c>
-      <c r="Q13" s="24" t="n"/>
-      <c r="R13" s="30" t="inlineStr">
+      <c r="Q13" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="R13" s="24" t="n"/>
+      <c r="S13" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="S13" s="30" t="n"/>
       <c r="T13" s="30" t="n"/>
       <c r="U13" s="30" t="n"/>
       <c r="V13" s="30" t="n"/>
       <c r="W13" s="30" t="n"/>
       <c r="X13" s="30" t="n"/>
-      <c r="Y13" s="24" t="n"/>
+      <c r="Y13" s="30" t="n"/>
       <c r="Z13" s="24" t="n"/>
-      <c r="AA13" s="24" t="inlineStr">
+      <c r="AA13" s="24" t="n"/>
+      <c r="AB13" s="24" t="inlineStr">
         <is>
           <t>Not designed yet</t>
         </is>
@@ -2430,69 +2556,74 @@
           <t>Carousel</t>
         </is>
       </c>
-      <c r="F14" s="28" t="inlineStr">
+      <c r="F14" s="24" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G14" s="28" t="inlineStr">
         <is>
           <t>Instagram feed + GBP</t>
         </is>
       </c>
-      <c r="G14" s="28" t="inlineStr">
+      <c r="H14" s="28" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
       </c>
-      <c r="H14" s="28" t="inlineStr">
+      <c r="I14" s="28" t="inlineStr">
         <is>
           <t>What 20 Units Actually Looks Like | Unit math, finally explained.</t>
         </is>
       </c>
-      <c r="I14" s="28" t="inlineStr">
+      <c r="J14" s="28" t="inlineStr">
         <is>
           <t>You have seen the price per unit. But what does 20 units actually do? Here is the honest breakdown of dosing, areas, and why cheaper per unit is not cheaper overall.
 #botox #botoxeducation #botoxmyths #preventativebotox #antiwrinkleinjections #nurseinjector #medspa #naturalbotox #botoxbeforeandafter #aestheticnurse</t>
         </is>
       </c>
-      <c r="J14" s="28" t="inlineStr">
+      <c r="K14" s="28" t="inlineStr">
         <is>
           <t>Save this for your consult</t>
         </is>
       </c>
-      <c r="K14" s="28" t="inlineStr">
+      <c r="L14" s="28" t="inlineStr">
         <is>
           <t>Set A</t>
         </is>
       </c>
-      <c r="L14" s="28" t="inlineStr">
+      <c r="M14" s="28" t="inlineStr">
         <is>
           <t>Design in editorial template + dosing diagram</t>
         </is>
       </c>
-      <c r="M14" s="24" t="n"/>
       <c r="N14" s="24" t="n"/>
-      <c r="O14" s="32" t="inlineStr">
+      <c r="O14" s="24" t="n"/>
+      <c r="P14" s="32" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P14" s="24" t="inlineStr">
-        <is>
-          <t>Not designed yet</t>
-        </is>
-      </c>
-      <c r="Q14" s="24" t="n"/>
-      <c r="R14" s="28" t="inlineStr">
+      <c r="Q14" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="R14" s="24" t="n"/>
+      <c r="S14" s="28" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="S14" s="28" t="n"/>
       <c r="T14" s="28" t="n"/>
       <c r="U14" s="28" t="n"/>
       <c r="V14" s="28" t="n"/>
       <c r="W14" s="28" t="n"/>
       <c r="X14" s="28" t="n"/>
-      <c r="Y14" s="24" t="n"/>
+      <c r="Y14" s="28" t="n"/>
       <c r="Z14" s="24" t="n"/>
-      <c r="AA14" s="24" t="inlineStr">
+      <c r="AA14" s="24" t="n"/>
+      <c r="AB14" s="24" t="inlineStr">
         <is>
           <t>Not designed yet</t>
         </is>
@@ -2520,69 +2651,74 @@
           <t>Single Image</t>
         </is>
       </c>
-      <c r="F15" s="30" t="inlineStr">
+      <c r="F15" s="24" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G15" s="30" t="inlineStr">
         <is>
           <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
-      <c r="G15" s="30" t="inlineStr">
+      <c r="H15" s="30" t="inlineStr">
         <is>
           <t>Personality &amp; BTS</t>
         </is>
       </c>
-      <c r="H15" s="30" t="inlineStr">
+      <c r="I15" s="30" t="inlineStr">
         <is>
           <t>Meet Your Injector | Board certified. Botox obsessed. Brutally honest.</t>
         </is>
       </c>
-      <c r="I15" s="30" t="inlineStr">
+      <c r="J15" s="30" t="inlineStr">
         <is>
           <t>Your face deserves a nurse practitioner who tells the truth about what you need and what you do not. Hi, I am Cleo. 💛
 #npinjector #nursepractitioner #medspalife #luxurybeauty #aestheticnurse #skincareexpert #beautyclinic #selfcare #naturalresults #honestbeauty</t>
         </is>
       </c>
-      <c r="J15" s="30" t="inlineStr">
+      <c r="K15" s="30" t="inlineStr">
         <is>
           <t>Say hi in the comments</t>
         </is>
       </c>
-      <c r="K15" s="30" t="inlineStr">
+      <c r="L15" s="30" t="inlineStr">
         <is>
           <t>Set C</t>
         </is>
       </c>
-      <c r="L15" s="30" t="inlineStr">
+      <c r="M15" s="30" t="inlineStr">
         <is>
           <t>Single image: Cleo portrait + credentials hook</t>
         </is>
       </c>
-      <c r="M15" s="24" t="n"/>
       <c r="N15" s="24" t="n"/>
-      <c r="O15" s="34" t="inlineStr">
+      <c r="O15" s="24" t="n"/>
+      <c r="P15" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P15" s="24" t="inlineStr">
-        <is>
-          <t>Not designed yet</t>
-        </is>
-      </c>
-      <c r="Q15" s="24" t="n"/>
-      <c r="R15" s="30" t="inlineStr">
+      <c r="Q15" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="R15" s="24" t="n"/>
+      <c r="S15" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="S15" s="30" t="n"/>
       <c r="T15" s="30" t="n"/>
       <c r="U15" s="30" t="n"/>
       <c r="V15" s="30" t="n"/>
       <c r="W15" s="30" t="n"/>
       <c r="X15" s="30" t="n"/>
-      <c r="Y15" s="24" t="n"/>
+      <c r="Y15" s="30" t="n"/>
       <c r="Z15" s="24" t="n"/>
-      <c r="AA15" s="24" t="inlineStr">
+      <c r="AA15" s="24" t="n"/>
+      <c r="AB15" s="24" t="inlineStr">
         <is>
           <t>Not designed yet</t>
         </is>
@@ -2610,69 +2746,74 @@
           <t>Single Image</t>
         </is>
       </c>
-      <c r="F16" s="30" t="inlineStr">
+      <c r="F16" s="24" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G16" s="30" t="inlineStr">
         <is>
           <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
-      <c r="G16" s="30" t="inlineStr">
+      <c r="H16" s="30" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
       </c>
-      <c r="H16" s="30" t="inlineStr">
+      <c r="I16" s="30" t="inlineStr">
         <is>
           <t>Quote: Prevention Beats Erasing | Brand quote card.</t>
         </is>
       </c>
-      <c r="I16" s="30" t="inlineStr">
+      <c r="J16" s="30" t="inlineStr">
         <is>
           <t>Lines are easier to prevent than to erase. Save this reminder.
 #npinjector #nursepractitioner #medspalife #luxurybeauty #aestheticnurse #skincareexpert #beautyclinic #selfcare #naturalresults #honestbeauty</t>
         </is>
       </c>
-      <c r="J16" s="30" t="inlineStr">
+      <c r="K16" s="30" t="inlineStr">
         <is>
           <t>Save this</t>
         </is>
       </c>
-      <c r="K16" s="30" t="inlineStr">
+      <c r="L16" s="30" t="inlineStr">
         <is>
           <t>Set C</t>
         </is>
       </c>
-      <c r="L16" s="30" t="inlineStr">
+      <c r="M16" s="30" t="inlineStr">
         <is>
           <t>Quote card in brand style</t>
         </is>
       </c>
-      <c r="M16" s="24" t="n"/>
       <c r="N16" s="24" t="n"/>
-      <c r="O16" s="34" t="inlineStr">
+      <c r="O16" s="24" t="n"/>
+      <c r="P16" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P16" s="24" t="inlineStr">
-        <is>
-          <t>Not designed yet</t>
-        </is>
-      </c>
-      <c r="Q16" s="24" t="n"/>
-      <c r="R16" s="30" t="inlineStr">
+      <c r="Q16" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="R16" s="24" t="n"/>
+      <c r="S16" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="S16" s="30" t="n"/>
       <c r="T16" s="30" t="n"/>
       <c r="U16" s="30" t="n"/>
       <c r="V16" s="30" t="n"/>
       <c r="W16" s="30" t="n"/>
       <c r="X16" s="30" t="n"/>
-      <c r="Y16" s="24" t="n"/>
+      <c r="Y16" s="30" t="n"/>
       <c r="Z16" s="24" t="n"/>
-      <c r="AA16" s="24" t="inlineStr">
+      <c r="AA16" s="24" t="n"/>
+      <c r="AB16" s="24" t="inlineStr">
         <is>
           <t>Not designed yet</t>
         </is>
@@ -2700,69 +2841,74 @@
           <t>Carousel</t>
         </is>
       </c>
-      <c r="F17" s="28" t="inlineStr">
+      <c r="F17" s="24" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G17" s="28" t="inlineStr">
         <is>
           <t>Instagram feed + GBP</t>
         </is>
       </c>
-      <c r="G17" s="28" t="inlineStr">
+      <c r="H17" s="28" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
       </c>
-      <c r="H17" s="28" t="inlineStr">
+      <c r="I17" s="28" t="inlineStr">
         <is>
           <t>Botox vs Dysport: The Real Difference | Same family. Different personalities.</t>
         </is>
       </c>
-      <c r="I17" s="28" t="inlineStr">
+      <c r="J17" s="28" t="inlineStr">
         <is>
           <t>The most Googled question in aesthetics, answered honestly. Slide 5 explains why you should never compare prices unit to unit. Save this for later.
 #botox #botoxeducation #botoxmyths #preventativebotox #antiwrinkleinjections #nurseinjector #medspa #naturalbotox #botoxbeforeandafter #aestheticnurse</t>
         </is>
       </c>
-      <c r="J17" s="28" t="inlineStr">
+      <c r="K17" s="28" t="inlineStr">
         <is>
           <t>Book a consult. Link in bio</t>
         </is>
       </c>
-      <c r="K17" s="28" t="inlineStr">
+      <c r="L17" s="28" t="inlineStr">
         <is>
           <t>Set A</t>
         </is>
       </c>
-      <c r="L17" s="28" t="inlineStr">
+      <c r="M17" s="28" t="inlineStr">
         <is>
           <t>Design in editorial template</t>
         </is>
       </c>
-      <c r="M17" s="24" t="n"/>
       <c r="N17" s="24" t="n"/>
-      <c r="O17" s="32" t="inlineStr">
+      <c r="O17" s="24" t="n"/>
+      <c r="P17" s="32" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P17" s="24" t="inlineStr">
-        <is>
-          <t>Not designed yet</t>
-        </is>
-      </c>
-      <c r="Q17" s="24" t="n"/>
-      <c r="R17" s="28" t="inlineStr">
+      <c r="Q17" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="R17" s="24" t="n"/>
+      <c r="S17" s="28" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="S17" s="28" t="n"/>
       <c r="T17" s="28" t="n"/>
       <c r="U17" s="28" t="n"/>
       <c r="V17" s="28" t="n"/>
       <c r="W17" s="28" t="n"/>
       <c r="X17" s="28" t="n"/>
-      <c r="Y17" s="24" t="n"/>
+      <c r="Y17" s="28" t="n"/>
       <c r="Z17" s="24" t="n"/>
-      <c r="AA17" s="24" t="inlineStr">
+      <c r="AA17" s="24" t="n"/>
+      <c r="AB17" s="24" t="inlineStr">
         <is>
           <t>Not designed yet</t>
         </is>
@@ -2790,69 +2936,74 @@
           <t>Single Image</t>
         </is>
       </c>
-      <c r="F18" s="30" t="inlineStr">
+      <c r="F18" s="24" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G18" s="30" t="inlineStr">
         <is>
           <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
-      <c r="G18" s="30" t="inlineStr">
+      <c r="H18" s="30" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
       </c>
-      <c r="H18" s="30" t="inlineStr">
+      <c r="I18" s="30" t="inlineStr">
         <is>
           <t>Botox vs Dysport at a Glance | Same family. Different personalities.</t>
         </is>
       </c>
-      <c r="I18" s="30" t="inlineStr">
+      <c r="J18" s="30" t="inlineStr">
         <is>
           <t>Dysport kicks in faster and spreads wider. Botox is precise. The right one depends on your face, not the price list.
 #botox #botoxeducation #botoxmyths #preventativebotox #antiwrinkleinjections #nurseinjector #medspa #naturalbotox #botoxbeforeandafter #aestheticnurse</t>
         </is>
       </c>
-      <c r="J18" s="30" t="inlineStr">
+      <c r="K18" s="30" t="inlineStr">
         <is>
           <t>Full breakdown on our feed</t>
         </is>
       </c>
-      <c r="K18" s="30" t="inlineStr">
+      <c r="L18" s="30" t="inlineStr">
         <is>
           <t>Set A</t>
         </is>
       </c>
-      <c r="L18" s="30" t="inlineStr">
+      <c r="M18" s="30" t="inlineStr">
         <is>
           <t>Single image: side-by-side comparison card</t>
         </is>
       </c>
-      <c r="M18" s="24" t="n"/>
       <c r="N18" s="24" t="n"/>
-      <c r="O18" s="34" t="inlineStr">
+      <c r="O18" s="24" t="n"/>
+      <c r="P18" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P18" s="24" t="inlineStr">
-        <is>
-          <t>Not designed yet</t>
-        </is>
-      </c>
-      <c r="Q18" s="24" t="n"/>
-      <c r="R18" s="30" t="inlineStr">
+      <c r="Q18" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="R18" s="24" t="n"/>
+      <c r="S18" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="S18" s="30" t="n"/>
       <c r="T18" s="30" t="n"/>
       <c r="U18" s="30" t="n"/>
       <c r="V18" s="30" t="n"/>
       <c r="W18" s="30" t="n"/>
       <c r="X18" s="30" t="n"/>
-      <c r="Y18" s="24" t="n"/>
+      <c r="Y18" s="30" t="n"/>
       <c r="Z18" s="24" t="n"/>
-      <c r="AA18" s="24" t="inlineStr">
+      <c r="AA18" s="24" t="n"/>
+      <c r="AB18" s="24" t="inlineStr">
         <is>
           <t>Not designed yet</t>
         </is>
@@ -2880,69 +3031,74 @@
           <t>Carousel</t>
         </is>
       </c>
-      <c r="F19" s="28" t="inlineStr">
+      <c r="F19" s="24" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G19" s="28" t="inlineStr">
         <is>
           <t>Instagram feed + GBP</t>
         </is>
       </c>
-      <c r="G19" s="28" t="inlineStr">
+      <c r="H19" s="28" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
       </c>
-      <c r="H19" s="28" t="inlineStr">
+      <c r="I19" s="28" t="inlineStr">
         <is>
           <t>Botox Aftercare: The First 48 Hours | You got Botox. Now what?</t>
         </is>
       </c>
-      <c r="I19" s="28" t="inlineStr">
+      <c r="J19" s="28" t="inlineStr">
         <is>
           <t>The first 48 hours matter more than most people think. Here is exactly what to do, what to skip, and when to call me. Bookmark this one.
 #botox #botoxeducation #botoxmyths #preventativebotox #antiwrinkleinjections #nurseinjector #medspa #naturalbotox #botoxbeforeandafter #aestheticnurse</t>
         </is>
       </c>
-      <c r="J19" s="28" t="inlineStr">
+      <c r="K19" s="28" t="inlineStr">
         <is>
           <t>Save this guide</t>
         </is>
       </c>
-      <c r="K19" s="28" t="inlineStr">
+      <c r="L19" s="28" t="inlineStr">
         <is>
           <t>Set A</t>
         </is>
       </c>
-      <c r="L19" s="28" t="inlineStr">
+      <c r="M19" s="28" t="inlineStr">
         <is>
           <t>Design in editorial template</t>
         </is>
       </c>
-      <c r="M19" s="24" t="n"/>
       <c r="N19" s="24" t="n"/>
-      <c r="O19" s="32" t="inlineStr">
+      <c r="O19" s="24" t="n"/>
+      <c r="P19" s="32" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P19" s="24" t="inlineStr">
-        <is>
-          <t>Not designed yet</t>
-        </is>
-      </c>
-      <c r="Q19" s="24" t="n"/>
-      <c r="R19" s="28" t="inlineStr">
+      <c r="Q19" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="R19" s="24" t="n"/>
+      <c r="S19" s="28" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="S19" s="28" t="n"/>
       <c r="T19" s="28" t="n"/>
       <c r="U19" s="28" t="n"/>
       <c r="V19" s="28" t="n"/>
       <c r="W19" s="28" t="n"/>
       <c r="X19" s="28" t="n"/>
-      <c r="Y19" s="24" t="n"/>
+      <c r="Y19" s="28" t="n"/>
       <c r="Z19" s="24" t="n"/>
-      <c r="AA19" s="24" t="inlineStr">
+      <c r="AA19" s="24" t="n"/>
+      <c r="AB19" s="24" t="inlineStr">
         <is>
           <t>Not designed yet</t>
         </is>
@@ -2970,69 +3126,74 @@
           <t>Single Image</t>
         </is>
       </c>
-      <c r="F20" s="30" t="inlineStr">
+      <c r="F20" s="24" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G20" s="30" t="inlineStr">
         <is>
           <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
-      <c r="G20" s="30" t="inlineStr">
+      <c r="H20" s="30" t="inlineStr">
         <is>
           <t>Trust &amp; Proof</t>
         </is>
       </c>
-      <c r="H20" s="30" t="inlineStr">
+      <c r="I20" s="30" t="inlineStr">
         <is>
           <t>The Face Map | Every face gets a plan.</t>
         </is>
       </c>
-      <c r="I20" s="30" t="inlineStr">
+      <c r="J20" s="30" t="inlineStr">
         <is>
           <t>Nothing touches your skin before I map your anatomy, your movement, and your goals. Planning is the treatment.
 #npinjector #nursepractitioner #medspalife #luxurybeauty #aestheticnurse #skincareexpert #beautyclinic #selfcare #naturalresults #honestbeauty</t>
         </is>
       </c>
-      <c r="J20" s="30" t="inlineStr">
+      <c r="K20" s="30" t="inlineStr">
         <is>
           <t>Book your mapping. Link in bio</t>
         </is>
       </c>
-      <c r="K20" s="30" t="inlineStr">
+      <c r="L20" s="30" t="inlineStr">
         <is>
           <t>Set C</t>
         </is>
       </c>
-      <c r="L20" s="30" t="inlineStr">
+      <c r="M20" s="30" t="inlineStr">
         <is>
           <t>Single image: assessment photo + hook</t>
         </is>
       </c>
-      <c r="M20" s="24" t="n"/>
       <c r="N20" s="24" t="n"/>
-      <c r="O20" s="34" t="inlineStr">
+      <c r="O20" s="24" t="n"/>
+      <c r="P20" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P20" s="24" t="inlineStr">
-        <is>
-          <t>Not designed yet</t>
-        </is>
-      </c>
-      <c r="Q20" s="24" t="n"/>
-      <c r="R20" s="30" t="inlineStr">
+      <c r="Q20" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="R20" s="24" t="n"/>
+      <c r="S20" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="S20" s="30" t="n"/>
       <c r="T20" s="30" t="n"/>
       <c r="U20" s="30" t="n"/>
       <c r="V20" s="30" t="n"/>
       <c r="W20" s="30" t="n"/>
       <c r="X20" s="30" t="n"/>
-      <c r="Y20" s="24" t="n"/>
+      <c r="Y20" s="30" t="n"/>
       <c r="Z20" s="24" t="n"/>
-      <c r="AA20" s="24" t="inlineStr">
+      <c r="AA20" s="24" t="n"/>
+      <c r="AB20" s="24" t="inlineStr">
         <is>
           <t>Not designed yet</t>
         </is>
@@ -3060,69 +3221,74 @@
           <t>Single Image</t>
         </is>
       </c>
-      <c r="F21" s="30" t="inlineStr">
+      <c r="F21" s="24" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G21" s="30" t="inlineStr">
         <is>
           <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
-      <c r="G21" s="30" t="inlineStr">
+      <c r="H21" s="30" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
       </c>
-      <c r="H21" s="30" t="inlineStr">
+      <c r="I21" s="30" t="inlineStr">
         <is>
           <t>FAQ: Does Botox Hurt? | Honest answer, no fluff.</t>
         </is>
       </c>
-      <c r="I21" s="30" t="inlineStr">
+      <c r="J21" s="30" t="inlineStr">
         <is>
           <t>Honestly? Less than plucking a brow. Tiny needle, a few seconds per area, and numbing if you want it. Most people say wait, that was it?
 #npinjector #nursepractitioner #medspalife #luxurybeauty #aestheticnurse #skincareexpert #beautyclinic #selfcare #naturalresults #honestbeauty</t>
         </is>
       </c>
-      <c r="J21" s="30" t="inlineStr">
+      <c r="K21" s="30" t="inlineStr">
         <is>
           <t>More questions? DM me</t>
         </is>
       </c>
-      <c r="K21" s="30" t="inlineStr">
+      <c r="L21" s="30" t="inlineStr">
         <is>
           <t>Set C</t>
         </is>
       </c>
-      <c r="L21" s="30" t="inlineStr">
+      <c r="M21" s="30" t="inlineStr">
         <is>
           <t>FAQ card in brand style</t>
         </is>
       </c>
-      <c r="M21" s="24" t="n"/>
       <c r="N21" s="24" t="n"/>
-      <c r="O21" s="34" t="inlineStr">
+      <c r="O21" s="24" t="n"/>
+      <c r="P21" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P21" s="24" t="inlineStr">
-        <is>
-          <t>Not designed yet</t>
-        </is>
-      </c>
-      <c r="Q21" s="24" t="n"/>
-      <c r="R21" s="30" t="inlineStr">
+      <c r="Q21" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="R21" s="24" t="n"/>
+      <c r="S21" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="S21" s="30" t="n"/>
       <c r="T21" s="30" t="n"/>
       <c r="U21" s="30" t="n"/>
       <c r="V21" s="30" t="n"/>
       <c r="W21" s="30" t="n"/>
       <c r="X21" s="30" t="n"/>
-      <c r="Y21" s="24" t="n"/>
+      <c r="Y21" s="30" t="n"/>
       <c r="Z21" s="24" t="n"/>
-      <c r="AA21" s="24" t="inlineStr">
+      <c r="AA21" s="24" t="n"/>
+      <c r="AB21" s="24" t="inlineStr">
         <is>
           <t>Not designed yet</t>
         </is>
@@ -3150,69 +3316,74 @@
           <t>Carousel</t>
         </is>
       </c>
-      <c r="F22" s="28" t="inlineStr">
+      <c r="F22" s="24" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G22" s="28" t="inlineStr">
         <is>
           <t>Instagram feed + GBP</t>
         </is>
       </c>
-      <c r="G22" s="28" t="inlineStr">
+      <c r="H22" s="28" t="inlineStr">
         <is>
           <t>Trust &amp; Proof</t>
         </is>
       </c>
-      <c r="H22" s="28" t="inlineStr">
+      <c r="I22" s="28" t="inlineStr">
         <is>
           <t>5 Things Botox Can't Do | Honest expectations, always.</t>
         </is>
       </c>
-      <c r="I22" s="28" t="inlineStr">
+      <c r="J22" s="28" t="inlineStr">
         <is>
           <t>Botox is amazing at what it does. But it cannot do everything, and anyone who says otherwise is selling you something. Here is what it fixes and what needs a different plan.
 #botox #botoxeducation #botoxmyths #preventativebotox #antiwrinkleinjections #nurseinjector #medspa #naturalbotox #botoxbeforeandafter #aestheticnurse</t>
         </is>
       </c>
-      <c r="J22" s="28" t="inlineStr">
+      <c r="K22" s="28" t="inlineStr">
         <is>
           <t>Comment your questions</t>
         </is>
       </c>
-      <c r="K22" s="28" t="inlineStr">
+      <c r="L22" s="28" t="inlineStr">
         <is>
           <t>Set A</t>
         </is>
       </c>
-      <c r="L22" s="28" t="inlineStr">
+      <c r="M22" s="28" t="inlineStr">
         <is>
           <t>Design in editorial template</t>
         </is>
       </c>
-      <c r="M22" s="24" t="n"/>
       <c r="N22" s="24" t="n"/>
-      <c r="O22" s="32" t="inlineStr">
+      <c r="O22" s="24" t="n"/>
+      <c r="P22" s="32" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P22" s="24" t="inlineStr">
-        <is>
-          <t>Not designed yet</t>
-        </is>
-      </c>
-      <c r="Q22" s="24" t="n"/>
-      <c r="R22" s="28" t="inlineStr">
+      <c r="Q22" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="R22" s="24" t="n"/>
+      <c r="S22" s="28" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="S22" s="28" t="n"/>
       <c r="T22" s="28" t="n"/>
       <c r="U22" s="28" t="n"/>
       <c r="V22" s="28" t="n"/>
       <c r="W22" s="28" t="n"/>
       <c r="X22" s="28" t="n"/>
-      <c r="Y22" s="24" t="n"/>
+      <c r="Y22" s="28" t="n"/>
       <c r="Z22" s="24" t="n"/>
-      <c r="AA22" s="24" t="inlineStr">
+      <c r="AA22" s="24" t="n"/>
+      <c r="AB22" s="24" t="inlineStr">
         <is>
           <t>Not designed yet</t>
         </is>
@@ -3240,69 +3411,74 @@
           <t>Single Image</t>
         </is>
       </c>
-      <c r="F23" s="30" t="inlineStr">
+      <c r="F23" s="24" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G23" s="30" t="inlineStr">
         <is>
           <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
-      <c r="G23" s="30" t="inlineStr">
+      <c r="H23" s="30" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
       </c>
-      <c r="H23" s="30" t="inlineStr">
+      <c r="I23" s="30" t="inlineStr">
         <is>
           <t>What Botox Can't Fix | Honest expectations, always.</t>
         </is>
       </c>
-      <c r="I23" s="30" t="inlineStr">
+      <c r="J23" s="30" t="inlineStr">
         <is>
           <t>Sagging skin, volume loss, texture. Botox is not the tool for everything, and I would rather tell you that now than take your money and disappoint you.
 #botox #botoxeducation #botoxmyths #preventativebotox #antiwrinkleinjections #nurseinjector #medspa #naturalbotox #botoxbeforeandafter #aestheticnurse</t>
         </is>
       </c>
-      <c r="J23" s="30" t="inlineStr">
+      <c r="K23" s="30" t="inlineStr">
         <is>
           <t>Save this</t>
         </is>
       </c>
-      <c r="K23" s="30" t="inlineStr">
+      <c r="L23" s="30" t="inlineStr">
         <is>
           <t>Set A</t>
         </is>
       </c>
-      <c r="L23" s="30" t="inlineStr">
+      <c r="M23" s="30" t="inlineStr">
         <is>
           <t>Single image: myth-vs-reality card</t>
         </is>
       </c>
-      <c r="M23" s="24" t="n"/>
       <c r="N23" s="24" t="n"/>
-      <c r="O23" s="34" t="inlineStr">
+      <c r="O23" s="24" t="n"/>
+      <c r="P23" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P23" s="24" t="inlineStr">
-        <is>
-          <t>Not designed yet</t>
-        </is>
-      </c>
-      <c r="Q23" s="24" t="n"/>
-      <c r="R23" s="30" t="inlineStr">
+      <c r="Q23" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="R23" s="24" t="n"/>
+      <c r="S23" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="S23" s="30" t="n"/>
       <c r="T23" s="30" t="n"/>
       <c r="U23" s="30" t="n"/>
       <c r="V23" s="30" t="n"/>
       <c r="W23" s="30" t="n"/>
       <c r="X23" s="30" t="n"/>
-      <c r="Y23" s="24" t="n"/>
+      <c r="Y23" s="30" t="n"/>
       <c r="Z23" s="24" t="n"/>
-      <c r="AA23" s="24" t="inlineStr">
+      <c r="AA23" s="24" t="n"/>
+      <c r="AB23" s="24" t="inlineStr">
         <is>
           <t>Not designed yet</t>
         </is>
@@ -3330,69 +3506,74 @@
           <t>Carousel</t>
         </is>
       </c>
-      <c r="F24" s="28" t="inlineStr">
+      <c r="F24" s="24" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G24" s="28" t="inlineStr">
         <is>
           <t>Instagram feed + GBP</t>
         </is>
       </c>
-      <c r="G24" s="28" t="inlineStr">
+      <c r="H24" s="28" t="inlineStr">
         <is>
           <t>Trust &amp; Proof</t>
         </is>
       </c>
-      <c r="H24" s="28" t="inlineStr">
+      <c r="I24" s="28" t="inlineStr">
         <is>
           <t>Still You, Just Refreshed | You won't look done. You'll look rested.</t>
         </is>
       </c>
-      <c r="I24" s="28" t="inlineStr">
+      <c r="J24" s="28" t="inlineStr">
         <is>
           <t>The 2026 standard is not transformation. It is restoration. My goal is that people ask if you have been on vacation, not what you had done. 💛
 #npinjector #nursepractitioner #medspalife #luxurybeauty #aestheticnurse #skincareexpert #beautyclinic #selfcare #naturalresults #honestbeauty</t>
         </is>
       </c>
-      <c r="J24" s="28" t="inlineStr">
+      <c r="K24" s="28" t="inlineStr">
         <is>
           <t>DM GLOW to start</t>
         </is>
       </c>
-      <c r="K24" s="28" t="inlineStr">
+      <c r="L24" s="28" t="inlineStr">
         <is>
           <t>Set C</t>
         </is>
       </c>
-      <c r="L24" s="28" t="inlineStr">
+      <c r="M24" s="28" t="inlineStr">
         <is>
           <t>Template exists (design/slides.html), needs photos</t>
         </is>
       </c>
-      <c r="M24" s="24" t="n"/>
       <c r="N24" s="24" t="n"/>
-      <c r="O24" s="32" t="inlineStr">
+      <c r="O24" s="24" t="n"/>
+      <c r="P24" s="32" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P24" s="24" t="inlineStr">
-        <is>
-          <t>Not designed yet</t>
-        </is>
-      </c>
-      <c r="Q24" s="24" t="n"/>
-      <c r="R24" s="28" t="inlineStr">
+      <c r="Q24" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="R24" s="24" t="n"/>
+      <c r="S24" s="28" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="S24" s="28" t="n"/>
       <c r="T24" s="28" t="n"/>
       <c r="U24" s="28" t="n"/>
       <c r="V24" s="28" t="n"/>
       <c r="W24" s="28" t="n"/>
       <c r="X24" s="28" t="n"/>
-      <c r="Y24" s="24" t="n"/>
+      <c r="Y24" s="28" t="n"/>
       <c r="Z24" s="24" t="n"/>
-      <c r="AA24" s="24" t="inlineStr">
+      <c r="AA24" s="24" t="n"/>
+      <c r="AB24" s="24" t="inlineStr">
         <is>
           <t>Not designed yet</t>
         </is>
@@ -3420,69 +3601,74 @@
           <t>Single Image</t>
         </is>
       </c>
-      <c r="F25" s="30" t="inlineStr">
+      <c r="F25" s="24" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G25" s="30" t="inlineStr">
         <is>
           <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
-      <c r="G25" s="30" t="inlineStr">
+      <c r="H25" s="30" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
       </c>
-      <c r="H25" s="30" t="inlineStr">
+      <c r="I25" s="30" t="inlineStr">
         <is>
           <t>Myth vs Truth: The Frozen Face | The classic fear, debunked.</t>
         </is>
       </c>
-      <c r="I25" s="30" t="inlineStr">
+      <c r="J25" s="30" t="inlineStr">
         <is>
           <t>MYTH: Botox freezes your face. TRUTH: correct dosing softens movement while you keep every expression that makes you, you.
 #botox #botoxeducation #botoxmyths #preventativebotox #antiwrinkleinjections #nurseinjector #medspa #naturalbotox #botoxbeforeandafter #aestheticnurse</t>
         </is>
       </c>
-      <c r="J25" s="30" t="inlineStr">
+      <c r="K25" s="30" t="inlineStr">
         <is>
           <t>Share with a friend</t>
         </is>
       </c>
-      <c r="K25" s="30" t="inlineStr">
+      <c r="L25" s="30" t="inlineStr">
         <is>
           <t>Set A</t>
         </is>
       </c>
-      <c r="L25" s="30" t="inlineStr">
+      <c r="M25" s="30" t="inlineStr">
         <is>
           <t>Single image: myth vs truth split card</t>
         </is>
       </c>
-      <c r="M25" s="24" t="n"/>
       <c r="N25" s="24" t="n"/>
-      <c r="O25" s="34" t="inlineStr">
+      <c r="O25" s="24" t="n"/>
+      <c r="P25" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P25" s="24" t="inlineStr">
-        <is>
-          <t>Not designed yet</t>
-        </is>
-      </c>
-      <c r="Q25" s="24" t="n"/>
-      <c r="R25" s="30" t="inlineStr">
+      <c r="Q25" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="R25" s="24" t="n"/>
+      <c r="S25" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="S25" s="30" t="n"/>
       <c r="T25" s="30" t="n"/>
       <c r="U25" s="30" t="n"/>
       <c r="V25" s="30" t="n"/>
       <c r="W25" s="30" t="n"/>
       <c r="X25" s="30" t="n"/>
-      <c r="Y25" s="24" t="n"/>
+      <c r="Y25" s="30" t="n"/>
       <c r="Z25" s="24" t="n"/>
-      <c r="AA25" s="24" t="inlineStr">
+      <c r="AA25" s="24" t="n"/>
+      <c r="AB25" s="24" t="inlineStr">
         <is>
           <t>Not designed yet</t>
         </is>
@@ -3510,69 +3696,74 @@
           <t>Single Image</t>
         </is>
       </c>
-      <c r="F26" s="30" t="inlineStr">
+      <c r="F26" s="24" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G26" s="30" t="inlineStr">
         <is>
           <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
-      <c r="G26" s="30" t="inlineStr">
+      <c r="H26" s="30" t="inlineStr">
         <is>
           <t>Trust &amp; Proof</t>
         </is>
       </c>
-      <c r="H26" s="30" t="inlineStr">
+      <c r="I26" s="30" t="inlineStr">
         <is>
           <t>Client Words: Natural Results | Testimonial card.</t>
         </is>
       </c>
-      <c r="I26" s="30" t="inlineStr">
+      <c r="J26" s="30" t="inlineStr">
         <is>
           <t>Nobody could tell. They just kept saying I looked happy and rested. That is the whole goal. 💛 (Shared with permission.)
 #npinjector #nursepractitioner #medspalife #luxurybeauty #aestheticnurse #skincareexpert #beautyclinic #selfcare #naturalresults #honestbeauty</t>
         </is>
       </c>
-      <c r="J26" s="30" t="inlineStr">
+      <c r="K26" s="30" t="inlineStr">
         <is>
           <t>Your turn. Link in bio</t>
         </is>
       </c>
-      <c r="K26" s="30" t="inlineStr">
+      <c r="L26" s="30" t="inlineStr">
         <is>
           <t>Set C</t>
         </is>
       </c>
-      <c r="L26" s="30" t="inlineStr">
+      <c r="M26" s="30" t="inlineStr">
         <is>
           <t>Testimonial quote card (with consent)</t>
         </is>
       </c>
-      <c r="M26" s="24" t="n"/>
       <c r="N26" s="24" t="n"/>
-      <c r="O26" s="34" t="inlineStr">
+      <c r="O26" s="24" t="n"/>
+      <c r="P26" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P26" s="24" t="inlineStr">
-        <is>
-          <t>Not designed yet</t>
-        </is>
-      </c>
-      <c r="Q26" s="24" t="n"/>
-      <c r="R26" s="30" t="inlineStr">
+      <c r="Q26" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="R26" s="24" t="n"/>
+      <c r="S26" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="S26" s="30" t="n"/>
       <c r="T26" s="30" t="n"/>
       <c r="U26" s="30" t="n"/>
       <c r="V26" s="30" t="n"/>
       <c r="W26" s="30" t="n"/>
       <c r="X26" s="30" t="n"/>
-      <c r="Y26" s="24" t="n"/>
+      <c r="Y26" s="30" t="n"/>
       <c r="Z26" s="24" t="n"/>
-      <c r="AA26" s="24" t="inlineStr">
+      <c r="AA26" s="24" t="n"/>
+      <c r="AB26" s="24" t="inlineStr">
         <is>
           <t>Not designed yet</t>
         </is>
@@ -3600,69 +3791,74 @@
           <t>Carousel</t>
         </is>
       </c>
-      <c r="F27" s="28" t="inlineStr">
+      <c r="F27" s="24" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G27" s="28" t="inlineStr">
         <is>
           <t>Instagram feed + GBP</t>
         </is>
       </c>
-      <c r="G27" s="28" t="inlineStr">
+      <c r="H27" s="28" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
       </c>
-      <c r="H27" s="28" t="inlineStr">
+      <c r="I27" s="28" t="inlineStr">
         <is>
           <t>Botox or Filler? You Might Be Asking for the Wrong One | Lines or volume? They are not the same problem.</t>
         </is>
       </c>
-      <c r="I27" s="28" t="inlineStr">
+      <c r="J27" s="28" t="inlineStr">
         <is>
           <t>Half the DMs I get ask for the wrong treatment. Here is the simple way to know whether your concern is about movement or volume, and what that means for your plan.
 #dermalfiller #lipfiller #cheekfiller #naturalfiller #facialbalancing #lipfillernatural #aestheticnurse #medspa #fillerjourney #lipgoals</t>
         </is>
       </c>
-      <c r="J27" s="28" t="inlineStr">
+      <c r="K27" s="28" t="inlineStr">
         <is>
           <t>DM CONSULT and I will help</t>
         </is>
       </c>
-      <c r="K27" s="28" t="inlineStr">
+      <c r="L27" s="28" t="inlineStr">
         <is>
           <t>Set B</t>
         </is>
       </c>
-      <c r="L27" s="28" t="inlineStr">
+      <c r="M27" s="28" t="inlineStr">
         <is>
           <t>Design in editorial template</t>
         </is>
       </c>
-      <c r="M27" s="24" t="n"/>
       <c r="N27" s="24" t="n"/>
-      <c r="O27" s="32" t="inlineStr">
+      <c r="O27" s="24" t="n"/>
+      <c r="P27" s="32" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P27" s="24" t="inlineStr">
-        <is>
-          <t>Not designed yet</t>
-        </is>
-      </c>
-      <c r="Q27" s="24" t="n"/>
-      <c r="R27" s="28" t="inlineStr">
+      <c r="Q27" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="R27" s="24" t="n"/>
+      <c r="S27" s="28" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="S27" s="28" t="n"/>
       <c r="T27" s="28" t="n"/>
       <c r="U27" s="28" t="n"/>
       <c r="V27" s="28" t="n"/>
       <c r="W27" s="28" t="n"/>
       <c r="X27" s="28" t="n"/>
-      <c r="Y27" s="24" t="n"/>
+      <c r="Y27" s="28" t="n"/>
       <c r="Z27" s="24" t="n"/>
-      <c r="AA27" s="24" t="inlineStr">
+      <c r="AA27" s="24" t="n"/>
+      <c r="AB27" s="24" t="inlineStr">
         <is>
           <t>Not designed yet</t>
         </is>
@@ -3690,69 +3886,74 @@
           <t>Single Image</t>
         </is>
       </c>
-      <c r="F28" s="30" t="inlineStr">
+      <c r="F28" s="24" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G28" s="30" t="inlineStr">
         <is>
           <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
-      <c r="G28" s="30" t="inlineStr">
+      <c r="H28" s="30" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
       </c>
-      <c r="H28" s="30" t="inlineStr">
+      <c r="I28" s="30" t="inlineStr">
         <is>
           <t>Lines vs Volume | Which one is your concern?</t>
         </is>
       </c>
-      <c r="I28" s="30" t="inlineStr">
+      <c r="J28" s="30" t="inlineStr">
         <is>
           <t>Smile in the mirror. Movement lines need Botox. Lost volume needs filler. The answer decides your plan.
 #dermalfiller #lipfiller #cheekfiller #naturalfiller #facialbalancing #lipfillernatural #aestheticnurse #medspa #fillerjourney #lipgoals</t>
         </is>
       </c>
-      <c r="J28" s="30" t="inlineStr">
+      <c r="K28" s="30" t="inlineStr">
         <is>
           <t>DM CONSULT for help</t>
         </is>
       </c>
-      <c r="K28" s="30" t="inlineStr">
+      <c r="L28" s="30" t="inlineStr">
         <is>
           <t>Set B</t>
         </is>
       </c>
-      <c r="L28" s="30" t="inlineStr">
+      <c r="M28" s="30" t="inlineStr">
         <is>
           <t>Single image: two-column explainer card</t>
         </is>
       </c>
-      <c r="M28" s="24" t="n"/>
       <c r="N28" s="24" t="n"/>
-      <c r="O28" s="34" t="inlineStr">
+      <c r="O28" s="24" t="n"/>
+      <c r="P28" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P28" s="24" t="inlineStr">
-        <is>
-          <t>Not designed yet</t>
-        </is>
-      </c>
-      <c r="Q28" s="24" t="n"/>
-      <c r="R28" s="30" t="inlineStr">
+      <c r="Q28" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="R28" s="24" t="n"/>
+      <c r="S28" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="S28" s="30" t="n"/>
       <c r="T28" s="30" t="n"/>
       <c r="U28" s="30" t="n"/>
       <c r="V28" s="30" t="n"/>
       <c r="W28" s="30" t="n"/>
       <c r="X28" s="30" t="n"/>
-      <c r="Y28" s="24" t="n"/>
+      <c r="Y28" s="30" t="n"/>
       <c r="Z28" s="24" t="n"/>
-      <c r="AA28" s="24" t="inlineStr">
+      <c r="AA28" s="24" t="n"/>
+      <c r="AB28" s="24" t="inlineStr">
         <is>
           <t>Not designed yet</t>
         </is>
@@ -3780,69 +3981,74 @@
           <t>Carousel</t>
         </is>
       </c>
-      <c r="F29" s="28" t="inlineStr">
+      <c r="F29" s="24" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G29" s="28" t="inlineStr">
         <is>
           <t>Instagram feed + GBP</t>
         </is>
       </c>
-      <c r="G29" s="28" t="inlineStr">
+      <c r="H29" s="28" t="inlineStr">
         <is>
           <t>Personality &amp; BTS</t>
         </is>
       </c>
-      <c r="H29" s="28" t="inlineStr">
+      <c r="I29" s="28" t="inlineStr">
         <is>
           <t>Ask NP Cleo: Your Questions, Answered Honestly | You asked. I answered. No filter.</t>
         </is>
       </c>
-      <c r="I29" s="28" t="inlineStr">
+      <c r="J29" s="28" t="inlineStr">
         <is>
           <t>This month you sent amazing questions. Here are the honest answers, including the one nobody else will give you about cheap Botox. Keep them coming. 👇
 #npinjector #nursepractitioner #medspalife #luxurybeauty #aestheticnurse #skincareexpert #beautyclinic #selfcare #naturalresults #honestbeauty</t>
         </is>
       </c>
-      <c r="J29" s="28" t="inlineStr">
+      <c r="K29" s="28" t="inlineStr">
         <is>
           <t>Drop your question below</t>
         </is>
       </c>
-      <c r="K29" s="28" t="inlineStr">
+      <c r="L29" s="28" t="inlineStr">
         <is>
           <t>Set C</t>
         </is>
       </c>
-      <c r="L29" s="28" t="inlineStr">
+      <c r="M29" s="28" t="inlineStr">
         <is>
           <t>Design Q&amp;A layout from real DM questions</t>
         </is>
       </c>
-      <c r="M29" s="24" t="n"/>
       <c r="N29" s="24" t="n"/>
-      <c r="O29" s="32" t="inlineStr">
+      <c r="O29" s="24" t="n"/>
+      <c r="P29" s="32" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P29" s="24" t="inlineStr">
-        <is>
-          <t>Not designed yet</t>
-        </is>
-      </c>
-      <c r="Q29" s="24" t="n"/>
-      <c r="R29" s="28" t="inlineStr">
+      <c r="Q29" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="R29" s="24" t="n"/>
+      <c r="S29" s="28" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="S29" s="28" t="n"/>
       <c r="T29" s="28" t="n"/>
       <c r="U29" s="28" t="n"/>
       <c r="V29" s="28" t="n"/>
       <c r="W29" s="28" t="n"/>
       <c r="X29" s="28" t="n"/>
-      <c r="Y29" s="24" t="n"/>
+      <c r="Y29" s="28" t="n"/>
       <c r="Z29" s="24" t="n"/>
-      <c r="AA29" s="24" t="inlineStr">
+      <c r="AA29" s="24" t="n"/>
+      <c r="AB29" s="24" t="inlineStr">
         <is>
           <t>Not designed yet</t>
         </is>
@@ -3870,69 +4076,74 @@
           <t>Single Image</t>
         </is>
       </c>
-      <c r="F30" s="30" t="inlineStr">
+      <c r="F30" s="24" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G30" s="30" t="inlineStr">
         <is>
           <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
-      <c r="G30" s="30" t="inlineStr">
+      <c r="H30" s="30" t="inlineStr">
         <is>
           <t>Personality &amp; BTS</t>
         </is>
       </c>
-      <c r="H30" s="30" t="inlineStr">
+      <c r="I30" s="30" t="inlineStr">
         <is>
           <t>Your DMs, Answered | The question everyone asks quietly.</t>
         </is>
       </c>
-      <c r="I30" s="30" t="inlineStr">
+      <c r="J30" s="30" t="inlineStr">
         <is>
           <t>You asked: will people know I had work done? Honest answer: only if you want them to. Subtle is the standard here.
 #npinjector #nursepractitioner #medspalife #luxurybeauty #aestheticnurse #skincareexpert #beautyclinic #selfcare #naturalresults #honestbeauty</t>
         </is>
       </c>
-      <c r="J30" s="30" t="inlineStr">
+      <c r="K30" s="30" t="inlineStr">
         <is>
           <t>Send your question</t>
         </is>
       </c>
-      <c r="K30" s="30" t="inlineStr">
+      <c r="L30" s="30" t="inlineStr">
         <is>
           <t>Set C</t>
         </is>
       </c>
-      <c r="L30" s="30" t="inlineStr">
+      <c r="M30" s="30" t="inlineStr">
         <is>
           <t>Single image: Q&amp;A card in brand style</t>
         </is>
       </c>
-      <c r="M30" s="24" t="n"/>
       <c r="N30" s="24" t="n"/>
-      <c r="O30" s="34" t="inlineStr">
+      <c r="O30" s="24" t="n"/>
+      <c r="P30" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P30" s="24" t="inlineStr">
-        <is>
-          <t>Not designed yet</t>
-        </is>
-      </c>
-      <c r="Q30" s="24" t="n"/>
-      <c r="R30" s="30" t="inlineStr">
+      <c r="Q30" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="R30" s="24" t="n"/>
+      <c r="S30" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="S30" s="30" t="n"/>
       <c r="T30" s="30" t="n"/>
       <c r="U30" s="30" t="n"/>
       <c r="V30" s="30" t="n"/>
       <c r="W30" s="30" t="n"/>
       <c r="X30" s="30" t="n"/>
-      <c r="Y30" s="24" t="n"/>
+      <c r="Y30" s="30" t="n"/>
       <c r="Z30" s="24" t="n"/>
-      <c r="AA30" s="24" t="inlineStr">
+      <c r="AA30" s="24" t="n"/>
+      <c r="AB30" s="24" t="inlineStr">
         <is>
           <t>Not designed yet</t>
         </is>
@@ -3960,69 +4171,74 @@
           <t>Single Image</t>
         </is>
       </c>
-      <c r="F31" s="30" t="inlineStr">
+      <c r="F31" s="24" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G31" s="30" t="inlineStr">
         <is>
           <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
-      <c r="G31" s="30" t="inlineStr">
+      <c r="H31" s="30" t="inlineStr">
         <is>
           <t>Personality &amp; BTS</t>
         </is>
       </c>
-      <c r="H31" s="30" t="inlineStr">
+      <c r="I31" s="30" t="inlineStr">
         <is>
           <t>Poll: What Should NP Cleo Cover Next? | Audience chooses next month's content.</t>
         </is>
       </c>
-      <c r="I31" s="30" t="inlineStr">
+      <c r="J31" s="30" t="inlineStr">
         <is>
           <t>October is filler month. What do you want the truth about first: lips, cheeks, or under eyes? Vote. 👇
 #npinjector #nursepractitioner #medspalife #luxurybeauty #aestheticnurse #skincareexpert #beautyclinic #selfcare #naturalresults #honestbeauty</t>
         </is>
       </c>
-      <c r="J31" s="30" t="inlineStr">
+      <c r="K31" s="30" t="inlineStr">
         <is>
           <t>Vote in comments</t>
         </is>
       </c>
-      <c r="K31" s="30" t="inlineStr">
+      <c r="L31" s="30" t="inlineStr">
         <is>
           <t>Set C</t>
         </is>
       </c>
-      <c r="L31" s="30" t="inlineStr">
+      <c r="M31" s="30" t="inlineStr">
         <is>
           <t>Poll card + matching story poll</t>
         </is>
       </c>
-      <c r="M31" s="24" t="n"/>
       <c r="N31" s="24" t="n"/>
-      <c r="O31" s="34" t="inlineStr">
+      <c r="O31" s="24" t="n"/>
+      <c r="P31" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P31" s="24" t="inlineStr">
-        <is>
-          <t>Not designed yet</t>
-        </is>
-      </c>
-      <c r="Q31" s="24" t="n"/>
-      <c r="R31" s="30" t="inlineStr">
+      <c r="Q31" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="R31" s="24" t="n"/>
+      <c r="S31" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="S31" s="30" t="n"/>
       <c r="T31" s="30" t="n"/>
       <c r="U31" s="30" t="n"/>
       <c r="V31" s="30" t="n"/>
       <c r="W31" s="30" t="n"/>
       <c r="X31" s="30" t="n"/>
-      <c r="Y31" s="24" t="n"/>
+      <c r="Y31" s="30" t="n"/>
       <c r="Z31" s="24" t="n"/>
-      <c r="AA31" s="24" t="inlineStr">
+      <c r="AA31" s="24" t="n"/>
+      <c r="AB31" s="24" t="inlineStr">
         <is>
           <t>Not designed yet</t>
         </is>
@@ -4050,69 +4266,74 @@
           <t>Carousel</t>
         </is>
       </c>
-      <c r="F32" s="28" t="inlineStr">
+      <c r="F32" s="24" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G32" s="28" t="inlineStr">
         <is>
           <t>Instagram feed + GBP</t>
         </is>
       </c>
-      <c r="G32" s="28" t="inlineStr">
+      <c r="H32" s="28" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
       </c>
-      <c r="H32" s="28" t="inlineStr">
+      <c r="I32" s="28" t="inlineStr">
         <is>
           <t>How Long Does Botox Really Last? | The honest timeline, month by month.</t>
         </is>
       </c>
-      <c r="I32" s="28" t="inlineStr">
+      <c r="J32" s="28" t="inlineStr">
         <is>
           <t>Anyone promising six months is overpromising. Here is the real timeline, what makes it fade faster, and how to make results last longer.
 #botox #botoxeducation #botoxmyths #preventativebotox #antiwrinkleinjections #nurseinjector #medspa #naturalbotox #botoxbeforeandafter #aestheticnurse</t>
         </is>
       </c>
-      <c r="J32" s="28" t="inlineStr">
+      <c r="K32" s="28" t="inlineStr">
         <is>
           <t>Save this timeline</t>
         </is>
       </c>
-      <c r="K32" s="28" t="inlineStr">
+      <c r="L32" s="28" t="inlineStr">
         <is>
           <t>Set A</t>
         </is>
       </c>
-      <c r="L32" s="28" t="inlineStr">
+      <c r="M32" s="28" t="inlineStr">
         <is>
           <t>Design timeline layout in editorial template</t>
         </is>
       </c>
-      <c r="M32" s="24" t="n"/>
       <c r="N32" s="24" t="n"/>
-      <c r="O32" s="32" t="inlineStr">
+      <c r="O32" s="24" t="n"/>
+      <c r="P32" s="32" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P32" s="24" t="inlineStr">
-        <is>
-          <t>Not designed yet</t>
-        </is>
-      </c>
-      <c r="Q32" s="24" t="n"/>
-      <c r="R32" s="28" t="inlineStr">
+      <c r="Q32" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="R32" s="24" t="n"/>
+      <c r="S32" s="28" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="S32" s="28" t="n"/>
       <c r="T32" s="28" t="n"/>
       <c r="U32" s="28" t="n"/>
       <c r="V32" s="28" t="n"/>
       <c r="W32" s="28" t="n"/>
       <c r="X32" s="28" t="n"/>
-      <c r="Y32" s="24" t="n"/>
+      <c r="Y32" s="28" t="n"/>
       <c r="Z32" s="24" t="n"/>
-      <c r="AA32" s="24" t="inlineStr">
+      <c r="AA32" s="24" t="n"/>
+      <c r="AB32" s="24" t="inlineStr">
         <is>
           <t>Not designed yet</t>
         </is>
@@ -4140,69 +4361,74 @@
           <t>Single Image</t>
         </is>
       </c>
-      <c r="F33" s="30" t="inlineStr">
+      <c r="F33" s="24" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G33" s="30" t="inlineStr">
         <is>
           <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
-      <c r="G33" s="30" t="inlineStr">
+      <c r="H33" s="30" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
       </c>
-      <c r="H33" s="30" t="inlineStr">
+      <c r="I33" s="30" t="inlineStr">
         <is>
           <t>The 3-Month Botox Timeline | Week by week, what to expect.</t>
         </is>
       </c>
-      <c r="I33" s="30" t="inlineStr">
+      <c r="J33" s="30" t="inlineStr">
         <is>
           <t>Day 3 it starts. Week 2 it settles. Month 3 it softens. Save this so you know exactly what is normal.
 #botox #botoxeducation #botoxmyths #preventativebotox #antiwrinkleinjections #nurseinjector #medspa #naturalbotox #botoxbeforeandafter #aestheticnurse</t>
         </is>
       </c>
-      <c r="J33" s="30" t="inlineStr">
+      <c r="K33" s="30" t="inlineStr">
         <is>
           <t>Save this timeline</t>
         </is>
       </c>
-      <c r="K33" s="30" t="inlineStr">
+      <c r="L33" s="30" t="inlineStr">
         <is>
           <t>Set A</t>
         </is>
       </c>
-      <c r="L33" s="30" t="inlineStr">
+      <c r="M33" s="30" t="inlineStr">
         <is>
           <t>Single image: timeline infographic card</t>
         </is>
       </c>
-      <c r="M33" s="24" t="n"/>
       <c r="N33" s="24" t="n"/>
-      <c r="O33" s="34" t="inlineStr">
+      <c r="O33" s="24" t="n"/>
+      <c r="P33" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P33" s="24" t="inlineStr">
-        <is>
-          <t>Not designed yet</t>
-        </is>
-      </c>
-      <c r="Q33" s="24" t="n"/>
-      <c r="R33" s="30" t="inlineStr">
+      <c r="Q33" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="R33" s="24" t="n"/>
+      <c r="S33" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="S33" s="30" t="n"/>
       <c r="T33" s="30" t="n"/>
       <c r="U33" s="30" t="n"/>
       <c r="V33" s="30" t="n"/>
       <c r="W33" s="30" t="n"/>
       <c r="X33" s="30" t="n"/>
-      <c r="Y33" s="24" t="n"/>
+      <c r="Y33" s="30" t="n"/>
       <c r="Z33" s="24" t="n"/>
-      <c r="AA33" s="24" t="inlineStr">
+      <c r="AA33" s="24" t="n"/>
+      <c r="AB33" s="24" t="inlineStr">
         <is>
           <t>Not designed yet</t>
         </is>
@@ -4230,69 +4456,74 @@
           <t>Carousel</t>
         </is>
       </c>
-      <c r="F34" s="28" t="inlineStr">
+      <c r="F34" s="24" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G34" s="28" t="inlineStr">
         <is>
           <t>Instagram feed + GBP</t>
         </is>
       </c>
-      <c r="G34" s="28" t="inlineStr">
+      <c r="H34" s="28" t="inlineStr">
         <is>
           <t>Trust &amp; Proof</t>
         </is>
       </c>
-      <c r="H34" s="28" t="inlineStr">
+      <c r="I34" s="28" t="inlineStr">
         <is>
           <t>Why We Sometimes Say No | A provider who says yes to everyone is a red flag.</t>
         </is>
       </c>
-      <c r="I34" s="28" t="inlineStr">
+      <c r="J34" s="28" t="inlineStr">
         <is>
           <t>I have turned people away, and they thanked me later. Here is why honest candidacy matters and what it says about any provider who never says no.
 #npinjector #nursepractitioner #medspalife #luxurybeauty #aestheticnurse #skincareexpert #beautyclinic #selfcare #naturalresults #honestbeauty</t>
         </is>
       </c>
-      <c r="J34" s="28" t="inlineStr">
+      <c r="K34" s="28" t="inlineStr">
         <is>
           <t>Book an honest consult</t>
         </is>
       </c>
-      <c r="K34" s="28" t="inlineStr">
+      <c r="L34" s="28" t="inlineStr">
         <is>
           <t>Set C</t>
         </is>
       </c>
-      <c r="L34" s="28" t="inlineStr">
+      <c r="M34" s="28" t="inlineStr">
         <is>
           <t>Design in editorial template</t>
         </is>
       </c>
-      <c r="M34" s="24" t="n"/>
       <c r="N34" s="24" t="n"/>
-      <c r="O34" s="32" t="inlineStr">
+      <c r="O34" s="24" t="n"/>
+      <c r="P34" s="32" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P34" s="24" t="inlineStr">
-        <is>
-          <t>Not designed yet</t>
-        </is>
-      </c>
-      <c r="Q34" s="24" t="n"/>
-      <c r="R34" s="28" t="inlineStr">
+      <c r="Q34" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="R34" s="24" t="n"/>
+      <c r="S34" s="28" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="S34" s="28" t="n"/>
       <c r="T34" s="28" t="n"/>
       <c r="U34" s="28" t="n"/>
       <c r="V34" s="28" t="n"/>
       <c r="W34" s="28" t="n"/>
       <c r="X34" s="28" t="n"/>
-      <c r="Y34" s="24" t="n"/>
+      <c r="Y34" s="28" t="n"/>
       <c r="Z34" s="24" t="n"/>
-      <c r="AA34" s="24" t="inlineStr">
+      <c r="AA34" s="24" t="n"/>
+      <c r="AB34" s="24" t="inlineStr">
         <is>
           <t>Not designed yet</t>
         </is>
@@ -4320,69 +4551,74 @@
           <t>Single Image</t>
         </is>
       </c>
-      <c r="F35" s="30" t="inlineStr">
+      <c r="F35" s="24" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G35" s="30" t="inlineStr">
         <is>
           <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
-      <c r="G35" s="30" t="inlineStr">
+      <c r="H35" s="30" t="inlineStr">
         <is>
           <t>Trust &amp; Proof</t>
         </is>
       </c>
-      <c r="H35" s="30" t="inlineStr">
+      <c r="I35" s="30" t="inlineStr">
         <is>
           <t>What I Tell Every First-Timer | The pep talk before every first appointment.</t>
         </is>
       </c>
-      <c r="I35" s="30" t="inlineStr">
+      <c r="J35" s="30" t="inlineStr">
         <is>
           <t>You do not need to know the treatment names. You just need to show up honest about your goals. I handle the rest. 💛
 #npinjector #nursepractitioner #medspalife #luxurybeauty #aestheticnurse #skincareexpert #beautyclinic #selfcare #naturalresults #honestbeauty</t>
         </is>
       </c>
-      <c r="J35" s="30" t="inlineStr">
+      <c r="K35" s="30" t="inlineStr">
         <is>
           <t>Book your first visit</t>
         </is>
       </c>
-      <c r="K35" s="30" t="inlineStr">
+      <c r="L35" s="30" t="inlineStr">
         <is>
           <t>Set C</t>
         </is>
       </c>
-      <c r="L35" s="30" t="inlineStr">
+      <c r="M35" s="30" t="inlineStr">
         <is>
           <t>Single image: Cleo photo + quote overlay</t>
         </is>
       </c>
-      <c r="M35" s="24" t="n"/>
       <c r="N35" s="24" t="n"/>
-      <c r="O35" s="34" t="inlineStr">
+      <c r="O35" s="24" t="n"/>
+      <c r="P35" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P35" s="24" t="inlineStr">
-        <is>
-          <t>Not designed yet</t>
-        </is>
-      </c>
-      <c r="Q35" s="24" t="n"/>
-      <c r="R35" s="30" t="inlineStr">
+      <c r="Q35" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="R35" s="24" t="n"/>
+      <c r="S35" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="S35" s="30" t="n"/>
       <c r="T35" s="30" t="n"/>
       <c r="U35" s="30" t="n"/>
       <c r="V35" s="30" t="n"/>
       <c r="W35" s="30" t="n"/>
       <c r="X35" s="30" t="n"/>
-      <c r="Y35" s="24" t="n"/>
+      <c r="Y35" s="30" t="n"/>
       <c r="Z35" s="24" t="n"/>
-      <c r="AA35" s="24" t="inlineStr">
+      <c r="AA35" s="24" t="n"/>
+      <c r="AB35" s="24" t="inlineStr">
         <is>
           <t>Not designed yet</t>
         </is>
@@ -4410,69 +4646,74 @@
           <t>Single Image</t>
         </is>
       </c>
-      <c r="F36" s="30" t="inlineStr">
+      <c r="F36" s="24" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G36" s="30" t="inlineStr">
         <is>
           <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
-      <c r="G36" s="30" t="inlineStr">
+      <c r="H36" s="30" t="inlineStr">
         <is>
           <t>Trust &amp; Proof</t>
         </is>
       </c>
-      <c r="H36" s="30" t="inlineStr">
+      <c r="I36" s="30" t="inlineStr">
         <is>
           <t>Quote: No Is Protection | Brand quote card.</t>
         </is>
       </c>
-      <c r="I36" s="30" t="inlineStr">
+      <c r="J36" s="30" t="inlineStr">
         <is>
           <t>An honest provider will sometimes tell you no. That is protection, not rejection.
 #npinjector #nursepractitioner #medspalife #luxurybeauty #aestheticnurse #skincareexpert #beautyclinic #selfcare #naturalresults #honestbeauty</t>
         </is>
       </c>
-      <c r="J36" s="30" t="inlineStr">
+      <c r="K36" s="30" t="inlineStr">
         <is>
           <t>Share this</t>
         </is>
       </c>
-      <c r="K36" s="30" t="inlineStr">
+      <c r="L36" s="30" t="inlineStr">
         <is>
           <t>Set C</t>
         </is>
       </c>
-      <c r="L36" s="30" t="inlineStr">
+      <c r="M36" s="30" t="inlineStr">
         <is>
           <t>Quote card in brand style</t>
         </is>
       </c>
-      <c r="M36" s="24" t="n"/>
       <c r="N36" s="24" t="n"/>
-      <c r="O36" s="34" t="inlineStr">
+      <c r="O36" s="24" t="n"/>
+      <c r="P36" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P36" s="24" t="inlineStr">
-        <is>
-          <t>Not designed yet</t>
-        </is>
-      </c>
-      <c r="Q36" s="24" t="n"/>
-      <c r="R36" s="30" t="inlineStr">
+      <c r="Q36" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="R36" s="24" t="n"/>
+      <c r="S36" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="S36" s="30" t="n"/>
       <c r="T36" s="30" t="n"/>
       <c r="U36" s="30" t="n"/>
       <c r="V36" s="30" t="n"/>
       <c r="W36" s="30" t="n"/>
       <c r="X36" s="30" t="n"/>
-      <c r="Y36" s="24" t="n"/>
+      <c r="Y36" s="30" t="n"/>
       <c r="Z36" s="24" t="n"/>
-      <c r="AA36" s="24" t="inlineStr">
+      <c r="AA36" s="24" t="n"/>
+      <c r="AB36" s="24" t="inlineStr">
         <is>
           <t>Not designed yet</t>
         </is>
@@ -4500,69 +4741,74 @@
           <t>Carousel</t>
         </is>
       </c>
-      <c r="F37" s="28" t="inlineStr">
+      <c r="F37" s="24" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G37" s="28" t="inlineStr">
         <is>
           <t>Instagram feed + GBP</t>
         </is>
       </c>
-      <c r="G37" s="28" t="inlineStr">
+      <c r="H37" s="28" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
       </c>
-      <c r="H37" s="28" t="inlineStr">
+      <c r="I37" s="28" t="inlineStr">
         <is>
           <t>Filler Won't Make You Look Fake. Bad Technique Does. | The fear is real. The cause is not what you think.</t>
         </is>
       </c>
-      <c r="I37" s="28" t="inlineStr">
+      <c r="J37" s="28" t="inlineStr">
         <is>
           <t>Every overdone face you have seen came from heavy hands, not from filler itself. Great work is invisible. You have seen it a hundred times without knowing.
 #dermalfiller #lipfiller #cheekfiller #naturalfiller #facialbalancing #lipfillernatural #aestheticnurse #medspa #fillerjourney #lipgoals</t>
         </is>
       </c>
-      <c r="J37" s="28" t="inlineStr">
+      <c r="K37" s="28" t="inlineStr">
         <is>
           <t>DM FILLER for a consult</t>
         </is>
       </c>
-      <c r="K37" s="28" t="inlineStr">
+      <c r="L37" s="28" t="inlineStr">
         <is>
           <t>Set B</t>
         </is>
       </c>
-      <c r="L37" s="28" t="inlineStr">
+      <c r="M37" s="28" t="inlineStr">
         <is>
           <t>Design in editorial template. October filler month opener</t>
         </is>
       </c>
-      <c r="M37" s="24" t="n"/>
       <c r="N37" s="24" t="n"/>
-      <c r="O37" s="32" t="inlineStr">
+      <c r="O37" s="24" t="n"/>
+      <c r="P37" s="32" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P37" s="24" t="inlineStr">
-        <is>
-          <t>Not designed yet</t>
-        </is>
-      </c>
-      <c r="Q37" s="24" t="n"/>
-      <c r="R37" s="28" t="inlineStr">
+      <c r="Q37" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="R37" s="24" t="n"/>
+      <c r="S37" s="28" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="S37" s="28" t="n"/>
       <c r="T37" s="28" t="n"/>
       <c r="U37" s="28" t="n"/>
       <c r="V37" s="28" t="n"/>
       <c r="W37" s="28" t="n"/>
       <c r="X37" s="28" t="n"/>
-      <c r="Y37" s="24" t="n"/>
+      <c r="Y37" s="28" t="n"/>
       <c r="Z37" s="24" t="n"/>
-      <c r="AA37" s="24" t="inlineStr">
+      <c r="AA37" s="24" t="n"/>
+      <c r="AB37" s="24" t="inlineStr">
         <is>
           <t>Not designed yet</t>
         </is>
@@ -4590,69 +4836,74 @@
           <t>Single Image</t>
         </is>
       </c>
-      <c r="F38" s="30" t="inlineStr">
+      <c r="F38" s="24" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G38" s="30" t="inlineStr">
         <is>
           <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
-      <c r="G38" s="30" t="inlineStr">
+      <c r="H38" s="30" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
       </c>
-      <c r="H38" s="30" t="inlineStr">
+      <c r="I38" s="30" t="inlineStr">
         <is>
           <t>Service Spotlight: Dermal Filler | Volume where you lost it. Nowhere else.</t>
         </is>
       </c>
-      <c r="I38" s="30" t="inlineStr">
+      <c r="J38" s="30" t="inlineStr">
         <is>
           <t>Filler is not about changing your face. It is about restoring what time quietly took. October is filler month. 👀
 #dermalfiller #lipfiller #cheekfiller #naturalfiller #facialbalancing #lipfillernatural #aestheticnurse #medspa #fillerjourney #lipgoals</t>
         </is>
       </c>
-      <c r="J38" s="30" t="inlineStr">
+      <c r="K38" s="30" t="inlineStr">
         <is>
           <t>DM FILLER to start</t>
         </is>
       </c>
-      <c r="K38" s="30" t="inlineStr">
+      <c r="L38" s="30" t="inlineStr">
         <is>
           <t>Set B</t>
         </is>
       </c>
-      <c r="L38" s="30" t="inlineStr">
+      <c r="M38" s="30" t="inlineStr">
         <is>
           <t>Single image: filler product or treatment photo + hook</t>
         </is>
       </c>
-      <c r="M38" s="24" t="n"/>
       <c r="N38" s="24" t="n"/>
-      <c r="O38" s="34" t="inlineStr">
+      <c r="O38" s="24" t="n"/>
+      <c r="P38" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P38" s="24" t="inlineStr">
-        <is>
-          <t>Not designed yet</t>
-        </is>
-      </c>
-      <c r="Q38" s="24" t="n"/>
-      <c r="R38" s="30" t="inlineStr">
+      <c r="Q38" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="R38" s="24" t="n"/>
+      <c r="S38" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="S38" s="30" t="n"/>
       <c r="T38" s="30" t="n"/>
       <c r="U38" s="30" t="n"/>
       <c r="V38" s="30" t="n"/>
       <c r="W38" s="30" t="n"/>
       <c r="X38" s="30" t="n"/>
-      <c r="Y38" s="24" t="n"/>
+      <c r="Y38" s="30" t="n"/>
       <c r="Z38" s="24" t="n"/>
-      <c r="AA38" s="24" t="inlineStr">
+      <c r="AA38" s="24" t="n"/>
+      <c r="AB38" s="24" t="inlineStr">
         <is>
           <t>Not designed yet</t>
         </is>
@@ -4680,80 +4931,85 @@
           <t>Carousel</t>
         </is>
       </c>
-      <c r="F39" s="28" t="inlineStr">
+      <c r="F39" s="24" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G39" s="28" t="inlineStr">
         <is>
           <t>Instagram feed + GBP</t>
         </is>
       </c>
-      <c r="G39" s="28" t="inlineStr">
+      <c r="H39" s="28" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
       </c>
-      <c r="H39" s="28" t="inlineStr">
+      <c r="I39" s="28" t="inlineStr">
         <is>
           <t>Lip Filler: Natural vs Overdone | The difference is the injector.</t>
         </is>
       </c>
-      <c r="I39" s="28" t="inlineStr">
+      <c r="J39" s="28" t="inlineStr">
         <is>
           <t>Soft, balanced, still you. Here is what separates natural lip results from the duck lips everyone fears, and the questions to ask before anyone touches your lips.
 #dermalfiller #lipfiller #cheekfiller #naturalfiller #facialbalancing #lipfillernatural #aestheticnurse #medspa #fillerjourney #lipgoals</t>
         </is>
       </c>
-      <c r="J39" s="28" t="inlineStr">
+      <c r="K39" s="28" t="inlineStr">
         <is>
           <t>Save before you book anywhere</t>
         </is>
       </c>
-      <c r="K39" s="28" t="inlineStr">
+      <c r="L39" s="28" t="inlineStr">
         <is>
           <t>Set B</t>
         </is>
       </c>
-      <c r="L39" s="28" t="inlineStr">
+      <c r="M39" s="28" t="inlineStr">
         <is>
           <t>READY: before and after result card in this post's folder</t>
         </is>
       </c>
-      <c r="M39" s="24" t="inlineStr">
+      <c r="N39" s="24" t="inlineStr">
         <is>
           <t>img_9908 (before), img_9912 (after)</t>
         </is>
       </c>
-      <c r="N39" s="24" t="inlineStr">
+      <c r="O39" s="24" t="inlineStr">
         <is>
           <t>Not needed</t>
         </is>
       </c>
-      <c r="O39" s="32" t="inlineStr">
+      <c r="P39" s="32" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P39" s="33" t="inlineStr">
+      <c r="Q39" s="33" t="inlineStr">
         <is>
           <t>View image</t>
         </is>
       </c>
-      <c r="Q39" s="24">
+      <c r="R39" s="24">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-10-08-lip-filler-natural-vs-overdone/images/before-after-result.png")</f>
         <v/>
       </c>
-      <c r="R39" s="28" t="inlineStr">
+      <c r="S39" s="28" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="S39" s="28" t="n"/>
       <c r="T39" s="28" t="n"/>
       <c r="U39" s="28" t="n"/>
       <c r="V39" s="28" t="n"/>
       <c r="W39" s="28" t="n"/>
       <c r="X39" s="28" t="n"/>
-      <c r="Y39" s="24" t="n"/>
+      <c r="Y39" s="28" t="n"/>
       <c r="Z39" s="24" t="n"/>
-      <c r="AA39" s="24" t="inlineStr">
+      <c r="AA39" s="24" t="n"/>
+      <c r="AB39" s="24" t="inlineStr">
         <is>
           <t>Not designed yet</t>
         </is>
@@ -4781,69 +5037,74 @@
           <t>Single Image</t>
         </is>
       </c>
-      <c r="F40" s="30" t="inlineStr">
+      <c r="F40" s="24" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G40" s="30" t="inlineStr">
         <is>
           <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
-      <c r="G40" s="30" t="inlineStr">
+      <c r="H40" s="30" t="inlineStr">
         <is>
           <t>Personality &amp; BTS</t>
         </is>
       </c>
-      <c r="H40" s="30" t="inlineStr">
+      <c r="I40" s="30" t="inlineStr">
         <is>
           <t>Inside the Filler Appointment | Planned to the last drop.</t>
         </is>
       </c>
-      <c r="I40" s="30" t="inlineStr">
+      <c r="J40" s="30" t="inlineStr">
         <is>
           <t>Cannulas, numbing, and a plan drawn before we start. This is what careful looks like.
 #dermalfiller #lipfiller #cheekfiller #naturalfiller #facialbalancing #lipfillernatural #aestheticnurse #medspa #fillerjourney #lipgoals</t>
         </is>
       </c>
-      <c r="J40" s="30" t="inlineStr">
+      <c r="K40" s="30" t="inlineStr">
         <is>
           <t>Follow for filler month</t>
         </is>
       </c>
-      <c r="K40" s="30" t="inlineStr">
+      <c r="L40" s="30" t="inlineStr">
         <is>
           <t>Set B</t>
         </is>
       </c>
-      <c r="L40" s="30" t="inlineStr">
+      <c r="M40" s="30" t="inlineStr">
         <is>
           <t>Single image: filler prep photo + hook</t>
         </is>
       </c>
-      <c r="M40" s="24" t="n"/>
       <c r="N40" s="24" t="n"/>
-      <c r="O40" s="34" t="inlineStr">
+      <c r="O40" s="24" t="n"/>
+      <c r="P40" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P40" s="24" t="inlineStr">
-        <is>
-          <t>Not designed yet</t>
-        </is>
-      </c>
-      <c r="Q40" s="24" t="n"/>
-      <c r="R40" s="30" t="inlineStr">
+      <c r="Q40" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="R40" s="24" t="n"/>
+      <c r="S40" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="S40" s="30" t="n"/>
       <c r="T40" s="30" t="n"/>
       <c r="U40" s="30" t="n"/>
       <c r="V40" s="30" t="n"/>
       <c r="W40" s="30" t="n"/>
       <c r="X40" s="30" t="n"/>
-      <c r="Y40" s="24" t="n"/>
+      <c r="Y40" s="30" t="n"/>
       <c r="Z40" s="24" t="n"/>
-      <c r="AA40" s="24" t="inlineStr">
+      <c r="AA40" s="24" t="n"/>
+      <c r="AB40" s="24" t="inlineStr">
         <is>
           <t>Not designed yet</t>
         </is>
@@ -4871,80 +5132,85 @@
           <t>Before/After</t>
         </is>
       </c>
-      <c r="F41" s="30" t="inlineStr">
+      <c r="F41" s="24" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G41" s="30" t="inlineStr">
         <is>
           <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
-      <c r="G41" s="30" t="inlineStr">
+      <c r="H41" s="30" t="inlineStr">
         <is>
           <t>Trust &amp; Proof</t>
         </is>
       </c>
-      <c r="H41" s="30" t="inlineStr">
+      <c r="I41" s="30" t="inlineStr">
         <is>
           <t>Subtle Is the New Dramatic | The quote, proved.</t>
         </is>
       </c>
-      <c r="I41" s="30" t="inlineStr">
+      <c r="J41" s="30" t="inlineStr">
         <is>
           <t>Subtle is the new dramatic. The best work whispers. This is one syringe, healed and settled, on a client who did not want anyone to know. Individual results vary. Shared with consent. 💛
 #npinjector #nursepractitioner #medspalife #luxurybeauty #aestheticnurse #skincareexpert #beautyclinic #selfcare #naturalresults #honestbeauty</t>
         </is>
       </c>
-      <c r="J41" s="30" t="inlineStr">
+      <c r="K41" s="30" t="inlineStr">
         <is>
           <t>Save this</t>
         </is>
       </c>
-      <c r="K41" s="30" t="inlineStr">
+      <c r="L41" s="30" t="inlineStr">
         <is>
           <t>Set C</t>
         </is>
       </c>
-      <c r="L41" s="30" t="inlineStr">
+      <c r="M41" s="30" t="inlineStr">
         <is>
           <t>Before and after card in editorial template. Crop to treatment area, no faces</t>
         </is>
       </c>
-      <c r="M41" s="24" t="inlineStr">
+      <c r="N41" s="24" t="inlineStr">
         <is>
           <t>img_1119 (before), img_1123 (after)</t>
         </is>
       </c>
-      <c r="N41" s="24" t="inlineStr">
+      <c r="O41" s="24" t="inlineStr">
         <is>
           <t>On file</t>
         </is>
       </c>
-      <c r="O41" s="34" t="inlineStr">
+      <c r="P41" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P41" s="33" t="inlineStr">
+      <c r="Q41" s="33" t="inlineStr">
         <is>
           <t>View image</t>
         </is>
       </c>
-      <c r="Q41" s="24">
+      <c r="R41" s="24">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-10-10-subtle-is-the-new-dramatic/images/before-after-result.png")</f>
         <v/>
       </c>
-      <c r="R41" s="30" t="inlineStr">
+      <c r="S41" s="30" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="S41" s="30" t="n"/>
       <c r="T41" s="30" t="n"/>
       <c r="U41" s="30" t="n"/>
       <c r="V41" s="30" t="n"/>
       <c r="W41" s="30" t="n"/>
       <c r="X41" s="30" t="n"/>
-      <c r="Y41" s="24" t="n"/>
+      <c r="Y41" s="30" t="n"/>
       <c r="Z41" s="24" t="n"/>
-      <c r="AA41" s="24" t="inlineStr">
+      <c r="AA41" s="24" t="n"/>
+      <c r="AB41" s="24" t="inlineStr">
         <is>
           <t>Not designed yet</t>
         </is>
@@ -4972,69 +5238,74 @@
           <t>Carousel</t>
         </is>
       </c>
-      <c r="F42" s="28" t="inlineStr">
+      <c r="F42" s="24" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G42" s="28" t="inlineStr">
         <is>
           <t>Instagram feed + GBP</t>
         </is>
       </c>
-      <c r="G42" s="28" t="inlineStr">
+      <c r="H42" s="28" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
       </c>
-      <c r="H42" s="28" t="inlineStr">
+      <c r="I42" s="28" t="inlineStr">
         <is>
           <t>Cheek Filler: The Secret Nobody Talks About | The treatment behind the best natural glow-ups.</t>
         </is>
       </c>
-      <c r="I42" s="28" t="inlineStr">
+      <c r="J42" s="28" t="inlineStr">
         <is>
           <t>Everyone asks about lips. But cheek filler is quietly behind some of the most natural transformations you have seen. Here is how facial balancing works.
 #dermalfiller #lipfiller #cheekfiller #naturalfiller #facialbalancing #lipfillernatural #aestheticnurse #medspa #fillerjourney #lipgoals</t>
         </is>
       </c>
-      <c r="J42" s="28" t="inlineStr">
+      <c r="K42" s="28" t="inlineStr">
         <is>
           <t>DM CHEEKS to learn more</t>
         </is>
       </c>
-      <c r="K42" s="28" t="inlineStr">
+      <c r="L42" s="28" t="inlineStr">
         <is>
           <t>Set B</t>
         </is>
       </c>
-      <c r="L42" s="28" t="inlineStr">
+      <c r="M42" s="28" t="inlineStr">
         <is>
           <t>Design in editorial template</t>
         </is>
       </c>
-      <c r="M42" s="24" t="n"/>
       <c r="N42" s="24" t="n"/>
-      <c r="O42" s="32" t="inlineStr">
+      <c r="O42" s="24" t="n"/>
+      <c r="P42" s="32" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P42" s="24" t="inlineStr">
-        <is>
-          <t>Not designed yet</t>
-        </is>
-      </c>
-      <c r="Q42" s="24" t="n"/>
-      <c r="R42" s="28" t="inlineStr">
+      <c r="Q42" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="R42" s="24" t="n"/>
+      <c r="S42" s="28" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="S42" s="28" t="n"/>
       <c r="T42" s="28" t="n"/>
       <c r="U42" s="28" t="n"/>
       <c r="V42" s="28" t="n"/>
       <c r="W42" s="28" t="n"/>
       <c r="X42" s="28" t="n"/>
-      <c r="Y42" s="24" t="n"/>
+      <c r="Y42" s="28" t="n"/>
       <c r="Z42" s="24" t="n"/>
-      <c r="AA42" s="24" t="inlineStr">
+      <c r="AA42" s="24" t="n"/>
+      <c r="AB42" s="24" t="inlineStr">
         <is>
           <t>Not designed yet</t>
         </is>
@@ -5062,69 +5333,74 @@
           <t>Single Image</t>
         </is>
       </c>
-      <c r="F43" s="30" t="inlineStr">
+      <c r="F43" s="24" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G43" s="30" t="inlineStr">
         <is>
           <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
-      <c r="G43" s="30" t="inlineStr">
+      <c r="H43" s="30" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
       </c>
-      <c r="H43" s="30" t="inlineStr">
+      <c r="I43" s="30" t="inlineStr">
         <is>
           <t>Service Spotlight: Cheek Filler | The lift nobody talks about.</t>
         </is>
       </c>
-      <c r="I43" s="30" t="inlineStr">
+      <c r="J43" s="30" t="inlineStr">
         <is>
           <t>Lifted, refreshed, never puffy. Cheek filler is quietly behind the most natural glow-ups you have seen.
 #dermalfiller #lipfiller #cheekfiller #naturalfiller #facialbalancing #lipfillernatural #aestheticnurse #medspa #fillerjourney #lipgoals</t>
         </is>
       </c>
-      <c r="J43" s="30" t="inlineStr">
+      <c r="K43" s="30" t="inlineStr">
         <is>
           <t>DM CHEEKS to learn more</t>
         </is>
       </c>
-      <c r="K43" s="30" t="inlineStr">
+      <c r="L43" s="30" t="inlineStr">
         <is>
           <t>Set B</t>
         </is>
       </c>
-      <c r="L43" s="30" t="inlineStr">
+      <c r="M43" s="30" t="inlineStr">
         <is>
           <t>Single image: cheek treatment photo + hook</t>
         </is>
       </c>
-      <c r="M43" s="24" t="n"/>
       <c r="N43" s="24" t="n"/>
-      <c r="O43" s="34" t="inlineStr">
+      <c r="O43" s="24" t="n"/>
+      <c r="P43" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P43" s="24" t="inlineStr">
-        <is>
-          <t>Not designed yet</t>
-        </is>
-      </c>
-      <c r="Q43" s="24" t="n"/>
-      <c r="R43" s="30" t="inlineStr">
+      <c r="Q43" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="R43" s="24" t="n"/>
+      <c r="S43" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="S43" s="30" t="n"/>
       <c r="T43" s="30" t="n"/>
       <c r="U43" s="30" t="n"/>
       <c r="V43" s="30" t="n"/>
       <c r="W43" s="30" t="n"/>
       <c r="X43" s="30" t="n"/>
-      <c r="Y43" s="24" t="n"/>
+      <c r="Y43" s="30" t="n"/>
       <c r="Z43" s="24" t="n"/>
-      <c r="AA43" s="24" t="inlineStr">
+      <c r="AA43" s="24" t="n"/>
+      <c r="AB43" s="24" t="inlineStr">
         <is>
           <t>Not designed yet</t>
         </is>
@@ -5152,80 +5428,85 @@
           <t>Carousel</t>
         </is>
       </c>
-      <c r="F44" s="28" t="inlineStr">
+      <c r="F44" s="24" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G44" s="28" t="inlineStr">
         <is>
           <t>Instagram feed + GBP</t>
         </is>
       </c>
-      <c r="G44" s="28" t="inlineStr">
+      <c r="H44" s="28" t="inlineStr">
         <is>
           <t>Trust &amp; Proof</t>
         </is>
       </c>
-      <c r="H44" s="28" t="inlineStr">
+      <c r="I44" s="28" t="inlineStr">
         <is>
           <t>Real Lips. Real Results. | Four clients. One syringe each.</t>
         </is>
       </c>
-      <c r="I44" s="28" t="inlineStr">
+      <c r="J44" s="28" t="inlineStr">
         <is>
           <t>No filters, no angles, no tricks. Four real clients, one syringe each, photographed in the same light on the same day. Swipe to see what natural actually looks like. Individual results vary. All shared with consent.
 #dermalfiller #lipfiller #cheekfiller #naturalfiller #facialbalancing #lipfillernatural #aestheticnurse #medspa #fillerjourney #lipgoals</t>
         </is>
       </c>
-      <c r="J44" s="28" t="inlineStr">
+      <c r="K44" s="28" t="inlineStr">
         <is>
           <t>DM LIPS to book yours</t>
         </is>
       </c>
-      <c r="K44" s="28" t="inlineStr">
+      <c r="L44" s="28" t="inlineStr">
         <is>
           <t>Set B</t>
         </is>
       </c>
-      <c r="L44" s="28" t="inlineStr">
+      <c r="M44" s="28" t="inlineStr">
         <is>
           <t>Carousel: cover + 5 before and after slides + CTA. Crop to treatment area, no faces</t>
         </is>
       </c>
-      <c r="M44" s="24" t="inlineStr">
+      <c r="N44" s="24" t="inlineStr">
         <is>
           <t>Pairs: 9908/9912, 0221/0233, 0962/0998, 1119/1123, 9848/9850</t>
         </is>
       </c>
-      <c r="N44" s="24" t="inlineStr">
+      <c r="O44" s="24" t="inlineStr">
         <is>
           <t>On file</t>
         </is>
       </c>
-      <c r="O44" s="32" t="inlineStr">
+      <c r="P44" s="32" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P44" s="33" t="inlineStr">
+      <c r="Q44" s="33" t="inlineStr">
         <is>
           <t>View 7 slides</t>
         </is>
       </c>
-      <c r="Q44" s="24">
+      <c r="R44" s="24">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-10-15-real-lips-real-results/images/slide-1.png")</f>
         <v/>
       </c>
-      <c r="R44" s="28" t="inlineStr">
+      <c r="S44" s="28" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="S44" s="28" t="n"/>
       <c r="T44" s="28" t="n"/>
       <c r="U44" s="28" t="n"/>
       <c r="V44" s="28" t="n"/>
       <c r="W44" s="28" t="n"/>
       <c r="X44" s="28" t="n"/>
-      <c r="Y44" s="24" t="n"/>
+      <c r="Y44" s="28" t="n"/>
       <c r="Z44" s="24" t="n"/>
-      <c r="AA44" s="24" t="inlineStr">
+      <c r="AA44" s="24" t="n"/>
+      <c r="AB44" s="24" t="inlineStr">
         <is>
           <t>Not designed yet</t>
         </is>
@@ -5253,69 +5534,74 @@
           <t>Single Image</t>
         </is>
       </c>
-      <c r="F45" s="30" t="inlineStr">
+      <c r="F45" s="24" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G45" s="30" t="inlineStr">
         <is>
           <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
-      <c r="G45" s="30" t="inlineStr">
+      <c r="H45" s="30" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
       </c>
-      <c r="H45" s="30" t="inlineStr">
+      <c r="I45" s="30" t="inlineStr">
         <is>
           <t>Facial Balancing 101 | One plan beats three syringes.</t>
         </is>
       </c>
-      <c r="I45" s="30" t="inlineStr">
+      <c r="J45" s="30" t="inlineStr">
         <is>
           <t>One syringe in the right place beats three in the wrong ones. Balance first, volume second. Always.
 #dermalfiller #lipfiller #cheekfiller #naturalfiller #facialbalancing #lipfillernatural #aestheticnurse #medspa #fillerjourney #lipgoals</t>
         </is>
       </c>
-      <c r="J45" s="30" t="inlineStr">
+      <c r="K45" s="30" t="inlineStr">
         <is>
           <t>Book a balancing consult</t>
         </is>
       </c>
-      <c r="K45" s="30" t="inlineStr">
+      <c r="L45" s="30" t="inlineStr">
         <is>
           <t>Set B</t>
         </is>
       </c>
-      <c r="L45" s="30" t="inlineStr">
+      <c r="M45" s="30" t="inlineStr">
         <is>
           <t>Single image: face-map diagram card</t>
         </is>
       </c>
-      <c r="M45" s="24" t="n"/>
       <c r="N45" s="24" t="n"/>
-      <c r="O45" s="34" t="inlineStr">
+      <c r="O45" s="24" t="n"/>
+      <c r="P45" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P45" s="24" t="inlineStr">
-        <is>
-          <t>Not designed yet</t>
-        </is>
-      </c>
-      <c r="Q45" s="24" t="n"/>
-      <c r="R45" s="30" t="inlineStr">
+      <c r="Q45" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="R45" s="24" t="n"/>
+      <c r="S45" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="S45" s="30" t="n"/>
       <c r="T45" s="30" t="n"/>
       <c r="U45" s="30" t="n"/>
       <c r="V45" s="30" t="n"/>
       <c r="W45" s="30" t="n"/>
       <c r="X45" s="30" t="n"/>
-      <c r="Y45" s="24" t="n"/>
+      <c r="Y45" s="30" t="n"/>
       <c r="Z45" s="24" t="n"/>
-      <c r="AA45" s="24" t="inlineStr">
+      <c r="AA45" s="24" t="n"/>
+      <c r="AB45" s="24" t="inlineStr">
         <is>
           <t>Not designed yet</t>
         </is>
@@ -5343,69 +5629,74 @@
           <t>Single Image</t>
         </is>
       </c>
-      <c r="F46" s="30" t="inlineStr">
+      <c r="F46" s="24" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G46" s="30" t="inlineStr">
         <is>
           <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
-      <c r="G46" s="30" t="inlineStr">
+      <c r="H46" s="30" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
       </c>
-      <c r="H46" s="30" t="inlineStr">
+      <c r="I46" s="30" t="inlineStr">
         <is>
           <t>FAQ: How Much Filler Do I Need? | The honest answer.</t>
         </is>
       </c>
-      <c r="I46" s="30" t="inlineStr">
+      <c r="J46" s="30" t="inlineStr">
         <is>
           <t>Less than Instagram makes you think. Most natural results start with one syringe or less. Here is why.
 #npinjector #nursepractitioner #medspalife #luxurybeauty #aestheticnurse #skincareexpert #beautyclinic #selfcare #naturalresults #honestbeauty</t>
         </is>
       </c>
-      <c r="J46" s="30" t="inlineStr">
+      <c r="K46" s="30" t="inlineStr">
         <is>
           <t>More FAQs? DM me</t>
         </is>
       </c>
-      <c r="K46" s="30" t="inlineStr">
+      <c r="L46" s="30" t="inlineStr">
         <is>
           <t>Set C</t>
         </is>
       </c>
-      <c r="L46" s="30" t="inlineStr">
+      <c r="M46" s="30" t="inlineStr">
         <is>
           <t>FAQ card in brand style</t>
         </is>
       </c>
-      <c r="M46" s="24" t="n"/>
       <c r="N46" s="24" t="n"/>
-      <c r="O46" s="34" t="inlineStr">
+      <c r="O46" s="24" t="n"/>
+      <c r="P46" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P46" s="24" t="inlineStr">
-        <is>
-          <t>Not designed yet</t>
-        </is>
-      </c>
-      <c r="Q46" s="24" t="n"/>
-      <c r="R46" s="30" t="inlineStr">
+      <c r="Q46" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="R46" s="24" t="n"/>
+      <c r="S46" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="S46" s="30" t="n"/>
       <c r="T46" s="30" t="n"/>
       <c r="U46" s="30" t="n"/>
       <c r="V46" s="30" t="n"/>
       <c r="W46" s="30" t="n"/>
       <c r="X46" s="30" t="n"/>
-      <c r="Y46" s="24" t="n"/>
+      <c r="Y46" s="30" t="n"/>
       <c r="Z46" s="24" t="n"/>
-      <c r="AA46" s="24" t="inlineStr">
+      <c r="AA46" s="24" t="n"/>
+      <c r="AB46" s="24" t="inlineStr">
         <is>
           <t>Not designed yet</t>
         </is>
@@ -5433,69 +5724,74 @@
           <t>Carousel</t>
         </is>
       </c>
-      <c r="F47" s="28" t="inlineStr">
+      <c r="F47" s="24" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G47" s="28" t="inlineStr">
         <is>
           <t>Instagram feed + GBP</t>
         </is>
       </c>
-      <c r="G47" s="28" t="inlineStr">
+      <c r="H47" s="28" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
       </c>
-      <c r="H47" s="28" t="inlineStr">
+      <c r="I47" s="28" t="inlineStr">
         <is>
           <t>Filler Dissolves. Here Is the Real Timeline. | What they do not tell you about longevity.</t>
         </is>
       </c>
-      <c r="I47" s="28" t="inlineStr">
+      <c r="J47" s="28" t="inlineStr">
         <is>
           <t>Filler is not forever, and honestly, that is a good thing. Here is how long each area really lasts and what keeping it up actually looks like.
 #dermalfiller #lipfiller #cheekfiller #naturalfiller #facialbalancing #lipfillernatural #aestheticnurse #medspa #fillerjourney #lipgoals</t>
         </is>
       </c>
-      <c r="J47" s="28" t="inlineStr">
+      <c r="K47" s="28" t="inlineStr">
         <is>
           <t>Book your plan. Link in bio</t>
         </is>
       </c>
-      <c r="K47" s="28" t="inlineStr">
+      <c r="L47" s="28" t="inlineStr">
         <is>
           <t>Set B</t>
         </is>
       </c>
-      <c r="L47" s="28" t="inlineStr">
+      <c r="M47" s="28" t="inlineStr">
         <is>
           <t>Design timeline layout</t>
         </is>
       </c>
-      <c r="M47" s="24" t="n"/>
       <c r="N47" s="24" t="n"/>
-      <c r="O47" s="32" t="inlineStr">
+      <c r="O47" s="24" t="n"/>
+      <c r="P47" s="32" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P47" s="24" t="inlineStr">
-        <is>
-          <t>Not designed yet</t>
-        </is>
-      </c>
-      <c r="Q47" s="24" t="n"/>
-      <c r="R47" s="28" t="inlineStr">
+      <c r="Q47" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="R47" s="24" t="n"/>
+      <c r="S47" s="28" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="S47" s="28" t="n"/>
       <c r="T47" s="28" t="n"/>
       <c r="U47" s="28" t="n"/>
       <c r="V47" s="28" t="n"/>
       <c r="W47" s="28" t="n"/>
       <c r="X47" s="28" t="n"/>
-      <c r="Y47" s="24" t="n"/>
+      <c r="Y47" s="28" t="n"/>
       <c r="Z47" s="24" t="n"/>
-      <c r="AA47" s="24" t="inlineStr">
+      <c r="AA47" s="24" t="n"/>
+      <c r="AB47" s="24" t="inlineStr">
         <is>
           <t>Not designed yet</t>
         </is>
@@ -5523,69 +5819,74 @@
           <t>Single Image</t>
         </is>
       </c>
-      <c r="F48" s="30" t="inlineStr">
+      <c r="F48" s="24" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G48" s="30" t="inlineStr">
         <is>
           <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
-      <c r="G48" s="30" t="inlineStr">
+      <c r="H48" s="30" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
       </c>
-      <c r="H48" s="30" t="inlineStr">
+      <c r="I48" s="30" t="inlineStr">
         <is>
           <t>The Filler Timeline | What happens as it fades.</t>
         </is>
       </c>
-      <c r="I48" s="30" t="inlineStr">
+      <c r="J48" s="30" t="inlineStr">
         <is>
           <t>Filler does not vanish overnight and you will not deflate. It softens slowly, on a schedule you can plan around.
 #dermalfiller #lipfiller #cheekfiller #naturalfiller #facialbalancing #lipfillernatural #aestheticnurse #medspa #fillerjourney #lipgoals</t>
         </is>
       </c>
-      <c r="J48" s="30" t="inlineStr">
+      <c r="K48" s="30" t="inlineStr">
         <is>
           <t>Save this</t>
         </is>
       </c>
-      <c r="K48" s="30" t="inlineStr">
+      <c r="L48" s="30" t="inlineStr">
         <is>
           <t>Set B</t>
         </is>
       </c>
-      <c r="L48" s="30" t="inlineStr">
+      <c r="M48" s="30" t="inlineStr">
         <is>
           <t>Single image: timeline infographic card</t>
         </is>
       </c>
-      <c r="M48" s="24" t="n"/>
       <c r="N48" s="24" t="n"/>
-      <c r="O48" s="34" t="inlineStr">
+      <c r="O48" s="24" t="n"/>
+      <c r="P48" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P48" s="24" t="inlineStr">
-        <is>
-          <t>Not designed yet</t>
-        </is>
-      </c>
-      <c r="Q48" s="24" t="n"/>
-      <c r="R48" s="30" t="inlineStr">
+      <c r="Q48" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="R48" s="24" t="n"/>
+      <c r="S48" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="S48" s="30" t="n"/>
       <c r="T48" s="30" t="n"/>
       <c r="U48" s="30" t="n"/>
       <c r="V48" s="30" t="n"/>
       <c r="W48" s="30" t="n"/>
       <c r="X48" s="30" t="n"/>
-      <c r="Y48" s="24" t="n"/>
+      <c r="Y48" s="30" t="n"/>
       <c r="Z48" s="24" t="n"/>
-      <c r="AA48" s="24" t="inlineStr">
+      <c r="AA48" s="24" t="n"/>
+      <c r="AB48" s="24" t="inlineStr">
         <is>
           <t>Not designed yet</t>
         </is>
@@ -5613,80 +5914,85 @@
           <t>Carousel</t>
         </is>
       </c>
-      <c r="F49" s="28" t="inlineStr">
+      <c r="F49" s="24" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G49" s="28" t="inlineStr">
         <is>
           <t>Instagram feed + GBP</t>
         </is>
       </c>
-      <c r="G49" s="28" t="inlineStr">
+      <c r="H49" s="28" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
       </c>
-      <c r="H49" s="28" t="inlineStr">
+      <c r="I49" s="28" t="inlineStr">
         <is>
           <t>Lip Filler Aftercare: Your First Week | Swelling is normal. Panic is optional.</t>
         </is>
       </c>
-      <c r="I49" s="28" t="inlineStr">
+      <c r="J49" s="28" t="inlineStr">
         <is>
           <t>Day 1 looks different from day 7. Here is the honest day-by-day so you know exactly what is normal and when to reach out. Save this before your appointment.
 #dermalfiller #lipfiller #cheekfiller #naturalfiller #facialbalancing #lipfillernatural #aestheticnurse #medspa #fillerjourney #lipgoals</t>
         </is>
       </c>
-      <c r="J49" s="28" t="inlineStr">
+      <c r="K49" s="28" t="inlineStr">
         <is>
           <t>Save this guide</t>
         </is>
       </c>
-      <c r="K49" s="28" t="inlineStr">
+      <c r="L49" s="28" t="inlineStr">
         <is>
           <t>Set B</t>
         </is>
       </c>
-      <c r="L49" s="28" t="inlineStr">
+      <c r="M49" s="28" t="inlineStr">
         <is>
           <t>Carousel: day by day. Day zero card built from the img_9848 / img_9850 pair. Crop to treatment area, no faces</t>
         </is>
       </c>
-      <c r="M49" s="24" t="inlineStr">
+      <c r="N49" s="24" t="inlineStr">
         <is>
           <t>img_9848 (before) + img_9850 (right after); img_7715, whatsapp composite</t>
         </is>
       </c>
-      <c r="N49" s="24" t="inlineStr">
+      <c r="O49" s="24" t="inlineStr">
         <is>
           <t>On file</t>
         </is>
       </c>
-      <c r="O49" s="32" t="inlineStr">
+      <c r="P49" s="32" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P49" s="33" t="inlineStr">
+      <c r="Q49" s="33" t="inlineStr">
         <is>
           <t>View image</t>
         </is>
       </c>
-      <c r="Q49" s="24">
+      <c r="R49" s="24">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-10-22-lip-filler-aftercare-your-first/images/day-zero-before-after.png")</f>
         <v/>
       </c>
-      <c r="R49" s="28" t="inlineStr">
+      <c r="S49" s="28" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="S49" s="28" t="n"/>
       <c r="T49" s="28" t="n"/>
       <c r="U49" s="28" t="n"/>
       <c r="V49" s="28" t="n"/>
       <c r="W49" s="28" t="n"/>
       <c r="X49" s="28" t="n"/>
-      <c r="Y49" s="24" t="n"/>
+      <c r="Y49" s="28" t="n"/>
       <c r="Z49" s="24" t="n"/>
-      <c r="AA49" s="24" t="inlineStr">
+      <c r="AA49" s="24" t="n"/>
+      <c r="AB49" s="24" t="inlineStr">
         <is>
           <t>Not designed yet</t>
         </is>
@@ -5714,69 +6020,74 @@
           <t>Single Image</t>
         </is>
       </c>
-      <c r="F50" s="30" t="inlineStr">
+      <c r="F50" s="24" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G50" s="30" t="inlineStr">
         <is>
           <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
-      <c r="G50" s="30" t="inlineStr">
+      <c r="H50" s="30" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
       </c>
-      <c r="H50" s="30" t="inlineStr">
+      <c r="I50" s="30" t="inlineStr">
         <is>
           <t>Aftercare Essentials | Save this for after your appointment.</t>
         </is>
       </c>
-      <c r="I50" s="30" t="inlineStr">
+      <c r="J50" s="30" t="inlineStr">
         <is>
           <t>Ice, no gym for 24 hours, sleep on your back, and message me with anything. That is it. Save this.
 #dermalfiller #lipfiller #cheekfiller #naturalfiller #facialbalancing #lipfillernatural #aestheticnurse #medspa #fillerjourney #lipgoals</t>
         </is>
       </c>
-      <c r="J50" s="30" t="inlineStr">
+      <c r="K50" s="30" t="inlineStr">
         <is>
           <t>Save + share</t>
         </is>
       </c>
-      <c r="K50" s="30" t="inlineStr">
+      <c r="L50" s="30" t="inlineStr">
         <is>
           <t>Set B</t>
         </is>
       </c>
-      <c r="L50" s="30" t="inlineStr">
+      <c r="M50" s="30" t="inlineStr">
         <is>
           <t>Single image: 4-point checklist card</t>
         </is>
       </c>
-      <c r="M50" s="24" t="n"/>
       <c r="N50" s="24" t="n"/>
-      <c r="O50" s="34" t="inlineStr">
+      <c r="O50" s="24" t="n"/>
+      <c r="P50" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P50" s="24" t="inlineStr">
-        <is>
-          <t>Not designed yet</t>
-        </is>
-      </c>
-      <c r="Q50" s="24" t="n"/>
-      <c r="R50" s="30" t="inlineStr">
+      <c r="Q50" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="R50" s="24" t="n"/>
+      <c r="S50" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="S50" s="30" t="n"/>
       <c r="T50" s="30" t="n"/>
       <c r="U50" s="30" t="n"/>
       <c r="V50" s="30" t="n"/>
       <c r="W50" s="30" t="n"/>
       <c r="X50" s="30" t="n"/>
-      <c r="Y50" s="24" t="n"/>
+      <c r="Y50" s="30" t="n"/>
       <c r="Z50" s="24" t="n"/>
-      <c r="AA50" s="24" t="inlineStr">
+      <c r="AA50" s="24" t="n"/>
+      <c r="AB50" s="24" t="inlineStr">
         <is>
           <t>Not designed yet</t>
         </is>
@@ -5804,80 +6115,85 @@
           <t>Before/After</t>
         </is>
       </c>
-      <c r="F51" s="30" t="inlineStr">
+      <c r="F51" s="24" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G51" s="30" t="inlineStr">
         <is>
           <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
-      <c r="G51" s="30" t="inlineStr">
+      <c r="H51" s="30" t="inlineStr">
         <is>
           <t>Trust &amp; Proof</t>
         </is>
       </c>
-      <c r="H51" s="30" t="inlineStr">
+      <c r="I51" s="30" t="inlineStr">
         <is>
           <t>Client Words: The Lip Glow-Up | Her words, her result.</t>
         </is>
       </c>
-      <c r="I51" s="30" t="inlineStr">
+      <c r="J51" s="30" t="inlineStr">
         <is>
           <t>I finally got my lips done and nobody said filler. They said I looked prettier and could not say why. Here is the result she is talking about. Individual results vary. Shared with permission. 💛
 #npinjector #nursepractitioner #medspalife #luxurybeauty #aestheticnurse #skincareexpert #beautyclinic #selfcare #naturalresults #honestbeauty</t>
         </is>
       </c>
-      <c r="J51" s="30" t="inlineStr">
+      <c r="K51" s="30" t="inlineStr">
         <is>
           <t>Your turn. DM FILLER</t>
         </is>
       </c>
-      <c r="K51" s="30" t="inlineStr">
+      <c r="L51" s="30" t="inlineStr">
         <is>
           <t>Set C</t>
         </is>
       </c>
-      <c r="L51" s="30" t="inlineStr">
+      <c r="M51" s="30" t="inlineStr">
         <is>
           <t>Testimonial quote over before and after card. Crop to treatment area, no faces</t>
         </is>
       </c>
-      <c r="M51" s="24" t="inlineStr">
+      <c r="N51" s="24" t="inlineStr">
         <is>
           <t>img_0962 (before), img_0998 (after)</t>
         </is>
       </c>
-      <c r="N51" s="24" t="inlineStr">
+      <c r="O51" s="24" t="inlineStr">
         <is>
           <t>On file</t>
         </is>
       </c>
-      <c r="O51" s="34" t="inlineStr">
+      <c r="P51" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P51" s="33" t="inlineStr">
+      <c r="Q51" s="33" t="inlineStr">
         <is>
           <t>View image</t>
         </is>
       </c>
-      <c r="Q51" s="24">
+      <c r="R51" s="24">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-10-24-client-words-the-lip-glow/images/before-after-result.png")</f>
         <v/>
       </c>
-      <c r="R51" s="30" t="inlineStr">
+      <c r="S51" s="30" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="S51" s="30" t="n"/>
       <c r="T51" s="30" t="n"/>
       <c r="U51" s="30" t="n"/>
       <c r="V51" s="30" t="n"/>
       <c r="W51" s="30" t="n"/>
       <c r="X51" s="30" t="n"/>
-      <c r="Y51" s="24" t="n"/>
+      <c r="Y51" s="30" t="n"/>
       <c r="Z51" s="24" t="n"/>
-      <c r="AA51" s="24" t="inlineStr">
+      <c r="AA51" s="24" t="n"/>
+      <c r="AB51" s="24" t="inlineStr">
         <is>
           <t>Not designed yet</t>
         </is>
@@ -5905,69 +6221,74 @@
           <t>Carousel</t>
         </is>
       </c>
-      <c r="F52" s="28" t="inlineStr">
+      <c r="F52" s="24" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G52" s="28" t="inlineStr">
         <is>
           <t>Instagram feed + GBP</t>
         </is>
       </c>
-      <c r="G52" s="28" t="inlineStr">
+      <c r="H52" s="28" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
       </c>
-      <c r="H52" s="28" t="inlineStr">
+      <c r="I52" s="28" t="inlineStr">
         <is>
           <t>5 Filler Lies You Still Believe | The sequel you asked for.</t>
         </is>
       </c>
-      <c r="I52" s="28" t="inlineStr">
+      <c r="J52" s="28" t="inlineStr">
         <is>
           <t>You loved the Botox edition, so here is the filler truth round. Slide 4 is the one that surprises everyone. Share it with your group chat.
 #dermalfiller #lipfiller #cheekfiller #naturalfiller #facialbalancing #lipfillernatural #aestheticnurse #medspa #fillerjourney #lipgoals</t>
         </is>
       </c>
-      <c r="J52" s="28" t="inlineStr">
+      <c r="K52" s="28" t="inlineStr">
         <is>
           <t>Share with a friend</t>
         </is>
       </c>
-      <c r="K52" s="28" t="inlineStr">
+      <c r="L52" s="28" t="inlineStr">
         <is>
           <t>Set B</t>
         </is>
       </c>
-      <c r="L52" s="28" t="inlineStr">
+      <c r="M52" s="28" t="inlineStr">
         <is>
           <t>Design in editorial template. Sequel to Botox lies</t>
         </is>
       </c>
-      <c r="M52" s="24" t="n"/>
       <c r="N52" s="24" t="n"/>
-      <c r="O52" s="32" t="inlineStr">
+      <c r="O52" s="24" t="n"/>
+      <c r="P52" s="32" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P52" s="24" t="inlineStr">
-        <is>
-          <t>Not designed yet</t>
-        </is>
-      </c>
-      <c r="Q52" s="24" t="n"/>
-      <c r="R52" s="28" t="inlineStr">
+      <c r="Q52" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="R52" s="24" t="n"/>
+      <c r="S52" s="28" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="S52" s="28" t="n"/>
       <c r="T52" s="28" t="n"/>
       <c r="U52" s="28" t="n"/>
       <c r="V52" s="28" t="n"/>
       <c r="W52" s="28" t="n"/>
       <c r="X52" s="28" t="n"/>
-      <c r="Y52" s="24" t="n"/>
+      <c r="Y52" s="28" t="n"/>
       <c r="Z52" s="24" t="n"/>
-      <c r="AA52" s="24" t="inlineStr">
+      <c r="AA52" s="24" t="n"/>
+      <c r="AB52" s="24" t="inlineStr">
         <is>
           <t>Not designed yet</t>
         </is>
@@ -5995,69 +6316,74 @@
           <t>Single Image</t>
         </is>
       </c>
-      <c r="F53" s="30" t="inlineStr">
+      <c r="F53" s="24" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G53" s="30" t="inlineStr">
         <is>
           <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
-      <c r="G53" s="30" t="inlineStr">
+      <c r="H53" s="30" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
       </c>
-      <c r="H53" s="30" t="inlineStr">
+      <c r="I53" s="30" t="inlineStr">
         <is>
           <t>Myth vs Truth: Filler Edition | The one everyone believes.</t>
         </is>
       </c>
-      <c r="I53" s="30" t="inlineStr">
+      <c r="J53" s="30" t="inlineStr">
         <is>
           <t>MYTH: filler stretches your lips forever. TRUTH: treated well, your lips return to baseline as filler softens.
 #dermalfiller #lipfiller #cheekfiller #naturalfiller #facialbalancing #lipfillernatural #aestheticnurse #medspa #fillerjourney #lipgoals</t>
         </is>
       </c>
-      <c r="J53" s="30" t="inlineStr">
+      <c r="K53" s="30" t="inlineStr">
         <is>
           <t>Full carousel on our feed</t>
         </is>
       </c>
-      <c r="K53" s="30" t="inlineStr">
+      <c r="L53" s="30" t="inlineStr">
         <is>
           <t>Set B</t>
         </is>
       </c>
-      <c r="L53" s="30" t="inlineStr">
+      <c r="M53" s="30" t="inlineStr">
         <is>
           <t>Single image: myth vs truth split card</t>
         </is>
       </c>
-      <c r="M53" s="24" t="n"/>
       <c r="N53" s="24" t="n"/>
-      <c r="O53" s="34" t="inlineStr">
+      <c r="O53" s="24" t="n"/>
+      <c r="P53" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P53" s="24" t="inlineStr">
-        <is>
-          <t>Not designed yet</t>
-        </is>
-      </c>
-      <c r="Q53" s="24" t="n"/>
-      <c r="R53" s="30" t="inlineStr">
+      <c r="Q53" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="R53" s="24" t="n"/>
+      <c r="S53" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="S53" s="30" t="n"/>
       <c r="T53" s="30" t="n"/>
       <c r="U53" s="30" t="n"/>
       <c r="V53" s="30" t="n"/>
       <c r="W53" s="30" t="n"/>
       <c r="X53" s="30" t="n"/>
-      <c r="Y53" s="24" t="n"/>
+      <c r="Y53" s="30" t="n"/>
       <c r="Z53" s="24" t="n"/>
-      <c r="AA53" s="24" t="inlineStr">
+      <c r="AA53" s="24" t="n"/>
+      <c r="AB53" s="24" t="inlineStr">
         <is>
           <t>Not designed yet</t>
         </is>
@@ -6085,69 +6411,74 @@
           <t>Carousel</t>
         </is>
       </c>
-      <c r="F54" s="28" t="inlineStr">
+      <c r="F54" s="24" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G54" s="28" t="inlineStr">
         <is>
           <t>Instagram feed + GBP</t>
         </is>
       </c>
-      <c r="G54" s="28" t="inlineStr">
+      <c r="H54" s="28" t="inlineStr">
         <is>
           <t>Trust &amp; Proof</t>
         </is>
       </c>
-      <c r="H54" s="28" t="inlineStr">
+      <c r="I54" s="28" t="inlineStr">
         <is>
           <t>Facial Balancing: Why We Treat Faces, Not Lines | Chasing lines is old school.</t>
         </is>
       </c>
-      <c r="I54" s="28" t="inlineStr">
+      <c r="J54" s="28" t="inlineStr">
         <is>
           <t>Great aesthetics looks at the whole face: proportions, balance, harmony. Here is why the best results come from a plan, not a single syringe.
 #dermalfiller #lipfiller #cheekfiller #naturalfiller #facialbalancing #lipfillernatural #aestheticnurse #medspa #fillerjourney #lipgoals</t>
         </is>
       </c>
-      <c r="J54" s="28" t="inlineStr">
+      <c r="K54" s="28" t="inlineStr">
         <is>
           <t>DM BALANCE for a consult</t>
         </is>
       </c>
-      <c r="K54" s="28" t="inlineStr">
+      <c r="L54" s="28" t="inlineStr">
         <is>
           <t>Set B</t>
         </is>
       </c>
-      <c r="L54" s="28" t="inlineStr">
+      <c r="M54" s="28" t="inlineStr">
         <is>
           <t>Design in editorial template</t>
         </is>
       </c>
-      <c r="M54" s="24" t="n"/>
       <c r="N54" s="24" t="n"/>
-      <c r="O54" s="32" t="inlineStr">
+      <c r="O54" s="24" t="n"/>
+      <c r="P54" s="32" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P54" s="24" t="inlineStr">
-        <is>
-          <t>Not designed yet</t>
-        </is>
-      </c>
-      <c r="Q54" s="24" t="n"/>
-      <c r="R54" s="28" t="inlineStr">
+      <c r="Q54" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="R54" s="24" t="n"/>
+      <c r="S54" s="28" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="S54" s="28" t="n"/>
       <c r="T54" s="28" t="n"/>
       <c r="U54" s="28" t="n"/>
       <c r="V54" s="28" t="n"/>
       <c r="W54" s="28" t="n"/>
       <c r="X54" s="28" t="n"/>
-      <c r="Y54" s="24" t="n"/>
+      <c r="Y54" s="28" t="n"/>
       <c r="Z54" s="24" t="n"/>
-      <c r="AA54" s="24" t="inlineStr">
+      <c r="AA54" s="24" t="n"/>
+      <c r="AB54" s="24" t="inlineStr">
         <is>
           <t>Not designed yet</t>
         </is>
@@ -6175,80 +6506,85 @@
           <t>Before/After</t>
         </is>
       </c>
-      <c r="F55" s="30" t="inlineStr">
+      <c r="F55" s="24" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G55" s="30" t="inlineStr">
         <is>
           <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
-      <c r="G55" s="30" t="inlineStr">
+      <c r="H55" s="30" t="inlineStr">
         <is>
           <t>Trust &amp; Proof</t>
         </is>
       </c>
-      <c r="H55" s="30" t="inlineStr">
+      <c r="I55" s="30" t="inlineStr">
         <is>
           <t>One Syringe. Balanced Lips. | Faces, not lines.</t>
         </is>
       </c>
-      <c r="I55" s="30" t="inlineStr">
+      <c r="J55" s="30" t="inlineStr">
         <is>
           <t>Chasing individual lines is old school. Balance is why my clients look rested instead of done. One syringe, placed where her lip actually needed it. Individual results vary. Shared with consent.
 #dermalfiller #lipfiller #cheekfiller #naturalfiller #facialbalancing #lipfillernatural #aestheticnurse #medspa #fillerjourney #lipgoals</t>
         </is>
       </c>
-      <c r="J55" s="30" t="inlineStr">
+      <c r="K55" s="30" t="inlineStr">
         <is>
           <t>Book a consult. Link in bio</t>
         </is>
       </c>
-      <c r="K55" s="30" t="inlineStr">
+      <c r="L55" s="30" t="inlineStr">
         <is>
           <t>Set B</t>
         </is>
       </c>
-      <c r="L55" s="30" t="inlineStr">
+      <c r="M55" s="30" t="inlineStr">
         <is>
           <t>Before and after card in editorial template. Crop to treatment area, no faces</t>
         </is>
       </c>
-      <c r="M55" s="24" t="inlineStr">
+      <c r="N55" s="24" t="inlineStr">
         <is>
           <t>img_0221 (before), img_0233 (after)</t>
         </is>
       </c>
-      <c r="N55" s="24" t="inlineStr">
+      <c r="O55" s="24" t="inlineStr">
         <is>
           <t>On file</t>
         </is>
       </c>
-      <c r="O55" s="34" t="inlineStr">
+      <c r="P55" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P55" s="33" t="inlineStr">
+      <c r="Q55" s="33" t="inlineStr">
         <is>
           <t>View image</t>
         </is>
       </c>
-      <c r="Q55" s="24">
+      <c r="R55" s="24">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-10-30-one-syringe-balanced-lips/images/before-after-result.png")</f>
         <v/>
       </c>
-      <c r="R55" s="30" t="inlineStr">
+      <c r="S55" s="30" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="S55" s="30" t="n"/>
       <c r="T55" s="30" t="n"/>
       <c r="U55" s="30" t="n"/>
       <c r="V55" s="30" t="n"/>
       <c r="W55" s="30" t="n"/>
       <c r="X55" s="30" t="n"/>
-      <c r="Y55" s="24" t="n"/>
+      <c r="Y55" s="30" t="n"/>
       <c r="Z55" s="24" t="n"/>
-      <c r="AA55" s="24" t="inlineStr">
+      <c r="AA55" s="24" t="n"/>
+      <c r="AB55" s="24" t="inlineStr">
         <is>
           <t>Not designed yet</t>
         </is>
@@ -6276,69 +6612,74 @@
           <t>Single Image</t>
         </is>
       </c>
-      <c r="F56" s="30" t="inlineStr">
+      <c r="F56" s="24" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G56" s="30" t="inlineStr">
         <is>
           <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
-      <c r="G56" s="30" t="inlineStr">
+      <c r="H56" s="30" t="inlineStr">
         <is>
           <t>Personality &amp; BTS</t>
         </is>
       </c>
-      <c r="H56" s="30" t="inlineStr">
+      <c r="I56" s="30" t="inlineStr">
         <is>
           <t>Ask Anything: Filler Edition | Engagement post.</t>
         </is>
       </c>
-      <c r="I56" s="30" t="inlineStr">
+      <c r="J56" s="30" t="inlineStr">
         <is>
           <t>Filler month is almost over. Drop every remaining question below and I will answer all of them. No judgment. 👇
 #npinjector #nursepractitioner #medspalife #luxurybeauty #aestheticnurse #skincareexpert #beautyclinic #selfcare #naturalresults #honestbeauty</t>
         </is>
       </c>
-      <c r="J56" s="30" t="inlineStr">
+      <c r="K56" s="30" t="inlineStr">
         <is>
           <t>Comment your question</t>
         </is>
       </c>
-      <c r="K56" s="30" t="inlineStr">
+      <c r="L56" s="30" t="inlineStr">
         <is>
           <t>Set C</t>
         </is>
       </c>
-      <c r="L56" s="30" t="inlineStr">
+      <c r="M56" s="30" t="inlineStr">
         <is>
           <t>Engagement card in brand style</t>
         </is>
       </c>
-      <c r="M56" s="24" t="n"/>
       <c r="N56" s="24" t="n"/>
-      <c r="O56" s="34" t="inlineStr">
+      <c r="O56" s="24" t="n"/>
+      <c r="P56" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P56" s="24" t="inlineStr">
-        <is>
-          <t>Not designed yet</t>
-        </is>
-      </c>
-      <c r="Q56" s="24" t="n"/>
-      <c r="R56" s="30" t="inlineStr">
+      <c r="Q56" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="R56" s="24" t="n"/>
+      <c r="S56" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="S56" s="30" t="n"/>
       <c r="T56" s="30" t="n"/>
       <c r="U56" s="30" t="n"/>
       <c r="V56" s="30" t="n"/>
       <c r="W56" s="30" t="n"/>
       <c r="X56" s="30" t="n"/>
-      <c r="Y56" s="24" t="n"/>
+      <c r="Y56" s="30" t="n"/>
       <c r="Z56" s="24" t="n"/>
-      <c r="AA56" s="24" t="inlineStr">
+      <c r="AA56" s="24" t="n"/>
+      <c r="AB56" s="24" t="inlineStr">
         <is>
           <t>Not designed yet</t>
         </is>
@@ -6366,69 +6707,74 @@
           <t>Carousel</t>
         </is>
       </c>
-      <c r="F57" s="28" t="inlineStr">
+      <c r="F57" s="24" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G57" s="28" t="inlineStr">
         <is>
           <t>Instagram feed + GBP</t>
         </is>
       </c>
-      <c r="G57" s="28" t="inlineStr">
+      <c r="H57" s="28" t="inlineStr">
         <is>
           <t>Promo &amp; CTA</t>
         </is>
       </c>
-      <c r="H57" s="28" t="inlineStr">
+      <c r="I57" s="28" t="inlineStr">
         <is>
           <t>Rested by the Holidays: Your Treatment Timeline | Party season is closer than you think.</t>
         </is>
       </c>
-      <c r="I57" s="28" t="inlineStr">
+      <c r="J57" s="28" t="inlineStr">
         <is>
           <t>Botox needs 2 weeks to settle. Filler needs up to 4. If you want to glow in the December photos, here is exactly when to book each treatment. 🗓️
 #holidayglow #treatyourself #giftcertificate #bookyourappointment #medspaspecial #glowupseason #selfcaregift #luxuryselfcare #holidayready #giftideas</t>
         </is>
       </c>
-      <c r="J57" s="28" t="inlineStr">
+      <c r="K57" s="28" t="inlineStr">
         <is>
           <t>Book now. Link in bio</t>
         </is>
       </c>
-      <c r="K57" s="28" t="inlineStr">
+      <c r="L57" s="28" t="inlineStr">
         <is>
           <t>Set E</t>
         </is>
       </c>
-      <c r="L57" s="28" t="inlineStr">
+      <c r="M57" s="28" t="inlineStr">
         <is>
           <t>Design holiday timeline layout</t>
         </is>
       </c>
-      <c r="M57" s="24" t="n"/>
       <c r="N57" s="24" t="n"/>
-      <c r="O57" s="32" t="inlineStr">
+      <c r="O57" s="24" t="n"/>
+      <c r="P57" s="32" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P57" s="24" t="inlineStr">
-        <is>
-          <t>Not designed yet</t>
-        </is>
-      </c>
-      <c r="Q57" s="24" t="n"/>
-      <c r="R57" s="28" t="inlineStr">
+      <c r="Q57" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="R57" s="24" t="n"/>
+      <c r="S57" s="28" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="S57" s="28" t="n"/>
       <c r="T57" s="28" t="n"/>
       <c r="U57" s="28" t="n"/>
       <c r="V57" s="28" t="n"/>
       <c r="W57" s="28" t="n"/>
       <c r="X57" s="28" t="n"/>
-      <c r="Y57" s="24" t="n"/>
+      <c r="Y57" s="28" t="n"/>
       <c r="Z57" s="24" t="n"/>
-      <c r="AA57" s="24" t="inlineStr">
+      <c r="AA57" s="24" t="n"/>
+      <c r="AB57" s="24" t="inlineStr">
         <is>
           <t>Not designed yet</t>
         </is>
@@ -6456,69 +6802,74 @@
           <t>Single Image</t>
         </is>
       </c>
-      <c r="F58" s="30" t="inlineStr">
+      <c r="F58" s="24" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G58" s="30" t="inlineStr">
         <is>
           <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
-      <c r="G58" s="30" t="inlineStr">
+      <c r="H58" s="30" t="inlineStr">
         <is>
           <t>Promo &amp; CTA</t>
         </is>
       </c>
-      <c r="H58" s="30" t="inlineStr">
+      <c r="I58" s="30" t="inlineStr">
         <is>
           <t>Holiday Countdown: Book by These Dates | Work backwards from party season.</t>
         </is>
       </c>
-      <c r="I58" s="30" t="inlineStr">
+      <c r="J58" s="30" t="inlineStr">
         <is>
           <t>Botox needs 2 weeks. Filler needs 4. If you want to glow in the December photos, these are your deadlines. 🗓️
 #holidayglow #treatyourself #giftcertificate #bookyourappointment #medspaspecial #glowupseason #selfcaregift #luxuryselfcare #holidayready #giftideas</t>
         </is>
       </c>
-      <c r="J58" s="30" t="inlineStr">
+      <c r="K58" s="30" t="inlineStr">
         <is>
           <t>Book now. Link in bio</t>
         </is>
       </c>
-      <c r="K58" s="30" t="inlineStr">
+      <c r="L58" s="30" t="inlineStr">
         <is>
           <t>Set E</t>
         </is>
       </c>
-      <c r="L58" s="30" t="inlineStr">
+      <c r="M58" s="30" t="inlineStr">
         <is>
           <t>Single image: countdown-dates card</t>
         </is>
       </c>
-      <c r="M58" s="24" t="n"/>
       <c r="N58" s="24" t="n"/>
-      <c r="O58" s="34" t="inlineStr">
+      <c r="O58" s="24" t="n"/>
+      <c r="P58" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P58" s="24" t="inlineStr">
-        <is>
-          <t>Not designed yet</t>
-        </is>
-      </c>
-      <c r="Q58" s="24" t="n"/>
-      <c r="R58" s="30" t="inlineStr">
+      <c r="Q58" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="R58" s="24" t="n"/>
+      <c r="S58" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="S58" s="30" t="n"/>
       <c r="T58" s="30" t="n"/>
       <c r="U58" s="30" t="n"/>
       <c r="V58" s="30" t="n"/>
       <c r="W58" s="30" t="n"/>
       <c r="X58" s="30" t="n"/>
-      <c r="Y58" s="24" t="n"/>
+      <c r="Y58" s="30" t="n"/>
       <c r="Z58" s="24" t="n"/>
-      <c r="AA58" s="24" t="inlineStr">
+      <c r="AA58" s="24" t="n"/>
+      <c r="AB58" s="24" t="inlineStr">
         <is>
           <t>Not designed yet</t>
         </is>
@@ -6546,69 +6897,74 @@
           <t>Carousel</t>
         </is>
       </c>
-      <c r="F59" s="28" t="inlineStr">
+      <c r="F59" s="24" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G59" s="28" t="inlineStr">
         <is>
           <t>Instagram feed + GBP</t>
         </is>
       </c>
-      <c r="G59" s="28" t="inlineStr">
+      <c r="H59" s="28" t="inlineStr">
         <is>
           <t>Promo &amp; CTA</t>
         </is>
       </c>
-      <c r="H59" s="28" t="inlineStr">
+      <c r="I59" s="28" t="inlineStr">
         <is>
           <t>Party Season Prep: What to Book and When | Your holiday glow, planned backwards.</t>
         </is>
       </c>
-      <c r="I59" s="28" t="inlineStr">
+      <c r="J59" s="28" t="inlineStr">
         <is>
           <t>Work back from your event date and nothing is rushed, nothing is swollen, and everything looks like you. Here is the smart booking order.
 #holidayglow #treatyourself #giftcertificate #bookyourappointment #medspaspecial #glowupseason #selfcaregift #luxuryselfcare #holidayready #giftideas</t>
         </is>
       </c>
-      <c r="J59" s="28" t="inlineStr">
+      <c r="K59" s="28" t="inlineStr">
         <is>
           <t>DM HOLIDAY to book</t>
         </is>
       </c>
-      <c r="K59" s="28" t="inlineStr">
+      <c r="L59" s="28" t="inlineStr">
         <is>
           <t>Set E</t>
         </is>
       </c>
-      <c r="L59" s="28" t="inlineStr">
+      <c r="M59" s="28" t="inlineStr">
         <is>
           <t>Design in editorial template</t>
         </is>
       </c>
-      <c r="M59" s="24" t="n"/>
       <c r="N59" s="24" t="n"/>
-      <c r="O59" s="32" t="inlineStr">
+      <c r="O59" s="24" t="n"/>
+      <c r="P59" s="32" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P59" s="24" t="inlineStr">
-        <is>
-          <t>Not designed yet</t>
-        </is>
-      </c>
-      <c r="Q59" s="24" t="n"/>
-      <c r="R59" s="28" t="inlineStr">
+      <c r="Q59" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="R59" s="24" t="n"/>
+      <c r="S59" s="28" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="S59" s="28" t="n"/>
       <c r="T59" s="28" t="n"/>
       <c r="U59" s="28" t="n"/>
       <c r="V59" s="28" t="n"/>
       <c r="W59" s="28" t="n"/>
       <c r="X59" s="28" t="n"/>
-      <c r="Y59" s="24" t="n"/>
+      <c r="Y59" s="28" t="n"/>
       <c r="Z59" s="24" t="n"/>
-      <c r="AA59" s="24" t="inlineStr">
+      <c r="AA59" s="24" t="n"/>
+      <c r="AB59" s="24" t="inlineStr">
         <is>
           <t>Not designed yet</t>
         </is>
@@ -6636,80 +6992,85 @@
           <t>Carousel</t>
         </is>
       </c>
-      <c r="F60" s="30" t="inlineStr">
+      <c r="F60" s="24" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G60" s="30" t="inlineStr">
         <is>
           <t>Instagram feed + GBP</t>
         </is>
       </c>
-      <c r="G60" s="30" t="inlineStr">
+      <c r="H60" s="30" t="inlineStr">
         <is>
           <t>Trust &amp; Proof</t>
         </is>
       </c>
-      <c r="H60" s="30" t="inlineStr">
+      <c r="I60" s="30" t="inlineStr">
         <is>
           <t>One Result, Every Angle | No flattering angle. Every angle.</t>
         </is>
       </c>
-      <c r="I60" s="30" t="inlineStr">
+      <c r="J60" s="30" t="inlineStr">
         <is>
           <t>Anyone can find one good angle. This is the same client, same lips, six angles, fully healed. That is the whole test. Individual results vary. Shared with consent.
 #dermalfiller #lipfiller #cheekfiller #naturalfiller #facialbalancing #lipfillernatural #aestheticnurse #medspa #fillerjourney #lipgoals</t>
         </is>
       </c>
-      <c r="J60" s="30" t="inlineStr">
+      <c r="K60" s="30" t="inlineStr">
         <is>
           <t>DM LIPS to book</t>
         </is>
       </c>
-      <c r="K60" s="30" t="inlineStr">
+      <c r="L60" s="30" t="inlineStr">
         <is>
           <t>Set B</t>
         </is>
       </c>
-      <c r="L60" s="30" t="inlineStr">
+      <c r="M60" s="30" t="inlineStr">
         <is>
           <t>Carousel: 6 angles of one healed result. Crop to treatment area, no faces</t>
         </is>
       </c>
-      <c r="M60" s="24" t="inlineStr">
+      <c r="N60" s="24" t="inlineStr">
         <is>
           <t>img_4775, 4777, 4778, 4780, 4781, 4782</t>
         </is>
       </c>
-      <c r="N60" s="24" t="inlineStr">
+      <c r="O60" s="24" t="inlineStr">
         <is>
           <t>On file</t>
         </is>
       </c>
-      <c r="O60" s="34" t="inlineStr">
+      <c r="P60" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P60" s="33" t="inlineStr">
+      <c r="Q60" s="33" t="inlineStr">
         <is>
           <t>View 7 slides</t>
         </is>
       </c>
-      <c r="Q60" s="24">
+      <c r="R60" s="24">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-11-06-one-result-every-angle/images/slide-1.png")</f>
         <v/>
       </c>
-      <c r="R60" s="30" t="inlineStr">
+      <c r="S60" s="30" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="S60" s="30" t="n"/>
       <c r="T60" s="30" t="n"/>
       <c r="U60" s="30" t="n"/>
       <c r="V60" s="30" t="n"/>
       <c r="W60" s="30" t="n"/>
       <c r="X60" s="30" t="n"/>
-      <c r="Y60" s="24" t="n"/>
+      <c r="Y60" s="30" t="n"/>
       <c r="Z60" s="24" t="n"/>
-      <c r="AA60" s="24" t="inlineStr">
+      <c r="AA60" s="24" t="n"/>
+      <c r="AB60" s="24" t="inlineStr">
         <is>
           <t>Not designed yet</t>
         </is>
@@ -6737,69 +7098,74 @@
           <t>Single Image</t>
         </is>
       </c>
-      <c r="F61" s="30" t="inlineStr">
+      <c r="F61" s="24" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G61" s="30" t="inlineStr">
         <is>
           <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
-      <c r="G61" s="30" t="inlineStr">
+      <c r="H61" s="30" t="inlineStr">
         <is>
           <t>Promo &amp; CTA</t>
         </is>
       </c>
-      <c r="H61" s="30" t="inlineStr">
+      <c r="I61" s="30" t="inlineStr">
         <is>
           <t>Quote: Book the Appointment | Seasonal self-care push.</t>
         </is>
       </c>
-      <c r="I61" s="30" t="inlineStr">
+      <c r="J61" s="30" t="inlineStr">
         <is>
           <t>You cannot pour from an empty cup. Book the appointment. Take the hour. You have earned it. 💛
 #holidayglow #treatyourself #giftcertificate #bookyourappointment #medspaspecial #glowupseason #selfcaregift #luxuryselfcare #holidayready #giftideas</t>
         </is>
       </c>
-      <c r="J61" s="30" t="inlineStr">
+      <c r="K61" s="30" t="inlineStr">
         <is>
           <t>Link in bio</t>
         </is>
       </c>
-      <c r="K61" s="30" t="inlineStr">
+      <c r="L61" s="30" t="inlineStr">
         <is>
           <t>Set E</t>
         </is>
       </c>
-      <c r="L61" s="30" t="inlineStr">
+      <c r="M61" s="30" t="inlineStr">
         <is>
           <t>Quote card in brand style</t>
         </is>
       </c>
-      <c r="M61" s="24" t="n"/>
       <c r="N61" s="24" t="n"/>
-      <c r="O61" s="34" t="inlineStr">
+      <c r="O61" s="24" t="n"/>
+      <c r="P61" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P61" s="24" t="inlineStr">
-        <is>
-          <t>Not designed yet</t>
-        </is>
-      </c>
-      <c r="Q61" s="24" t="n"/>
-      <c r="R61" s="30" t="inlineStr">
+      <c r="Q61" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="R61" s="24" t="n"/>
+      <c r="S61" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="S61" s="30" t="n"/>
       <c r="T61" s="30" t="n"/>
       <c r="U61" s="30" t="n"/>
       <c r="V61" s="30" t="n"/>
       <c r="W61" s="30" t="n"/>
       <c r="X61" s="30" t="n"/>
-      <c r="Y61" s="24" t="n"/>
+      <c r="Y61" s="30" t="n"/>
       <c r="Z61" s="24" t="n"/>
-      <c r="AA61" s="24" t="inlineStr">
+      <c r="AA61" s="24" t="n"/>
+      <c r="AB61" s="24" t="inlineStr">
         <is>
           <t>Not designed yet</t>
         </is>
@@ -6827,69 +7193,74 @@
           <t>Carousel</t>
         </is>
       </c>
-      <c r="F62" s="28" t="inlineStr">
+      <c r="F62" s="24" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G62" s="28" t="inlineStr">
         <is>
           <t>Instagram feed + GBP</t>
         </is>
       </c>
-      <c r="G62" s="28" t="inlineStr">
+      <c r="H62" s="28" t="inlineStr">
         <is>
           <t>Promo &amp; CTA</t>
         </is>
       </c>
-      <c r="H62" s="28" t="inlineStr">
+      <c r="I62" s="28" t="inlineStr">
         <is>
           <t>The Gift of Glow: Gift Certificates Are Here | The present nobody returns.</t>
         </is>
       </c>
-      <c r="I62" s="28" t="inlineStr">
+      <c r="J62" s="28" t="inlineStr">
         <is>
           <t>Give the people you love something they actually want. Luxury Beauty gift certificates are available in any amount, wrapped and ready. 🎁
 #holidayglow #treatyourself #giftcertificate #bookyourappointment #medspaspecial #glowupseason #selfcaregift #luxuryselfcare #holidayready #giftideas</t>
         </is>
       </c>
-      <c r="J62" s="28" t="inlineStr">
+      <c r="K62" s="28" t="inlineStr">
         <is>
           <t>DM GIFT to order</t>
         </is>
       </c>
-      <c r="K62" s="28" t="inlineStr">
+      <c r="L62" s="28" t="inlineStr">
         <is>
           <t>Set E</t>
         </is>
       </c>
-      <c r="L62" s="28" t="inlineStr">
+      <c r="M62" s="28" t="inlineStr">
         <is>
           <t>Design gift certificate reveal layout</t>
         </is>
       </c>
-      <c r="M62" s="24" t="n"/>
       <c r="N62" s="24" t="n"/>
-      <c r="O62" s="32" t="inlineStr">
+      <c r="O62" s="24" t="n"/>
+      <c r="P62" s="32" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P62" s="24" t="inlineStr">
-        <is>
-          <t>Not designed yet</t>
-        </is>
-      </c>
-      <c r="Q62" s="24" t="n"/>
-      <c r="R62" s="28" t="inlineStr">
+      <c r="Q62" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="R62" s="24" t="n"/>
+      <c r="S62" s="28" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="S62" s="28" t="n"/>
       <c r="T62" s="28" t="n"/>
       <c r="U62" s="28" t="n"/>
       <c r="V62" s="28" t="n"/>
       <c r="W62" s="28" t="n"/>
       <c r="X62" s="28" t="n"/>
-      <c r="Y62" s="24" t="n"/>
+      <c r="Y62" s="28" t="n"/>
       <c r="Z62" s="24" t="n"/>
-      <c r="AA62" s="24" t="inlineStr">
+      <c r="AA62" s="24" t="n"/>
+      <c r="AB62" s="24" t="inlineStr">
         <is>
           <t>Not designed yet</t>
         </is>
@@ -6917,69 +7288,74 @@
           <t>Single Image</t>
         </is>
       </c>
-      <c r="F63" s="30" t="inlineStr">
+      <c r="F63" s="24" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G63" s="30" t="inlineStr">
         <is>
           <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
-      <c r="G63" s="30" t="inlineStr">
+      <c r="H63" s="30" t="inlineStr">
         <is>
           <t>Promo &amp; CTA</t>
         </is>
       </c>
-      <c r="H63" s="30" t="inlineStr">
+      <c r="I63" s="30" t="inlineStr">
         <is>
           <t>Gift Certificates Are Here | The present nobody returns.</t>
         </is>
       </c>
-      <c r="I63" s="30" t="inlineStr">
+      <c r="J63" s="30" t="inlineStr">
         <is>
           <t>In any amount, wrapped and beautiful. Give the people you love something they actually want. 🎁
 #holidayglow #treatyourself #giftcertificate #bookyourappointment #medspaspecial #glowupseason #selfcaregift #luxuryselfcare #holidayready #giftideas</t>
         </is>
       </c>
-      <c r="J63" s="30" t="inlineStr">
+      <c r="K63" s="30" t="inlineStr">
         <is>
           <t>DM GIFT to order</t>
         </is>
       </c>
-      <c r="K63" s="30" t="inlineStr">
+      <c r="L63" s="30" t="inlineStr">
         <is>
           <t>Set E</t>
         </is>
       </c>
-      <c r="L63" s="30" t="inlineStr">
+      <c r="M63" s="30" t="inlineStr">
         <is>
           <t>Single image: gift certificate photo + hook</t>
         </is>
       </c>
-      <c r="M63" s="24" t="n"/>
       <c r="N63" s="24" t="n"/>
-      <c r="O63" s="34" t="inlineStr">
+      <c r="O63" s="24" t="n"/>
+      <c r="P63" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P63" s="24" t="inlineStr">
-        <is>
-          <t>Not designed yet</t>
-        </is>
-      </c>
-      <c r="Q63" s="24" t="n"/>
-      <c r="R63" s="30" t="inlineStr">
+      <c r="Q63" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="R63" s="24" t="n"/>
+      <c r="S63" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="S63" s="30" t="n"/>
       <c r="T63" s="30" t="n"/>
       <c r="U63" s="30" t="n"/>
       <c r="V63" s="30" t="n"/>
       <c r="W63" s="30" t="n"/>
       <c r="X63" s="30" t="n"/>
-      <c r="Y63" s="24" t="n"/>
+      <c r="Y63" s="30" t="n"/>
       <c r="Z63" s="24" t="n"/>
-      <c r="AA63" s="24" t="inlineStr">
+      <c r="AA63" s="24" t="n"/>
+      <c r="AB63" s="24" t="inlineStr">
         <is>
           <t>Not designed yet</t>
         </is>
@@ -7007,69 +7383,74 @@
           <t>Carousel</t>
         </is>
       </c>
-      <c r="F64" s="28" t="inlineStr">
+      <c r="F64" s="24" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G64" s="28" t="inlineStr">
         <is>
           <t>Instagram feed + GBP</t>
         </is>
       </c>
-      <c r="G64" s="28" t="inlineStr">
+      <c r="H64" s="28" t="inlineStr">
         <is>
           <t>Trust &amp; Proof</t>
         </is>
       </c>
-      <c r="H64" s="28" t="inlineStr">
+      <c r="I64" s="28" t="inlineStr">
         <is>
           <t>3 Months of Honest Answers: The Recap | Real education. Real results. Thank you.</t>
         </is>
       </c>
-      <c r="I64" s="28" t="inlineStr">
+      <c r="J64" s="28" t="inlineStr">
         <is>
           <t>Since August we have busted myths, answered your questions, and kept every promise about natural results. Here are the posts you loved most, in case you missed one. 💛
 #npinjector #nursepractitioner #medspalife #luxurybeauty #aestheticnurse #skincareexpert #beautyclinic #selfcare #naturalresults #honestbeauty</t>
         </is>
       </c>
-      <c r="J64" s="28" t="inlineStr">
+      <c r="K64" s="28" t="inlineStr">
         <is>
           <t>Follow for what is next</t>
         </is>
       </c>
-      <c r="K64" s="28" t="inlineStr">
+      <c r="L64" s="28" t="inlineStr">
         <is>
           <t>Set C</t>
         </is>
       </c>
-      <c r="L64" s="28" t="inlineStr">
+      <c r="M64" s="28" t="inlineStr">
         <is>
           <t>Compile top slides from past carousels</t>
         </is>
       </c>
-      <c r="M64" s="24" t="n"/>
       <c r="N64" s="24" t="n"/>
-      <c r="O64" s="32" t="inlineStr">
+      <c r="O64" s="24" t="n"/>
+      <c r="P64" s="32" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P64" s="24" t="inlineStr">
-        <is>
-          <t>Not designed yet</t>
-        </is>
-      </c>
-      <c r="Q64" s="24" t="n"/>
-      <c r="R64" s="28" t="inlineStr">
+      <c r="Q64" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="R64" s="24" t="n"/>
+      <c r="S64" s="28" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="S64" s="28" t="n"/>
       <c r="T64" s="28" t="n"/>
       <c r="U64" s="28" t="n"/>
       <c r="V64" s="28" t="n"/>
       <c r="W64" s="28" t="n"/>
       <c r="X64" s="28" t="n"/>
-      <c r="Y64" s="24" t="n"/>
+      <c r="Y64" s="28" t="n"/>
       <c r="Z64" s="24" t="n"/>
-      <c r="AA64" s="24" t="inlineStr">
+      <c r="AA64" s="24" t="n"/>
+      <c r="AB64" s="24" t="inlineStr">
         <is>
           <t>Not designed yet</t>
         </is>
@@ -7097,69 +7478,74 @@
           <t>Single Image</t>
         </is>
       </c>
-      <c r="F65" s="30" t="inlineStr">
+      <c r="F65" s="24" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G65" s="30" t="inlineStr">
         <is>
           <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
-      <c r="G65" s="30" t="inlineStr">
+      <c r="H65" s="30" t="inlineStr">
         <is>
           <t>Personality &amp; BTS</t>
         </is>
       </c>
-      <c r="H65" s="30" t="inlineStr">
+      <c r="I65" s="30" t="inlineStr">
         <is>
           <t>Thank You: 3 Months of Honest Aesthetics | Gratitude post.</t>
         </is>
       </c>
-      <c r="I65" s="30" t="inlineStr">
+      <c r="J65" s="30" t="inlineStr">
         <is>
           <t>Since August you have asked incredible questions and trusted us with the answers. Here is to honest aesthetics. Thank you. 💛
 #npinjector #nursepractitioner #medspalife #luxurybeauty #aestheticnurse #skincareexpert #beautyclinic #selfcare #naturalresults #honestbeauty</t>
         </is>
       </c>
-      <c r="J65" s="30" t="inlineStr">
+      <c r="K65" s="30" t="inlineStr">
         <is>
           <t>Follow for what is next</t>
         </is>
       </c>
-      <c r="K65" s="30" t="inlineStr">
+      <c r="L65" s="30" t="inlineStr">
         <is>
           <t>Set C</t>
         </is>
       </c>
-      <c r="L65" s="30" t="inlineStr">
+      <c r="M65" s="30" t="inlineStr">
         <is>
           <t>Single image: team or Cleo photo + thank you overlay</t>
         </is>
       </c>
-      <c r="M65" s="24" t="n"/>
       <c r="N65" s="24" t="n"/>
-      <c r="O65" s="34" t="inlineStr">
+      <c r="O65" s="24" t="n"/>
+      <c r="P65" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P65" s="24" t="inlineStr">
-        <is>
-          <t>Not designed yet</t>
-        </is>
-      </c>
-      <c r="Q65" s="24" t="n"/>
-      <c r="R65" s="30" t="inlineStr">
+      <c r="Q65" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="R65" s="24" t="n"/>
+      <c r="S65" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="S65" s="30" t="n"/>
       <c r="T65" s="30" t="n"/>
       <c r="U65" s="30" t="n"/>
       <c r="V65" s="30" t="n"/>
       <c r="W65" s="30" t="n"/>
       <c r="X65" s="30" t="n"/>
-      <c r="Y65" s="24" t="n"/>
+      <c r="Y65" s="30" t="n"/>
       <c r="Z65" s="24" t="n"/>
-      <c r="AA65" s="24" t="inlineStr">
+      <c r="AA65" s="24" t="n"/>
+      <c r="AB65" s="24" t="inlineStr">
         <is>
           <t>Not designed yet</t>
         </is>
@@ -7187,69 +7573,74 @@
           <t>Single Image</t>
         </is>
       </c>
-      <c r="F66" s="30" t="inlineStr">
+      <c r="F66" s="24" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G66" s="30" t="inlineStr">
         <is>
           <t>IG + FB + TikTok photo + GBP</t>
         </is>
       </c>
-      <c r="G66" s="30" t="inlineStr">
+      <c r="H66" s="30" t="inlineStr">
         <is>
           <t>Promo &amp; CTA</t>
         </is>
       </c>
-      <c r="H66" s="30" t="inlineStr">
+      <c r="I66" s="30" t="inlineStr">
         <is>
           <t>Tag Someone Who Deserves a Glow-Up Gift | Engagement + promo close.</t>
         </is>
       </c>
-      <c r="I66" s="30" t="inlineStr">
+      <c r="J66" s="30" t="inlineStr">
         <is>
           <t>Know someone who never treats themselves? Tag them below. We will take care of the rest. 🎁
 #holidayglow #treatyourself #giftcertificate #bookyourappointment #medspaspecial #glowupseason #selfcaregift #luxuryselfcare #holidayready #giftideas</t>
         </is>
       </c>
-      <c r="J66" s="30" t="inlineStr">
+      <c r="K66" s="30" t="inlineStr">
         <is>
           <t>Tag a friend</t>
         </is>
       </c>
-      <c r="K66" s="30" t="inlineStr">
+      <c r="L66" s="30" t="inlineStr">
         <is>
           <t>Set E</t>
         </is>
       </c>
-      <c r="L66" s="30" t="inlineStr">
+      <c r="M66" s="30" t="inlineStr">
         <is>
           <t>Engagement card in brand style</t>
         </is>
       </c>
-      <c r="M66" s="24" t="n"/>
       <c r="N66" s="24" t="n"/>
-      <c r="O66" s="34" t="inlineStr">
+      <c r="O66" s="24" t="n"/>
+      <c r="P66" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
         </is>
       </c>
-      <c r="P66" s="24" t="inlineStr">
-        <is>
-          <t>Not designed yet</t>
-        </is>
-      </c>
-      <c r="Q66" s="24" t="n"/>
-      <c r="R66" s="30" t="inlineStr">
+      <c r="Q66" s="24" t="inlineStr">
+        <is>
+          <t>Not designed yet</t>
+        </is>
+      </c>
+      <c r="R66" s="24" t="n"/>
+      <c r="S66" s="30" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="S66" s="30" t="n"/>
       <c r="T66" s="30" t="n"/>
       <c r="U66" s="30" t="n"/>
       <c r="V66" s="30" t="n"/>
       <c r="W66" s="30" t="n"/>
       <c r="X66" s="30" t="n"/>
-      <c r="Y66" s="24" t="n"/>
+      <c r="Y66" s="30" t="n"/>
       <c r="Z66" s="24" t="n"/>
-      <c r="AA66" s="24" t="inlineStr">
+      <c r="AA66" s="24" t="n"/>
+      <c r="AB66" s="24" t="inlineStr">
         <is>
           <t>Not designed yet</t>
         </is>

--- a/strategy/ig-content-strategy.xlsx
+++ b/strategy/ig-content-strategy.xlsx
@@ -25,7 +25,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mmm\ d&quot;, &quot;yyyy"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -121,6 +121,18 @@
       <sz val="10"/>
       <u val="single"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="002E2A23"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="FF6E6557"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -181,7 +193,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -281,6 +293,10 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -530,522 +546,417 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C55"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <dimension ref="B2:C43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="3" customWidth="1" style="13" min="1" max="1"/>
-    <col width="30" customWidth="1" style="13" min="2" max="2"/>
-    <col width="50" customWidth="1" style="13" min="3" max="3"/>
-    <col width="30" customWidth="1" style="13" min="4" max="4"/>
-    <col width="20" customWidth="1" style="13" min="5" max="6"/>
+    <col width="3" customWidth="1" style="14" min="1" max="1"/>
+    <col width="22" customWidth="1" style="14" min="2" max="2"/>
+    <col width="95" customWidth="1" style="14" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2" ht="19.7" customHeight="1" s="14">
-      <c r="B2" s="15" t="inlineStr">
+    <row r="2">
+      <c r="B2" s="35" t="inlineStr">
         <is>
           <t>Luxury Beauty by Cleo R</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="14">
-      <c r="B3" s="16" t="inlineStr">
-        <is>
-          <t>Instagram Content Strategy. Aug 17 to Nov 15, 2026 (13 weeks, 65 posts, 7 photo-backed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4"/>
-    <row r="5" ht="15" customHeight="1" s="14">
-      <c r="B5" s="17" t="n"/>
-      <c r="C5" s="18" t="n"/>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="14">
-      <c r="B6" s="19" t="inlineStr">
-        <is>
-          <t>WEEKLY RHYTHM (5 posts per week)</t>
-        </is>
-      </c>
-      <c r="C6" s="18" t="n"/>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="14">
-      <c r="B7" s="17" t="inlineStr">
+    <row r="3">
+      <c r="B3" s="36" t="inlineStr">
+        <is>
+          <t>Instagram + Google Business Profile content plan. Aug 17 to Nov 15, 2026. 13 weeks, 65 posts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="37" t="inlineStr">
+        <is>
+          <t>THE CLINIC</t>
+        </is>
+      </c>
+      <c r="C5" s="38" t="n"/>
+    </row>
+    <row r="6">
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>Address</t>
+        </is>
+      </c>
+      <c r="C6" s="24" t="inlineStr">
+        <is>
+          <t>3060 Preserve Dr, Oakville, ON L6M 4L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>Service area</t>
+        </is>
+      </c>
+      <c r="C7" s="24" t="inlineStr">
+        <is>
+          <t>Oakville, Burlington, Milton, Mississauga</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C8" s="24" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>Booking</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t>DM on Instagram for now. Swap every "Learn more" link once a booking page exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="37" t="inlineStr">
+        <is>
+          <t>WEEKLY RHYTHM</t>
+        </is>
+      </c>
+      <c r="C11" s="38" t="n"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>Carousel 1: education pillar. Your biggest post of the week.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="14">
-      <c r="B8" s="17" t="inlineStr">
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>Carousel, education pillar. The biggest post of the week.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C13" s="24" t="inlineStr">
         <is>
           <t>Single image with a strong hook. Cross-post to Facebook and TikTok.</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="14">
-      <c r="B9" s="17" t="inlineStr">
+    <row r="14">
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>Carousel 2: trust, proof, or personality pillar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="14">
-      <c r="B10" s="17" t="inlineStr">
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>Carousel: trust, proof or personality pillar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C15" s="24" t="inlineStr">
         <is>
           <t>Single image with a strong hook. Cross-post to Facebook and TikTok.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="14">
-      <c r="B11" s="17" t="inlineStr">
+    <row r="16">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>Quote, testimonial, or engagement image. Cross-post to FB and TikTok.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="14">
-      <c r="B12" s="17" t="n"/>
-      <c r="C12" s="18" t="n"/>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="14">
-      <c r="B13" s="19" t="inlineStr">
-        <is>
-          <t>HOW TO WORK THIS SHEET</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="n"/>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="14">
-      <c r="B14" s="17" t="inlineStr">
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>Result, testimonial or engagement post.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>Every post</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>Also goes to Google Business Profile using the GBP columns, never the Instagram file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="37" t="inlineStr">
+        <is>
+          <t>WORKING THE SHEET</t>
+        </is>
+      </c>
+      <c r="C19" s="38" t="n"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t>1. Plan</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>Everything is pre-filled in the Posting Schedule tab. Adjust topics freely.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="14">
-      <c r="B15" s="17" t="inlineStr">
+      <c r="C20" s="24" t="inlineStr">
+        <is>
+          <t>Everything is pre-filled in Posting Schedule. Adjust topics freely; check the Tone column before moving dates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>2. Design</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>Ask Claude to build any post from its row. Week 1 Monday is already done.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="23.85" customHeight="1" s="14">
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>2b. Files</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>Every post has its own folder in the repo. Click its Folder Link for the brief and final images.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="23.85" customHeight="1" s="14">
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>3. Track</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>Update the Status dropdown as each post moves: Idea, Design, Ready, Posted.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="14">
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>4. Measure</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>After 48 hours, fill Reach, Saves, Comments, DMs, Bookings from IG Insights.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="14">
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>5. Repeat winners</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>Anything with high saves or DMs becomes next month's sequel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="14">
-      <c r="B20" s="17" t="n"/>
-      <c r="C20" s="18" t="n"/>
-    </row>
-    <row r="21" ht="23.85" customHeight="1" s="14">
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>YOU EDIT</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>Status, Posted Link, and the performance columns. Everything else is a draft you may rewrite.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="14">
-      <c r="B22" s="17" t="n"/>
-      <c r="C22" s="18" t="n"/>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="14">
-      <c r="B23" s="19" t="inlineStr">
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>Ask Claude to build any post from its row. All of August is done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>3. Files</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>Every post has a repo folder. Folder Link opens it, Image Link opens the artwork, Preview shows a live thumbnail once this file is in Google Sheets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>4. Post</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
+        <is>
+          <t>Instagram gets the caption and hashtags. GBP gets the GBP caption, the GBP image, and a button pointed at the Instagram profile.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>5. Track</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t>Move Status as each post progresses: Idea, Design, Ready, Posted. Hold means blocked, see the row notes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>6. Measure</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
+        <is>
+          <t>After 48 hours fill Reach, Saves, Comments, DMs, Bookings from IG Insights. Saves and DMs are the numbers that matter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>7. Repeat</t>
+        </is>
+      </c>
+      <c r="C26" s="24" t="inlineStr">
+        <is>
+          <t>Anything with high saves or DMs becomes next month’s sequel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="37" t="inlineStr">
+        <is>
+          <t>HOUSE RULES</t>
+        </is>
+      </c>
+      <c r="C28" s="38" t="n"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="22" t="inlineStr">
+        <is>
+          <t>Client photos</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="inlineStr">
+        <is>
+          <t>Written consent on file before anything is posted. Every photo is cropped to the treatment area: no eyes, brows, tattoos or jewellery. Always add "individual results vary". Never boost before and after posts on IG or TikTok; organic only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>Grid tone</t>
+        </is>
+      </c>
+      <c r="C30" s="24" t="inlineStr">
+        <is>
+          <t>The profile grid runs three tiles per row, newest first. Keep exactly one Dark or Photo-dark tile per row and never let two Dark tiles touch. The Tone column tracks this; re-check it whenever a date moves.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="C31" s="24" t="inlineStr">
+        <is>
+          <t>No hashtags on GBP, they do not work there. The offer goes in the first 80 characters. Images are 1200x900 with everything inside the centre 900x900 square, because Maps crops to a square.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="22" t="inlineStr">
+        <is>
+          <t>Hashtags</t>
+        </is>
+      </c>
+      <c r="C32" s="24" t="inlineStr">
+        <is>
+          <t>Every set leads with local tags (Oakville, Burlington, Milton, Mississauga, Halton). Location plus service is the highest-intent combination. Sets live on the Hashtag Sets tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="22" t="inlineStr">
+        <is>
+          <t>Voice</t>
+        </is>
+      </c>
+      <c r="C33" s="24" t="inlineStr">
+        <is>
+          <t>Plain, direct, first person. No em dashes, no sparkle emoji, no borrowed captions. If a line sounds like a template, rewrite it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="22" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="C34" s="24" t="inlineStr">
+        <is>
+          <t>Botox is a prescription drug in Canada and Health Canada restricts consumer advertising of prescription drugs. The brand name in this plan is pending a compliance check; "neuromodulator" is the safe swap. Credentials read RN(EC), College of Nurses of Ontario.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="37" t="inlineStr">
         <is>
           <t>STATUS SNAPSHOT</t>
         </is>
       </c>
-      <c r="C23" s="18" t="n"/>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="14">
-      <c r="B24" s="20" t="inlineStr">
-        <is>
-          <t>Total posts planned</t>
-        </is>
-      </c>
-      <c r="C24" s="17">
+      <c r="C36" s="38" t="n"/>
+    </row>
+    <row r="37">
+      <c r="B37" s="22" t="inlineStr">
+        <is>
+          <t>Posts planned</t>
+        </is>
+      </c>
+      <c r="C37" s="24">
         <f>COUNTA('Posting Schedule'!A2:A66)</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" s="14">
-      <c r="B25" s="20" t="inlineStr">
+    <row r="38">
+      <c r="B38" s="22" t="inlineStr">
         <is>
           <t>Ideas</t>
         </is>
       </c>
-      <c r="C25" s="17">
-        <f>COUNTIF('Posting Schedule'!P2:P66,"Idea")</f>
+      <c r="C38" s="24">
+        <f>COUNTIF('Posting Schedule'!S2:S66,"Idea")</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" s="14">
-      <c r="B26" s="20" t="inlineStr">
-        <is>
-          <t>In design</t>
-        </is>
-      </c>
-      <c r="C26" s="17">
-        <f>COUNTIF('Posting Schedule'!P2:P66,"Design")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="14">
-      <c r="B27" s="20" t="inlineStr">
-        <is>
-          <t>Ready to post</t>
-        </is>
-      </c>
-      <c r="C27" s="17">
-        <f>COUNTIF('Posting Schedule'!P2:P66,"Ready")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="14">
-      <c r="B28" s="20" t="inlineStr">
-        <is>
-          <t>Posted</t>
-        </is>
-      </c>
-      <c r="C28" s="17">
-        <f>COUNTIF('Posting Schedule'!P2:P66,"Posted")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29"/>
-    <row r="30" ht="15" customHeight="1" s="14">
-      <c r="B30" s="21" t="inlineStr">
-        <is>
-          <t>Import to Google Sheets: drive.google.com &gt; New &gt; File upload &gt; pick this file &gt; open with Google Sheets.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="B32" s="22" t="inlineStr">
-        <is>
-          <t>BEFORE AND AFTER RULES</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="23" t="inlineStr">
-        <is>
-          <t>Consent</t>
-        </is>
-      </c>
-      <c r="C33" s="24" t="inlineStr">
-        <is>
-          <t>Written social media consent on file before any client photo is posted.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="23" t="inlineStr">
-        <is>
-          <t>Faces</t>
-        </is>
-      </c>
-      <c r="C34" s="24" t="inlineStr">
-        <is>
-          <t>Crop every result photo to the treatment area. No eyes, brows, tattoos or jewellery.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="23" t="inlineStr">
-        <is>
-          <t>Wording</t>
-        </is>
-      </c>
-      <c r="C35" s="24" t="inlineStr">
-        <is>
-          <t>Always add "individual results vary". Never guarantee an outcome.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="23" t="inlineStr">
-        <is>
-          <t>Paid ads</t>
-        </is>
-      </c>
-      <c r="C36" s="24" t="inlineStr">
-        <is>
-          <t>IG and TikTok restrict boosting before and after cosmetic imagery. Organic only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="23" t="inlineStr">
-        <is>
-          <t>Photo Library</t>
-        </is>
-      </c>
-      <c r="C37" s="24" t="inlineStr">
-        <is>
-          <t>The Photo Library tab tracks every client photo, its consent status and where it is used.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38"/>
     <row r="39">
       <c r="B39" s="22" t="inlineStr">
         <is>
-          <t>Image Link</t>
-        </is>
-      </c>
-      <c r="C39" s="24" t="inlineStr">
-        <is>
-          <t>Click to see the finished image for that post. Single-image posts open the picture directly; carousels open the folder of slides. "Not designed yet" means the post has a brief but no artwork.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40"/>
+          <t>In design</t>
+        </is>
+      </c>
+      <c r="C39" s="24">
+        <f>COUNTIF('Posting Schedule'!S2:S66,"Design")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="22" t="inlineStr">
+        <is>
+          <t>Ready to post</t>
+        </is>
+      </c>
+      <c r="C40" s="24">
+        <f>COUNTIF('Posting Schedule'!S2:S66,"Ready")</f>
+        <v/>
+      </c>
+    </row>
     <row r="41">
       <c r="B41" s="22" t="inlineStr">
         <is>
-          <t>GOOGLE BUSINESS PROFILE</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="23" t="inlineStr">
-        <is>
-          <t>Image</t>
-        </is>
-      </c>
-      <c r="C42" s="24" t="inlineStr">
-        <is>
-          <t>Use the GBP Image Link, not the Instagram one. GBP is 1200x900 and crops to a square in Maps.</t>
-        </is>
+          <t>Posted</t>
+        </is>
+      </c>
+      <c r="C41" s="24">
+        <f>COUNTIF('Posting Schedule'!S2:S66,"Posted")</f>
+        <v/>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="23" t="inlineStr">
-        <is>
-          <t>Caption</t>
+      <c r="B43" s="22" t="inlineStr">
+        <is>
+          <t>Google Sheets</t>
         </is>
       </c>
       <c r="C43" s="24" t="inlineStr">
         <is>
-          <t>GBP Caption has no hashtags. They do not work on GBP. Only the first 80 characters show before the fold.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="23" t="inlineStr">
-        <is>
-          <t>Button</t>
-        </is>
-      </c>
-      <c r="C44" s="24" t="inlineStr">
-        <is>
-          <t>Set the post button to Learn more and point it at the Instagram profile until a booking page exists.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="23" t="inlineStr">
-        <is>
-          <t>Carousels</t>
-        </is>
-      </c>
-      <c r="C45" s="24" t="inlineStr">
-        <is>
-          <t>GBP has no carousel. One image per post, so carousels use their cover.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" s="22" t="inlineStr">
-        <is>
-          <t>LOCATION</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="23" t="inlineStr">
-        <is>
-          <t>Address</t>
-        </is>
-      </c>
-      <c r="C47" s="24" t="inlineStr">
-        <is>
-          <t>3060 Preserve Dr, Oakville, ON L6M 4L9</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="23" t="inlineStr">
-        <is>
-          <t>Service area</t>
-        </is>
-      </c>
-      <c r="C48" s="24" t="inlineStr">
-        <is>
-          <t>Oakville, Burlington, Milton, Mississauga</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="B49" s="23" t="inlineStr">
-        <is>
-          <t>Hashtags</t>
-        </is>
-      </c>
-      <c r="C49" s="24" t="inlineStr">
-        <is>
-          <t>Every set now leads with local tags. Location plus service is the highest intent combination.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="22" t="inlineStr">
-        <is>
-          <t>GRID RHYTHM</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="B52" s="23" t="inlineStr">
-        <is>
-          <t>Rule</t>
-        </is>
-      </c>
-      <c r="C52" s="24" t="inlineStr">
-        <is>
-          <t>The profile grid runs three tiles per row, newest first. Keep exactly one Dark or dark-photo tile in each row of three, and never let two Dark tiles sit side by side.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="23" t="inlineStr">
-        <is>
-          <t>Tone column</t>
-        </is>
-      </c>
-      <c r="C53" s="24" t="inlineStr">
-        <is>
-          <t>Light = cream, Dark = ink variant, Photo = photo led cover. Check it when moving dates: swapping two posts can put two Dark tiles together.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="23" t="inlineStr">
-        <is>
-          <t>How</t>
-        </is>
-      </c>
-      <c r="C54" s="24" t="inlineStr">
-        <is>
-          <t>The single-image and carousel templates take a dark theme flag, so flipping a post is a one-line change and a re-render, not a redesign.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="B55" s="23" t="inlineStr">
-        <is>
-          <t>Sept onward</t>
-        </is>
-      </c>
-      <c r="C55" s="24" t="inlineStr">
-        <is>
-          <t>September to November posts are all Light today. Assign Dark to roughly one post per week when designing them, matching the August rhythm.</t>
+          <t>drive.google.com &gt; New &gt; File upload &gt; pick this file &gt; open with Google Sheets. Preview thumbnails and links work there.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -1288,7 +1199,11 @@
         </is>
       </c>
       <c r="N2" s="24" t="n"/>
-      <c r="O2" s="24" t="n"/>
+      <c r="O2" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-08-17-5-botox-lies-you-still</t>
+        </is>
+      </c>
       <c r="P2" s="32" t="inlineStr">
         <is>
           <t>Open folder</t>
@@ -1315,7 +1230,11 @@
       <c r="X2" s="28" t="n"/>
       <c r="Y2" s="28" t="n"/>
       <c r="Z2" s="24" t="n"/>
-      <c r="AA2" s="24" t="n"/>
+      <c r="AA2" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/RepoKing23/InstagramCarousel/blob/claude/convert-images-jpg-5jeayb/content/2026-08-17-5-botox-lies-you-still/images/gbp.png?raw=1</t>
+        </is>
+      </c>
       <c r="AB2" s="33" t="inlineStr">
         <is>
           <t>View GBP image</t>
@@ -1386,7 +1305,11 @@
         </is>
       </c>
       <c r="N3" s="24" t="n"/>
-      <c r="O3" s="24" t="n"/>
+      <c r="O3" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-08-18-service-spotlight-botox</t>
+        </is>
+      </c>
       <c r="P3" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
@@ -1413,7 +1336,11 @@
       <c r="X3" s="30" t="n"/>
       <c r="Y3" s="30" t="n"/>
       <c r="Z3" s="24" t="n"/>
-      <c r="AA3" s="24" t="n"/>
+      <c r="AA3" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/RepoKing23/InstagramCarousel/blob/claude/convert-images-jpg-5jeayb/content/2026-08-18-service-spotlight-botox/images/gbp.png?raw=1</t>
+        </is>
+      </c>
       <c r="AB3" s="33" t="inlineStr">
         <is>
           <t>View GBP image</t>
@@ -1490,7 +1417,11 @@
         </is>
       </c>
       <c r="N4" s="24" t="n"/>
-      <c r="O4" s="24" t="n"/>
+      <c r="O4" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-08-20-5-red-flags-at-a</t>
+        </is>
+      </c>
       <c r="P4" s="32" t="inlineStr">
         <is>
           <t>Open folder</t>
@@ -1602,7 +1533,11 @@
         </is>
       </c>
       <c r="N5" s="24" t="n"/>
-      <c r="O5" s="24" t="n"/>
+      <c r="O5" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-08-21-behind-the-scenes-the-prep</t>
+        </is>
+      </c>
       <c r="P5" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
@@ -1835,7 +1770,11 @@
         </is>
       </c>
       <c r="N7" s="24" t="n"/>
-      <c r="O7" s="24" t="n"/>
+      <c r="O7" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-08-24-your-first-visit-step-by</t>
+        </is>
+      </c>
       <c r="P7" s="32" t="inlineStr">
         <is>
           <t>Open folder</t>
@@ -1950,7 +1889,11 @@
         </is>
       </c>
       <c r="N8" s="24" t="n"/>
-      <c r="O8" s="24" t="n"/>
+      <c r="O8" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-08-25-why-i-do-not-post</t>
+        </is>
+      </c>
       <c r="P8" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
@@ -2063,7 +2006,11 @@
         </is>
       </c>
       <c r="N9" s="24" t="n"/>
-      <c r="O9" s="24" t="n"/>
+      <c r="O9" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-08-27-meet-np-cleo-the-face</t>
+        </is>
+      </c>
       <c r="P9" s="32" t="inlineStr">
         <is>
           <t>Open folder</t>
@@ -2174,7 +2121,11 @@
         </is>
       </c>
       <c r="N10" s="24" t="n"/>
-      <c r="O10" s="24" t="n"/>
+      <c r="O10" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-08-28-welcome-to-the-treatment-room</t>
+        </is>
+      </c>
       <c r="P10" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
@@ -2284,7 +2235,11 @@
         </is>
       </c>
       <c r="N11" s="24" t="n"/>
-      <c r="O11" s="24" t="n"/>
+      <c r="O11" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-08-29-this-or-that-rested-vs</t>
+        </is>
+      </c>
       <c r="P11" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
@@ -2397,7 +2352,11 @@
         </is>
       </c>
       <c r="N12" s="24" t="n"/>
-      <c r="O12" s="24" t="n"/>
+      <c r="O12" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-08-31-preventative-botox-when-to-actually</t>
+        </is>
+      </c>
       <c r="P12" s="32" t="inlineStr">
         <is>
           <t>Open folder</t>
@@ -2463,7 +2422,7 @@
       </c>
       <c r="F13" s="24" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="G13" s="30" t="inlineStr">
@@ -2503,7 +2462,11 @@
         </is>
       </c>
       <c r="N13" s="24" t="n"/>
-      <c r="O13" s="24" t="n"/>
+      <c r="O13" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-09-01-service-spotlight-preventative-botox</t>
+        </is>
+      </c>
       <c r="P13" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
@@ -2598,7 +2561,11 @@
         </is>
       </c>
       <c r="N14" s="24" t="n"/>
-      <c r="O14" s="24" t="n"/>
+      <c r="O14" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-09-03-what-20-units-actually-looks</t>
+        </is>
+      </c>
       <c r="P14" s="32" t="inlineStr">
         <is>
           <t>Open folder</t>
@@ -2668,7 +2635,7 @@
       </c>
       <c r="I15" s="30" t="inlineStr">
         <is>
-          <t>Meet Your Injector | Board certified. Botox obsessed. Brutally honest.</t>
+          <t>Meet Your Injector | RN(EC). Botox obsessed. Brutally honest.</t>
         </is>
       </c>
       <c r="J15" s="30" t="inlineStr">
@@ -2693,7 +2660,11 @@
         </is>
       </c>
       <c r="N15" s="24" t="n"/>
-      <c r="O15" s="24" t="n"/>
+      <c r="O15" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-09-04-meet-your-injector</t>
+        </is>
+      </c>
       <c r="P15" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
@@ -2763,7 +2734,7 @@
       </c>
       <c r="I16" s="30" t="inlineStr">
         <is>
-          <t>Quote: Prevention Beats Erasing | Brand quote card.</t>
+          <t>Quote: Prevention Beats Erasing | Prevention beats erasing. Ask your friend who started early.</t>
         </is>
       </c>
       <c r="J16" s="30" t="inlineStr">
@@ -2788,7 +2759,11 @@
         </is>
       </c>
       <c r="N16" s="24" t="n"/>
-      <c r="O16" s="24" t="n"/>
+      <c r="O16" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-09-05-quote-prevention-beats-erasing</t>
+        </is>
+      </c>
       <c r="P16" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
@@ -2843,7 +2818,7 @@
       </c>
       <c r="F17" s="24" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="G17" s="28" t="inlineStr">
@@ -2883,7 +2858,11 @@
         </is>
       </c>
       <c r="N17" s="24" t="n"/>
-      <c r="O17" s="24" t="n"/>
+      <c r="O17" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-09-07-botox-vs-dysport-the-real</t>
+        </is>
+      </c>
       <c r="P17" s="32" t="inlineStr">
         <is>
           <t>Open folder</t>
@@ -2978,7 +2957,11 @@
         </is>
       </c>
       <c r="N18" s="24" t="n"/>
-      <c r="O18" s="24" t="n"/>
+      <c r="O18" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-09-08-botox-vs-dysport-at-a</t>
+        </is>
+      </c>
       <c r="P18" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
@@ -3073,7 +3056,11 @@
         </is>
       </c>
       <c r="N19" s="24" t="n"/>
-      <c r="O19" s="24" t="n"/>
+      <c r="O19" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-09-10-botox-aftercare-the-first-48</t>
+        </is>
+      </c>
       <c r="P19" s="32" t="inlineStr">
         <is>
           <t>Open folder</t>
@@ -3168,7 +3155,11 @@
         </is>
       </c>
       <c r="N20" s="24" t="n"/>
-      <c r="O20" s="24" t="n"/>
+      <c r="O20" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-09-11-the-face-map</t>
+        </is>
+      </c>
       <c r="P20" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
@@ -3223,7 +3214,7 @@
       </c>
       <c r="F21" s="24" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="G21" s="30" t="inlineStr">
@@ -3263,7 +3254,11 @@
         </is>
       </c>
       <c r="N21" s="24" t="n"/>
-      <c r="O21" s="24" t="n"/>
+      <c r="O21" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-09-12-faq-does-botox-hurt</t>
+        </is>
+      </c>
       <c r="P21" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
@@ -3318,7 +3313,7 @@
       </c>
       <c r="F22" s="24" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="G22" s="28" t="inlineStr">
@@ -3358,7 +3353,11 @@
         </is>
       </c>
       <c r="N22" s="24" t="n"/>
-      <c r="O22" s="24" t="n"/>
+      <c r="O22" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-09-14-5-things-botox-can-t</t>
+        </is>
+      </c>
       <c r="P22" s="32" t="inlineStr">
         <is>
           <t>Open folder</t>
@@ -3453,7 +3452,11 @@
         </is>
       </c>
       <c r="N23" s="24" t="n"/>
-      <c r="O23" s="24" t="n"/>
+      <c r="O23" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-09-15-what-botox-can-t-fix</t>
+        </is>
+      </c>
       <c r="P23" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
@@ -3548,7 +3551,11 @@
         </is>
       </c>
       <c r="N24" s="24" t="n"/>
-      <c r="O24" s="24" t="n"/>
+      <c r="O24" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-09-17-still-you-just-refreshed</t>
+        </is>
+      </c>
       <c r="P24" s="32" t="inlineStr">
         <is>
           <t>Open folder</t>
@@ -3643,7 +3650,11 @@
         </is>
       </c>
       <c r="N25" s="24" t="n"/>
-      <c r="O25" s="24" t="n"/>
+      <c r="O25" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-09-18-myth-vs-truth-the-frozen</t>
+        </is>
+      </c>
       <c r="P25" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
@@ -3698,7 +3709,7 @@
       </c>
       <c r="F26" s="24" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="G26" s="30" t="inlineStr">
@@ -3713,7 +3724,7 @@
       </c>
       <c r="I26" s="30" t="inlineStr">
         <is>
-          <t>Client Words: Natural Results | Testimonial card.</t>
+          <t>Client Words: Natural Results | Nobody guessed. That was the whole point.</t>
         </is>
       </c>
       <c r="J26" s="30" t="inlineStr">
@@ -3738,7 +3749,11 @@
         </is>
       </c>
       <c r="N26" s="24" t="n"/>
-      <c r="O26" s="24" t="n"/>
+      <c r="O26" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-09-19-client-words-natural-results</t>
+        </is>
+      </c>
       <c r="P26" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
@@ -3833,7 +3848,11 @@
         </is>
       </c>
       <c r="N27" s="24" t="n"/>
-      <c r="O27" s="24" t="n"/>
+      <c r="O27" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-09-21-botox-or-filler-you-might</t>
+        </is>
+      </c>
       <c r="P27" s="32" t="inlineStr">
         <is>
           <t>Open folder</t>
@@ -3928,7 +3947,11 @@
         </is>
       </c>
       <c r="N28" s="24" t="n"/>
-      <c r="O28" s="24" t="n"/>
+      <c r="O28" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-09-22-lines-vs-volume</t>
+        </is>
+      </c>
       <c r="P28" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
@@ -4023,7 +4046,11 @@
         </is>
       </c>
       <c r="N29" s="24" t="n"/>
-      <c r="O29" s="24" t="n"/>
+      <c r="O29" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-09-24-ask-np-cleo-your-questions</t>
+        </is>
+      </c>
       <c r="P29" s="32" t="inlineStr">
         <is>
           <t>Open folder</t>
@@ -4078,7 +4105,7 @@
       </c>
       <c r="F30" s="24" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="G30" s="30" t="inlineStr">
@@ -4118,7 +4145,11 @@
         </is>
       </c>
       <c r="N30" s="24" t="n"/>
-      <c r="O30" s="24" t="n"/>
+      <c r="O30" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-09-25-your-dms-answered</t>
+        </is>
+      </c>
       <c r="P30" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
@@ -4173,7 +4204,7 @@
       </c>
       <c r="F31" s="24" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="G31" s="30" t="inlineStr">
@@ -4188,7 +4219,7 @@
       </c>
       <c r="I31" s="30" t="inlineStr">
         <is>
-          <t>Poll: What Should NP Cleo Cover Next? | Audience chooses next month's content.</t>
+          <t>Poll: What Should NP Cleo Cover Next? | You pick what I cover next month.</t>
         </is>
       </c>
       <c r="J31" s="30" t="inlineStr">
@@ -4213,7 +4244,11 @@
         </is>
       </c>
       <c r="N31" s="24" t="n"/>
-      <c r="O31" s="24" t="n"/>
+      <c r="O31" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-09-26-poll-what-should-np-cleo</t>
+        </is>
+      </c>
       <c r="P31" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
@@ -4308,7 +4343,11 @@
         </is>
       </c>
       <c r="N32" s="24" t="n"/>
-      <c r="O32" s="24" t="n"/>
+      <c r="O32" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-09-28-how-long-does-botox-really</t>
+        </is>
+      </c>
       <c r="P32" s="32" t="inlineStr">
         <is>
           <t>Open folder</t>
@@ -4403,7 +4442,11 @@
         </is>
       </c>
       <c r="N33" s="24" t="n"/>
-      <c r="O33" s="24" t="n"/>
+      <c r="O33" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-09-29-the-3-month-botox-timeline</t>
+        </is>
+      </c>
       <c r="P33" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
@@ -4498,7 +4541,11 @@
         </is>
       </c>
       <c r="N34" s="24" t="n"/>
-      <c r="O34" s="24" t="n"/>
+      <c r="O34" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-10-01-why-we-sometimes-say-no</t>
+        </is>
+      </c>
       <c r="P34" s="32" t="inlineStr">
         <is>
           <t>Open folder</t>
@@ -4553,7 +4600,7 @@
       </c>
       <c r="F35" s="24" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="G35" s="30" t="inlineStr">
@@ -4593,7 +4640,11 @@
         </is>
       </c>
       <c r="N35" s="24" t="n"/>
-      <c r="O35" s="24" t="n"/>
+      <c r="O35" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-10-02-what-i-tell-every-first</t>
+        </is>
+      </c>
       <c r="P35" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
@@ -4663,7 +4714,7 @@
       </c>
       <c r="I36" s="30" t="inlineStr">
         <is>
-          <t>Quote: No Is Protection | Brand quote card.</t>
+          <t>Quote: No Is Protection | No is a full sentence, and sometimes it is the treatment plan.</t>
         </is>
       </c>
       <c r="J36" s="30" t="inlineStr">
@@ -4688,7 +4739,11 @@
         </is>
       </c>
       <c r="N36" s="24" t="n"/>
-      <c r="O36" s="24" t="n"/>
+      <c r="O36" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-10-03-quote-no-is-protection</t>
+        </is>
+      </c>
       <c r="P36" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
@@ -4783,7 +4838,11 @@
         </is>
       </c>
       <c r="N37" s="24" t="n"/>
-      <c r="O37" s="24" t="n"/>
+      <c r="O37" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-10-05-filler-won-t-make-you</t>
+        </is>
+      </c>
       <c r="P37" s="32" t="inlineStr">
         <is>
           <t>Open folder</t>
@@ -4838,7 +4897,7 @@
       </c>
       <c r="F38" s="24" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="G38" s="30" t="inlineStr">
@@ -4878,7 +4937,11 @@
         </is>
       </c>
       <c r="N38" s="24" t="n"/>
-      <c r="O38" s="24" t="n"/>
+      <c r="O38" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-10-06-service-spotlight-dermal-filler</t>
+        </is>
+      </c>
       <c r="P38" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
@@ -4933,7 +4996,7 @@
       </c>
       <c r="F39" s="24" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Photo</t>
         </is>
       </c>
       <c r="G39" s="28" t="inlineStr">
@@ -5039,7 +5102,7 @@
       </c>
       <c r="F40" s="24" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="G40" s="30" t="inlineStr">
@@ -5079,7 +5142,11 @@
         </is>
       </c>
       <c r="N40" s="24" t="n"/>
-      <c r="O40" s="24" t="n"/>
+      <c r="O40" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-10-09-inside-the-filler-appointment</t>
+        </is>
+      </c>
       <c r="P40" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
@@ -5134,7 +5201,7 @@
       </c>
       <c r="F41" s="24" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Photo</t>
         </is>
       </c>
       <c r="G41" s="30" t="inlineStr">
@@ -5280,7 +5347,11 @@
         </is>
       </c>
       <c r="N42" s="24" t="n"/>
-      <c r="O42" s="24" t="n"/>
+      <c r="O42" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-10-12-cheek-filler-the-secret-nobody</t>
+        </is>
+      </c>
       <c r="P42" s="32" t="inlineStr">
         <is>
           <t>Open folder</t>
@@ -5375,7 +5446,11 @@
         </is>
       </c>
       <c r="N43" s="24" t="n"/>
-      <c r="O43" s="24" t="n"/>
+      <c r="O43" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-10-13-service-spotlight-cheek-filler</t>
+        </is>
+      </c>
       <c r="P43" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
@@ -5430,7 +5505,7 @@
       </c>
       <c r="F44" s="24" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Photo</t>
         </is>
       </c>
       <c r="G44" s="28" t="inlineStr">
@@ -5536,7 +5611,7 @@
       </c>
       <c r="F45" s="24" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="G45" s="30" t="inlineStr">
@@ -5576,7 +5651,11 @@
         </is>
       </c>
       <c r="N45" s="24" t="n"/>
-      <c r="O45" s="24" t="n"/>
+      <c r="O45" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-10-16-facial-balancing-101</t>
+        </is>
+      </c>
       <c r="P45" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
@@ -5671,7 +5750,11 @@
         </is>
       </c>
       <c r="N46" s="24" t="n"/>
-      <c r="O46" s="24" t="n"/>
+      <c r="O46" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-10-17-faq-how-much-filler-do</t>
+        </is>
+      </c>
       <c r="P46" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
@@ -5766,7 +5849,11 @@
         </is>
       </c>
       <c r="N47" s="24" t="n"/>
-      <c r="O47" s="24" t="n"/>
+      <c r="O47" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-10-19-filler-dissolves-here-is-the</t>
+        </is>
+      </c>
       <c r="P47" s="32" t="inlineStr">
         <is>
           <t>Open folder</t>
@@ -5821,7 +5908,7 @@
       </c>
       <c r="F48" s="24" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="G48" s="30" t="inlineStr">
@@ -5861,7 +5948,11 @@
         </is>
       </c>
       <c r="N48" s="24" t="n"/>
-      <c r="O48" s="24" t="n"/>
+      <c r="O48" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-10-20-the-filler-timeline</t>
+        </is>
+      </c>
       <c r="P48" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
@@ -5916,7 +6007,7 @@
       </c>
       <c r="F49" s="24" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Photo</t>
         </is>
       </c>
       <c r="G49" s="28" t="inlineStr">
@@ -6022,7 +6113,7 @@
       </c>
       <c r="F50" s="24" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="G50" s="30" t="inlineStr">
@@ -6062,7 +6153,11 @@
         </is>
       </c>
       <c r="N50" s="24" t="n"/>
-      <c r="O50" s="24" t="n"/>
+      <c r="O50" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-10-23-aftercare-essentials</t>
+        </is>
+      </c>
       <c r="P50" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
@@ -6117,7 +6212,7 @@
       </c>
       <c r="F51" s="24" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Photo</t>
         </is>
       </c>
       <c r="G51" s="30" t="inlineStr">
@@ -6263,7 +6358,11 @@
         </is>
       </c>
       <c r="N52" s="24" t="n"/>
-      <c r="O52" s="24" t="n"/>
+      <c r="O52" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-10-26-5-filler-lies-you-still</t>
+        </is>
+      </c>
       <c r="P52" s="32" t="inlineStr">
         <is>
           <t>Open folder</t>
@@ -6318,7 +6417,7 @@
       </c>
       <c r="F53" s="24" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="G53" s="30" t="inlineStr">
@@ -6358,7 +6457,11 @@
         </is>
       </c>
       <c r="N53" s="24" t="n"/>
-      <c r="O53" s="24" t="n"/>
+      <c r="O53" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-10-27-myth-vs-truth-filler-edition</t>
+        </is>
+      </c>
       <c r="P53" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
@@ -6453,7 +6556,11 @@
         </is>
       </c>
       <c r="N54" s="24" t="n"/>
-      <c r="O54" s="24" t="n"/>
+      <c r="O54" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-10-29-facial-balancing-why-we-treat</t>
+        </is>
+      </c>
       <c r="P54" s="32" t="inlineStr">
         <is>
           <t>Open folder</t>
@@ -6508,7 +6615,7 @@
       </c>
       <c r="F55" s="24" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Photo</t>
         </is>
       </c>
       <c r="G55" s="30" t="inlineStr">
@@ -6629,7 +6736,7 @@
       </c>
       <c r="I56" s="30" t="inlineStr">
         <is>
-          <t>Ask Anything: Filler Edition | Engagement post.</t>
+          <t>Ask Anything: Filler Edition | Ask me the filler question you have been sitting on.</t>
         </is>
       </c>
       <c r="J56" s="30" t="inlineStr">
@@ -6654,7 +6761,11 @@
         </is>
       </c>
       <c r="N56" s="24" t="n"/>
-      <c r="O56" s="24" t="n"/>
+      <c r="O56" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-10-31-ask-anything-filler-edition</t>
+        </is>
+      </c>
       <c r="P56" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
@@ -6709,7 +6820,7 @@
       </c>
       <c r="F57" s="24" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="G57" s="28" t="inlineStr">
@@ -6749,7 +6860,11 @@
         </is>
       </c>
       <c r="N57" s="24" t="n"/>
-      <c r="O57" s="24" t="n"/>
+      <c r="O57" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-11-02-rested-by-the-holidays-your</t>
+        </is>
+      </c>
       <c r="P57" s="32" t="inlineStr">
         <is>
           <t>Open folder</t>
@@ -6804,7 +6919,7 @@
       </c>
       <c r="F58" s="24" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="G58" s="30" t="inlineStr">
@@ -6844,7 +6959,11 @@
         </is>
       </c>
       <c r="N58" s="24" t="n"/>
-      <c r="O58" s="24" t="n"/>
+      <c r="O58" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-11-03-holiday-countdown-book-by-these</t>
+        </is>
+      </c>
       <c r="P58" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
@@ -6939,7 +7058,11 @@
         </is>
       </c>
       <c r="N59" s="24" t="n"/>
-      <c r="O59" s="24" t="n"/>
+      <c r="O59" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-11-05-party-season-prep-what-to</t>
+        </is>
+      </c>
       <c r="P59" s="32" t="inlineStr">
         <is>
           <t>Open folder</t>
@@ -6994,7 +7117,7 @@
       </c>
       <c r="F60" s="24" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Photo</t>
         </is>
       </c>
       <c r="G60" s="30" t="inlineStr">
@@ -7140,7 +7263,11 @@
         </is>
       </c>
       <c r="N61" s="24" t="n"/>
-      <c r="O61" s="24" t="n"/>
+      <c r="O61" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-11-07-quote-book-the-appointment</t>
+        </is>
+      </c>
       <c r="P61" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
@@ -7195,7 +7322,7 @@
       </c>
       <c r="F62" s="24" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="G62" s="28" t="inlineStr">
@@ -7235,7 +7362,11 @@
         </is>
       </c>
       <c r="N62" s="24" t="n"/>
-      <c r="O62" s="24" t="n"/>
+      <c r="O62" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-11-09-the-gift-of-glow-gift</t>
+        </is>
+      </c>
       <c r="P62" s="32" t="inlineStr">
         <is>
           <t>Open folder</t>
@@ -7330,7 +7461,11 @@
         </is>
       </c>
       <c r="N63" s="24" t="n"/>
-      <c r="O63" s="24" t="n"/>
+      <c r="O63" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-11-10-gift-certificates-are-here</t>
+        </is>
+      </c>
       <c r="P63" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
@@ -7425,7 +7560,11 @@
         </is>
       </c>
       <c r="N64" s="24" t="n"/>
-      <c r="O64" s="24" t="n"/>
+      <c r="O64" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-11-12-3-months-of-honest-answers</t>
+        </is>
+      </c>
       <c r="P64" s="32" t="inlineStr">
         <is>
           <t>Open folder</t>
@@ -7495,7 +7634,7 @@
       </c>
       <c r="I65" s="30" t="inlineStr">
         <is>
-          <t>Thank You: 3 Months of Honest Aesthetics | Gratitude post.</t>
+          <t>Thank You: 3 Months of Honest Aesthetics | Three months of honest answers. Thank you for every one.</t>
         </is>
       </c>
       <c r="J65" s="30" t="inlineStr">
@@ -7520,7 +7659,11 @@
         </is>
       </c>
       <c r="N65" s="24" t="n"/>
-      <c r="O65" s="24" t="n"/>
+      <c r="O65" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-11-13-thank-you-3-months-of</t>
+        </is>
+      </c>
       <c r="P65" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>
@@ -7575,7 +7718,7 @@
       </c>
       <c r="F66" s="24" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="G66" s="30" t="inlineStr">
@@ -7615,7 +7758,11 @@
         </is>
       </c>
       <c r="N66" s="24" t="n"/>
-      <c r="O66" s="24" t="n"/>
+      <c r="O66" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-11-14-tag-someone-who-deserves-a</t>
+        </is>
+      </c>
       <c r="P66" s="34" t="inlineStr">
         <is>
           <t>Open folder</t>

--- a/strategy/ig-content-strategy.xlsx
+++ b/strategy/ig-content-strategy.xlsx
@@ -1211,11 +1211,11 @@
       </c>
       <c r="Q2" s="33" t="inlineStr">
         <is>
-          <t>View 8 slides</t>
+          <t>View 8 slides (jpg)</t>
         </is>
       </c>
       <c r="R2" s="24">
-        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-08-17-5-botox-lies-you-still/images/slide-1.png")</f>
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-08-17-5-botox-lies-you-still/images/slide-1.jpg")</f>
         <v/>
       </c>
       <c r="S2" s="28" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="AB2" s="33" t="inlineStr">
         <is>
-          <t>View GBP image</t>
+          <t>View GBP image (jpg)</t>
         </is>
       </c>
     </row>
@@ -1317,11 +1317,11 @@
       </c>
       <c r="Q3" s="33" t="inlineStr">
         <is>
-          <t>View image</t>
+          <t>View image (jpg)</t>
         </is>
       </c>
       <c r="R3" s="24">
-        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-08-18-service-spotlight-botox/images/post.png")</f>
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-08-18-service-spotlight-botox/images/post.jpg")</f>
         <v/>
       </c>
       <c r="S3" s="30" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="AB3" s="33" t="inlineStr">
         <is>
-          <t>View GBP image</t>
+          <t>View GBP image (jpg)</t>
         </is>
       </c>
     </row>
@@ -1429,11 +1429,11 @@
       </c>
       <c r="Q4" s="33" t="inlineStr">
         <is>
-          <t>View 7 slides</t>
+          <t>View 7 slides (jpg)</t>
         </is>
       </c>
       <c r="R4" s="24">
-        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-08-20-5-red-flags-at-a/images/slide-1.png")</f>
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-08-20-5-red-flags-at-a/images/slide-1.jpg")</f>
         <v/>
       </c>
       <c r="S4" s="28" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="AB4" s="33" t="inlineStr">
         <is>
-          <t>View GBP image</t>
+          <t>View GBP image (jpg)</t>
         </is>
       </c>
     </row>
@@ -1545,11 +1545,11 @@
       </c>
       <c r="Q5" s="33" t="inlineStr">
         <is>
-          <t>View image</t>
+          <t>View image (jpg)</t>
         </is>
       </c>
       <c r="R5" s="24">
-        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-08-21-behind-the-scenes-the-prep/images/post.png")</f>
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-08-21-behind-the-scenes-the-prep/images/post.jpg")</f>
         <v/>
       </c>
       <c r="S5" s="30" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="AB5" s="33" t="inlineStr">
         <is>
-          <t>View GBP image</t>
+          <t>View GBP image (jpg)</t>
         </is>
       </c>
     </row>
@@ -1665,11 +1665,11 @@
       </c>
       <c r="Q6" s="33" t="inlineStr">
         <is>
-          <t>View image</t>
+          <t>View image (jpg)</t>
         </is>
       </c>
       <c r="R6" s="24">
-        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-08-22-great-work-is-invisible/images/before-after-result.png")</f>
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-08-22-great-work-is-invisible/images/before-after-result.jpg")</f>
         <v/>
       </c>
       <c r="S6" s="30" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="AB6" s="33" t="inlineStr">
         <is>
-          <t>View GBP image</t>
+          <t>View GBP image (jpg)</t>
         </is>
       </c>
     </row>
@@ -1782,11 +1782,11 @@
       </c>
       <c r="Q7" s="33" t="inlineStr">
         <is>
-          <t>View 8 slides</t>
+          <t>View 8 slides (jpg)</t>
         </is>
       </c>
       <c r="R7" s="24">
-        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-08-24-your-first-visit-step-by/images/slide-1.png")</f>
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-08-24-your-first-visit-step-by/images/slide-1.jpg")</f>
         <v/>
       </c>
       <c r="S7" s="28" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="AB7" s="33" t="inlineStr">
         <is>
-          <t>View GBP image</t>
+          <t>View GBP image (jpg)</t>
         </is>
       </c>
     </row>
@@ -1901,11 +1901,11 @@
       </c>
       <c r="Q8" s="33" t="inlineStr">
         <is>
-          <t>View image</t>
+          <t>View image (jpg)</t>
         </is>
       </c>
       <c r="R8" s="24">
-        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-08-25-why-i-do-not-post/images/post.png")</f>
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-08-25-why-i-do-not-post/images/post.jpg")</f>
         <v/>
       </c>
       <c r="S8" s="30" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="AB8" s="33" t="inlineStr">
         <is>
-          <t>View GBP image</t>
+          <t>View GBP image (jpg)</t>
         </is>
       </c>
     </row>
@@ -2018,11 +2018,11 @@
       </c>
       <c r="Q9" s="33" t="inlineStr">
         <is>
-          <t>View 5 slides</t>
+          <t>View 5 slides (jpg)</t>
         </is>
       </c>
       <c r="R9" s="24">
-        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-08-27-meet-np-cleo-the-face/images/slide-1.png")</f>
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-08-27-meet-np-cleo-the-face/images/slide-1.jpg")</f>
         <v/>
       </c>
       <c r="S9" s="28" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="AB9" s="33" t="inlineStr">
         <is>
-          <t>View GBP image</t>
+          <t>View GBP image (jpg)</t>
         </is>
       </c>
     </row>
@@ -2133,11 +2133,11 @@
       </c>
       <c r="Q10" s="33" t="inlineStr">
         <is>
-          <t>View image</t>
+          <t>View image (jpg)</t>
         </is>
       </c>
       <c r="R10" s="24">
-        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-08-28-welcome-to-the-treatment-room/images/post.png")</f>
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-08-28-welcome-to-the-treatment-room/images/post.jpg")</f>
         <v/>
       </c>
       <c r="S10" s="30" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="AB10" s="33" t="inlineStr">
         <is>
-          <t>View GBP image</t>
+          <t>View GBP image (jpg)</t>
         </is>
       </c>
     </row>
@@ -2247,11 +2247,11 @@
       </c>
       <c r="Q11" s="33" t="inlineStr">
         <is>
-          <t>View image</t>
+          <t>View image (jpg)</t>
         </is>
       </c>
       <c r="R11" s="24">
-        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-08-29-this-or-that-rested-vs/images/post.png")</f>
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-08-29-this-or-that-rested-vs/images/post.jpg")</f>
         <v/>
       </c>
       <c r="S11" s="30" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="AB11" s="33" t="inlineStr">
         <is>
-          <t>View GBP image</t>
+          <t>View GBP image (jpg)</t>
         </is>
       </c>
     </row>
@@ -2364,11 +2364,11 @@
       </c>
       <c r="Q12" s="33" t="inlineStr">
         <is>
-          <t>View 7 slides</t>
+          <t>View 7 slides (jpg)</t>
         </is>
       </c>
       <c r="R12" s="24">
-        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-08-31-preventative-botox-when-to-actually/images/slide-1.png")</f>
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-08-31-preventative-botox-when-to-actually/images/slide-1.jpg")</f>
         <v/>
       </c>
       <c r="S12" s="28" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="AB12" s="33" t="inlineStr">
         <is>
-          <t>View GBP image</t>
+          <t>View GBP image (jpg)</t>
         </is>
       </c>
     </row>
@@ -5052,11 +5052,11 @@
       </c>
       <c r="Q39" s="33" t="inlineStr">
         <is>
-          <t>View image</t>
+          <t>View image (jpg)</t>
         </is>
       </c>
       <c r="R39" s="24">
-        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-10-08-lip-filler-natural-vs-overdone/images/before-after-result.png")</f>
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-10-08-lip-filler-natural-vs-overdone/images/before-after-result.jpg")</f>
         <v/>
       </c>
       <c r="S39" s="28" t="inlineStr">
@@ -5257,11 +5257,11 @@
       </c>
       <c r="Q41" s="33" t="inlineStr">
         <is>
-          <t>View image</t>
+          <t>View image (jpg)</t>
         </is>
       </c>
       <c r="R41" s="24">
-        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-10-10-subtle-is-the-new-dramatic/images/before-after-result.png")</f>
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-10-10-subtle-is-the-new-dramatic/images/before-after-result.jpg")</f>
         <v/>
       </c>
       <c r="S41" s="30" t="inlineStr">
@@ -5561,11 +5561,11 @@
       </c>
       <c r="Q44" s="33" t="inlineStr">
         <is>
-          <t>View 7 slides</t>
+          <t>View 7 slides (jpg)</t>
         </is>
       </c>
       <c r="R44" s="24">
-        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-10-15-real-lips-real-results/images/slide-1.png")</f>
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-10-15-real-lips-real-results/images/slide-1.jpg")</f>
         <v/>
       </c>
       <c r="S44" s="28" t="inlineStr">
@@ -6063,11 +6063,11 @@
       </c>
       <c r="Q49" s="33" t="inlineStr">
         <is>
-          <t>View image</t>
+          <t>View image (jpg)</t>
         </is>
       </c>
       <c r="R49" s="24">
-        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-10-22-lip-filler-aftercare-your-first/images/day-zero-before-after.png")</f>
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-10-22-lip-filler-aftercare-your-first/images/day-zero-before-after.jpg")</f>
         <v/>
       </c>
       <c r="S49" s="28" t="inlineStr">
@@ -6268,11 +6268,11 @@
       </c>
       <c r="Q51" s="33" t="inlineStr">
         <is>
-          <t>View image</t>
+          <t>View image (jpg)</t>
         </is>
       </c>
       <c r="R51" s="24">
-        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-10-24-client-words-the-lip-glow/images/before-after-result.png")</f>
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-10-24-client-words-the-lip-glow/images/before-after-result.jpg")</f>
         <v/>
       </c>
       <c r="S51" s="30" t="inlineStr">
@@ -6671,11 +6671,11 @@
       </c>
       <c r="Q55" s="33" t="inlineStr">
         <is>
-          <t>View image</t>
+          <t>View image (jpg)</t>
         </is>
       </c>
       <c r="R55" s="24">
-        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-10-30-one-syringe-balanced-lips/images/before-after-result.png")</f>
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-10-30-one-syringe-balanced-lips/images/before-after-result.jpg")</f>
         <v/>
       </c>
       <c r="S55" s="30" t="inlineStr">
@@ -7173,11 +7173,11 @@
       </c>
       <c r="Q60" s="33" t="inlineStr">
         <is>
-          <t>View 7 slides</t>
+          <t>View 7 slides (jpg)</t>
         </is>
       </c>
       <c r="R60" s="24">
-        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-11-06-one-result-every-angle/images/slide-1.png")</f>
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-11-06-one-result-every-angle/images/slide-1.jpg")</f>
         <v/>
       </c>
       <c r="S60" s="30" t="inlineStr">
@@ -7802,98 +7802,127 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA2" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P3" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA3" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O4" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P4" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA4" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O5" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P5" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA5" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O6" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P6" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA6" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P7" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA7" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O8" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P8" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA8" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P9" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA9" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P10" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA10" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P11" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA11" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P12" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA12" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O39" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P39" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P41" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P44" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O45" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O46" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P49" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O50" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O51" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P51" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O52" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O53" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O54" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O55" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P55" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O56" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O57" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O58" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O59" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O60" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P60" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O61" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O62" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O63" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O64" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O65" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O66" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA2" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB2" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P3" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA3" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB3" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O4" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P4" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q4" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA4" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB4" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O5" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P5" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q5" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA5" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB5" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O6" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P6" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q6" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA6" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB6" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P7" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA7" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB7" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O8" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P8" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA8" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB8" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P9" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA9" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB9" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P10" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA10" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB10" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P11" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA11" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB11" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P12" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA12" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB12" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O39" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P39" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q39" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P41" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q41" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P44" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q44" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O45" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O46" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P49" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q49" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O50" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O51" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P51" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q51" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O52" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O53" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O54" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O55" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P55" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q55" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O56" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O57" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O58" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O59" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O60" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P60" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q60" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O61" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O62" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O63" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O64" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O65" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O66" r:id="rId123"/>
   </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/strategy/ig-content-strategy.xlsx
+++ b/strategy/ig-content-strategy.xlsx
@@ -1201,7 +1201,7 @@
       <c r="N2" s="24" t="n"/>
       <c r="O2" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-08-17-5-botox-lies-you-still</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-08-17-5-botox-lies-you-still</t>
         </is>
       </c>
       <c r="P2" s="32" t="inlineStr">
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="R2" s="24">
-        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-08-17-5-botox-lies-you-still/images/slide-1.jpg")</f>
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/image-size-format-instagram-855nfc/content/2026-08-17-5-botox-lies-you-still/images/slide-1.jpg")</f>
         <v/>
       </c>
       <c r="S2" s="28" t="inlineStr">
@@ -1232,7 +1232,7 @@
       <c r="Z2" s="24" t="n"/>
       <c r="AA2" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/blob/claude/convert-images-jpg-5jeayb/content/2026-08-17-5-botox-lies-you-still/images/gbp.png?raw=1</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/blob/claude/image-size-format-instagram-855nfc/content/2026-08-17-5-botox-lies-you-still/images/gbp.jpg?raw=1</t>
         </is>
       </c>
       <c r="AB2" s="33" t="inlineStr">
@@ -1307,7 +1307,7 @@
       <c r="N3" s="24" t="n"/>
       <c r="O3" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-08-18-service-spotlight-botox</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-08-18-service-spotlight-botox</t>
         </is>
       </c>
       <c r="P3" s="34" t="inlineStr">
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="R3" s="24">
-        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-08-18-service-spotlight-botox/images/post.jpg")</f>
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/image-size-format-instagram-855nfc/content/2026-08-18-service-spotlight-botox/images/post.jpg")</f>
         <v/>
       </c>
       <c r="S3" s="30" t="inlineStr">
@@ -1338,7 +1338,7 @@
       <c r="Z3" s="24" t="n"/>
       <c r="AA3" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/blob/claude/convert-images-jpg-5jeayb/content/2026-08-18-service-spotlight-botox/images/gbp.png?raw=1</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/blob/claude/image-size-format-instagram-855nfc/content/2026-08-18-service-spotlight-botox/images/gbp.jpg?raw=1</t>
         </is>
       </c>
       <c r="AB3" s="33" t="inlineStr">
@@ -1419,7 +1419,7 @@
       <c r="N4" s="24" t="n"/>
       <c r="O4" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-08-20-5-red-flags-at-a</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-08-20-5-red-flags-at-a</t>
         </is>
       </c>
       <c r="P4" s="32" t="inlineStr">
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="R4" s="24">
-        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-08-20-5-red-flags-at-a/images/slide-1.jpg")</f>
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/image-size-format-instagram-855nfc/content/2026-08-20-5-red-flags-at-a/images/slide-1.jpg")</f>
         <v/>
       </c>
       <c r="S4" s="28" t="inlineStr">
@@ -1535,7 +1535,7 @@
       <c r="N5" s="24" t="n"/>
       <c r="O5" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-08-21-behind-the-scenes-the-prep</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-08-21-behind-the-scenes-the-prep</t>
         </is>
       </c>
       <c r="P5" s="34" t="inlineStr">
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="R5" s="24">
-        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-08-21-behind-the-scenes-the-prep/images/post.jpg")</f>
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/image-size-format-instagram-855nfc/content/2026-08-21-behind-the-scenes-the-prep/images/post.jpg")</f>
         <v/>
       </c>
       <c r="S5" s="30" t="inlineStr">
@@ -1669,7 +1669,7 @@
         </is>
       </c>
       <c r="R6" s="24">
-        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-08-22-great-work-is-invisible/images/before-after-result.jpg")</f>
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/image-size-format-instagram-855nfc/content/2026-08-22-great-work-is-invisible/images/before-after-result.jpg")</f>
         <v/>
       </c>
       <c r="S6" s="30" t="inlineStr">
@@ -1772,7 +1772,7 @@
       <c r="N7" s="24" t="n"/>
       <c r="O7" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-08-24-your-first-visit-step-by</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-08-24-your-first-visit-step-by</t>
         </is>
       </c>
       <c r="P7" s="32" t="inlineStr">
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="R7" s="24">
-        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-08-24-your-first-visit-step-by/images/slide-1.jpg")</f>
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/image-size-format-instagram-855nfc/content/2026-08-24-your-first-visit-step-by/images/slide-1.jpg")</f>
         <v/>
       </c>
       <c r="S7" s="28" t="inlineStr">
@@ -1891,7 +1891,7 @@
       <c r="N8" s="24" t="n"/>
       <c r="O8" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-08-25-why-i-do-not-post</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-08-25-why-i-do-not-post</t>
         </is>
       </c>
       <c r="P8" s="34" t="inlineStr">
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="R8" s="24">
-        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-08-25-why-i-do-not-post/images/post.jpg")</f>
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/image-size-format-instagram-855nfc/content/2026-08-25-why-i-do-not-post/images/post.jpg")</f>
         <v/>
       </c>
       <c r="S8" s="30" t="inlineStr">
@@ -2008,7 +2008,7 @@
       <c r="N9" s="24" t="n"/>
       <c r="O9" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-08-27-meet-np-cleo-the-face</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-08-27-meet-np-cleo-the-face</t>
         </is>
       </c>
       <c r="P9" s="32" t="inlineStr">
@@ -2022,7 +2022,7 @@
         </is>
       </c>
       <c r="R9" s="24">
-        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-08-27-meet-np-cleo-the-face/images/slide-1.jpg")</f>
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/image-size-format-instagram-855nfc/content/2026-08-27-meet-np-cleo-the-face/images/slide-1.jpg")</f>
         <v/>
       </c>
       <c r="S9" s="28" t="inlineStr">
@@ -2123,7 +2123,7 @@
       <c r="N10" s="24" t="n"/>
       <c r="O10" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-08-28-welcome-to-the-treatment-room</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-08-28-welcome-to-the-treatment-room</t>
         </is>
       </c>
       <c r="P10" s="34" t="inlineStr">
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="R10" s="24">
-        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-08-28-welcome-to-the-treatment-room/images/post.jpg")</f>
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/image-size-format-instagram-855nfc/content/2026-08-28-welcome-to-the-treatment-room/images/post.jpg")</f>
         <v/>
       </c>
       <c r="S10" s="30" t="inlineStr">
@@ -2237,7 +2237,7 @@
       <c r="N11" s="24" t="n"/>
       <c r="O11" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-08-29-this-or-that-rested-vs</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-08-29-this-or-that-rested-vs</t>
         </is>
       </c>
       <c r="P11" s="34" t="inlineStr">
@@ -2251,7 +2251,7 @@
         </is>
       </c>
       <c r="R11" s="24">
-        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-08-29-this-or-that-rested-vs/images/post.jpg")</f>
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/image-size-format-instagram-855nfc/content/2026-08-29-this-or-that-rested-vs/images/post.jpg")</f>
         <v/>
       </c>
       <c r="S11" s="30" t="inlineStr">
@@ -2354,7 +2354,7 @@
       <c r="N12" s="24" t="n"/>
       <c r="O12" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-08-31-preventative-botox-when-to-actually</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-08-31-preventative-botox-when-to-actually</t>
         </is>
       </c>
       <c r="P12" s="32" t="inlineStr">
@@ -2368,7 +2368,7 @@
         </is>
       </c>
       <c r="R12" s="24">
-        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-08-31-preventative-botox-when-to-actually/images/slide-1.jpg")</f>
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/image-size-format-instagram-855nfc/content/2026-08-31-preventative-botox-when-to-actually/images/slide-1.jpg")</f>
         <v/>
       </c>
       <c r="S12" s="28" t="inlineStr">
@@ -2464,7 +2464,7 @@
       <c r="N13" s="24" t="n"/>
       <c r="O13" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-09-01-service-spotlight-preventative-botox</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-09-01-service-spotlight-preventative-botox</t>
         </is>
       </c>
       <c r="P13" s="34" t="inlineStr">
@@ -2563,7 +2563,7 @@
       <c r="N14" s="24" t="n"/>
       <c r="O14" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-09-03-what-20-units-actually-looks</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-09-03-what-20-units-actually-looks</t>
         </is>
       </c>
       <c r="P14" s="32" t="inlineStr">
@@ -2662,7 +2662,7 @@
       <c r="N15" s="24" t="n"/>
       <c r="O15" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-09-04-meet-your-injector</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-09-04-meet-your-injector</t>
         </is>
       </c>
       <c r="P15" s="34" t="inlineStr">
@@ -2761,7 +2761,7 @@
       <c r="N16" s="24" t="n"/>
       <c r="O16" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-09-05-quote-prevention-beats-erasing</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-09-05-quote-prevention-beats-erasing</t>
         </is>
       </c>
       <c r="P16" s="34" t="inlineStr">
@@ -2860,7 +2860,7 @@
       <c r="N17" s="24" t="n"/>
       <c r="O17" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-09-07-botox-vs-dysport-the-real</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-09-07-botox-vs-dysport-the-real</t>
         </is>
       </c>
       <c r="P17" s="32" t="inlineStr">
@@ -2959,7 +2959,7 @@
       <c r="N18" s="24" t="n"/>
       <c r="O18" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-09-08-botox-vs-dysport-at-a</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-09-08-botox-vs-dysport-at-a</t>
         </is>
       </c>
       <c r="P18" s="34" t="inlineStr">
@@ -3058,7 +3058,7 @@
       <c r="N19" s="24" t="n"/>
       <c r="O19" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-09-10-botox-aftercare-the-first-48</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-09-10-botox-aftercare-the-first-48</t>
         </is>
       </c>
       <c r="P19" s="32" t="inlineStr">
@@ -3157,7 +3157,7 @@
       <c r="N20" s="24" t="n"/>
       <c r="O20" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-09-11-the-face-map</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-09-11-the-face-map</t>
         </is>
       </c>
       <c r="P20" s="34" t="inlineStr">
@@ -3256,7 +3256,7 @@
       <c r="N21" s="24" t="n"/>
       <c r="O21" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-09-12-faq-does-botox-hurt</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-09-12-faq-does-botox-hurt</t>
         </is>
       </c>
       <c r="P21" s="34" t="inlineStr">
@@ -3355,7 +3355,7 @@
       <c r="N22" s="24" t="n"/>
       <c r="O22" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-09-14-5-things-botox-can-t</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-09-14-5-things-botox-can-t</t>
         </is>
       </c>
       <c r="P22" s="32" t="inlineStr">
@@ -3454,7 +3454,7 @@
       <c r="N23" s="24" t="n"/>
       <c r="O23" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-09-15-what-botox-can-t-fix</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-09-15-what-botox-can-t-fix</t>
         </is>
       </c>
       <c r="P23" s="34" t="inlineStr">
@@ -3553,7 +3553,7 @@
       <c r="N24" s="24" t="n"/>
       <c r="O24" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-09-17-still-you-just-refreshed</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-09-17-still-you-just-refreshed</t>
         </is>
       </c>
       <c r="P24" s="32" t="inlineStr">
@@ -3652,7 +3652,7 @@
       <c r="N25" s="24" t="n"/>
       <c r="O25" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-09-18-myth-vs-truth-the-frozen</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-09-18-myth-vs-truth-the-frozen</t>
         </is>
       </c>
       <c r="P25" s="34" t="inlineStr">
@@ -3751,7 +3751,7 @@
       <c r="N26" s="24" t="n"/>
       <c r="O26" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-09-19-client-words-natural-results</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-09-19-client-words-natural-results</t>
         </is>
       </c>
       <c r="P26" s="34" t="inlineStr">
@@ -3850,7 +3850,7 @@
       <c r="N27" s="24" t="n"/>
       <c r="O27" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-09-21-botox-or-filler-you-might</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-09-21-botox-or-filler-you-might</t>
         </is>
       </c>
       <c r="P27" s="32" t="inlineStr">
@@ -3949,7 +3949,7 @@
       <c r="N28" s="24" t="n"/>
       <c r="O28" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-09-22-lines-vs-volume</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-09-22-lines-vs-volume</t>
         </is>
       </c>
       <c r="P28" s="34" t="inlineStr">
@@ -4048,7 +4048,7 @@
       <c r="N29" s="24" t="n"/>
       <c r="O29" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-09-24-ask-np-cleo-your-questions</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-09-24-ask-np-cleo-your-questions</t>
         </is>
       </c>
       <c r="P29" s="32" t="inlineStr">
@@ -4147,7 +4147,7 @@
       <c r="N30" s="24" t="n"/>
       <c r="O30" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-09-25-your-dms-answered</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-09-25-your-dms-answered</t>
         </is>
       </c>
       <c r="P30" s="34" t="inlineStr">
@@ -4246,7 +4246,7 @@
       <c r="N31" s="24" t="n"/>
       <c r="O31" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-09-26-poll-what-should-np-cleo</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-09-26-poll-what-should-np-cleo</t>
         </is>
       </c>
       <c r="P31" s="34" t="inlineStr">
@@ -4345,7 +4345,7 @@
       <c r="N32" s="24" t="n"/>
       <c r="O32" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-09-28-how-long-does-botox-really</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-09-28-how-long-does-botox-really</t>
         </is>
       </c>
       <c r="P32" s="32" t="inlineStr">
@@ -4444,7 +4444,7 @@
       <c r="N33" s="24" t="n"/>
       <c r="O33" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-09-29-the-3-month-botox-timeline</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-09-29-the-3-month-botox-timeline</t>
         </is>
       </c>
       <c r="P33" s="34" t="inlineStr">
@@ -4543,7 +4543,7 @@
       <c r="N34" s="24" t="n"/>
       <c r="O34" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-10-01-why-we-sometimes-say-no</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-10-01-why-we-sometimes-say-no</t>
         </is>
       </c>
       <c r="P34" s="32" t="inlineStr">
@@ -4642,7 +4642,7 @@
       <c r="N35" s="24" t="n"/>
       <c r="O35" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-10-02-what-i-tell-every-first</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-10-02-what-i-tell-every-first</t>
         </is>
       </c>
       <c r="P35" s="34" t="inlineStr">
@@ -4741,7 +4741,7 @@
       <c r="N36" s="24" t="n"/>
       <c r="O36" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-10-03-quote-no-is-protection</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-10-03-quote-no-is-protection</t>
         </is>
       </c>
       <c r="P36" s="34" t="inlineStr">
@@ -4840,7 +4840,7 @@
       <c r="N37" s="24" t="n"/>
       <c r="O37" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-10-05-filler-won-t-make-you</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-10-05-filler-won-t-make-you</t>
         </is>
       </c>
       <c r="P37" s="32" t="inlineStr">
@@ -4939,7 +4939,7 @@
       <c r="N38" s="24" t="n"/>
       <c r="O38" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-10-06-service-spotlight-dermal-filler</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-10-06-service-spotlight-dermal-filler</t>
         </is>
       </c>
       <c r="P38" s="34" t="inlineStr">
@@ -5056,7 +5056,7 @@
         </is>
       </c>
       <c r="R39" s="24">
-        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-10-08-lip-filler-natural-vs-overdone/images/before-after-result.jpg")</f>
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/image-size-format-instagram-855nfc/content/2026-10-08-lip-filler-natural-vs-overdone/images/before-after-result.jpg")</f>
         <v/>
       </c>
       <c r="S39" s="28" t="inlineStr">
@@ -5144,7 +5144,7 @@
       <c r="N40" s="24" t="n"/>
       <c r="O40" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-10-09-inside-the-filler-appointment</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-10-09-inside-the-filler-appointment</t>
         </is>
       </c>
       <c r="P40" s="34" t="inlineStr">
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="R41" s="24">
-        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-10-10-subtle-is-the-new-dramatic/images/before-after-result.jpg")</f>
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/image-size-format-instagram-855nfc/content/2026-10-10-subtle-is-the-new-dramatic/images/before-after-result.jpg")</f>
         <v/>
       </c>
       <c r="S41" s="30" t="inlineStr">
@@ -5349,7 +5349,7 @@
       <c r="N42" s="24" t="n"/>
       <c r="O42" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-10-12-cheek-filler-the-secret-nobody</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-10-12-cheek-filler-the-secret-nobody</t>
         </is>
       </c>
       <c r="P42" s="32" t="inlineStr">
@@ -5448,7 +5448,7 @@
       <c r="N43" s="24" t="n"/>
       <c r="O43" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-10-13-service-spotlight-cheek-filler</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-10-13-service-spotlight-cheek-filler</t>
         </is>
       </c>
       <c r="P43" s="34" t="inlineStr">
@@ -5565,7 +5565,7 @@
         </is>
       </c>
       <c r="R44" s="24">
-        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-10-15-real-lips-real-results/images/slide-1.jpg")</f>
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/image-size-format-instagram-855nfc/content/2026-10-15-real-lips-real-results/images/slide-1.jpg")</f>
         <v/>
       </c>
       <c r="S44" s="28" t="inlineStr">
@@ -5653,7 +5653,7 @@
       <c r="N45" s="24" t="n"/>
       <c r="O45" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-10-16-facial-balancing-101</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-10-16-facial-balancing-101</t>
         </is>
       </c>
       <c r="P45" s="34" t="inlineStr">
@@ -5752,7 +5752,7 @@
       <c r="N46" s="24" t="n"/>
       <c r="O46" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-10-17-faq-how-much-filler-do</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-10-17-faq-how-much-filler-do</t>
         </is>
       </c>
       <c r="P46" s="34" t="inlineStr">
@@ -5851,7 +5851,7 @@
       <c r="N47" s="24" t="n"/>
       <c r="O47" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-10-19-filler-dissolves-here-is-the</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-10-19-filler-dissolves-here-is-the</t>
         </is>
       </c>
       <c r="P47" s="32" t="inlineStr">
@@ -5950,7 +5950,7 @@
       <c r="N48" s="24" t="n"/>
       <c r="O48" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-10-20-the-filler-timeline</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-10-20-the-filler-timeline</t>
         </is>
       </c>
       <c r="P48" s="34" t="inlineStr">
@@ -6067,7 +6067,7 @@
         </is>
       </c>
       <c r="R49" s="24">
-        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-10-22-lip-filler-aftercare-your-first/images/day-zero-before-after.jpg")</f>
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/image-size-format-instagram-855nfc/content/2026-10-22-lip-filler-aftercare-your-first/images/day-zero-before-after.jpg")</f>
         <v/>
       </c>
       <c r="S49" s="28" t="inlineStr">
@@ -6155,7 +6155,7 @@
       <c r="N50" s="24" t="n"/>
       <c r="O50" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-10-23-aftercare-essentials</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-10-23-aftercare-essentials</t>
         </is>
       </c>
       <c r="P50" s="34" t="inlineStr">
@@ -6272,7 +6272,7 @@
         </is>
       </c>
       <c r="R51" s="24">
-        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-10-24-client-words-the-lip-glow/images/before-after-result.jpg")</f>
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/image-size-format-instagram-855nfc/content/2026-10-24-client-words-the-lip-glow/images/before-after-result.jpg")</f>
         <v/>
       </c>
       <c r="S51" s="30" t="inlineStr">
@@ -6360,7 +6360,7 @@
       <c r="N52" s="24" t="n"/>
       <c r="O52" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-10-26-5-filler-lies-you-still</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-10-26-5-filler-lies-you-still</t>
         </is>
       </c>
       <c r="P52" s="32" t="inlineStr">
@@ -6459,7 +6459,7 @@
       <c r="N53" s="24" t="n"/>
       <c r="O53" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-10-27-myth-vs-truth-filler-edition</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-10-27-myth-vs-truth-filler-edition</t>
         </is>
       </c>
       <c r="P53" s="34" t="inlineStr">
@@ -6558,7 +6558,7 @@
       <c r="N54" s="24" t="n"/>
       <c r="O54" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-10-29-facial-balancing-why-we-treat</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-10-29-facial-balancing-why-we-treat</t>
         </is>
       </c>
       <c r="P54" s="32" t="inlineStr">
@@ -6675,7 +6675,7 @@
         </is>
       </c>
       <c r="R55" s="24">
-        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-10-30-one-syringe-balanced-lips/images/before-after-result.jpg")</f>
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/image-size-format-instagram-855nfc/content/2026-10-30-one-syringe-balanced-lips/images/before-after-result.jpg")</f>
         <v/>
       </c>
       <c r="S55" s="30" t="inlineStr">
@@ -6763,7 +6763,7 @@
       <c r="N56" s="24" t="n"/>
       <c r="O56" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-10-31-ask-anything-filler-edition</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-10-31-ask-anything-filler-edition</t>
         </is>
       </c>
       <c r="P56" s="34" t="inlineStr">
@@ -6862,7 +6862,7 @@
       <c r="N57" s="24" t="n"/>
       <c r="O57" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-11-02-rested-by-the-holidays-your</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-11-02-rested-by-the-holidays-your</t>
         </is>
       </c>
       <c r="P57" s="32" t="inlineStr">
@@ -6961,7 +6961,7 @@
       <c r="N58" s="24" t="n"/>
       <c r="O58" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-11-03-holiday-countdown-book-by-these</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-11-03-holiday-countdown-book-by-these</t>
         </is>
       </c>
       <c r="P58" s="34" t="inlineStr">
@@ -7060,7 +7060,7 @@
       <c r="N59" s="24" t="n"/>
       <c r="O59" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-11-05-party-season-prep-what-to</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-11-05-party-season-prep-what-to</t>
         </is>
       </c>
       <c r="P59" s="32" t="inlineStr">
@@ -7177,7 +7177,7 @@
         </is>
       </c>
       <c r="R60" s="24">
-        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/convert-images-jpg-5jeayb/content/2026-11-06-one-result-every-angle/images/slide-1.jpg")</f>
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/image-size-format-instagram-855nfc/content/2026-11-06-one-result-every-angle/images/slide-1.jpg")</f>
         <v/>
       </c>
       <c r="S60" s="30" t="inlineStr">
@@ -7265,7 +7265,7 @@
       <c r="N61" s="24" t="n"/>
       <c r="O61" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-11-07-quote-book-the-appointment</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-11-07-quote-book-the-appointment</t>
         </is>
       </c>
       <c r="P61" s="34" t="inlineStr">
@@ -7364,7 +7364,7 @@
       <c r="N62" s="24" t="n"/>
       <c r="O62" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-11-09-the-gift-of-glow-gift</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-11-09-the-gift-of-glow-gift</t>
         </is>
       </c>
       <c r="P62" s="32" t="inlineStr">
@@ -7463,7 +7463,7 @@
       <c r="N63" s="24" t="n"/>
       <c r="O63" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-11-10-gift-certificates-are-here</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-11-10-gift-certificates-are-here</t>
         </is>
       </c>
       <c r="P63" s="34" t="inlineStr">
@@ -7562,7 +7562,7 @@
       <c r="N64" s="24" t="n"/>
       <c r="O64" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-11-12-3-months-of-honest-answers</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-11-12-3-months-of-honest-answers</t>
         </is>
       </c>
       <c r="P64" s="32" t="inlineStr">
@@ -7661,7 +7661,7 @@
       <c r="N65" s="24" t="n"/>
       <c r="O65" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-11-13-thank-you-3-months-of</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-11-13-thank-you-3-months-of</t>
         </is>
       </c>
       <c r="P65" s="34" t="inlineStr">
@@ -7760,7 +7760,7 @@
       <c r="N66" s="24" t="n"/>
       <c r="O66" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/convert-images-jpg-5jeayb/content/2026-11-14-tag-someone-who-deserves-a</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-11-14-tag-someone-who-deserves-a</t>
         </is>
       </c>
       <c r="P66" s="34" t="inlineStr">

--- a/strategy/ig-content-strategy.xlsx
+++ b/strategy/ig-content-strategy.xlsx
@@ -1201,7 +1201,7 @@
       <c r="N2" s="24" t="n"/>
       <c r="O2" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-08-17-5-botox-lies-you-still</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-08-17-5-botox-lies-you-still</t>
         </is>
       </c>
       <c r="P2" s="32" t="inlineStr">
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="R2" s="24">
-        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/image-size-format-instagram-855nfc/content/2026-08-17-5-botox-lies-you-still/images/slide-1.jpg")</f>
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/2026-08-17-5-botox-lies-you-still/images/slide-1.jpg")</f>
         <v/>
       </c>
       <c r="S2" s="28" t="inlineStr">
@@ -1232,7 +1232,7 @@
       <c r="Z2" s="24" t="n"/>
       <c r="AA2" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/blob/claude/image-size-format-instagram-855nfc/content/2026-08-17-5-botox-lies-you-still/images/gbp.jpg?raw=1</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/blob/claude/med-spa-carousel-ideas-sim9wz/content/2026-08-17-5-botox-lies-you-still/images/gbp.jpg?raw=1</t>
         </is>
       </c>
       <c r="AB2" s="33" t="inlineStr">
@@ -1307,7 +1307,7 @@
       <c r="N3" s="24" t="n"/>
       <c r="O3" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-08-18-service-spotlight-botox</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-08-18-service-spotlight-botox</t>
         </is>
       </c>
       <c r="P3" s="34" t="inlineStr">
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="R3" s="24">
-        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/image-size-format-instagram-855nfc/content/2026-08-18-service-spotlight-botox/images/post.jpg")</f>
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/2026-08-18-service-spotlight-botox/images/post.jpg")</f>
         <v/>
       </c>
       <c r="S3" s="30" t="inlineStr">
@@ -1338,7 +1338,7 @@
       <c r="Z3" s="24" t="n"/>
       <c r="AA3" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/blob/claude/image-size-format-instagram-855nfc/content/2026-08-18-service-spotlight-botox/images/gbp.jpg?raw=1</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/blob/claude/med-spa-carousel-ideas-sim9wz/content/2026-08-18-service-spotlight-botox/images/gbp.jpg?raw=1</t>
         </is>
       </c>
       <c r="AB3" s="33" t="inlineStr">
@@ -1419,7 +1419,7 @@
       <c r="N4" s="24" t="n"/>
       <c r="O4" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-08-20-5-red-flags-at-a</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-08-20-5-red-flags-at-a</t>
         </is>
       </c>
       <c r="P4" s="32" t="inlineStr">
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="R4" s="24">
-        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/image-size-format-instagram-855nfc/content/2026-08-20-5-red-flags-at-a/images/slide-1.jpg")</f>
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/2026-08-20-5-red-flags-at-a/images/slide-1.jpg")</f>
         <v/>
       </c>
       <c r="S4" s="28" t="inlineStr">
@@ -1535,7 +1535,7 @@
       <c r="N5" s="24" t="n"/>
       <c r="O5" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-08-21-behind-the-scenes-the-prep</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-08-21-behind-the-scenes-the-prep</t>
         </is>
       </c>
       <c r="P5" s="34" t="inlineStr">
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="R5" s="24">
-        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/image-size-format-instagram-855nfc/content/2026-08-21-behind-the-scenes-the-prep/images/post.jpg")</f>
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/2026-08-21-behind-the-scenes-the-prep/images/post.jpg")</f>
         <v/>
       </c>
       <c r="S5" s="30" t="inlineStr">
@@ -1669,7 +1669,7 @@
         </is>
       </c>
       <c r="R6" s="24">
-        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/image-size-format-instagram-855nfc/content/2026-08-22-great-work-is-invisible/images/before-after-result.jpg")</f>
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/2026-08-22-great-work-is-invisible/images/before-after-result.jpg")</f>
         <v/>
       </c>
       <c r="S6" s="30" t="inlineStr">
@@ -1772,7 +1772,7 @@
       <c r="N7" s="24" t="n"/>
       <c r="O7" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-08-24-your-first-visit-step-by</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-08-24-your-first-visit-step-by</t>
         </is>
       </c>
       <c r="P7" s="32" t="inlineStr">
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="R7" s="24">
-        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/image-size-format-instagram-855nfc/content/2026-08-24-your-first-visit-step-by/images/slide-1.jpg")</f>
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/2026-08-24-your-first-visit-step-by/images/slide-1.jpg")</f>
         <v/>
       </c>
       <c r="S7" s="28" t="inlineStr">
@@ -1891,7 +1891,7 @@
       <c r="N8" s="24" t="n"/>
       <c r="O8" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-08-25-why-i-do-not-post</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-08-25-why-i-do-not-post</t>
         </is>
       </c>
       <c r="P8" s="34" t="inlineStr">
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="R8" s="24">
-        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/image-size-format-instagram-855nfc/content/2026-08-25-why-i-do-not-post/images/post.jpg")</f>
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/2026-08-25-why-i-do-not-post/images/post.jpg")</f>
         <v/>
       </c>
       <c r="S8" s="30" t="inlineStr">
@@ -2008,7 +2008,7 @@
       <c r="N9" s="24" t="n"/>
       <c r="O9" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-08-27-meet-np-cleo-the-face</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-08-27-meet-np-cleo-the-face</t>
         </is>
       </c>
       <c r="P9" s="32" t="inlineStr">
@@ -2022,7 +2022,7 @@
         </is>
       </c>
       <c r="R9" s="24">
-        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/image-size-format-instagram-855nfc/content/2026-08-27-meet-np-cleo-the-face/images/slide-1.jpg")</f>
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/2026-08-27-meet-np-cleo-the-face/images/slide-1.jpg")</f>
         <v/>
       </c>
       <c r="S9" s="28" t="inlineStr">
@@ -2123,7 +2123,7 @@
       <c r="N10" s="24" t="n"/>
       <c r="O10" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-08-28-welcome-to-the-treatment-room</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-08-28-welcome-to-the-treatment-room</t>
         </is>
       </c>
       <c r="P10" s="34" t="inlineStr">
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="R10" s="24">
-        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/image-size-format-instagram-855nfc/content/2026-08-28-welcome-to-the-treatment-room/images/post.jpg")</f>
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/2026-08-28-welcome-to-the-treatment-room/images/post.jpg")</f>
         <v/>
       </c>
       <c r="S10" s="30" t="inlineStr">
@@ -2237,7 +2237,7 @@
       <c r="N11" s="24" t="n"/>
       <c r="O11" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-08-29-this-or-that-rested-vs</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-08-29-this-or-that-rested-vs</t>
         </is>
       </c>
       <c r="P11" s="34" t="inlineStr">
@@ -2251,7 +2251,7 @@
         </is>
       </c>
       <c r="R11" s="24">
-        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/image-size-format-instagram-855nfc/content/2026-08-29-this-or-that-rested-vs/images/post.jpg")</f>
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/2026-08-29-this-or-that-rested-vs/images/post.jpg")</f>
         <v/>
       </c>
       <c r="S11" s="30" t="inlineStr">
@@ -2354,7 +2354,7 @@
       <c r="N12" s="24" t="n"/>
       <c r="O12" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-08-31-preventative-botox-when-to-actually</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-08-31-preventative-botox-when-to-actually</t>
         </is>
       </c>
       <c r="P12" s="32" t="inlineStr">
@@ -2368,7 +2368,7 @@
         </is>
       </c>
       <c r="R12" s="24">
-        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/image-size-format-instagram-855nfc/content/2026-08-31-preventative-botox-when-to-actually/images/slide-1.jpg")</f>
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/2026-08-31-preventative-botox-when-to-actually/images/slide-1.jpg")</f>
         <v/>
       </c>
       <c r="S12" s="28" t="inlineStr">
@@ -2464,7 +2464,7 @@
       <c r="N13" s="24" t="n"/>
       <c r="O13" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-09-01-service-spotlight-preventative-botox</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-01-service-spotlight-preventative-botox</t>
         </is>
       </c>
       <c r="P13" s="34" t="inlineStr">
@@ -2563,7 +2563,7 @@
       <c r="N14" s="24" t="n"/>
       <c r="O14" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-09-03-what-20-units-actually-looks</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-03-what-20-units-actually-looks</t>
         </is>
       </c>
       <c r="P14" s="32" t="inlineStr">
@@ -2662,7 +2662,7 @@
       <c r="N15" s="24" t="n"/>
       <c r="O15" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-09-04-meet-your-injector</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-04-meet-your-injector</t>
         </is>
       </c>
       <c r="P15" s="34" t="inlineStr">
@@ -2761,7 +2761,7 @@
       <c r="N16" s="24" t="n"/>
       <c r="O16" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-09-05-quote-prevention-beats-erasing</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-05-quote-prevention-beats-erasing</t>
         </is>
       </c>
       <c r="P16" s="34" t="inlineStr">
@@ -2860,7 +2860,7 @@
       <c r="N17" s="24" t="n"/>
       <c r="O17" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-09-07-botox-vs-dysport-the-real</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-07-botox-vs-dysport-the-real</t>
         </is>
       </c>
       <c r="P17" s="32" t="inlineStr">
@@ -2959,7 +2959,7 @@
       <c r="N18" s="24" t="n"/>
       <c r="O18" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-09-08-botox-vs-dysport-at-a</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-08-botox-vs-dysport-at-a</t>
         </is>
       </c>
       <c r="P18" s="34" t="inlineStr">
@@ -3058,7 +3058,7 @@
       <c r="N19" s="24" t="n"/>
       <c r="O19" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-09-10-botox-aftercare-the-first-48</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-10-botox-aftercare-the-first-48</t>
         </is>
       </c>
       <c r="P19" s="32" t="inlineStr">
@@ -3157,7 +3157,7 @@
       <c r="N20" s="24" t="n"/>
       <c r="O20" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-09-11-the-face-map</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-11-the-face-map</t>
         </is>
       </c>
       <c r="P20" s="34" t="inlineStr">
@@ -3256,7 +3256,7 @@
       <c r="N21" s="24" t="n"/>
       <c r="O21" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-09-12-faq-does-botox-hurt</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-12-faq-does-botox-hurt</t>
         </is>
       </c>
       <c r="P21" s="34" t="inlineStr">
@@ -3355,7 +3355,7 @@
       <c r="N22" s="24" t="n"/>
       <c r="O22" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-09-14-5-things-botox-can-t</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-14-5-things-botox-can-t</t>
         </is>
       </c>
       <c r="P22" s="32" t="inlineStr">
@@ -3454,7 +3454,7 @@
       <c r="N23" s="24" t="n"/>
       <c r="O23" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-09-15-what-botox-can-t-fix</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-15-what-botox-can-t-fix</t>
         </is>
       </c>
       <c r="P23" s="34" t="inlineStr">
@@ -3553,7 +3553,7 @@
       <c r="N24" s="24" t="n"/>
       <c r="O24" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-09-17-still-you-just-refreshed</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-17-still-you-just-refreshed</t>
         </is>
       </c>
       <c r="P24" s="32" t="inlineStr">
@@ -3652,7 +3652,7 @@
       <c r="N25" s="24" t="n"/>
       <c r="O25" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-09-18-myth-vs-truth-the-frozen</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-18-myth-vs-truth-the-frozen</t>
         </is>
       </c>
       <c r="P25" s="34" t="inlineStr">
@@ -3751,7 +3751,7 @@
       <c r="N26" s="24" t="n"/>
       <c r="O26" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-09-19-client-words-natural-results</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-19-client-words-natural-results</t>
         </is>
       </c>
       <c r="P26" s="34" t="inlineStr">
@@ -3850,7 +3850,7 @@
       <c r="N27" s="24" t="n"/>
       <c r="O27" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-09-21-botox-or-filler-you-might</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-21-botox-or-filler-you-might</t>
         </is>
       </c>
       <c r="P27" s="32" t="inlineStr">
@@ -3949,7 +3949,7 @@
       <c r="N28" s="24" t="n"/>
       <c r="O28" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-09-22-lines-vs-volume</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-22-lines-vs-volume</t>
         </is>
       </c>
       <c r="P28" s="34" t="inlineStr">
@@ -4048,7 +4048,7 @@
       <c r="N29" s="24" t="n"/>
       <c r="O29" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-09-24-ask-np-cleo-your-questions</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-24-ask-np-cleo-your-questions</t>
         </is>
       </c>
       <c r="P29" s="32" t="inlineStr">
@@ -4147,7 +4147,7 @@
       <c r="N30" s="24" t="n"/>
       <c r="O30" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-09-25-your-dms-answered</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-25-your-dms-answered</t>
         </is>
       </c>
       <c r="P30" s="34" t="inlineStr">
@@ -4246,7 +4246,7 @@
       <c r="N31" s="24" t="n"/>
       <c r="O31" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-09-26-poll-what-should-np-cleo</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-26-poll-what-should-np-cleo</t>
         </is>
       </c>
       <c r="P31" s="34" t="inlineStr">
@@ -4345,7 +4345,7 @@
       <c r="N32" s="24" t="n"/>
       <c r="O32" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-09-28-how-long-does-botox-really</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-28-how-long-does-botox-really</t>
         </is>
       </c>
       <c r="P32" s="32" t="inlineStr">
@@ -4444,7 +4444,7 @@
       <c r="N33" s="24" t="n"/>
       <c r="O33" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-09-29-the-3-month-botox-timeline</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-09-29-the-3-month-botox-timeline</t>
         </is>
       </c>
       <c r="P33" s="34" t="inlineStr">
@@ -4543,7 +4543,7 @@
       <c r="N34" s="24" t="n"/>
       <c r="O34" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-10-01-why-we-sometimes-say-no</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-01-why-we-sometimes-say-no</t>
         </is>
       </c>
       <c r="P34" s="32" t="inlineStr">
@@ -4642,7 +4642,7 @@
       <c r="N35" s="24" t="n"/>
       <c r="O35" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-10-02-what-i-tell-every-first</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-02-what-i-tell-every-first</t>
         </is>
       </c>
       <c r="P35" s="34" t="inlineStr">
@@ -4741,7 +4741,7 @@
       <c r="N36" s="24" t="n"/>
       <c r="O36" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-10-03-quote-no-is-protection</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-03-quote-no-is-protection</t>
         </is>
       </c>
       <c r="P36" s="34" t="inlineStr">
@@ -4840,7 +4840,7 @@
       <c r="N37" s="24" t="n"/>
       <c r="O37" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-10-05-filler-won-t-make-you</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-05-filler-won-t-make-you</t>
         </is>
       </c>
       <c r="P37" s="32" t="inlineStr">
@@ -4939,7 +4939,7 @@
       <c r="N38" s="24" t="n"/>
       <c r="O38" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-10-06-service-spotlight-dermal-filler</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-06-service-spotlight-dermal-filler</t>
         </is>
       </c>
       <c r="P38" s="34" t="inlineStr">
@@ -5056,7 +5056,7 @@
         </is>
       </c>
       <c r="R39" s="24">
-        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/image-size-format-instagram-855nfc/content/2026-10-08-lip-filler-natural-vs-overdone/images/before-after-result.jpg")</f>
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-08-lip-filler-natural-vs-overdone/images/before-after-result.jpg")</f>
         <v/>
       </c>
       <c r="S39" s="28" t="inlineStr">
@@ -5144,7 +5144,7 @@
       <c r="N40" s="24" t="n"/>
       <c r="O40" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-10-09-inside-the-filler-appointment</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-09-inside-the-filler-appointment</t>
         </is>
       </c>
       <c r="P40" s="34" t="inlineStr">
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="R41" s="24">
-        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/image-size-format-instagram-855nfc/content/2026-10-10-subtle-is-the-new-dramatic/images/before-after-result.jpg")</f>
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-10-subtle-is-the-new-dramatic/images/before-after-result.jpg")</f>
         <v/>
       </c>
       <c r="S41" s="30" t="inlineStr">
@@ -5349,7 +5349,7 @@
       <c r="N42" s="24" t="n"/>
       <c r="O42" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-10-12-cheek-filler-the-secret-nobody</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-12-cheek-filler-the-secret-nobody</t>
         </is>
       </c>
       <c r="P42" s="32" t="inlineStr">
@@ -5448,7 +5448,7 @@
       <c r="N43" s="24" t="n"/>
       <c r="O43" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-10-13-service-spotlight-cheek-filler</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-13-service-spotlight-cheek-filler</t>
         </is>
       </c>
       <c r="P43" s="34" t="inlineStr">
@@ -5565,7 +5565,7 @@
         </is>
       </c>
       <c r="R44" s="24">
-        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/image-size-format-instagram-855nfc/content/2026-10-15-real-lips-real-results/images/slide-1.jpg")</f>
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-15-real-lips-real-results/images/slide-1.jpg")</f>
         <v/>
       </c>
       <c r="S44" s="28" t="inlineStr">
@@ -5653,7 +5653,7 @@
       <c r="N45" s="24" t="n"/>
       <c r="O45" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-10-16-facial-balancing-101</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-16-facial-balancing-101</t>
         </is>
       </c>
       <c r="P45" s="34" t="inlineStr">
@@ -5752,7 +5752,7 @@
       <c r="N46" s="24" t="n"/>
       <c r="O46" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-10-17-faq-how-much-filler-do</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-17-faq-how-much-filler-do</t>
         </is>
       </c>
       <c r="P46" s="34" t="inlineStr">
@@ -5851,7 +5851,7 @@
       <c r="N47" s="24" t="n"/>
       <c r="O47" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-10-19-filler-dissolves-here-is-the</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-19-filler-dissolves-here-is-the</t>
         </is>
       </c>
       <c r="P47" s="32" t="inlineStr">
@@ -5950,7 +5950,7 @@
       <c r="N48" s="24" t="n"/>
       <c r="O48" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-10-20-the-filler-timeline</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-20-the-filler-timeline</t>
         </is>
       </c>
       <c r="P48" s="34" t="inlineStr">
@@ -6067,7 +6067,7 @@
         </is>
       </c>
       <c r="R49" s="24">
-        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/image-size-format-instagram-855nfc/content/2026-10-22-lip-filler-aftercare-your-first/images/day-zero-before-after.jpg")</f>
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-22-lip-filler-aftercare-your-first/images/day-zero-before-after.jpg")</f>
         <v/>
       </c>
       <c r="S49" s="28" t="inlineStr">
@@ -6155,7 +6155,7 @@
       <c r="N50" s="24" t="n"/>
       <c r="O50" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-10-23-aftercare-essentials</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-23-aftercare-essentials</t>
         </is>
       </c>
       <c r="P50" s="34" t="inlineStr">
@@ -6272,7 +6272,7 @@
         </is>
       </c>
       <c r="R51" s="24">
-        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/image-size-format-instagram-855nfc/content/2026-10-24-client-words-the-lip-glow/images/before-after-result.jpg")</f>
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-24-client-words-the-lip-glow/images/before-after-result.jpg")</f>
         <v/>
       </c>
       <c r="S51" s="30" t="inlineStr">
@@ -6360,7 +6360,7 @@
       <c r="N52" s="24" t="n"/>
       <c r="O52" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-10-26-5-filler-lies-you-still</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-26-5-filler-lies-you-still</t>
         </is>
       </c>
       <c r="P52" s="32" t="inlineStr">
@@ -6459,7 +6459,7 @@
       <c r="N53" s="24" t="n"/>
       <c r="O53" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-10-27-myth-vs-truth-filler-edition</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-27-myth-vs-truth-filler-edition</t>
         </is>
       </c>
       <c r="P53" s="34" t="inlineStr">
@@ -6558,7 +6558,7 @@
       <c r="N54" s="24" t="n"/>
       <c r="O54" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-10-29-facial-balancing-why-we-treat</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-29-facial-balancing-why-we-treat</t>
         </is>
       </c>
       <c r="P54" s="32" t="inlineStr">
@@ -6675,7 +6675,7 @@
         </is>
       </c>
       <c r="R55" s="24">
-        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/image-size-format-instagram-855nfc/content/2026-10-30-one-syringe-balanced-lips/images/before-after-result.jpg")</f>
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-30-one-syringe-balanced-lips/images/before-after-result.jpg")</f>
         <v/>
       </c>
       <c r="S55" s="30" t="inlineStr">
@@ -6763,7 +6763,7 @@
       <c r="N56" s="24" t="n"/>
       <c r="O56" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-10-31-ask-anything-filler-edition</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-10-31-ask-anything-filler-edition</t>
         </is>
       </c>
       <c r="P56" s="34" t="inlineStr">
@@ -6862,7 +6862,7 @@
       <c r="N57" s="24" t="n"/>
       <c r="O57" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-11-02-rested-by-the-holidays-your</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-11-02-rested-by-the-holidays-your</t>
         </is>
       </c>
       <c r="P57" s="32" t="inlineStr">
@@ -6961,7 +6961,7 @@
       <c r="N58" s="24" t="n"/>
       <c r="O58" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-11-03-holiday-countdown-book-by-these</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-11-03-holiday-countdown-book-by-these</t>
         </is>
       </c>
       <c r="P58" s="34" t="inlineStr">
@@ -7060,7 +7060,7 @@
       <c r="N59" s="24" t="n"/>
       <c r="O59" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-11-05-party-season-prep-what-to</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-11-05-party-season-prep-what-to</t>
         </is>
       </c>
       <c r="P59" s="32" t="inlineStr">
@@ -7177,7 +7177,7 @@
         </is>
       </c>
       <c r="R60" s="24">
-        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/image-size-format-instagram-855nfc/content/2026-11-06-one-result-every-angle/images/slide-1.jpg")</f>
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/2026-11-06-one-result-every-angle/images/slide-1.jpg")</f>
         <v/>
       </c>
       <c r="S60" s="30" t="inlineStr">
@@ -7265,7 +7265,7 @@
       <c r="N61" s="24" t="n"/>
       <c r="O61" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-11-07-quote-book-the-appointment</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-11-07-quote-book-the-appointment</t>
         </is>
       </c>
       <c r="P61" s="34" t="inlineStr">
@@ -7364,7 +7364,7 @@
       <c r="N62" s="24" t="n"/>
       <c r="O62" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-11-09-the-gift-of-glow-gift</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-11-09-the-gift-of-glow-gift</t>
         </is>
       </c>
       <c r="P62" s="32" t="inlineStr">
@@ -7463,7 +7463,7 @@
       <c r="N63" s="24" t="n"/>
       <c r="O63" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-11-10-gift-certificates-are-here</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-11-10-gift-certificates-are-here</t>
         </is>
       </c>
       <c r="P63" s="34" t="inlineStr">
@@ -7562,7 +7562,7 @@
       <c r="N64" s="24" t="n"/>
       <c r="O64" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-11-12-3-months-of-honest-answers</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-11-12-3-months-of-honest-answers</t>
         </is>
       </c>
       <c r="P64" s="32" t="inlineStr">
@@ -7661,7 +7661,7 @@
       <c r="N65" s="24" t="n"/>
       <c r="O65" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-11-13-thank-you-3-months-of</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-11-13-thank-you-3-months-of</t>
         </is>
       </c>
       <c r="P65" s="34" t="inlineStr">
@@ -7760,7 +7760,7 @@
       <c r="N66" s="24" t="n"/>
       <c r="O66" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/image-size-format-instagram-855nfc/content/2026-11-14-tag-someone-who-deserves-a</t>
+          <t>https://github.com/RepoKing23/InstagramCarousel/tree/claude/med-spa-carousel-ideas-sim9wz/content/2026-11-14-tag-someone-who-deserves-a</t>
         </is>
       </c>
       <c r="P66" s="34" t="inlineStr">

--- a/strategy/ig-content-strategy.xlsx
+++ b/strategy/ig-content-strategy.xlsx
@@ -9,11 +9,12 @@
   <sheets>
     <sheet name="How to Use" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Posting Schedule" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Monthly Themes" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Content Pillars" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Hashtag Sets" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Photo Library" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Ideas Backlog" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="GBP Daily" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Monthly Themes" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Content Pillars" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Hashtag Sets" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Photo Library" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Ideas Backlog" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -22,10 +23,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="mmm\ d&quot;, &quot;yyyy"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -133,8 +135,26 @@
       <color rgb="FF6E6557"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="10"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -156,6 +176,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2E2A23"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E2A23"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3EEE5"/>
       </patternFill>
     </fill>
   </fills>
@@ -183,7 +213,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="6">
+  <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -192,8 +222,9 @@
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -297,14 +328,36 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="19" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="6"/>
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="6"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="19" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="7">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
     <cellStyle name="Currency" xfId="3" builtinId="4"/>
     <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
     <cellStyle name="Percent" xfId="5" builtinId="5"/>
+    <cellStyle name="Hyperlink" xfId="6" builtinId="8" hidden="0"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -550,7 +603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:C43"/>
+  <dimension ref="B2:C45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" style="14" min="1" max="1"/>
@@ -753,203 +806,227 @@
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="22" t="inlineStr">
-        <is>
-          <t>4. Post</t>
-        </is>
-      </c>
-      <c r="C23" s="24" t="inlineStr">
-        <is>
-          <t>Instagram gets the caption and hashtags. GBP gets the GBP caption, the GBP image, and a button pointed at the Instagram profile.</t>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Every day</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="inlineStr">
+        <is>
+          <t>Google Business Profile also posts on Wednesday and Sunday, when Instagram does not. Those days are evergreen and live on the GBP Daily tab.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="22" t="inlineStr">
-        <is>
-          <t>5. Track</t>
-        </is>
-      </c>
-      <c r="C24" s="24" t="inlineStr">
-        <is>
-          <t>Move Status as each post progresses: Idea, Design, Ready, Posted. Hold means blocked, see the row notes.</t>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>GBP Daily tab</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="inlineStr">
+        <is>
+          <t>One row per day, Aug 19 to Sep 30. Image, post text and the Learn more link, ready to paste. Shaded rows are the GBP only days. Full plan in strategy/gbp-daily-plan.md.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="22" t="inlineStr">
         <is>
-          <t>6. Measure</t>
+          <t>4. Post</t>
         </is>
       </c>
       <c r="C25" s="24" t="inlineStr">
         <is>
-          <t>After 48 hours fill Reach, Saves, Comments, DMs, Bookings from IG Insights. Saves and DMs are the numbers that matter.</t>
+          <t>Instagram gets the caption and hashtags. GBP gets the GBP caption, the GBP image, and a button pointed at the Instagram profile.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="22" t="inlineStr">
         <is>
+          <t>5. Track</t>
+        </is>
+      </c>
+      <c r="C26" s="24" t="inlineStr">
+        <is>
+          <t>Move Status as each post progresses: Idea, Design, Ready, Posted. Hold means blocked, see the row notes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>6. Measure</t>
+        </is>
+      </c>
+      <c r="C27" s="24" t="inlineStr">
+        <is>
+          <t>After 48 hours fill Reach, Saves, Comments, DMs, Bookings from IG Insights. Saves and DMs are the numbers that matter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="22" t="inlineStr">
+        <is>
           <t>7. Repeat</t>
         </is>
       </c>
-      <c r="C26" s="24" t="inlineStr">
+      <c r="C28" s="24" t="inlineStr">
         <is>
           <t>Anything with high saves or DMs becomes next month’s sequel.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="37" t="inlineStr">
+    <row r="30">
+      <c r="B30" s="37" t="inlineStr">
         <is>
           <t>HOUSE RULES</t>
         </is>
       </c>
-      <c r="C28" s="38" t="n"/>
-    </row>
-    <row r="29">
-      <c r="B29" s="22" t="inlineStr">
-        <is>
-          <t>Client photos</t>
-        </is>
-      </c>
-      <c r="C29" s="24" t="inlineStr">
-        <is>
-          <t>Written consent on file before anything is posted. Every photo is cropped to the treatment area: no eyes, brows, tattoos or jewellery. Always add "individual results vary". Never boost before and after posts on IG or TikTok; organic only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="22" t="inlineStr">
-        <is>
-          <t>Grid tone</t>
-        </is>
-      </c>
-      <c r="C30" s="24" t="inlineStr">
-        <is>
-          <t>The profile grid runs three tiles per row, newest first. Keep exactly one Dark or Photo-dark tile per row and never let two Dark tiles touch. The Tone column tracks this; re-check it whenever a date moves.</t>
-        </is>
-      </c>
+      <c r="C30" s="38" t="n"/>
     </row>
     <row r="31">
       <c r="B31" s="22" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>Client photos</t>
         </is>
       </c>
       <c r="C31" s="24" t="inlineStr">
         <is>
-          <t>No hashtags on GBP, they do not work there. The offer goes in the first 80 characters. Images are 1200x900 with everything inside the centre 900x900 square, because Maps crops to a square.</t>
+          <t>Written consent on file before anything is posted. Every photo is cropped to the treatment area: no eyes, brows, tattoos or jewellery. Always add "individual results vary". Never boost before and after posts on IG or TikTok; organic only.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="22" t="inlineStr">
         <is>
-          <t>Hashtags</t>
+          <t>Grid tone</t>
         </is>
       </c>
       <c r="C32" s="24" t="inlineStr">
         <is>
-          <t>Every set leads with local tags (Oakville, Burlington, Milton, Mississauga, Halton). Location plus service is the highest-intent combination. Sets live on the Hashtag Sets tab.</t>
+          <t>The profile grid runs three tiles per row, newest first. Keep exactly one Dark or Photo-dark tile per row and never let two Dark tiles touch. The Tone column tracks this; re-check it whenever a date moves.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="22" t="inlineStr">
         <is>
-          <t>Voice</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="C33" s="24" t="inlineStr">
         <is>
-          <t>Plain, direct, first person. No em dashes, no sparkle emoji, no borrowed captions. If a line sounds like a template, rewrite it.</t>
+          <t>No hashtags on GBP, they do not work there. The offer goes in the first 80 characters. Images are 1200x900 with everything inside the centre 900x900 square, because Maps crops to a square.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="22" t="inlineStr">
         <is>
+          <t>Hashtags</t>
+        </is>
+      </c>
+      <c r="C34" s="24" t="inlineStr">
+        <is>
+          <t>Every set leads with local tags (Oakville, Burlington, Milton, Mississauga, Halton). Location plus service is the highest-intent combination. Sets live on the Hashtag Sets tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="22" t="inlineStr">
+        <is>
+          <t>Voice</t>
+        </is>
+      </c>
+      <c r="C35" s="24" t="inlineStr">
+        <is>
+          <t>Plain, direct, first person. No em dashes, no sparkle emoji, no borrowed captions. If a line sounds like a template, rewrite it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="22" t="inlineStr">
+        <is>
           <t>Compliance</t>
         </is>
       </c>
-      <c r="C34" s="24" t="inlineStr">
+      <c r="C36" s="24" t="inlineStr">
         <is>
           <t>Botox is a prescription drug in Canada and Health Canada restricts consumer advertising of prescription drugs. The brand name in this plan is pending a compliance check; "neuromodulator" is the safe swap. Credentials read RN(EC), College of Nurses of Ontario.</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="B36" s="37" t="inlineStr">
+    <row r="38">
+      <c r="B38" s="37" t="inlineStr">
         <is>
           <t>STATUS SNAPSHOT</t>
         </is>
       </c>
-      <c r="C36" s="38" t="n"/>
-    </row>
-    <row r="37">
-      <c r="B37" s="22" t="inlineStr">
+      <c r="C38" s="38" t="n"/>
+    </row>
+    <row r="39">
+      <c r="B39" s="22" t="inlineStr">
         <is>
           <t>Posts planned</t>
         </is>
       </c>
-      <c r="C37" s="24">
+      <c r="C39" s="24">
         <f>COUNTA('Posting Schedule'!A2:A66)</f>
         <v/>
       </c>
     </row>
-    <row r="38">
-      <c r="B38" s="22" t="inlineStr">
+    <row r="40">
+      <c r="B40" s="22" t="inlineStr">
         <is>
           <t>Ideas</t>
         </is>
       </c>
-      <c r="C38" s="24">
+      <c r="C40" s="24">
         <f>COUNTIF('Posting Schedule'!S2:S66,"Idea")</f>
         <v/>
       </c>
     </row>
-    <row r="39">
-      <c r="B39" s="22" t="inlineStr">
+    <row r="41">
+      <c r="B41" s="22" t="inlineStr">
         <is>
           <t>In design</t>
         </is>
       </c>
-      <c r="C39" s="24">
+      <c r="C41" s="24">
         <f>COUNTIF('Posting Schedule'!S2:S66,"Design")</f>
         <v/>
       </c>
     </row>
-    <row r="40">
-      <c r="B40" s="22" t="inlineStr">
+    <row r="42">
+      <c r="B42" s="22" t="inlineStr">
         <is>
           <t>Ready to post</t>
         </is>
       </c>
-      <c r="C40" s="24">
+      <c r="C42" s="24">
         <f>COUNTIF('Posting Schedule'!S2:S66,"Ready")</f>
         <v/>
       </c>
     </row>
-    <row r="41">
-      <c r="B41" s="22" t="inlineStr">
+    <row r="43">
+      <c r="B43" s="22" t="inlineStr">
         <is>
           <t>Posted</t>
         </is>
       </c>
-      <c r="C41" s="24">
+      <c r="C43" s="24">
         <f>COUNTIF('Posting Schedule'!S2:S66,"Posted")</f>
         <v/>
       </c>
     </row>
-    <row r="43">
-      <c r="B43" s="22" t="inlineStr">
+    <row r="45">
+      <c r="B45" s="22" t="inlineStr">
         <is>
           <t>Google Sheets</t>
         </is>
       </c>
-      <c r="C43" s="24" t="inlineStr">
+      <c r="C45" s="24" t="inlineStr">
         <is>
           <t>drive.google.com &gt; New &gt; File upload &gt; pick this file &gt; open with Google Sheets. Preview thumbnails and links work there.</t>
         </is>
@@ -7932,6 +8009,2684 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" style="14" min="1" max="1"/>
+    <col width="6" customWidth="1" style="14" min="2" max="2"/>
+    <col width="34" customWidth="1" style="14" min="3" max="3"/>
+    <col width="18" customWidth="1" style="14" min="4" max="4"/>
+    <col width="78" customWidth="1" style="14" min="5" max="5"/>
+    <col width="7" customWidth="1" style="14" min="6" max="6"/>
+    <col width="12" customWidth="1" style="14" min="7" max="7"/>
+    <col width="26" customWidth="1" style="14" min="8" max="8"/>
+    <col width="34" customWidth="1" style="14" min="9" max="9"/>
+    <col width="12" customWidth="1" style="14" min="10" max="10"/>
+    <col width="14" customWidth="1" style="14" min="11" max="11"/>
+    <col width="10" customWidth="1" style="14" min="12" max="12"/>
+    <col width="30" customWidth="1" style="14" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="39" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="39" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="C1" s="39" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="D1" s="39" t="inlineStr">
+        <is>
+          <t>Pillar</t>
+        </is>
+      </c>
+      <c r="E1" s="39" t="inlineStr">
+        <is>
+          <t>Post Text (first 80 chars show)</t>
+        </is>
+      </c>
+      <c r="F1" s="39" t="inlineStr">
+        <is>
+          <t>Chars</t>
+        </is>
+      </c>
+      <c r="G1" s="39" t="inlineStr">
+        <is>
+          <t>CTA Button</t>
+        </is>
+      </c>
+      <c r="H1" s="39" t="inlineStr">
+        <is>
+          <t>CTA Link</t>
+        </is>
+      </c>
+      <c r="I1" s="39" t="inlineStr">
+        <is>
+          <t>Image File</t>
+        </is>
+      </c>
+      <c r="J1" s="39" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="K1" s="39" t="inlineStr">
+        <is>
+          <t>Preview</t>
+        </is>
+      </c>
+      <c r="L1" s="39" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="M1" s="39" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="58" customHeight="1" s="14">
+      <c r="A2" s="50" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B2" s="41" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="C2" s="41" t="inlineStr">
+        <is>
+          <t>GBP only</t>
+        </is>
+      </c>
+      <c r="D2" s="41" t="inlineStr">
+        <is>
+          <t>Trust &amp; Proof</t>
+        </is>
+      </c>
+      <c r="E2" s="42" t="inlineStr">
+        <is>
+          <t>One client in the room at a time, in a private Oakville studio. No busy waiting room, no rushing the person ahead of you, no rushing you. Injections are done by a nurse practitioner and never delegated. See the room and the work on Instagram.</t>
+        </is>
+      </c>
+      <c r="F2" s="41" t="n">
+        <v>242</v>
+      </c>
+      <c r="G2" s="41" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="H2" s="43" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="I2" s="41" t="inlineStr">
+        <is>
+          <t>2026-08-19-one-client-at-a-time.jpg</t>
+        </is>
+      </c>
+      <c r="J2" s="43" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="K2" s="41">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-08-19-one-client-at-a-time.jpg")</f>
+        <v/>
+      </c>
+      <c r="L2" s="41" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="M2" s="42" t="inlineStr"/>
+    </row>
+    <row r="3" ht="58" customHeight="1" s="14">
+      <c r="A3" s="51" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B3" s="45" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C3" s="45" t="inlineStr">
+        <is>
+          <t>IG: 5 Red Flags at a Med Spa</t>
+        </is>
+      </c>
+      <c r="D3" s="45" t="inlineStr">
+        <is>
+          <t>Trust &amp; Proof</t>
+        </is>
+      </c>
+      <c r="E3" s="46" t="inlineStr">
+        <is>
+          <t>Five things to walk away from at a med spa: no consultation, bargain pricing, a provider who never says no, no named injector, and pressure to decide today. Your face is not the place to find out you picked wrong. The full list is on Instagram.</t>
+        </is>
+      </c>
+      <c r="F3" s="45" t="n">
+        <v>244</v>
+      </c>
+      <c r="G3" s="45" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="H3" s="47" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="I3" s="45" t="inlineStr">
+        <is>
+          <t>2026-08-20-5-red-flags.jpg</t>
+        </is>
+      </c>
+      <c r="J3" s="47" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="K3" s="45">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-08-20-5-red-flags.jpg")</f>
+        <v/>
+      </c>
+      <c r="L3" s="45" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="M3" s="46" t="inlineStr"/>
+    </row>
+    <row r="4" ht="58" customHeight="1" s="14">
+      <c r="A4" s="51" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B4" s="45" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="C4" s="45" t="inlineStr">
+        <is>
+          <t>IG: Behind the Scenes, The Prep</t>
+        </is>
+      </c>
+      <c r="D4" s="45" t="inlineStr">
+        <is>
+          <t>Personality &amp; BTS</t>
+        </is>
+      </c>
+      <c r="E4" s="46" t="inlineStr">
+        <is>
+          <t>Every appointment starts the same way. A new tray, product opened sealed in front of you, and your face mapped while it moves, not while it sits still. The prep is the part nobody photographs. We photographed it, on Instagram.</t>
+        </is>
+      </c>
+      <c r="F4" s="45" t="n">
+        <v>226</v>
+      </c>
+      <c r="G4" s="45" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="H4" s="47" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="I4" s="45" t="inlineStr">
+        <is>
+          <t>2026-08-21-before-the-needle.jpg</t>
+        </is>
+      </c>
+      <c r="J4" s="47" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="K4" s="45">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-08-21-before-the-needle.jpg")</f>
+        <v/>
+      </c>
+      <c r="L4" s="45" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="M4" s="46" t="inlineStr"/>
+    </row>
+    <row r="5" ht="58" customHeight="1" s="14">
+      <c r="A5" s="51" t="n">
+        <v>46256</v>
+      </c>
+      <c r="B5" s="45" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="C5" s="45" t="inlineStr">
+        <is>
+          <t>IG: Great Work Is Invisible</t>
+        </is>
+      </c>
+      <c r="D5" s="45" t="inlineStr">
+        <is>
+          <t>Trust &amp; Proof</t>
+        </is>
+      </c>
+      <c r="E5" s="46" t="inlineStr">
+        <is>
+          <t>One syringe of lip filler, with her own lip shape kept exactly where it was. If it reads as good skin and a good night of sleep rather than work, that was the goal. Shared with client consent, individual results vary. More on Instagram.</t>
+        </is>
+      </c>
+      <c r="F5" s="45" t="n">
+        <v>236</v>
+      </c>
+      <c r="G5" s="45" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="H5" s="47" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="I5" s="45" t="inlineStr">
+        <is>
+          <t>2026-08-22-great-work-is-invisible.jpg</t>
+        </is>
+      </c>
+      <c r="J5" s="47" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="K5" s="45">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-08-22-great-work-is-invisible.jpg")</f>
+        <v/>
+      </c>
+      <c r="L5" s="45" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="M5" s="46" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1" s="14">
+      <c r="A6" s="50" t="n">
+        <v>46257</v>
+      </c>
+      <c r="B6" s="41" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="C6" s="41" t="inlineStr">
+        <is>
+          <t>GBP only</t>
+        </is>
+      </c>
+      <c r="D6" s="41" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="E6" s="42" t="inlineStr">
+        <is>
+          <t>A first visit runs about 45 minutes and most of that is talking. Consultation, mapping your face in motion, and agreeing a plan and a price before anything is opened. The injecting itself takes roughly ten minutes. Questions welcome on Instagram.</t>
+        </is>
+      </c>
+      <c r="F6" s="41" t="n">
+        <v>246</v>
+      </c>
+      <c r="G6" s="41" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="H6" s="43" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="I6" s="41" t="inlineStr">
+        <is>
+          <t>2026-08-23-how-long-does-it-take.jpg</t>
+        </is>
+      </c>
+      <c r="J6" s="43" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="K6" s="41">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-08-23-how-long-does-it-take.jpg")</f>
+        <v/>
+      </c>
+      <c r="L6" s="41" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="M6" s="42" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1" s="14">
+      <c r="A7" s="51" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B7" s="45" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C7" s="45" t="inlineStr">
+        <is>
+          <t>IG: Your First Visit, Step by Step</t>
+        </is>
+      </c>
+      <c r="D7" s="45" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="E7" s="46" t="inlineStr">
+        <is>
+          <t>Nervous about a first appointment? Here is the whole thing. A real consultation, your face mapped in motion, a written plan and price agreed before anything is opened, then about ten minutes of treatment. Step by step on Instagram.</t>
+        </is>
+      </c>
+      <c r="F7" s="45" t="n">
+        <v>231</v>
+      </c>
+      <c r="G7" s="45" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="H7" s="47" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="I7" s="45" t="inlineStr">
+        <is>
+          <t>2026-08-24-what-actually-happens.jpg</t>
+        </is>
+      </c>
+      <c r="J7" s="47" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="K7" s="45">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-08-24-what-actually-happens.jpg")</f>
+        <v/>
+      </c>
+      <c r="L7" s="45" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="M7" s="46" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1" s="14">
+      <c r="A8" s="51" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B8" s="45" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C8" s="45" t="inlineStr">
+        <is>
+          <t>IG: Why I Do Not Post Prices</t>
+        </is>
+      </c>
+      <c r="D8" s="45" t="inlineStr">
+        <is>
+          <t>Trust &amp; Proof</t>
+        </is>
+      </c>
+      <c r="E8" s="46" t="inlineStr">
+        <is>
+          <t>Why there is no price list. Doses differ from face to face, so a single flat price either overcharges you or under treats you. You get a written number at your consultation, before anything is opened. The honest version is on Instagram.</t>
+        </is>
+      </c>
+      <c r="F8" s="45" t="n">
+        <v>236</v>
+      </c>
+      <c r="G8" s="45" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="H8" s="47" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="I8" s="45" t="inlineStr">
+        <is>
+          <t>2026-08-25-why-no-prices.jpg</t>
+        </is>
+      </c>
+      <c r="J8" s="47" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="K8" s="45">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-08-25-why-no-prices.jpg")</f>
+        <v/>
+      </c>
+      <c r="L8" s="45" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="M8" s="46" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1" s="14">
+      <c r="A9" s="50" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B9" s="41" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="C9" s="41" t="inlineStr">
+        <is>
+          <t>GBP only</t>
+        </is>
+      </c>
+      <c r="D9" s="41" t="inlineStr">
+        <is>
+          <t>Trust &amp; Proof</t>
+        </is>
+      </c>
+      <c r="E9" s="42" t="inlineStr">
+        <is>
+          <t>Ask any clinic who is actually holding the needle. Here it is a nurse practitioner, RN(EC), registered with the College of Nurses of Ontario. Every appointment is injected by Cleo, never delegated to someone you have not met. Meet her on Instagram.</t>
+        </is>
+      </c>
+      <c r="F9" s="41" t="n">
+        <v>248</v>
+      </c>
+      <c r="G9" s="41" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="H9" s="43" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="I9" s="41" t="inlineStr">
+        <is>
+          <t>2026-08-26-who-injects-you.jpg</t>
+        </is>
+      </c>
+      <c r="J9" s="43" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="K9" s="41">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-08-26-who-injects-you.jpg")</f>
+        <v/>
+      </c>
+      <c r="L9" s="41" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="M9" s="42" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1" s="14">
+      <c r="A10" s="51" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B10" s="45" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C10" s="45" t="inlineStr">
+        <is>
+          <t>IG: Meet NP Cleo</t>
+        </is>
+      </c>
+      <c r="D10" s="45" t="inlineStr">
+        <is>
+          <t>Personality &amp; BTS</t>
+        </is>
+      </c>
+      <c r="E10" s="46" t="inlineStr">
+        <is>
+          <t>Meet NP Cleo. Nurse practitioner and injector, and the person who will tell you no when the honest answer is no. Every appointment is injected by her, never delegated. The full introduction is on Instagram.</t>
+        </is>
+      </c>
+      <c r="F10" s="45" t="n">
+        <v>206</v>
+      </c>
+      <c r="G10" s="45" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="H10" s="47" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="I10" s="45" t="inlineStr">
+        <is>
+          <t>2026-08-27-meet-np-cleo.jpg</t>
+        </is>
+      </c>
+      <c r="J10" s="47" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="K10" s="45">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-08-27-meet-np-cleo.jpg")</f>
+        <v/>
+      </c>
+      <c r="L10" s="45" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="M10" s="46" t="inlineStr"/>
+    </row>
+    <row r="11" ht="58" customHeight="1" s="14">
+      <c r="A11" s="51" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B11" s="45" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="C11" s="45" t="inlineStr">
+        <is>
+          <t>IG: Welcome to the Treatment Room</t>
+        </is>
+      </c>
+      <c r="D11" s="45" t="inlineStr">
+        <is>
+          <t>Personality &amp; BTS</t>
+        </is>
+      </c>
+      <c r="E11" s="46" t="inlineStr">
+        <is>
+          <t>One client in the treatment room at a time. Nobody rushes the person before you, so nobody rushes you. The door stays shut and the questions stay welcome, however small they feel. Come see the room on Instagram.</t>
+        </is>
+      </c>
+      <c r="F11" s="45" t="n">
+        <v>211</v>
+      </c>
+      <c r="G11" s="45" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="H11" s="47" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="I11" s="45" t="inlineStr">
+        <is>
+          <t>2026-08-28-where-calm-meets-careful.jpg</t>
+        </is>
+      </c>
+      <c r="J11" s="47" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="K11" s="45">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-08-28-where-calm-meets-careful.jpg")</f>
+        <v/>
+      </c>
+      <c r="L11" s="45" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="M11" s="46" t="inlineStr"/>
+    </row>
+    <row r="12" ht="58" customHeight="1" s="14">
+      <c r="A12" s="51" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B12" s="45" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="C12" s="45" t="inlineStr">
+        <is>
+          <t>IG: This or That, Rested vs Frozen</t>
+        </is>
+      </c>
+      <c r="D12" s="45" t="inlineStr">
+        <is>
+          <t>Trust &amp; Proof</t>
+        </is>
+      </c>
+      <c r="E12" s="46" t="inlineStr">
+        <is>
+          <t>Rested, not frozen. You should still frown, squint and smile afterwards. If people ask what you had done instead of whether you slept well, the dose was wrong. See the difference side by side on Instagram.</t>
+        </is>
+      </c>
+      <c r="F12" s="45" t="n">
+        <v>205</v>
+      </c>
+      <c r="G12" s="45" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="H12" s="47" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="I12" s="45" t="inlineStr">
+        <is>
+          <t>2026-08-29-rested-or-frozen.jpg</t>
+        </is>
+      </c>
+      <c r="J12" s="47" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="K12" s="45">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-08-29-rested-or-frozen.jpg")</f>
+        <v/>
+      </c>
+      <c r="L12" s="45" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="M12" s="46" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1" s="14">
+      <c r="A13" s="50" t="n">
+        <v>46264</v>
+      </c>
+      <c r="B13" s="41" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="C13" s="41" t="inlineStr">
+        <is>
+          <t>GBP only</t>
+        </is>
+      </c>
+      <c r="D13" s="41" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="E13" s="42" t="inlineStr">
+        <is>
+          <t>A consultation is not a sales appointment. We go through your goals, map your face in motion, and talk about what will work, what will not, and what it costs, in writing. You can leave without booking anything. More on Instagram.</t>
+        </is>
+      </c>
+      <c r="F13" s="41" t="n">
+        <v>229</v>
+      </c>
+      <c r="G13" s="41" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="H13" s="43" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="I13" s="41" t="inlineStr">
+        <is>
+          <t>2026-08-30-what-a-consult-includes.jpg</t>
+        </is>
+      </c>
+      <c r="J13" s="43" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="K13" s="41">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-08-30-what-a-consult-includes.jpg")</f>
+        <v/>
+      </c>
+      <c r="L13" s="41" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="M13" s="42" t="inlineStr"/>
+    </row>
+    <row r="14" ht="58" customHeight="1" s="14">
+      <c r="A14" s="51" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B14" s="45" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C14" s="45" t="inlineStr">
+        <is>
+          <t>IG: Preventative Botox, When to Start</t>
+        </is>
+      </c>
+      <c r="D14" s="45" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="E14" s="46" t="inlineStr">
+        <is>
+          <t>When should you actually start preventative Botox? It is not about your age. Make your strongest expression, relax your face, and see if the line stays behind. That is the one setting in. The full explanation is on Instagram.</t>
+        </is>
+      </c>
+      <c r="F14" s="45" t="n">
+        <v>225</v>
+      </c>
+      <c r="G14" s="45" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="H14" s="47" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="I14" s="45" t="inlineStr">
+        <is>
+          <t>2026-08-31-when-to-start.jpg</t>
+        </is>
+      </c>
+      <c r="J14" s="47" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="K14" s="45">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-08-31-when-to-start.jpg")</f>
+        <v/>
+      </c>
+      <c r="L14" s="45" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="M14" s="46" t="inlineStr"/>
+    </row>
+    <row r="15" ht="58" customHeight="1" s="14">
+      <c r="A15" s="51" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B15" s="45" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C15" s="45" t="inlineStr">
+        <is>
+          <t>IG: Service Spotlight, Preventative Botox</t>
+        </is>
+      </c>
+      <c r="D15" s="45" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="E15" s="46" t="inlineStr">
+        <is>
+          <t>Preventative Botox, explained plainly. Small doses started before a line sets in, so it never becomes permanent. It is easier to stop a line than to erase one. Dosed to your muscle, never to a template. More on Instagram.</t>
+        </is>
+      </c>
+      <c r="F15" s="45" t="n">
+        <v>221</v>
+      </c>
+      <c r="G15" s="45" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="H15" s="47" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="I15" s="45" t="inlineStr">
+        <is>
+          <t>2026-09-01-spotlight-preventative.jpg</t>
+        </is>
+      </c>
+      <c r="J15" s="47" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="K15" s="45">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-01-spotlight-preventative.jpg")</f>
+        <v/>
+      </c>
+      <c r="L15" s="45" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="M15" s="46" t="inlineStr"/>
+    </row>
+    <row r="16" ht="58" customHeight="1" s="14">
+      <c r="A16" s="50" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B16" s="41" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="C16" s="41" t="inlineStr">
+        <is>
+          <t>GBP only</t>
+        </is>
+      </c>
+      <c r="D16" s="41" t="inlineStr">
+        <is>
+          <t>Trust &amp; Proof</t>
+        </is>
+      </c>
+      <c r="E16" s="42" t="inlineStr">
+        <is>
+          <t>The question people are too polite to ask. Product is Health Canada approved, opened sealed in front of you, and injected by a nurse practitioner registered with the College of Nurses of Ontario. Ask me anything on Instagram.</t>
+        </is>
+      </c>
+      <c r="F16" s="41" t="n">
+        <v>225</v>
+      </c>
+      <c r="G16" s="41" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="H16" s="43" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="I16" s="41" t="inlineStr">
+        <is>
+          <t>2026-09-02-is-it-safe.jpg</t>
+        </is>
+      </c>
+      <c r="J16" s="43" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="K16" s="41">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-02-is-it-safe.jpg")</f>
+        <v/>
+      </c>
+      <c r="L16" s="41" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="M16" s="42" t="inlineStr"/>
+    </row>
+    <row r="17" ht="58" customHeight="1" s="14">
+      <c r="A17" s="51" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B17" s="45" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C17" s="45" t="inlineStr">
+        <is>
+          <t>IG: What 20 Units Actually Looks Like</t>
+        </is>
+      </c>
+      <c r="D17" s="45" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="E17" s="46" t="inlineStr">
+        <is>
+          <t>Unit math, finally explained. Units measure dose, not strength, and the number you need depends on how strong your muscle is, not on a price menu. That is why a flat per-area price rarely tells the truth. Breakdown on Instagram.</t>
+        </is>
+      </c>
+      <c r="F17" s="45" t="n">
+        <v>228</v>
+      </c>
+      <c r="G17" s="45" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="H17" s="47" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="I17" s="45" t="inlineStr">
+        <is>
+          <t>2026-09-03-20-units.jpg</t>
+        </is>
+      </c>
+      <c r="J17" s="47" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="K17" s="45">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-03-20-units.jpg")</f>
+        <v/>
+      </c>
+      <c r="L17" s="45" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="M17" s="46" t="inlineStr"/>
+    </row>
+    <row r="18" ht="58" customHeight="1" s="14">
+      <c r="A18" s="51" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B18" s="45" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="C18" s="45" t="inlineStr">
+        <is>
+          <t>IG: Meet Your Injector</t>
+        </is>
+      </c>
+      <c r="D18" s="45" t="inlineStr">
+        <is>
+          <t>Personality &amp; BTS</t>
+        </is>
+      </c>
+      <c r="E18" s="46" t="inlineStr">
+        <is>
+          <t>Your injector is a nurse practitioner, RN(EC), registered with the College of Nurses of Ontario. Also the person who will talk you out of a treatment when it is not right for your face. Get to know her on Instagram.</t>
+        </is>
+      </c>
+      <c r="F18" s="45" t="n">
+        <v>215</v>
+      </c>
+      <c r="G18" s="45" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="H18" s="47" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="I18" s="45" t="inlineStr">
+        <is>
+          <t>2026-09-04-meet-your-injector.jpg</t>
+        </is>
+      </c>
+      <c r="J18" s="47" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="K18" s="45">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-04-meet-your-injector.jpg")</f>
+        <v/>
+      </c>
+      <c r="L18" s="45" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="M18" s="46" t="inlineStr"/>
+    </row>
+    <row r="19" ht="58" customHeight="1" s="14">
+      <c r="A19" s="51" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B19" s="45" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="C19" s="45" t="inlineStr">
+        <is>
+          <t>IG: Prevention Beats Erasing</t>
+        </is>
+      </c>
+      <c r="D19" s="45" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="E19" s="46" t="inlineStr">
+        <is>
+          <t>Prevention beats erasing. Ask the friend who never seems to age. Softening a line before it sets into the skin takes less product, less money and less time than chasing it years later. More on Instagram.</t>
+        </is>
+      </c>
+      <c r="F19" s="45" t="n">
+        <v>203</v>
+      </c>
+      <c r="G19" s="45" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="H19" s="47" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="I19" s="45" t="inlineStr">
+        <is>
+          <t>2026-09-05-prevention-beats-erasing.jpg</t>
+        </is>
+      </c>
+      <c r="J19" s="47" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="K19" s="45">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-05-prevention-beats-erasing.jpg")</f>
+        <v/>
+      </c>
+      <c r="L19" s="45" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="M19" s="46" t="inlineStr"/>
+    </row>
+    <row r="20" ht="58" customHeight="1" s="14">
+      <c r="A20" s="50" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B20" s="41" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="C20" s="41" t="inlineStr">
+        <is>
+          <t>GBP only</t>
+        </is>
+      </c>
+      <c r="D20" s="41" t="inlineStr">
+        <is>
+          <t>Trust &amp; Proof</t>
+        </is>
+      </c>
+      <c r="E20" s="42" t="inlineStr">
+        <is>
+          <t>Never had injectables before? Most first appointments start with a question the person thinks sounds silly. Bring all of them. You can book a consultation, ask everything, and leave without treatment. No pressure, ever. DM on Instagram.</t>
+        </is>
+      </c>
+      <c r="F20" s="41" t="n">
+        <v>236</v>
+      </c>
+      <c r="G20" s="41" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="H20" s="43" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="I20" s="41" t="inlineStr">
+        <is>
+          <t>2026-09-06-first-timer.jpg</t>
+        </is>
+      </c>
+      <c r="J20" s="43" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="K20" s="41">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-06-first-timer.jpg")</f>
+        <v/>
+      </c>
+      <c r="L20" s="41" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="M20" s="42" t="inlineStr"/>
+    </row>
+    <row r="21" ht="58" customHeight="1" s="14">
+      <c r="A21" s="51" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B21" s="45" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C21" s="45" t="inlineStr">
+        <is>
+          <t>IG: Botox vs Dysport</t>
+        </is>
+      </c>
+      <c r="D21" s="45" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="E21" s="46" t="inlineStr">
+        <is>
+          <t>Botox or Dysport? Same family, different personalities. One spreads slightly more, one tends to kick in faster. Which suits you depends on the area and your muscle, not on which name you have heard of. Full comparison on Instagram.</t>
+        </is>
+      </c>
+      <c r="F21" s="45" t="n">
+        <v>231</v>
+      </c>
+      <c r="G21" s="45" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="H21" s="47" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="I21" s="45" t="inlineStr">
+        <is>
+          <t>2026-09-07-botox-vs-dysport.jpg</t>
+        </is>
+      </c>
+      <c r="J21" s="47" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="K21" s="45">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-07-botox-vs-dysport.jpg")</f>
+        <v/>
+      </c>
+      <c r="L21" s="45" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="M21" s="46" t="inlineStr"/>
+    </row>
+    <row r="22" ht="58" customHeight="1" s="14">
+      <c r="A22" s="51" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B22" s="45" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C22" s="45" t="inlineStr">
+        <is>
+          <t>IG: Botox vs Dysport at a Glance</t>
+        </is>
+      </c>
+      <c r="D22" s="45" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="E22" s="46" t="inlineStr">
+        <is>
+          <t>Onset, spread and how long each one lasts, side by side. Not so you can pick for yourself, but so you can ask a sharper question at your consultation. The comparison card is on Instagram.</t>
+        </is>
+      </c>
+      <c r="F22" s="45" t="n">
+        <v>187</v>
+      </c>
+      <c r="G22" s="45" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="H22" s="47" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="I22" s="45" t="inlineStr">
+        <is>
+          <t>2026-09-08-at-a-glance.jpg</t>
+        </is>
+      </c>
+      <c r="J22" s="47" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="K22" s="45">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-08-at-a-glance.jpg")</f>
+        <v/>
+      </c>
+      <c r="L22" s="45" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="M22" s="46" t="inlineStr"/>
+    </row>
+    <row r="23" ht="58" customHeight="1" s="14">
+      <c r="A23" s="50" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B23" s="41" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="C23" s="41" t="inlineStr">
+        <is>
+          <t>GBP only</t>
+        </is>
+      </c>
+      <c r="D23" s="41" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="E23" s="42" t="inlineStr">
+        <is>
+          <t>Aftercare, the short version. Stay upright for four hours, skip the gym for the rest of the day, and leave the treated area alone. Three rules that matter more than everything else you will read online. Full guide on Instagram.</t>
+        </is>
+      </c>
+      <c r="F23" s="41" t="n">
+        <v>227</v>
+      </c>
+      <c r="G23" s="41" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="H23" s="43" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="I23" s="41" t="inlineStr">
+        <is>
+          <t>2026-09-09-aftercare-rules.jpg</t>
+        </is>
+      </c>
+      <c r="J23" s="43" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="K23" s="41">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-09-aftercare-rules.jpg")</f>
+        <v/>
+      </c>
+      <c r="L23" s="41" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="M23" s="42" t="inlineStr"/>
+    </row>
+    <row r="24" ht="58" customHeight="1" s="14">
+      <c r="A24" s="51" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B24" s="45" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C24" s="45" t="inlineStr">
+        <is>
+          <t>IG: Botox Aftercare, The First 48 Hours</t>
+        </is>
+      </c>
+      <c r="D24" s="45" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="E24" s="46" t="inlineStr">
+        <is>
+          <t>You got Botox. Now what? What to do, what to skip, and which small things are completely normal in the first 48 hours. Save it before your appointment, not after. The full guide is on Instagram.</t>
+        </is>
+      </c>
+      <c r="F24" s="45" t="n">
+        <v>194</v>
+      </c>
+      <c r="G24" s="45" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="H24" s="47" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="I24" s="45" t="inlineStr">
+        <is>
+          <t>2026-09-10-first-48-hours.jpg</t>
+        </is>
+      </c>
+      <c r="J24" s="47" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="K24" s="45">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-10-first-48-hours.jpg")</f>
+        <v/>
+      </c>
+      <c r="L24" s="45" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="M24" s="46" t="inlineStr"/>
+    </row>
+    <row r="25" ht="58" customHeight="1" s="14">
+      <c r="A25" s="51" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B25" s="45" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="C25" s="45" t="inlineStr">
+        <is>
+          <t>IG: The Face Map</t>
+        </is>
+      </c>
+      <c r="D25" s="45" t="inlineStr">
+        <is>
+          <t>Trust &amp; Proof</t>
+        </is>
+      </c>
+      <c r="E25" s="46" t="inlineStr">
+        <is>
+          <t>Every face gets its own map. Yours is drawn while it moves, because a muscle sitting still tells you almost nothing about where the product should go. That map is why two people never get the same dose. On Instagram.</t>
+        </is>
+      </c>
+      <c r="F25" s="45" t="n">
+        <v>216</v>
+      </c>
+      <c r="G25" s="45" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="H25" s="47" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="I25" s="45" t="inlineStr">
+        <is>
+          <t>2026-09-11-the-face-map.jpg</t>
+        </is>
+      </c>
+      <c r="J25" s="47" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="K25" s="45">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-11-the-face-map.jpg")</f>
+        <v/>
+      </c>
+      <c r="L25" s="45" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="M25" s="46" t="inlineStr"/>
+    </row>
+    <row r="26" ht="58" customHeight="1" s="14">
+      <c r="A26" s="51" t="n">
+        <v>46277</v>
+      </c>
+      <c r="B26" s="45" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="C26" s="45" t="inlineStr">
+        <is>
+          <t>IG: FAQ, Does Botox Hurt?</t>
+        </is>
+      </c>
+      <c r="D26" s="45" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="E26" s="46" t="inlineStr">
+        <is>
+          <t>Does it hurt? Honest answer, a quick pinch and a few seconds per area. The needle is very fine and most people say it was easier than the version they had built up in their head. No fluff, on Instagram.</t>
+        </is>
+      </c>
+      <c r="F26" s="45" t="n">
+        <v>202</v>
+      </c>
+      <c r="G26" s="45" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="H26" s="47" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="I26" s="45" t="inlineStr">
+        <is>
+          <t>2026-09-12-does-it-hurt.jpg</t>
+        </is>
+      </c>
+      <c r="J26" s="47" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="K26" s="45">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-12-does-it-hurt.jpg")</f>
+        <v/>
+      </c>
+      <c r="L26" s="45" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="M26" s="46" t="inlineStr"/>
+    </row>
+    <row r="27" ht="58" customHeight="1" s="14">
+      <c r="A27" s="50" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B27" s="41" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="C27" s="41" t="inlineStr">
+        <is>
+          <t>GBP only</t>
+        </is>
+      </c>
+      <c r="D27" s="41" t="inlineStr">
+        <is>
+          <t>Trust &amp; Proof</t>
+        </is>
+      </c>
+      <c r="E27" s="42" t="inlineStr">
+        <is>
+          <t>The goal is never a new face. It is your face on a better week, with nobody able to say quite why. If the result announces itself, something went wrong. See what that looks like on Instagram.</t>
+        </is>
+      </c>
+      <c r="F27" s="41" t="n">
+        <v>191</v>
+      </c>
+      <c r="G27" s="41" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="H27" s="43" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="I27" s="41" t="inlineStr">
+        <is>
+          <t>2026-09-13-still-look-like-you.jpg</t>
+        </is>
+      </c>
+      <c r="J27" s="43" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="K27" s="41">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-13-still-look-like-you.jpg")</f>
+        <v/>
+      </c>
+      <c r="L27" s="41" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="M27" s="42" t="inlineStr"/>
+    </row>
+    <row r="28" ht="58" customHeight="1" s="14">
+      <c r="A28" s="51" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B28" s="45" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C28" s="45" t="inlineStr">
+        <is>
+          <t>IG: 5 Things Botox Can't Do</t>
+        </is>
+      </c>
+      <c r="D28" s="45" t="inlineStr">
+        <is>
+          <t>Trust &amp; Proof</t>
+        </is>
+      </c>
+      <c r="E28" s="46" t="inlineStr">
+        <is>
+          <t>Five things Botox cannot do. It softens lines made by movement. It will not lift heavy skin, replace lost volume, or undo sun damage. Knowing the limits is how you avoid paying for the wrong treatment. Full list on Instagram.</t>
+        </is>
+      </c>
+      <c r="F28" s="45" t="n">
+        <v>225</v>
+      </c>
+      <c r="G28" s="45" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="H28" s="47" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="I28" s="45" t="inlineStr">
+        <is>
+          <t>2026-09-14-5-things-botox-cannot-do.jpg</t>
+        </is>
+      </c>
+      <c r="J28" s="47" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="K28" s="45">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-14-5-things-botox-cannot-do.jpg")</f>
+        <v/>
+      </c>
+      <c r="L28" s="45" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="M28" s="46" t="inlineStr"/>
+    </row>
+    <row r="29" ht="58" customHeight="1" s="14">
+      <c r="A29" s="51" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B29" s="45" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C29" s="45" t="inlineStr">
+        <is>
+          <t>IG: What Botox Can't Fix</t>
+        </is>
+      </c>
+      <c r="D29" s="45" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="E29" s="46" t="inlineStr">
+        <is>
+          <t>If a line is still there when your face is completely still, Botox is not the answer for it. That is a volume or a skin quality question, and it needs a different plan. Honest expectations, always. More on Instagram.</t>
+        </is>
+      </c>
+      <c r="F29" s="45" t="n">
+        <v>216</v>
+      </c>
+      <c r="G29" s="45" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="H29" s="47" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="I29" s="45" t="inlineStr">
+        <is>
+          <t>2026-09-15-what-it-cannot-fix.jpg</t>
+        </is>
+      </c>
+      <c r="J29" s="47" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="K29" s="45">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-15-what-it-cannot-fix.jpg")</f>
+        <v/>
+      </c>
+      <c r="L29" s="45" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="M29" s="46" t="inlineStr"/>
+    </row>
+    <row r="30" ht="58" customHeight="1" s="14">
+      <c r="A30" s="50" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B30" s="41" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="C30" s="41" t="inlineStr">
+        <is>
+          <t>GBP only</t>
+        </is>
+      </c>
+      <c r="D30" s="41" t="inlineStr">
+        <is>
+          <t>Trust &amp; Proof</t>
+        </is>
+      </c>
+      <c r="E30" s="42" t="inlineStr">
+        <is>
+          <t>Booking is a message, not a phone tree. Send a DM on Instagram and it is answered by Cleo herself, usually the same day. Tell me what is bothering you and I will tell you honestly whether I can help. We are at 3060 Preserve Dr, Oakville.</t>
+        </is>
+      </c>
+      <c r="F30" s="41" t="n">
+        <v>237</v>
+      </c>
+      <c r="G30" s="41" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="H30" s="43" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="I30" s="41" t="inlineStr">
+        <is>
+          <t>2026-09-16-how-to-book.jpg</t>
+        </is>
+      </c>
+      <c r="J30" s="43" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="K30" s="41">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-16-how-to-book.jpg")</f>
+        <v/>
+      </c>
+      <c r="L30" s="41" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="M30" s="42" t="inlineStr"/>
+    </row>
+    <row r="31" ht="58" customHeight="1" s="14">
+      <c r="A31" s="51" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B31" s="45" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C31" s="45" t="inlineStr">
+        <is>
+          <t>IG: Still You, Just Refreshed</t>
+        </is>
+      </c>
+      <c r="D31" s="45" t="inlineStr">
+        <is>
+          <t>Trust &amp; Proof</t>
+        </is>
+      </c>
+      <c r="E31" s="46" t="inlineStr">
+        <is>
+          <t>You will not look done. You will look like you slept properly for a week. That is the whole standard here, and it is why the dose is built around your face instead of a template. See it on Instagram.</t>
+        </is>
+      </c>
+      <c r="F31" s="45" t="n">
+        <v>199</v>
+      </c>
+      <c r="G31" s="45" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="H31" s="47" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="I31" s="45" t="inlineStr">
+        <is>
+          <t>2026-09-17-still-you-just-refreshed.jpg</t>
+        </is>
+      </c>
+      <c r="J31" s="47" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="K31" s="45">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-17-still-you-just-refreshed.jpg")</f>
+        <v/>
+      </c>
+      <c r="L31" s="45" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="M31" s="46" t="inlineStr"/>
+    </row>
+    <row r="32" ht="58" customHeight="1" s="14">
+      <c r="A32" s="51" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B32" s="45" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="C32" s="45" t="inlineStr">
+        <is>
+          <t>IG: Myth vs Truth, The Frozen Face</t>
+        </is>
+      </c>
+      <c r="D32" s="45" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="E32" s="46" t="inlineStr">
+        <is>
+          <t>The frozen face is a dosing mistake, not what the treatment does. Done properly you keep your expressions and lose the deep etched lines. The classic fear, debunked on Instagram.</t>
+        </is>
+      </c>
+      <c r="F32" s="45" t="n">
+        <v>178</v>
+      </c>
+      <c r="G32" s="45" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="H32" s="47" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="I32" s="45" t="inlineStr">
+        <is>
+          <t>2026-09-18-frozen-face-myth.jpg</t>
+        </is>
+      </c>
+      <c r="J32" s="47" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="K32" s="45">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-18-frozen-face-myth.jpg")</f>
+        <v/>
+      </c>
+      <c r="L32" s="45" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="M32" s="46" t="inlineStr"/>
+    </row>
+    <row r="33" ht="58" customHeight="1" s="14">
+      <c r="A33" s="51" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B33" s="45" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="C33" s="45" t="inlineStr">
+        <is>
+          <t>IG: Client Words, Natural Results</t>
+        </is>
+      </c>
+      <c r="D33" s="45" t="inlineStr">
+        <is>
+          <t>Trust &amp; Proof</t>
+        </is>
+      </c>
+      <c r="E33" s="46" t="inlineStr">
+        <is>
+          <t>Nobody guessed. That was the point. The compliment we are aiming for is whether you changed your skincare or got back from holiday, never what you had done. Client words on Instagram.</t>
+        </is>
+      </c>
+      <c r="F33" s="45" t="n">
+        <v>183</v>
+      </c>
+      <c r="G33" s="45" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="H33" s="47" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="I33" s="45" t="inlineStr">
+        <is>
+          <t>2026-09-19-nobody-guessed.jpg</t>
+        </is>
+      </c>
+      <c r="J33" s="47" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="K33" s="45">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-19-nobody-guessed.jpg")</f>
+        <v/>
+      </c>
+      <c r="L33" s="45" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="M33" s="46" t="inlineStr"/>
+    </row>
+    <row r="34" ht="58" customHeight="1" s="14">
+      <c r="A34" s="50" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B34" s="41" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="C34" s="41" t="inlineStr">
+        <is>
+          <t>GBP only</t>
+        </is>
+      </c>
+      <c r="D34" s="41" t="inlineStr">
+        <is>
+          <t>Trust &amp; Proof</t>
+        </is>
+      </c>
+      <c r="E34" s="42" t="inlineStr">
+        <is>
+          <t>Based at 3060 Preserve Dr in Oakville, with clients coming from Burlington, Milton and Mississauga. Private studio, free parking at the door, one appointment in the room at a time. Say hello on Instagram.</t>
+        </is>
+      </c>
+      <c r="F34" s="41" t="n">
+        <v>204</v>
+      </c>
+      <c r="G34" s="41" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="H34" s="43" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="I34" s="41" t="inlineStr">
+        <is>
+          <t>2026-09-20-service-area.jpg</t>
+        </is>
+      </c>
+      <c r="J34" s="43" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="K34" s="41">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-20-service-area.jpg")</f>
+        <v/>
+      </c>
+      <c r="L34" s="41" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="M34" s="42" t="inlineStr"/>
+    </row>
+    <row r="35" ht="58" customHeight="1" s="14">
+      <c r="A35" s="51" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B35" s="45" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C35" s="45" t="inlineStr">
+        <is>
+          <t>IG: Botox or Filler?</t>
+        </is>
+      </c>
+      <c r="D35" s="45" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="E35" s="46" t="inlineStr">
+        <is>
+          <t>Botox or filler? You might be asking for the wrong one. Lines made by movement need a neuromodulator. Hollowness and lost volume need filler. Booking the wrong one is the most common and most expensive mistake. Explained on Instagram.</t>
+        </is>
+      </c>
+      <c r="F35" s="45" t="n">
+        <v>234</v>
+      </c>
+      <c r="G35" s="45" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="H35" s="47" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="I35" s="45" t="inlineStr">
+        <is>
+          <t>2026-09-21-botox-or-filler.jpg</t>
+        </is>
+      </c>
+      <c r="J35" s="47" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="K35" s="45">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-21-botox-or-filler.jpg")</f>
+        <v/>
+      </c>
+      <c r="L35" s="45" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="M35" s="46" t="inlineStr"/>
+    </row>
+    <row r="36" ht="58" customHeight="1" s="14">
+      <c r="A36" s="51" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B36" s="45" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C36" s="45" t="inlineStr">
+        <is>
+          <t>IG: Lines vs Volume</t>
+        </is>
+      </c>
+      <c r="D36" s="45" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="E36" s="46" t="inlineStr">
+        <is>
+          <t>Here is the test. Gently pull the skin taut. If the line disappears it is a movement line. If it stays put, it is a volume question. Which one is your actual concern? More on Instagram.</t>
+        </is>
+      </c>
+      <c r="F36" s="45" t="n">
+        <v>185</v>
+      </c>
+      <c r="G36" s="45" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="H36" s="47" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="I36" s="45" t="inlineStr">
+        <is>
+          <t>2026-09-22-lines-vs-volume.jpg</t>
+        </is>
+      </c>
+      <c r="J36" s="47" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="K36" s="45">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-22-lines-vs-volume.jpg")</f>
+        <v/>
+      </c>
+      <c r="L36" s="45" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="M36" s="46" t="inlineStr"/>
+    </row>
+    <row r="37" ht="58" customHeight="1" s="14">
+      <c r="A37" s="50" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B37" s="41" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="C37" s="41" t="inlineStr">
+        <is>
+          <t>GBP only</t>
+        </is>
+      </c>
+      <c r="D37" s="41" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="E37" s="42" t="inlineStr">
+        <is>
+          <t>Five questions worth asking any clinic, including this one. Who is injecting me, what are your credentials, which product, what dose, and what happens if I am not happy. A good clinic answers all five without flinching. More on Instagram.</t>
+        </is>
+      </c>
+      <c r="F37" s="41" t="n">
+        <v>238</v>
+      </c>
+      <c r="G37" s="41" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="H37" s="43" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="I37" s="41" t="inlineStr">
+        <is>
+          <t>2026-09-23-what-to-ask.jpg</t>
+        </is>
+      </c>
+      <c r="J37" s="43" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="K37" s="41">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-23-what-to-ask.jpg")</f>
+        <v/>
+      </c>
+      <c r="L37" s="41" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="M37" s="42" t="inlineStr"/>
+    </row>
+    <row r="38" ht="58" customHeight="1" s="14">
+      <c r="A38" s="51" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B38" s="45" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C38" s="45" t="inlineStr">
+        <is>
+          <t>IG: Ask NP Cleo</t>
+        </is>
+      </c>
+      <c r="D38" s="45" t="inlineStr">
+        <is>
+          <t>Personality &amp; BTS</t>
+        </is>
+      </c>
+      <c r="E38" s="46" t="inlineStr">
+        <is>
+          <t>You asked, so here are the honest answers. The questions that land in my DMs every week, answered without the marketing gloss, including the ones clinics usually dodge. Read them on Instagram.</t>
+        </is>
+      </c>
+      <c r="F38" s="45" t="n">
+        <v>192</v>
+      </c>
+      <c r="G38" s="45" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="H38" s="47" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="I38" s="45" t="inlineStr">
+        <is>
+          <t>2026-09-24-ask-np-cleo.jpg</t>
+        </is>
+      </c>
+      <c r="J38" s="47" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="K38" s="45">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-24-ask-np-cleo.jpg")</f>
+        <v/>
+      </c>
+      <c r="L38" s="45" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="M38" s="46" t="inlineStr"/>
+    </row>
+    <row r="39" ht="58" customHeight="1" s="14">
+      <c r="A39" s="51" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B39" s="45" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="C39" s="45" t="inlineStr">
+        <is>
+          <t>IG: Your DMs, Answered</t>
+        </is>
+      </c>
+      <c r="D39" s="45" t="inlineStr">
+        <is>
+          <t>Personality &amp; BTS</t>
+        </is>
+      </c>
+      <c r="E39" s="46" t="inlineStr">
+        <is>
+          <t>The question people ask quietly, in private, almost every week. Here it is in public with a straight answer and nothing dressed up. Your questions are always welcome on Instagram.</t>
+        </is>
+      </c>
+      <c r="F39" s="45" t="n">
+        <v>179</v>
+      </c>
+      <c r="G39" s="45" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="H39" s="47" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="I39" s="45" t="inlineStr">
+        <is>
+          <t>2026-09-25-your-dms-answered.jpg</t>
+        </is>
+      </c>
+      <c r="J39" s="47" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="K39" s="45">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-25-your-dms-answered.jpg")</f>
+        <v/>
+      </c>
+      <c r="L39" s="45" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="M39" s="46" t="inlineStr"/>
+    </row>
+    <row r="40" ht="58" customHeight="1" s="14">
+      <c r="A40" s="51" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B40" s="45" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="C40" s="45" t="inlineStr">
+        <is>
+          <t>IG: Poll, What Should NP Cleo Cover Next?</t>
+        </is>
+      </c>
+      <c r="D40" s="45" t="inlineStr">
+        <is>
+          <t>Personality &amp; BTS</t>
+        </is>
+      </c>
+      <c r="E40" s="46" t="inlineStr">
+        <is>
+          <t>You pick what I cover next. The topic with the most votes becomes the next post, whether that is pricing, a treatment breakdown, or something nobody wants to explain properly. Vote on Instagram.</t>
+        </is>
+      </c>
+      <c r="F40" s="45" t="n">
+        <v>194</v>
+      </c>
+      <c r="G40" s="45" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="H40" s="47" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="I40" s="45" t="inlineStr">
+        <is>
+          <t>2026-09-26-what-next.jpg</t>
+        </is>
+      </c>
+      <c r="J40" s="47" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="K40" s="45">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-26-what-next.jpg")</f>
+        <v/>
+      </c>
+      <c r="L40" s="45" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="M40" s="46" t="inlineStr"/>
+    </row>
+    <row r="41" ht="58" customHeight="1" s="14">
+      <c r="A41" s="50" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B41" s="41" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="C41" s="41" t="inlineStr">
+        <is>
+          <t>GBP only</t>
+        </is>
+      </c>
+      <c r="D41" s="41" t="inlineStr">
+        <is>
+          <t>Trust &amp; Proof</t>
+        </is>
+      </c>
+      <c r="E41" s="42" t="inlineStr">
+        <is>
+          <t>Your two week follow up is part of the treatment, not an extra. Botox takes about fourteen days to settle, so that is when we look properly and make small adjustments if anything needs it. No charge for that visit. More on Instagram.</t>
+        </is>
+      </c>
+      <c r="F41" s="41" t="n">
+        <v>233</v>
+      </c>
+      <c r="G41" s="41" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="H41" s="43" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="I41" s="41" t="inlineStr">
+        <is>
+          <t>2026-09-27-two-week-review.jpg</t>
+        </is>
+      </c>
+      <c r="J41" s="43" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="K41" s="41">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-27-two-week-review.jpg")</f>
+        <v/>
+      </c>
+      <c r="L41" s="41" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="M41" s="42" t="inlineStr"/>
+    </row>
+    <row r="42" ht="58" customHeight="1" s="14">
+      <c r="A42" s="51" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B42" s="45" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C42" s="45" t="inlineStr">
+        <is>
+          <t>IG: How Long Does Botox Really Last?</t>
+        </is>
+      </c>
+      <c r="D42" s="45" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="E42" s="46" t="inlineStr">
+        <is>
+          <t>Three to four months for most people, and the honest reasons it varies. Your metabolism, the dose, how strong the muscle is, and how long you have been treating it. The month by month timeline is on Instagram.</t>
+        </is>
+      </c>
+      <c r="F42" s="45" t="n">
+        <v>209</v>
+      </c>
+      <c r="G42" s="45" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="H42" s="47" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="I42" s="45" t="inlineStr">
+        <is>
+          <t>2026-09-28-how-long-does-it-last.jpg</t>
+        </is>
+      </c>
+      <c r="J42" s="47" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="K42" s="45">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-28-how-long-does-it-last.jpg")</f>
+        <v/>
+      </c>
+      <c r="L42" s="45" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="M42" s="46" t="inlineStr"/>
+    </row>
+    <row r="43" ht="58" customHeight="1" s="14">
+      <c r="A43" s="51" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B43" s="45" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C43" s="45" t="inlineStr">
+        <is>
+          <t>IG: The 3-Month Botox Timeline</t>
+        </is>
+      </c>
+      <c r="D43" s="45" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="E43" s="46" t="inlineStr">
+        <is>
+          <t>Week by week, what to expect. Movement starts easing around day three, it fully settles at two weeks, softens through month three, and by month four you are due. Knowing the curve stops the day five panic. On Instagram.</t>
+        </is>
+      </c>
+      <c r="F43" s="45" t="n">
+        <v>219</v>
+      </c>
+      <c r="G43" s="45" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="H43" s="47" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="I43" s="45" t="inlineStr">
+        <is>
+          <t>2026-09-29-three-month-timeline.jpg</t>
+        </is>
+      </c>
+      <c r="J43" s="47" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="K43" s="45">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-29-three-month-timeline.jpg")</f>
+        <v/>
+      </c>
+      <c r="L43" s="45" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="M43" s="46" t="inlineStr"/>
+    </row>
+    <row r="44" ht="58" customHeight="1" s="14">
+      <c r="A44" s="50" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B44" s="41" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="C44" s="41" t="inlineStr">
+        <is>
+          <t>GBP only</t>
+        </is>
+      </c>
+      <c r="D44" s="41" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="E44" s="42" t="inlineStr">
+        <is>
+          <t>October is a month about lips. What one syringe actually does, the difference between natural and overdone, aftercare that matters, and real results shared with consent. Follow along on Instagram so you do not miss the start.</t>
+        </is>
+      </c>
+      <c r="F44" s="41" t="n">
+        <v>225</v>
+      </c>
+      <c r="G44" s="41" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="H44" s="43" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="I44" s="41" t="inlineStr">
+        <is>
+          <t>2026-09-30-october-preview.jpg</t>
+        </is>
+      </c>
+      <c r="J44" s="43" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="K44" s="41">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-30-october-preview.jpg")</f>
+        <v/>
+      </c>
+      <c r="L44" s="41" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="M44" s="42" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId86"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
@@ -8088,7 +10843,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8246,7 +11001,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8369,7 +11124,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9137,7 +11892,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/strategy/ig-content-strategy.xlsx
+++ b/strategy/ig-content-strategy.xlsx
@@ -23,9 +23,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="mmm\ d&quot;, &quot;yyyy"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -8013,7 +8014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:N44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="14" min="1" max="1"/>
@@ -8025,10 +8026,11 @@
     <col width="12" customWidth="1" style="14" min="7" max="7"/>
     <col width="26" customWidth="1" style="14" min="8" max="8"/>
     <col width="34" customWidth="1" style="14" min="9" max="9"/>
-    <col width="12" customWidth="1" style="14" min="10" max="10"/>
+    <col width="13" customWidth="1" style="14" min="10" max="10"/>
     <col width="14" customWidth="1" style="14" min="11" max="11"/>
-    <col width="10" customWidth="1" style="14" min="12" max="12"/>
-    <col width="30" customWidth="1" style="14" min="13" max="13"/>
+    <col width="24" customWidth="1" style="14" min="12" max="12"/>
+    <col width="10" customWidth="1" style="14" min="13" max="13"/>
+    <col width="30" customWidth="1" style="14" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8079,7 +8081,7 @@
       </c>
       <c r="J1" s="39" t="inlineStr">
         <is>
-          <t>Image</t>
+          <t>Open Image</t>
         </is>
       </c>
       <c r="K1" s="39" t="inlineStr">
@@ -8089,10 +8091,15 @@
       </c>
       <c r="L1" s="39" t="inlineStr">
         <is>
+          <t>Photo Credit</t>
+        </is>
+      </c>
+      <c r="M1" s="39" t="inlineStr">
+        <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="M1" s="39" t="inlineStr">
+      <c r="N1" s="39" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -8149,12 +8156,17 @@
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-08-19-one-client-at-a-time.jpg")</f>
         <v/>
       </c>
-      <c r="L2" s="41" t="inlineStr">
+      <c r="L2" s="43" t="inlineStr">
+        <is>
+          <t>Wco Global / Unsplash</t>
+        </is>
+      </c>
+      <c r="M2" s="41" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="M2" s="42" t="inlineStr"/>
+      <c r="N2" s="42" t="inlineStr"/>
     </row>
     <row r="3" ht="58" customHeight="1" s="14">
       <c r="A3" s="51" t="n">
@@ -8207,12 +8219,17 @@
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-08-20-5-red-flags.jpg")</f>
         <v/>
       </c>
-      <c r="L3" s="45" t="inlineStr">
+      <c r="L3" s="47" t="inlineStr">
+        <is>
+          <t>Look Studio / Unsplash</t>
+        </is>
+      </c>
+      <c r="M3" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="M3" s="46" t="inlineStr"/>
+      <c r="N3" s="46" t="inlineStr"/>
     </row>
     <row r="4" ht="58" customHeight="1" s="14">
       <c r="A4" s="51" t="n">
@@ -8265,12 +8282,17 @@
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-08-21-before-the-needle.jpg")</f>
         <v/>
       </c>
-      <c r="L4" s="45" t="inlineStr">
+      <c r="L4" s="47" t="inlineStr">
+        <is>
+          <t>CRYSTALWEED cannabis / Unsplash</t>
+        </is>
+      </c>
+      <c r="M4" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="M4" s="46" t="inlineStr"/>
+      <c r="N4" s="46" t="inlineStr"/>
     </row>
     <row r="5" ht="58" customHeight="1" s="14">
       <c r="A5" s="51" t="n">
@@ -8323,12 +8345,17 @@
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-08-22-great-work-is-invisible.jpg")</f>
         <v/>
       </c>
-      <c r="L5" s="45" t="inlineStr">
+      <c r="L5" s="47" t="inlineStr">
+        <is>
+          <t>Alef Morais / Unsplash</t>
+        </is>
+      </c>
+      <c r="M5" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="M5" s="46" t="inlineStr"/>
+      <c r="N5" s="46" t="inlineStr"/>
     </row>
     <row r="6" ht="58" customHeight="1" s="14">
       <c r="A6" s="50" t="n">
@@ -8381,12 +8408,17 @@
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-08-23-how-long-does-it-take.jpg")</f>
         <v/>
       </c>
-      <c r="L6" s="41" t="inlineStr">
+      <c r="L6" s="43" t="inlineStr">
+        <is>
+          <t>Ionela Mat / Unsplash</t>
+        </is>
+      </c>
+      <c r="M6" s="41" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="M6" s="42" t="inlineStr"/>
+      <c r="N6" s="42" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1" s="14">
       <c r="A7" s="51" t="n">
@@ -8439,12 +8471,17 @@
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-08-24-what-actually-happens.jpg")</f>
         <v/>
       </c>
-      <c r="L7" s="45" t="inlineStr">
+      <c r="L7" s="47" t="inlineStr">
+        <is>
+          <t>karelys Ruiz / Unsplash</t>
+        </is>
+      </c>
+      <c r="M7" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="M7" s="46" t="inlineStr"/>
+      <c r="N7" s="46" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1" s="14">
       <c r="A8" s="51" t="n">
@@ -8497,12 +8534,17 @@
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-08-25-why-no-prices.jpg")</f>
         <v/>
       </c>
-      <c r="L8" s="45" t="inlineStr">
+      <c r="L8" s="47" t="inlineStr">
+        <is>
+          <t>Lina Verovaya / Unsplash</t>
+        </is>
+      </c>
+      <c r="M8" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="M8" s="46" t="inlineStr"/>
+      <c r="N8" s="46" t="inlineStr"/>
     </row>
     <row r="9" ht="58" customHeight="1" s="14">
       <c r="A9" s="50" t="n">
@@ -8555,12 +8597,17 @@
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-08-26-who-injects-you.jpg")</f>
         <v/>
       </c>
-      <c r="L9" s="41" t="inlineStr">
+      <c r="L9" s="43" t="inlineStr">
+        <is>
+          <t>Anuruddha Lokuhapuarachchi / Unsplash</t>
+        </is>
+      </c>
+      <c r="M9" s="41" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="M9" s="42" t="inlineStr"/>
+      <c r="N9" s="42" t="inlineStr"/>
     </row>
     <row r="10" ht="58" customHeight="1" s="14">
       <c r="A10" s="51" t="n">
@@ -8613,12 +8660,17 @@
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-08-27-meet-np-cleo.jpg")</f>
         <v/>
       </c>
-      <c r="L10" s="45" t="inlineStr">
+      <c r="L10" s="47" t="inlineStr">
+        <is>
+          <t>Look Studio / Unsplash</t>
+        </is>
+      </c>
+      <c r="M10" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="M10" s="46" t="inlineStr"/>
+      <c r="N10" s="46" t="inlineStr"/>
     </row>
     <row r="11" ht="58" customHeight="1" s="14">
       <c r="A11" s="51" t="n">
@@ -8671,12 +8723,17 @@
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-08-28-where-calm-meets-careful.jpg")</f>
         <v/>
       </c>
-      <c r="L11" s="45" t="inlineStr">
+      <c r="L11" s="47" t="inlineStr">
+        <is>
+          <t>Masum Rahimi / Unsplash</t>
+        </is>
+      </c>
+      <c r="M11" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="M11" s="46" t="inlineStr"/>
+      <c r="N11" s="46" t="inlineStr"/>
     </row>
     <row r="12" ht="58" customHeight="1" s="14">
       <c r="A12" s="51" t="n">
@@ -8729,12 +8786,17 @@
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-08-29-rested-or-frozen.jpg")</f>
         <v/>
       </c>
-      <c r="L12" s="45" t="inlineStr">
+      <c r="L12" s="47" t="inlineStr">
+        <is>
+          <t>engin akyurt / Unsplash</t>
+        </is>
+      </c>
+      <c r="M12" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="M12" s="46" t="inlineStr"/>
+      <c r="N12" s="46" t="inlineStr"/>
     </row>
     <row r="13" ht="58" customHeight="1" s="14">
       <c r="A13" s="50" t="n">
@@ -8787,12 +8849,17 @@
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-08-30-what-a-consult-includes.jpg")</f>
         <v/>
       </c>
-      <c r="L13" s="41" t="inlineStr">
+      <c r="L13" s="43" t="inlineStr">
+        <is>
+          <t>Calugar Ana Maria / Unsplash</t>
+        </is>
+      </c>
+      <c r="M13" s="41" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="M13" s="42" t="inlineStr"/>
+      <c r="N13" s="42" t="inlineStr"/>
     </row>
     <row r="14" ht="58" customHeight="1" s="14">
       <c r="A14" s="51" t="n">
@@ -8845,12 +8912,17 @@
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-08-31-when-to-start.jpg")</f>
         <v/>
       </c>
-      <c r="L14" s="45" t="inlineStr">
+      <c r="L14" s="47" t="inlineStr">
+        <is>
+          <t>Fleur Kaan / Unsplash</t>
+        </is>
+      </c>
+      <c r="M14" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="M14" s="46" t="inlineStr"/>
+      <c r="N14" s="46" t="inlineStr"/>
     </row>
     <row r="15" ht="58" customHeight="1" s="14">
       <c r="A15" s="51" t="n">
@@ -8903,12 +8975,17 @@
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-01-spotlight-preventative.jpg")</f>
         <v/>
       </c>
-      <c r="L15" s="45" t="inlineStr">
+      <c r="L15" s="47" t="inlineStr">
+        <is>
+          <t>Fleur Kaan / Unsplash</t>
+        </is>
+      </c>
+      <c r="M15" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="M15" s="46" t="inlineStr"/>
+      <c r="N15" s="46" t="inlineStr"/>
     </row>
     <row r="16" ht="58" customHeight="1" s="14">
       <c r="A16" s="50" t="n">
@@ -8961,12 +9038,17 @@
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-02-is-it-safe.jpg")</f>
         <v/>
       </c>
-      <c r="L16" s="41" t="inlineStr">
+      <c r="L16" s="43" t="inlineStr">
+        <is>
+          <t>Atikah Akhtar / Unsplash</t>
+        </is>
+      </c>
+      <c r="M16" s="41" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="M16" s="42" t="inlineStr"/>
+      <c r="N16" s="42" t="inlineStr"/>
     </row>
     <row r="17" ht="58" customHeight="1" s="14">
       <c r="A17" s="51" t="n">
@@ -9019,12 +9101,17 @@
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-03-20-units.jpg")</f>
         <v/>
       </c>
-      <c r="L17" s="45" t="inlineStr">
+      <c r="L17" s="47" t="inlineStr">
+        <is>
+          <t>ONNE Beauty / Unsplash</t>
+        </is>
+      </c>
+      <c r="M17" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="M17" s="46" t="inlineStr"/>
+      <c r="N17" s="46" t="inlineStr"/>
     </row>
     <row r="18" ht="58" customHeight="1" s="14">
       <c r="A18" s="51" t="n">
@@ -9077,12 +9164,17 @@
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-04-meet-your-injector.jpg")</f>
         <v/>
       </c>
-      <c r="L18" s="45" t="inlineStr">
+      <c r="L18" s="47" t="inlineStr">
+        <is>
+          <t>Masum Rahimi / Unsplash</t>
+        </is>
+      </c>
+      <c r="M18" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="M18" s="46" t="inlineStr"/>
+      <c r="N18" s="46" t="inlineStr"/>
     </row>
     <row r="19" ht="58" customHeight="1" s="14">
       <c r="A19" s="51" t="n">
@@ -9135,12 +9227,17 @@
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-05-prevention-beats-erasing.jpg")</f>
         <v/>
       </c>
-      <c r="L19" s="45" t="inlineStr">
+      <c r="L19" s="47" t="inlineStr">
+        <is>
+          <t>Elist Nguyen / Unsplash</t>
+        </is>
+      </c>
+      <c r="M19" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="M19" s="46" t="inlineStr"/>
+      <c r="N19" s="46" t="inlineStr"/>
     </row>
     <row r="20" ht="58" customHeight="1" s="14">
       <c r="A20" s="50" t="n">
@@ -9193,12 +9290,17 @@
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-06-first-timer.jpg")</f>
         <v/>
       </c>
-      <c r="L20" s="41" t="inlineStr">
+      <c r="L20" s="43" t="inlineStr">
+        <is>
+          <t>engin akyurt / Unsplash</t>
+        </is>
+      </c>
+      <c r="M20" s="41" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="M20" s="42" t="inlineStr"/>
+      <c r="N20" s="42" t="inlineStr"/>
     </row>
     <row r="21" ht="58" customHeight="1" s="14">
       <c r="A21" s="51" t="n">
@@ -9251,12 +9353,17 @@
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-07-botox-vs-dysport.jpg")</f>
         <v/>
       </c>
-      <c r="L21" s="45" t="inlineStr">
+      <c r="L21" s="47" t="inlineStr">
+        <is>
+          <t>Catherine Grimes / Unsplash</t>
+        </is>
+      </c>
+      <c r="M21" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="M21" s="46" t="inlineStr"/>
+      <c r="N21" s="46" t="inlineStr"/>
     </row>
     <row r="22" ht="58" customHeight="1" s="14">
       <c r="A22" s="51" t="n">
@@ -9309,12 +9416,17 @@
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-08-at-a-glance.jpg")</f>
         <v/>
       </c>
-      <c r="L22" s="45" t="inlineStr">
+      <c r="L22" s="47" t="inlineStr">
+        <is>
+          <t>Gabrielle Henderson / Unsplash</t>
+        </is>
+      </c>
+      <c r="M22" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="M22" s="46" t="inlineStr"/>
+      <c r="N22" s="46" t="inlineStr"/>
     </row>
     <row r="23" ht="58" customHeight="1" s="14">
       <c r="A23" s="50" t="n">
@@ -9367,12 +9479,17 @@
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-09-aftercare-rules.jpg")</f>
         <v/>
       </c>
-      <c r="L23" s="41" t="inlineStr">
+      <c r="L23" s="43" t="inlineStr">
+        <is>
+          <t>Gabrielle Henderson / Unsplash</t>
+        </is>
+      </c>
+      <c r="M23" s="41" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="M23" s="42" t="inlineStr"/>
+      <c r="N23" s="42" t="inlineStr"/>
     </row>
     <row r="24" ht="58" customHeight="1" s="14">
       <c r="A24" s="51" t="n">
@@ -9425,12 +9542,17 @@
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-10-first-48-hours.jpg")</f>
         <v/>
       </c>
-      <c r="L24" s="45" t="inlineStr">
+      <c r="L24" s="47" t="inlineStr">
+        <is>
+          <t>ONNE Beauty / Unsplash</t>
+        </is>
+      </c>
+      <c r="M24" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="M24" s="46" t="inlineStr"/>
+      <c r="N24" s="46" t="inlineStr"/>
     </row>
     <row r="25" ht="58" customHeight="1" s="14">
       <c r="A25" s="51" t="n">
@@ -9483,12 +9605,17 @@
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-11-the-face-map.jpg")</f>
         <v/>
       </c>
-      <c r="L25" s="45" t="inlineStr">
+      <c r="L25" s="47" t="inlineStr">
+        <is>
+          <t>JEaLiFe Pictures / Unsplash</t>
+        </is>
+      </c>
+      <c r="M25" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="M25" s="46" t="inlineStr"/>
+      <c r="N25" s="46" t="inlineStr"/>
     </row>
     <row r="26" ht="58" customHeight="1" s="14">
       <c r="A26" s="51" t="n">
@@ -9541,12 +9668,17 @@
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-12-does-it-hurt.jpg")</f>
         <v/>
       </c>
-      <c r="L26" s="45" t="inlineStr">
+      <c r="L26" s="47" t="inlineStr">
+        <is>
+          <t>Victor Meza / Unsplash</t>
+        </is>
+      </c>
+      <c r="M26" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="M26" s="46" t="inlineStr"/>
+      <c r="N26" s="46" t="inlineStr"/>
     </row>
     <row r="27" ht="58" customHeight="1" s="14">
       <c r="A27" s="50" t="n">
@@ -9599,12 +9731,17 @@
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-13-still-look-like-you.jpg")</f>
         <v/>
       </c>
-      <c r="L27" s="41" t="inlineStr">
+      <c r="L27" s="43" t="inlineStr">
+        <is>
+          <t>Zac Taheriyan / Unsplash</t>
+        </is>
+      </c>
+      <c r="M27" s="41" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="M27" s="42" t="inlineStr"/>
+      <c r="N27" s="42" t="inlineStr"/>
     </row>
     <row r="28" ht="58" customHeight="1" s="14">
       <c r="A28" s="51" t="n">
@@ -9657,12 +9794,17 @@
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-14-5-things-botox-cannot-do.jpg")</f>
         <v/>
       </c>
-      <c r="L28" s="45" t="inlineStr">
+      <c r="L28" s="47" t="inlineStr">
+        <is>
+          <t>engin akyurt / Unsplash</t>
+        </is>
+      </c>
+      <c r="M28" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="M28" s="46" t="inlineStr"/>
+      <c r="N28" s="46" t="inlineStr"/>
     </row>
     <row r="29" ht="58" customHeight="1" s="14">
       <c r="A29" s="51" t="n">
@@ -9715,12 +9857,17 @@
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-15-what-it-cannot-fix.jpg")</f>
         <v/>
       </c>
-      <c r="L29" s="45" t="inlineStr">
+      <c r="L29" s="47" t="inlineStr">
+        <is>
+          <t>engin akyurt / Unsplash</t>
+        </is>
+      </c>
+      <c r="M29" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="M29" s="46" t="inlineStr"/>
+      <c r="N29" s="46" t="inlineStr"/>
     </row>
     <row r="30" ht="58" customHeight="1" s="14">
       <c r="A30" s="50" t="n">
@@ -9773,12 +9920,17 @@
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-16-how-to-book.jpg")</f>
         <v/>
       </c>
-      <c r="L30" s="41" t="inlineStr">
+      <c r="L30" s="43" t="inlineStr">
+        <is>
+          <t>Bee Naturalles / Unsplash</t>
+        </is>
+      </c>
+      <c r="M30" s="41" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="M30" s="42" t="inlineStr"/>
+      <c r="N30" s="42" t="inlineStr"/>
     </row>
     <row r="31" ht="58" customHeight="1" s="14">
       <c r="A31" s="51" t="n">
@@ -9831,12 +9983,17 @@
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-17-still-you-just-refreshed.jpg")</f>
         <v/>
       </c>
-      <c r="L31" s="45" t="inlineStr">
+      <c r="L31" s="47" t="inlineStr">
+        <is>
+          <t>Zulfugar Karimov / Unsplash</t>
+        </is>
+      </c>
+      <c r="M31" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="M31" s="46" t="inlineStr"/>
+      <c r="N31" s="46" t="inlineStr"/>
     </row>
     <row r="32" ht="58" customHeight="1" s="14">
       <c r="A32" s="51" t="n">
@@ -9889,12 +10046,17 @@
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-18-frozen-face-myth.jpg")</f>
         <v/>
       </c>
-      <c r="L32" s="45" t="inlineStr">
+      <c r="L32" s="47" t="inlineStr">
+        <is>
+          <t>Neda Vidakovic / Unsplash</t>
+        </is>
+      </c>
+      <c r="M32" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="M32" s="46" t="inlineStr"/>
+      <c r="N32" s="46" t="inlineStr"/>
     </row>
     <row r="33" ht="58" customHeight="1" s="14">
       <c r="A33" s="51" t="n">
@@ -9947,12 +10109,17 @@
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-19-nobody-guessed.jpg")</f>
         <v/>
       </c>
-      <c r="L33" s="45" t="inlineStr">
+      <c r="L33" s="47" t="inlineStr">
+        <is>
+          <t>Vitaliy Shevchenko / Unsplash</t>
+        </is>
+      </c>
+      <c r="M33" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="M33" s="46" t="inlineStr"/>
+      <c r="N33" s="46" t="inlineStr"/>
     </row>
     <row r="34" ht="58" customHeight="1" s="14">
       <c r="A34" s="50" t="n">
@@ -10005,12 +10172,17 @@
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-20-service-area.jpg")</f>
         <v/>
       </c>
-      <c r="L34" s="41" t="inlineStr">
+      <c r="L34" s="43" t="inlineStr">
+        <is>
+          <t>Elist Nguyen / Unsplash</t>
+        </is>
+      </c>
+      <c r="M34" s="41" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="M34" s="42" t="inlineStr"/>
+      <c r="N34" s="42" t="inlineStr"/>
     </row>
     <row r="35" ht="58" customHeight="1" s="14">
       <c r="A35" s="51" t="n">
@@ -10063,12 +10235,17 @@
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-21-botox-or-filler.jpg")</f>
         <v/>
       </c>
-      <c r="L35" s="45" t="inlineStr">
+      <c r="L35" s="47" t="inlineStr">
+        <is>
+          <t>Alef Morais / Unsplash</t>
+        </is>
+      </c>
+      <c r="M35" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="M35" s="46" t="inlineStr"/>
+      <c r="N35" s="46" t="inlineStr"/>
     </row>
     <row r="36" ht="58" customHeight="1" s="14">
       <c r="A36" s="51" t="n">
@@ -10121,12 +10298,17 @@
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-22-lines-vs-volume.jpg")</f>
         <v/>
       </c>
-      <c r="L36" s="45" t="inlineStr">
+      <c r="L36" s="47" t="inlineStr">
+        <is>
+          <t>Rosa Rafael / Unsplash</t>
+        </is>
+      </c>
+      <c r="M36" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="M36" s="46" t="inlineStr"/>
+      <c r="N36" s="46" t="inlineStr"/>
     </row>
     <row r="37" ht="58" customHeight="1" s="14">
       <c r="A37" s="50" t="n">
@@ -10179,12 +10361,17 @@
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-23-what-to-ask.jpg")</f>
         <v/>
       </c>
-      <c r="L37" s="41" t="inlineStr">
+      <c r="L37" s="43" t="inlineStr">
+        <is>
+          <t>Soheil Kmp / Unsplash</t>
+        </is>
+      </c>
+      <c r="M37" s="41" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="M37" s="42" t="inlineStr"/>
+      <c r="N37" s="42" t="inlineStr"/>
     </row>
     <row r="38" ht="58" customHeight="1" s="14">
       <c r="A38" s="51" t="n">
@@ -10237,12 +10424,17 @@
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-24-ask-np-cleo.jpg")</f>
         <v/>
       </c>
-      <c r="L38" s="45" t="inlineStr">
+      <c r="L38" s="47" t="inlineStr">
+        <is>
+          <t>Look Studio / Unsplash</t>
+        </is>
+      </c>
+      <c r="M38" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="M38" s="46" t="inlineStr"/>
+      <c r="N38" s="46" t="inlineStr"/>
     </row>
     <row r="39" ht="58" customHeight="1" s="14">
       <c r="A39" s="51" t="n">
@@ -10295,12 +10487,17 @@
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-25-your-dms-answered.jpg")</f>
         <v/>
       </c>
-      <c r="L39" s="45" t="inlineStr">
+      <c r="L39" s="47" t="inlineStr">
+        <is>
+          <t>Masum Rahimi / Unsplash</t>
+        </is>
+      </c>
+      <c r="M39" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="M39" s="46" t="inlineStr"/>
+      <c r="N39" s="46" t="inlineStr"/>
     </row>
     <row r="40" ht="58" customHeight="1" s="14">
       <c r="A40" s="51" t="n">
@@ -10353,12 +10550,17 @@
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-26-what-next.jpg")</f>
         <v/>
       </c>
-      <c r="L40" s="45" t="inlineStr">
+      <c r="L40" s="47" t="inlineStr">
+        <is>
+          <t>Calugar Ana Maria / Unsplash</t>
+        </is>
+      </c>
+      <c r="M40" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="M40" s="46" t="inlineStr"/>
+      <c r="N40" s="46" t="inlineStr"/>
     </row>
     <row r="41" ht="58" customHeight="1" s="14">
       <c r="A41" s="50" t="n">
@@ -10411,12 +10613,17 @@
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-27-two-week-review.jpg")</f>
         <v/>
       </c>
-      <c r="L41" s="41" t="inlineStr">
+      <c r="L41" s="43" t="inlineStr">
+        <is>
+          <t>Ionela Mat / Unsplash</t>
+        </is>
+      </c>
+      <c r="M41" s="41" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="M41" s="42" t="inlineStr"/>
+      <c r="N41" s="42" t="inlineStr"/>
     </row>
     <row r="42" ht="58" customHeight="1" s="14">
       <c r="A42" s="51" t="n">
@@ -10469,12 +10676,17 @@
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-28-how-long-does-it-last.jpg")</f>
         <v/>
       </c>
-      <c r="L42" s="45" t="inlineStr">
+      <c r="L42" s="47" t="inlineStr">
+        <is>
+          <t>ONNE Beauty / Unsplash</t>
+        </is>
+      </c>
+      <c r="M42" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="M42" s="46" t="inlineStr"/>
+      <c r="N42" s="46" t="inlineStr"/>
     </row>
     <row r="43" ht="58" customHeight="1" s="14">
       <c r="A43" s="51" t="n">
@@ -10527,12 +10739,17 @@
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-29-three-month-timeline.jpg")</f>
         <v/>
       </c>
-      <c r="L43" s="45" t="inlineStr">
+      <c r="L43" s="47" t="inlineStr">
+        <is>
+          <t>Catherine Grimes / Unsplash</t>
+        </is>
+      </c>
+      <c r="M43" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="M43" s="46" t="inlineStr"/>
+      <c r="N43" s="46" t="inlineStr"/>
     </row>
     <row r="44" ht="58" customHeight="1" s="14">
       <c r="A44" s="50" t="n">
@@ -10585,101 +10802,149 @@
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-30-october-preview.jpg")</f>
         <v/>
       </c>
-      <c r="L44" s="41" t="inlineStr">
+      <c r="L44" s="43" t="inlineStr">
+        <is>
+          <t>Christin Hume / Unsplash</t>
+        </is>
+      </c>
+      <c r="M44" s="41" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="M44" s="42" t="inlineStr"/>
+      <c r="N44" s="42" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId129"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/strategy/ig-content-strategy.xlsx
+++ b/strategy/ig-content-strategy.xlsx
@@ -8014,23 +8014,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N44"/>
+  <dimension ref="A1:P44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="14" min="1" max="1"/>
     <col width="6" customWidth="1" style="14" min="2" max="2"/>
-    <col width="34" customWidth="1" style="14" min="3" max="3"/>
-    <col width="18" customWidth="1" style="14" min="4" max="4"/>
-    <col width="78" customWidth="1" style="14" min="5" max="5"/>
+    <col width="32" customWidth="1" style="14" min="3" max="3"/>
+    <col width="17" customWidth="1" style="14" min="4" max="4"/>
+    <col width="54" customWidth="1" style="14" min="5" max="5"/>
     <col width="7" customWidth="1" style="14" min="6" max="6"/>
-    <col width="12" customWidth="1" style="14" min="7" max="7"/>
-    <col width="26" customWidth="1" style="14" min="8" max="8"/>
-    <col width="34" customWidth="1" style="14" min="9" max="9"/>
-    <col width="13" customWidth="1" style="14" min="10" max="10"/>
-    <col width="14" customWidth="1" style="14" min="11" max="11"/>
-    <col width="24" customWidth="1" style="14" min="12" max="12"/>
-    <col width="10" customWidth="1" style="14" min="13" max="13"/>
-    <col width="30" customWidth="1" style="14" min="14" max="14"/>
+    <col width="96" customWidth="1" style="14" min="7" max="7"/>
+    <col width="8" customWidth="1" style="14" min="8" max="8"/>
+    <col width="12" customWidth="1" style="14" min="9" max="9"/>
+    <col width="26" customWidth="1" style="14" min="10" max="10"/>
+    <col width="32" customWidth="1" style="14" min="11" max="11"/>
+    <col width="13" customWidth="1" style="14" min="12" max="12"/>
+    <col width="14" customWidth="1" style="14" min="13" max="13"/>
+    <col width="24" customWidth="1" style="14" min="14" max="14"/>
+    <col width="10" customWidth="1" style="14" min="15" max="15"/>
+    <col width="28" customWidth="1" style="14" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8056,7 +8058,7 @@
       </c>
       <c r="E1" s="39" t="inlineStr">
         <is>
-          <t>Post Text (first 80 chars show)</t>
+          <t>Post Text (short)</t>
         </is>
       </c>
       <c r="F1" s="39" t="inlineStr">
@@ -8066,46 +8068,56 @@
       </c>
       <c r="G1" s="39" t="inlineStr">
         <is>
+          <t>Description (long, SEO)</t>
+        </is>
+      </c>
+      <c r="H1" s="39" t="inlineStr">
+        <is>
+          <t>Desc Chars</t>
+        </is>
+      </c>
+      <c r="I1" s="39" t="inlineStr">
+        <is>
           <t>CTA Button</t>
         </is>
       </c>
-      <c r="H1" s="39" t="inlineStr">
+      <c r="J1" s="39" t="inlineStr">
         <is>
           <t>CTA Link</t>
         </is>
       </c>
-      <c r="I1" s="39" t="inlineStr">
+      <c r="K1" s="39" t="inlineStr">
         <is>
           <t>Image File</t>
         </is>
       </c>
-      <c r="J1" s="39" t="inlineStr">
+      <c r="L1" s="39" t="inlineStr">
         <is>
           <t>Open Image</t>
         </is>
       </c>
-      <c r="K1" s="39" t="inlineStr">
+      <c r="M1" s="39" t="inlineStr">
         <is>
           <t>Preview</t>
         </is>
       </c>
-      <c r="L1" s="39" t="inlineStr">
+      <c r="N1" s="39" t="inlineStr">
         <is>
           <t>Photo Credit</t>
         </is>
       </c>
-      <c r="M1" s="39" t="inlineStr">
+      <c r="O1" s="39" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="N1" s="39" t="inlineStr">
+      <c r="P1" s="39" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="58" customHeight="1" s="14">
+    <row r="2" ht="132" customHeight="1" s="14">
       <c r="A2" s="50" t="n">
         <v>46253</v>
       </c>
@@ -8132,43 +8144,53 @@
       <c r="F2" s="41" t="n">
         <v>242</v>
       </c>
-      <c r="G2" s="41" t="inlineStr">
+      <c r="G2" s="42" t="inlineStr">
+        <is>
+          <t>One client in the room at a time, in a private Oakville studio. That is a scheduling choice, not a luxury one. When two people are booked over each other, someone gets rushed, and the person being rushed is usually the one asking the most questions.
+Your appointment is injected by a nurse practitioner, never handed to whoever is free. You get the same face across visits, which matters more than people expect. Dose is built on what your muscles did last time, so the second appointment is always better informed than the first.
+The studio is on Preserve Dr with free parking at the door, and people drive in from Burlington, Milton and Mississauga for Botox and filler. Come see the room and the work on Instagram.</t>
+        </is>
+      </c>
+      <c r="H2" s="41" t="n">
+        <v>719</v>
+      </c>
+      <c r="I2" s="41" t="inlineStr">
         <is>
           <t>Learn more</t>
         </is>
       </c>
-      <c r="H2" s="43" t="inlineStr">
+      <c r="J2" s="43" t="inlineStr">
         <is>
           <t>@luxury_beauty_aestheticz</t>
         </is>
       </c>
-      <c r="I2" s="41" t="inlineStr">
+      <c r="K2" s="41" t="inlineStr">
         <is>
           <t>2026-08-19-one-client-at-a-time.jpg</t>
         </is>
       </c>
-      <c r="J2" s="43" t="inlineStr">
+      <c r="L2" s="43" t="inlineStr">
         <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="K2" s="41">
+      <c r="M2" s="41">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-08-19-one-client-at-a-time.jpg")</f>
         <v/>
       </c>
-      <c r="L2" s="43" t="inlineStr">
+      <c r="N2" s="43" t="inlineStr">
         <is>
           <t>Wco Global / Unsplash</t>
         </is>
       </c>
-      <c r="M2" s="41" t="inlineStr">
+      <c r="O2" s="41" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="N2" s="42" t="inlineStr"/>
-    </row>
-    <row r="3" ht="58" customHeight="1" s="14">
+      <c r="P2" s="42" t="inlineStr"/>
+    </row>
+    <row r="3" ht="132" customHeight="1" s="14">
       <c r="A3" s="51" t="n">
         <v>46254</v>
       </c>
@@ -8195,43 +8217,54 @@
       <c r="F3" s="45" t="n">
         <v>244</v>
       </c>
-      <c r="G3" s="45" t="inlineStr">
+      <c r="G3" s="46" t="inlineStr">
+        <is>
+          <t>Five things to walk away from at a med spa: no consultation, bargain pricing, a provider who never says no, no named injector, and pressure to decide today.
+The consultation is the one people skip. If nobody watched your face move before picking a dose, the dose is a guess. Bargain pricing is the second. Neuromodulator has a real per unit cost, so a price well under the going rate in Oakville usually means the product is overdiluted or the units are short.
+The hardest one to spot is a provider who agrees with everything. Some faces should not get what they came in asking for, and you want the person holding the needle to say so.
+Ask who is injecting you, what their credentials are, and what happens if you are unhappy. The full list is on Instagram.</t>
+        </is>
+      </c>
+      <c r="H3" s="45" t="n">
+        <v>761</v>
+      </c>
+      <c r="I3" s="45" t="inlineStr">
         <is>
           <t>Learn more</t>
         </is>
       </c>
-      <c r="H3" s="47" t="inlineStr">
+      <c r="J3" s="47" t="inlineStr">
         <is>
           <t>@luxury_beauty_aestheticz</t>
         </is>
       </c>
-      <c r="I3" s="45" t="inlineStr">
+      <c r="K3" s="45" t="inlineStr">
         <is>
           <t>2026-08-20-5-red-flags.jpg</t>
         </is>
       </c>
-      <c r="J3" s="47" t="inlineStr">
+      <c r="L3" s="47" t="inlineStr">
         <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="K3" s="45">
+      <c r="M3" s="45">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-08-20-5-red-flags.jpg")</f>
         <v/>
       </c>
-      <c r="L3" s="47" t="inlineStr">
+      <c r="N3" s="47" t="inlineStr">
         <is>
           <t>Look Studio / Unsplash</t>
         </is>
       </c>
-      <c r="M3" s="45" t="inlineStr">
+      <c r="O3" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="N3" s="46" t="inlineStr"/>
-    </row>
-    <row r="4" ht="58" customHeight="1" s="14">
+      <c r="P3" s="46" t="inlineStr"/>
+    </row>
+    <row r="4" ht="132" customHeight="1" s="14">
       <c r="A4" s="51" t="n">
         <v>46255</v>
       </c>
@@ -8258,43 +8291,53 @@
       <c r="F4" s="45" t="n">
         <v>226</v>
       </c>
-      <c r="G4" s="45" t="inlineStr">
+      <c r="G4" s="46" t="inlineStr">
+        <is>
+          <t>Every appointment here starts the same way. A new tray, product opened sealed in front of you, and your face mapped while it moves.
+Mapping in motion is the part that changes the result. A forehead at rest tells you almost nothing. I need to see you frown, lift, squint and smile, because that is where the muscle is actually pulling and where the product needs to sit. Two people with identical lines often get very different plans.
+Prep is the unglamorous part nobody photographs, and it is most of what separates good Botox from the kind people notice. We photographed it anyway. On Instagram.</t>
+        </is>
+      </c>
+      <c r="H4" s="45" t="n">
+        <v>598</v>
+      </c>
+      <c r="I4" s="45" t="inlineStr">
         <is>
           <t>Learn more</t>
         </is>
       </c>
-      <c r="H4" s="47" t="inlineStr">
+      <c r="J4" s="47" t="inlineStr">
         <is>
           <t>@luxury_beauty_aestheticz</t>
         </is>
       </c>
-      <c r="I4" s="45" t="inlineStr">
+      <c r="K4" s="45" t="inlineStr">
         <is>
           <t>2026-08-21-before-the-needle.jpg</t>
         </is>
       </c>
-      <c r="J4" s="47" t="inlineStr">
+      <c r="L4" s="47" t="inlineStr">
         <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="K4" s="45">
+      <c r="M4" s="45">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-08-21-before-the-needle.jpg")</f>
         <v/>
       </c>
-      <c r="L4" s="47" t="inlineStr">
+      <c r="N4" s="47" t="inlineStr">
         <is>
           <t>CRYSTALWEED cannabis / Unsplash</t>
         </is>
       </c>
-      <c r="M4" s="45" t="inlineStr">
+      <c r="O4" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="N4" s="46" t="inlineStr"/>
-    </row>
-    <row r="5" ht="58" customHeight="1" s="14">
+      <c r="P4" s="46" t="inlineStr"/>
+    </row>
+    <row r="5" ht="132" customHeight="1" s="14">
       <c r="A5" s="51" t="n">
         <v>46256</v>
       </c>
@@ -8321,43 +8364,54 @@
       <c r="F5" s="45" t="n">
         <v>236</v>
       </c>
-      <c r="G5" s="45" t="inlineStr">
+      <c r="G5" s="46" t="inlineStr">
+        <is>
+          <t>One syringe of lip filler, with her own lip shape kept exactly where it was.
+This is the standard I work to. Filler should follow the border you already have rather than invent a new one. That means respecting the ratio between top and bottom lip, keeping the cupid's bow, and stopping while it still looks like a good day rather than a decision.
+One syringe goes further than most people think when it is placed well. The difference between natural and obvious is rarely the volume. It is where it sits and whether the injector was willing to stop.
+Shared with client consent. Individual results vary, and lips in particular differ with anatomy and swelling. More natural lip filler work from our Oakville studio on Instagram.</t>
+        </is>
+      </c>
+      <c r="H5" s="45" t="n">
+        <v>730</v>
+      </c>
+      <c r="I5" s="45" t="inlineStr">
         <is>
           <t>Learn more</t>
         </is>
       </c>
-      <c r="H5" s="47" t="inlineStr">
+      <c r="J5" s="47" t="inlineStr">
         <is>
           <t>@luxury_beauty_aestheticz</t>
         </is>
       </c>
-      <c r="I5" s="45" t="inlineStr">
+      <c r="K5" s="45" t="inlineStr">
         <is>
           <t>2026-08-22-great-work-is-invisible.jpg</t>
         </is>
       </c>
-      <c r="J5" s="47" t="inlineStr">
+      <c r="L5" s="47" t="inlineStr">
         <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="K5" s="45">
+      <c r="M5" s="45">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-08-22-great-work-is-invisible.jpg")</f>
         <v/>
       </c>
-      <c r="L5" s="47" t="inlineStr">
+      <c r="N5" s="47" t="inlineStr">
         <is>
           <t>Alef Morais / Unsplash</t>
         </is>
       </c>
-      <c r="M5" s="45" t="inlineStr">
+      <c r="O5" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="N5" s="46" t="inlineStr"/>
-    </row>
-    <row r="6" ht="58" customHeight="1" s="14">
+      <c r="P5" s="46" t="inlineStr"/>
+    </row>
+    <row r="6" ht="132" customHeight="1" s="14">
       <c r="A6" s="50" t="n">
         <v>46257</v>
       </c>
@@ -8384,43 +8438,54 @@
       <c r="F6" s="41" t="n">
         <v>246</v>
       </c>
-      <c r="G6" s="41" t="inlineStr">
+      <c r="G6" s="42" t="inlineStr">
+        <is>
+          <t>A first visit runs about 45 minutes, and most of that is talking.
+Here is the breakdown. Fifteen to twenty minutes on what is actually bothering you and what you want your face to do. Then mapping, where I watch your expressions and mark where the muscle pulls. Then a plan and a price, agreed and written down before anything is opened.
+The injecting itself is closer to ten minutes. People are usually surprised by how short that part is, and how long the rest takes. That ratio is deliberate.
+You can book a Botox consultation in Oakville and leave without treatment. Plenty do, and it is a completely normal outcome. Ask anything on Instagram.</t>
+        </is>
+      </c>
+      <c r="H6" s="41" t="n">
+        <v>650</v>
+      </c>
+      <c r="I6" s="41" t="inlineStr">
         <is>
           <t>Learn more</t>
         </is>
       </c>
-      <c r="H6" s="43" t="inlineStr">
+      <c r="J6" s="43" t="inlineStr">
         <is>
           <t>@luxury_beauty_aestheticz</t>
         </is>
       </c>
-      <c r="I6" s="41" t="inlineStr">
+      <c r="K6" s="41" t="inlineStr">
         <is>
           <t>2026-08-23-how-long-does-it-take.jpg</t>
         </is>
       </c>
-      <c r="J6" s="43" t="inlineStr">
+      <c r="L6" s="43" t="inlineStr">
         <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="K6" s="41">
+      <c r="M6" s="41">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-08-23-how-long-does-it-take.jpg")</f>
         <v/>
       </c>
-      <c r="L6" s="43" t="inlineStr">
+      <c r="N6" s="43" t="inlineStr">
         <is>
           <t>Ionela Mat / Unsplash</t>
         </is>
       </c>
-      <c r="M6" s="41" t="inlineStr">
+      <c r="O6" s="41" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="N6" s="42" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1" s="14">
+      <c r="P6" s="42" t="inlineStr"/>
+    </row>
+    <row r="7" ht="132" customHeight="1" s="14">
       <c r="A7" s="51" t="n">
         <v>46258</v>
       </c>
@@ -8447,43 +8512,54 @@
       <c r="F7" s="45" t="n">
         <v>231</v>
       </c>
-      <c r="G7" s="45" t="inlineStr">
+      <c r="G7" s="46" t="inlineStr">
+        <is>
+          <t>Nervous about a first appointment? Here is the whole thing, start to finish.
+You arrive and we talk before anything else. I want to know what you notice in photos, what you have been told elsewhere, and what you are worried about. Then I map your face in motion. Then you get a written plan and a written price, and nothing is opened until you have agreed to both.
+Treatment takes about ten minutes. You go straight back to your day, with the aftercare rules on a card: stay upright four hours, skip the gym, leave the area alone.
+At two weeks you come back so we can look properly and adjust if anything needs it. That visit is included in the price of your Botox. Step by step on Instagram.</t>
+        </is>
+      </c>
+      <c r="H7" s="45" t="n">
+        <v>695</v>
+      </c>
+      <c r="I7" s="45" t="inlineStr">
         <is>
           <t>Learn more</t>
         </is>
       </c>
-      <c r="H7" s="47" t="inlineStr">
+      <c r="J7" s="47" t="inlineStr">
         <is>
           <t>@luxury_beauty_aestheticz</t>
         </is>
       </c>
-      <c r="I7" s="45" t="inlineStr">
+      <c r="K7" s="45" t="inlineStr">
         <is>
           <t>2026-08-24-what-actually-happens.jpg</t>
         </is>
       </c>
-      <c r="J7" s="47" t="inlineStr">
+      <c r="L7" s="47" t="inlineStr">
         <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="K7" s="45">
+      <c r="M7" s="45">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-08-24-what-actually-happens.jpg")</f>
         <v/>
       </c>
-      <c r="L7" s="47" t="inlineStr">
+      <c r="N7" s="47" t="inlineStr">
         <is>
           <t>karelys Ruiz / Unsplash</t>
         </is>
       </c>
-      <c r="M7" s="45" t="inlineStr">
+      <c r="O7" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="N7" s="46" t="inlineStr"/>
-    </row>
-    <row r="8" ht="58" customHeight="1" s="14">
+      <c r="P7" s="46" t="inlineStr"/>
+    </row>
+    <row r="8" ht="132" customHeight="1" s="14">
       <c r="A8" s="51" t="n">
         <v>46259</v>
       </c>
@@ -8510,43 +8586,54 @@
       <c r="F8" s="45" t="n">
         <v>236</v>
       </c>
-      <c r="G8" s="45" t="inlineStr">
+      <c r="G8" s="46" t="inlineStr">
+        <is>
+          <t>Why there is no price list on this page. Doses differ from face to face, so one flat price either overcharges you or under treats you.
+A strong forehead muscle needs more units than a light one. Someone treating a line for the first time needs a different amount than someone maintaining. Publishing a single number for an area means one of those people is paying for units they do not need and the other is being quietly short dosed to keep the number attractive.
+What you get instead is a written number at your consultation, based on your face and the units it actually takes. No moving target once you are in the chair.
+If you want a ballpark before booking, message me on Instagram and describe what is bothering you. I will give you an honest range for Botox or filler at our Oakville studio.</t>
+        </is>
+      </c>
+      <c r="H8" s="45" t="n">
+        <v>801</v>
+      </c>
+      <c r="I8" s="45" t="inlineStr">
         <is>
           <t>Learn more</t>
         </is>
       </c>
-      <c r="H8" s="47" t="inlineStr">
+      <c r="J8" s="47" t="inlineStr">
         <is>
           <t>@luxury_beauty_aestheticz</t>
         </is>
       </c>
-      <c r="I8" s="45" t="inlineStr">
+      <c r="K8" s="45" t="inlineStr">
         <is>
           <t>2026-08-25-why-no-prices.jpg</t>
         </is>
       </c>
-      <c r="J8" s="47" t="inlineStr">
+      <c r="L8" s="47" t="inlineStr">
         <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="K8" s="45">
+      <c r="M8" s="45">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-08-25-why-no-prices.jpg")</f>
         <v/>
       </c>
-      <c r="L8" s="47" t="inlineStr">
+      <c r="N8" s="47" t="inlineStr">
         <is>
           <t>Lina Verovaya / Unsplash</t>
         </is>
       </c>
-      <c r="M8" s="45" t="inlineStr">
+      <c r="O8" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="N8" s="46" t="inlineStr"/>
-    </row>
-    <row r="9" ht="58" customHeight="1" s="14">
+      <c r="P8" s="46" t="inlineStr"/>
+    </row>
+    <row r="9" ht="132" customHeight="1" s="14">
       <c r="A9" s="50" t="n">
         <v>46260</v>
       </c>
@@ -8573,43 +8660,54 @@
       <c r="F9" s="41" t="n">
         <v>248</v>
       </c>
-      <c r="G9" s="41" t="inlineStr">
+      <c r="G9" s="42" t="inlineStr">
+        <is>
+          <t>Ask any clinic who is actually holding the needle. It is a fair question and a good clinic will not flinch at it.
+Here it is a nurse practitioner, RN(EC), registered with the College of Nurses of Ontario. Every appointment is injected by Cleo. Nothing is delegated to someone you have not met, and nothing is handed off partway through.
+That continuity is not just about credentials. Seeing the same face each visit means the plan builds. I know how your muscles responded last time, how long it lasted for you, and where we went lighter on purpose.
+Credentials are public and worth checking, here or anywhere else you are considering for Botox in Oakville. Meet her on Instagram.</t>
+        </is>
+      </c>
+      <c r="H9" s="41" t="n">
+        <v>683</v>
+      </c>
+      <c r="I9" s="41" t="inlineStr">
         <is>
           <t>Learn more</t>
         </is>
       </c>
-      <c r="H9" s="43" t="inlineStr">
+      <c r="J9" s="43" t="inlineStr">
         <is>
           <t>@luxury_beauty_aestheticz</t>
         </is>
       </c>
-      <c r="I9" s="41" t="inlineStr">
+      <c r="K9" s="41" t="inlineStr">
         <is>
           <t>2026-08-26-who-injects-you.jpg</t>
         </is>
       </c>
-      <c r="J9" s="43" t="inlineStr">
+      <c r="L9" s="43" t="inlineStr">
         <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="K9" s="41">
+      <c r="M9" s="41">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-08-26-who-injects-you.jpg")</f>
         <v/>
       </c>
-      <c r="L9" s="43" t="inlineStr">
+      <c r="N9" s="43" t="inlineStr">
         <is>
           <t>Anuruddha Lokuhapuarachchi / Unsplash</t>
         </is>
       </c>
-      <c r="M9" s="41" t="inlineStr">
+      <c r="O9" s="41" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="N9" s="42" t="inlineStr"/>
-    </row>
-    <row r="10" ht="58" customHeight="1" s="14">
+      <c r="P9" s="42" t="inlineStr"/>
+    </row>
+    <row r="10" ht="132" customHeight="1" s="14">
       <c r="A10" s="51" t="n">
         <v>46261</v>
       </c>
@@ -8636,43 +8734,54 @@
       <c r="F10" s="45" t="n">
         <v>206</v>
       </c>
-      <c r="G10" s="45" t="inlineStr">
+      <c r="G10" s="46" t="inlineStr">
+        <is>
+          <t>Meet NP Cleo. Nurse practitioner, injector, and the person who will tell you no when the honest answer is no.
+That last part costs money and keeps the work good. Some requests do not suit the face in front of me. Sometimes the line someone wants softened is a volume issue and a neuromodulator will not touch it. Saying so loses the booking and saves the result.
+Every appointment at this Oakville studio is injected by Cleo, never delegated. Clients come from Burlington, Milton and Mississauga, mostly on referral from someone whose work nobody could identify.
+The full introduction, and the reasoning behind how she doses, is on Instagram.</t>
+        </is>
+      </c>
+      <c r="H10" s="45" t="n">
+        <v>645</v>
+      </c>
+      <c r="I10" s="45" t="inlineStr">
         <is>
           <t>Learn more</t>
         </is>
       </c>
-      <c r="H10" s="47" t="inlineStr">
+      <c r="J10" s="47" t="inlineStr">
         <is>
           <t>@luxury_beauty_aestheticz</t>
         </is>
       </c>
-      <c r="I10" s="45" t="inlineStr">
+      <c r="K10" s="45" t="inlineStr">
         <is>
           <t>2026-08-27-meet-np-cleo.jpg</t>
         </is>
       </c>
-      <c r="J10" s="47" t="inlineStr">
+      <c r="L10" s="47" t="inlineStr">
         <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="K10" s="45">
+      <c r="M10" s="45">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-08-27-meet-np-cleo.jpg")</f>
         <v/>
       </c>
-      <c r="L10" s="47" t="inlineStr">
+      <c r="N10" s="47" t="inlineStr">
         <is>
           <t>Look Studio / Unsplash</t>
         </is>
       </c>
-      <c r="M10" s="45" t="inlineStr">
+      <c r="O10" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="N10" s="46" t="inlineStr"/>
-    </row>
-    <row r="11" ht="58" customHeight="1" s="14">
+      <c r="P10" s="46" t="inlineStr"/>
+    </row>
+    <row r="11" ht="132" customHeight="1" s="14">
       <c r="A11" s="51" t="n">
         <v>46262</v>
       </c>
@@ -8699,43 +8808,54 @@
       <c r="F11" s="45" t="n">
         <v>211</v>
       </c>
-      <c r="G11" s="45" t="inlineStr">
+      <c r="G11" s="46" t="inlineStr">
+        <is>
+          <t>One client in the treatment room at a time. Nobody rushes the person before you, so nobody rushes you.
+A private room changes what people are willing to ask. The questions that matter most are usually the ones people feel silly saying out loud in a waiting area, about cost, about looking overdone, about whether they will still look like themselves at a family event.
+The door stays shut and those questions stay welcome, however small they feel. There is no upsell script here and no add on being pushed while you are already in the chair.
+There is no upsell script here and no add on being pushed while you are already in the chair. Come see the Oakville treatment room on Instagram, and message if you want to know anything before you book Botox or filler.</t>
+        </is>
+      </c>
+      <c r="H11" s="45" t="n">
+        <v>763</v>
+      </c>
+      <c r="I11" s="45" t="inlineStr">
         <is>
           <t>Learn more</t>
         </is>
       </c>
-      <c r="H11" s="47" t="inlineStr">
+      <c r="J11" s="47" t="inlineStr">
         <is>
           <t>@luxury_beauty_aestheticz</t>
         </is>
       </c>
-      <c r="I11" s="45" t="inlineStr">
+      <c r="K11" s="45" t="inlineStr">
         <is>
           <t>2026-08-28-where-calm-meets-careful.jpg</t>
         </is>
       </c>
-      <c r="J11" s="47" t="inlineStr">
+      <c r="L11" s="47" t="inlineStr">
         <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="K11" s="45">
+      <c r="M11" s="45">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-08-28-where-calm-meets-careful.jpg")</f>
         <v/>
       </c>
-      <c r="L11" s="47" t="inlineStr">
+      <c r="N11" s="47" t="inlineStr">
         <is>
           <t>Masum Rahimi / Unsplash</t>
         </is>
       </c>
-      <c r="M11" s="45" t="inlineStr">
+      <c r="O11" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="N11" s="46" t="inlineStr"/>
-    </row>
-    <row r="12" ht="58" customHeight="1" s="14">
+      <c r="P11" s="46" t="inlineStr"/>
+    </row>
+    <row r="12" ht="132" customHeight="1" s="14">
       <c r="A12" s="51" t="n">
         <v>46263</v>
       </c>
@@ -8762,43 +8882,54 @@
       <c r="F12" s="45" t="n">
         <v>205</v>
       </c>
-      <c r="G12" s="45" t="inlineStr">
+      <c r="G12" s="46" t="inlineStr">
+        <is>
+          <t>Rested, not frozen. You should still frown, squint and smile after treatment.
+Movement is not a side effect you tolerate, it is the goal. A face that cannot move reads as work done. A face that moves with softer lines reads as sleep, water and a good few weeks. The second one is what people are actually paying for.
+Getting there is a dosing decision, not a product one. It means treating the muscle that is pulling hardest and leaving the ones doing useful work alone. It often means using fewer units than someone expects and asking them back at two weeks rather than chasing it all in one sitting.
+If people ask what you had done instead of whether you slept well, the Botox dose was wrong. See the difference side by side on Instagram.</t>
+        </is>
+      </c>
+      <c r="H12" s="45" t="n">
+        <v>743</v>
+      </c>
+      <c r="I12" s="45" t="inlineStr">
         <is>
           <t>Learn more</t>
         </is>
       </c>
-      <c r="H12" s="47" t="inlineStr">
+      <c r="J12" s="47" t="inlineStr">
         <is>
           <t>@luxury_beauty_aestheticz</t>
         </is>
       </c>
-      <c r="I12" s="45" t="inlineStr">
+      <c r="K12" s="45" t="inlineStr">
         <is>
           <t>2026-08-29-rested-or-frozen.jpg</t>
         </is>
       </c>
-      <c r="J12" s="47" t="inlineStr">
+      <c r="L12" s="47" t="inlineStr">
         <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="K12" s="45">
+      <c r="M12" s="45">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-08-29-rested-or-frozen.jpg")</f>
         <v/>
       </c>
-      <c r="L12" s="47" t="inlineStr">
+      <c r="N12" s="47" t="inlineStr">
         <is>
           <t>engin akyurt / Unsplash</t>
         </is>
       </c>
-      <c r="M12" s="45" t="inlineStr">
+      <c r="O12" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="N12" s="46" t="inlineStr"/>
-    </row>
-    <row r="13" ht="58" customHeight="1" s="14">
+      <c r="P12" s="46" t="inlineStr"/>
+    </row>
+    <row r="13" ht="132" customHeight="1" s="14">
       <c r="A13" s="50" t="n">
         <v>46264</v>
       </c>
@@ -8825,43 +8956,54 @@
       <c r="F13" s="41" t="n">
         <v>229</v>
       </c>
-      <c r="G13" s="41" t="inlineStr">
+      <c r="G13" s="42" t="inlineStr">
+        <is>
+          <t>A consultation is not a sales appointment. You can leave without booking anything and that is a completely normal outcome.
+What it actually includes: your goals in your own words, your face mapped while it moves, and a straight answer about what will work and what will not. If the thing bothering you is not a neuromodulator problem, I will tell you that rather than sell you the closest thing I offer.
+You leave with a written plan and a written price. No deposit to hear it, no pressure to decide in the room, and no follow up chasing you.
+Booking a consultation at our Oakville studio is a message on Instagram. Tell me what you are considering and we will start there.</t>
+        </is>
+      </c>
+      <c r="H13" s="41" t="n">
+        <v>676</v>
+      </c>
+      <c r="I13" s="41" t="inlineStr">
         <is>
           <t>Learn more</t>
         </is>
       </c>
-      <c r="H13" s="43" t="inlineStr">
+      <c r="J13" s="43" t="inlineStr">
         <is>
           <t>@luxury_beauty_aestheticz</t>
         </is>
       </c>
-      <c r="I13" s="41" t="inlineStr">
+      <c r="K13" s="41" t="inlineStr">
         <is>
           <t>2026-08-30-what-a-consult-includes.jpg</t>
         </is>
       </c>
-      <c r="J13" s="43" t="inlineStr">
+      <c r="L13" s="43" t="inlineStr">
         <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="K13" s="41">
+      <c r="M13" s="41">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-08-30-what-a-consult-includes.jpg")</f>
         <v/>
       </c>
-      <c r="L13" s="43" t="inlineStr">
+      <c r="N13" s="43" t="inlineStr">
         <is>
           <t>Calugar Ana Maria / Unsplash</t>
         </is>
       </c>
-      <c r="M13" s="41" t="inlineStr">
+      <c r="O13" s="41" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="N13" s="42" t="inlineStr"/>
-    </row>
-    <row r="14" ht="58" customHeight="1" s="14">
+      <c r="P13" s="42" t="inlineStr"/>
+    </row>
+    <row r="14" ht="132" customHeight="1" s="14">
       <c r="A14" s="51" t="n">
         <v>46265</v>
       </c>
@@ -8888,43 +9030,54 @@
       <c r="F14" s="45" t="n">
         <v>225</v>
       </c>
-      <c r="G14" s="45" t="inlineStr">
+      <c r="G14" s="46" t="inlineStr">
+        <is>
+          <t>When should you actually start preventative Botox? It is not about your age, and the birthday number people quote is meaningless.
+Here is the test. Make your strongest expression, hold it, then relax your face completely. If a line stays behind after everything has released, that one is setting into the skin. That is the line worth treating early, whether you are 26 or 41.
+Starting before a line is etched means smaller doses, spaced further apart, and a softer result than chasing it later. Waiting until it is permanent does not make treatment impossible, it makes it slower and more expensive.
+If you are not sure what you are looking at, take a photo mid expression and one relaxed and send both. Preventative Botox in Oakville, explained properly on Instagram.</t>
+        </is>
+      </c>
+      <c r="H14" s="45" t="n">
+        <v>771</v>
+      </c>
+      <c r="I14" s="45" t="inlineStr">
         <is>
           <t>Learn more</t>
         </is>
       </c>
-      <c r="H14" s="47" t="inlineStr">
+      <c r="J14" s="47" t="inlineStr">
         <is>
           <t>@luxury_beauty_aestheticz</t>
         </is>
       </c>
-      <c r="I14" s="45" t="inlineStr">
+      <c r="K14" s="45" t="inlineStr">
         <is>
           <t>2026-08-31-when-to-start.jpg</t>
         </is>
       </c>
-      <c r="J14" s="47" t="inlineStr">
+      <c r="L14" s="47" t="inlineStr">
         <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="K14" s="45">
+      <c r="M14" s="45">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-08-31-when-to-start.jpg")</f>
         <v/>
       </c>
-      <c r="L14" s="47" t="inlineStr">
+      <c r="N14" s="47" t="inlineStr">
         <is>
           <t>Fleur Kaan / Unsplash</t>
         </is>
       </c>
-      <c r="M14" s="45" t="inlineStr">
+      <c r="O14" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="N14" s="46" t="inlineStr"/>
-    </row>
-    <row r="15" ht="58" customHeight="1" s="14">
+      <c r="P14" s="46" t="inlineStr"/>
+    </row>
+    <row r="15" ht="132" customHeight="1" s="14">
       <c r="A15" s="51" t="n">
         <v>46266</v>
       </c>
@@ -8951,43 +9104,54 @@
       <c r="F15" s="45" t="n">
         <v>221</v>
       </c>
-      <c r="G15" s="45" t="inlineStr">
+      <c r="G15" s="46" t="inlineStr">
+        <is>
+          <t>Preventative Botox, explained plainly. Small doses started before a line sets in, so it never becomes permanent.
+The muscle folds the skin the same way thousands of times. Early on the skin springs back. Over years it stops, and the crease stays after the expression has gone. Treating before that point keeps the fold from becoming a fixture.
+It is dosed lighter than corrective work. The aim is to soften how hard the muscle pulls while leaving you full expression, not to shut movement down. Most people start with fewer units than they expect and come back at two weeks.
+Not every face needs it yet, and I will say so. Book a consultation at our Oakville studio, or ask on Instagram first.</t>
+        </is>
+      </c>
+      <c r="H15" s="45" t="n">
+        <v>696</v>
+      </c>
+      <c r="I15" s="45" t="inlineStr">
         <is>
           <t>Learn more</t>
         </is>
       </c>
-      <c r="H15" s="47" t="inlineStr">
+      <c r="J15" s="47" t="inlineStr">
         <is>
           <t>@luxury_beauty_aestheticz</t>
         </is>
       </c>
-      <c r="I15" s="45" t="inlineStr">
+      <c r="K15" s="45" t="inlineStr">
         <is>
           <t>2026-09-01-spotlight-preventative.jpg</t>
         </is>
       </c>
-      <c r="J15" s="47" t="inlineStr">
+      <c r="L15" s="47" t="inlineStr">
         <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="K15" s="45">
+      <c r="M15" s="45">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-01-spotlight-preventative.jpg")</f>
         <v/>
       </c>
-      <c r="L15" s="47" t="inlineStr">
+      <c r="N15" s="47" t="inlineStr">
         <is>
           <t>Fleur Kaan / Unsplash</t>
         </is>
       </c>
-      <c r="M15" s="45" t="inlineStr">
+      <c r="O15" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="N15" s="46" t="inlineStr"/>
-    </row>
-    <row r="16" ht="58" customHeight="1" s="14">
+      <c r="P15" s="46" t="inlineStr"/>
+    </row>
+    <row r="16" ht="132" customHeight="1" s="14">
       <c r="A16" s="50" t="n">
         <v>46267</v>
       </c>
@@ -9014,43 +9178,54 @@
       <c r="F16" s="41" t="n">
         <v>225</v>
       </c>
-      <c r="G16" s="41" t="inlineStr">
+      <c r="G16" s="42" t="inlineStr">
+        <is>
+          <t>The question people are too polite to ask out loud. Is it safe.
+Product is Health Canada approved and opened sealed in front of you, so you can see what is going in. It is injected by a nurse practitioner registered with the College of Nurses of Ontario, in a private room with single use needles and a new tray for every appointment.
+Side effects are usually small and short: a pinprick mark, occasional bruising, sometimes a mild headache the first day. The rarer issues, like a heavy lid, almost always come from product placed where it should not have been. That is a technique problem, which is exactly why who injects you matters more than which brand is on the vial.
+Who injects you matters more than which brand is on the vial. Ask me anything about Botox safety on Instagram. No question is too basic.</t>
+        </is>
+      </c>
+      <c r="H16" s="41" t="n">
+        <v>813</v>
+      </c>
+      <c r="I16" s="41" t="inlineStr">
         <is>
           <t>Learn more</t>
         </is>
       </c>
-      <c r="H16" s="43" t="inlineStr">
+      <c r="J16" s="43" t="inlineStr">
         <is>
           <t>@luxury_beauty_aestheticz</t>
         </is>
       </c>
-      <c r="I16" s="41" t="inlineStr">
+      <c r="K16" s="41" t="inlineStr">
         <is>
           <t>2026-09-02-is-it-safe.jpg</t>
         </is>
       </c>
-      <c r="J16" s="43" t="inlineStr">
+      <c r="L16" s="43" t="inlineStr">
         <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="K16" s="41">
+      <c r="M16" s="41">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-02-is-it-safe.jpg")</f>
         <v/>
       </c>
-      <c r="L16" s="43" t="inlineStr">
+      <c r="N16" s="43" t="inlineStr">
         <is>
           <t>Atikah Akhtar / Unsplash</t>
         </is>
       </c>
-      <c r="M16" s="41" t="inlineStr">
+      <c r="O16" s="41" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="N16" s="42" t="inlineStr"/>
-    </row>
-    <row r="17" ht="58" customHeight="1" s="14">
+      <c r="P16" s="42" t="inlineStr"/>
+    </row>
+    <row r="17" ht="132" customHeight="1" s="14">
       <c r="A17" s="51" t="n">
         <v>46268</v>
       </c>
@@ -9077,43 +9252,54 @@
       <c r="F17" s="45" t="n">
         <v>228</v>
       </c>
-      <c r="G17" s="45" t="inlineStr">
+      <c r="G17" s="46" t="inlineStr">
+        <is>
+          <t>Unit math, finally explained. Units measure dose, not strength, and the number you need depends on how hard your muscle pulls.
+Twenty units in a strong frown muscle and twenty in a light one give completely different results. This is why a flat per area price rarely tells the truth. Two people book the same treatment, one gets enough product and the other quietly gets short dosed to keep the price attractive.
+It is also why comparing your number to a friend's is a dead end. Hers might be right for her face and wrong for yours in either direction.
+What you should get is a unit count in writing before anything is opened, and an explanation of why that number. That is how Botox is priced here in Oakville. The full breakdown is on Instagram.</t>
+        </is>
+      </c>
+      <c r="H17" s="45" t="n">
+        <v>750</v>
+      </c>
+      <c r="I17" s="45" t="inlineStr">
         <is>
           <t>Learn more</t>
         </is>
       </c>
-      <c r="H17" s="47" t="inlineStr">
+      <c r="J17" s="47" t="inlineStr">
         <is>
           <t>@luxury_beauty_aestheticz</t>
         </is>
       </c>
-      <c r="I17" s="45" t="inlineStr">
+      <c r="K17" s="45" t="inlineStr">
         <is>
           <t>2026-09-03-20-units.jpg</t>
         </is>
       </c>
-      <c r="J17" s="47" t="inlineStr">
+      <c r="L17" s="47" t="inlineStr">
         <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="K17" s="45">
+      <c r="M17" s="45">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-03-20-units.jpg")</f>
         <v/>
       </c>
-      <c r="L17" s="47" t="inlineStr">
+      <c r="N17" s="47" t="inlineStr">
         <is>
           <t>ONNE Beauty / Unsplash</t>
         </is>
       </c>
-      <c r="M17" s="45" t="inlineStr">
+      <c r="O17" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="N17" s="46" t="inlineStr"/>
-    </row>
-    <row r="18" ht="58" customHeight="1" s="14">
+      <c r="P17" s="46" t="inlineStr"/>
+    </row>
+    <row r="18" ht="132" customHeight="1" s="14">
       <c r="A18" s="51" t="n">
         <v>46269</v>
       </c>
@@ -9140,43 +9326,54 @@
       <c r="F18" s="45" t="n">
         <v>215</v>
       </c>
-      <c r="G18" s="45" t="inlineStr">
+      <c r="G18" s="46" t="inlineStr">
+        <is>
+          <t>Your injector is a nurse practitioner, RN(EC), registered with the College of Nurses of Ontario.
+An NP scope means assessing you properly, not just administering. That covers your medical history, what medications you are on, previous work someone else did, and whether treatment is right for you at all. It also means being able to say no with a reason attached.
+The honest part is what people remember. If your concern is skin quality or lost volume, a neuromodulator is not the answer and you will hear that instead of a booking. It is the least profitable sentence in this business and the one that keeps clients for years.
+Look mine up, and look up anyone else you are considering for Botox in Oakville. It takes two minutes and it is the single most useful thing you can do before booking. Get to know her on Instagram.</t>
+        </is>
+      </c>
+      <c r="H18" s="45" t="n">
+        <v>828</v>
+      </c>
+      <c r="I18" s="45" t="inlineStr">
         <is>
           <t>Learn more</t>
         </is>
       </c>
-      <c r="H18" s="47" t="inlineStr">
+      <c r="J18" s="47" t="inlineStr">
         <is>
           <t>@luxury_beauty_aestheticz</t>
         </is>
       </c>
-      <c r="I18" s="45" t="inlineStr">
+      <c r="K18" s="45" t="inlineStr">
         <is>
           <t>2026-09-04-meet-your-injector.jpg</t>
         </is>
       </c>
-      <c r="J18" s="47" t="inlineStr">
+      <c r="L18" s="47" t="inlineStr">
         <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="K18" s="45">
+      <c r="M18" s="45">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-04-meet-your-injector.jpg")</f>
         <v/>
       </c>
-      <c r="L18" s="47" t="inlineStr">
+      <c r="N18" s="47" t="inlineStr">
         <is>
           <t>Masum Rahimi / Unsplash</t>
         </is>
       </c>
-      <c r="M18" s="45" t="inlineStr">
+      <c r="O18" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="N18" s="46" t="inlineStr"/>
-    </row>
-    <row r="19" ht="58" customHeight="1" s="14">
+      <c r="P18" s="46" t="inlineStr"/>
+    </row>
+    <row r="19" ht="132" customHeight="1" s="14">
       <c r="A19" s="51" t="n">
         <v>46270</v>
       </c>
@@ -9203,43 +9400,54 @@
       <c r="F19" s="45" t="n">
         <v>203</v>
       </c>
-      <c r="G19" s="45" t="inlineStr">
+      <c r="G19" s="46" t="inlineStr">
+        <is>
+          <t>Prevention beats erasing. Ask the friend who never seems to age and started early.
+A line has two stages. First it appears only when you move. Later it stays when your face is still, because the skin has been folded the same way for years and stopped springing back. Treating in the first stage takes less product, less often, and holds better.
+By the second stage a neuromodulator still helps, but it is softening something already set rather than stopping it forming. That usually means pairing it with something else and a longer timeline.
+This is not an argument for treating everyone early. It is an argument for looking at your own face honestly and knowing which stage you are in. More on preventative treatment in Oakville, on Instagram.</t>
+        </is>
+      </c>
+      <c r="H19" s="45" t="n">
+        <v>748</v>
+      </c>
+      <c r="I19" s="45" t="inlineStr">
         <is>
           <t>Learn more</t>
         </is>
       </c>
-      <c r="H19" s="47" t="inlineStr">
+      <c r="J19" s="47" t="inlineStr">
         <is>
           <t>@luxury_beauty_aestheticz</t>
         </is>
       </c>
-      <c r="I19" s="45" t="inlineStr">
+      <c r="K19" s="45" t="inlineStr">
         <is>
           <t>2026-09-05-prevention-beats-erasing.jpg</t>
         </is>
       </c>
-      <c r="J19" s="47" t="inlineStr">
+      <c r="L19" s="47" t="inlineStr">
         <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="K19" s="45">
+      <c r="M19" s="45">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-05-prevention-beats-erasing.jpg")</f>
         <v/>
       </c>
-      <c r="L19" s="47" t="inlineStr">
+      <c r="N19" s="47" t="inlineStr">
         <is>
           <t>Elist Nguyen / Unsplash</t>
         </is>
       </c>
-      <c r="M19" s="45" t="inlineStr">
+      <c r="O19" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="N19" s="46" t="inlineStr"/>
-    </row>
-    <row r="20" ht="58" customHeight="1" s="14">
+      <c r="P19" s="46" t="inlineStr"/>
+    </row>
+    <row r="20" ht="132" customHeight="1" s="14">
       <c r="A20" s="50" t="n">
         <v>46271</v>
       </c>
@@ -9266,43 +9474,54 @@
       <c r="F20" s="41" t="n">
         <v>236</v>
       </c>
-      <c r="G20" s="41" t="inlineStr">
+      <c r="G20" s="42" t="inlineStr">
+        <is>
+          <t>Never had injectables before? Most first appointments open with a question the person thinks sounds silly.
+They are not. The ones I hear most: will I look done, will people notice, what happens if I hate it, and can I still raise my eyebrows at my kids. All reasonable, all worth asking before anything is opened.
+You can book a consultation, ask every one of them, and leave with treatment nothing more than an option. No deposit to have the conversation. No follow up chasing you afterwards.
+If booking a room still feels like too much, message first. I answer my own DMs on Instagram and you will get a straight answer rather than a booking link. First timers welcome, in Oakville and from Burlington, Milton and Mississauga.</t>
+        </is>
+      </c>
+      <c r="H20" s="41" t="n">
+        <v>731</v>
+      </c>
+      <c r="I20" s="41" t="inlineStr">
         <is>
           <t>Learn more</t>
         </is>
       </c>
-      <c r="H20" s="43" t="inlineStr">
+      <c r="J20" s="43" t="inlineStr">
         <is>
           <t>@luxury_beauty_aestheticz</t>
         </is>
       </c>
-      <c r="I20" s="41" t="inlineStr">
+      <c r="K20" s="41" t="inlineStr">
         <is>
           <t>2026-09-06-first-timer.jpg</t>
         </is>
       </c>
-      <c r="J20" s="43" t="inlineStr">
+      <c r="L20" s="43" t="inlineStr">
         <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="K20" s="41">
+      <c r="M20" s="41">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-06-first-timer.jpg")</f>
         <v/>
       </c>
-      <c r="L20" s="43" t="inlineStr">
+      <c r="N20" s="43" t="inlineStr">
         <is>
           <t>engin akyurt / Unsplash</t>
         </is>
       </c>
-      <c r="M20" s="41" t="inlineStr">
+      <c r="O20" s="41" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="N20" s="42" t="inlineStr"/>
-    </row>
-    <row r="21" ht="58" customHeight="1" s="14">
+      <c r="P20" s="42" t="inlineStr"/>
+    </row>
+    <row r="21" ht="132" customHeight="1" s="14">
       <c r="A21" s="51" t="n">
         <v>46272</v>
       </c>
@@ -9329,43 +9548,54 @@
       <c r="F21" s="45" t="n">
         <v>231</v>
       </c>
-      <c r="G21" s="45" t="inlineStr">
+      <c r="G21" s="46" t="inlineStr">
+        <is>
+          <t>Botox or Dysport? Same family, different personalities, and the choice matters less than most comparison articles suggest.
+Dysport tends to spread a little more from the injection point and often kicks in a day or two sooner. Botox tends to stay put more precisely, which is useful in small areas where you want a tight boundary. Both relax the muscle the same way.
+Which suits you depends on the area being treated and how your muscle behaves, not on which name you recognise. A broad forehead and a small crow's foot are not the same problem.
+If you have had one and it wore off faster than expected, mention it at your consultation. Sometimes the answer is the other product, more often it is the dose. Full comparison, from an Oakville injector, on Instagram.</t>
+        </is>
+      </c>
+      <c r="H21" s="45" t="n">
+        <v>766</v>
+      </c>
+      <c r="I21" s="45" t="inlineStr">
         <is>
           <t>Learn more</t>
         </is>
       </c>
-      <c r="H21" s="47" t="inlineStr">
+      <c r="J21" s="47" t="inlineStr">
         <is>
           <t>@luxury_beauty_aestheticz</t>
         </is>
       </c>
-      <c r="I21" s="45" t="inlineStr">
+      <c r="K21" s="45" t="inlineStr">
         <is>
           <t>2026-09-07-botox-vs-dysport.jpg</t>
         </is>
       </c>
-      <c r="J21" s="47" t="inlineStr">
+      <c r="L21" s="47" t="inlineStr">
         <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="K21" s="45">
+      <c r="M21" s="45">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-07-botox-vs-dysport.jpg")</f>
         <v/>
       </c>
-      <c r="L21" s="47" t="inlineStr">
+      <c r="N21" s="47" t="inlineStr">
         <is>
           <t>Catherine Grimes / Unsplash</t>
         </is>
       </c>
-      <c r="M21" s="45" t="inlineStr">
+      <c r="O21" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="N21" s="46" t="inlineStr"/>
-    </row>
-    <row r="22" ht="58" customHeight="1" s="14">
+      <c r="P21" s="46" t="inlineStr"/>
+    </row>
+    <row r="22" ht="132" customHeight="1" s="14">
       <c r="A22" s="51" t="n">
         <v>46273</v>
       </c>
@@ -9392,43 +9622,54 @@
       <c r="F22" s="45" t="n">
         <v>187</v>
       </c>
-      <c r="G22" s="45" t="inlineStr">
+      <c r="G22" s="46" t="inlineStr">
+        <is>
+          <t>Onset, spread and duration side by side, so you can ask a sharper question at your consultation.
+Onset: Dysport often shows in two to three days, Botox around three to five. Both fully settle at two weeks, which is when we judge the result, not before. Spread: Dysport diffuses a little wider from each point, Botox stays tighter. Duration: three to four months for most people with either one.
+That is the honest extent of the difference. Anyone telling you one is dramatically better than the other is selling something.
+The more useful conversation is about your muscle, your area and your dose. Bring the comparison to a consultation in Oakville and we will work from there. The card is on Instagram.</t>
+        </is>
+      </c>
+      <c r="H22" s="45" t="n">
+        <v>707</v>
+      </c>
+      <c r="I22" s="45" t="inlineStr">
         <is>
           <t>Learn more</t>
         </is>
       </c>
-      <c r="H22" s="47" t="inlineStr">
+      <c r="J22" s="47" t="inlineStr">
         <is>
           <t>@luxury_beauty_aestheticz</t>
         </is>
       </c>
-      <c r="I22" s="45" t="inlineStr">
+      <c r="K22" s="45" t="inlineStr">
         <is>
           <t>2026-09-08-at-a-glance.jpg</t>
         </is>
       </c>
-      <c r="J22" s="47" t="inlineStr">
+      <c r="L22" s="47" t="inlineStr">
         <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="K22" s="45">
+      <c r="M22" s="45">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-08-at-a-glance.jpg")</f>
         <v/>
       </c>
-      <c r="L22" s="47" t="inlineStr">
+      <c r="N22" s="47" t="inlineStr">
         <is>
           <t>Gabrielle Henderson / Unsplash</t>
         </is>
       </c>
-      <c r="M22" s="45" t="inlineStr">
+      <c r="O22" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="N22" s="46" t="inlineStr"/>
-    </row>
-    <row r="23" ht="58" customHeight="1" s="14">
+      <c r="P22" s="46" t="inlineStr"/>
+    </row>
+    <row r="23" ht="132" customHeight="1" s="14">
       <c r="A23" s="50" t="n">
         <v>46274</v>
       </c>
@@ -9455,43 +9696,54 @@
       <c r="F23" s="41" t="n">
         <v>227</v>
       </c>
-      <c r="G23" s="41" t="inlineStr">
+      <c r="G23" s="42" t="inlineStr">
+        <is>
+          <t>Aftercare, the short version. Stay upright for four hours, skip the gym for the rest of the day, and leave the treated area alone.
+The reasoning is the same for all three. Product needs to stay where it was placed while it binds. Lying flat, raising your heart rate hard, or rubbing the area can move it a few millimetres, and a few millimetres is the difference between a good result and a heavy brow.
+Things that are fine: normal walking, work, makeup after a few hours, a glass of wine. Things worth avoiding for 24 hours: hot yoga, saunas, facials and face down massage.
+A small raised bump at each point is normal and settles within an hour. The full Botox aftercare guide is on Instagram, worth saving before your appointment rather than after.</t>
+        </is>
+      </c>
+      <c r="H23" s="41" t="n">
+        <v>753</v>
+      </c>
+      <c r="I23" s="41" t="inlineStr">
         <is>
           <t>Learn more</t>
         </is>
       </c>
-      <c r="H23" s="43" t="inlineStr">
+      <c r="J23" s="43" t="inlineStr">
         <is>
           <t>@luxury_beauty_aestheticz</t>
         </is>
       </c>
-      <c r="I23" s="41" t="inlineStr">
+      <c r="K23" s="41" t="inlineStr">
         <is>
           <t>2026-09-09-aftercare-rules.jpg</t>
         </is>
       </c>
-      <c r="J23" s="43" t="inlineStr">
+      <c r="L23" s="43" t="inlineStr">
         <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="K23" s="41">
+      <c r="M23" s="41">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-09-aftercare-rules.jpg")</f>
         <v/>
       </c>
-      <c r="L23" s="43" t="inlineStr">
+      <c r="N23" s="43" t="inlineStr">
         <is>
           <t>Gabrielle Henderson / Unsplash</t>
         </is>
       </c>
-      <c r="M23" s="41" t="inlineStr">
+      <c r="O23" s="41" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="N23" s="42" t="inlineStr"/>
-    </row>
-    <row r="24" ht="58" customHeight="1" s="14">
+      <c r="P23" s="42" t="inlineStr"/>
+    </row>
+    <row r="24" ht="132" customHeight="1" s="14">
       <c r="A24" s="51" t="n">
         <v>46275</v>
       </c>
@@ -9518,43 +9770,54 @@
       <c r="F24" s="45" t="n">
         <v>194</v>
       </c>
-      <c r="G24" s="45" t="inlineStr">
+      <c r="G24" s="46" t="inlineStr">
+        <is>
+          <t>You got Botox. Now what? Here is what the first 48 hours actually look like.
+First four hours: stay upright and leave the area alone. First day: no gym, no sauna, no face down massage. Small raised bumps at each injection point settle within the hour, and a pinprick mark or light bruise is common and covers with makeup after a few hours.
+Day two to three is when most people notice movement starting to ease. It is gradual, and it is uneven at first, which is normal and not a sign something went wrong.
+Do not judge anything until two weeks. That is when Botox has fully settled and when we look properly at your follow up, included with every appointment in Oakville. Save the full guide from Instagram.</t>
+        </is>
+      </c>
+      <c r="H24" s="45" t="n">
+        <v>710</v>
+      </c>
+      <c r="I24" s="45" t="inlineStr">
         <is>
           <t>Learn more</t>
         </is>
       </c>
-      <c r="H24" s="47" t="inlineStr">
+      <c r="J24" s="47" t="inlineStr">
         <is>
           <t>@luxury_beauty_aestheticz</t>
         </is>
       </c>
-      <c r="I24" s="45" t="inlineStr">
+      <c r="K24" s="45" t="inlineStr">
         <is>
           <t>2026-09-10-first-48-hours.jpg</t>
         </is>
       </c>
-      <c r="J24" s="47" t="inlineStr">
+      <c r="L24" s="47" t="inlineStr">
         <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="K24" s="45">
+      <c r="M24" s="45">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-10-first-48-hours.jpg")</f>
         <v/>
       </c>
-      <c r="L24" s="47" t="inlineStr">
+      <c r="N24" s="47" t="inlineStr">
         <is>
           <t>ONNE Beauty / Unsplash</t>
         </is>
       </c>
-      <c r="M24" s="45" t="inlineStr">
+      <c r="O24" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="N24" s="46" t="inlineStr"/>
-    </row>
-    <row r="25" ht="58" customHeight="1" s="14">
+      <c r="P24" s="46" t="inlineStr"/>
+    </row>
+    <row r="25" ht="132" customHeight="1" s="14">
       <c r="A25" s="51" t="n">
         <v>46276</v>
       </c>
@@ -9581,43 +9844,54 @@
       <c r="F25" s="45" t="n">
         <v>216</v>
       </c>
-      <c r="G25" s="45" t="inlineStr">
+      <c r="G25" s="46" t="inlineStr">
+        <is>
+          <t>Every face gets its own map, and yours is drawn while it moves.
+A muscle sitting still tells you almost nothing. I need to see the frown, the lift, the squint and the smile, because that is where the pull actually is. People are rarely symmetrical. One brow usually works harder, and treating both sides identically is how you end up with a lift on one side and not the other.
+The map is why two people with the same concern get different unit counts and different placements. It is also why I keep yours between visits. The second appointment starts from what your face did with the first one, rather than from scratch.
+That is the difference between a plan and a menu, and it is why no two Botox appointments here use the same numbers. See how the mapping works on Instagram.</t>
+        </is>
+      </c>
+      <c r="H25" s="45" t="n">
+        <v>780</v>
+      </c>
+      <c r="I25" s="45" t="inlineStr">
         <is>
           <t>Learn more</t>
         </is>
       </c>
-      <c r="H25" s="47" t="inlineStr">
+      <c r="J25" s="47" t="inlineStr">
         <is>
           <t>@luxury_beauty_aestheticz</t>
         </is>
       </c>
-      <c r="I25" s="45" t="inlineStr">
+      <c r="K25" s="45" t="inlineStr">
         <is>
           <t>2026-09-11-the-face-map.jpg</t>
         </is>
       </c>
-      <c r="J25" s="47" t="inlineStr">
+      <c r="L25" s="47" t="inlineStr">
         <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="K25" s="45">
+      <c r="M25" s="45">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-11-the-face-map.jpg")</f>
         <v/>
       </c>
-      <c r="L25" s="47" t="inlineStr">
+      <c r="N25" s="47" t="inlineStr">
         <is>
           <t>JEaLiFe Pictures / Unsplash</t>
         </is>
       </c>
-      <c r="M25" s="45" t="inlineStr">
+      <c r="O25" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="N25" s="46" t="inlineStr"/>
-    </row>
-    <row r="26" ht="58" customHeight="1" s="14">
+      <c r="P25" s="46" t="inlineStr"/>
+    </row>
+    <row r="26" ht="132" customHeight="1" s="14">
       <c r="A26" s="51" t="n">
         <v>46277</v>
       </c>
@@ -9644,43 +9918,54 @@
       <c r="F26" s="45" t="n">
         <v>202</v>
       </c>
-      <c r="G26" s="45" t="inlineStr">
+      <c r="G26" s="46" t="inlineStr">
+        <is>
+          <t>Does it hurt? Honest answer: a quick pinch, a few seconds per area.
+The needle is very fine, finer than the one used for bloodwork, and each injection point takes about a second. A forehead is usually four to six points. Most people describe it as a sharp scratch that is over before they have finished bracing for it.
+Some spots are more sensitive than others. Between the brows is the one people feel most. The area around the eyes is usually the easiest. No numbing cream is needed for a neuromodulator, though it is an option for filler.
+Most people say it was easier than the version they had built up in their head, and the second appointment is always easier than the first. Ask me anything about Botox in Oakville on Instagram.</t>
+        </is>
+      </c>
+      <c r="H26" s="45" t="n">
+        <v>738</v>
+      </c>
+      <c r="I26" s="45" t="inlineStr">
         <is>
           <t>Learn more</t>
         </is>
       </c>
-      <c r="H26" s="47" t="inlineStr">
+      <c r="J26" s="47" t="inlineStr">
         <is>
           <t>@luxury_beauty_aestheticz</t>
         </is>
       </c>
-      <c r="I26" s="45" t="inlineStr">
+      <c r="K26" s="45" t="inlineStr">
         <is>
           <t>2026-09-12-does-it-hurt.jpg</t>
         </is>
       </c>
-      <c r="J26" s="47" t="inlineStr">
+      <c r="L26" s="47" t="inlineStr">
         <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="K26" s="45">
+      <c r="M26" s="45">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-12-does-it-hurt.jpg")</f>
         <v/>
       </c>
-      <c r="L26" s="47" t="inlineStr">
+      <c r="N26" s="47" t="inlineStr">
         <is>
           <t>Victor Meza / Unsplash</t>
         </is>
       </c>
-      <c r="M26" s="45" t="inlineStr">
+      <c r="O26" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="N26" s="46" t="inlineStr"/>
-    </row>
-    <row r="27" ht="58" customHeight="1" s="14">
+      <c r="P26" s="46" t="inlineStr"/>
+    </row>
+    <row r="27" ht="132" customHeight="1" s="14">
       <c r="A27" s="50" t="n">
         <v>46278</v>
       </c>
@@ -9707,43 +9992,54 @@
       <c r="F27" s="41" t="n">
         <v>191</v>
       </c>
-      <c r="G27" s="41" t="inlineStr">
+      <c r="G27" s="42" t="inlineStr">
+        <is>
+          <t>The goal is never a new face. It is your face on a better week, with nobody able to say quite why.
+That sounds modest until you see the alternative. Overdone work announces itself: a forehead that will not move, brows sitting in a place they have never sat, lips that arrive in a room first. Once a face crosses that line, everyone reads it as work, including people who cannot name what changed.
+Staying on the right side of it is mostly about restraint. Fewer units than the maximum. Stopping while it still looks understated. Being willing to leave asymmetry that is actually just your face.
+If a result announces itself, something went wrong. That standard is why people drive to this Oakville studio from Burlington and Milton for Botox. See the alternative on Instagram.</t>
+        </is>
+      </c>
+      <c r="H27" s="41" t="n">
+        <v>779</v>
+      </c>
+      <c r="I27" s="41" t="inlineStr">
         <is>
           <t>Learn more</t>
         </is>
       </c>
-      <c r="H27" s="43" t="inlineStr">
+      <c r="J27" s="43" t="inlineStr">
         <is>
           <t>@luxury_beauty_aestheticz</t>
         </is>
       </c>
-      <c r="I27" s="41" t="inlineStr">
+      <c r="K27" s="41" t="inlineStr">
         <is>
           <t>2026-09-13-still-look-like-you.jpg</t>
         </is>
       </c>
-      <c r="J27" s="43" t="inlineStr">
+      <c r="L27" s="43" t="inlineStr">
         <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="K27" s="41">
+      <c r="M27" s="41">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-13-still-look-like-you.jpg")</f>
         <v/>
       </c>
-      <c r="L27" s="43" t="inlineStr">
+      <c r="N27" s="43" t="inlineStr">
         <is>
           <t>Zac Taheriyan / Unsplash</t>
         </is>
       </c>
-      <c r="M27" s="41" t="inlineStr">
+      <c r="O27" s="41" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="N27" s="42" t="inlineStr"/>
-    </row>
-    <row r="28" ht="58" customHeight="1" s="14">
+      <c r="P27" s="42" t="inlineStr"/>
+    </row>
+    <row r="28" ht="132" customHeight="1" s="14">
       <c r="A28" s="51" t="n">
         <v>46279</v>
       </c>
@@ -9770,43 +10066,54 @@
       <c r="F28" s="45" t="n">
         <v>225</v>
       </c>
-      <c r="G28" s="45" t="inlineStr">
+      <c r="G28" s="46" t="inlineStr">
+        <is>
+          <t>Five things Botox cannot do, so you do not pay for the wrong treatment.
+It will not lift heavy skin. That is a laxity issue and needs energy based treatment or surgery. It will not replace lost volume, which is what filler is for. It will not undo sun damage or fix pigment and texture, which is a skin health question. It will not shrink pores. And it will not remove a line that is fully etched at rest, though it will soften it and stop it deepening.
+What it does do, well, is relax the muscle making a movement line so the skin above it stops folding.
+If your concern is on this list, say so at your consultation and we will talk about what actually addresses it, whether that is filler, a skin plan, or nothing at all. Full list on Instagram.</t>
+        </is>
+      </c>
+      <c r="H28" s="45" t="n">
+        <v>750</v>
+      </c>
+      <c r="I28" s="45" t="inlineStr">
         <is>
           <t>Learn more</t>
         </is>
       </c>
-      <c r="H28" s="47" t="inlineStr">
+      <c r="J28" s="47" t="inlineStr">
         <is>
           <t>@luxury_beauty_aestheticz</t>
         </is>
       </c>
-      <c r="I28" s="45" t="inlineStr">
+      <c r="K28" s="45" t="inlineStr">
         <is>
           <t>2026-09-14-5-things-botox-cannot-do.jpg</t>
         </is>
       </c>
-      <c r="J28" s="47" t="inlineStr">
+      <c r="L28" s="47" t="inlineStr">
         <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="K28" s="45">
+      <c r="M28" s="45">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-14-5-things-botox-cannot-do.jpg")</f>
         <v/>
       </c>
-      <c r="L28" s="47" t="inlineStr">
+      <c r="N28" s="47" t="inlineStr">
         <is>
           <t>engin akyurt / Unsplash</t>
         </is>
       </c>
-      <c r="M28" s="45" t="inlineStr">
+      <c r="O28" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="N28" s="46" t="inlineStr"/>
-    </row>
-    <row r="29" ht="58" customHeight="1" s="14">
+      <c r="P28" s="46" t="inlineStr"/>
+    </row>
+    <row r="29" ht="132" customHeight="1" s="14">
       <c r="A29" s="51" t="n">
         <v>46280</v>
       </c>
@@ -9833,43 +10140,54 @@
       <c r="F29" s="45" t="n">
         <v>216</v>
       </c>
-      <c r="G29" s="45" t="inlineStr">
+      <c r="G29" s="46" t="inlineStr">
+        <is>
+          <t>If a line is still there when your face is completely still, a neuromodulator is not the answer for it.
+That is the simplest test I can give you. Relax everything, look straight ahead, and see what remains. A line that only shows when you move is a muscle problem, which is what Botox treats. A line sitting there at rest is either volume loss or skin quality, and both need a different plan.
+Plenty of faces have both at once. The nasolabial folds are the usual example, where people book a neuromodulator and are disappointed because the fold was never about movement.
+Honest expectations save money, and they are the reason people keep coming back to this Oakville studio. Send a relaxed photo and a moving one if you want a straight answer before booking. More on Instagram.</t>
+        </is>
+      </c>
+      <c r="H29" s="45" t="n">
+        <v>781</v>
+      </c>
+      <c r="I29" s="45" t="inlineStr">
         <is>
           <t>Learn more</t>
         </is>
       </c>
-      <c r="H29" s="47" t="inlineStr">
+      <c r="J29" s="47" t="inlineStr">
         <is>
           <t>@luxury_beauty_aestheticz</t>
         </is>
       </c>
-      <c r="I29" s="45" t="inlineStr">
+      <c r="K29" s="45" t="inlineStr">
         <is>
           <t>2026-09-15-what-it-cannot-fix.jpg</t>
         </is>
       </c>
-      <c r="J29" s="47" t="inlineStr">
+      <c r="L29" s="47" t="inlineStr">
         <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="K29" s="45">
+      <c r="M29" s="45">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-15-what-it-cannot-fix.jpg")</f>
         <v/>
       </c>
-      <c r="L29" s="47" t="inlineStr">
+      <c r="N29" s="47" t="inlineStr">
         <is>
           <t>engin akyurt / Unsplash</t>
         </is>
       </c>
-      <c r="M29" s="45" t="inlineStr">
+      <c r="O29" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="N29" s="46" t="inlineStr"/>
-    </row>
-    <row r="30" ht="58" customHeight="1" s="14">
+      <c r="P29" s="46" t="inlineStr"/>
+    </row>
+    <row r="30" ht="132" customHeight="1" s="14">
       <c r="A30" s="50" t="n">
         <v>46281</v>
       </c>
@@ -9896,43 +10214,54 @@
       <c r="F30" s="41" t="n">
         <v>237</v>
       </c>
-      <c r="G30" s="41" t="inlineStr">
+      <c r="G30" s="42" t="inlineStr">
+        <is>
+          <t>Booking is a message, not a phone tree. Send a DM on Instagram and it is answered by Cleo, usually the same day.
+Tell me what is bothering you, in whatever words you have. You do not need to know the treatment name or the area. Plenty of people open with a photo and a sentence about hating one particular line, and that is enough to start.
+I will tell you honestly whether I can help, roughly what it would take, and what it costs. If the answer is that you do not need anything yet, you will get that too.
+We are at 3060 Preserve Dr in Oakville, with free parking at the door, seeing Botox and filler clients from Burlington, Milton and Mississauga. One appointment in the room at a time.</t>
+        </is>
+      </c>
+      <c r="H30" s="41" t="n">
+        <v>693</v>
+      </c>
+      <c r="I30" s="41" t="inlineStr">
         <is>
           <t>Learn more</t>
         </is>
       </c>
-      <c r="H30" s="43" t="inlineStr">
+      <c r="J30" s="43" t="inlineStr">
         <is>
           <t>@luxury_beauty_aestheticz</t>
         </is>
       </c>
-      <c r="I30" s="41" t="inlineStr">
+      <c r="K30" s="41" t="inlineStr">
         <is>
           <t>2026-09-16-how-to-book.jpg</t>
         </is>
       </c>
-      <c r="J30" s="43" t="inlineStr">
+      <c r="L30" s="43" t="inlineStr">
         <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="K30" s="41">
+      <c r="M30" s="41">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-16-how-to-book.jpg")</f>
         <v/>
       </c>
-      <c r="L30" s="43" t="inlineStr">
+      <c r="N30" s="43" t="inlineStr">
         <is>
           <t>Bee Naturalles / Unsplash</t>
         </is>
       </c>
-      <c r="M30" s="41" t="inlineStr">
+      <c r="O30" s="41" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="N30" s="42" t="inlineStr"/>
-    </row>
-    <row r="31" ht="58" customHeight="1" s="14">
+      <c r="P30" s="42" t="inlineStr"/>
+    </row>
+    <row r="31" ht="132" customHeight="1" s="14">
       <c r="A31" s="51" t="n">
         <v>46282</v>
       </c>
@@ -9959,43 +10288,54 @@
       <c r="F31" s="45" t="n">
         <v>199</v>
       </c>
-      <c r="G31" s="45" t="inlineStr">
+      <c r="G31" s="46" t="inlineStr">
+        <is>
+          <t>You will not look done. You will look like you slept properly for a week.
+That is the whole standard, and it drives every dosing decision here. The dose is built around your face rather than a template, which usually means fewer units than a chart would suggest and a follow up at two weeks to fine tune rather than one heavy session.
+It also means leaving movement alone where movement is doing useful work. A completely still forehead is easy to achieve and almost always reads as work. Softer lines with full expression takes more judgement and is what people actually want when they describe looking refreshed.
+Still you, just less tired. That is what good Botox looks like in Oakville, and you can see it on Instagram.</t>
+        </is>
+      </c>
+      <c r="H31" s="45" t="n">
+        <v>726</v>
+      </c>
+      <c r="I31" s="45" t="inlineStr">
         <is>
           <t>Learn more</t>
         </is>
       </c>
-      <c r="H31" s="47" t="inlineStr">
+      <c r="J31" s="47" t="inlineStr">
         <is>
           <t>@luxury_beauty_aestheticz</t>
         </is>
       </c>
-      <c r="I31" s="45" t="inlineStr">
+      <c r="K31" s="45" t="inlineStr">
         <is>
           <t>2026-09-17-still-you-just-refreshed.jpg</t>
         </is>
       </c>
-      <c r="J31" s="47" t="inlineStr">
+      <c r="L31" s="47" t="inlineStr">
         <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="K31" s="45">
+      <c r="M31" s="45">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-17-still-you-just-refreshed.jpg")</f>
         <v/>
       </c>
-      <c r="L31" s="47" t="inlineStr">
+      <c r="N31" s="47" t="inlineStr">
         <is>
           <t>Zulfugar Karimov / Unsplash</t>
         </is>
       </c>
-      <c r="M31" s="45" t="inlineStr">
+      <c r="O31" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="N31" s="46" t="inlineStr"/>
-    </row>
-    <row r="32" ht="58" customHeight="1" s="14">
+      <c r="P31" s="46" t="inlineStr"/>
+    </row>
+    <row r="32" ht="132" customHeight="1" s="14">
       <c r="A32" s="51" t="n">
         <v>46283</v>
       </c>
@@ -10022,43 +10362,54 @@
       <c r="F32" s="45" t="n">
         <v>178</v>
       </c>
-      <c r="G32" s="45" t="inlineStr">
+      <c r="G32" s="46" t="inlineStr">
+        <is>
+          <t>The frozen face is a dosing mistake, not what the treatment does.
+It happens when too much product goes into too many muscles at once, usually because someone treated a whole area by default rather than the specific muscle that was pulling. The result is a face that cannot express, which is the outcome everyone is afraid of and the reason plenty of people never book.
+Done properly you keep your expressions and lose the deep etched lines. You should still be able to frown, lift your brows and squint. The difference shows in photos, where you look like yourself rather than smoothed over.
+If frozen is what has put you off Botox, say that at your consultation. It changes how I dose. The classic fear, debunked on Instagram.</t>
+        </is>
+      </c>
+      <c r="H32" s="45" t="n">
+        <v>731</v>
+      </c>
+      <c r="I32" s="45" t="inlineStr">
         <is>
           <t>Learn more</t>
         </is>
       </c>
-      <c r="H32" s="47" t="inlineStr">
+      <c r="J32" s="47" t="inlineStr">
         <is>
           <t>@luxury_beauty_aestheticz</t>
         </is>
       </c>
-      <c r="I32" s="45" t="inlineStr">
+      <c r="K32" s="45" t="inlineStr">
         <is>
           <t>2026-09-18-frozen-face-myth.jpg</t>
         </is>
       </c>
-      <c r="J32" s="47" t="inlineStr">
+      <c r="L32" s="47" t="inlineStr">
         <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="K32" s="45">
+      <c r="M32" s="45">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-18-frozen-face-myth.jpg")</f>
         <v/>
       </c>
-      <c r="L32" s="47" t="inlineStr">
+      <c r="N32" s="47" t="inlineStr">
         <is>
           <t>Neda Vidakovic / Unsplash</t>
         </is>
       </c>
-      <c r="M32" s="45" t="inlineStr">
+      <c r="O32" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="N32" s="46" t="inlineStr"/>
-    </row>
-    <row r="33" ht="58" customHeight="1" s="14">
+      <c r="P32" s="46" t="inlineStr"/>
+    </row>
+    <row r="33" ht="132" customHeight="1" s="14">
       <c r="A33" s="51" t="n">
         <v>46284</v>
       </c>
@@ -10085,43 +10436,54 @@
       <c r="F33" s="45" t="n">
         <v>183</v>
       </c>
-      <c r="G33" s="45" t="inlineStr">
+      <c r="G33" s="46" t="inlineStr">
+        <is>
+          <t>Nobody guessed. That was the point.
+The compliments worth aiming for are the vague ones. Did you change your skincare. Have you been away. You look well rested. Nobody in that list is identifying a treatment, which means the work sat inside the range where it reads as you on a good week.
+Getting there is unglamorous. It is conservative dosing, a two week follow up rather than one heavy session, and being willing to leave a small asymmetry that is just how your face is built.
+The clients who come to this Oakville studio from Burlington, Milton and Mississauga mostly arrive on referral from someone whose Botox nobody could place. That is the referral I want. Client words on Instagram.</t>
+        </is>
+      </c>
+      <c r="H33" s="45" t="n">
+        <v>694</v>
+      </c>
+      <c r="I33" s="45" t="inlineStr">
         <is>
           <t>Learn more</t>
         </is>
       </c>
-      <c r="H33" s="47" t="inlineStr">
+      <c r="J33" s="47" t="inlineStr">
         <is>
           <t>@luxury_beauty_aestheticz</t>
         </is>
       </c>
-      <c r="I33" s="45" t="inlineStr">
+      <c r="K33" s="45" t="inlineStr">
         <is>
           <t>2026-09-19-nobody-guessed.jpg</t>
         </is>
       </c>
-      <c r="J33" s="47" t="inlineStr">
+      <c r="L33" s="47" t="inlineStr">
         <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="K33" s="45">
+      <c r="M33" s="45">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-19-nobody-guessed.jpg")</f>
         <v/>
       </c>
-      <c r="L33" s="47" t="inlineStr">
+      <c r="N33" s="47" t="inlineStr">
         <is>
           <t>Vitaliy Shevchenko / Unsplash</t>
         </is>
       </c>
-      <c r="M33" s="45" t="inlineStr">
+      <c r="O33" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="N33" s="46" t="inlineStr"/>
-    </row>
-    <row r="34" ht="58" customHeight="1" s="14">
+      <c r="P33" s="46" t="inlineStr"/>
+    </row>
+    <row r="34" ht="132" customHeight="1" s="14">
       <c r="A34" s="50" t="n">
         <v>46285</v>
       </c>
@@ -10148,43 +10510,54 @@
       <c r="F34" s="41" t="n">
         <v>204</v>
       </c>
-      <c r="G34" s="41" t="inlineStr">
+      <c r="G34" s="42" t="inlineStr">
+        <is>
+          <t>Based at 3060 Preserve Dr in Oakville, seeing clients from Burlington, Milton and Mississauga.
+It is a private studio rather than a clinic floor, with free parking at the door and one appointment in the room at a time. Most people are in and out inside an hour for a first visit, closer to twenty minutes once they are established.
+People travel here for a specific reason and it is usually not location. It is that the same nurse practitioner injects every appointment, the dose is explained before anything is opened, and the answer is sometimes no.
+If you are anywhere in Halton or west Mississauga and weighing up where to go for Botox or filler, message me on Instagram and ask whatever you need to before booking.</t>
+        </is>
+      </c>
+      <c r="H34" s="41" t="n">
+        <v>722</v>
+      </c>
+      <c r="I34" s="41" t="inlineStr">
         <is>
           <t>Learn more</t>
         </is>
       </c>
-      <c r="H34" s="43" t="inlineStr">
+      <c r="J34" s="43" t="inlineStr">
         <is>
           <t>@luxury_beauty_aestheticz</t>
         </is>
       </c>
-      <c r="I34" s="41" t="inlineStr">
+      <c r="K34" s="41" t="inlineStr">
         <is>
           <t>2026-09-20-service-area.jpg</t>
         </is>
       </c>
-      <c r="J34" s="43" t="inlineStr">
+      <c r="L34" s="43" t="inlineStr">
         <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="K34" s="41">
+      <c r="M34" s="41">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-20-service-area.jpg")</f>
         <v/>
       </c>
-      <c r="L34" s="43" t="inlineStr">
+      <c r="N34" s="43" t="inlineStr">
         <is>
           <t>Elist Nguyen / Unsplash</t>
         </is>
       </c>
-      <c r="M34" s="41" t="inlineStr">
+      <c r="O34" s="41" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="N34" s="42" t="inlineStr"/>
-    </row>
-    <row r="35" ht="58" customHeight="1" s="14">
+      <c r="P34" s="42" t="inlineStr"/>
+    </row>
+    <row r="35" ht="132" customHeight="1" s="14">
       <c r="A35" s="51" t="n">
         <v>46286</v>
       </c>
@@ -10211,43 +10584,54 @@
       <c r="F35" s="45" t="n">
         <v>234</v>
       </c>
-      <c r="G35" s="45" t="inlineStr">
+      <c r="G35" s="46" t="inlineStr">
+        <is>
+          <t>Botox or filler? You might be asking for the wrong one, and it is the most expensive mistake in this business.
+Lines made by movement need a neuromodulator, which relaxes the muscle doing the folding. Hollowness, flatness and lost volume need filler, which replaces structure that is no longer there. They solve different problems and neither substitutes for the other.
+The confusion is understandable because the complaint sounds the same. Someone points at their lower face and says it looks tired. That can be volume, skin quality, movement, or all three at once.
+This is exactly what a consultation is for. Bring the concern, not the treatment name, and we will work out whether it is Botox or filler you actually need. Explained on Instagram, or book in Oakville.</t>
+        </is>
+      </c>
+      <c r="H35" s="45" t="n">
+        <v>771</v>
+      </c>
+      <c r="I35" s="45" t="inlineStr">
         <is>
           <t>Learn more</t>
         </is>
       </c>
-      <c r="H35" s="47" t="inlineStr">
+      <c r="J35" s="47" t="inlineStr">
         <is>
           <t>@luxury_beauty_aestheticz</t>
         </is>
       </c>
-      <c r="I35" s="45" t="inlineStr">
+      <c r="K35" s="45" t="inlineStr">
         <is>
           <t>2026-09-21-botox-or-filler.jpg</t>
         </is>
       </c>
-      <c r="J35" s="47" t="inlineStr">
+      <c r="L35" s="47" t="inlineStr">
         <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="K35" s="45">
+      <c r="M35" s="45">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-21-botox-or-filler.jpg")</f>
         <v/>
       </c>
-      <c r="L35" s="47" t="inlineStr">
+      <c r="N35" s="47" t="inlineStr">
         <is>
           <t>Alef Morais / Unsplash</t>
         </is>
       </c>
-      <c r="M35" s="45" t="inlineStr">
+      <c r="O35" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="N35" s="46" t="inlineStr"/>
-    </row>
-    <row r="36" ht="58" customHeight="1" s="14">
+      <c r="P35" s="46" t="inlineStr"/>
+    </row>
+    <row r="36" ht="132" customHeight="1" s="14">
       <c r="A36" s="51" t="n">
         <v>46287</v>
       </c>
@@ -10274,43 +10658,54 @@
       <c r="F36" s="45" t="n">
         <v>185</v>
       </c>
-      <c r="G36" s="45" t="inlineStr">
+      <c r="G36" s="46" t="inlineStr">
+        <is>
+          <t>Here is the test you can do at home. Gently pull the skin taut beside the line.
+If it disappears, it is a movement line and a neuromodulator is the right tool. If it stays put, you are looking at volume loss or skin quality, and filler or a skin plan is the conversation instead.
+Do it in decent light with your face completely relaxed. The result surprises people fairly often, usually because the line they have been trying to treat for years was never a muscle problem.
+This is not a substitute for an assessment, and plenty of faces show both at once. But it will get you asking a much better question when you book Botox or filler in Oakville. More on Instagram.</t>
+        </is>
+      </c>
+      <c r="H36" s="45" t="n">
+        <v>670</v>
+      </c>
+      <c r="I36" s="45" t="inlineStr">
         <is>
           <t>Learn more</t>
         </is>
       </c>
-      <c r="H36" s="47" t="inlineStr">
+      <c r="J36" s="47" t="inlineStr">
         <is>
           <t>@luxury_beauty_aestheticz</t>
         </is>
       </c>
-      <c r="I36" s="45" t="inlineStr">
+      <c r="K36" s="45" t="inlineStr">
         <is>
           <t>2026-09-22-lines-vs-volume.jpg</t>
         </is>
       </c>
-      <c r="J36" s="47" t="inlineStr">
+      <c r="L36" s="47" t="inlineStr">
         <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="K36" s="45">
+      <c r="M36" s="45">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-22-lines-vs-volume.jpg")</f>
         <v/>
       </c>
-      <c r="L36" s="47" t="inlineStr">
+      <c r="N36" s="47" t="inlineStr">
         <is>
           <t>Rosa Rafael / Unsplash</t>
         </is>
       </c>
-      <c r="M36" s="45" t="inlineStr">
+      <c r="O36" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="N36" s="46" t="inlineStr"/>
-    </row>
-    <row r="37" ht="58" customHeight="1" s="14">
+      <c r="P36" s="46" t="inlineStr"/>
+    </row>
+    <row r="37" ht="132" customHeight="1" s="14">
       <c r="A37" s="50" t="n">
         <v>46288</v>
       </c>
@@ -10337,43 +10732,54 @@
       <c r="F37" s="41" t="n">
         <v>238</v>
       </c>
-      <c r="G37" s="41" t="inlineStr">
+      <c r="G37" s="42" t="inlineStr">
+        <is>
+          <t>Five questions worth asking any clinic, including this one.
+Who is injecting me, and will it be the same person next time. What are your credentials, and where can I verify them. Which product are you using and is it Health Canada approved. How many units, and why that number for my face. What happens if I am not happy at two weeks.
+A good clinic answers all five without hesitating or getting defensive. Vague answers on any of them are worth walking out over, particularly the first two.
+Ask them here too. Any injector worth booking, in Oakville or anywhere else, will answer all five about your Botox without hesitating. Answers on Instagram.</t>
+        </is>
+      </c>
+      <c r="H37" s="41" t="n">
+        <v>651</v>
+      </c>
+      <c r="I37" s="41" t="inlineStr">
         <is>
           <t>Learn more</t>
         </is>
       </c>
-      <c r="H37" s="43" t="inlineStr">
+      <c r="J37" s="43" t="inlineStr">
         <is>
           <t>@luxury_beauty_aestheticz</t>
         </is>
       </c>
-      <c r="I37" s="41" t="inlineStr">
+      <c r="K37" s="41" t="inlineStr">
         <is>
           <t>2026-09-23-what-to-ask.jpg</t>
         </is>
       </c>
-      <c r="J37" s="43" t="inlineStr">
+      <c r="L37" s="43" t="inlineStr">
         <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="K37" s="41">
+      <c r="M37" s="41">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-23-what-to-ask.jpg")</f>
         <v/>
       </c>
-      <c r="L37" s="43" t="inlineStr">
+      <c r="N37" s="43" t="inlineStr">
         <is>
           <t>Soheil Kmp / Unsplash</t>
         </is>
       </c>
-      <c r="M37" s="41" t="inlineStr">
+      <c r="O37" s="41" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="N37" s="42" t="inlineStr"/>
-    </row>
-    <row r="38" ht="58" customHeight="1" s="14">
+      <c r="P37" s="42" t="inlineStr"/>
+    </row>
+    <row r="38" ht="132" customHeight="1" s="14">
       <c r="A38" s="51" t="n">
         <v>46289</v>
       </c>
@@ -10400,43 +10806,54 @@
       <c r="F38" s="45" t="n">
         <v>192</v>
       </c>
-      <c r="G38" s="45" t="inlineStr">
+      <c r="G38" s="46" t="inlineStr">
+        <is>
+          <t>You asked, so here are the honest answers, including the ones clinics usually dodge.
+The questions that land in my DMs most weeks: what does it actually cost, will I need it forever, what if I stop, does it get worse when it wears off, and can you tell when someone has had it done.
+Short version on the two that worry people most. Nothing gets worse when you stop. The muscle simply returns to what it was doing before, and any line that had softened goes back to where it would have been. And no, you cannot tell when it is dosed properly, which is the entire point.
+No marketing gloss on any of them. Read the full set on Instagram, and send me the Botox question nobody has answered for you properly.</t>
+        </is>
+      </c>
+      <c r="H38" s="45" t="n">
+        <v>707</v>
+      </c>
+      <c r="I38" s="45" t="inlineStr">
         <is>
           <t>Learn more</t>
         </is>
       </c>
-      <c r="H38" s="47" t="inlineStr">
+      <c r="J38" s="47" t="inlineStr">
         <is>
           <t>@luxury_beauty_aestheticz</t>
         </is>
       </c>
-      <c r="I38" s="45" t="inlineStr">
+      <c r="K38" s="45" t="inlineStr">
         <is>
           <t>2026-09-24-ask-np-cleo.jpg</t>
         </is>
       </c>
-      <c r="J38" s="47" t="inlineStr">
+      <c r="L38" s="47" t="inlineStr">
         <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="K38" s="45">
+      <c r="M38" s="45">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-24-ask-np-cleo.jpg")</f>
         <v/>
       </c>
-      <c r="L38" s="47" t="inlineStr">
+      <c r="N38" s="47" t="inlineStr">
         <is>
           <t>Look Studio / Unsplash</t>
         </is>
       </c>
-      <c r="M38" s="45" t="inlineStr">
+      <c r="O38" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="N38" s="46" t="inlineStr"/>
-    </row>
-    <row r="39" ht="58" customHeight="1" s="14">
+      <c r="P38" s="46" t="inlineStr"/>
+    </row>
+    <row r="39" ht="132" customHeight="1" s="14">
       <c r="A39" s="51" t="n">
         <v>46290</v>
       </c>
@@ -10463,43 +10880,54 @@
       <c r="F39" s="45" t="n">
         <v>179</v>
       </c>
-      <c r="G39" s="45" t="inlineStr">
+      <c r="G39" s="46" t="inlineStr">
+        <is>
+          <t>The question people ask quietly, in private, almost every week.
+It is usually some version of: am I too young for this, or am I too late. Both come with a bit of embarrassment attached, which is why they arrive as a DM at eleven at night rather than out loud in a room.
+The answer to both is that age is not the measure. What matters is whether a line stays behind when your face is fully relaxed. That is a question about your skin and your muscle, not your birthday, and it is why two people the same age often need completely different plans.
+Nothing you ask here is silly and nothing gets repeated. Whether it is Botox, filler or neither, your questions are always welcome on Instagram.</t>
+        </is>
+      </c>
+      <c r="H39" s="45" t="n">
+        <v>693</v>
+      </c>
+      <c r="I39" s="45" t="inlineStr">
         <is>
           <t>Learn more</t>
         </is>
       </c>
-      <c r="H39" s="47" t="inlineStr">
+      <c r="J39" s="47" t="inlineStr">
         <is>
           <t>@luxury_beauty_aestheticz</t>
         </is>
       </c>
-      <c r="I39" s="45" t="inlineStr">
+      <c r="K39" s="45" t="inlineStr">
         <is>
           <t>2026-09-25-your-dms-answered.jpg</t>
         </is>
       </c>
-      <c r="J39" s="47" t="inlineStr">
+      <c r="L39" s="47" t="inlineStr">
         <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="K39" s="45">
+      <c r="M39" s="45">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-25-your-dms-answered.jpg")</f>
         <v/>
       </c>
-      <c r="L39" s="47" t="inlineStr">
+      <c r="N39" s="47" t="inlineStr">
         <is>
           <t>Masum Rahimi / Unsplash</t>
         </is>
       </c>
-      <c r="M39" s="45" t="inlineStr">
+      <c r="O39" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="N39" s="46" t="inlineStr"/>
-    </row>
-    <row r="40" ht="58" customHeight="1" s="14">
+      <c r="P39" s="46" t="inlineStr"/>
+    </row>
+    <row r="40" ht="132" customHeight="1" s="14">
       <c r="A40" s="51" t="n">
         <v>46291</v>
       </c>
@@ -10526,43 +10954,54 @@
       <c r="F40" s="45" t="n">
         <v>194</v>
       </c>
-      <c r="G40" s="45" t="inlineStr">
+      <c r="G40" s="46" t="inlineStr">
+        <is>
+          <t>You pick what I cover next. The topic with the most votes becomes the next post.
+On the list so far: what treatments actually cost and why, how to tell a good injector from a confident one, what happens to your face if you stop, and a full breakdown of what filler can and cannot fix.
+I would rather answer the thing people are actually wondering about than publish whatever is trending. The most useful posts here have all come from a question someone sent privately and assumed was too basic to ask.
+Vote on Instagram, or send a topic that is not on the list. If enough people in Oakville are wondering the same thing about Botox or filler, it gets made.</t>
+        </is>
+      </c>
+      <c r="H40" s="45" t="n">
+        <v>659</v>
+      </c>
+      <c r="I40" s="45" t="inlineStr">
         <is>
           <t>Learn more</t>
         </is>
       </c>
-      <c r="H40" s="47" t="inlineStr">
+      <c r="J40" s="47" t="inlineStr">
         <is>
           <t>@luxury_beauty_aestheticz</t>
         </is>
       </c>
-      <c r="I40" s="45" t="inlineStr">
+      <c r="K40" s="45" t="inlineStr">
         <is>
           <t>2026-09-26-what-next.jpg</t>
         </is>
       </c>
-      <c r="J40" s="47" t="inlineStr">
+      <c r="L40" s="47" t="inlineStr">
         <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="K40" s="45">
+      <c r="M40" s="45">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-26-what-next.jpg")</f>
         <v/>
       </c>
-      <c r="L40" s="47" t="inlineStr">
+      <c r="N40" s="47" t="inlineStr">
         <is>
           <t>Calugar Ana Maria / Unsplash</t>
         </is>
       </c>
-      <c r="M40" s="45" t="inlineStr">
+      <c r="O40" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="N40" s="46" t="inlineStr"/>
-    </row>
-    <row r="41" ht="58" customHeight="1" s="14">
+      <c r="P40" s="46" t="inlineStr"/>
+    </row>
+    <row r="41" ht="132" customHeight="1" s="14">
       <c r="A41" s="50" t="n">
         <v>46292</v>
       </c>
@@ -10589,43 +11028,54 @@
       <c r="F41" s="41" t="n">
         <v>233</v>
       </c>
-      <c r="G41" s="41" t="inlineStr">
+      <c r="G41" s="42" t="inlineStr">
+        <is>
+          <t>Your two week follow up is part of the treatment, not an extra.
+A neuromodulator takes about fourteen days to fully settle. Judging the result before that is how people end up chasing a dose, because at day five it looks uneven and at day fourteen it usually does not. So we look properly at two weeks, when what you see is what you have.
+If something needs adjusting, a small top up in one spot, a touch more on the side that pulls harder, that happens at the follow up and there is no charge for it.
+This is also why I dose conservatively the first time. It is easy to add a little at two weeks. There is nothing to be done about too much except wait it out. Book at our Oakville studio, or ask on Instagram.</t>
+        </is>
+      </c>
+      <c r="H41" s="41" t="n">
+        <v>713</v>
+      </c>
+      <c r="I41" s="41" t="inlineStr">
         <is>
           <t>Learn more</t>
         </is>
       </c>
-      <c r="H41" s="43" t="inlineStr">
+      <c r="J41" s="43" t="inlineStr">
         <is>
           <t>@luxury_beauty_aestheticz</t>
         </is>
       </c>
-      <c r="I41" s="41" t="inlineStr">
+      <c r="K41" s="41" t="inlineStr">
         <is>
           <t>2026-09-27-two-week-review.jpg</t>
         </is>
       </c>
-      <c r="J41" s="43" t="inlineStr">
+      <c r="L41" s="43" t="inlineStr">
         <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="K41" s="41">
+      <c r="M41" s="41">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-27-two-week-review.jpg")</f>
         <v/>
       </c>
-      <c r="L41" s="43" t="inlineStr">
+      <c r="N41" s="43" t="inlineStr">
         <is>
           <t>Ionela Mat / Unsplash</t>
         </is>
       </c>
-      <c r="M41" s="41" t="inlineStr">
+      <c r="O41" s="41" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="N41" s="42" t="inlineStr"/>
-    </row>
-    <row r="42" ht="58" customHeight="1" s="14">
+      <c r="P41" s="42" t="inlineStr"/>
+    </row>
+    <row r="42" ht="132" customHeight="1" s="14">
       <c r="A42" s="51" t="n">
         <v>46293</v>
       </c>
@@ -10652,43 +11102,54 @@
       <c r="F42" s="45" t="n">
         <v>209</v>
       </c>
-      <c r="G42" s="45" t="inlineStr">
+      <c r="G42" s="46" t="inlineStr">
+        <is>
+          <t>Three to four months for most people, and here are the honest reasons it varies.
+Metabolism plays a part, and people who train hard often find it wears off sooner. Dose matters, since a light preventative dose fades before a fuller corrective one. Muscle strength matters, because a strong frown works through product faster than a light one. And history matters, as people who have treated consistently for years often stretch further between appointments.
+What is not true is that it stops working. If yours seems to be fading faster than it used to, the usual answer is that the dose is no longer right rather than any resistance to the product.
+What is not true is that it stops working. If your Botox seems to be fading faster than it used to, the usual answer is that the dose is no longer right rather than any resistance to the product. Month by month timeline on Instagram.</t>
+        </is>
+      </c>
+      <c r="H42" s="45" t="n">
+        <v>885</v>
+      </c>
+      <c r="I42" s="45" t="inlineStr">
         <is>
           <t>Learn more</t>
         </is>
       </c>
-      <c r="H42" s="47" t="inlineStr">
+      <c r="J42" s="47" t="inlineStr">
         <is>
           <t>@luxury_beauty_aestheticz</t>
         </is>
       </c>
-      <c r="I42" s="45" t="inlineStr">
+      <c r="K42" s="45" t="inlineStr">
         <is>
           <t>2026-09-28-how-long-does-it-last.jpg</t>
         </is>
       </c>
-      <c r="J42" s="47" t="inlineStr">
+      <c r="L42" s="47" t="inlineStr">
         <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="K42" s="45">
+      <c r="M42" s="45">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-28-how-long-does-it-last.jpg")</f>
         <v/>
       </c>
-      <c r="L42" s="47" t="inlineStr">
+      <c r="N42" s="47" t="inlineStr">
         <is>
           <t>ONNE Beauty / Unsplash</t>
         </is>
       </c>
-      <c r="M42" s="45" t="inlineStr">
+      <c r="O42" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="N42" s="46" t="inlineStr"/>
-    </row>
-    <row r="43" ht="58" customHeight="1" s="14">
+      <c r="P42" s="46" t="inlineStr"/>
+    </row>
+    <row r="43" ht="132" customHeight="1" s="14">
       <c r="A43" s="51" t="n">
         <v>46294</v>
       </c>
@@ -10715,43 +11176,54 @@
       <c r="F43" s="45" t="n">
         <v>219</v>
       </c>
-      <c r="G43" s="45" t="inlineStr">
+      <c r="G43" s="46" t="inlineStr">
+        <is>
+          <t>Week by week, what to expect after treatment.
+Day three is when most people first notice movement easing. It is gradual and it is uneven at the start, which is normal. Two weeks is when it has fully settled, and the only fair point to judge the result or adjust it. Month one to two is the plateau, where it looks its best and you stop thinking about it.
+Month three is when movement starts creeping back, usually in the strongest muscle first. By month four most people are due, though plenty stretch further, particularly after a few consistent rounds.
+Knowing the curve stops the day five panic, which is far and away the most common message I get after Botox. Save the timeline from Instagram, or book a follow up in Oakville.</t>
+        </is>
+      </c>
+      <c r="H43" s="45" t="n">
+        <v>733</v>
+      </c>
+      <c r="I43" s="45" t="inlineStr">
         <is>
           <t>Learn more</t>
         </is>
       </c>
-      <c r="H43" s="47" t="inlineStr">
+      <c r="J43" s="47" t="inlineStr">
         <is>
           <t>@luxury_beauty_aestheticz</t>
         </is>
       </c>
-      <c r="I43" s="45" t="inlineStr">
+      <c r="K43" s="45" t="inlineStr">
         <is>
           <t>2026-09-29-three-month-timeline.jpg</t>
         </is>
       </c>
-      <c r="J43" s="47" t="inlineStr">
+      <c r="L43" s="47" t="inlineStr">
         <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="K43" s="45">
+      <c r="M43" s="45">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-29-three-month-timeline.jpg")</f>
         <v/>
       </c>
-      <c r="L43" s="47" t="inlineStr">
+      <c r="N43" s="47" t="inlineStr">
         <is>
           <t>Catherine Grimes / Unsplash</t>
         </is>
       </c>
-      <c r="M43" s="45" t="inlineStr">
+      <c r="O43" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="N43" s="46" t="inlineStr"/>
-    </row>
-    <row r="44" ht="58" customHeight="1" s="14">
+      <c r="P43" s="46" t="inlineStr"/>
+    </row>
+    <row r="44" ht="132" customHeight="1" s="14">
       <c r="A44" s="50" t="n">
         <v>46295</v>
       </c>
@@ -10778,173 +11250,184 @@
       <c r="F44" s="41" t="n">
         <v>225</v>
       </c>
-      <c r="G44" s="41" t="inlineStr">
+      <c r="G44" s="42" t="inlineStr">
+        <is>
+          <t>October is a month about lips, and it starts next week.
+What is coming: what one syringe of filler actually does and how far it goes, the real difference between natural and overdone, aftercare that matters in the first 48 hours, and real results shared with client consent.
+Lip filler in Oakville attracts more bad information than almost anything else I treat. Most of it comes from people who saw one obvious result and assumed that is what the treatment does. The work worth showing is the kind nobody identifies.
+If lips are something you have thought about and talked yourself out of, this is the month to ask. Follow along on Instagram so you do not miss the start.</t>
+        </is>
+      </c>
+      <c r="H44" s="41" t="n">
+        <v>675</v>
+      </c>
+      <c r="I44" s="41" t="inlineStr">
         <is>
           <t>Learn more</t>
         </is>
       </c>
-      <c r="H44" s="43" t="inlineStr">
+      <c r="J44" s="43" t="inlineStr">
         <is>
           <t>@luxury_beauty_aestheticz</t>
         </is>
       </c>
-      <c r="I44" s="41" t="inlineStr">
+      <c r="K44" s="41" t="inlineStr">
         <is>
           <t>2026-09-30-october-preview.jpg</t>
         </is>
       </c>
-      <c r="J44" s="43" t="inlineStr">
+      <c r="L44" s="43" t="inlineStr">
         <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="K44" s="41">
+      <c r="M44" s="41">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-30-october-preview.jpg")</f>
         <v/>
       </c>
-      <c r="L44" s="43" t="inlineStr">
+      <c r="N44" s="43" t="inlineStr">
         <is>
           <t>Christin Hume / Unsplash</t>
         </is>
       </c>
-      <c r="M44" s="41" t="inlineStr">
+      <c r="O44" s="41" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="N44" s="42" t="inlineStr"/>
+      <c r="P44" s="42" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N4" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N5" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N7" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N8" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N9" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N10" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N11" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N12" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N13" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N14" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N17" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N20" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N21" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N22" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N24" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N25" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N28" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N29" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N30" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N31" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N32" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N33" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N34" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N35" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N36" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N37" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N38" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N39" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N40" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N41" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N42" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N43" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N44" r:id="rId129"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/strategy/ig-content-strategy.xlsx
+++ b/strategy/ig-content-strategy.xlsx
@@ -8014,7 +8014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P44"/>
+  <dimension ref="A1:Q44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="14" min="1" max="1"/>
@@ -8029,10 +8029,11 @@
     <col width="26" customWidth="1" style="14" min="10" max="10"/>
     <col width="32" customWidth="1" style="14" min="11" max="11"/>
     <col width="13" customWidth="1" style="14" min="12" max="12"/>
-    <col width="14" customWidth="1" style="14" min="13" max="13"/>
-    <col width="24" customWidth="1" style="14" min="14" max="14"/>
-    <col width="10" customWidth="1" style="14" min="15" max="15"/>
-    <col width="28" customWidth="1" style="14" min="16" max="16"/>
+    <col width="13" customWidth="1" style="14" min="13" max="13"/>
+    <col width="14" customWidth="1" style="14" min="14" max="14"/>
+    <col width="24" customWidth="1" style="14" min="15" max="15"/>
+    <col width="10" customWidth="1" style="14" min="16" max="16"/>
+    <col width="28" customWidth="1" style="14" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8093,25 +8094,30 @@
       </c>
       <c r="L1" s="39" t="inlineStr">
         <is>
+          <t>Open Folder</t>
+        </is>
+      </c>
+      <c r="M1" s="39" t="inlineStr">
+        <is>
           <t>Open Image</t>
         </is>
       </c>
-      <c r="M1" s="39" t="inlineStr">
+      <c r="N1" s="39" t="inlineStr">
         <is>
           <t>Preview</t>
         </is>
       </c>
-      <c r="N1" s="39" t="inlineStr">
+      <c r="O1" s="39" t="inlineStr">
         <is>
           <t>Photo Credit</t>
         </is>
       </c>
-      <c r="O1" s="39" t="inlineStr">
+      <c r="P1" s="39" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="P1" s="39" t="inlineStr">
+      <c r="Q1" s="39" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -8171,24 +8177,29 @@
       </c>
       <c r="L2" s="43" t="inlineStr">
         <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M2" s="43" t="inlineStr">
+        <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="M2" s="41">
+      <c r="N2" s="41">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-08-19-one-client-at-a-time.jpg")</f>
         <v/>
       </c>
-      <c r="N2" s="43" t="inlineStr">
+      <c r="O2" s="43" t="inlineStr">
         <is>
           <t>Wco Global / Unsplash</t>
         </is>
       </c>
-      <c r="O2" s="41" t="inlineStr">
+      <c r="P2" s="41" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="P2" s="42" t="inlineStr"/>
+      <c r="Q2" s="42" t="inlineStr"/>
     </row>
     <row r="3" ht="132" customHeight="1" s="14">
       <c r="A3" s="51" t="n">
@@ -8245,24 +8256,29 @@
       </c>
       <c r="L3" s="47" t="inlineStr">
         <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M3" s="47" t="inlineStr">
+        <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="M3" s="45">
+      <c r="N3" s="45">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-08-20-5-red-flags.jpg")</f>
         <v/>
       </c>
-      <c r="N3" s="47" t="inlineStr">
+      <c r="O3" s="47" t="inlineStr">
         <is>
           <t>Look Studio / Unsplash</t>
         </is>
       </c>
-      <c r="O3" s="45" t="inlineStr">
+      <c r="P3" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="P3" s="46" t="inlineStr"/>
+      <c r="Q3" s="46" t="inlineStr"/>
     </row>
     <row r="4" ht="132" customHeight="1" s="14">
       <c r="A4" s="51" t="n">
@@ -8318,24 +8334,29 @@
       </c>
       <c r="L4" s="47" t="inlineStr">
         <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M4" s="47" t="inlineStr">
+        <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="M4" s="45">
+      <c r="N4" s="45">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-08-21-before-the-needle.jpg")</f>
         <v/>
       </c>
-      <c r="N4" s="47" t="inlineStr">
+      <c r="O4" s="47" t="inlineStr">
         <is>
           <t>CRYSTALWEED cannabis / Unsplash</t>
         </is>
       </c>
-      <c r="O4" s="45" t="inlineStr">
+      <c r="P4" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="P4" s="46" t="inlineStr"/>
+      <c r="Q4" s="46" t="inlineStr"/>
     </row>
     <row r="5" ht="132" customHeight="1" s="14">
       <c r="A5" s="51" t="n">
@@ -8392,24 +8413,29 @@
       </c>
       <c r="L5" s="47" t="inlineStr">
         <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M5" s="47" t="inlineStr">
+        <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="M5" s="45">
+      <c r="N5" s="45">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-08-22-great-work-is-invisible.jpg")</f>
         <v/>
       </c>
-      <c r="N5" s="47" t="inlineStr">
+      <c r="O5" s="47" t="inlineStr">
         <is>
           <t>Alef Morais / Unsplash</t>
         </is>
       </c>
-      <c r="O5" s="45" t="inlineStr">
+      <c r="P5" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="P5" s="46" t="inlineStr"/>
+      <c r="Q5" s="46" t="inlineStr"/>
     </row>
     <row r="6" ht="132" customHeight="1" s="14">
       <c r="A6" s="50" t="n">
@@ -8466,24 +8492,29 @@
       </c>
       <c r="L6" s="43" t="inlineStr">
         <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M6" s="43" t="inlineStr">
+        <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="M6" s="41">
+      <c r="N6" s="41">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-08-23-how-long-does-it-take.jpg")</f>
         <v/>
       </c>
-      <c r="N6" s="43" t="inlineStr">
+      <c r="O6" s="43" t="inlineStr">
         <is>
           <t>Ionela Mat / Unsplash</t>
         </is>
       </c>
-      <c r="O6" s="41" t="inlineStr">
+      <c r="P6" s="41" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="P6" s="42" t="inlineStr"/>
+      <c r="Q6" s="42" t="inlineStr"/>
     </row>
     <row r="7" ht="132" customHeight="1" s="14">
       <c r="A7" s="51" t="n">
@@ -8540,24 +8571,29 @@
       </c>
       <c r="L7" s="47" t="inlineStr">
         <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M7" s="47" t="inlineStr">
+        <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="M7" s="45">
+      <c r="N7" s="45">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-08-24-what-actually-happens.jpg")</f>
         <v/>
       </c>
-      <c r="N7" s="47" t="inlineStr">
+      <c r="O7" s="47" t="inlineStr">
         <is>
           <t>karelys Ruiz / Unsplash</t>
         </is>
       </c>
-      <c r="O7" s="45" t="inlineStr">
+      <c r="P7" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="P7" s="46" t="inlineStr"/>
+      <c r="Q7" s="46" t="inlineStr"/>
     </row>
     <row r="8" ht="132" customHeight="1" s="14">
       <c r="A8" s="51" t="n">
@@ -8614,24 +8650,29 @@
       </c>
       <c r="L8" s="47" t="inlineStr">
         <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M8" s="47" t="inlineStr">
+        <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="M8" s="45">
+      <c r="N8" s="45">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-08-25-why-no-prices.jpg")</f>
         <v/>
       </c>
-      <c r="N8" s="47" t="inlineStr">
+      <c r="O8" s="47" t="inlineStr">
         <is>
           <t>Lina Verovaya / Unsplash</t>
         </is>
       </c>
-      <c r="O8" s="45" t="inlineStr">
+      <c r="P8" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="P8" s="46" t="inlineStr"/>
+      <c r="Q8" s="46" t="inlineStr"/>
     </row>
     <row r="9" ht="132" customHeight="1" s="14">
       <c r="A9" s="50" t="n">
@@ -8688,24 +8729,29 @@
       </c>
       <c r="L9" s="43" t="inlineStr">
         <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M9" s="43" t="inlineStr">
+        <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="M9" s="41">
+      <c r="N9" s="41">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-08-26-who-injects-you.jpg")</f>
         <v/>
       </c>
-      <c r="N9" s="43" t="inlineStr">
+      <c r="O9" s="43" t="inlineStr">
         <is>
           <t>Anuruddha Lokuhapuarachchi / Unsplash</t>
         </is>
       </c>
-      <c r="O9" s="41" t="inlineStr">
+      <c r="P9" s="41" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="P9" s="42" t="inlineStr"/>
+      <c r="Q9" s="42" t="inlineStr"/>
     </row>
     <row r="10" ht="132" customHeight="1" s="14">
       <c r="A10" s="51" t="n">
@@ -8762,24 +8808,29 @@
       </c>
       <c r="L10" s="47" t="inlineStr">
         <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M10" s="47" t="inlineStr">
+        <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="M10" s="45">
+      <c r="N10" s="45">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-08-27-meet-np-cleo.jpg")</f>
         <v/>
       </c>
-      <c r="N10" s="47" t="inlineStr">
+      <c r="O10" s="47" t="inlineStr">
         <is>
           <t>Look Studio / Unsplash</t>
         </is>
       </c>
-      <c r="O10" s="45" t="inlineStr">
+      <c r="P10" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="P10" s="46" t="inlineStr"/>
+      <c r="Q10" s="46" t="inlineStr"/>
     </row>
     <row r="11" ht="132" customHeight="1" s="14">
       <c r="A11" s="51" t="n">
@@ -8836,24 +8887,29 @@
       </c>
       <c r="L11" s="47" t="inlineStr">
         <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M11" s="47" t="inlineStr">
+        <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="M11" s="45">
+      <c r="N11" s="45">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-08-28-where-calm-meets-careful.jpg")</f>
         <v/>
       </c>
-      <c r="N11" s="47" t="inlineStr">
+      <c r="O11" s="47" t="inlineStr">
         <is>
           <t>Masum Rahimi / Unsplash</t>
         </is>
       </c>
-      <c r="O11" s="45" t="inlineStr">
+      <c r="P11" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="P11" s="46" t="inlineStr"/>
+      <c r="Q11" s="46" t="inlineStr"/>
     </row>
     <row r="12" ht="132" customHeight="1" s="14">
       <c r="A12" s="51" t="n">
@@ -8910,24 +8966,29 @@
       </c>
       <c r="L12" s="47" t="inlineStr">
         <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M12" s="47" t="inlineStr">
+        <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="M12" s="45">
+      <c r="N12" s="45">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-08-29-rested-or-frozen.jpg")</f>
         <v/>
       </c>
-      <c r="N12" s="47" t="inlineStr">
+      <c r="O12" s="47" t="inlineStr">
         <is>
           <t>engin akyurt / Unsplash</t>
         </is>
       </c>
-      <c r="O12" s="45" t="inlineStr">
+      <c r="P12" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="P12" s="46" t="inlineStr"/>
+      <c r="Q12" s="46" t="inlineStr"/>
     </row>
     <row r="13" ht="132" customHeight="1" s="14">
       <c r="A13" s="50" t="n">
@@ -8984,24 +9045,29 @@
       </c>
       <c r="L13" s="43" t="inlineStr">
         <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M13" s="43" t="inlineStr">
+        <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="M13" s="41">
+      <c r="N13" s="41">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-08-30-what-a-consult-includes.jpg")</f>
         <v/>
       </c>
-      <c r="N13" s="43" t="inlineStr">
+      <c r="O13" s="43" t="inlineStr">
         <is>
           <t>Calugar Ana Maria / Unsplash</t>
         </is>
       </c>
-      <c r="O13" s="41" t="inlineStr">
+      <c r="P13" s="41" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="P13" s="42" t="inlineStr"/>
+      <c r="Q13" s="42" t="inlineStr"/>
     </row>
     <row r="14" ht="132" customHeight="1" s="14">
       <c r="A14" s="51" t="n">
@@ -9058,24 +9124,29 @@
       </c>
       <c r="L14" s="47" t="inlineStr">
         <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M14" s="47" t="inlineStr">
+        <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="M14" s="45">
+      <c r="N14" s="45">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-08-31-when-to-start.jpg")</f>
         <v/>
       </c>
-      <c r="N14" s="47" t="inlineStr">
+      <c r="O14" s="47" t="inlineStr">
         <is>
           <t>Fleur Kaan / Unsplash</t>
         </is>
       </c>
-      <c r="O14" s="45" t="inlineStr">
+      <c r="P14" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="P14" s="46" t="inlineStr"/>
+      <c r="Q14" s="46" t="inlineStr"/>
     </row>
     <row r="15" ht="132" customHeight="1" s="14">
       <c r="A15" s="51" t="n">
@@ -9132,24 +9203,29 @@
       </c>
       <c r="L15" s="47" t="inlineStr">
         <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M15" s="47" t="inlineStr">
+        <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="M15" s="45">
+      <c r="N15" s="45">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-01-spotlight-preventative.jpg")</f>
         <v/>
       </c>
-      <c r="N15" s="47" t="inlineStr">
+      <c r="O15" s="47" t="inlineStr">
         <is>
           <t>Fleur Kaan / Unsplash</t>
         </is>
       </c>
-      <c r="O15" s="45" t="inlineStr">
+      <c r="P15" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="P15" s="46" t="inlineStr"/>
+      <c r="Q15" s="46" t="inlineStr"/>
     </row>
     <row r="16" ht="132" customHeight="1" s="14">
       <c r="A16" s="50" t="n">
@@ -9206,24 +9282,29 @@
       </c>
       <c r="L16" s="43" t="inlineStr">
         <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M16" s="43" t="inlineStr">
+        <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="M16" s="41">
+      <c r="N16" s="41">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-02-is-it-safe.jpg")</f>
         <v/>
       </c>
-      <c r="N16" s="43" t="inlineStr">
+      <c r="O16" s="43" t="inlineStr">
         <is>
           <t>Atikah Akhtar / Unsplash</t>
         </is>
       </c>
-      <c r="O16" s="41" t="inlineStr">
+      <c r="P16" s="41" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="P16" s="42" t="inlineStr"/>
+      <c r="Q16" s="42" t="inlineStr"/>
     </row>
     <row r="17" ht="132" customHeight="1" s="14">
       <c r="A17" s="51" t="n">
@@ -9280,24 +9361,29 @@
       </c>
       <c r="L17" s="47" t="inlineStr">
         <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M17" s="47" t="inlineStr">
+        <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="M17" s="45">
+      <c r="N17" s="45">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-03-20-units.jpg")</f>
         <v/>
       </c>
-      <c r="N17" s="47" t="inlineStr">
+      <c r="O17" s="47" t="inlineStr">
         <is>
           <t>ONNE Beauty / Unsplash</t>
         </is>
       </c>
-      <c r="O17" s="45" t="inlineStr">
+      <c r="P17" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="P17" s="46" t="inlineStr"/>
+      <c r="Q17" s="46" t="inlineStr"/>
     </row>
     <row r="18" ht="132" customHeight="1" s="14">
       <c r="A18" s="51" t="n">
@@ -9354,24 +9440,29 @@
       </c>
       <c r="L18" s="47" t="inlineStr">
         <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M18" s="47" t="inlineStr">
+        <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="M18" s="45">
+      <c r="N18" s="45">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-04-meet-your-injector.jpg")</f>
         <v/>
       </c>
-      <c r="N18" s="47" t="inlineStr">
+      <c r="O18" s="47" t="inlineStr">
         <is>
           <t>Masum Rahimi / Unsplash</t>
         </is>
       </c>
-      <c r="O18" s="45" t="inlineStr">
+      <c r="P18" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="P18" s="46" t="inlineStr"/>
+      <c r="Q18" s="46" t="inlineStr"/>
     </row>
     <row r="19" ht="132" customHeight="1" s="14">
       <c r="A19" s="51" t="n">
@@ -9428,24 +9519,29 @@
       </c>
       <c r="L19" s="47" t="inlineStr">
         <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M19" s="47" t="inlineStr">
+        <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="M19" s="45">
+      <c r="N19" s="45">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-05-prevention-beats-erasing.jpg")</f>
         <v/>
       </c>
-      <c r="N19" s="47" t="inlineStr">
+      <c r="O19" s="47" t="inlineStr">
         <is>
           <t>Elist Nguyen / Unsplash</t>
         </is>
       </c>
-      <c r="O19" s="45" t="inlineStr">
+      <c r="P19" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="P19" s="46" t="inlineStr"/>
+      <c r="Q19" s="46" t="inlineStr"/>
     </row>
     <row r="20" ht="132" customHeight="1" s="14">
       <c r="A20" s="50" t="n">
@@ -9502,24 +9598,29 @@
       </c>
       <c r="L20" s="43" t="inlineStr">
         <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M20" s="43" t="inlineStr">
+        <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="M20" s="41">
+      <c r="N20" s="41">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-06-first-timer.jpg")</f>
         <v/>
       </c>
-      <c r="N20" s="43" t="inlineStr">
+      <c r="O20" s="43" t="inlineStr">
         <is>
           <t>engin akyurt / Unsplash</t>
         </is>
       </c>
-      <c r="O20" s="41" t="inlineStr">
+      <c r="P20" s="41" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="P20" s="42" t="inlineStr"/>
+      <c r="Q20" s="42" t="inlineStr"/>
     </row>
     <row r="21" ht="132" customHeight="1" s="14">
       <c r="A21" s="51" t="n">
@@ -9576,24 +9677,29 @@
       </c>
       <c r="L21" s="47" t="inlineStr">
         <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M21" s="47" t="inlineStr">
+        <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="M21" s="45">
+      <c r="N21" s="45">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-07-botox-vs-dysport.jpg")</f>
         <v/>
       </c>
-      <c r="N21" s="47" t="inlineStr">
+      <c r="O21" s="47" t="inlineStr">
         <is>
           <t>Catherine Grimes / Unsplash</t>
         </is>
       </c>
-      <c r="O21" s="45" t="inlineStr">
+      <c r="P21" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="P21" s="46" t="inlineStr"/>
+      <c r="Q21" s="46" t="inlineStr"/>
     </row>
     <row r="22" ht="132" customHeight="1" s="14">
       <c r="A22" s="51" t="n">
@@ -9650,24 +9756,29 @@
       </c>
       <c r="L22" s="47" t="inlineStr">
         <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M22" s="47" t="inlineStr">
+        <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="M22" s="45">
+      <c r="N22" s="45">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-08-at-a-glance.jpg")</f>
         <v/>
       </c>
-      <c r="N22" s="47" t="inlineStr">
+      <c r="O22" s="47" t="inlineStr">
         <is>
           <t>Gabrielle Henderson / Unsplash</t>
         </is>
       </c>
-      <c r="O22" s="45" t="inlineStr">
+      <c r="P22" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="P22" s="46" t="inlineStr"/>
+      <c r="Q22" s="46" t="inlineStr"/>
     </row>
     <row r="23" ht="132" customHeight="1" s="14">
       <c r="A23" s="50" t="n">
@@ -9724,24 +9835,29 @@
       </c>
       <c r="L23" s="43" t="inlineStr">
         <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M23" s="43" t="inlineStr">
+        <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="M23" s="41">
+      <c r="N23" s="41">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-09-aftercare-rules.jpg")</f>
         <v/>
       </c>
-      <c r="N23" s="43" t="inlineStr">
+      <c r="O23" s="43" t="inlineStr">
         <is>
           <t>Gabrielle Henderson / Unsplash</t>
         </is>
       </c>
-      <c r="O23" s="41" t="inlineStr">
+      <c r="P23" s="41" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="P23" s="42" t="inlineStr"/>
+      <c r="Q23" s="42" t="inlineStr"/>
     </row>
     <row r="24" ht="132" customHeight="1" s="14">
       <c r="A24" s="51" t="n">
@@ -9798,24 +9914,29 @@
       </c>
       <c r="L24" s="47" t="inlineStr">
         <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M24" s="47" t="inlineStr">
+        <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="M24" s="45">
+      <c r="N24" s="45">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-10-first-48-hours.jpg")</f>
         <v/>
       </c>
-      <c r="N24" s="47" t="inlineStr">
+      <c r="O24" s="47" t="inlineStr">
         <is>
           <t>ONNE Beauty / Unsplash</t>
         </is>
       </c>
-      <c r="O24" s="45" t="inlineStr">
+      <c r="P24" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="P24" s="46" t="inlineStr"/>
+      <c r="Q24" s="46" t="inlineStr"/>
     </row>
     <row r="25" ht="132" customHeight="1" s="14">
       <c r="A25" s="51" t="n">
@@ -9872,24 +9993,29 @@
       </c>
       <c r="L25" s="47" t="inlineStr">
         <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M25" s="47" t="inlineStr">
+        <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="M25" s="45">
+      <c r="N25" s="45">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-11-the-face-map.jpg")</f>
         <v/>
       </c>
-      <c r="N25" s="47" t="inlineStr">
+      <c r="O25" s="47" t="inlineStr">
         <is>
           <t>JEaLiFe Pictures / Unsplash</t>
         </is>
       </c>
-      <c r="O25" s="45" t="inlineStr">
+      <c r="P25" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="P25" s="46" t="inlineStr"/>
+      <c r="Q25" s="46" t="inlineStr"/>
     </row>
     <row r="26" ht="132" customHeight="1" s="14">
       <c r="A26" s="51" t="n">
@@ -9946,24 +10072,29 @@
       </c>
       <c r="L26" s="47" t="inlineStr">
         <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M26" s="47" t="inlineStr">
+        <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="M26" s="45">
+      <c r="N26" s="45">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-12-does-it-hurt.jpg")</f>
         <v/>
       </c>
-      <c r="N26" s="47" t="inlineStr">
+      <c r="O26" s="47" t="inlineStr">
         <is>
           <t>Victor Meza / Unsplash</t>
         </is>
       </c>
-      <c r="O26" s="45" t="inlineStr">
+      <c r="P26" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="P26" s="46" t="inlineStr"/>
+      <c r="Q26" s="46" t="inlineStr"/>
     </row>
     <row r="27" ht="132" customHeight="1" s="14">
       <c r="A27" s="50" t="n">
@@ -10020,24 +10151,29 @@
       </c>
       <c r="L27" s="43" t="inlineStr">
         <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M27" s="43" t="inlineStr">
+        <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="M27" s="41">
+      <c r="N27" s="41">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-13-still-look-like-you.jpg")</f>
         <v/>
       </c>
-      <c r="N27" s="43" t="inlineStr">
+      <c r="O27" s="43" t="inlineStr">
         <is>
           <t>Zac Taheriyan / Unsplash</t>
         </is>
       </c>
-      <c r="O27" s="41" t="inlineStr">
+      <c r="P27" s="41" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="P27" s="42" t="inlineStr"/>
+      <c r="Q27" s="42" t="inlineStr"/>
     </row>
     <row r="28" ht="132" customHeight="1" s="14">
       <c r="A28" s="51" t="n">
@@ -10094,24 +10230,29 @@
       </c>
       <c r="L28" s="47" t="inlineStr">
         <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M28" s="47" t="inlineStr">
+        <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="M28" s="45">
+      <c r="N28" s="45">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-14-5-things-botox-cannot-do.jpg")</f>
         <v/>
       </c>
-      <c r="N28" s="47" t="inlineStr">
+      <c r="O28" s="47" t="inlineStr">
         <is>
           <t>engin akyurt / Unsplash</t>
         </is>
       </c>
-      <c r="O28" s="45" t="inlineStr">
+      <c r="P28" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="P28" s="46" t="inlineStr"/>
+      <c r="Q28" s="46" t="inlineStr"/>
     </row>
     <row r="29" ht="132" customHeight="1" s="14">
       <c r="A29" s="51" t="n">
@@ -10168,24 +10309,29 @@
       </c>
       <c r="L29" s="47" t="inlineStr">
         <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M29" s="47" t="inlineStr">
+        <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="M29" s="45">
+      <c r="N29" s="45">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-15-what-it-cannot-fix.jpg")</f>
         <v/>
       </c>
-      <c r="N29" s="47" t="inlineStr">
+      <c r="O29" s="47" t="inlineStr">
         <is>
           <t>engin akyurt / Unsplash</t>
         </is>
       </c>
-      <c r="O29" s="45" t="inlineStr">
+      <c r="P29" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="P29" s="46" t="inlineStr"/>
+      <c r="Q29" s="46" t="inlineStr"/>
     </row>
     <row r="30" ht="132" customHeight="1" s="14">
       <c r="A30" s="50" t="n">
@@ -10242,24 +10388,29 @@
       </c>
       <c r="L30" s="43" t="inlineStr">
         <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M30" s="43" t="inlineStr">
+        <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="M30" s="41">
+      <c r="N30" s="41">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-16-how-to-book.jpg")</f>
         <v/>
       </c>
-      <c r="N30" s="43" t="inlineStr">
+      <c r="O30" s="43" t="inlineStr">
         <is>
           <t>Bee Naturalles / Unsplash</t>
         </is>
       </c>
-      <c r="O30" s="41" t="inlineStr">
+      <c r="P30" s="41" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="P30" s="42" t="inlineStr"/>
+      <c r="Q30" s="42" t="inlineStr"/>
     </row>
     <row r="31" ht="132" customHeight="1" s="14">
       <c r="A31" s="51" t="n">
@@ -10316,24 +10467,29 @@
       </c>
       <c r="L31" s="47" t="inlineStr">
         <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M31" s="47" t="inlineStr">
+        <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="M31" s="45">
+      <c r="N31" s="45">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-17-still-you-just-refreshed.jpg")</f>
         <v/>
       </c>
-      <c r="N31" s="47" t="inlineStr">
+      <c r="O31" s="47" t="inlineStr">
         <is>
           <t>Zulfugar Karimov / Unsplash</t>
         </is>
       </c>
-      <c r="O31" s="45" t="inlineStr">
+      <c r="P31" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="P31" s="46" t="inlineStr"/>
+      <c r="Q31" s="46" t="inlineStr"/>
     </row>
     <row r="32" ht="132" customHeight="1" s="14">
       <c r="A32" s="51" t="n">
@@ -10390,24 +10546,29 @@
       </c>
       <c r="L32" s="47" t="inlineStr">
         <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M32" s="47" t="inlineStr">
+        <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="M32" s="45">
+      <c r="N32" s="45">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-18-frozen-face-myth.jpg")</f>
         <v/>
       </c>
-      <c r="N32" s="47" t="inlineStr">
+      <c r="O32" s="47" t="inlineStr">
         <is>
           <t>Neda Vidakovic / Unsplash</t>
         </is>
       </c>
-      <c r="O32" s="45" t="inlineStr">
+      <c r="P32" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="P32" s="46" t="inlineStr"/>
+      <c r="Q32" s="46" t="inlineStr"/>
     </row>
     <row r="33" ht="132" customHeight="1" s="14">
       <c r="A33" s="51" t="n">
@@ -10464,24 +10625,29 @@
       </c>
       <c r="L33" s="47" t="inlineStr">
         <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M33" s="47" t="inlineStr">
+        <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="M33" s="45">
+      <c r="N33" s="45">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-19-nobody-guessed.jpg")</f>
         <v/>
       </c>
-      <c r="N33" s="47" t="inlineStr">
+      <c r="O33" s="47" t="inlineStr">
         <is>
           <t>Vitaliy Shevchenko / Unsplash</t>
         </is>
       </c>
-      <c r="O33" s="45" t="inlineStr">
+      <c r="P33" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="P33" s="46" t="inlineStr"/>
+      <c r="Q33" s="46" t="inlineStr"/>
     </row>
     <row r="34" ht="132" customHeight="1" s="14">
       <c r="A34" s="50" t="n">
@@ -10538,24 +10704,29 @@
       </c>
       <c r="L34" s="43" t="inlineStr">
         <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M34" s="43" t="inlineStr">
+        <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="M34" s="41">
+      <c r="N34" s="41">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-20-service-area.jpg")</f>
         <v/>
       </c>
-      <c r="N34" s="43" t="inlineStr">
+      <c r="O34" s="43" t="inlineStr">
         <is>
           <t>Elist Nguyen / Unsplash</t>
         </is>
       </c>
-      <c r="O34" s="41" t="inlineStr">
+      <c r="P34" s="41" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="P34" s="42" t="inlineStr"/>
+      <c r="Q34" s="42" t="inlineStr"/>
     </row>
     <row r="35" ht="132" customHeight="1" s="14">
       <c r="A35" s="51" t="n">
@@ -10612,24 +10783,29 @@
       </c>
       <c r="L35" s="47" t="inlineStr">
         <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M35" s="47" t="inlineStr">
+        <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="M35" s="45">
+      <c r="N35" s="45">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-21-botox-or-filler.jpg")</f>
         <v/>
       </c>
-      <c r="N35" s="47" t="inlineStr">
+      <c r="O35" s="47" t="inlineStr">
         <is>
           <t>Alef Morais / Unsplash</t>
         </is>
       </c>
-      <c r="O35" s="45" t="inlineStr">
+      <c r="P35" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="P35" s="46" t="inlineStr"/>
+      <c r="Q35" s="46" t="inlineStr"/>
     </row>
     <row r="36" ht="132" customHeight="1" s="14">
       <c r="A36" s="51" t="n">
@@ -10686,24 +10862,29 @@
       </c>
       <c r="L36" s="47" t="inlineStr">
         <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M36" s="47" t="inlineStr">
+        <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="M36" s="45">
+      <c r="N36" s="45">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-22-lines-vs-volume.jpg")</f>
         <v/>
       </c>
-      <c r="N36" s="47" t="inlineStr">
+      <c r="O36" s="47" t="inlineStr">
         <is>
           <t>Rosa Rafael / Unsplash</t>
         </is>
       </c>
-      <c r="O36" s="45" t="inlineStr">
+      <c r="P36" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="P36" s="46" t="inlineStr"/>
+      <c r="Q36" s="46" t="inlineStr"/>
     </row>
     <row r="37" ht="132" customHeight="1" s="14">
       <c r="A37" s="50" t="n">
@@ -10760,24 +10941,29 @@
       </c>
       <c r="L37" s="43" t="inlineStr">
         <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M37" s="43" t="inlineStr">
+        <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="M37" s="41">
+      <c r="N37" s="41">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-23-what-to-ask.jpg")</f>
         <v/>
       </c>
-      <c r="N37" s="43" t="inlineStr">
+      <c r="O37" s="43" t="inlineStr">
         <is>
           <t>Soheil Kmp / Unsplash</t>
         </is>
       </c>
-      <c r="O37" s="41" t="inlineStr">
+      <c r="P37" s="41" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="P37" s="42" t="inlineStr"/>
+      <c r="Q37" s="42" t="inlineStr"/>
     </row>
     <row r="38" ht="132" customHeight="1" s="14">
       <c r="A38" s="51" t="n">
@@ -10834,24 +11020,29 @@
       </c>
       <c r="L38" s="47" t="inlineStr">
         <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M38" s="47" t="inlineStr">
+        <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="M38" s="45">
+      <c r="N38" s="45">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-24-ask-np-cleo.jpg")</f>
         <v/>
       </c>
-      <c r="N38" s="47" t="inlineStr">
+      <c r="O38" s="47" t="inlineStr">
         <is>
           <t>Look Studio / Unsplash</t>
         </is>
       </c>
-      <c r="O38" s="45" t="inlineStr">
+      <c r="P38" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="P38" s="46" t="inlineStr"/>
+      <c r="Q38" s="46" t="inlineStr"/>
     </row>
     <row r="39" ht="132" customHeight="1" s="14">
       <c r="A39" s="51" t="n">
@@ -10908,24 +11099,29 @@
       </c>
       <c r="L39" s="47" t="inlineStr">
         <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M39" s="47" t="inlineStr">
+        <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="M39" s="45">
+      <c r="N39" s="45">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-25-your-dms-answered.jpg")</f>
         <v/>
       </c>
-      <c r="N39" s="47" t="inlineStr">
+      <c r="O39" s="47" t="inlineStr">
         <is>
           <t>Masum Rahimi / Unsplash</t>
         </is>
       </c>
-      <c r="O39" s="45" t="inlineStr">
+      <c r="P39" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="P39" s="46" t="inlineStr"/>
+      <c r="Q39" s="46" t="inlineStr"/>
     </row>
     <row r="40" ht="132" customHeight="1" s="14">
       <c r="A40" s="51" t="n">
@@ -10982,24 +11178,29 @@
       </c>
       <c r="L40" s="47" t="inlineStr">
         <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M40" s="47" t="inlineStr">
+        <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="M40" s="45">
+      <c r="N40" s="45">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-26-what-next.jpg")</f>
         <v/>
       </c>
-      <c r="N40" s="47" t="inlineStr">
+      <c r="O40" s="47" t="inlineStr">
         <is>
           <t>Calugar Ana Maria / Unsplash</t>
         </is>
       </c>
-      <c r="O40" s="45" t="inlineStr">
+      <c r="P40" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="P40" s="46" t="inlineStr"/>
+      <c r="Q40" s="46" t="inlineStr"/>
     </row>
     <row r="41" ht="132" customHeight="1" s="14">
       <c r="A41" s="50" t="n">
@@ -11056,24 +11257,29 @@
       </c>
       <c r="L41" s="43" t="inlineStr">
         <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M41" s="43" t="inlineStr">
+        <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="M41" s="41">
+      <c r="N41" s="41">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-27-two-week-review.jpg")</f>
         <v/>
       </c>
-      <c r="N41" s="43" t="inlineStr">
+      <c r="O41" s="43" t="inlineStr">
         <is>
           <t>Ionela Mat / Unsplash</t>
         </is>
       </c>
-      <c r="O41" s="41" t="inlineStr">
+      <c r="P41" s="41" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="P41" s="42" t="inlineStr"/>
+      <c r="Q41" s="42" t="inlineStr"/>
     </row>
     <row r="42" ht="132" customHeight="1" s="14">
       <c r="A42" s="51" t="n">
@@ -11130,24 +11336,29 @@
       </c>
       <c r="L42" s="47" t="inlineStr">
         <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M42" s="47" t="inlineStr">
+        <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="M42" s="45">
+      <c r="N42" s="45">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-28-how-long-does-it-last.jpg")</f>
         <v/>
       </c>
-      <c r="N42" s="47" t="inlineStr">
+      <c r="O42" s="47" t="inlineStr">
         <is>
           <t>ONNE Beauty / Unsplash</t>
         </is>
       </c>
-      <c r="O42" s="45" t="inlineStr">
+      <c r="P42" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="P42" s="46" t="inlineStr"/>
+      <c r="Q42" s="46" t="inlineStr"/>
     </row>
     <row r="43" ht="132" customHeight="1" s="14">
       <c r="A43" s="51" t="n">
@@ -11204,24 +11415,29 @@
       </c>
       <c r="L43" s="47" t="inlineStr">
         <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M43" s="47" t="inlineStr">
+        <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="M43" s="45">
+      <c r="N43" s="45">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-29-three-month-timeline.jpg")</f>
         <v/>
       </c>
-      <c r="N43" s="47" t="inlineStr">
+      <c r="O43" s="47" t="inlineStr">
         <is>
           <t>Catherine Grimes / Unsplash</t>
         </is>
       </c>
-      <c r="O43" s="45" t="inlineStr">
+      <c r="P43" s="45" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="P43" s="46" t="inlineStr"/>
+      <c r="Q43" s="46" t="inlineStr"/>
     </row>
     <row r="44" ht="132" customHeight="1" s="14">
       <c r="A44" s="50" t="n">
@@ -11278,156 +11494,204 @@
       </c>
       <c r="L44" s="43" t="inlineStr">
         <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M44" s="43" t="inlineStr">
+        <is>
           <t>Open image</t>
         </is>
       </c>
-      <c r="M44" s="41">
+      <c r="N44" s="41">
         <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-09-30-october-preview.jpg")</f>
         <v/>
       </c>
-      <c r="N44" s="43" t="inlineStr">
+      <c r="O44" s="43" t="inlineStr">
         <is>
           <t>Christin Hume / Unsplash</t>
         </is>
       </c>
-      <c r="O44" s="41" t="inlineStr">
+      <c r="P44" s="41" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="P44" s="42" t="inlineStr"/>
+      <c r="Q44" s="42" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N4" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N5" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N7" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N8" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N9" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N10" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N11" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N12" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N13" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N14" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N17" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N20" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N21" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N22" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N24" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N25" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N28" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N29" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N30" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N31" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N32" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N33" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N34" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N35" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N36" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N37" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N38" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N39" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N40" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N41" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N42" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N43" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N44" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O4" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O5" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O6" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O8" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M30" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M32" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M33" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O39" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M43" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M44" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId172"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/strategy/ig-content-strategy.xlsx
+++ b/strategy/ig-content-strategy.xlsx
@@ -16,19 +16,26 @@
     <sheet name="Photo Library" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Ideas Backlog" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Posting Schedule'!$A$1:$AB$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GBP Daily'!$A$1:$Q$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Monthly Themes'!$A$1:$E$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Content Pillars'!$A$1:$E$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Hashtag Sets'!$A$1:$C$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Photo Library'!$A$1:$G$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Ideas Backlog'!$A$1:$E$15</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="mmm\ d&quot;, &quot;yyyy"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="23">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -154,8 +161,18 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -187,6 +204,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F3EEE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF6DF"/>
       </patternFill>
     </fill>
   </fills>
@@ -225,7 +247,7 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -350,6 +372,22 @@
     </xf>
     <xf numFmtId="165" fontId="19" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -601,17 +639,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="002E2A23"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:C45"/>
+  <dimension ref="A1:C56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" style="14" min="1" max="1"/>
-    <col width="22" customWidth="1" style="14" min="2" max="2"/>
-    <col width="95" customWidth="1" style="14" min="3" max="3"/>
+    <col width="26" customWidth="1" style="14" min="2" max="2"/>
+    <col width="104" customWidth="1" style="14" min="3" max="3"/>
   </cols>
   <sheetData>
+    <row r="1" s="14">
+      <c r="A1" s="57" t="n"/>
+      <c r="B1" s="57" t="n"/>
+      <c r="C1" s="57" t="n"/>
+    </row>
     <row r="2">
       <c r="B2" s="35" t="inlineStr">
         <is>
@@ -1030,6 +1074,103 @@
       <c r="C45" s="24" t="inlineStr">
         <is>
           <t>drive.google.com &gt; New &gt; File upload &gt; pick this file &gt; open with Google Sheets. Preview thumbnails and links work there.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="56" t="inlineStr">
+        <is>
+          <t>GBP DAILY SNAPSHOT</t>
+        </is>
+      </c>
+      <c r="C47" s="49" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="B48" s="56" t="inlineStr">
+        <is>
+          <t>Daily posts planned</t>
+        </is>
+      </c>
+      <c r="C48" s="49">
+        <f>COUNTA('GBP Daily'!A2:A44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="56" t="inlineStr">
+        <is>
+          <t>Ready to post</t>
+        </is>
+      </c>
+      <c r="C49" s="49">
+        <f>COUNTIF('GBP Daily'!P2:P44,"Ready")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="56" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
+      <c r="C50" s="49">
+        <f>COUNTIF('GBP Daily'!P2:P44,"Posted")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="56" t="inlineStr">
+        <is>
+          <t>READING THIS FILE</t>
+        </is>
+      </c>
+      <c r="C52" s="49" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="B53" s="56" t="inlineStr">
+        <is>
+          <t>Shaded cells</t>
+        </is>
+      </c>
+      <c r="C53" s="49" t="inlineStr">
+        <is>
+          <t>The cream shaded columns are yours to fill in: Status, Posted Link, Reach, Saves, Comments, DMs, Bookings on the schedule, and Status and Notes on GBP Daily. Everything else is generated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="56" t="inlineStr">
+        <is>
+          <t>Which tab wins</t>
+        </is>
+      </c>
+      <c r="C54" s="49" t="inlineStr">
+        <is>
+          <t>GBP Daily is the source of truth for Google Business Profile from Aug 19 to Sep 30, one post every day. The GBP Caption, GBP CTA and GBP Image Link columns on Posting Schedule cover the Instagram posting days only, and run past Sep 30 where GBP Daily stops.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="56" t="inlineStr">
+        <is>
+          <t>Preview column</t>
+        </is>
+      </c>
+      <c r="C55" s="49" t="inlineStr">
+        <is>
+          <t>Preview uses IMAGE(), which is a Google Sheets function. It shows a live thumbnail there and an error in Excel. Open Folder, Open Image and every other link work in both.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="56" t="inlineStr">
+        <is>
+          <t>Regenerating</t>
+        </is>
+      </c>
+      <c r="C56" s="49" t="inlineStr">
+        <is>
+          <t>GBP Daily is rebuilt by design/build-gbp-daily.py from strategy/gbp-daily-content.json. Run strategy/organize-workbook.py afterwards to restore this formatting. Status and Notes survive a rebuild, matched by date; other edits to that tab do not.</t>
         </is>
       </c>
     </row>
@@ -1041,6 +1182,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
+    <tabColor rgb="00C9A85C"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
@@ -1071,143 +1213,143 @@
     <col width="20" customWidth="1" style="14" min="26" max="26"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="14">
-      <c r="A1" s="25" t="inlineStr">
+    <row r="1" ht="30" customHeight="1" s="14">
+      <c r="A1" s="53" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="25" t="inlineStr">
+      <c r="B1" s="53" t="inlineStr">
         <is>
           <t>Day</t>
         </is>
       </c>
-      <c r="C1" s="25" t="inlineStr">
+      <c r="C1" s="53" t="inlineStr">
         <is>
           <t>Week</t>
         </is>
       </c>
-      <c r="D1" s="25" t="inlineStr">
+      <c r="D1" s="53" t="inlineStr">
         <is>
           <t>Month Theme</t>
         </is>
       </c>
-      <c r="E1" s="25" t="inlineStr">
+      <c r="E1" s="53" t="inlineStr">
         <is>
           <t>Format</t>
         </is>
       </c>
-      <c r="F1" s="26" t="inlineStr">
+      <c r="F1" s="52" t="inlineStr">
         <is>
           <t>Tone</t>
         </is>
       </c>
-      <c r="G1" s="25" t="inlineStr">
+      <c r="G1" s="53" t="inlineStr">
         <is>
           <t>Platforms</t>
         </is>
       </c>
-      <c r="H1" s="25" t="inlineStr">
+      <c r="H1" s="53" t="inlineStr">
         <is>
           <t>Pillar</t>
         </is>
       </c>
-      <c r="I1" s="25" t="inlineStr">
+      <c r="I1" s="53" t="inlineStr">
         <is>
           <t>Topic &amp; Hook</t>
         </is>
       </c>
-      <c r="J1" s="25" t="inlineStr">
+      <c r="J1" s="53" t="inlineStr">
         <is>
           <t>Caption Draft</t>
         </is>
       </c>
-      <c r="K1" s="25" t="inlineStr">
+      <c r="K1" s="53" t="inlineStr">
         <is>
           <t>CTA</t>
         </is>
       </c>
-      <c r="L1" s="25" t="inlineStr">
+      <c r="L1" s="53" t="inlineStr">
         <is>
           <t>Hashtag Set</t>
         </is>
       </c>
-      <c r="M1" s="25" t="inlineStr">
+      <c r="M1" s="53" t="inlineStr">
         <is>
           <t>Visual / Asset</t>
         </is>
       </c>
-      <c r="N1" s="26" t="inlineStr">
+      <c r="N1" s="52" t="inlineStr">
         <is>
           <t>Photo Assets</t>
         </is>
       </c>
-      <c r="O1" s="26" t="inlineStr">
+      <c r="O1" s="52" t="inlineStr">
         <is>
           <t>Consent</t>
         </is>
       </c>
-      <c r="P1" s="25" t="inlineStr">
+      <c r="P1" s="53" t="inlineStr">
         <is>
           <t>Folder Link</t>
         </is>
       </c>
-      <c r="Q1" s="26" t="inlineStr">
+      <c r="Q1" s="52" t="inlineStr">
         <is>
           <t>Image Link</t>
         </is>
       </c>
-      <c r="R1" s="26" t="inlineStr">
+      <c r="R1" s="52" t="inlineStr">
         <is>
           <t>Preview</t>
         </is>
       </c>
-      <c r="S1" s="25" t="inlineStr">
+      <c r="S1" s="53" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="T1" s="25" t="inlineStr">
+      <c r="T1" s="53" t="inlineStr">
         <is>
           <t>Posted Link</t>
         </is>
       </c>
-      <c r="U1" s="25" t="inlineStr">
+      <c r="U1" s="53" t="inlineStr">
         <is>
           <t>Reach</t>
         </is>
       </c>
-      <c r="V1" s="25" t="inlineStr">
+      <c r="V1" s="53" t="inlineStr">
         <is>
           <t>Saves</t>
         </is>
       </c>
-      <c r="W1" s="25" t="inlineStr">
+      <c r="W1" s="53" t="inlineStr">
         <is>
           <t>Comments</t>
         </is>
       </c>
-      <c r="X1" s="25" t="inlineStr">
+      <c r="X1" s="53" t="inlineStr">
         <is>
           <t>DMs</t>
         </is>
       </c>
-      <c r="Y1" s="25" t="inlineStr">
+      <c r="Y1" s="53" t="inlineStr">
         <is>
           <t>Bookings</t>
         </is>
       </c>
-      <c r="Z1" s="26" t="inlineStr">
+      <c r="Z1" s="52" t="inlineStr">
         <is>
           <t>GBP Caption</t>
         </is>
       </c>
-      <c r="AA1" s="26" t="inlineStr">
+      <c r="AA1" s="52" t="inlineStr">
         <is>
           <t>GBP CTA</t>
         </is>
       </c>
-      <c r="AB1" s="26" t="inlineStr">
+      <c r="AB1" s="52" t="inlineStr">
         <is>
           <t>GBP Image Link</t>
         </is>
@@ -1301,16 +1443,16 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="T2" s="28" t="n"/>
-      <c r="U2" s="28" t="n"/>
-      <c r="V2" s="28" t="n"/>
-      <c r="W2" s="28" t="n"/>
-      <c r="X2" s="28" t="n"/>
-      <c r="Y2" s="28" t="n"/>
+      <c r="T2" s="54" t="n"/>
+      <c r="U2" s="54" t="n"/>
+      <c r="V2" s="54" t="n"/>
+      <c r="W2" s="54" t="n"/>
+      <c r="X2" s="54" t="n"/>
+      <c r="Y2" s="54" t="n"/>
       <c r="Z2" s="24" t="n"/>
       <c r="AA2" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/blob/claude/med-spa-carousel-ideas-sim9wz/content/2026-08-17-5-botox-lies-you-still/images/gbp.jpg?raw=1</t>
+          <t>Learn more &gt; Instagram</t>
         </is>
       </c>
       <c r="AB2" s="33" t="inlineStr">
@@ -1407,16 +1549,16 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="T3" s="30" t="n"/>
-      <c r="U3" s="30" t="n"/>
-      <c r="V3" s="30" t="n"/>
-      <c r="W3" s="30" t="n"/>
-      <c r="X3" s="30" t="n"/>
-      <c r="Y3" s="30" t="n"/>
+      <c r="T3" s="54" t="n"/>
+      <c r="U3" s="54" t="n"/>
+      <c r="V3" s="54" t="n"/>
+      <c r="W3" s="54" t="n"/>
+      <c r="X3" s="54" t="n"/>
+      <c r="Y3" s="54" t="n"/>
       <c r="Z3" s="24" t="n"/>
       <c r="AA3" s="24" t="inlineStr">
         <is>
-          <t>https://github.com/RepoKing23/InstagramCarousel/blob/claude/med-spa-carousel-ideas-sim9wz/content/2026-08-18-service-spotlight-botox/images/gbp.jpg?raw=1</t>
+          <t>Learn more &gt; Instagram</t>
         </is>
       </c>
       <c r="AB3" s="33" t="inlineStr">
@@ -1519,12 +1661,12 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="T4" s="28" t="n"/>
-      <c r="U4" s="28" t="n"/>
-      <c r="V4" s="28" t="n"/>
-      <c r="W4" s="28" t="n"/>
-      <c r="X4" s="28" t="n"/>
-      <c r="Y4" s="28" t="n"/>
+      <c r="T4" s="54" t="n"/>
+      <c r="U4" s="54" t="n"/>
+      <c r="V4" s="54" t="n"/>
+      <c r="W4" s="54" t="n"/>
+      <c r="X4" s="54" t="n"/>
+      <c r="Y4" s="54" t="n"/>
       <c r="Z4" s="24" t="inlineStr">
         <is>
           <t>Five things to walk away from at a med spa: no consultation, bargain pricing, a provider who never says no, no named injector, and no plan for complications. Know them before you book anywhere. Serving Oakville, Burlington, Milton and Mississauga.</t>
@@ -1635,12 +1777,12 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="T5" s="30" t="n"/>
-      <c r="U5" s="30" t="n"/>
-      <c r="V5" s="30" t="n"/>
-      <c r="W5" s="30" t="n"/>
-      <c r="X5" s="30" t="n"/>
-      <c r="Y5" s="30" t="n"/>
+      <c r="T5" s="54" t="n"/>
+      <c r="U5" s="54" t="n"/>
+      <c r="V5" s="54" t="n"/>
+      <c r="W5" s="54" t="n"/>
+      <c r="X5" s="54" t="n"/>
+      <c r="Y5" s="54" t="n"/>
       <c r="Z5" s="24" t="inlineStr">
         <is>
           <t>Every appointment starts the same way. New tray, sealed product opened in front of you, and your face mapped while it moves so the plan fits how you actually move. Ask to watch. Serving Oakville, Burlington, Milton and Mississauga.</t>
@@ -1755,12 +1897,12 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="T6" s="30" t="n"/>
-      <c r="U6" s="30" t="n"/>
-      <c r="V6" s="30" t="n"/>
-      <c r="W6" s="30" t="n"/>
-      <c r="X6" s="30" t="n"/>
-      <c r="Y6" s="30" t="n"/>
+      <c r="T6" s="54" t="n"/>
+      <c r="U6" s="54" t="n"/>
+      <c r="V6" s="54" t="n"/>
+      <c r="W6" s="54" t="n"/>
+      <c r="X6" s="54" t="n"/>
+      <c r="Y6" s="54" t="n"/>
       <c r="Z6" s="24" t="inlineStr">
         <is>
           <t>One syringe of lip filler, with her own lip shape kept exactly where it was. Natural results are the whole point of how we practise. Shared with client consent, individual results vary. Serving Oakville, Burlington, Milton and Mississauga.</t>
@@ -1872,12 +2014,12 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="T7" s="28" t="n"/>
-      <c r="U7" s="28" t="n"/>
-      <c r="V7" s="28" t="n"/>
-      <c r="W7" s="28" t="n"/>
-      <c r="X7" s="28" t="n"/>
-      <c r="Y7" s="28" t="n"/>
+      <c r="T7" s="54" t="n"/>
+      <c r="U7" s="54" t="n"/>
+      <c r="V7" s="54" t="n"/>
+      <c r="W7" s="54" t="n"/>
+      <c r="X7" s="54" t="n"/>
+      <c r="Y7" s="54" t="n"/>
       <c r="Z7" s="24" t="inlineStr">
         <is>
           <t>Nervous about your first appointment? A real consultation, your face mapped in motion, then the areas and the price agreed before anything is opened. The treatment itself takes about ten minutes. Serving Oakville, Burlington, Milton and Mississauga.</t>
@@ -1991,12 +2133,12 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="T8" s="30" t="n"/>
-      <c r="U8" s="30" t="n"/>
-      <c r="V8" s="30" t="n"/>
-      <c r="W8" s="30" t="n"/>
-      <c r="X8" s="30" t="n"/>
-      <c r="Y8" s="30" t="n"/>
+      <c r="T8" s="54" t="n"/>
+      <c r="U8" s="54" t="n"/>
+      <c r="V8" s="54" t="n"/>
+      <c r="W8" s="54" t="n"/>
+      <c r="X8" s="54" t="n"/>
+      <c r="Y8" s="54" t="n"/>
       <c r="Z8" s="24" t="inlineStr">
         <is>
           <t>Why we do not post a price list. Doses differ from face to face, so one flat price either overcharges you or under treats you. You get a written number at your consult, before anything is opened. Serving Oakville, Burlington, Milton and Mississauga.</t>
@@ -2108,12 +2250,12 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="T9" s="28" t="n"/>
-      <c r="U9" s="28" t="n"/>
-      <c r="V9" s="28" t="n"/>
-      <c r="W9" s="28" t="n"/>
-      <c r="X9" s="28" t="n"/>
-      <c r="Y9" s="28" t="n"/>
+      <c r="T9" s="54" t="n"/>
+      <c r="U9" s="54" t="n"/>
+      <c r="V9" s="54" t="n"/>
+      <c r="W9" s="54" t="n"/>
+      <c r="X9" s="54" t="n"/>
+      <c r="Y9" s="54" t="n"/>
       <c r="Z9" s="24" t="inlineStr">
         <is>
           <t>Meet NP Cleo. Nurse practitioner and injector, and the person who will tell you no when the honest answer is not yet. Every appointment is injected by Cleo, never delegated. Serving Oakville, Burlington, Milton and Mississauga.</t>
@@ -2223,12 +2365,12 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="T10" s="30" t="n"/>
-      <c r="U10" s="30" t="n"/>
-      <c r="V10" s="30" t="n"/>
-      <c r="W10" s="30" t="n"/>
-      <c r="X10" s="30" t="n"/>
-      <c r="Y10" s="30" t="n"/>
+      <c r="T10" s="54" t="n"/>
+      <c r="U10" s="54" t="n"/>
+      <c r="V10" s="54" t="n"/>
+      <c r="W10" s="54" t="n"/>
+      <c r="X10" s="54" t="n"/>
+      <c r="Y10" s="54" t="n"/>
       <c r="Z10" s="24" t="inlineStr">
         <is>
           <t>One client in the treatment room at a time. Nobody rushes the person before you, so nobody rushes you. Questions welcome, and a plan agreed before anything happens. Serving Oakville, Burlington, Milton and Mississauga.</t>
@@ -2337,12 +2479,12 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="T11" s="30" t="n"/>
-      <c r="U11" s="30" t="n"/>
-      <c r="V11" s="30" t="n"/>
-      <c r="W11" s="30" t="n"/>
-      <c r="X11" s="30" t="n"/>
-      <c r="Y11" s="30" t="n"/>
+      <c r="T11" s="54" t="n"/>
+      <c r="U11" s="54" t="n"/>
+      <c r="V11" s="54" t="n"/>
+      <c r="W11" s="54" t="n"/>
+      <c r="X11" s="54" t="n"/>
+      <c r="Y11" s="54" t="n"/>
       <c r="Z11" s="24" t="inlineStr">
         <is>
           <t>Rested, not frozen. You should still frown, squint and smile. If people ask what you had done instead of whether you slept well, the dose was wrong. Serving Oakville, Burlington, Milton and Mississauga.</t>
@@ -2454,12 +2596,12 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="T12" s="28" t="n"/>
-      <c r="U12" s="28" t="n"/>
-      <c r="V12" s="28" t="n"/>
-      <c r="W12" s="28" t="n"/>
-      <c r="X12" s="28" t="n"/>
-      <c r="Y12" s="28" t="n"/>
+      <c r="T12" s="54" t="n"/>
+      <c r="U12" s="54" t="n"/>
+      <c r="V12" s="54" t="n"/>
+      <c r="W12" s="54" t="n"/>
+      <c r="X12" s="54" t="n"/>
+      <c r="Y12" s="54" t="n"/>
       <c r="Z12" s="24" t="inlineStr">
         <is>
           <t>When should you actually start preventative treatment? It is not about your age. Make your strongest expression, then relax completely. A line that stays is one that is setting in. Serving Oakville, Burlington, Milton and Mississauga.</t>
@@ -2561,12 +2703,12 @@
           <t>Idea</t>
         </is>
       </c>
-      <c r="T13" s="30" t="n"/>
-      <c r="U13" s="30" t="n"/>
-      <c r="V13" s="30" t="n"/>
-      <c r="W13" s="30" t="n"/>
-      <c r="X13" s="30" t="n"/>
-      <c r="Y13" s="30" t="n"/>
+      <c r="T13" s="54" t="n"/>
+      <c r="U13" s="54" t="n"/>
+      <c r="V13" s="54" t="n"/>
+      <c r="W13" s="54" t="n"/>
+      <c r="X13" s="54" t="n"/>
+      <c r="Y13" s="54" t="n"/>
       <c r="Z13" s="24" t="n"/>
       <c r="AA13" s="24" t="n"/>
       <c r="AB13" s="24" t="inlineStr">
@@ -2660,12 +2802,12 @@
           <t>Idea</t>
         </is>
       </c>
-      <c r="T14" s="28" t="n"/>
-      <c r="U14" s="28" t="n"/>
-      <c r="V14" s="28" t="n"/>
-      <c r="W14" s="28" t="n"/>
-      <c r="X14" s="28" t="n"/>
-      <c r="Y14" s="28" t="n"/>
+      <c r="T14" s="54" t="n"/>
+      <c r="U14" s="54" t="n"/>
+      <c r="V14" s="54" t="n"/>
+      <c r="W14" s="54" t="n"/>
+      <c r="X14" s="54" t="n"/>
+      <c r="Y14" s="54" t="n"/>
       <c r="Z14" s="24" t="n"/>
       <c r="AA14" s="24" t="n"/>
       <c r="AB14" s="24" t="inlineStr">
@@ -2759,12 +2901,12 @@
           <t>Idea</t>
         </is>
       </c>
-      <c r="T15" s="30" t="n"/>
-      <c r="U15" s="30" t="n"/>
-      <c r="V15" s="30" t="n"/>
-      <c r="W15" s="30" t="n"/>
-      <c r="X15" s="30" t="n"/>
-      <c r="Y15" s="30" t="n"/>
+      <c r="T15" s="54" t="n"/>
+      <c r="U15" s="54" t="n"/>
+      <c r="V15" s="54" t="n"/>
+      <c r="W15" s="54" t="n"/>
+      <c r="X15" s="54" t="n"/>
+      <c r="Y15" s="54" t="n"/>
       <c r="Z15" s="24" t="n"/>
       <c r="AA15" s="24" t="n"/>
       <c r="AB15" s="24" t="inlineStr">
@@ -2858,12 +3000,12 @@
           <t>Idea</t>
         </is>
       </c>
-      <c r="T16" s="30" t="n"/>
-      <c r="U16" s="30" t="n"/>
-      <c r="V16" s="30" t="n"/>
-      <c r="W16" s="30" t="n"/>
-      <c r="X16" s="30" t="n"/>
-      <c r="Y16" s="30" t="n"/>
+      <c r="T16" s="54" t="n"/>
+      <c r="U16" s="54" t="n"/>
+      <c r="V16" s="54" t="n"/>
+      <c r="W16" s="54" t="n"/>
+      <c r="X16" s="54" t="n"/>
+      <c r="Y16" s="54" t="n"/>
       <c r="Z16" s="24" t="n"/>
       <c r="AA16" s="24" t="n"/>
       <c r="AB16" s="24" t="inlineStr">
@@ -2957,12 +3099,12 @@
           <t>Idea</t>
         </is>
       </c>
-      <c r="T17" s="28" t="n"/>
-      <c r="U17" s="28" t="n"/>
-      <c r="V17" s="28" t="n"/>
-      <c r="W17" s="28" t="n"/>
-      <c r="X17" s="28" t="n"/>
-      <c r="Y17" s="28" t="n"/>
+      <c r="T17" s="54" t="n"/>
+      <c r="U17" s="54" t="n"/>
+      <c r="V17" s="54" t="n"/>
+      <c r="W17" s="54" t="n"/>
+      <c r="X17" s="54" t="n"/>
+      <c r="Y17" s="54" t="n"/>
       <c r="Z17" s="24" t="n"/>
       <c r="AA17" s="24" t="n"/>
       <c r="AB17" s="24" t="inlineStr">
@@ -3056,12 +3198,12 @@
           <t>Idea</t>
         </is>
       </c>
-      <c r="T18" s="30" t="n"/>
-      <c r="U18" s="30" t="n"/>
-      <c r="V18" s="30" t="n"/>
-      <c r="W18" s="30" t="n"/>
-      <c r="X18" s="30" t="n"/>
-      <c r="Y18" s="30" t="n"/>
+      <c r="T18" s="54" t="n"/>
+      <c r="U18" s="54" t="n"/>
+      <c r="V18" s="54" t="n"/>
+      <c r="W18" s="54" t="n"/>
+      <c r="X18" s="54" t="n"/>
+      <c r="Y18" s="54" t="n"/>
       <c r="Z18" s="24" t="n"/>
       <c r="AA18" s="24" t="n"/>
       <c r="AB18" s="24" t="inlineStr">
@@ -3155,12 +3297,12 @@
           <t>Idea</t>
         </is>
       </c>
-      <c r="T19" s="28" t="n"/>
-      <c r="U19" s="28" t="n"/>
-      <c r="V19" s="28" t="n"/>
-      <c r="W19" s="28" t="n"/>
-      <c r="X19" s="28" t="n"/>
-      <c r="Y19" s="28" t="n"/>
+      <c r="T19" s="54" t="n"/>
+      <c r="U19" s="54" t="n"/>
+      <c r="V19" s="54" t="n"/>
+      <c r="W19" s="54" t="n"/>
+      <c r="X19" s="54" t="n"/>
+      <c r="Y19" s="54" t="n"/>
       <c r="Z19" s="24" t="n"/>
       <c r="AA19" s="24" t="n"/>
       <c r="AB19" s="24" t="inlineStr">
@@ -3254,12 +3396,12 @@
           <t>Idea</t>
         </is>
       </c>
-      <c r="T20" s="30" t="n"/>
-      <c r="U20" s="30" t="n"/>
-      <c r="V20" s="30" t="n"/>
-      <c r="W20" s="30" t="n"/>
-      <c r="X20" s="30" t="n"/>
-      <c r="Y20" s="30" t="n"/>
+      <c r="T20" s="54" t="n"/>
+      <c r="U20" s="54" t="n"/>
+      <c r="V20" s="54" t="n"/>
+      <c r="W20" s="54" t="n"/>
+      <c r="X20" s="54" t="n"/>
+      <c r="Y20" s="54" t="n"/>
       <c r="Z20" s="24" t="n"/>
       <c r="AA20" s="24" t="n"/>
       <c r="AB20" s="24" t="inlineStr">
@@ -3353,12 +3495,12 @@
           <t>Idea</t>
         </is>
       </c>
-      <c r="T21" s="30" t="n"/>
-      <c r="U21" s="30" t="n"/>
-      <c r="V21" s="30" t="n"/>
-      <c r="W21" s="30" t="n"/>
-      <c r="X21" s="30" t="n"/>
-      <c r="Y21" s="30" t="n"/>
+      <c r="T21" s="54" t="n"/>
+      <c r="U21" s="54" t="n"/>
+      <c r="V21" s="54" t="n"/>
+      <c r="W21" s="54" t="n"/>
+      <c r="X21" s="54" t="n"/>
+      <c r="Y21" s="54" t="n"/>
       <c r="Z21" s="24" t="n"/>
       <c r="AA21" s="24" t="n"/>
       <c r="AB21" s="24" t="inlineStr">
@@ -3452,12 +3594,12 @@
           <t>Idea</t>
         </is>
       </c>
-      <c r="T22" s="28" t="n"/>
-      <c r="U22" s="28" t="n"/>
-      <c r="V22" s="28" t="n"/>
-      <c r="W22" s="28" t="n"/>
-      <c r="X22" s="28" t="n"/>
-      <c r="Y22" s="28" t="n"/>
+      <c r="T22" s="54" t="n"/>
+      <c r="U22" s="54" t="n"/>
+      <c r="V22" s="54" t="n"/>
+      <c r="W22" s="54" t="n"/>
+      <c r="X22" s="54" t="n"/>
+      <c r="Y22" s="54" t="n"/>
       <c r="Z22" s="24" t="n"/>
       <c r="AA22" s="24" t="n"/>
       <c r="AB22" s="24" t="inlineStr">
@@ -3551,12 +3693,12 @@
           <t>Idea</t>
         </is>
       </c>
-      <c r="T23" s="30" t="n"/>
-      <c r="U23" s="30" t="n"/>
-      <c r="V23" s="30" t="n"/>
-      <c r="W23" s="30" t="n"/>
-      <c r="X23" s="30" t="n"/>
-      <c r="Y23" s="30" t="n"/>
+      <c r="T23" s="54" t="n"/>
+      <c r="U23" s="54" t="n"/>
+      <c r="V23" s="54" t="n"/>
+      <c r="W23" s="54" t="n"/>
+      <c r="X23" s="54" t="n"/>
+      <c r="Y23" s="54" t="n"/>
       <c r="Z23" s="24" t="n"/>
       <c r="AA23" s="24" t="n"/>
       <c r="AB23" s="24" t="inlineStr">
@@ -3650,12 +3792,12 @@
           <t>Idea</t>
         </is>
       </c>
-      <c r="T24" s="28" t="n"/>
-      <c r="U24" s="28" t="n"/>
-      <c r="V24" s="28" t="n"/>
-      <c r="W24" s="28" t="n"/>
-      <c r="X24" s="28" t="n"/>
-      <c r="Y24" s="28" t="n"/>
+      <c r="T24" s="54" t="n"/>
+      <c r="U24" s="54" t="n"/>
+      <c r="V24" s="54" t="n"/>
+      <c r="W24" s="54" t="n"/>
+      <c r="X24" s="54" t="n"/>
+      <c r="Y24" s="54" t="n"/>
       <c r="Z24" s="24" t="n"/>
       <c r="AA24" s="24" t="n"/>
       <c r="AB24" s="24" t="inlineStr">
@@ -3749,12 +3891,12 @@
           <t>Idea</t>
         </is>
       </c>
-      <c r="T25" s="30" t="n"/>
-      <c r="U25" s="30" t="n"/>
-      <c r="V25" s="30" t="n"/>
-      <c r="W25" s="30" t="n"/>
-      <c r="X25" s="30" t="n"/>
-      <c r="Y25" s="30" t="n"/>
+      <c r="T25" s="54" t="n"/>
+      <c r="U25" s="54" t="n"/>
+      <c r="V25" s="54" t="n"/>
+      <c r="W25" s="54" t="n"/>
+      <c r="X25" s="54" t="n"/>
+      <c r="Y25" s="54" t="n"/>
       <c r="Z25" s="24" t="n"/>
       <c r="AA25" s="24" t="n"/>
       <c r="AB25" s="24" t="inlineStr">
@@ -3848,12 +3990,12 @@
           <t>Idea</t>
         </is>
       </c>
-      <c r="T26" s="30" t="n"/>
-      <c r="U26" s="30" t="n"/>
-      <c r="V26" s="30" t="n"/>
-      <c r="W26" s="30" t="n"/>
-      <c r="X26" s="30" t="n"/>
-      <c r="Y26" s="30" t="n"/>
+      <c r="T26" s="54" t="n"/>
+      <c r="U26" s="54" t="n"/>
+      <c r="V26" s="54" t="n"/>
+      <c r="W26" s="54" t="n"/>
+      <c r="X26" s="54" t="n"/>
+      <c r="Y26" s="54" t="n"/>
       <c r="Z26" s="24" t="n"/>
       <c r="AA26" s="24" t="n"/>
       <c r="AB26" s="24" t="inlineStr">
@@ -3947,12 +4089,12 @@
           <t>Idea</t>
         </is>
       </c>
-      <c r="T27" s="28" t="n"/>
-      <c r="U27" s="28" t="n"/>
-      <c r="V27" s="28" t="n"/>
-      <c r="W27" s="28" t="n"/>
-      <c r="X27" s="28" t="n"/>
-      <c r="Y27" s="28" t="n"/>
+      <c r="T27" s="54" t="n"/>
+      <c r="U27" s="54" t="n"/>
+      <c r="V27" s="54" t="n"/>
+      <c r="W27" s="54" t="n"/>
+      <c r="X27" s="54" t="n"/>
+      <c r="Y27" s="54" t="n"/>
       <c r="Z27" s="24" t="n"/>
       <c r="AA27" s="24" t="n"/>
       <c r="AB27" s="24" t="inlineStr">
@@ -4046,12 +4188,12 @@
           <t>Idea</t>
         </is>
       </c>
-      <c r="T28" s="30" t="n"/>
-      <c r="U28" s="30" t="n"/>
-      <c r="V28" s="30" t="n"/>
-      <c r="W28" s="30" t="n"/>
-      <c r="X28" s="30" t="n"/>
-      <c r="Y28" s="30" t="n"/>
+      <c r="T28" s="54" t="n"/>
+      <c r="U28" s="54" t="n"/>
+      <c r="V28" s="54" t="n"/>
+      <c r="W28" s="54" t="n"/>
+      <c r="X28" s="54" t="n"/>
+      <c r="Y28" s="54" t="n"/>
       <c r="Z28" s="24" t="n"/>
       <c r="AA28" s="24" t="n"/>
       <c r="AB28" s="24" t="inlineStr">
@@ -4145,12 +4287,12 @@
           <t>Idea</t>
         </is>
       </c>
-      <c r="T29" s="28" t="n"/>
-      <c r="U29" s="28" t="n"/>
-      <c r="V29" s="28" t="n"/>
-      <c r="W29" s="28" t="n"/>
-      <c r="X29" s="28" t="n"/>
-      <c r="Y29" s="28" t="n"/>
+      <c r="T29" s="54" t="n"/>
+      <c r="U29" s="54" t="n"/>
+      <c r="V29" s="54" t="n"/>
+      <c r="W29" s="54" t="n"/>
+      <c r="X29" s="54" t="n"/>
+      <c r="Y29" s="54" t="n"/>
       <c r="Z29" s="24" t="n"/>
       <c r="AA29" s="24" t="n"/>
       <c r="AB29" s="24" t="inlineStr">
@@ -4244,12 +4386,12 @@
           <t>Idea</t>
         </is>
       </c>
-      <c r="T30" s="30" t="n"/>
-      <c r="U30" s="30" t="n"/>
-      <c r="V30" s="30" t="n"/>
-      <c r="W30" s="30" t="n"/>
-      <c r="X30" s="30" t="n"/>
-      <c r="Y30" s="30" t="n"/>
+      <c r="T30" s="54" t="n"/>
+      <c r="U30" s="54" t="n"/>
+      <c r="V30" s="54" t="n"/>
+      <c r="W30" s="54" t="n"/>
+      <c r="X30" s="54" t="n"/>
+      <c r="Y30" s="54" t="n"/>
       <c r="Z30" s="24" t="n"/>
       <c r="AA30" s="24" t="n"/>
       <c r="AB30" s="24" t="inlineStr">
@@ -4343,12 +4485,12 @@
           <t>Idea</t>
         </is>
       </c>
-      <c r="T31" s="30" t="n"/>
-      <c r="U31" s="30" t="n"/>
-      <c r="V31" s="30" t="n"/>
-      <c r="W31" s="30" t="n"/>
-      <c r="X31" s="30" t="n"/>
-      <c r="Y31" s="30" t="n"/>
+      <c r="T31" s="54" t="n"/>
+      <c r="U31" s="54" t="n"/>
+      <c r="V31" s="54" t="n"/>
+      <c r="W31" s="54" t="n"/>
+      <c r="X31" s="54" t="n"/>
+      <c r="Y31" s="54" t="n"/>
       <c r="Z31" s="24" t="n"/>
       <c r="AA31" s="24" t="n"/>
       <c r="AB31" s="24" t="inlineStr">
@@ -4442,12 +4584,12 @@
           <t>Idea</t>
         </is>
       </c>
-      <c r="T32" s="28" t="n"/>
-      <c r="U32" s="28" t="n"/>
-      <c r="V32" s="28" t="n"/>
-      <c r="W32" s="28" t="n"/>
-      <c r="X32" s="28" t="n"/>
-      <c r="Y32" s="28" t="n"/>
+      <c r="T32" s="54" t="n"/>
+      <c r="U32" s="54" t="n"/>
+      <c r="V32" s="54" t="n"/>
+      <c r="W32" s="54" t="n"/>
+      <c r="X32" s="54" t="n"/>
+      <c r="Y32" s="54" t="n"/>
       <c r="Z32" s="24" t="n"/>
       <c r="AA32" s="24" t="n"/>
       <c r="AB32" s="24" t="inlineStr">
@@ -4541,12 +4683,12 @@
           <t>Idea</t>
         </is>
       </c>
-      <c r="T33" s="30" t="n"/>
-      <c r="U33" s="30" t="n"/>
-      <c r="V33" s="30" t="n"/>
-      <c r="W33" s="30" t="n"/>
-      <c r="X33" s="30" t="n"/>
-      <c r="Y33" s="30" t="n"/>
+      <c r="T33" s="54" t="n"/>
+      <c r="U33" s="54" t="n"/>
+      <c r="V33" s="54" t="n"/>
+      <c r="W33" s="54" t="n"/>
+      <c r="X33" s="54" t="n"/>
+      <c r="Y33" s="54" t="n"/>
       <c r="Z33" s="24" t="n"/>
       <c r="AA33" s="24" t="n"/>
       <c r="AB33" s="24" t="inlineStr">
@@ -4640,12 +4782,12 @@
           <t>Idea</t>
         </is>
       </c>
-      <c r="T34" s="28" t="n"/>
-      <c r="U34" s="28" t="n"/>
-      <c r="V34" s="28" t="n"/>
-      <c r="W34" s="28" t="n"/>
-      <c r="X34" s="28" t="n"/>
-      <c r="Y34" s="28" t="n"/>
+      <c r="T34" s="54" t="n"/>
+      <c r="U34" s="54" t="n"/>
+      <c r="V34" s="54" t="n"/>
+      <c r="W34" s="54" t="n"/>
+      <c r="X34" s="54" t="n"/>
+      <c r="Y34" s="54" t="n"/>
       <c r="Z34" s="24" t="n"/>
       <c r="AA34" s="24" t="n"/>
       <c r="AB34" s="24" t="inlineStr">
@@ -4739,12 +4881,12 @@
           <t>Idea</t>
         </is>
       </c>
-      <c r="T35" s="30" t="n"/>
-      <c r="U35" s="30" t="n"/>
-      <c r="V35" s="30" t="n"/>
-      <c r="W35" s="30" t="n"/>
-      <c r="X35" s="30" t="n"/>
-      <c r="Y35" s="30" t="n"/>
+      <c r="T35" s="54" t="n"/>
+      <c r="U35" s="54" t="n"/>
+      <c r="V35" s="54" t="n"/>
+      <c r="W35" s="54" t="n"/>
+      <c r="X35" s="54" t="n"/>
+      <c r="Y35" s="54" t="n"/>
       <c r="Z35" s="24" t="n"/>
       <c r="AA35" s="24" t="n"/>
       <c r="AB35" s="24" t="inlineStr">
@@ -4838,12 +4980,12 @@
           <t>Idea</t>
         </is>
       </c>
-      <c r="T36" s="30" t="n"/>
-      <c r="U36" s="30" t="n"/>
-      <c r="V36" s="30" t="n"/>
-      <c r="W36" s="30" t="n"/>
-      <c r="X36" s="30" t="n"/>
-      <c r="Y36" s="30" t="n"/>
+      <c r="T36" s="54" t="n"/>
+      <c r="U36" s="54" t="n"/>
+      <c r="V36" s="54" t="n"/>
+      <c r="W36" s="54" t="n"/>
+      <c r="X36" s="54" t="n"/>
+      <c r="Y36" s="54" t="n"/>
       <c r="Z36" s="24" t="n"/>
       <c r="AA36" s="24" t="n"/>
       <c r="AB36" s="24" t="inlineStr">
@@ -4937,12 +5079,12 @@
           <t>Idea</t>
         </is>
       </c>
-      <c r="T37" s="28" t="n"/>
-      <c r="U37" s="28" t="n"/>
-      <c r="V37" s="28" t="n"/>
-      <c r="W37" s="28" t="n"/>
-      <c r="X37" s="28" t="n"/>
-      <c r="Y37" s="28" t="n"/>
+      <c r="T37" s="54" t="n"/>
+      <c r="U37" s="54" t="n"/>
+      <c r="V37" s="54" t="n"/>
+      <c r="W37" s="54" t="n"/>
+      <c r="X37" s="54" t="n"/>
+      <c r="Y37" s="54" t="n"/>
       <c r="Z37" s="24" t="n"/>
       <c r="AA37" s="24" t="n"/>
       <c r="AB37" s="24" t="inlineStr">
@@ -5036,12 +5178,12 @@
           <t>Idea</t>
         </is>
       </c>
-      <c r="T38" s="30" t="n"/>
-      <c r="U38" s="30" t="n"/>
-      <c r="V38" s="30" t="n"/>
-      <c r="W38" s="30" t="n"/>
-      <c r="X38" s="30" t="n"/>
-      <c r="Y38" s="30" t="n"/>
+      <c r="T38" s="54" t="n"/>
+      <c r="U38" s="54" t="n"/>
+      <c r="V38" s="54" t="n"/>
+      <c r="W38" s="54" t="n"/>
+      <c r="X38" s="54" t="n"/>
+      <c r="Y38" s="54" t="n"/>
       <c r="Z38" s="24" t="n"/>
       <c r="AA38" s="24" t="n"/>
       <c r="AB38" s="24" t="inlineStr">
@@ -5142,12 +5284,12 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="T39" s="28" t="n"/>
-      <c r="U39" s="28" t="n"/>
-      <c r="V39" s="28" t="n"/>
-      <c r="W39" s="28" t="n"/>
-      <c r="X39" s="28" t="n"/>
-      <c r="Y39" s="28" t="n"/>
+      <c r="T39" s="54" t="n"/>
+      <c r="U39" s="54" t="n"/>
+      <c r="V39" s="54" t="n"/>
+      <c r="W39" s="54" t="n"/>
+      <c r="X39" s="54" t="n"/>
+      <c r="Y39" s="54" t="n"/>
       <c r="Z39" s="24" t="n"/>
       <c r="AA39" s="24" t="n"/>
       <c r="AB39" s="24" t="inlineStr">
@@ -5241,12 +5383,12 @@
           <t>Idea</t>
         </is>
       </c>
-      <c r="T40" s="30" t="n"/>
-      <c r="U40" s="30" t="n"/>
-      <c r="V40" s="30" t="n"/>
-      <c r="W40" s="30" t="n"/>
-      <c r="X40" s="30" t="n"/>
-      <c r="Y40" s="30" t="n"/>
+      <c r="T40" s="54" t="n"/>
+      <c r="U40" s="54" t="n"/>
+      <c r="V40" s="54" t="n"/>
+      <c r="W40" s="54" t="n"/>
+      <c r="X40" s="54" t="n"/>
+      <c r="Y40" s="54" t="n"/>
       <c r="Z40" s="24" t="n"/>
       <c r="AA40" s="24" t="n"/>
       <c r="AB40" s="24" t="inlineStr">
@@ -5347,12 +5489,12 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="T41" s="30" t="n"/>
-      <c r="U41" s="30" t="n"/>
-      <c r="V41" s="30" t="n"/>
-      <c r="W41" s="30" t="n"/>
-      <c r="X41" s="30" t="n"/>
-      <c r="Y41" s="30" t="n"/>
+      <c r="T41" s="54" t="n"/>
+      <c r="U41" s="54" t="n"/>
+      <c r="V41" s="54" t="n"/>
+      <c r="W41" s="54" t="n"/>
+      <c r="X41" s="54" t="n"/>
+      <c r="Y41" s="54" t="n"/>
       <c r="Z41" s="24" t="n"/>
       <c r="AA41" s="24" t="n"/>
       <c r="AB41" s="24" t="inlineStr">
@@ -5446,12 +5588,12 @@
           <t>Idea</t>
         </is>
       </c>
-      <c r="T42" s="28" t="n"/>
-      <c r="U42" s="28" t="n"/>
-      <c r="V42" s="28" t="n"/>
-      <c r="W42" s="28" t="n"/>
-      <c r="X42" s="28" t="n"/>
-      <c r="Y42" s="28" t="n"/>
+      <c r="T42" s="54" t="n"/>
+      <c r="U42" s="54" t="n"/>
+      <c r="V42" s="54" t="n"/>
+      <c r="W42" s="54" t="n"/>
+      <c r="X42" s="54" t="n"/>
+      <c r="Y42" s="54" t="n"/>
       <c r="Z42" s="24" t="n"/>
       <c r="AA42" s="24" t="n"/>
       <c r="AB42" s="24" t="inlineStr">
@@ -5545,12 +5687,12 @@
           <t>Idea</t>
         </is>
       </c>
-      <c r="T43" s="30" t="n"/>
-      <c r="U43" s="30" t="n"/>
-      <c r="V43" s="30" t="n"/>
-      <c r="W43" s="30" t="n"/>
-      <c r="X43" s="30" t="n"/>
-      <c r="Y43" s="30" t="n"/>
+      <c r="T43" s="54" t="n"/>
+      <c r="U43" s="54" t="n"/>
+      <c r="V43" s="54" t="n"/>
+      <c r="W43" s="54" t="n"/>
+      <c r="X43" s="54" t="n"/>
+      <c r="Y43" s="54" t="n"/>
       <c r="Z43" s="24" t="n"/>
       <c r="AA43" s="24" t="n"/>
       <c r="AB43" s="24" t="inlineStr">
@@ -5651,12 +5793,12 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="T44" s="28" t="n"/>
-      <c r="U44" s="28" t="n"/>
-      <c r="V44" s="28" t="n"/>
-      <c r="W44" s="28" t="n"/>
-      <c r="X44" s="28" t="n"/>
-      <c r="Y44" s="28" t="n"/>
+      <c r="T44" s="54" t="n"/>
+      <c r="U44" s="54" t="n"/>
+      <c r="V44" s="54" t="n"/>
+      <c r="W44" s="54" t="n"/>
+      <c r="X44" s="54" t="n"/>
+      <c r="Y44" s="54" t="n"/>
       <c r="Z44" s="24" t="n"/>
       <c r="AA44" s="24" t="n"/>
       <c r="AB44" s="24" t="inlineStr">
@@ -5750,12 +5892,12 @@
           <t>Idea</t>
         </is>
       </c>
-      <c r="T45" s="30" t="n"/>
-      <c r="U45" s="30" t="n"/>
-      <c r="V45" s="30" t="n"/>
-      <c r="W45" s="30" t="n"/>
-      <c r="X45" s="30" t="n"/>
-      <c r="Y45" s="30" t="n"/>
+      <c r="T45" s="54" t="n"/>
+      <c r="U45" s="54" t="n"/>
+      <c r="V45" s="54" t="n"/>
+      <c r="W45" s="54" t="n"/>
+      <c r="X45" s="54" t="n"/>
+      <c r="Y45" s="54" t="n"/>
       <c r="Z45" s="24" t="n"/>
       <c r="AA45" s="24" t="n"/>
       <c r="AB45" s="24" t="inlineStr">
@@ -5849,12 +5991,12 @@
           <t>Idea</t>
         </is>
       </c>
-      <c r="T46" s="30" t="n"/>
-      <c r="U46" s="30" t="n"/>
-      <c r="V46" s="30" t="n"/>
-      <c r="W46" s="30" t="n"/>
-      <c r="X46" s="30" t="n"/>
-      <c r="Y46" s="30" t="n"/>
+      <c r="T46" s="54" t="n"/>
+      <c r="U46" s="54" t="n"/>
+      <c r="V46" s="54" t="n"/>
+      <c r="W46" s="54" t="n"/>
+      <c r="X46" s="54" t="n"/>
+      <c r="Y46" s="54" t="n"/>
       <c r="Z46" s="24" t="n"/>
       <c r="AA46" s="24" t="n"/>
       <c r="AB46" s="24" t="inlineStr">
@@ -5948,12 +6090,12 @@
           <t>Idea</t>
         </is>
       </c>
-      <c r="T47" s="28" t="n"/>
-      <c r="U47" s="28" t="n"/>
-      <c r="V47" s="28" t="n"/>
-      <c r="W47" s="28" t="n"/>
-      <c r="X47" s="28" t="n"/>
-      <c r="Y47" s="28" t="n"/>
+      <c r="T47" s="54" t="n"/>
+      <c r="U47" s="54" t="n"/>
+      <c r="V47" s="54" t="n"/>
+      <c r="W47" s="54" t="n"/>
+      <c r="X47" s="54" t="n"/>
+      <c r="Y47" s="54" t="n"/>
       <c r="Z47" s="24" t="n"/>
       <c r="AA47" s="24" t="n"/>
       <c r="AB47" s="24" t="inlineStr">
@@ -6047,12 +6189,12 @@
           <t>Idea</t>
         </is>
       </c>
-      <c r="T48" s="30" t="n"/>
-      <c r="U48" s="30" t="n"/>
-      <c r="V48" s="30" t="n"/>
-      <c r="W48" s="30" t="n"/>
-      <c r="X48" s="30" t="n"/>
-      <c r="Y48" s="30" t="n"/>
+      <c r="T48" s="54" t="n"/>
+      <c r="U48" s="54" t="n"/>
+      <c r="V48" s="54" t="n"/>
+      <c r="W48" s="54" t="n"/>
+      <c r="X48" s="54" t="n"/>
+      <c r="Y48" s="54" t="n"/>
       <c r="Z48" s="24" t="n"/>
       <c r="AA48" s="24" t="n"/>
       <c r="AB48" s="24" t="inlineStr">
@@ -6153,12 +6295,12 @@
           <t>Design</t>
         </is>
       </c>
-      <c r="T49" s="28" t="n"/>
-      <c r="U49" s="28" t="n"/>
-      <c r="V49" s="28" t="n"/>
-      <c r="W49" s="28" t="n"/>
-      <c r="X49" s="28" t="n"/>
-      <c r="Y49" s="28" t="n"/>
+      <c r="T49" s="54" t="n"/>
+      <c r="U49" s="54" t="n"/>
+      <c r="V49" s="54" t="n"/>
+      <c r="W49" s="54" t="n"/>
+      <c r="X49" s="54" t="n"/>
+      <c r="Y49" s="54" t="n"/>
       <c r="Z49" s="24" t="n"/>
       <c r="AA49" s="24" t="n"/>
       <c r="AB49" s="24" t="inlineStr">
@@ -6252,12 +6394,12 @@
           <t>Idea</t>
         </is>
       </c>
-      <c r="T50" s="30" t="n"/>
-      <c r="U50" s="30" t="n"/>
-      <c r="V50" s="30" t="n"/>
-      <c r="W50" s="30" t="n"/>
-      <c r="X50" s="30" t="n"/>
-      <c r="Y50" s="30" t="n"/>
+      <c r="T50" s="54" t="n"/>
+      <c r="U50" s="54" t="n"/>
+      <c r="V50" s="54" t="n"/>
+      <c r="W50" s="54" t="n"/>
+      <c r="X50" s="54" t="n"/>
+      <c r="Y50" s="54" t="n"/>
       <c r="Z50" s="24" t="n"/>
       <c r="AA50" s="24" t="n"/>
       <c r="AB50" s="24" t="inlineStr">
@@ -6358,12 +6500,12 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="T51" s="30" t="n"/>
-      <c r="U51" s="30" t="n"/>
-      <c r="V51" s="30" t="n"/>
-      <c r="W51" s="30" t="n"/>
-      <c r="X51" s="30" t="n"/>
-      <c r="Y51" s="30" t="n"/>
+      <c r="T51" s="54" t="n"/>
+      <c r="U51" s="54" t="n"/>
+      <c r="V51" s="54" t="n"/>
+      <c r="W51" s="54" t="n"/>
+      <c r="X51" s="54" t="n"/>
+      <c r="Y51" s="54" t="n"/>
       <c r="Z51" s="24" t="n"/>
       <c r="AA51" s="24" t="n"/>
       <c r="AB51" s="24" t="inlineStr">
@@ -6457,12 +6599,12 @@
           <t>Idea</t>
         </is>
       </c>
-      <c r="T52" s="28" t="n"/>
-      <c r="U52" s="28" t="n"/>
-      <c r="V52" s="28" t="n"/>
-      <c r="W52" s="28" t="n"/>
-      <c r="X52" s="28" t="n"/>
-      <c r="Y52" s="28" t="n"/>
+      <c r="T52" s="54" t="n"/>
+      <c r="U52" s="54" t="n"/>
+      <c r="V52" s="54" t="n"/>
+      <c r="W52" s="54" t="n"/>
+      <c r="X52" s="54" t="n"/>
+      <c r="Y52" s="54" t="n"/>
       <c r="Z52" s="24" t="n"/>
       <c r="AA52" s="24" t="n"/>
       <c r="AB52" s="24" t="inlineStr">
@@ -6556,12 +6698,12 @@
           <t>Idea</t>
         </is>
       </c>
-      <c r="T53" s="30" t="n"/>
-      <c r="U53" s="30" t="n"/>
-      <c r="V53" s="30" t="n"/>
-      <c r="W53" s="30" t="n"/>
-      <c r="X53" s="30" t="n"/>
-      <c r="Y53" s="30" t="n"/>
+      <c r="T53" s="54" t="n"/>
+      <c r="U53" s="54" t="n"/>
+      <c r="V53" s="54" t="n"/>
+      <c r="W53" s="54" t="n"/>
+      <c r="X53" s="54" t="n"/>
+      <c r="Y53" s="54" t="n"/>
       <c r="Z53" s="24" t="n"/>
       <c r="AA53" s="24" t="n"/>
       <c r="AB53" s="24" t="inlineStr">
@@ -6655,12 +6797,12 @@
           <t>Idea</t>
         </is>
       </c>
-      <c r="T54" s="28" t="n"/>
-      <c r="U54" s="28" t="n"/>
-      <c r="V54" s="28" t="n"/>
-      <c r="W54" s="28" t="n"/>
-      <c r="X54" s="28" t="n"/>
-      <c r="Y54" s="28" t="n"/>
+      <c r="T54" s="54" t="n"/>
+      <c r="U54" s="54" t="n"/>
+      <c r="V54" s="54" t="n"/>
+      <c r="W54" s="54" t="n"/>
+      <c r="X54" s="54" t="n"/>
+      <c r="Y54" s="54" t="n"/>
       <c r="Z54" s="24" t="n"/>
       <c r="AA54" s="24" t="n"/>
       <c r="AB54" s="24" t="inlineStr">
@@ -6761,12 +6903,12 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="T55" s="30" t="n"/>
-      <c r="U55" s="30" t="n"/>
-      <c r="V55" s="30" t="n"/>
-      <c r="W55" s="30" t="n"/>
-      <c r="X55" s="30" t="n"/>
-      <c r="Y55" s="30" t="n"/>
+      <c r="T55" s="54" t="n"/>
+      <c r="U55" s="54" t="n"/>
+      <c r="V55" s="54" t="n"/>
+      <c r="W55" s="54" t="n"/>
+      <c r="X55" s="54" t="n"/>
+      <c r="Y55" s="54" t="n"/>
       <c r="Z55" s="24" t="n"/>
       <c r="AA55" s="24" t="n"/>
       <c r="AB55" s="24" t="inlineStr">
@@ -6860,12 +7002,12 @@
           <t>Idea</t>
         </is>
       </c>
-      <c r="T56" s="30" t="n"/>
-      <c r="U56" s="30" t="n"/>
-      <c r="V56" s="30" t="n"/>
-      <c r="W56" s="30" t="n"/>
-      <c r="X56" s="30" t="n"/>
-      <c r="Y56" s="30" t="n"/>
+      <c r="T56" s="54" t="n"/>
+      <c r="U56" s="54" t="n"/>
+      <c r="V56" s="54" t="n"/>
+      <c r="W56" s="54" t="n"/>
+      <c r="X56" s="54" t="n"/>
+      <c r="Y56" s="54" t="n"/>
       <c r="Z56" s="24" t="n"/>
       <c r="AA56" s="24" t="n"/>
       <c r="AB56" s="24" t="inlineStr">
@@ -6959,12 +7101,12 @@
           <t>Idea</t>
         </is>
       </c>
-      <c r="T57" s="28" t="n"/>
-      <c r="U57" s="28" t="n"/>
-      <c r="V57" s="28" t="n"/>
-      <c r="W57" s="28" t="n"/>
-      <c r="X57" s="28" t="n"/>
-      <c r="Y57" s="28" t="n"/>
+      <c r="T57" s="54" t="n"/>
+      <c r="U57" s="54" t="n"/>
+      <c r="V57" s="54" t="n"/>
+      <c r="W57" s="54" t="n"/>
+      <c r="X57" s="54" t="n"/>
+      <c r="Y57" s="54" t="n"/>
       <c r="Z57" s="24" t="n"/>
       <c r="AA57" s="24" t="n"/>
       <c r="AB57" s="24" t="inlineStr">
@@ -7058,12 +7200,12 @@
           <t>Idea</t>
         </is>
       </c>
-      <c r="T58" s="30" t="n"/>
-      <c r="U58" s="30" t="n"/>
-      <c r="V58" s="30" t="n"/>
-      <c r="W58" s="30" t="n"/>
-      <c r="X58" s="30" t="n"/>
-      <c r="Y58" s="30" t="n"/>
+      <c r="T58" s="54" t="n"/>
+      <c r="U58" s="54" t="n"/>
+      <c r="V58" s="54" t="n"/>
+      <c r="W58" s="54" t="n"/>
+      <c r="X58" s="54" t="n"/>
+      <c r="Y58" s="54" t="n"/>
       <c r="Z58" s="24" t="n"/>
       <c r="AA58" s="24" t="n"/>
       <c r="AB58" s="24" t="inlineStr">
@@ -7157,12 +7299,12 @@
           <t>Idea</t>
         </is>
       </c>
-      <c r="T59" s="28" t="n"/>
-      <c r="U59" s="28" t="n"/>
-      <c r="V59" s="28" t="n"/>
-      <c r="W59" s="28" t="n"/>
-      <c r="X59" s="28" t="n"/>
-      <c r="Y59" s="28" t="n"/>
+      <c r="T59" s="54" t="n"/>
+      <c r="U59" s="54" t="n"/>
+      <c r="V59" s="54" t="n"/>
+      <c r="W59" s="54" t="n"/>
+      <c r="X59" s="54" t="n"/>
+      <c r="Y59" s="54" t="n"/>
       <c r="Z59" s="24" t="n"/>
       <c r="AA59" s="24" t="n"/>
       <c r="AB59" s="24" t="inlineStr">
@@ -7263,12 +7405,12 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="T60" s="30" t="n"/>
-      <c r="U60" s="30" t="n"/>
-      <c r="V60" s="30" t="n"/>
-      <c r="W60" s="30" t="n"/>
-      <c r="X60" s="30" t="n"/>
-      <c r="Y60" s="30" t="n"/>
+      <c r="T60" s="54" t="n"/>
+      <c r="U60" s="54" t="n"/>
+      <c r="V60" s="54" t="n"/>
+      <c r="W60" s="54" t="n"/>
+      <c r="X60" s="54" t="n"/>
+      <c r="Y60" s="54" t="n"/>
       <c r="Z60" s="24" t="n"/>
       <c r="AA60" s="24" t="n"/>
       <c r="AB60" s="24" t="inlineStr">
@@ -7362,12 +7504,12 @@
           <t>Idea</t>
         </is>
       </c>
-      <c r="T61" s="30" t="n"/>
-      <c r="U61" s="30" t="n"/>
-      <c r="V61" s="30" t="n"/>
-      <c r="W61" s="30" t="n"/>
-      <c r="X61" s="30" t="n"/>
-      <c r="Y61" s="30" t="n"/>
+      <c r="T61" s="54" t="n"/>
+      <c r="U61" s="54" t="n"/>
+      <c r="V61" s="54" t="n"/>
+      <c r="W61" s="54" t="n"/>
+      <c r="X61" s="54" t="n"/>
+      <c r="Y61" s="54" t="n"/>
       <c r="Z61" s="24" t="n"/>
       <c r="AA61" s="24" t="n"/>
       <c r="AB61" s="24" t="inlineStr">
@@ -7461,12 +7603,12 @@
           <t>Idea</t>
         </is>
       </c>
-      <c r="T62" s="28" t="n"/>
-      <c r="U62" s="28" t="n"/>
-      <c r="V62" s="28" t="n"/>
-      <c r="W62" s="28" t="n"/>
-      <c r="X62" s="28" t="n"/>
-      <c r="Y62" s="28" t="n"/>
+      <c r="T62" s="54" t="n"/>
+      <c r="U62" s="54" t="n"/>
+      <c r="V62" s="54" t="n"/>
+      <c r="W62" s="54" t="n"/>
+      <c r="X62" s="54" t="n"/>
+      <c r="Y62" s="54" t="n"/>
       <c r="Z62" s="24" t="n"/>
       <c r="AA62" s="24" t="n"/>
       <c r="AB62" s="24" t="inlineStr">
@@ -7560,12 +7702,12 @@
           <t>Idea</t>
         </is>
       </c>
-      <c r="T63" s="30" t="n"/>
-      <c r="U63" s="30" t="n"/>
-      <c r="V63" s="30" t="n"/>
-      <c r="W63" s="30" t="n"/>
-      <c r="X63" s="30" t="n"/>
-      <c r="Y63" s="30" t="n"/>
+      <c r="T63" s="54" t="n"/>
+      <c r="U63" s="54" t="n"/>
+      <c r="V63" s="54" t="n"/>
+      <c r="W63" s="54" t="n"/>
+      <c r="X63" s="54" t="n"/>
+      <c r="Y63" s="54" t="n"/>
       <c r="Z63" s="24" t="n"/>
       <c r="AA63" s="24" t="n"/>
       <c r="AB63" s="24" t="inlineStr">
@@ -7659,12 +7801,12 @@
           <t>Idea</t>
         </is>
       </c>
-      <c r="T64" s="28" t="n"/>
-      <c r="U64" s="28" t="n"/>
-      <c r="V64" s="28" t="n"/>
-      <c r="W64" s="28" t="n"/>
-      <c r="X64" s="28" t="n"/>
-      <c r="Y64" s="28" t="n"/>
+      <c r="T64" s="54" t="n"/>
+      <c r="U64" s="54" t="n"/>
+      <c r="V64" s="54" t="n"/>
+      <c r="W64" s="54" t="n"/>
+      <c r="X64" s="54" t="n"/>
+      <c r="Y64" s="54" t="n"/>
       <c r="Z64" s="24" t="n"/>
       <c r="AA64" s="24" t="n"/>
       <c r="AB64" s="24" t="inlineStr">
@@ -7758,12 +7900,12 @@
           <t>Idea</t>
         </is>
       </c>
-      <c r="T65" s="30" t="n"/>
-      <c r="U65" s="30" t="n"/>
-      <c r="V65" s="30" t="n"/>
-      <c r="W65" s="30" t="n"/>
-      <c r="X65" s="30" t="n"/>
-      <c r="Y65" s="30" t="n"/>
+      <c r="T65" s="54" t="n"/>
+      <c r="U65" s="54" t="n"/>
+      <c r="V65" s="54" t="n"/>
+      <c r="W65" s="54" t="n"/>
+      <c r="X65" s="54" t="n"/>
+      <c r="Y65" s="54" t="n"/>
       <c r="Z65" s="24" t="n"/>
       <c r="AA65" s="24" t="n"/>
       <c r="AB65" s="24" t="inlineStr">
@@ -7857,12 +7999,12 @@
           <t>Idea</t>
         </is>
       </c>
-      <c r="T66" s="30" t="n"/>
-      <c r="U66" s="30" t="n"/>
-      <c r="V66" s="30" t="n"/>
-      <c r="W66" s="30" t="n"/>
-      <c r="X66" s="30" t="n"/>
-      <c r="Y66" s="30" t="n"/>
+      <c r="T66" s="54" t="n"/>
+      <c r="U66" s="54" t="n"/>
+      <c r="V66" s="54" t="n"/>
+      <c r="W66" s="54" t="n"/>
+      <c r="X66" s="54" t="n"/>
+      <c r="Y66" s="54" t="n"/>
       <c r="Z66" s="24" t="n"/>
       <c r="AA66" s="24" t="n"/>
       <c r="AB66" s="24" t="inlineStr">
@@ -7872,6 +8014,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AB66"/>
   <dataValidations count="1">
     <dataValidation sqref="P2:P66" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Idea,Design,Ready,Hold,Posted"</formula1>
@@ -8011,6 +8154,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00C9A85C"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -8036,88 +8180,88 @@
     <col width="28" customWidth="1" style="14" min="17" max="17"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="39" t="inlineStr">
+    <row r="1" ht="30" customHeight="1" s="14">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="39" t="inlineStr">
+      <c r="B1" s="52" t="inlineStr">
         <is>
           <t>Day</t>
         </is>
       </c>
-      <c r="C1" s="39" t="inlineStr">
+      <c r="C1" s="52" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="D1" s="39" t="inlineStr">
+      <c r="D1" s="52" t="inlineStr">
         <is>
           <t>Pillar</t>
         </is>
       </c>
-      <c r="E1" s="39" t="inlineStr">
+      <c r="E1" s="52" t="inlineStr">
         <is>
           <t>Post Text (short)</t>
         </is>
       </c>
-      <c r="F1" s="39" t="inlineStr">
+      <c r="F1" s="52" t="inlineStr">
         <is>
           <t>Chars</t>
         </is>
       </c>
-      <c r="G1" s="39" t="inlineStr">
+      <c r="G1" s="52" t="inlineStr">
         <is>
           <t>Description (long, SEO)</t>
         </is>
       </c>
-      <c r="H1" s="39" t="inlineStr">
+      <c r="H1" s="52" t="inlineStr">
         <is>
           <t>Desc Chars</t>
         </is>
       </c>
-      <c r="I1" s="39" t="inlineStr">
+      <c r="I1" s="52" t="inlineStr">
         <is>
           <t>CTA Button</t>
         </is>
       </c>
-      <c r="J1" s="39" t="inlineStr">
+      <c r="J1" s="52" t="inlineStr">
         <is>
           <t>CTA Link</t>
         </is>
       </c>
-      <c r="K1" s="39" t="inlineStr">
+      <c r="K1" s="52" t="inlineStr">
         <is>
           <t>Image File</t>
         </is>
       </c>
-      <c r="L1" s="39" t="inlineStr">
+      <c r="L1" s="52" t="inlineStr">
         <is>
           <t>Open Folder</t>
         </is>
       </c>
-      <c r="M1" s="39" t="inlineStr">
+      <c r="M1" s="52" t="inlineStr">
         <is>
           <t>Open Image</t>
         </is>
       </c>
-      <c r="N1" s="39" t="inlineStr">
+      <c r="N1" s="52" t="inlineStr">
         <is>
           <t>Preview</t>
         </is>
       </c>
-      <c r="O1" s="39" t="inlineStr">
+      <c r="O1" s="52" t="inlineStr">
         <is>
           <t>Photo Credit</t>
         </is>
       </c>
-      <c r="P1" s="39" t="inlineStr">
+      <c r="P1" s="52" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="Q1" s="39" t="inlineStr">
+      <c r="Q1" s="52" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -8199,7 +8343,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q2" s="42" t="inlineStr"/>
+      <c r="Q2" s="55" t="inlineStr"/>
     </row>
     <row r="3" ht="132" customHeight="1" s="14">
       <c r="A3" s="51" t="n">
@@ -8278,7 +8422,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q3" s="46" t="inlineStr"/>
+      <c r="Q3" s="55" t="inlineStr"/>
     </row>
     <row r="4" ht="132" customHeight="1" s="14">
       <c r="A4" s="51" t="n">
@@ -8356,7 +8500,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q4" s="46" t="inlineStr"/>
+      <c r="Q4" s="55" t="inlineStr"/>
     </row>
     <row r="5" ht="132" customHeight="1" s="14">
       <c r="A5" s="51" t="n">
@@ -8435,7 +8579,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q5" s="46" t="inlineStr"/>
+      <c r="Q5" s="55" t="inlineStr"/>
     </row>
     <row r="6" ht="132" customHeight="1" s="14">
       <c r="A6" s="50" t="n">
@@ -8514,7 +8658,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q6" s="42" t="inlineStr"/>
+      <c r="Q6" s="55" t="inlineStr"/>
     </row>
     <row r="7" ht="132" customHeight="1" s="14">
       <c r="A7" s="51" t="n">
@@ -8593,7 +8737,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q7" s="46" t="inlineStr"/>
+      <c r="Q7" s="55" t="inlineStr"/>
     </row>
     <row r="8" ht="132" customHeight="1" s="14">
       <c r="A8" s="51" t="n">
@@ -8672,7 +8816,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q8" s="46" t="inlineStr"/>
+      <c r="Q8" s="55" t="inlineStr"/>
     </row>
     <row r="9" ht="132" customHeight="1" s="14">
       <c r="A9" s="50" t="n">
@@ -8751,7 +8895,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q9" s="42" t="inlineStr"/>
+      <c r="Q9" s="55" t="inlineStr"/>
     </row>
     <row r="10" ht="132" customHeight="1" s="14">
       <c r="A10" s="51" t="n">
@@ -8830,7 +8974,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q10" s="46" t="inlineStr"/>
+      <c r="Q10" s="55" t="inlineStr"/>
     </row>
     <row r="11" ht="132" customHeight="1" s="14">
       <c r="A11" s="51" t="n">
@@ -8909,7 +9053,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q11" s="46" t="inlineStr"/>
+      <c r="Q11" s="55" t="inlineStr"/>
     </row>
     <row r="12" ht="132" customHeight="1" s="14">
       <c r="A12" s="51" t="n">
@@ -8988,7 +9132,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q12" s="46" t="inlineStr"/>
+      <c r="Q12" s="55" t="inlineStr"/>
     </row>
     <row r="13" ht="132" customHeight="1" s="14">
       <c r="A13" s="50" t="n">
@@ -9067,7 +9211,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q13" s="42" t="inlineStr"/>
+      <c r="Q13" s="55" t="inlineStr"/>
     </row>
     <row r="14" ht="132" customHeight="1" s="14">
       <c r="A14" s="51" t="n">
@@ -9146,7 +9290,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q14" s="46" t="inlineStr"/>
+      <c r="Q14" s="55" t="inlineStr"/>
     </row>
     <row r="15" ht="132" customHeight="1" s="14">
       <c r="A15" s="51" t="n">
@@ -9225,7 +9369,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q15" s="46" t="inlineStr"/>
+      <c r="Q15" s="55" t="inlineStr"/>
     </row>
     <row r="16" ht="132" customHeight="1" s="14">
       <c r="A16" s="50" t="n">
@@ -9304,7 +9448,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q16" s="42" t="inlineStr"/>
+      <c r="Q16" s="55" t="inlineStr"/>
     </row>
     <row r="17" ht="132" customHeight="1" s="14">
       <c r="A17" s="51" t="n">
@@ -9383,7 +9527,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q17" s="46" t="inlineStr"/>
+      <c r="Q17" s="55" t="inlineStr"/>
     </row>
     <row r="18" ht="132" customHeight="1" s="14">
       <c r="A18" s="51" t="n">
@@ -9462,7 +9606,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q18" s="46" t="inlineStr"/>
+      <c r="Q18" s="55" t="inlineStr"/>
     </row>
     <row r="19" ht="132" customHeight="1" s="14">
       <c r="A19" s="51" t="n">
@@ -9541,7 +9685,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q19" s="46" t="inlineStr"/>
+      <c r="Q19" s="55" t="inlineStr"/>
     </row>
     <row r="20" ht="132" customHeight="1" s="14">
       <c r="A20" s="50" t="n">
@@ -9620,7 +9764,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q20" s="42" t="inlineStr"/>
+      <c r="Q20" s="55" t="inlineStr"/>
     </row>
     <row r="21" ht="132" customHeight="1" s="14">
       <c r="A21" s="51" t="n">
@@ -9699,7 +9843,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q21" s="46" t="inlineStr"/>
+      <c r="Q21" s="55" t="inlineStr"/>
     </row>
     <row r="22" ht="132" customHeight="1" s="14">
       <c r="A22" s="51" t="n">
@@ -9778,7 +9922,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q22" s="46" t="inlineStr"/>
+      <c r="Q22" s="55" t="inlineStr"/>
     </row>
     <row r="23" ht="132" customHeight="1" s="14">
       <c r="A23" s="50" t="n">
@@ -9857,7 +10001,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q23" s="42" t="inlineStr"/>
+      <c r="Q23" s="55" t="inlineStr"/>
     </row>
     <row r="24" ht="132" customHeight="1" s="14">
       <c r="A24" s="51" t="n">
@@ -9936,7 +10080,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q24" s="46" t="inlineStr"/>
+      <c r="Q24" s="55" t="inlineStr"/>
     </row>
     <row r="25" ht="132" customHeight="1" s="14">
       <c r="A25" s="51" t="n">
@@ -10015,7 +10159,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q25" s="46" t="inlineStr"/>
+      <c r="Q25" s="55" t="inlineStr"/>
     </row>
     <row r="26" ht="132" customHeight="1" s="14">
       <c r="A26" s="51" t="n">
@@ -10094,7 +10238,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q26" s="46" t="inlineStr"/>
+      <c r="Q26" s="55" t="inlineStr"/>
     </row>
     <row r="27" ht="132" customHeight="1" s="14">
       <c r="A27" s="50" t="n">
@@ -10173,7 +10317,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q27" s="42" t="inlineStr"/>
+      <c r="Q27" s="55" t="inlineStr"/>
     </row>
     <row r="28" ht="132" customHeight="1" s="14">
       <c r="A28" s="51" t="n">
@@ -10252,7 +10396,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q28" s="46" t="inlineStr"/>
+      <c r="Q28" s="55" t="inlineStr"/>
     </row>
     <row r="29" ht="132" customHeight="1" s="14">
       <c r="A29" s="51" t="n">
@@ -10331,7 +10475,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q29" s="46" t="inlineStr"/>
+      <c r="Q29" s="55" t="inlineStr"/>
     </row>
     <row r="30" ht="132" customHeight="1" s="14">
       <c r="A30" s="50" t="n">
@@ -10410,7 +10554,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q30" s="42" t="inlineStr"/>
+      <c r="Q30" s="55" t="inlineStr"/>
     </row>
     <row r="31" ht="132" customHeight="1" s="14">
       <c r="A31" s="51" t="n">
@@ -10489,7 +10633,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q31" s="46" t="inlineStr"/>
+      <c r="Q31" s="55" t="inlineStr"/>
     </row>
     <row r="32" ht="132" customHeight="1" s="14">
       <c r="A32" s="51" t="n">
@@ -10568,7 +10712,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q32" s="46" t="inlineStr"/>
+      <c r="Q32" s="55" t="inlineStr"/>
     </row>
     <row r="33" ht="132" customHeight="1" s="14">
       <c r="A33" s="51" t="n">
@@ -10647,7 +10791,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q33" s="46" t="inlineStr"/>
+      <c r="Q33" s="55" t="inlineStr"/>
     </row>
     <row r="34" ht="132" customHeight="1" s="14">
       <c r="A34" s="50" t="n">
@@ -10726,7 +10870,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q34" s="42" t="inlineStr"/>
+      <c r="Q34" s="55" t="inlineStr"/>
     </row>
     <row r="35" ht="132" customHeight="1" s="14">
       <c r="A35" s="51" t="n">
@@ -10805,7 +10949,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q35" s="46" t="inlineStr"/>
+      <c r="Q35" s="55" t="inlineStr"/>
     </row>
     <row r="36" ht="132" customHeight="1" s="14">
       <c r="A36" s="51" t="n">
@@ -10884,7 +11028,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q36" s="46" t="inlineStr"/>
+      <c r="Q36" s="55" t="inlineStr"/>
     </row>
     <row r="37" ht="132" customHeight="1" s="14">
       <c r="A37" s="50" t="n">
@@ -10963,7 +11107,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q37" s="42" t="inlineStr"/>
+      <c r="Q37" s="55" t="inlineStr"/>
     </row>
     <row r="38" ht="132" customHeight="1" s="14">
       <c r="A38" s="51" t="n">
@@ -11042,7 +11186,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q38" s="46" t="inlineStr"/>
+      <c r="Q38" s="55" t="inlineStr"/>
     </row>
     <row r="39" ht="132" customHeight="1" s="14">
       <c r="A39" s="51" t="n">
@@ -11121,7 +11265,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q39" s="46" t="inlineStr"/>
+      <c r="Q39" s="55" t="inlineStr"/>
     </row>
     <row r="40" ht="132" customHeight="1" s="14">
       <c r="A40" s="51" t="n">
@@ -11200,7 +11344,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q40" s="46" t="inlineStr"/>
+      <c r="Q40" s="55" t="inlineStr"/>
     </row>
     <row r="41" ht="132" customHeight="1" s="14">
       <c r="A41" s="50" t="n">
@@ -11279,7 +11423,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q41" s="42" t="inlineStr"/>
+      <c r="Q41" s="55" t="inlineStr"/>
     </row>
     <row r="42" ht="132" customHeight="1" s="14">
       <c r="A42" s="51" t="n">
@@ -11358,7 +11502,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q42" s="46" t="inlineStr"/>
+      <c r="Q42" s="55" t="inlineStr"/>
     </row>
     <row r="43" ht="132" customHeight="1" s="14">
       <c r="A43" s="51" t="n">
@@ -11437,7 +11581,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q43" s="46" t="inlineStr"/>
+      <c r="Q43" s="55" t="inlineStr"/>
     </row>
     <row r="44" ht="132" customHeight="1" s="14">
       <c r="A44" s="50" t="n">
@@ -11516,9 +11660,10 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q44" s="42" t="inlineStr"/>
+      <c r="Q44" s="55" t="inlineStr"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:Q44"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -11700,6 +11845,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
+    <tabColor rgb="008A8578"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
@@ -11713,28 +11859,28 @@
     <col width="46" customWidth="1" style="13" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="14">
-      <c r="A1" s="25" t="inlineStr">
+    <row r="1" ht="30" customHeight="1" s="14">
+      <c r="A1" s="53" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="B1" s="25" t="inlineStr">
+      <c r="B1" s="53" t="inlineStr">
         <is>
           <t>Theme</t>
         </is>
       </c>
-      <c r="C1" s="25" t="inlineStr">
+      <c r="C1" s="53" t="inlineStr">
         <is>
           <t>Goal</t>
         </is>
       </c>
-      <c r="D1" s="25" t="inlineStr">
+      <c r="D1" s="53" t="inlineStr">
         <is>
           <t>Carousel Topics</t>
         </is>
       </c>
-      <c r="E1" s="25" t="inlineStr">
+      <c r="E1" s="53" t="inlineStr">
         <is>
           <t>Reel / Syndication Focus</t>
         </is>
@@ -11849,6 +11995,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E5"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -11858,6 +12005,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
+    <tabColor rgb="008A8578"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
@@ -11871,28 +12019,28 @@
     <col width="20" customWidth="1" style="13" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="14">
-      <c r="A1" s="25" t="inlineStr">
+    <row r="1" ht="30" customHeight="1" s="14">
+      <c r="A1" s="53" t="inlineStr">
         <is>
           <t>Pillar</t>
         </is>
       </c>
-      <c r="B1" s="25" t="inlineStr">
+      <c r="B1" s="53" t="inlineStr">
         <is>
           <t>Share of Posts</t>
         </is>
       </c>
-      <c r="C1" s="25" t="inlineStr">
+      <c r="C1" s="53" t="inlineStr">
         <is>
           <t>What It Is</t>
         </is>
       </c>
-      <c r="D1" s="25" t="inlineStr">
+      <c r="D1" s="53" t="inlineStr">
         <is>
           <t>Formats</t>
         </is>
       </c>
-      <c r="E1" s="25" t="inlineStr">
+      <c r="E1" s="53" t="inlineStr">
         <is>
           <t>Success Metric</t>
         </is>
@@ -12007,6 +12155,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E5"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -12016,6 +12165,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
+    <tabColor rgb="008A8578"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
@@ -12027,18 +12177,18 @@
     <col width="110" customWidth="1" style="13" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="14">
-      <c r="A1" s="25" t="inlineStr">
+    <row r="1" ht="30" customHeight="1" s="14">
+      <c r="A1" s="53" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="B1" s="25" t="inlineStr">
+      <c r="B1" s="53" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" s="25" t="inlineStr">
+      <c r="C1" s="53" t="inlineStr">
         <is>
           <t>Hashtags (copy-paste)</t>
         </is>
@@ -12130,6 +12280,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C6"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -12139,6 +12290,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="008A8578"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -12154,38 +12306,38 @@
     <col width="52" customWidth="1" style="14" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="26" t="inlineStr">
+    <row r="1" ht="30" customHeight="1" s="14">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>File</t>
         </is>
       </c>
-      <c r="B1" s="26" t="inlineStr">
+      <c r="B1" s="52" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="C1" s="26" t="inlineStr">
+      <c r="C1" s="52" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="D1" s="26" t="inlineStr">
+      <c r="D1" s="52" t="inlineStr">
         <is>
           <t>Pair</t>
         </is>
       </c>
-      <c r="E1" s="26" t="inlineStr">
+      <c r="E1" s="52" t="inlineStr">
         <is>
           <t>Consent</t>
         </is>
       </c>
-      <c r="F1" s="26" t="inlineStr">
+      <c r="F1" s="52" t="inlineStr">
         <is>
           <t>Used In</t>
         </is>
       </c>
-      <c r="G1" s="26" t="inlineStr">
+      <c r="G1" s="52" t="inlineStr">
         <is>
           <t>Client Notes</t>
         </is>
@@ -12900,6 +13052,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12907,6 +13060,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
+    <tabColor rgb="008A8578"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
@@ -12920,28 +13074,28 @@
     <col width="45" customWidth="1" style="13" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="14">
-      <c r="A1" s="25" t="inlineStr">
+    <row r="1" ht="30" customHeight="1" s="14">
+      <c r="A1" s="53" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="B1" s="25" t="inlineStr">
+      <c r="B1" s="53" t="inlineStr">
         <is>
           <t>Format</t>
         </is>
       </c>
-      <c r="C1" s="25" t="inlineStr">
+      <c r="C1" s="53" t="inlineStr">
         <is>
           <t>Pillar</t>
         </is>
       </c>
-      <c r="D1" s="25" t="inlineStr">
+      <c r="D1" s="53" t="inlineStr">
         <is>
           <t>Hook</t>
         </is>
       </c>
-      <c r="E1" s="25" t="inlineStr">
+      <c r="E1" s="53" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -13326,6 +13480,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E15"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/strategy/ig-content-strategy.xlsx
+++ b/strategy/ig-content-strategy.xlsx
@@ -8492,7 +8492,7 @@
       </c>
       <c r="O4" s="47" t="inlineStr">
         <is>
-          <t>CRYSTALWEED cannabis / Unsplash</t>
+          <t>Masum Rahimi / Unsplash</t>
         </is>
       </c>
       <c r="P4" s="45" t="inlineStr">
@@ -8808,7 +8808,7 @@
       </c>
       <c r="O8" s="47" t="inlineStr">
         <is>
-          <t>Lina Verovaya / Unsplash</t>
+          <t>Vitaliy Shevchenko / Unsplash</t>
         </is>
       </c>
       <c r="P8" s="45" t="inlineStr">
@@ -9203,7 +9203,7 @@
       </c>
       <c r="O13" s="43" t="inlineStr">
         <is>
-          <t>Calugar Ana Maria / Unsplash</t>
+          <t>Elist Nguyen / Unsplash</t>
         </is>
       </c>
       <c r="P13" s="41" t="inlineStr">
@@ -9440,7 +9440,7 @@
       </c>
       <c r="O16" s="43" t="inlineStr">
         <is>
-          <t>Atikah Akhtar / Unsplash</t>
+          <t>Look Studio / Unsplash</t>
         </is>
       </c>
       <c r="P16" s="41" t="inlineStr">
@@ -9519,7 +9519,7 @@
       </c>
       <c r="O17" s="47" t="inlineStr">
         <is>
-          <t>ONNE Beauty / Unsplash</t>
+          <t>Soheil Kmp / Unsplash</t>
         </is>
       </c>
       <c r="P17" s="45" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="O20" s="43" t="inlineStr">
         <is>
-          <t>engin akyurt / Unsplash</t>
+          <t>Ionela Mat / Unsplash</t>
         </is>
       </c>
       <c r="P20" s="41" t="inlineStr">
@@ -9835,7 +9835,7 @@
       </c>
       <c r="O21" s="47" t="inlineStr">
         <is>
-          <t>Catherine Grimes / Unsplash</t>
+          <t>Neda Vidakovic / Unsplash</t>
         </is>
       </c>
       <c r="P21" s="45" t="inlineStr">
@@ -9914,7 +9914,7 @@
       </c>
       <c r="O22" s="47" t="inlineStr">
         <is>
-          <t>Gabrielle Henderson / Unsplash</t>
+          <t>Vitaliy Shevchenko / Unsplash</t>
         </is>
       </c>
       <c r="P22" s="45" t="inlineStr">
@@ -9993,7 +9993,7 @@
       </c>
       <c r="O23" s="43" t="inlineStr">
         <is>
-          <t>Gabrielle Henderson / Unsplash</t>
+          <t>Soheil Kmp / Unsplash</t>
         </is>
       </c>
       <c r="P23" s="41" t="inlineStr">
@@ -10072,7 +10072,7 @@
       </c>
       <c r="O24" s="47" t="inlineStr">
         <is>
-          <t>ONNE Beauty / Unsplash</t>
+          <t>Masum Rahimi / Unsplash</t>
         </is>
       </c>
       <c r="P24" s="45" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="O28" s="47" t="inlineStr">
         <is>
-          <t>engin akyurt / Unsplash</t>
+          <t>Fleur Kaan / Unsplash</t>
         </is>
       </c>
       <c r="P28" s="45" t="inlineStr">
@@ -10467,7 +10467,7 @@
       </c>
       <c r="O29" s="47" t="inlineStr">
         <is>
-          <t>engin akyurt / Unsplash</t>
+          <t>Fleur Kaan / Unsplash</t>
         </is>
       </c>
       <c r="P29" s="45" t="inlineStr">
@@ -10546,7 +10546,7 @@
       </c>
       <c r="O30" s="43" t="inlineStr">
         <is>
-          <t>Bee Naturalles / Unsplash</t>
+          <t>Wco Global / Unsplash</t>
         </is>
       </c>
       <c r="P30" s="41" t="inlineStr">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="O40" s="47" t="inlineStr">
         <is>
-          <t>Calugar Ana Maria / Unsplash</t>
+          <t>Elist Nguyen / Unsplash</t>
         </is>
       </c>
       <c r="P40" s="45" t="inlineStr">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="O42" s="47" t="inlineStr">
         <is>
-          <t>ONNE Beauty / Unsplash</t>
+          <t>Zac Taheriyan / Unsplash</t>
         </is>
       </c>
       <c r="P42" s="45" t="inlineStr">
@@ -11573,7 +11573,7 @@
       </c>
       <c r="O43" s="47" t="inlineStr">
         <is>
-          <t>Catherine Grimes / Unsplash</t>
+          <t>Zulfugar Karimov / Unsplash</t>
         </is>
       </c>
       <c r="P43" s="45" t="inlineStr">

--- a/strategy/ig-content-strategy.xlsx
+++ b/strategy/ig-content-strategy.xlsx
@@ -18,7 +18,6 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Posting Schedule'!$A$1:$AB$66</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GBP Daily'!$A$1:$Q$44</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Monthly Themes'!$A$1:$E$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Content Pillars'!$A$1:$E$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Hashtag Sets'!$A$1:$C$6</definedName>
@@ -31,9 +30,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="mmm\ d&quot;, &quot;yyyy"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -8154,7 +8154,6 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00C9A85C"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -8180,88 +8179,88 @@
     <col width="28" customWidth="1" style="14" min="17" max="17"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" s="14">
-      <c r="A1" s="52" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="39" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="52" t="inlineStr">
+      <c r="B1" s="39" t="inlineStr">
         <is>
           <t>Day</t>
         </is>
       </c>
-      <c r="C1" s="52" t="inlineStr">
+      <c r="C1" s="39" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="D1" s="52" t="inlineStr">
+      <c r="D1" s="39" t="inlineStr">
         <is>
           <t>Pillar</t>
         </is>
       </c>
-      <c r="E1" s="52" t="inlineStr">
+      <c r="E1" s="39" t="inlineStr">
         <is>
           <t>Post Text (short)</t>
         </is>
       </c>
-      <c r="F1" s="52" t="inlineStr">
+      <c r="F1" s="39" t="inlineStr">
         <is>
           <t>Chars</t>
         </is>
       </c>
-      <c r="G1" s="52" t="inlineStr">
+      <c r="G1" s="39" t="inlineStr">
         <is>
           <t>Description (long, SEO)</t>
         </is>
       </c>
-      <c r="H1" s="52" t="inlineStr">
+      <c r="H1" s="39" t="inlineStr">
         <is>
           <t>Desc Chars</t>
         </is>
       </c>
-      <c r="I1" s="52" t="inlineStr">
+      <c r="I1" s="39" t="inlineStr">
         <is>
           <t>CTA Button</t>
         </is>
       </c>
-      <c r="J1" s="52" t="inlineStr">
+      <c r="J1" s="39" t="inlineStr">
         <is>
           <t>CTA Link</t>
         </is>
       </c>
-      <c r="K1" s="52" t="inlineStr">
+      <c r="K1" s="39" t="inlineStr">
         <is>
           <t>Image File</t>
         </is>
       </c>
-      <c r="L1" s="52" t="inlineStr">
+      <c r="L1" s="39" t="inlineStr">
         <is>
           <t>Open Folder</t>
         </is>
       </c>
-      <c r="M1" s="52" t="inlineStr">
+      <c r="M1" s="39" t="inlineStr">
         <is>
           <t>Open Image</t>
         </is>
       </c>
-      <c r="N1" s="52" t="inlineStr">
+      <c r="N1" s="39" t="inlineStr">
         <is>
           <t>Preview</t>
         </is>
       </c>
-      <c r="O1" s="52" t="inlineStr">
+      <c r="O1" s="39" t="inlineStr">
         <is>
           <t>Photo Credit</t>
         </is>
       </c>
-      <c r="P1" s="52" t="inlineStr">
+      <c r="P1" s="39" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="Q1" s="52" t="inlineStr">
+      <c r="Q1" s="39" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -8343,7 +8342,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q2" s="55" t="inlineStr"/>
+      <c r="Q2" s="42" t="inlineStr"/>
     </row>
     <row r="3" ht="132" customHeight="1" s="14">
       <c r="A3" s="51" t="n">
@@ -8422,7 +8421,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q3" s="55" t="inlineStr"/>
+      <c r="Q3" s="46" t="inlineStr"/>
     </row>
     <row r="4" ht="132" customHeight="1" s="14">
       <c r="A4" s="51" t="n">
@@ -8500,7 +8499,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q4" s="55" t="inlineStr"/>
+      <c r="Q4" s="46" t="inlineStr"/>
     </row>
     <row r="5" ht="132" customHeight="1" s="14">
       <c r="A5" s="51" t="n">
@@ -8579,7 +8578,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q5" s="55" t="inlineStr"/>
+      <c r="Q5" s="46" t="inlineStr"/>
     </row>
     <row r="6" ht="132" customHeight="1" s="14">
       <c r="A6" s="50" t="n">
@@ -8658,7 +8657,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q6" s="55" t="inlineStr"/>
+      <c r="Q6" s="42" t="inlineStr"/>
     </row>
     <row r="7" ht="132" customHeight="1" s="14">
       <c r="A7" s="51" t="n">
@@ -8737,7 +8736,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q7" s="55" t="inlineStr"/>
+      <c r="Q7" s="46" t="inlineStr"/>
     </row>
     <row r="8" ht="132" customHeight="1" s="14">
       <c r="A8" s="51" t="n">
@@ -8816,7 +8815,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q8" s="55" t="inlineStr"/>
+      <c r="Q8" s="46" t="inlineStr"/>
     </row>
     <row r="9" ht="132" customHeight="1" s="14">
       <c r="A9" s="50" t="n">
@@ -8895,7 +8894,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q9" s="55" t="inlineStr"/>
+      <c r="Q9" s="42" t="inlineStr"/>
     </row>
     <row r="10" ht="132" customHeight="1" s="14">
       <c r="A10" s="51" t="n">
@@ -8974,7 +8973,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q10" s="55" t="inlineStr"/>
+      <c r="Q10" s="46" t="inlineStr"/>
     </row>
     <row r="11" ht="132" customHeight="1" s="14">
       <c r="A11" s="51" t="n">
@@ -9053,7 +9052,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q11" s="55" t="inlineStr"/>
+      <c r="Q11" s="46" t="inlineStr"/>
     </row>
     <row r="12" ht="132" customHeight="1" s="14">
       <c r="A12" s="51" t="n">
@@ -9132,7 +9131,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q12" s="55" t="inlineStr"/>
+      <c r="Q12" s="46" t="inlineStr"/>
     </row>
     <row r="13" ht="132" customHeight="1" s="14">
       <c r="A13" s="50" t="n">
@@ -9211,7 +9210,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q13" s="55" t="inlineStr"/>
+      <c r="Q13" s="42" t="inlineStr"/>
     </row>
     <row r="14" ht="132" customHeight="1" s="14">
       <c r="A14" s="51" t="n">
@@ -9290,7 +9289,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q14" s="55" t="inlineStr"/>
+      <c r="Q14" s="46" t="inlineStr"/>
     </row>
     <row r="15" ht="132" customHeight="1" s="14">
       <c r="A15" s="51" t="n">
@@ -9369,7 +9368,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q15" s="55" t="inlineStr"/>
+      <c r="Q15" s="46" t="inlineStr"/>
     </row>
     <row r="16" ht="132" customHeight="1" s="14">
       <c r="A16" s="50" t="n">
@@ -9448,7 +9447,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q16" s="55" t="inlineStr"/>
+      <c r="Q16" s="42" t="inlineStr"/>
     </row>
     <row r="17" ht="132" customHeight="1" s="14">
       <c r="A17" s="51" t="n">
@@ -9527,7 +9526,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q17" s="55" t="inlineStr"/>
+      <c r="Q17" s="46" t="inlineStr"/>
     </row>
     <row r="18" ht="132" customHeight="1" s="14">
       <c r="A18" s="51" t="n">
@@ -9606,7 +9605,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q18" s="55" t="inlineStr"/>
+      <c r="Q18" s="46" t="inlineStr"/>
     </row>
     <row r="19" ht="132" customHeight="1" s="14">
       <c r="A19" s="51" t="n">
@@ -9685,7 +9684,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q19" s="55" t="inlineStr"/>
+      <c r="Q19" s="46" t="inlineStr"/>
     </row>
     <row r="20" ht="132" customHeight="1" s="14">
       <c r="A20" s="50" t="n">
@@ -9764,7 +9763,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q20" s="55" t="inlineStr"/>
+      <c r="Q20" s="42" t="inlineStr"/>
     </row>
     <row r="21" ht="132" customHeight="1" s="14">
       <c r="A21" s="51" t="n">
@@ -9843,7 +9842,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q21" s="55" t="inlineStr"/>
+      <c r="Q21" s="46" t="inlineStr"/>
     </row>
     <row r="22" ht="132" customHeight="1" s="14">
       <c r="A22" s="51" t="n">
@@ -9922,7 +9921,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q22" s="55" t="inlineStr"/>
+      <c r="Q22" s="46" t="inlineStr"/>
     </row>
     <row r="23" ht="132" customHeight="1" s="14">
       <c r="A23" s="50" t="n">
@@ -10001,7 +10000,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q23" s="55" t="inlineStr"/>
+      <c r="Q23" s="42" t="inlineStr"/>
     </row>
     <row r="24" ht="132" customHeight="1" s="14">
       <c r="A24" s="51" t="n">
@@ -10080,7 +10079,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q24" s="55" t="inlineStr"/>
+      <c r="Q24" s="46" t="inlineStr"/>
     </row>
     <row r="25" ht="132" customHeight="1" s="14">
       <c r="A25" s="51" t="n">
@@ -10159,7 +10158,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q25" s="55" t="inlineStr"/>
+      <c r="Q25" s="46" t="inlineStr"/>
     </row>
     <row r="26" ht="132" customHeight="1" s="14">
       <c r="A26" s="51" t="n">
@@ -10238,7 +10237,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q26" s="55" t="inlineStr"/>
+      <c r="Q26" s="46" t="inlineStr"/>
     </row>
     <row r="27" ht="132" customHeight="1" s="14">
       <c r="A27" s="50" t="n">
@@ -10317,7 +10316,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q27" s="55" t="inlineStr"/>
+      <c r="Q27" s="42" t="inlineStr"/>
     </row>
     <row r="28" ht="132" customHeight="1" s="14">
       <c r="A28" s="51" t="n">
@@ -10396,7 +10395,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q28" s="55" t="inlineStr"/>
+      <c r="Q28" s="46" t="inlineStr"/>
     </row>
     <row r="29" ht="132" customHeight="1" s="14">
       <c r="A29" s="51" t="n">
@@ -10475,7 +10474,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q29" s="55" t="inlineStr"/>
+      <c r="Q29" s="46" t="inlineStr"/>
     </row>
     <row r="30" ht="132" customHeight="1" s="14">
       <c r="A30" s="50" t="n">
@@ -10554,7 +10553,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q30" s="55" t="inlineStr"/>
+      <c r="Q30" s="42" t="inlineStr"/>
     </row>
     <row r="31" ht="132" customHeight="1" s="14">
       <c r="A31" s="51" t="n">
@@ -10633,7 +10632,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q31" s="55" t="inlineStr"/>
+      <c r="Q31" s="46" t="inlineStr"/>
     </row>
     <row r="32" ht="132" customHeight="1" s="14">
       <c r="A32" s="51" t="n">
@@ -10712,7 +10711,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q32" s="55" t="inlineStr"/>
+      <c r="Q32" s="46" t="inlineStr"/>
     </row>
     <row r="33" ht="132" customHeight="1" s="14">
       <c r="A33" s="51" t="n">
@@ -10791,7 +10790,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q33" s="55" t="inlineStr"/>
+      <c r="Q33" s="46" t="inlineStr"/>
     </row>
     <row r="34" ht="132" customHeight="1" s="14">
       <c r="A34" s="50" t="n">
@@ -10870,7 +10869,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q34" s="55" t="inlineStr"/>
+      <c r="Q34" s="42" t="inlineStr"/>
     </row>
     <row r="35" ht="132" customHeight="1" s="14">
       <c r="A35" s="51" t="n">
@@ -10949,7 +10948,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q35" s="55" t="inlineStr"/>
+      <c r="Q35" s="46" t="inlineStr"/>
     </row>
     <row r="36" ht="132" customHeight="1" s="14">
       <c r="A36" s="51" t="n">
@@ -11028,7 +11027,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q36" s="55" t="inlineStr"/>
+      <c r="Q36" s="46" t="inlineStr"/>
     </row>
     <row r="37" ht="132" customHeight="1" s="14">
       <c r="A37" s="50" t="n">
@@ -11107,7 +11106,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q37" s="55" t="inlineStr"/>
+      <c r="Q37" s="42" t="inlineStr"/>
     </row>
     <row r="38" ht="132" customHeight="1" s="14">
       <c r="A38" s="51" t="n">
@@ -11186,7 +11185,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q38" s="55" t="inlineStr"/>
+      <c r="Q38" s="46" t="inlineStr"/>
     </row>
     <row r="39" ht="132" customHeight="1" s="14">
       <c r="A39" s="51" t="n">
@@ -11265,7 +11264,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q39" s="55" t="inlineStr"/>
+      <c r="Q39" s="46" t="inlineStr"/>
     </row>
     <row r="40" ht="132" customHeight="1" s="14">
       <c r="A40" s="51" t="n">
@@ -11344,7 +11343,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q40" s="55" t="inlineStr"/>
+      <c r="Q40" s="46" t="inlineStr"/>
     </row>
     <row r="41" ht="132" customHeight="1" s="14">
       <c r="A41" s="50" t="n">
@@ -11423,7 +11422,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q41" s="55" t="inlineStr"/>
+      <c r="Q41" s="42" t="inlineStr"/>
     </row>
     <row r="42" ht="132" customHeight="1" s="14">
       <c r="A42" s="51" t="n">
@@ -11502,7 +11501,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q42" s="55" t="inlineStr"/>
+      <c r="Q42" s="46" t="inlineStr"/>
     </row>
     <row r="43" ht="132" customHeight="1" s="14">
       <c r="A43" s="51" t="n">
@@ -11581,7 +11580,7 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q43" s="55" t="inlineStr"/>
+      <c r="Q43" s="46" t="inlineStr"/>
     </row>
     <row r="44" ht="132" customHeight="1" s="14">
       <c r="A44" s="50" t="n">
@@ -11660,10 +11659,9 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="Q44" s="55" t="inlineStr"/>
+      <c r="Q44" s="42" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q44"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>

--- a/strategy/ig-content-strategy.xlsx
+++ b/strategy/ig-content-strategy.xlsx
@@ -8157,7 +8157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q44"/>
+  <dimension ref="A1:Q75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="14" min="1" max="1"/>
@@ -11455,12 +11455,11 @@
         <is>
           <t>Three to four months for most people, and here are the honest reasons it varies.
 Metabolism plays a part, and people who train hard often find it wears off sooner. Dose matters, since a light preventative dose fades before a fuller corrective one. Muscle strength matters, because a strong frown works through product faster than a light one. And history matters, as people who have treated consistently for years often stretch further between appointments.
-What is not true is that it stops working. If yours seems to be fading faster than it used to, the usual answer is that the dose is no longer right rather than any resistance to the product.
 What is not true is that it stops working. If your Botox seems to be fading faster than it used to, the usual answer is that the dose is no longer right rather than any resistance to the product. Month by month timeline on Instagram.</t>
         </is>
       </c>
       <c r="H42" s="45" t="n">
-        <v>885</v>
+        <v>693</v>
       </c>
       <c r="I42" s="45" t="inlineStr">
         <is>
@@ -11660,6 +11659,2455 @@
         </is>
       </c>
       <c r="Q44" s="42" t="inlineStr"/>
+    </row>
+    <row r="45" ht="132" customHeight="1" s="14">
+      <c r="A45" s="51" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B45" s="45" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C45" s="45" t="inlineStr">
+        <is>
+          <t>IG: Why We Sometimes Say No</t>
+        </is>
+      </c>
+      <c r="D45" s="45" t="inlineStr">
+        <is>
+          <t>Trust &amp; Proof</t>
+        </is>
+      </c>
+      <c r="E45" s="46" t="inlineStr">
+        <is>
+          <t>I have turned people away from filler and had them thank me later. Some faces do not need it, and some do not need it yet. Candidacy is part of the assessment, not a step on the way to a sale. The full post is on Instagram.</t>
+        </is>
+      </c>
+      <c r="F45" s="45" t="n">
+        <v>223</v>
+      </c>
+      <c r="G45" s="46" t="inlineStr">
+        <is>
+          <t>I have turned people away from filler, and they thanked me later.
+Some faces do not need it. Some do not need it yet. And some are asking filler to fix something filler does not fix, usually skin quality or a heavy lower face that needs a different plan entirely. Saying yes to all three is easy. It is also how people end up with a result that never sat right and money spent twice.
+Candidacy is part of the assessment at our Oakville studio, not a step on the way to a sale. If I do not think you will be happy in six months, I will tell you at the consult and it costs you nothing.
+A provider who has never said no to anyone is telling you something. The full post is on Instagram.</t>
+        </is>
+      </c>
+      <c r="H45" s="45" t="n">
+        <v>687</v>
+      </c>
+      <c r="I45" s="45" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="J45" s="47" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="K45" s="45" t="inlineStr">
+        <is>
+          <t>2026-10-01-why-i-say-no.jpg</t>
+        </is>
+      </c>
+      <c r="L45" s="47" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M45" s="47" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="N45" s="45">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-10-01-why-i-say-no.jpg")</f>
+        <v/>
+      </c>
+      <c r="O45" s="47" t="inlineStr">
+        <is>
+          <t>Look Studio / Unsplash</t>
+        </is>
+      </c>
+      <c r="P45" s="45" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="Q45" s="46" t="inlineStr"/>
+    </row>
+    <row r="46" ht="132" customHeight="1" s="14">
+      <c r="A46" s="51" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B46" s="45" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="C46" s="45" t="inlineStr">
+        <is>
+          <t>IG: What I Tell Every First-Timer</t>
+        </is>
+      </c>
+      <c r="D46" s="45" t="inlineStr">
+        <is>
+          <t>Trust &amp; Proof</t>
+        </is>
+      </c>
+      <c r="E46" s="46" t="inlineStr">
+        <is>
+          <t>The same four things I tell every first time filler client. Start smaller than you think, judge it at two weeks, swelling is not your result, and you can always add. Nobody regrets going conservative first. On Instagram.</t>
+        </is>
+      </c>
+      <c r="F46" s="45" t="n">
+        <v>220</v>
+      </c>
+      <c r="G46" s="46" t="inlineStr">
+        <is>
+          <t>Four things I tell every first time filler client in Oakville, before anything is opened.
+Start smaller than you think. A partial syringe is a real option and a good one. Judge it at two weeks, not at day two, because what you see in the first 48 hours is swelling and not your result. Nothing about the first appointment has to be the final answer, since we can add at the review.
+And the last one, which matters most: tell me what you actually want to look like, not which treatment you think you want. The plan is my job. The goal is yours.
+Nobody has ever regretted going conservative on their first syringe. Book a consult, or read the full post on Instagram.</t>
+        </is>
+      </c>
+      <c r="H46" s="45" t="n">
+        <v>667</v>
+      </c>
+      <c r="I46" s="45" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="J46" s="47" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="K46" s="45" t="inlineStr">
+        <is>
+          <t>2026-10-02-every-first-timer.jpg</t>
+        </is>
+      </c>
+      <c r="L46" s="47" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M46" s="47" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="N46" s="45">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-10-02-every-first-timer.jpg")</f>
+        <v/>
+      </c>
+      <c r="O46" s="47" t="inlineStr">
+        <is>
+          <t>karelys Ruiz / Unsplash</t>
+        </is>
+      </c>
+      <c r="P46" s="45" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="Q46" s="46" t="inlineStr"/>
+    </row>
+    <row r="47" ht="132" customHeight="1" s="14">
+      <c r="A47" s="51" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B47" s="45" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="C47" s="45" t="inlineStr">
+        <is>
+          <t>IG: Quote: No Is Protection</t>
+        </is>
+      </c>
+      <c r="D47" s="45" t="inlineStr">
+        <is>
+          <t>Trust &amp; Proof</t>
+        </is>
+      </c>
+      <c r="E47" s="46" t="inlineStr">
+        <is>
+          <t>No is protection. It is the most underrated part of good injecting and the hardest thing to hear from someone you were ready to pay. A provider willing to lose the booking is the one worth booking. More on Instagram.</t>
+        </is>
+      </c>
+      <c r="F47" s="45" t="n">
+        <v>216</v>
+      </c>
+      <c r="G47" s="46" t="inlineStr">
+        <is>
+          <t>No is protection. It is the most underrated part of good injecting.
+It is also the hardest thing to hear from a provider you were already prepared to pay. Nobody arrives at a consult hoping to be told to wait, or to be told the thing they read about is not the thing their face needs. But the alternative is worse, and it is the reason a certain kind of result is recognisable across a room.
+A nurse practitioner willing to lose the booking is the one worth booking. That is the whole of it.
+If you have been told yes to everything you have ever asked for, that is not a compliment to your face. It is information about the person holding the syringe. More on Instagram, or come and ask in Oakville.</t>
+        </is>
+      </c>
+      <c r="H47" s="45" t="n">
+        <v>702</v>
+      </c>
+      <c r="I47" s="45" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="J47" s="47" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="K47" s="45" t="inlineStr">
+        <is>
+          <t>2026-10-03-no-is-protection.jpg</t>
+        </is>
+      </c>
+      <c r="L47" s="47" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M47" s="47" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="N47" s="45">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-10-03-no-is-protection.jpg")</f>
+        <v/>
+      </c>
+      <c r="O47" s="47" t="inlineStr">
+        <is>
+          <t>engin akyurt / Unsplash</t>
+        </is>
+      </c>
+      <c r="P47" s="45" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="Q47" s="46" t="inlineStr"/>
+    </row>
+    <row r="48" ht="132" customHeight="1" s="14">
+      <c r="A48" s="50" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B48" s="41" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="C48" s="41" t="inlineStr">
+        <is>
+          <t>GBP only</t>
+        </is>
+      </c>
+      <c r="D48" s="41" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="E48" s="42" t="inlineStr">
+        <is>
+          <t>The honest answer on filler safety. The fillers I use are hyaluronic acid, which the body already makes and which can be dissolved if a result is not right. Safety comes from the injector, the assessment and the anatomy. More on Instagram.</t>
+        </is>
+      </c>
+      <c r="F48" s="41" t="n">
+        <v>239</v>
+      </c>
+      <c r="G48" s="42" t="inlineStr">
+        <is>
+          <t>The honest answer on filler safety, without the sales gloss.
+The fillers used at the Oakville studio are hyaluronic acid, a substance the body already makes. That matters for one specific reason: it can be dissolved. If a result is not right, or settles unevenly, there is a way back. That is not true of every product on the market, which is exactly why I use these ones.
+The real safety question is not the product, it is the person holding the syringe and whether they know the anatomy underneath. Filler goes near vessels. Placement is the whole job.
+Injections here are done by a nurse practitioner and never delegated. Bring your questions to the consult, including the uncomfortable ones.</t>
+        </is>
+      </c>
+      <c r="H48" s="41" t="n">
+        <v>698</v>
+      </c>
+      <c r="I48" s="41" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="J48" s="43" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="K48" s="41" t="inlineStr">
+        <is>
+          <t>2026-10-04-is-filler-safe.jpg</t>
+        </is>
+      </c>
+      <c r="L48" s="43" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M48" s="43" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="N48" s="41">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-10-04-is-filler-safe.jpg")</f>
+        <v/>
+      </c>
+      <c r="O48" s="43" t="inlineStr">
+        <is>
+          <t>Look Studio / Unsplash</t>
+        </is>
+      </c>
+      <c r="P48" s="41" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="Q48" s="42" t="inlineStr"/>
+    </row>
+    <row r="49" ht="132" customHeight="1" s="14">
+      <c r="A49" s="51" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B49" s="45" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C49" s="45" t="inlineStr">
+        <is>
+          <t>IG: Filler Won't Make You Look Fake</t>
+        </is>
+      </c>
+      <c r="D49" s="45" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="E49" s="46" t="inlineStr">
+        <is>
+          <t>Filler is not what makes a face look fake. Volume in the wrong place, too much at once, and treating one feature while ignoring the rest are what make a face look done. The technique is the variable, not the product. On Instagram.</t>
+        </is>
+      </c>
+      <c r="F49" s="45" t="n">
+        <v>230</v>
+      </c>
+      <c r="G49" s="46" t="inlineStr">
+        <is>
+          <t>Filler does not make a face look fake. Technique does.
+The three things that actually cause it: too much product at one sitting, product placed in the wrong plane or the wrong compartment, and chasing one feature while the rest of the face is ignored. Lips built on a face that has lost midface support will always read as lips first, no matter how carefully they are shaped.
+This is why the assessment looks at the whole face even when you came in asking about one part of it. Balance is the point, and volume is only ever a means to it.
+The results people admire and cannot identify are filler too. You just never got told. See the full carousel on Instagram, or book an assessment in Oakville.</t>
+        </is>
+      </c>
+      <c r="H49" s="45" t="n">
+        <v>699</v>
+      </c>
+      <c r="I49" s="45" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="J49" s="47" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="K49" s="45" t="inlineStr">
+        <is>
+          <t>2026-10-05-fake-is-not-the-filler.jpg</t>
+        </is>
+      </c>
+      <c r="L49" s="47" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M49" s="47" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="N49" s="45">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-10-05-fake-is-not-the-filler.jpg")</f>
+        <v/>
+      </c>
+      <c r="O49" s="47" t="inlineStr">
+        <is>
+          <t>JEaLiFe Pictures / Unsplash</t>
+        </is>
+      </c>
+      <c r="P49" s="45" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="Q49" s="46" t="inlineStr"/>
+    </row>
+    <row r="50" ht="132" customHeight="1" s="14">
+      <c r="A50" s="51" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B50" s="45" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C50" s="45" t="inlineStr">
+        <is>
+          <t>IG: Service Spotlight: Dermal Filler</t>
+        </is>
+      </c>
+      <c r="D50" s="45" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="E50" s="46" t="inlineStr">
+        <is>
+          <t>Dermal filler, plainly. It replaces volume the face has lost or shapes what was always a little short, which is a different job from Botox. Lips, cheeks, chin and jawline, injected by a nurse practitioner in Oakville. See the spotlight on Instagram.</t>
+        </is>
+      </c>
+      <c r="F50" s="45" t="n">
+        <v>249</v>
+      </c>
+      <c r="G50" s="46" t="inlineStr">
+        <is>
+          <t>Dermal filler, explained plainly, because it gets confused with Botox constantly.
+Botox relaxes muscle, so it softens lines that movement creates. Filler adds structure, so it replaces volume the face has lost or shapes what was always a little short. Different problems, different tools, and plenty of faces need neither yet.
+At the Oakville studio I treat lips, cheeks, chin and jawline with hyaluronic acid filler, injected by a nurse practitioner and never delegated to anyone else.
+Most first appointments are one syringe or less. Results are visible immediately, settle over about two weeks, and last somewhere between six and eighteen months depending on the area and how your body handles it. See the spotlight on Instagram.</t>
+        </is>
+      </c>
+      <c r="H50" s="45" t="n">
+        <v>735</v>
+      </c>
+      <c r="I50" s="45" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="J50" s="47" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="K50" s="45" t="inlineStr">
+        <is>
+          <t>2026-10-06-spotlight-dermal-filler.jpg</t>
+        </is>
+      </c>
+      <c r="L50" s="47" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M50" s="47" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="N50" s="45">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-10-06-spotlight-dermal-filler.jpg")</f>
+        <v/>
+      </c>
+      <c r="O50" s="47" t="inlineStr">
+        <is>
+          <t>Elist Nguyen / Unsplash</t>
+        </is>
+      </c>
+      <c r="P50" s="45" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="Q50" s="46" t="inlineStr"/>
+    </row>
+    <row r="51" ht="132" customHeight="1" s="14">
+      <c r="A51" s="50" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B51" s="41" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="C51" s="41" t="inlineStr">
+        <is>
+          <t>GBP only</t>
+        </is>
+      </c>
+      <c r="D51" s="41" t="inlineStr">
+        <is>
+          <t>Trust &amp; Proof</t>
+        </is>
+      </c>
+      <c r="E51" s="42" t="inlineStr">
+        <is>
+          <t>What a filler consult includes at our Oakville studio. A full face assessment, your history and medications, an honest read on candidacy, a plan with an area and an amount, and a price before anything is opened. You can leave without booking.</t>
+        </is>
+      </c>
+      <c r="F51" s="41" t="n">
+        <v>242</v>
+      </c>
+      <c r="G51" s="42" t="inlineStr">
+        <is>
+          <t>What a filler consult includes, before anything is opened.
+We start with what is bothering you, in your words. Then a full face assessment, because the answer is often not where the complaint is. Then your health history and medications, since blood thinners and a few other things change the plan and the bruising risk.
+You leave with an area, an amount, a price and a realistic idea of what it will and will not do. If the honest answer is not yet, or not this, you get that instead, and it costs you nothing.
+No product is opened until you have agreed to the plan and the price. Nobody is talked into anything in this room. The studio is on Preserve Dr in Oakville, with free parking at the door.</t>
+        </is>
+      </c>
+      <c r="H51" s="41" t="n">
+        <v>702</v>
+      </c>
+      <c r="I51" s="41" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="J51" s="43" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="K51" s="41" t="inlineStr">
+        <is>
+          <t>2026-10-07-before-the-syringe.jpg</t>
+        </is>
+      </c>
+      <c r="L51" s="43" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M51" s="43" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="N51" s="41">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-10-07-before-the-syringe.jpg")</f>
+        <v/>
+      </c>
+      <c r="O51" s="43" t="inlineStr">
+        <is>
+          <t>Rosa Rafael / Unsplash</t>
+        </is>
+      </c>
+      <c r="P51" s="41" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="Q51" s="42" t="inlineStr"/>
+    </row>
+    <row r="52" ht="132" customHeight="1" s="14">
+      <c r="A52" s="51" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B52" s="45" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C52" s="45" t="inlineStr">
+        <is>
+          <t>IG: Lip Filler: Natural vs Overdone</t>
+        </is>
+      </c>
+      <c r="D52" s="45" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="E52" s="46" t="inlineStr">
+        <is>
+          <t>Natural versus overdone lips, side by side. The difference is ratio and shape, not the brand of filler. Respect the border, keep the lower fuller than the upper, and stop before it is obvious. Shared with client consent on Instagram.</t>
+        </is>
+      </c>
+      <c r="F52" s="45" t="n">
+        <v>233</v>
+      </c>
+      <c r="G52" s="46" t="inlineStr">
+        <is>
+          <t>Natural or overdone. The difference is ratio and shape, not the product.
+A lip that reads as natural keeps its border, keeps the lower lip fuller than the upper, and keeps the height of the upper lip in proportion to the space above it. A lip that reads as done usually broke one of those three, most often by filling past the border or by adding volume that the lip could not carry.
+Amount matters less than people assume. I have seen a full syringe look untouched and half of one look obvious, and the variable both times was placement.
+The lip filler work worth showing is the kind nobody identifies as work. Real examples, shared with client consent, are on Instagram. Assessments in Oakville.</t>
+        </is>
+      </c>
+      <c r="H52" s="45" t="n">
+        <v>700</v>
+      </c>
+      <c r="I52" s="45" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="J52" s="47" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="K52" s="45" t="inlineStr">
+        <is>
+          <t>2026-10-08-natural-or-overdone.jpg</t>
+        </is>
+      </c>
+      <c r="L52" s="47" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M52" s="47" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="N52" s="45">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-10-08-natural-or-overdone.jpg")</f>
+        <v/>
+      </c>
+      <c r="O52" s="47" t="inlineStr">
+        <is>
+          <t>Fleur Kaan / Unsplash</t>
+        </is>
+      </c>
+      <c r="P52" s="45" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="Q52" s="46" t="inlineStr"/>
+    </row>
+    <row r="53" ht="132" customHeight="1" s="14">
+      <c r="A53" s="51" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B53" s="45" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="C53" s="45" t="inlineStr">
+        <is>
+          <t>IG: Inside the Filler Appointment</t>
+        </is>
+      </c>
+      <c r="D53" s="45" t="inlineStr">
+        <is>
+          <t>Personality &amp; BTS</t>
+        </is>
+      </c>
+      <c r="E53" s="46" t="inlineStr">
+        <is>
+          <t>What a filler appointment actually looks like. Photos, numbing cream for around twenty minutes, mapping while it works, then injecting in small increments with a mirror check as we go. About forty five minutes door to door. On Instagram.</t>
+        </is>
+      </c>
+      <c r="F53" s="45" t="n">
+        <v>237</v>
+      </c>
+      <c r="G53" s="46" t="inlineStr">
+        <is>
+          <t>What a filler appointment actually looks like, start to finish.
+Photos first, because memory is unreliable and you will want the comparison. Numbing cream for about twenty minutes, and I map the face while it works. Then the injecting, done in small increments with a mirror in your hand at the checkpoints, not one long uninterrupted run.
+Most of the appointment is not the needle. Around forty five minutes door to door for a single area, and you leave with ice, aftercare in writing and my number.
+The part people are surprised by is how much talking there is in the middle of it. Adjusting as we go is not indecision, it is how a symmetrical result happens. Come and see the room on Instagram, or book in Oakville.</t>
+        </is>
+      </c>
+      <c r="H53" s="45" t="n">
+        <v>721</v>
+      </c>
+      <c r="I53" s="45" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="J53" s="47" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="K53" s="45" t="inlineStr">
+        <is>
+          <t>2026-10-09-inside-the-appointment.jpg</t>
+        </is>
+      </c>
+      <c r="L53" s="47" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M53" s="47" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="N53" s="45">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-10-09-inside-the-appointment.jpg")</f>
+        <v/>
+      </c>
+      <c r="O53" s="47" t="inlineStr">
+        <is>
+          <t>Anuruddha Lokuhapuarachchi / Unsplash</t>
+        </is>
+      </c>
+      <c r="P53" s="45" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="Q53" s="46" t="inlineStr"/>
+    </row>
+    <row r="54" ht="132" customHeight="1" s="14">
+      <c r="A54" s="51" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B54" s="45" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="C54" s="45" t="inlineStr">
+        <is>
+          <t>IG: Subtle Is the New Dramatic</t>
+        </is>
+      </c>
+      <c r="D54" s="45" t="inlineStr">
+        <is>
+          <t>Trust &amp; Proof</t>
+        </is>
+      </c>
+      <c r="E54" s="46" t="inlineStr">
+        <is>
+          <t>Subtle is not a compromise, it is the goal. If the first thing anyone notices about your face is the filler, something in the plan was wrong. A real result, shared with client consent, is on Instagram.</t>
+        </is>
+      </c>
+      <c r="F54" s="45" t="n">
+        <v>201</v>
+      </c>
+      <c r="G54" s="46" t="inlineStr">
+        <is>
+          <t>Subtle is not a compromise. It is the goal.
+The dramatic result is easy. Anyone can add volume until a change is undeniable. The difficult version is the one where your face looks rested and balanced and nobody can name what changed, which takes restraint, an honest read of proportion, and a willingness to stop early.
+If the first thing people notice about you is your filler, the plan was wrong before the needle came out.
+This is the standard everything at the Oakville studio is held to. Half a syringe placed properly beats a full one placed to be seen, every single time. A real result, shared with the client's consent, is on Instagram. Assessments for lips, cheeks and jawline are booked the same way.</t>
+        </is>
+      </c>
+      <c r="H54" s="45" t="n">
+        <v>713</v>
+      </c>
+      <c r="I54" s="45" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="J54" s="47" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="K54" s="45" t="inlineStr">
+        <is>
+          <t>2026-10-10-subtle-is-the-point.jpg</t>
+        </is>
+      </c>
+      <c r="L54" s="47" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M54" s="47" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="N54" s="45">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-10-10-subtle-is-the-point.jpg")</f>
+        <v/>
+      </c>
+      <c r="O54" s="47" t="inlineStr">
+        <is>
+          <t>Fleur Kaan / Unsplash</t>
+        </is>
+      </c>
+      <c r="P54" s="45" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="Q54" s="46" t="inlineStr"/>
+    </row>
+    <row r="55" ht="132" customHeight="1" s="14">
+      <c r="A55" s="50" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B55" s="41" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="C55" s="41" t="inlineStr">
+        <is>
+          <t>GBP only</t>
+        </is>
+      </c>
+      <c r="D55" s="41" t="inlineStr">
+        <is>
+          <t>Trust &amp; Proof</t>
+        </is>
+      </c>
+      <c r="E55" s="42" t="inlineStr">
+        <is>
+          <t>We are at 3060 Preserve Dr in Oakville, a private studio rather than a clinic floor, with free parking at the door. Clients come from Burlington, Milton and Mississauga for Botox and filler. Appointment only, evenings available.</t>
+        </is>
+      </c>
+      <c r="F55" s="41" t="n">
+        <v>228</v>
+      </c>
+      <c r="G55" s="42" t="inlineStr">
+        <is>
+          <t>A private studio in Oakville, not a clinic floor and not a shopping centre counter.
+We are at 3060 Preserve Dr, with free parking directly outside and no lobby to sit in. Appointments are one at a time, which is why the schedule is by booking only and why nobody is ever rushed through.
+Clients drive in from Burlington, Milton and Mississauga, and a good number from north Oakville who did not know there was anything closer than the QEW.
+Botox, dermal filler, lip filler and cheek filler, all injected by a nurse practitioner. Evening appointments are available for people coming after work, which is most of them. Send a message on Instagram to book, or ask for directions and I will send them.</t>
+        </is>
+      </c>
+      <c r="H55" s="41" t="n">
+        <v>700</v>
+      </c>
+      <c r="I55" s="41" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="J55" s="43" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="K55" s="41" t="inlineStr">
+        <is>
+          <t>2026-10-11-find-the-studio.jpg</t>
+        </is>
+      </c>
+      <c r="L55" s="43" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M55" s="43" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="N55" s="41">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-10-11-find-the-studio.jpg")</f>
+        <v/>
+      </c>
+      <c r="O55" s="43" t="inlineStr">
+        <is>
+          <t>Wco Global / Unsplash</t>
+        </is>
+      </c>
+      <c r="P55" s="41" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="Q55" s="42" t="inlineStr"/>
+    </row>
+    <row r="56" ht="132" customHeight="1" s="14">
+      <c r="A56" s="51" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B56" s="45" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C56" s="45" t="inlineStr">
+        <is>
+          <t>IG: Cheek Filler: The Secret Nobody Talks About</t>
+        </is>
+      </c>
+      <c r="D56" s="45" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="E56" s="46" t="inlineStr">
+        <is>
+          <t>The cheek is the most underrated area on the face. Support the midface and the lower face softens, because half of what looks heavy at the jaw is really volume that dropped from above. Most people ask for the wrong area first. On Instagram.</t>
+        </is>
+      </c>
+      <c r="F56" s="45" t="n">
+        <v>240</v>
+      </c>
+      <c r="G56" s="46" t="inlineStr">
+        <is>
+          <t>Cheeks hold the face up. That is the part nobody talks about.
+When the midface loses volume, the tissue below it has less to sit on, so it settles. That is why the lines at the mouth deepen, why the lower face starts reading heavy, and why treating either one directly often does very little. The problem is above where you are looking.
+Restore midface support and the lower face lifts with it. No filler in the lower face at all, and it still softens.
+This is the most common redirection I make at consults in Oakville. Someone comes in asking about the lines around the mouth and leaves with a plan for cheeks, and it is a smaller amount of product than they expected. The full explanation is on Instagram.</t>
+        </is>
+      </c>
+      <c r="H56" s="45" t="n">
+        <v>711</v>
+      </c>
+      <c r="I56" s="45" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="J56" s="47" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="K56" s="45" t="inlineStr">
+        <is>
+          <t>2026-10-12-cheeks-hold-the-face.jpg</t>
+        </is>
+      </c>
+      <c r="L56" s="47" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M56" s="47" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="N56" s="45">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-10-12-cheeks-hold-the-face.jpg")</f>
+        <v/>
+      </c>
+      <c r="O56" s="47" t="inlineStr">
+        <is>
+          <t>Elist Nguyen / Unsplash</t>
+        </is>
+      </c>
+      <c r="P56" s="45" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="Q56" s="46" t="inlineStr"/>
+    </row>
+    <row r="57" ht="132" customHeight="1" s="14">
+      <c r="A57" s="51" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B57" s="45" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C57" s="45" t="inlineStr">
+        <is>
+          <t>IG: Service Spotlight: Cheek Filler</t>
+        </is>
+      </c>
+      <c r="D57" s="45" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="E57" s="46" t="inlineStr">
+        <is>
+          <t>Cheek filler in Oakville, explained. Placed deep for structure rather than fullness, it restores the support the midface has lost. Usually one syringe, results visible immediately, settled by two weeks, lasting twelve to eighteen months. On Instagram.</t>
+        </is>
+      </c>
+      <c r="F57" s="45" t="n">
+        <v>251</v>
+      </c>
+      <c r="G57" s="46" t="inlineStr">
+        <is>
+          <t>Cheek filler is structure, not volume. That distinction is the entire treatment.
+Placed deep, on bone, it restores the support the midface lost rather than sitting shallow and making a face look fuller. Done well it reads as looking rested and slightly lifted. Done shallow or done too much, it reads as cheeks, which is the version everyone has seen and nobody wants.
+Most cheek appointments at the Oakville studio are one syringe, sometimes split across two visits so we can assess in between.
+Results are visible the same day, settle over about two weeks, and typically last twelve to eighteen months, longer than lips because the area moves less. Injected by a nurse practitioner. See the spotlight on Instagram.</t>
+        </is>
+      </c>
+      <c r="H57" s="45" t="n">
+        <v>719</v>
+      </c>
+      <c r="I57" s="45" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="J57" s="47" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="K57" s="45" t="inlineStr">
+        <is>
+          <t>2026-10-13-spotlight-cheek-filler.jpg</t>
+        </is>
+      </c>
+      <c r="L57" s="47" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M57" s="47" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="N57" s="45">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-10-13-spotlight-cheek-filler.jpg")</f>
+        <v/>
+      </c>
+      <c r="O57" s="47" t="inlineStr">
+        <is>
+          <t>Zac Taheriyan / Unsplash</t>
+        </is>
+      </c>
+      <c r="P57" s="45" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="Q57" s="46" t="inlineStr"/>
+    </row>
+    <row r="58" ht="132" customHeight="1" s="14">
+      <c r="A58" s="50" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B58" s="41" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="C58" s="41" t="inlineStr">
+        <is>
+          <t>GBP only</t>
+        </is>
+      </c>
+      <c r="D58" s="41" t="inlineStr">
+        <is>
+          <t>Trust &amp; Proof</t>
+        </is>
+      </c>
+      <c r="E58" s="42" t="inlineStr">
+        <is>
+          <t>Filler is not right for everyone, and not right for everyone today. Pregnancy and breastfeeding, an active skin infection at the site, certain medications and an event too close to the date are all reasons I will ask you to wait. Ask at the consult.</t>
+        </is>
+      </c>
+      <c r="F58" s="41" t="n">
+        <v>249</v>
+      </c>
+      <c r="G58" s="42" t="inlineStr">
+        <is>
+          <t>Filler is not right for everyone, and not right for everyone today.
+The clear ones: pregnancy and breastfeeding, an active skin infection or breakout at the injection site, and a recent dental procedure, which we sit out for two weeks in either direction. Some medications change the plan rather than cancel it, blood thinners in particular, so bring your full list to the consult.
+Timing is the one people fight me on. A wedding in ten days is not the week to start, because bruising and swelling need room.
+The other reason to wait is simply that your face does not need it yet, which is a real answer and one I give often at the Oakville studio. Ask me directly and you will get a direct answer.</t>
+        </is>
+      </c>
+      <c r="H58" s="41" t="n">
+        <v>701</v>
+      </c>
+      <c r="I58" s="41" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="J58" s="43" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="K58" s="41" t="inlineStr">
+        <is>
+          <t>2026-10-14-not-everyone-is-a-candidate.jpg</t>
+        </is>
+      </c>
+      <c r="L58" s="43" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M58" s="43" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="N58" s="41">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-10-14-not-everyone-is-a-candidate.jpg")</f>
+        <v/>
+      </c>
+      <c r="O58" s="43" t="inlineStr">
+        <is>
+          <t>Masum Rahimi / Unsplash</t>
+        </is>
+      </c>
+      <c r="P58" s="41" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="Q58" s="42" t="inlineStr"/>
+    </row>
+    <row r="59" ht="132" customHeight="1" s="14">
+      <c r="A59" s="51" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B59" s="45" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C59" s="45" t="inlineStr">
+        <is>
+          <t>IG: Real Lips. Real Results.</t>
+        </is>
+      </c>
+      <c r="D59" s="45" t="inlineStr">
+        <is>
+          <t>Trust &amp; Proof</t>
+        </is>
+      </c>
+      <c r="E59" s="46" t="inlineStr">
+        <is>
+          <t>Real lip filler results from the Oakville studio, shared with written client consent. Same lighting, same angle, no filter, no smoothing. Some are half a syringe. This is what the work actually looks like. On Instagram.</t>
+        </is>
+      </c>
+      <c r="F59" s="45" t="n">
+        <v>219</v>
+      </c>
+      <c r="G59" s="46" t="inlineStr">
+        <is>
+          <t>Real lips, real results, shared with written client consent.
+Every comparison is the same lighting, the same angle and the same distance, with no filter and no smoothing. That is a low bar and it should be standard, but it is not, which is why the change in some of these will look smaller than what you see elsewhere. Smaller is the point.
+A few of these are half a syringe. One is a correction of somebody else's work, and that is labelled, because it is a different job with a different starting point.
+If you want to know what lip filler in Oakville actually looks like on ordinary faces rather than on a screen, this is the honest version. The full set is on Instagram, and consultations are booked from there.</t>
+        </is>
+      </c>
+      <c r="H59" s="45" t="n">
+        <v>718</v>
+      </c>
+      <c r="I59" s="45" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="J59" s="47" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="K59" s="45" t="inlineStr">
+        <is>
+          <t>2026-10-15-real-lips-real-results.jpg</t>
+        </is>
+      </c>
+      <c r="L59" s="47" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M59" s="47" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="N59" s="45">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-10-15-real-lips-real-results.jpg")</f>
+        <v/>
+      </c>
+      <c r="O59" s="47" t="inlineStr">
+        <is>
+          <t>Vitaliy Shevchenko / Unsplash</t>
+        </is>
+      </c>
+      <c r="P59" s="45" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="Q59" s="46" t="inlineStr"/>
+    </row>
+    <row r="60" ht="132" customHeight="1" s="14">
+      <c r="A60" s="51" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B60" s="45" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="C60" s="45" t="inlineStr">
+        <is>
+          <t>IG: Facial Balancing 101</t>
+        </is>
+      </c>
+      <c r="D60" s="45" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="E60" s="46" t="inlineStr">
+        <is>
+          <t>Facial balancing, in one post. It treats the relationship between features rather than the one feature that bothers you. A chin that is slightly short changes how the lips read, so treating the lips alone would have chased the wrong thing. On Instagram.</t>
+        </is>
+      </c>
+      <c r="F60" s="45" t="n">
+        <v>253</v>
+      </c>
+      <c r="G60" s="46" t="inlineStr">
+        <is>
+          <t>Facial balancing treats proportion, not the feature you came in about.
+Here is the version that makes it click. A chin that sits slightly short makes the lower lip look like it is projecting further than it is, so someone comes in asking to have their upper lip built to match. Do that and you have made both problems worse. Support the chin and the lips read as balanced without touching them.
+The same logic runs through the midface, the jawline and the temples. Features are read against each other, never on their own.
+This is why a consult in Oakville looks at the whole face even when your question is about one part of it, and why the plan is often a smaller amount of product in a different place. The full explanation is on Instagram.</t>
+        </is>
+      </c>
+      <c r="H60" s="45" t="n">
+        <v>746</v>
+      </c>
+      <c r="I60" s="45" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="J60" s="47" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="K60" s="45" t="inlineStr">
+        <is>
+          <t>2026-10-16-facial-balancing-101.jpg</t>
+        </is>
+      </c>
+      <c r="L60" s="47" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M60" s="47" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="N60" s="45">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-10-16-facial-balancing-101.jpg")</f>
+        <v/>
+      </c>
+      <c r="O60" s="47" t="inlineStr">
+        <is>
+          <t>Masum Rahimi / Unsplash</t>
+        </is>
+      </c>
+      <c r="P60" s="45" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="Q60" s="46" t="inlineStr"/>
+    </row>
+    <row r="61" ht="132" customHeight="1" s="14">
+      <c r="A61" s="51" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B61" s="45" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="C61" s="45" t="inlineStr">
+        <is>
+          <t>IG: FAQ: How Much Filler Do I Need?</t>
+        </is>
+      </c>
+      <c r="D61" s="45" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="E61" s="46" t="inlineStr">
+        <is>
+          <t>How much filler do you need? Usually less than you think. One syringe is roughly a fifth of a teaspoon, and for lips that is often a full result or more than one appointment needs. Half syringes are a real option here. Details on Instagram.</t>
+        </is>
+      </c>
+      <c r="F61" s="45" t="n">
+        <v>240</v>
+      </c>
+      <c r="G61" s="46" t="inlineStr">
+        <is>
+          <t>How much filler do I need? Almost always less than you think.
+One syringe is about a millilitre, which is roughly a fifth of a teaspoon. On lips that is frequently a complete result, and for a first appointment half of one is often the better call. Cheeks usually take a full syringe per side over time, though rarely all at once. Chin and jawline sit somewhere in between.
+The number that matters is not how many syringes, it is how much your face can carry before it stops looking like your face.
+At the Oakville studio I would rather you come back in a month and add than sit with too much for the next year. Filler dissolves, but waiting it out is nobody's idea of a good outcome. Ask at the consult, or read the FAQ on Instagram.</t>
+        </is>
+      </c>
+      <c r="H61" s="45" t="n">
+        <v>737</v>
+      </c>
+      <c r="I61" s="45" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="J61" s="47" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="K61" s="45" t="inlineStr">
+        <is>
+          <t>2026-10-17-how-much-do-i-need.jpg</t>
+        </is>
+      </c>
+      <c r="L61" s="47" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M61" s="47" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="N61" s="45">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-10-17-how-much-do-i-need.jpg")</f>
+        <v/>
+      </c>
+      <c r="O61" s="47" t="inlineStr">
+        <is>
+          <t>Victor Meza / Unsplash</t>
+        </is>
+      </c>
+      <c r="P61" s="45" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="Q61" s="46" t="inlineStr"/>
+    </row>
+    <row r="62" ht="132" customHeight="1" s="14">
+      <c r="A62" s="50" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B62" s="41" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="C62" s="41" t="inlineStr">
+        <is>
+          <t>GBP only</t>
+        </is>
+      </c>
+      <c r="D62" s="41" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="E62" s="42" t="inlineStr">
+        <is>
+          <t>How to arrive for filler. Eat beforehand, skip alcohol for 24 hours, hold fish oil and ibuprofen if your doctor allows, come with a clean face and leave the evening plans open. Small things, and they change how the next two days go.</t>
+        </is>
+      </c>
+      <c r="F62" s="41" t="n">
+        <v>232</v>
+      </c>
+      <c r="G62" s="42" t="inlineStr">
+        <is>
+          <t>How to arrive for a filler appointment, so the next two days go easier.
+Eat first. People who come in on an empty stomach are the ones who feel lightheaded. Skip alcohol for the 24 hours before, since it thins the blood and bruising follows. If your own doctor is fine with it, hold fish oil, high dose vitamin E and ibuprofen for a few days beforehand, and never stop a prescribed blood thinner without asking them.
+Come with a clean face. Makeup goes off before we start anyway, so save yourself the step.
+And leave the evening open. You will look swollen, possibly uneven, and that is the treatment working rather than the result. Appointments at the Oakville studio run about forty five minutes, including numbing.</t>
+        </is>
+      </c>
+      <c r="H62" s="41" t="n">
+        <v>721</v>
+      </c>
+      <c r="I62" s="41" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="J62" s="43" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="K62" s="41" t="inlineStr">
+        <is>
+          <t>2026-10-18-on-the-day-itself.jpg</t>
+        </is>
+      </c>
+      <c r="L62" s="43" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M62" s="43" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="N62" s="41">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-10-18-on-the-day-itself.jpg")</f>
+        <v/>
+      </c>
+      <c r="O62" s="43" t="inlineStr">
+        <is>
+          <t>Christin Hume / Unsplash</t>
+        </is>
+      </c>
+      <c r="P62" s="41" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="Q62" s="42" t="inlineStr"/>
+    </row>
+    <row r="63" ht="132" customHeight="1" s="14">
+      <c r="A63" s="51" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B63" s="45" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C63" s="45" t="inlineStr">
+        <is>
+          <t>IG: Filler Dissolves. Here Is the Real Timeline.</t>
+        </is>
+      </c>
+      <c r="D63" s="45" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="E63" s="46" t="inlineStr">
+        <is>
+          <t>Filler is not permanent. Lips run six to twelve months, cheeks and jawline twelve to eighteen, because areas that move more break product down faster. And hyaluronic acid can be dissolved deliberately if a result is wrong. On Instagram.</t>
+        </is>
+      </c>
+      <c r="F63" s="45" t="n">
+        <v>236</v>
+      </c>
+      <c r="G63" s="46" t="inlineStr">
+        <is>
+          <t>Filler dissolves. Here is the real timeline, area by area.
+Lips run about six to twelve months, because the mouth never stops moving and movement breaks product down. Cheeks and jawline run twelve to eighteen for the opposite reason. Chin sits near the longer end. Your metabolism moves all of those numbers, and people who train hard usually sit at the short end of every range.
+What does not happen is filler disappearing overnight. It softens gradually, which is why people think it lasted longer than it did.
+And the part that should be said more often: hyaluronic acid filler can be dissolved deliberately, in one appointment, if a result is not right. That is not a hypothetical safety net, it is a treatment I actually perform in Oakville. Full timeline on Instagram.</t>
+        </is>
+      </c>
+      <c r="H63" s="45" t="n">
+        <v>777</v>
+      </c>
+      <c r="I63" s="45" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="J63" s="47" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="K63" s="45" t="inlineStr">
+        <is>
+          <t>2026-10-19-it-dissolves.jpg</t>
+        </is>
+      </c>
+      <c r="L63" s="47" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M63" s="47" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="N63" s="45">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-10-19-it-dissolves.jpg")</f>
+        <v/>
+      </c>
+      <c r="O63" s="47" t="inlineStr">
+        <is>
+          <t>Alef Morais / Unsplash</t>
+        </is>
+      </c>
+      <c r="P63" s="45" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="Q63" s="46" t="inlineStr"/>
+    </row>
+    <row r="64" ht="132" customHeight="1" s="14">
+      <c r="A64" s="51" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B64" s="45" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C64" s="45" t="inlineStr">
+        <is>
+          <t>IG: The Filler Timeline</t>
+        </is>
+      </c>
+      <c r="D64" s="45" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="E64" s="46" t="inlineStr">
+        <is>
+          <t>Day by day after lip filler. Day one is swollen and firm, day two is often the peak, by day three it is settling, bruising clears through week one, and two weeks is your actual result. Judge it then, not before. On Instagram.</t>
+        </is>
+      </c>
+      <c r="F64" s="45" t="n">
+        <v>225</v>
+      </c>
+      <c r="G64" s="46" t="inlineStr">
+        <is>
+          <t>Day one swollen. Day three settling. Two weeks is your result.
+Day one, expect firm and larger than the final shape, sometimes noticeably uneven. Day two is the swelling peak for most people, which is the day everybody messages me. Day three it begins to come down and starts to look like a lip again. Any bruising surfaces and clears through the first week.
+Week two is when the product has fully integrated and the shape is real. That is the only fair point to judge it, and the point at which we review.
+The day two panic is the single most common message I get after lip filler in Oakville, and it is almost never a problem. Save the timeline from Instagram so you have it on your phone when you need it.</t>
+        </is>
+      </c>
+      <c r="H64" s="45" t="n">
+        <v>711</v>
+      </c>
+      <c r="I64" s="45" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="J64" s="47" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="K64" s="45" t="inlineStr">
+        <is>
+          <t>2026-10-20-the-filler-timeline.jpg</t>
+        </is>
+      </c>
+      <c r="L64" s="47" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M64" s="47" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="N64" s="45">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-10-20-the-filler-timeline.jpg")</f>
+        <v/>
+      </c>
+      <c r="O64" s="47" t="inlineStr">
+        <is>
+          <t>Zulfugar Karimov / Unsplash</t>
+        </is>
+      </c>
+      <c r="P64" s="45" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="Q64" s="46" t="inlineStr"/>
+    </row>
+    <row r="65" ht="132" customHeight="1" s="14">
+      <c r="A65" s="50" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B65" s="41" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="C65" s="41" t="inlineStr">
+        <is>
+          <t>GBP only</t>
+        </is>
+      </c>
+      <c r="D65" s="41" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="E65" s="42" t="inlineStr">
+        <is>
+          <t>Will filler bruise? Sometimes, and it is not a sign anything went wrong. Lips bruise most because the tissue is vascular. Skip alcohol beforehand, hold blood thinning supplements if your doctor agrees, ice after, and expect it clear within a week.</t>
+        </is>
+      </c>
+      <c r="F65" s="41" t="n">
+        <v>247</v>
+      </c>
+      <c r="G65" s="42" t="inlineStr">
+        <is>
+          <t>Will I bruise? Sometimes, and it does not mean anything went wrong.
+Filler is placed in tissue that has blood vessels running through it, and lips have more of them than anywhere else I treat. A needle can meet one. Careful technique lowers the odds and no technique removes them, which is why I will not promise you a bruise free appointment.
+What helps: no alcohol for 24 hours beforehand, holding fish oil, vitamin E and ibuprofen for a few days if your own doctor agrees, ice afterwards, and arnica if you like it.
+Most bruising is small, most of it is coverable with makeup after 24 hours, and nearly all of it is gone inside a week. Book with a week of room before anything you care about, and you will never have to think about it.</t>
+        </is>
+      </c>
+      <c r="H65" s="41" t="n">
+        <v>741</v>
+      </c>
+      <c r="I65" s="41" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="J65" s="43" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="K65" s="41" t="inlineStr">
+        <is>
+          <t>2026-10-21-will-i-bruise.jpg</t>
+        </is>
+      </c>
+      <c r="L65" s="43" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M65" s="43" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="N65" s="41">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-10-21-will-i-bruise.jpg")</f>
+        <v/>
+      </c>
+      <c r="O65" s="43" t="inlineStr">
+        <is>
+          <t>Neda Vidakovic / Unsplash</t>
+        </is>
+      </c>
+      <c r="P65" s="41" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="Q65" s="42" t="inlineStr"/>
+    </row>
+    <row r="66" ht="132" customHeight="1" s="14">
+      <c r="A66" s="51" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B66" s="45" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C66" s="45" t="inlineStr">
+        <is>
+          <t>IG: Lip Filler Aftercare: Your First Week</t>
+        </is>
+      </c>
+      <c r="D66" s="45" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="E66" s="46" t="inlineStr">
+        <is>
+          <t>Lip filler aftercare for the first week. Ice on and off for the first day, sleep propped up, no gym, sauna or hot yoga for 48 hours, no pressing or massaging unless I asked you to, and keep the water up. Save the post on Instagram.</t>
+        </is>
+      </c>
+      <c r="F66" s="45" t="n">
+        <v>231</v>
+      </c>
+      <c r="G66" s="46" t="inlineStr">
+        <is>
+          <t>Your first week after lip filler, in the order it matters.
+First 48 hours: ice on and off, sleep propped up on an extra pillow, and skip the gym, sauna and hot yoga because heat and blood flow both make swelling worse. Do not press, pinch or massage the lips unless I have specifically told you to. No dental work, and hold off on flying if you can.
+Drink more water than usual. Hyaluronic acid draws water, and dehydrated lips feel tighter and look flatter.
+After 48 hours you are essentially back to normal. Small lumps in the first week are common and usually resolve on their own, but message me rather than sitting and worrying about it. Every client at the Oakville studio leaves with this in writing and my number. Save it from Instagram.</t>
+        </is>
+      </c>
+      <c r="H66" s="45" t="n">
+        <v>748</v>
+      </c>
+      <c r="I66" s="45" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="J66" s="47" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="K66" s="45" t="inlineStr">
+        <is>
+          <t>2026-10-22-the-first-week.jpg</t>
+        </is>
+      </c>
+      <c r="L66" s="47" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M66" s="47" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="N66" s="45">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-10-22-the-first-week.jpg")</f>
+        <v/>
+      </c>
+      <c r="O66" s="47" t="inlineStr">
+        <is>
+          <t>Soheil Kmp / Unsplash</t>
+        </is>
+      </c>
+      <c r="P66" s="45" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="Q66" s="46" t="inlineStr"/>
+    </row>
+    <row r="67" ht="132" customHeight="1" s="14">
+      <c r="A67" s="51" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B67" s="45" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="C67" s="45" t="inlineStr">
+        <is>
+          <t>IG: Aftercare Essentials</t>
+        </is>
+      </c>
+      <c r="D67" s="45" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="E67" s="46" t="inlineStr">
+        <is>
+          <t>The whole filler aftercare list on one card. Ice, water, an extra pillow, no heat or hard exercise for 48 hours, no pressing at it, and no judging the result before two weeks. Save it to your phone. On Instagram.</t>
+        </is>
+      </c>
+      <c r="F67" s="45" t="n">
+        <v>212</v>
+      </c>
+      <c r="G67" s="46" t="inlineStr">
+        <is>
+          <t>The entire filler aftercare list, on one card, because it really is short.
+Ice on and off for the first day. Water, more than you think. An extra pillow for two nights. No gym, sauna or hot yoga for 48 hours. No pressing, pinching or massaging the area. No judging the result until two weeks, which is the rule people break most.
+That is the list. Everything else you have read online is either a variation on those six or somebody selling you something.
+Every client at the Oakville studio leaves with this in writing and a way to reach me directly, because the reassuring answer at 9pm on day two is worth more than any leaflet. Save the card from Instagram so it is on your phone when you need it.</t>
+        </is>
+      </c>
+      <c r="H67" s="45" t="n">
+        <v>703</v>
+      </c>
+      <c r="I67" s="45" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="J67" s="47" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="K67" s="45" t="inlineStr">
+        <is>
+          <t>2026-10-23-aftercare-essentials.jpg</t>
+        </is>
+      </c>
+      <c r="L67" s="47" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M67" s="47" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="N67" s="45">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-10-23-aftercare-essentials.jpg")</f>
+        <v/>
+      </c>
+      <c r="O67" s="47" t="inlineStr">
+        <is>
+          <t>Rosa Rafael / Unsplash</t>
+        </is>
+      </c>
+      <c r="P67" s="45" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="Q67" s="46" t="inlineStr"/>
+    </row>
+    <row r="68" ht="132" customHeight="1" s="14">
+      <c r="A68" s="51" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B68" s="45" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="C68" s="45" t="inlineStr">
+        <is>
+          <t>IG: Client Words: The Lip Glow-Up</t>
+        </is>
+      </c>
+      <c r="D68" s="45" t="inlineStr">
+        <is>
+          <t>Trust &amp; Proof</t>
+        </is>
+      </c>
+      <c r="E68" s="46" t="inlineStr">
+        <is>
+          <t>In her words, shared with consent: she wanted lips that looked like hers on a good day, and nobody at work has asked what she had done. That is the brief, met. Her result is on Instagram beside it.</t>
+        </is>
+      </c>
+      <c r="F68" s="45" t="n">
+        <v>197</v>
+      </c>
+      <c r="G68" s="46" t="inlineStr">
+        <is>
+          <t>Her words, not mine, shared with her written consent.
+What she asked for was lips that looked like hers on a good day. Not bigger, not a shape she had saved from someone else. She had talked herself out of it twice, both times because of results she had seen on other people and did not want.
+We used less than one syringe, in a single appointment, and reviewed at two weeks.
+The line from her review that I keep thinking about: nobody at work has asked what she had done, and two people have asked if she has been sleeping better. That is the brief, met exactly. Her result is posted beside her words on Instagram, with permission. Lip filler consultations in Oakville are booked from there.</t>
+        </is>
+      </c>
+      <c r="H68" s="45" t="n">
+        <v>695</v>
+      </c>
+      <c r="I68" s="45" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="J68" s="47" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="K68" s="45" t="inlineStr">
+        <is>
+          <t>2026-10-24-client-words-lips.jpg</t>
+        </is>
+      </c>
+      <c r="L68" s="47" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M68" s="47" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="N68" s="45">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-10-24-client-words-lips.jpg")</f>
+        <v/>
+      </c>
+      <c r="O68" s="47" t="inlineStr">
+        <is>
+          <t>Elist Nguyen / Unsplash</t>
+        </is>
+      </c>
+      <c r="P68" s="45" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="Q68" s="46" t="inlineStr"/>
+    </row>
+    <row r="69" ht="132" customHeight="1" s="14">
+      <c r="A69" s="50" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B69" s="41" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="C69" s="41" t="inlineStr">
+        <is>
+          <t>GBP only</t>
+        </is>
+      </c>
+      <c r="D69" s="41" t="inlineStr">
+        <is>
+          <t>Trust &amp; Proof</t>
+        </is>
+      </c>
+      <c r="E69" s="42" t="inlineStr">
+        <is>
+          <t>Booking is straightforward. Send a message on Instagram with what is bothering you and roughly when suits, and we start with a consult. Evenings available. Appointment only, at 3060 Preserve Dr, Oakville, with free parking at the door.</t>
+        </is>
+      </c>
+      <c r="F69" s="41" t="n">
+        <v>235</v>
+      </c>
+      <c r="G69" s="42" t="inlineStr">
+        <is>
+          <t>Booking at the Oakville studio is straightforward, and it starts with a conversation.
+Send a message on Instagram with what is bothering you and roughly when suits. You do not need to know which treatment you want, and you do not need the vocabulary. Describing it in your own words is genuinely enough, and often more useful.
+Every new client starts with a consult, which can be the same visit as treatment if you are a clear candidate and comfortable going ahead.
+We are appointment only at 3060 Preserve Dr, with free parking at the door and evening slots for people coming after work. Clients travel in from Burlington, Milton and Mississauga. Botox, lip filler, cheek filler and jawline, all injected by a nurse practitioner.</t>
+        </is>
+      </c>
+      <c r="H69" s="41" t="n">
+        <v>733</v>
+      </c>
+      <c r="I69" s="41" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="J69" s="43" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="K69" s="41" t="inlineStr">
+        <is>
+          <t>2026-10-25-how-to-book-filler.jpg</t>
+        </is>
+      </c>
+      <c r="L69" s="43" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M69" s="43" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="N69" s="41">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-10-25-how-to-book-filler.jpg")</f>
+        <v/>
+      </c>
+      <c r="O69" s="43" t="inlineStr">
+        <is>
+          <t>Look Studio / Unsplash</t>
+        </is>
+      </c>
+      <c r="P69" s="41" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="Q69" s="42" t="inlineStr"/>
+    </row>
+    <row r="70" ht="132" customHeight="1" s="14">
+      <c r="A70" s="51" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B70" s="45" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C70" s="45" t="inlineStr">
+        <is>
+          <t>IG: 5 Filler Lies You Still Believe</t>
+        </is>
+      </c>
+      <c r="D70" s="45" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="E70" s="46" t="inlineStr">
+        <is>
+          <t>Five filler lies, taken apart. It does not migrate on its own, it does not stretch your skin, it is not permanent, you are not committed for life, and one syringe is not a dramatic change. Every one of them has a real answer. On Instagram.</t>
+        </is>
+      </c>
+      <c r="F70" s="45" t="n">
+        <v>239</v>
+      </c>
+      <c r="G70" s="46" t="inlineStr">
+        <is>
+          <t>Five things people still believe about filler, and what is actually true.
+It migrates on its own. It does not. Migration is overfilling or misplacement, and it is a technique problem, not a property of the product. It stretches your skin permanently. There is no good evidence for that at the volumes used properly. It is permanent. Hyaluronic acid filler is not, and it can be dissolved on purpose.
+Once you start you cannot stop. You can stop whenever you like, and your face returns to where it would have been.
+And the fifth, which is the most expensive one: that one syringe is a dramatic change. It is about a fifth of a teaspoon. All five taken apart properly on Instagram, or ask me directly at a consult in Oakville.</t>
+        </is>
+      </c>
+      <c r="H70" s="45" t="n">
+        <v>728</v>
+      </c>
+      <c r="I70" s="45" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="J70" s="47" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="K70" s="45" t="inlineStr">
+        <is>
+          <t>2026-10-26-five-filler-lies.jpg</t>
+        </is>
+      </c>
+      <c r="L70" s="47" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M70" s="47" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="N70" s="45">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-10-26-five-filler-lies.jpg")</f>
+        <v/>
+      </c>
+      <c r="O70" s="47" t="inlineStr">
+        <is>
+          <t>karelys Ruiz / Unsplash</t>
+        </is>
+      </c>
+      <c r="P70" s="45" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="Q70" s="46" t="inlineStr"/>
+    </row>
+    <row r="71" ht="132" customHeight="1" s="14">
+      <c r="A71" s="51" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B71" s="45" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C71" s="45" t="inlineStr">
+        <is>
+          <t>IG: Myth vs Truth: Filler Edition</t>
+        </is>
+      </c>
+      <c r="D71" s="45" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="E71" s="46" t="inlineStr">
+        <is>
+          <t>Myth versus truth, filler edition. Six claims side by side, with the real answer next to each one. If you have been putting off asking because of something you read, one of these is probably it. On Instagram.</t>
+        </is>
+      </c>
+      <c r="F71" s="45" t="n">
+        <v>208</v>
+      </c>
+      <c r="G71" s="46" t="inlineStr">
+        <is>
+          <t>Myth on one side, truth on the other, six of them.
+These are the six I hear most often at consults in Oakville, and they have a pattern. Every one of them started with somebody seeing a bad result and concluding that the treatment does that, rather than that the injector did that. Bad filler is loud and visible. Good filler is invisible by design, so it never gets counted.
+That asymmetry is the whole reason this misinformation survives.
+If you have been putting off asking a question because of something you read, there is a decent chance it is on this card with the real answer beside it. And if it is not, message me and I will answer it directly rather than sending you a leaflet. The card is on Instagram.</t>
+        </is>
+      </c>
+      <c r="H71" s="45" t="n">
+        <v>717</v>
+      </c>
+      <c r="I71" s="45" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="J71" s="47" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="K71" s="45" t="inlineStr">
+        <is>
+          <t>2026-10-27-myth-vs-truth-filler.jpg</t>
+        </is>
+      </c>
+      <c r="L71" s="47" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M71" s="47" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="N71" s="45">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-10-27-myth-vs-truth-filler.jpg")</f>
+        <v/>
+      </c>
+      <c r="O71" s="47" t="inlineStr">
+        <is>
+          <t>Ionela Mat / Unsplash</t>
+        </is>
+      </c>
+      <c r="P71" s="45" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="Q71" s="46" t="inlineStr"/>
+    </row>
+    <row r="72" ht="132" customHeight="1" s="14">
+      <c r="A72" s="50" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B72" s="41" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="C72" s="41" t="inlineStr">
+        <is>
+          <t>GBP only</t>
+        </is>
+      </c>
+      <c r="D72" s="41" t="inlineStr">
+        <is>
+          <t>Trust &amp; Proof</t>
+        </is>
+      </c>
+      <c r="E72" s="42" t="inlineStr">
+        <is>
+          <t>How filler is priced here. Per syringe, quoted at your consult once we know the area and the amount, and half a syringe is priced as half. No package pressure and no product opened before you have agreed to the number.</t>
+        </is>
+      </c>
+      <c r="F72" s="41" t="n">
+        <v>218</v>
+      </c>
+      <c r="G72" s="42" t="inlineStr">
+        <is>
+          <t>Filler is priced per syringe, and you get the number before anything is opened.
+I do not post a price list, for the same reason I do not post one for Botox. The honest figure depends on the area, how much it actually needs and whether we are starting fresh or working alongside existing product, and a number posted without that context is either a lure or a guess.
+What you get instead: a quote at your consult, in writing, for the plan we agreed on. Half a syringe is priced as half.
+There are no packages to commit to and no pressure to book a series at the Oakville studio. If the plan is one syringe and a review, that is what you pay for. Ask at the consult and you will get a straight number.</t>
+        </is>
+      </c>
+      <c r="H72" s="41" t="n">
+        <v>702</v>
+      </c>
+      <c r="I72" s="41" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="J72" s="43" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="K72" s="41" t="inlineStr">
+        <is>
+          <t>2026-10-28-priced-by-the-syringe.jpg</t>
+        </is>
+      </c>
+      <c r="L72" s="43" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M72" s="43" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="N72" s="41">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-10-28-priced-by-the-syringe.jpg")</f>
+        <v/>
+      </c>
+      <c r="O72" s="43" t="inlineStr">
+        <is>
+          <t>Masum Rahimi / Unsplash</t>
+        </is>
+      </c>
+      <c r="P72" s="41" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="Q72" s="42" t="inlineStr"/>
+    </row>
+    <row r="73" ht="132" customHeight="1" s="14">
+      <c r="A73" s="51" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B73" s="45" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C73" s="45" t="inlineStr">
+        <is>
+          <t>IG: Facial Balancing: Why We Treat Faces, Not Lines</t>
+        </is>
+      </c>
+      <c r="D73" s="45" t="inlineStr">
+        <is>
+          <t>Trust &amp; Proof</t>
+        </is>
+      </c>
+      <c r="E73" s="46" t="inlineStr">
+        <is>
+          <t>Why I treat faces and not lines. Chasing each line as it appears is how people end up overfilled and still unhappy, because the line was a symptom of lost support somewhere else. Fix the structure and the line softens. On Instagram.</t>
+        </is>
+      </c>
+      <c r="F73" s="45" t="n">
+        <v>232</v>
+      </c>
+      <c r="G73" s="46" t="inlineStr">
+        <is>
+          <t>Treating lines one at a time is how faces end up overfilled.
+A line is usually a symptom. The fold at the side of the mouth is the clearest example, since most of the time it is not a lack of volume at the fold, it is a lack of support above it that let the tissue settle. Fill the fold directly and you get a heavy, obvious result that still does not look right, and you will be back to fill it again.
+Support the structure and the line softens on its own, using less product in a place you were not looking at.
+This is the difference between an assessment and an order form. At the Oakville studio the consult starts with your whole face regardless of which line brought you in. The full explanation is on Instagram.</t>
+        </is>
+      </c>
+      <c r="H73" s="45" t="n">
+        <v>721</v>
+      </c>
+      <c r="I73" s="45" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="J73" s="47" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="K73" s="45" t="inlineStr">
+        <is>
+          <t>2026-10-29-faces-not-lines.jpg</t>
+        </is>
+      </c>
+      <c r="L73" s="47" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M73" s="47" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="N73" s="45">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-10-29-faces-not-lines.jpg")</f>
+        <v/>
+      </c>
+      <c r="O73" s="47" t="inlineStr">
+        <is>
+          <t>Elist Nguyen / Unsplash</t>
+        </is>
+      </c>
+      <c r="P73" s="45" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="Q73" s="46" t="inlineStr"/>
+    </row>
+    <row r="74" ht="132" customHeight="1" s="14">
+      <c r="A74" s="51" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B74" s="45" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="C74" s="45" t="inlineStr">
+        <is>
+          <t>IG: One Syringe. Balanced Lips.</t>
+        </is>
+      </c>
+      <c r="D74" s="45" t="inlineStr">
+        <is>
+          <t>Trust &amp; Proof</t>
+        </is>
+      </c>
+      <c r="E74" s="46" t="inlineStr">
+        <is>
+          <t>One syringe, one appointment, photographed two weeks apart in the same light. The upper lip was short against the lower, so the work was ratio rather than volume. Shared with client consent on Instagram.</t>
+        </is>
+      </c>
+      <c r="F74" s="45" t="n">
+        <v>203</v>
+      </c>
+      <c r="G74" s="46" t="inlineStr">
+        <is>
+          <t>One syringe, one appointment, and the photos are two weeks apart in the same light.
+The brief was balance rather than size. Her upper lip sat short against the lower, which made the whole mouth read slightly downturned in photos, and it was bothering her more in pictures than in the mirror. The work was ratio: height in the upper lip, support at the corners, nothing added for the sake of volume.
+Same lighting, same angle, no filter and no smoothing on either frame.
+If you look at these and think the change is subtle, that is the correct reaction and the reason she is happy with it. Shared with her written consent, on Instagram. Lip filler consultations in Oakville are booked from there, and half syringes are a real option.</t>
+        </is>
+      </c>
+      <c r="H74" s="45" t="n">
+        <v>735</v>
+      </c>
+      <c r="I74" s="45" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="J74" s="47" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="K74" s="45" t="inlineStr">
+        <is>
+          <t>2026-10-30-one-syringe-balanced-lips.jpg</t>
+        </is>
+      </c>
+      <c r="L74" s="47" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M74" s="47" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="N74" s="45">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-10-30-one-syringe-balanced-lips.jpg")</f>
+        <v/>
+      </c>
+      <c r="O74" s="47" t="inlineStr">
+        <is>
+          <t>Vitaliy Shevchenko / Unsplash</t>
+        </is>
+      </c>
+      <c r="P74" s="45" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="Q74" s="46" t="inlineStr"/>
+    </row>
+    <row r="75" ht="132" customHeight="1" s="14">
+      <c r="A75" s="51" t="n">
+        <v>46326</v>
+      </c>
+      <c r="B75" s="45" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="C75" s="45" t="inlineStr">
+        <is>
+          <t>IG: Ask Anything: Filler Edition</t>
+        </is>
+      </c>
+      <c r="D75" s="45" t="inlineStr">
+        <is>
+          <t>Personality &amp; BTS</t>
+        </is>
+      </c>
+      <c r="E75" s="46" t="inlineStr">
+        <is>
+          <t>The question box is open all weekend, filler edition. Anonymous, and I answer the awkward ones first. Cost, pain, migration, dissolving, whether you are too young or too late. Ask on Instagram and I will answer this week.</t>
+        </is>
+      </c>
+      <c r="F75" s="45" t="n">
+        <v>221</v>
+      </c>
+      <c r="G75" s="46" t="inlineStr">
+        <is>
+          <t>The question box is open all weekend, filler edition. Ask me anything.
+It is anonymous, and I answer the awkward ones first because those are the ones stopping people from booking. Cost, pain, migration, dissolving, whether you are too young to start or too late to bother, what happens if you stop, what to do about work you had done somewhere else and do not like.
+October here has been a month about filler, and this is where it lands.
+Every answer goes up this week, and nothing gets skipped for being uncomfortable. If a question is better answered in person, I will say so rather than guessing at your face from a paragraph. Ask on Instagram, or book a consult at the Oakville studio and ask across the room.</t>
+        </is>
+      </c>
+      <c r="H75" s="45" t="n">
+        <v>717</v>
+      </c>
+      <c r="I75" s="45" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="J75" s="47" t="inlineStr">
+        <is>
+          <t>@luxury_beauty_aestheticz</t>
+        </is>
+      </c>
+      <c r="K75" s="45" t="inlineStr">
+        <is>
+          <t>2026-10-31-ask-anything-filler.jpg</t>
+        </is>
+      </c>
+      <c r="L75" s="47" t="inlineStr">
+        <is>
+          <t>Open folder</t>
+        </is>
+      </c>
+      <c r="M75" s="47" t="inlineStr">
+        <is>
+          <t>Open image</t>
+        </is>
+      </c>
+      <c r="N75" s="45">
+        <f>IMAGE("https://raw.githubusercontent.com/RepoKing23/InstagramCarousel/claude/med-spa-carousel-ideas-sim9wz/content/gbp/2026-10-31-ask-anything-filler.jpg")</f>
+        <v/>
+      </c>
+      <c r="O75" s="47" t="inlineStr">
+        <is>
+          <t>Alef Morais / Unsplash</t>
+        </is>
+      </c>
+      <c r="P75" s="45" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="Q75" s="46" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -11835,6 +14283,130 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId170"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M44" r:id="rId171"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M45" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O45" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J46" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O46" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M47" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M48" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L49" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M49" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J50" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L50" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M50" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O50" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J51" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L51" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M51" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O51" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J52" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L52" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M52" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O52" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J53" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L53" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M53" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O53" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J54" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L54" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M54" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O54" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J55" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L55" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M55" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O55" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J56" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L56" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M56" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O56" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J57" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L57" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M57" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O57" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J58" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L58" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M58" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O58" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J59" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L59" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M59" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O59" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J60" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L60" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M60" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O60" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J61" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L61" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M61" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O61" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J62" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L62" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M62" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O62" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J63" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L63" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M63" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O63" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J64" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L64" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M64" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O64" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J65" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L65" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M65" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O65" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J66" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L66" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M66" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O66" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J67" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L67" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M67" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O67" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J68" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L68" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M68" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O68" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J69" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L69" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M69" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O69" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J70" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L70" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M70" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O70" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J71" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L71" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M71" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O71" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J72" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L72" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M72" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O72" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J73" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L73" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M73" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O73" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J74" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L74" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M74" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O74" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J75" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L75" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M75" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O75" r:id="rId296"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
